--- a/tests/e2e/testcases.xlsx
+++ b/tests/e2e/testcases.xlsx
@@ -3054,8 +3054,8 @@
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rDISK_write_overload --device=/data（不带 workers/size_mb）
-2. 检查 /data 下临时文件与 dd 进程数</t>
+          <t>1. 执行 dcat inject rDISK_write_overload --device=/tmp（不带 workers/size_mb）
+2. 检查 /tmp 下临时文件与 dd 进程数</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -33566,7 +33566,7 @@
       </c>
       <c r="K565" s="3" t="inlineStr">
         <is>
-          <t>exitcode:1</t>
+          <t>exitcode:0</t>
         </is>
       </c>
     </row>
@@ -33683,7 +33683,7 @@
       </c>
       <c r="K567" s="3" t="inlineStr">
         <is>
-          <t>exitcode:1</t>
+          <t>exitcode:0</t>
         </is>
       </c>
     </row>
@@ -34655,7 +34655,7 @@
       </c>
       <c r="K584" s="3" t="inlineStr">
         <is>
-          <t>exitcode:2</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>
@@ -34945,7 +34945,7 @@
       </c>
       <c r="K589" s="3" t="inlineStr">
         <is>
-          <t>state_contains:&lt;uid&gt;</t>
+          <t>exitcode:3</t>
         </is>
       </c>
     </row>
@@ -36014,7 +36014,7 @@
       </c>
       <c r="D608" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rDISK_write_overload --device=/data --workers=4 --size_mb=200
+          <t>1. dcat inject rDISK_write_overload --device=/tmp --workers=4 --size_mb=200
 2. pgrep -f 'dd if=/dev/zero' | wc -l</t>
         </is>
       </c>

--- a/tests/e2e/testcases.xlsx
+++ b/tests/e2e/testcases.xlsx
@@ -13645,7 +13645,7 @@
       </c>
       <c r="K225" s="3" t="inlineStr">
         <is>
-          <t>exitcode:1</t>
+          <t>exitcode:0</t>
         </is>
       </c>
     </row>
@@ -33029,7 +33029,7 @@
       </c>
       <c r="K556" s="3" t="inlineStr">
         <is>
-          <t>exitcode:1</t>
+          <t>exitcode:124</t>
         </is>
       </c>
     </row>
@@ -34166,7 +34166,7 @@
       </c>
       <c r="D576" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat list --config /tmp/test-demoncat.conf
+          <t>1. 执行 dcat list --config config/demoncat.conf
 2. 检查 list 输出</t>
         </is>
       </c>
@@ -34483,7 +34483,7 @@
       </c>
       <c r="K581" s="3" t="inlineStr">
         <is>
-          <t>exitcode:1</t>
+          <t>exitcode:0</t>
         </is>
       </c>
     </row>

--- a/tests/e2e/testcases.xlsx
+++ b/tests/e2e/testcases.xlsx
@@ -17749,7 +17749,7 @@
       </c>
       <c r="D296" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_bw_limit --chip=0 --bw_limit=1000 --force</t>
+          <t>1. dcat inject rNPU_bw_limit --chip=2 --bw_limit=1000 --force</t>
         </is>
       </c>
       <c r="E296" s="3" t="inlineStr">
@@ -17808,9 +17808,9 @@
       </c>
       <c r="D297" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rNPU_bw_limit --chip=0 --bw_limit=1000
-2. 执行 dcat query rNPU_bw_limit --chip=0
-3. 执行 dcat clean rNPU_bw_limit --chip=0</t>
+          <t>1. 执行 dcat inject rNPU_bw_limit --chip=2 --bw_limit=1000
+2. 执行 dcat query rNPU_bw_limit --chip=2
+3. 执行 dcat clean rNPU_bw_limit --chip=2</t>
         </is>
       </c>
       <c r="E297" s="3" t="inlineStr">
@@ -17869,7 +17869,7 @@
       </c>
       <c r="D298" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rNPU_bw_limit --chip=0 --bw_limit=0
+          <t>1. 执行 dcat inject rNPU_bw_limit --chip=2 --bw_limit=0
 2. 执行 --bw_limit=-1 / --bw_limit=abc</t>
         </is>
       </c>
@@ -17928,7 +17928,7 @@
       </c>
       <c r="D299" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_bw_limit --chip=0 --bw_limit=-1</t>
+          <t>1. dcat inject rNPU_bw_limit --chip=2 --bw_limit=-1</t>
         </is>
       </c>
       <c r="E299" s="3" t="inlineStr">
@@ -17985,7 +17985,7 @@
       </c>
       <c r="D300" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_bw_limit --chip=0 --bw_limit=0</t>
+          <t>1. dcat inject rNPU_bw_limit --chip=2 --bw_limit=0</t>
         </is>
       </c>
       <c r="E300" s="3" t="inlineStr">
@@ -18042,7 +18042,7 @@
       </c>
       <c r="D301" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_bw_limit --chip=0 --bw_limit=abc</t>
+          <t>1. dcat inject rNPU_bw_limit --chip=2 --bw_limit=abc</t>
         </is>
       </c>
       <c r="E301" s="3" t="inlineStr">
@@ -18099,7 +18099,7 @@
       </c>
       <c r="D302" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_bw_limit --chip=0 --bw_limit=1000
+          <t>1. dcat clean rNPU_bw_limit --chip=2 --bw_limit=1000
 2. dcat query（无 uid）</t>
         </is>
       </c>
@@ -18158,7 +18158,7 @@
       </c>
       <c r="D303" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_bw_limit --chip=0 --bw_limit=1000
+          <t>1. dcat clean rNPU_bw_limit --chip=2 --bw_limit=1000
 2. 检查恢复状态</t>
         </is>
       </c>
@@ -18275,7 +18275,7 @@
       </c>
       <c r="D305" s="3" t="inlineStr">
         <is>
-          <t>1. dcat query rNPU_bw_limit --chip=0 --bw_limit=1000</t>
+          <t>1. dcat query rNPU_bw_limit --chip=2 --bw_limit=1000</t>
         </is>
       </c>
       <c r="E305" s="3" t="inlineStr">
@@ -18333,8 +18333,8 @@
       </c>
       <c r="D306" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_bw_limit --chip=0 --bw_limit=1000
-2. 再次 dcat inject rNPU_bw_limit --chip=0 --bw_limit=1000</t>
+          <t>1. dcat inject rNPU_bw_limit --chip=2 --bw_limit=1000
+2. 再次 dcat inject rNPU_bw_limit --chip=2 --bw_limit=1000</t>
         </is>
       </c>
       <c r="E306" s="3" t="inlineStr">
@@ -18450,7 +18450,7 @@
       </c>
       <c r="D308" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_bw_limit --chip=0 --bw_limit=1000
+          <t>1. dcat inject rNPU_bw_limit --chip=2 --bw_limit=1000
 2. 检查注入状态</t>
         </is>
       </c>
@@ -18509,9 +18509,9 @@
       </c>
       <c r="D309" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_bw_limit --chip=0 --bw_limit=1000
+          <t>1. dcat inject rNPU_bw_limit --chip=2 --bw_limit=1000
 2. dcat query rNPU_bw_limit
-3. dcat clean rNPU_bw_limit --chip=0 --bw_limit=1000
+3. dcat clean rNPU_bw_limit --chip=2 --bw_limit=1000
 4. dcat query rNPU_bw_limit</t>
         </is>
       </c>
@@ -18572,8 +18572,8 @@
       </c>
       <c r="D310" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_bw_limit --chip=0 --bw_limit=1000
-2. 再次 dcat clean rNPU_bw_limit --chip=0 --bw_limit=1000</t>
+          <t>1. dcat clean rNPU_bw_limit --chip=2 --bw_limit=1000
+2. 再次 dcat clean rNPU_bw_limit --chip=2 --bw_limit=1000</t>
         </is>
       </c>
       <c r="E310" s="3" t="inlineStr">
@@ -18631,7 +18631,7 @@
       </c>
       <c r="D311" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_dscp_tc_change --chip=0 --dscp=46 --tc=0 --force</t>
+          <t>1. dcat inject rNPU_dscp_tc_change --chip=2 --dscp=46 --tc=0 --force</t>
         </is>
       </c>
       <c r="E311" s="3" t="inlineStr">
@@ -18690,9 +18690,9 @@
       </c>
       <c r="D312" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rNPU_dscp_tc_change --chip=0 --dscp=46 --tc=0
-2. 执行 dcat query rNPU_dscp_tc_change --chip=0 --dscp=46
-3. 执行 dcat clean rNPU_dscp_tc_change --chip=0 --dscp=46 --tc=0</t>
+          <t>1. 执行 dcat inject rNPU_dscp_tc_change --chip=2 --dscp=46 --tc=0
+2. 执行 dcat query rNPU_dscp_tc_change --chip=2 --dscp=46
+3. 执行 dcat clean rNPU_dscp_tc_change --chip=2 --dscp=46 --tc=0</t>
         </is>
       </c>
       <c r="E312" s="3" t="inlineStr">
@@ -18865,7 +18865,7 @@
       </c>
       <c r="D315" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_dscp_tc_change --chip=0 --dscp=46 --tc=0
+          <t>1. dcat clean rNPU_dscp_tc_change --chip=2 --dscp=46 --tc=0
 2. dcat query（无 uid）</t>
         </is>
       </c>
@@ -18924,7 +18924,7 @@
       </c>
       <c r="D316" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_dscp_tc_change --chip=0 --dscp=46 --tc=0
+          <t>1. dcat clean rNPU_dscp_tc_change --chip=2 --dscp=46 --tc=0
 2. 检查恢复状态</t>
         </is>
       </c>
@@ -18983,7 +18983,7 @@
       </c>
       <c r="D317" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_dscp_tc_change --chip=0 --dscp=-1 --tc=0</t>
+          <t>1. dcat inject rNPU_dscp_tc_change --chip=2 --dscp=-1 --tc=0</t>
         </is>
       </c>
       <c r="E317" s="3" t="inlineStr">
@@ -19040,7 +19040,7 @@
       </c>
       <c r="D318" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_dscp_tc_change --chip=0 --dscp=-1 --tc=0</t>
+          <t>1. dcat inject rNPU_dscp_tc_change --chip=2 --dscp=-1 --tc=0</t>
         </is>
       </c>
       <c r="E318" s="3" t="inlineStr">
@@ -19097,7 +19097,7 @@
       </c>
       <c r="D319" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_dscp_tc_change --chip=0 --dscp=0 --tc=0</t>
+          <t>1. dcat inject rNPU_dscp_tc_change --chip=2 --dscp=0 --tc=0</t>
         </is>
       </c>
       <c r="E319" s="3" t="inlineStr">
@@ -19154,7 +19154,7 @@
       </c>
       <c r="D320" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_dscp_tc_change --chip=0 --dscp=63 --tc=0</t>
+          <t>1. dcat inject rNPU_dscp_tc_change --chip=2 --dscp=63 --tc=0</t>
         </is>
       </c>
       <c r="E320" s="3" t="inlineStr">
@@ -19211,7 +19211,7 @@
       </c>
       <c r="D321" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_dscp_tc_change --chip=0 --dscp=64 --tc=0</t>
+          <t>1. dcat inject rNPU_dscp_tc_change --chip=2 --dscp=64 --tc=0</t>
         </is>
       </c>
       <c r="E321" s="3" t="inlineStr">
@@ -19326,7 +19326,7 @@
       </c>
       <c r="D323" s="3" t="inlineStr">
         <is>
-          <t>1. dcat query rNPU_dscp_tc_change --chip=0 --dscp=46 --tc=0</t>
+          <t>1. dcat query rNPU_dscp_tc_change --chip=2 --dscp=46 --tc=0</t>
         </is>
       </c>
       <c r="E323" s="3" t="inlineStr">
@@ -19384,7 +19384,7 @@
       </c>
       <c r="D324" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_dscp_tc_change --chip=0 --dscp=46 --tc=-1</t>
+          <t>1. dcat inject rNPU_dscp_tc_change --chip=2 --dscp=46 --tc=-1</t>
         </is>
       </c>
       <c r="E324" s="3" t="inlineStr">
@@ -19441,7 +19441,7 @@
       </c>
       <c r="D325" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_dscp_tc_change --chip=0 --dscp=46 --tc=0</t>
+          <t>1. dcat inject rNPU_dscp_tc_change --chip=2 --dscp=46 --tc=0</t>
         </is>
       </c>
       <c r="E325" s="3" t="inlineStr">
@@ -19498,7 +19498,7 @@
       </c>
       <c r="D326" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_dscp_tc_change --chip=0 --dscp=46 --tc=7</t>
+          <t>1. dcat inject rNPU_dscp_tc_change --chip=2 --dscp=46 --tc=7</t>
         </is>
       </c>
       <c r="E326" s="3" t="inlineStr">
@@ -19555,7 +19555,7 @@
       </c>
       <c r="D327" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_dscp_tc_change --chip=0 --dscp=46 --tc=8</t>
+          <t>1. dcat inject rNPU_dscp_tc_change --chip=2 --dscp=46 --tc=8</t>
         </is>
       </c>
       <c r="E327" s="3" t="inlineStr">
@@ -19612,8 +19612,8 @@
       </c>
       <c r="D328" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_dscp_tc_change --chip=0 --dscp=46 --tc=0
-2. 再次 dcat inject rNPU_dscp_tc_change --chip=0 --dscp=46 --tc=0</t>
+          <t>1. dcat inject rNPU_dscp_tc_change --chip=2 --dscp=46 --tc=0
+2. 再次 dcat inject rNPU_dscp_tc_change --chip=2 --dscp=46 --tc=0</t>
         </is>
       </c>
       <c r="E328" s="3" t="inlineStr">
@@ -19729,7 +19729,7 @@
       </c>
       <c r="D330" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_dscp_tc_change --chip=0 --dscp=46 --tc=0
+          <t>1. dcat inject rNPU_dscp_tc_change --chip=2 --dscp=46 --tc=0
 2. 检查注入状态</t>
         </is>
       </c>
@@ -19788,9 +19788,9 @@
       </c>
       <c r="D331" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_dscp_tc_change --chip=0 --dscp=46 --tc=0
+          <t>1. dcat inject rNPU_dscp_tc_change --chip=2 --dscp=46 --tc=0
 2. dcat query rNPU_dscp_tc_change
-3. dcat clean rNPU_dscp_tc_change --chip=0 --dscp=46 --tc=0
+3. dcat clean rNPU_dscp_tc_change --chip=2 --dscp=46 --tc=0
 4. dcat query rNPU_dscp_tc_change</t>
         </is>
       </c>
@@ -19851,8 +19851,8 @@
       </c>
       <c r="D332" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_dscp_tc_change --chip=0 --dscp=46 --tc=0
-2. 再次 dcat clean rNPU_dscp_tc_change --chip=0 --dscp=46 --tc=0</t>
+          <t>1. dcat clean rNPU_dscp_tc_change --chip=2 --dscp=46 --tc=0
+2. 再次 dcat clean rNPU_dscp_tc_change --chip=2 --dscp=46 --tc=0</t>
         </is>
       </c>
       <c r="E332" s="3" t="inlineStr">
@@ -20029,7 +20029,7 @@
       </c>
       <c r="D335" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rNPU_gw_change --chip=0 --gateway=&lt;同网段≠当前值&gt;</t>
+          <t>1. 执行 dcat inject rNPU_gw_change --chip=2 --gateway=&lt;同网段≠当前值&gt;</t>
         </is>
       </c>
       <c r="E335" s="3" t="inlineStr">
@@ -20433,7 +20433,7 @@
       </c>
       <c r="D342" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rNPU_gw_change --chip=0 --gateway=&lt;任意&gt;
+          <t>1. 执行 dcat inject rNPU_gw_change --chip=2 --gateway=&lt;任意&gt;
 2. 检查返回</t>
         </is>
       </c>
@@ -21132,7 +21132,7 @@
       </c>
       <c r="D354" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_ip_change --chip=0 --address=192.168.1.100 --netmask=255.255.255.0 --force</t>
+          <t>1. dcat inject rNPU_ip_change --chip=2 --address=192.168.1.100 --netmask=255.255.255.0 --force</t>
         </is>
       </c>
       <c r="E354" s="3" t="inlineStr">
@@ -21191,9 +21191,9 @@
       </c>
       <c r="D355" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rNPU_ip_change --chip=0 --address=192.168.1.100 --netmask=255.255.255.0
-2. 执行 dcat query rNPU_ip_change --chip=0
-3. 执行 dcat clean rNPU_ip_change --chip=0
+          <t>1. 执行 dcat inject rNPU_ip_change --chip=2 --address=192.168.1.100 --netmask=255.255.255.0
+2. 执行 dcat query rNPU_ip_change --chip=2
+3. 执行 dcat clean rNPU_ip_change --chip=2
 4. 模拟 sidecar 丢失后 clean 验证缺省值</t>
         </is>
       </c>
@@ -21254,7 +21254,7 @@
       </c>
       <c r="D356" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_ip_change --chip=0 --address=invalid --netmask=255.255.255.0</t>
+          <t>1. dcat inject rNPU_ip_change --chip=2 --address=invalid --netmask=255.255.255.0</t>
         </is>
       </c>
       <c r="E356" s="3" t="inlineStr">
@@ -21425,7 +21425,7 @@
       </c>
       <c r="D359" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_ip_change --chip=0 --address=192.168.1.100 --netmask=255.255.255.0
+          <t>1. dcat clean rNPU_ip_change --chip=2 --address=192.168.1.100 --netmask=255.255.255.0
 2. dcat query（无 uid）</t>
         </is>
       </c>
@@ -21484,7 +21484,7 @@
       </c>
       <c r="D360" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_ip_change --chip=0 --address=192.168.1.100 --netmask=255.255.255.0
+          <t>1. dcat clean rNPU_ip_change --chip=2 --address=192.168.1.100 --netmask=255.255.255.0
 2. 检查恢复状态</t>
         </is>
       </c>
@@ -21601,7 +21601,7 @@
       </c>
       <c r="D362" s="3" t="inlineStr">
         <is>
-          <t>1. dcat query rNPU_ip_change --chip=0 --address=192.168.1.100 --netmask=255.255.255.0</t>
+          <t>1. dcat query rNPU_ip_change --chip=2 --address=192.168.1.100 --netmask=255.255.255.0</t>
         </is>
       </c>
       <c r="E362" s="3" t="inlineStr">
@@ -21659,8 +21659,8 @@
       </c>
       <c r="D363" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_ip_change --chip=0 --address=192.168.1.100 --netmask=255.255.255.0
-2. 再次 dcat inject rNPU_ip_change --chip=0 --address=192.168.1.100 --netmask=255.255.255.0</t>
+          <t>1. dcat inject rNPU_ip_change --chip=2 --address=192.168.1.100 --netmask=255.255.255.0
+2. 再次 dcat inject rNPU_ip_change --chip=2 --address=192.168.1.100 --netmask=255.255.255.0</t>
         </is>
       </c>
       <c r="E363" s="3" t="inlineStr">
@@ -21776,7 +21776,7 @@
       </c>
       <c r="D365" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_ip_change --chip=0 --address=192.168.1.100 --netmask=255.255.255.0
+          <t>1. dcat inject rNPU_ip_change --chip=2 --address=192.168.1.100 --netmask=255.255.255.0
 2. 检查注入状态</t>
         </is>
       </c>
@@ -21835,9 +21835,9 @@
       </c>
       <c r="D366" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_ip_change --chip=0 --address=192.168.1.100 --netmask=255.255.255.0
+          <t>1. dcat inject rNPU_ip_change --chip=2 --address=192.168.1.100 --netmask=255.255.255.0
 2. dcat query rNPU_ip_change
-3. dcat clean rNPU_ip_change --chip=0 --address=192.168.1.100 --netmask=255.255.255.0
+3. dcat clean rNPU_ip_change --chip=2 --address=192.168.1.100 --netmask=255.255.255.0
 4. dcat query rNPU_ip_change</t>
         </is>
       </c>
@@ -21898,8 +21898,8 @@
       </c>
       <c r="D367" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_ip_change --chip=0 --address=192.168.1.100 --netmask=255.255.255.0
-2. 再次 dcat clean rNPU_ip_change --chip=0 --address=192.168.1.100 --netmask=255.255.255.0</t>
+          <t>1. dcat clean rNPU_ip_change --chip=2 --address=192.168.1.100 --netmask=255.255.255.0
+2. 再次 dcat clean rNPU_ip_change --chip=2 --address=192.168.1.100 --netmask=255.255.255.0</t>
         </is>
       </c>
       <c r="E367" s="3" t="inlineStr">
@@ -25705,7 +25705,7 @@
       </c>
       <c r="D432" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_link_down --chip=0 --force</t>
+          <t>1. dcat inject rNPU_link_down --chip=2 --force</t>
         </is>
       </c>
       <c r="E432" s="3" t="inlineStr">
@@ -25764,9 +25764,9 @@
       </c>
       <c r="D433" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rNPU_link_down --chip=0
-2. 执行 dcat query rNPU_link_down --chip=0
-3. 执行 dcat clean rNPU_link_down --chip=0</t>
+          <t>1. 执行 dcat inject rNPU_link_down --chip=2
+2. 执行 dcat query rNPU_link_down --chip=2
+3. 执行 dcat clean rNPU_link_down --chip=2</t>
         </is>
       </c>
       <c r="E433" s="3" t="inlineStr">
@@ -25996,7 +25996,7 @@
       </c>
       <c r="D437" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_link_down --chip=0
+          <t>1. dcat clean rNPU_link_down --chip=2
 2. dcat query（无 uid）</t>
         </is>
       </c>
@@ -26055,7 +26055,7 @@
       </c>
       <c r="D438" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_link_down --chip=0
+          <t>1. dcat clean rNPU_link_down --chip=2
 2. 检查恢复状态</t>
         </is>
       </c>
@@ -26172,7 +26172,7 @@
       </c>
       <c r="D440" s="3" t="inlineStr">
         <is>
-          <t>1. dcat query rNPU_link_down --chip=0</t>
+          <t>1. dcat query rNPU_link_down --chip=2</t>
         </is>
       </c>
       <c r="E440" s="3" t="inlineStr">
@@ -26230,8 +26230,8 @@
       </c>
       <c r="D441" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_link_down --chip=0
-2. 再次 dcat inject rNPU_link_down --chip=0</t>
+          <t>1. dcat inject rNPU_link_down --chip=2
+2. 再次 dcat inject rNPU_link_down --chip=2</t>
         </is>
       </c>
       <c r="E441" s="3" t="inlineStr">
@@ -26347,7 +26347,7 @@
       </c>
       <c r="D443" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_link_down --chip=0
+          <t>1. dcat inject rNPU_link_down --chip=2
 2. 检查注入状态</t>
         </is>
       </c>
@@ -26406,9 +26406,9 @@
       </c>
       <c r="D444" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_link_down --chip=0
+          <t>1. dcat inject rNPU_link_down --chip=2
 2. dcat query rNPU_link_down
-3. dcat clean rNPU_link_down --chip=0
+3. dcat clean rNPU_link_down --chip=2
 4. dcat query rNPU_link_down</t>
         </is>
       </c>
@@ -26469,8 +26469,8 @@
       </c>
       <c r="D445" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_link_down --chip=0
-2. 再次 dcat clean rNPU_link_down --chip=0</t>
+          <t>1. dcat clean rNPU_link_down --chip=2
+2. 再次 dcat clean rNPU_link_down --chip=2</t>
         </is>
       </c>
       <c r="E445" s="3" t="inlineStr">
@@ -26884,7 +26884,7 @@
       </c>
       <c r="D452" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rNPU_mtu_mismatch --chip=0 --size=0
+          <t>1. 执行 dcat inject rNPU_mtu_mismatch --chip=2 --size=0
 2. 执行 --size=-1 / --size=abc</t>
         </is>
       </c>
@@ -27412,7 +27412,7 @@
       </c>
       <c r="D461" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_netdetect_change --chip=0 --address=10.0.0.99 --force</t>
+          <t>1. dcat inject rNPU_netdetect_change --chip=2 --address=10.0.0.99 --force</t>
         </is>
       </c>
       <c r="E461" s="3" t="inlineStr">
@@ -27471,9 +27471,9 @@
       </c>
       <c r="D462" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rNPU_netdetect_change --chip=0 --address=10.0.0.99
-2. 执行 dcat query rNPU_netdetect_change --chip=0
-3. 执行 dcat clean rNPU_netdetect_change --chip=0</t>
+          <t>1. 执行 dcat inject rNPU_netdetect_change --chip=2 --address=10.0.0.99
+2. 执行 dcat query rNPU_netdetect_change --chip=2
+3. 执行 dcat clean rNPU_netdetect_change --chip=2</t>
         </is>
       </c>
       <c r="E462" s="3" t="inlineStr">
@@ -27532,7 +27532,7 @@
       </c>
       <c r="D463" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_netdetect_change --chip=0 --address=invalid</t>
+          <t>1. dcat inject rNPU_netdetect_change --chip=2 --address=invalid</t>
         </is>
       </c>
       <c r="E463" s="3" t="inlineStr">
@@ -27703,7 +27703,7 @@
       </c>
       <c r="D466" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_netdetect_change --chip=0 --address=10.0.0.99
+          <t>1. dcat clean rNPU_netdetect_change --chip=2 --address=10.0.0.99
 2. dcat query（无 uid）</t>
         </is>
       </c>
@@ -27762,7 +27762,7 @@
       </c>
       <c r="D467" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_netdetect_change --chip=0 --address=10.0.0.99
+          <t>1. dcat clean rNPU_netdetect_change --chip=2 --address=10.0.0.99
 2. 检查恢复状态</t>
         </is>
       </c>
@@ -27879,7 +27879,7 @@
       </c>
       <c r="D469" s="3" t="inlineStr">
         <is>
-          <t>1. dcat query rNPU_netdetect_change --chip=0 --address=10.0.0.99</t>
+          <t>1. dcat query rNPU_netdetect_change --chip=2 --address=10.0.0.99</t>
         </is>
       </c>
       <c r="E469" s="3" t="inlineStr">
@@ -27937,8 +27937,8 @@
       </c>
       <c r="D470" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_netdetect_change --chip=0 --address=10.0.0.99
-2. 再次 dcat inject rNPU_netdetect_change --chip=0 --address=10.0.0.99</t>
+          <t>1. dcat inject rNPU_netdetect_change --chip=2 --address=10.0.0.99
+2. 再次 dcat inject rNPU_netdetect_change --chip=2 --address=10.0.0.99</t>
         </is>
       </c>
       <c r="E470" s="3" t="inlineStr">
@@ -28054,7 +28054,7 @@
       </c>
       <c r="D472" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_netdetect_change --chip=0 --address=10.0.0.99
+          <t>1. dcat inject rNPU_netdetect_change --chip=2 --address=10.0.0.99
 2. 检查注入状态</t>
         </is>
       </c>
@@ -28113,9 +28113,9 @@
       </c>
       <c r="D473" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_netdetect_change --chip=0 --address=10.0.0.99
+          <t>1. dcat inject rNPU_netdetect_change --chip=2 --address=10.0.0.99
 2. dcat query rNPU_netdetect_change
-3. dcat clean rNPU_netdetect_change --chip=0 --address=10.0.0.99
+3. dcat clean rNPU_netdetect_change --chip=2 --address=10.0.0.99
 4. dcat query rNPU_netdetect_change</t>
         </is>
       </c>
@@ -28176,8 +28176,8 @@
       </c>
       <c r="D474" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_netdetect_change --chip=0 --address=10.0.0.99
-2. 再次 dcat clean rNPU_netdetect_change --chip=0 --address=10.0.0.99</t>
+          <t>1. dcat clean rNPU_netdetect_change --chip=2 --address=10.0.0.99
+2. 再次 dcat clean rNPU_netdetect_change --chip=2 --address=10.0.0.99</t>
         </is>
       </c>
       <c r="E474" s="3" t="inlineStr">
@@ -28235,7 +28235,7 @@
       </c>
       <c r="D475" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_roce_port_change --chip=0 --port=4792 --force</t>
+          <t>1. dcat inject rNPU_roce_port_change --chip=2 --port=4792 --force</t>
         </is>
       </c>
       <c r="E475" s="3" t="inlineStr">
@@ -28294,9 +28294,9 @@
       </c>
       <c r="D476" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rNPU_roce_port_change --chip=0 --port=4792
-2. 执行 dcat query rNPU_roce_port_change --chip=0
-3. 执行 dcat clean rNPU_roce_port_change --chip=0</t>
+          <t>1. 执行 dcat inject rNPU_roce_port_change --chip=2 --port=4792
+2. 执行 dcat query rNPU_roce_port_change --chip=2
+3. 执行 dcat clean rNPU_roce_port_change --chip=2</t>
         </is>
       </c>
       <c r="E476" s="3" t="inlineStr">
@@ -28355,7 +28355,7 @@
       </c>
       <c r="D477" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_roce_port_change --chip=0 --port=4792
+          <t>1. dcat clean rNPU_roce_port_change --chip=2 --port=4792
 2. dcat query（无 uid）</t>
         </is>
       </c>
@@ -28414,7 +28414,7 @@
       </c>
       <c r="D478" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_roce_port_change --chip=0 --port=4792
+          <t>1. dcat clean rNPU_roce_port_change --chip=2 --port=4792
 2. 检查恢复状态</t>
         </is>
       </c>
@@ -28473,7 +28473,7 @@
       </c>
       <c r="D479" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_roce_port_change --chip=0 --port=-1</t>
+          <t>1. dcat inject rNPU_roce_port_change --chip=2 --port=-1</t>
         </is>
       </c>
       <c r="E479" s="3" t="inlineStr">
@@ -28530,7 +28530,7 @@
       </c>
       <c r="D480" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_roce_port_change --chip=0 --port=0</t>
+          <t>1. dcat inject rNPU_roce_port_change --chip=2 --port=0</t>
         </is>
       </c>
       <c r="E480" s="3" t="inlineStr">
@@ -28587,7 +28587,7 @@
       </c>
       <c r="D481" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_roce_port_change --chip=0 --port=65536</t>
+          <t>1. dcat inject rNPU_roce_port_change --chip=2 --port=65536</t>
         </is>
       </c>
       <c r="E481" s="3" t="inlineStr">
@@ -28702,7 +28702,7 @@
       </c>
       <c r="D483" s="3" t="inlineStr">
         <is>
-          <t>1. dcat query rNPU_roce_port_change --chip=0 --port=4792</t>
+          <t>1. dcat query rNPU_roce_port_change --chip=2 --port=4792</t>
         </is>
       </c>
       <c r="E483" s="3" t="inlineStr">
@@ -28760,8 +28760,8 @@
       </c>
       <c r="D484" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_roce_port_change --chip=0 --port=4792
-2. 再次 dcat inject rNPU_roce_port_change --chip=0 --port=4792</t>
+          <t>1. dcat inject rNPU_roce_port_change --chip=2 --port=4792
+2. 再次 dcat inject rNPU_roce_port_change --chip=2 --port=4792</t>
         </is>
       </c>
       <c r="E484" s="3" t="inlineStr">
@@ -28877,7 +28877,7 @@
       </c>
       <c r="D486" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_roce_port_change --chip=0 --port=4792
+          <t>1. dcat inject rNPU_roce_port_change --chip=2 --port=4792
 2. 检查注入状态</t>
         </is>
       </c>
@@ -28936,9 +28936,9 @@
       </c>
       <c r="D487" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_roce_port_change --chip=0 --port=4792
+          <t>1. dcat inject rNPU_roce_port_change --chip=2 --port=4792
 2. dcat query rNPU_roce_port_change
-3. dcat clean rNPU_roce_port_change --chip=0 --port=4792
+3. dcat clean rNPU_roce_port_change --chip=2 --port=4792
 4. dcat query rNPU_roce_port_change</t>
         </is>
       </c>
@@ -28999,8 +28999,8 @@
       </c>
       <c r="D488" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_roce_port_change --chip=0 --port=4792
-2. 再次 dcat clean rNPU_roce_port_change --chip=0 --port=4792</t>
+          <t>1. dcat clean rNPU_roce_port_change --chip=2 --port=4792
+2. 再次 dcat clean rNPU_roce_port_change --chip=2 --port=4792</t>
         </is>
       </c>
       <c r="E488" s="3" t="inlineStr">
@@ -33914,7 +33914,7 @@
       </c>
       <c r="K571" s="3" t="inlineStr">
         <is>
-          <t>exitcode:1</t>
+          <t>exitcode:0</t>
         </is>
       </c>
     </row>
@@ -37009,7 +37009,7 @@
       </c>
       <c r="D625" s="3" t="inlineStr">
         <is>
-          <t>1. dcat query rNPU_link_down --chip=0</t>
+          <t>1. dcat query rNPU_link_down --chip=2</t>
         </is>
       </c>
       <c r="E625" s="3" t="inlineStr">
@@ -37067,7 +37067,7 @@
       </c>
       <c r="D626" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_link_down --chip=0
+          <t>1. dcat clean rNPU_link_down --chip=2
 2. hccn_tool -i 0 -link -g</t>
         </is>
       </c>
@@ -37126,7 +37126,7 @@
       </c>
       <c r="D627" s="3" t="inlineStr">
         <is>
-          <t>1. dcat query rNPU_ip_change --chip=0 --address=192.168.1.100 --netmask=255.255.255.0</t>
+          <t>1. dcat query rNPU_ip_change --chip=2 --address=192.168.1.100 --netmask=255.255.255.0</t>
         </is>
       </c>
       <c r="E627" s="3" t="inlineStr">
@@ -37184,7 +37184,7 @@
       </c>
       <c r="D628" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_ip_change --chip=0 --address=192.168.1.100 --netmask=255.255.255.0
+          <t>1. dcat clean rNPU_ip_change --chip=2 --address=192.168.1.100 --netmask=255.255.255.0
 2. hccn_tool -i 0 -ip -g</t>
         </is>
       </c>

--- a/tests/e2e/testcases.xlsx
+++ b/tests/e2e/testcases.xlsx
@@ -676,7 +676,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>exitcode:1</t>
+          <t>exitcode:0</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>exitcode:1</t>
+          <t>exitcode:0</t>
         </is>
       </c>
     </row>
@@ -1395,7 +1395,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>已注入 cores=2,3</t>
+          <t>root+sysfs_writable，已注入 cores=2,3</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>cat /sys/devices/system/cpu/cpu1/online 2&gt;/dev/null || echo NA</t>
+          <t>cat /sys/devices/system/cpu/cpu2/online 2&gt;/dev/null || echo NA</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>cat /sys/devices/system/cpu/cpu1/online 2&gt;/dev/null || echo NA</t>
+          <t>cat /sys/devices/system/cpu/cpu2/online 2&gt;/dev/null || echo NA</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>已注入 cores=2,3</t>
+          <t>root+sysfs_writable，已注入 cores=2,3</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -2588,14 +2588,13 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>rDISK_write_overload 已声明 inject_required=device</t>
+          <t>/tmp 可写</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rDISK_write_overload --device=/data（目录）
-2. 执行 dcat inject rDISK_write_overload --device=/dev/sdb1（非目录）
-3. 分别检查临时文件路径</t>
+          <t>1. 执行 dcat inject rDISK_write_overload --device=/tmp（目录）
+2. 分别检查临时文件路径</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -2763,12 +2762,12 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>/data 可写</t>
+          <t>/tmp 可写</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rDISK_write_overload --device=/data --size_mb=1</t>
+          <t>1. dcat inject rDISK_write_overload --device=/tmp --size_mb=1</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -2934,12 +2933,12 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>可写目录 /data</t>
+          <t>可写目录 /tmp</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rDISK_write_overload --device=/data --workers=1</t>
+          <t>1. dcat inject rDISK_write_overload --device=/tmp --workers=1</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
@@ -3397,7 +3396,7 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNET_bw_limit</t>
+          <t>root，tc_qdisc，已注入 rNET_bw_limit --iface={iface}</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
@@ -3455,12 +3454,12 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNET_bw_limit</t>
+          <t>root，tc_qdisc，已注入 rNET_bw_limit --iface={iface}</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>1. dcat query rNET_bw_limit --iface=eth0 --rate_kbps=1024</t>
+          <t>1. dcat query rNET_bw_limit --iface={iface} --rate_kbps=1024</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
@@ -3741,12 +3740,12 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>eth0 无 root qdisc</t>
+          <t>root，tc_qdisc，{iface} 无 root qdisc</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNET_bw_limit --iface=eth0 --rate_kbps=1</t>
+          <t>1. dcat inject rNET_bw_limit --iface={iface} --rate_kbps=1</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
@@ -3799,12 +3798,12 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>eth0 无 root qdisc</t>
+          <t>root，tc_qdisc，{iface} 无 root qdisc</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNET_bw_limit --iface=eth0 --rate_kbps=100000</t>
+          <t>1. dcat inject rNET_bw_limit --iface={iface} --rate_kbps=100000</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
@@ -3970,13 +3969,13 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNET_bw_limit</t>
+          <t>root，tc_qdisc，已注入 rNET_bw_limit --iface={iface}</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNET_bw_limit --iface=eth0 --rate_kbps=1024
-2. 再次 dcat inject rNET_bw_limit --iface=eth0 --rate_kbps=1024</t>
+          <t>1. dcat inject rNET_bw_limit --iface={iface} --rate_kbps=1024
+2. 再次 dcat inject rNET_bw_limit --iface={iface} --rate_kbps=1024</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
@@ -4029,13 +4028,13 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>eth0 无 root qdisc，具备 root+CAP_NET_ADMIN，依赖 sch_tbf</t>
+          <t>root，tc_qdisc，sch_tbf，{iface} 无 root qdisc</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rNET_bw_limit --iface=eth0 --rate_kbps=1024
-2. 执行 dcat query rNET_bw_limit --iface=eth0</t>
+          <t>1. 执行 dcat inject rNET_bw_limit --iface={iface} --rate_kbps=1024
+2. 执行 dcat query rNET_bw_limit --iface={iface}</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
@@ -4147,12 +4146,12 @@
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>rNET_bw_limit 可注入</t>
+          <t>root，tc_qdisc，rNET_bw_limit 可注入</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNET_bw_limit --iface=eth0 --rate_kbps=1024
+          <t>1. dcat inject rNET_bw_limit --iface={iface} --rate_kbps=1024
 2. 检查注入状态</t>
         </is>
       </c>

--- a/tests/e2e/testcases.xlsx
+++ b/tests/e2e/testcases.xlsx
@@ -4286,7 +4286,7 @@
       <c r="F65" s="3" t="inlineStr">
         <is>
           <t>1. 首次 status:ok
-2. 第二次 status:ok（幂等）</t>
+2. 第二次 exitcode:1（无活跃记录, DESIGN §5.2）</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>status:ok</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>
@@ -9762,7 +9762,7 @@
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>eth0 无 root qdisc，具备 CAP_NET_ADMIN</t>
+          <t>多核并发环境+精确计时器</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
@@ -10225,7 +10225,7 @@
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>系统未安装 python3</t>
+          <t>python3 缺失环境</t>
         </is>
       </c>
       <c r="D167" s="3" t="inlineStr">
@@ -12118,7 +12118,7 @@
       </c>
       <c r="F199" s="3" t="inlineStr">
         <is>
-          <t>1. 拒绝 status:error 退出码 1</t>
+          <t>1. 拒绝 status:error 退出码 3（precheck: 参数为空）</t>
         </is>
       </c>
       <c r="G199" s="5" t="inlineStr">
@@ -12143,7 +12143,7 @@
       </c>
       <c r="K199" s="3" t="inlineStr">
         <is>
-          <t>exitcode:1</t>
+          <t>exitcode:3</t>
         </is>
       </c>
     </row>
@@ -12477,7 +12477,7 @@
       <c r="F205" s="3" t="inlineStr">
         <is>
           <t>1. 首次 status:ok
-2. 第二次 status:ok（幂等）</t>
+2. 第二次 exitcode:1（无活跃记录, DESIGN §5.2）</t>
         </is>
       </c>
       <c r="G205" s="4" t="inlineStr">
@@ -12502,7 +12502,7 @@
       </c>
       <c r="K205" s="3" t="inlineStr">
         <is>
-          <t>status:ok</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>

--- a/tests/e2e/testcases.xlsx
+++ b/tests/e2e/testcases.xlsx
@@ -5399,7 +5399,7 @@
       <c r="F84" s="3" t="inlineStr">
         <is>
           <t>1. 首次 status:ok
-2. 第二次 status:ok（幂等）</t>
+2. 第二次 exitcode:1（无活跃记录, DESIGN §5.2）</t>
         </is>
       </c>
       <c r="G84" s="4" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>status:ok</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>
@@ -6221,7 +6221,7 @@
       <c r="F98" s="3" t="inlineStr">
         <is>
           <t>1. 首次 status:ok
-2. 第二次 status:ok（幂等）</t>
+2. 第二次 exitcode:1（无活跃记录, DESIGN §5.2）</t>
         </is>
       </c>
       <c r="G98" s="4" t="inlineStr">
@@ -6246,7 +6246,7 @@
       </c>
       <c r="K98" s="3" t="inlineStr">
         <is>
-          <t>status:ok</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>
@@ -6992,7 +6992,7 @@
       <c r="F111" s="3" t="inlineStr">
         <is>
           <t>1. 首次 status:ok
-2. 第二次 status:ok（幂等）</t>
+2. 第二次 exitcode:1（无活跃记录, DESIGN §5.2）</t>
         </is>
       </c>
       <c r="G111" s="4" t="inlineStr">
@@ -7017,7 +7017,7 @@
       </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
-          <t>status:ok</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>
@@ -8042,7 +8042,7 @@
       <c r="F129" s="3" t="inlineStr">
         <is>
           <t>1. 首次 status:ok
-2. 第二次 status:ok（幂等）</t>
+2. 第二次 exitcode:1（无活跃记录, DESIGN §5.2）</t>
         </is>
       </c>
       <c r="G129" s="4" t="inlineStr">
@@ -8067,7 +8067,7 @@
       </c>
       <c r="K129" s="3" t="inlineStr">
         <is>
-          <t>status:ok</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>
@@ -8976,7 +8976,7 @@
       <c r="F145" s="3" t="inlineStr">
         <is>
           <t>1. 首次 status:ok
-2. 第二次 status:ok（幂等）</t>
+2. 第二次 exitcode:1（无活跃记录, DESIGN §5.2）</t>
         </is>
       </c>
       <c r="G145" s="4" t="inlineStr">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="K145" s="3" t="inlineStr">
         <is>
-          <t>status:ok</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>
@@ -9383,10 +9383,7 @@
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
-          <t>1. 脚本语义校验拒绝（loss_pct 超过 100）
-2. 脚本非 0 退出
-3. dcat 返回 status:error、退出码 1
-4. 不写 state（dcat 仅做结构校验，范围校验由脚本负责）</t>
+          <t>1. 拒绝 status:error 退出码 1（loss_pct 超出 0-100）</t>
         </is>
       </c>
       <c r="G152" s="5" t="inlineStr">
@@ -9407,7 +9404,7 @@
       </c>
       <c r="K152" s="3" t="inlineStr">
         <is>
-          <t>&gt;=1</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>
@@ -10718,7 +10715,7 @@
       <c r="F175" s="3" t="inlineStr">
         <is>
           <t>1. 首次 status:ok
-2. 第二次 status:ok（幂等）</t>
+2. 第二次 exitcode:1（无活跃记录, DESIGN §5.2）</t>
         </is>
       </c>
       <c r="G175" s="4" t="inlineStr">
@@ -10743,7 +10740,7 @@
       </c>
       <c r="K175" s="3" t="inlineStr">
         <is>
-          <t>status:ok</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>
@@ -11768,7 +11765,7 @@
       <c r="F193" s="3" t="inlineStr">
         <is>
           <t>1. 首次 status:ok
-2. 第二次 status:ok（幂等）</t>
+2. 第二次 exitcode:1（无活跃记录, DESIGN §5.2）</t>
         </is>
       </c>
       <c r="G193" s="4" t="inlineStr">
@@ -11793,7 +11790,7 @@
       </c>
       <c r="K193" s="3" t="inlineStr">
         <is>
-          <t>status:ok</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>
@@ -14560,7 +14557,7 @@
       <c r="F241" s="3" t="inlineStr">
         <is>
           <t>1. 首次 status:ok
-2. 第二次 status:ok（幂等）</t>
+2. 第二次 exitcode:1（无活跃记录, DESIGN §5.2）</t>
         </is>
       </c>
       <c r="G241" s="4" t="inlineStr">
@@ -14585,7 +14582,7 @@
       </c>
       <c r="K241" s="3" t="inlineStr">
         <is>
-          <t>status:ok</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>
@@ -15606,7 +15603,7 @@
       <c r="F259" s="3" t="inlineStr">
         <is>
           <t>1. 首次 status:ok
-2. 第二次 status:ok（幂等）</t>
+2. 第二次 exitcode:1（无活跃记录, DESIGN §5.2）</t>
         </is>
       </c>
       <c r="G259" s="4" t="inlineStr">
@@ -15631,7 +15628,7 @@
       </c>
       <c r="K259" s="3" t="inlineStr">
         <is>
-          <t>status:ok</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>
@@ -16595,7 +16592,7 @@
       <c r="F276" s="3" t="inlineStr">
         <is>
           <t>1. 首次 status:ok
-2. 第二次 status:ok（幂等）</t>
+2. 第二次 exitcode:1（无活跃记录, DESIGN §5.2）</t>
         </is>
       </c>
       <c r="G276" s="4" t="inlineStr">
@@ -16620,7 +16617,7 @@
       </c>
       <c r="K276" s="3" t="inlineStr">
         <is>
-          <t>status:ok</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>
@@ -17702,7 +17699,7 @@
       <c r="F295" s="3" t="inlineStr">
         <is>
           <t>1. 首次 status:ok
-2. 第二次 status:ok（幂等）</t>
+2. 第二次 exitcode:1（无活跃记录, DESIGN §5.2）</t>
         </is>
       </c>
       <c r="G295" s="4" t="inlineStr">
@@ -17727,7 +17724,7 @@
       </c>
       <c r="K295" s="3" t="inlineStr">
         <is>
-          <t>status:ok</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>
@@ -18584,7 +18581,7 @@
       <c r="F310" s="3" t="inlineStr">
         <is>
           <t>1. 首次 status:ok
-2. 第二次 status:ok（幂等）</t>
+2. 第二次 exitcode:1（无活跃记录, DESIGN §5.2）</t>
         </is>
       </c>
       <c r="G310" s="4" t="inlineStr">
@@ -18609,7 +18606,7 @@
       </c>
       <c r="K310" s="3" t="inlineStr">
         <is>
-          <t>status:ok</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>
@@ -19863,7 +19860,7 @@
       <c r="F332" s="3" t="inlineStr">
         <is>
           <t>1. 首次 status:ok
-2. 第二次 status:ok（幂等）</t>
+2. 第二次 exitcode:1（无活跃记录, DESIGN §5.2）</t>
         </is>
       </c>
       <c r="G332" s="4" t="inlineStr">
@@ -19888,7 +19885,7 @@
       </c>
       <c r="K332" s="3" t="inlineStr">
         <is>
-          <t>status:ok</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>
@@ -21085,7 +21082,7 @@
       <c r="F353" s="3" t="inlineStr">
         <is>
           <t>1. 首次 status:ok
-2. 第二次 status:ok（幂等）</t>
+2. 第二次 exitcode:1（无活跃记录, DESIGN §5.2）</t>
         </is>
       </c>
       <c r="G353" s="4" t="inlineStr">
@@ -21110,7 +21107,7 @@
       </c>
       <c r="K353" s="3" t="inlineStr">
         <is>
-          <t>status:ok</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>
@@ -21910,7 +21907,7 @@
       <c r="F367" s="3" t="inlineStr">
         <is>
           <t>1. 首次 status:ok
-2. 第二次 status:ok（幂等）</t>
+2. 第二次 exitcode:1（无活跃记录, DESIGN §5.2）</t>
         </is>
       </c>
       <c r="G367" s="4" t="inlineStr">
@@ -21935,7 +21932,7 @@
       </c>
       <c r="K367" s="3" t="inlineStr">
         <is>
-          <t>status:ok</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>
@@ -22961,7 +22958,7 @@
       <c r="F385" s="3" t="inlineStr">
         <is>
           <t>1. 首次 status:ok
-2. 第二次 status:ok（幂等）</t>
+2. 第二次 exitcode:1（无活跃记录, DESIGN §5.2）</t>
         </is>
       </c>
       <c r="G385" s="4" t="inlineStr">
@@ -22986,7 +22983,7 @@
       </c>
       <c r="K385" s="3" t="inlineStr">
         <is>
-          <t>status:ok</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>
@@ -23784,7 +23781,7 @@
       <c r="F399" s="3" t="inlineStr">
         <is>
           <t>1. 首次 status:ok
-2. 第二次 status:ok（幂等）</t>
+2. 第二次 exitcode:1（无活跃记录, DESIGN §5.2）</t>
         </is>
       </c>
       <c r="G399" s="4" t="inlineStr">
@@ -23809,7 +23806,7 @@
       </c>
       <c r="K399" s="3" t="inlineStr">
         <is>
-          <t>status:ok</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>
@@ -24835,7 +24832,7 @@
       <c r="F417" s="3" t="inlineStr">
         <is>
           <t>1. 首次 status:ok
-2. 第二次 status:ok（幂等）</t>
+2. 第二次 exitcode:1（无活跃记录, DESIGN §5.2）</t>
         </is>
       </c>
       <c r="G417" s="4" t="inlineStr">
@@ -24860,7 +24857,7 @@
       </c>
       <c r="K417" s="3" t="inlineStr">
         <is>
-          <t>status:ok</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>
@@ -25658,7 +25655,7 @@
       <c r="F431" s="3" t="inlineStr">
         <is>
           <t>1. 首次 status:ok
-2. 第二次 status:ok（幂等）</t>
+2. 第二次 exitcode:1（无活跃记录, DESIGN §5.2）</t>
         </is>
       </c>
       <c r="G431" s="4" t="inlineStr">
@@ -25683,7 +25680,7 @@
       </c>
       <c r="K431" s="3" t="inlineStr">
         <is>
-          <t>status:ok</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>
@@ -26481,7 +26478,7 @@
       <c r="F445" s="3" t="inlineStr">
         <is>
           <t>1. 首次 status:ok
-2. 第二次 status:ok（幂等）</t>
+2. 第二次 exitcode:1（无活跃记录, DESIGN §5.2）</t>
         </is>
       </c>
       <c r="G445" s="4" t="inlineStr">
@@ -26506,7 +26503,7 @@
       </c>
       <c r="K445" s="3" t="inlineStr">
         <is>
-          <t>status:ok</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>
@@ -27365,7 +27362,7 @@
       <c r="F460" s="3" t="inlineStr">
         <is>
           <t>1. 首次 status:ok
-2. 第二次 status:ok（幂等）</t>
+2. 第二次 exitcode:1（无活跃记录, DESIGN §5.2）</t>
         </is>
       </c>
       <c r="G460" s="4" t="inlineStr">
@@ -27390,7 +27387,7 @@
       </c>
       <c r="K460" s="3" t="inlineStr">
         <is>
-          <t>status:ok</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>
@@ -28188,7 +28185,7 @@
       <c r="F474" s="3" t="inlineStr">
         <is>
           <t>1. 首次 status:ok
-2. 第二次 status:ok（幂等）</t>
+2. 第二次 exitcode:1（无活跃记录, DESIGN §5.2）</t>
         </is>
       </c>
       <c r="G474" s="4" t="inlineStr">
@@ -28213,7 +28210,7 @@
       </c>
       <c r="K474" s="3" t="inlineStr">
         <is>
-          <t>status:ok</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>
@@ -29011,7 +29008,7 @@
       <c r="F488" s="3" t="inlineStr">
         <is>
           <t>1. 首次 status:ok
-2. 第二次 status:ok（幂等）</t>
+2. 第二次 exitcode:1（无活跃记录, DESIGN §5.2）</t>
         </is>
       </c>
       <c r="G488" s="4" t="inlineStr">
@@ -29036,7 +29033,7 @@
       </c>
       <c r="K488" s="3" t="inlineStr">
         <is>
-          <t>status:ok</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>
@@ -29834,7 +29831,7 @@
       <c r="F502" s="3" t="inlineStr">
         <is>
           <t>1. 首次 status:ok
-2. 第二次 status:ok（幂等）</t>
+2. 第二次 exitcode:1（无活跃记录, DESIGN §5.2）</t>
         </is>
       </c>
       <c r="G502" s="4" t="inlineStr">
@@ -29859,7 +29856,7 @@
       </c>
       <c r="K502" s="3" t="inlineStr">
         <is>
-          <t>status:ok</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>
@@ -30657,7 +30654,7 @@
       <c r="F516" s="3" t="inlineStr">
         <is>
           <t>1. 首次 status:ok
-2. 第二次 status:ok（幂等）</t>
+2. 第二次 exitcode:1（无活跃记录, DESIGN §5.2）</t>
         </is>
       </c>
       <c r="G516" s="4" t="inlineStr">
@@ -30682,7 +30679,7 @@
       </c>
       <c r="K516" s="3" t="inlineStr">
         <is>
-          <t>status:ok</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>

--- a/tests/e2e/testcases.xlsx
+++ b/tests/e2e/testcases.xlsx
@@ -9759,13 +9759,12 @@
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>多核并发环境+精确计时器</t>
+          <t>已注入 rNET_loss</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>1. 两个进程同时执行 dcat inject rNET_loss --iface=eth0 --loss_pct=5
-2. 检查两结果与 state</t>
+          <t>1. 再次 dcat inject rNET_loss --iface=eth0 --loss_pct=5（重注入）</t>
         </is>
       </c>
       <c r="E159" s="3" t="inlineStr">
@@ -9775,9 +9774,7 @@
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t>1. 竞态下至多一个成功（返回 status:ok 与 record_id）
-2. 另一个因 state 已有同 iface 记录或 tc qdisc 已存在而失败（退出码 5 或 1）
-3. 不出现两个 qdisc 叠加</t>
+          <t>1. 拒绝 exitcode:5（同资源重注入被拒）</t>
         </is>
       </c>
       <c r="G159" s="4" t="inlineStr">

--- a/tests/e2e/testcases.xlsx
+++ b/tests/e2e/testcases.xlsx
@@ -11212,7 +11212,7 @@
       </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t>rNET_reorder-reorder_pct=0 最小值接受</t>
+          <t>rNET_reorder-reorder_pct=0 低于最小值拒绝</t>
         </is>
       </c>
       <c r="C184" s="3" t="inlineStr">
@@ -11232,7 +11232,7 @@
       </c>
       <c r="F184" s="3" t="inlineStr">
         <is>
-          <t>1. 注入成功 status:ok</t>
+          <t>1. 拒绝 status:error 退出码 1（reorder_pct 必须 1-100）</t>
         </is>
       </c>
       <c r="G184" s="4" t="inlineStr">
@@ -11257,7 +11257,7 @@
       </c>
       <c r="K184" s="3" t="inlineStr">
         <is>
-          <t>&gt;=1</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>

--- a/tests/e2e/testcases.xlsx
+++ b/tests/e2e/testcases.xlsx
@@ -15647,7 +15647,7 @@
       </c>
       <c r="C260" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_arp_del</t>
+          <t>npu_hardware，已注入 rNPU_arp_del</t>
         </is>
       </c>
       <c r="D260" s="3" t="inlineStr">
@@ -15706,7 +15706,7 @@
       </c>
       <c r="C261" s="3" t="inlineStr">
         <is>
-          <t>rNPU_arp_del 可注入</t>
+          <t>npu_hardware，rNPU_arp_del 可注入</t>
         </is>
       </c>
       <c r="D261" s="3" t="inlineStr">
@@ -15763,7 +15763,7 @@
       </c>
       <c r="C262" s="3" t="inlineStr">
         <is>
-          <t>rNPU_arp_del 可注入</t>
+          <t>npu_hardware，rNPU_arp_del 可注入</t>
         </is>
       </c>
       <c r="D262" s="3" t="inlineStr">
@@ -15820,7 +15820,7 @@
       </c>
       <c r="C263" s="3" t="inlineStr">
         <is>
-          <t>此类 NPU 故障无 /tmp 工件可枚举其标识</t>
+          <t>npu_hardware，此类 NPU 故障无 /tmp 工件可枚举其标识</t>
         </is>
       </c>
       <c r="D263" s="3" t="inlineStr">
@@ -15877,7 +15877,7 @@
       </c>
       <c r="C264" s="3" t="inlineStr">
         <is>
-          <t>已注入 arp_del，sidecar 保存原 MAC</t>
+          <t>npu_hardware，已注入 arp_del，sidecar 保存原 MAC</t>
         </is>
       </c>
       <c r="D264" s="3" t="inlineStr">
@@ -15933,7 +15933,7 @@
       </c>
       <c r="C265" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_arp_del</t>
+          <t>npu_hardware，已 clean rNPU_arp_del</t>
         </is>
       </c>
       <c r="D265" s="3" t="inlineStr">
@@ -15992,7 +15992,7 @@
       </c>
       <c r="C266" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_arp_del</t>
+          <t>npu_hardware，已注入 rNPU_arp_del</t>
         </is>
       </c>
       <c r="D266" s="3" t="inlineStr">
@@ -16051,7 +16051,7 @@
       </c>
       <c r="C267" s="3" t="inlineStr">
         <is>
-          <t>rNPU_arp_del 可注入</t>
+          <t>npu_hardware，rNPU_arp_del 可注入</t>
         </is>
       </c>
       <c r="D267" s="3" t="inlineStr">
@@ -16108,7 +16108,7 @@
       </c>
       <c r="C268" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_arp_del</t>
+          <t>npu_hardware，已注入 rNPU_arp_del</t>
         </is>
       </c>
       <c r="D268" s="3" t="inlineStr">
@@ -16166,7 +16166,7 @@
       </c>
       <c r="C269" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_arp_del</t>
+          <t>npu_hardware，已注入 rNPU_arp_del</t>
         </is>
       </c>
       <c r="D269" s="3" t="inlineStr">
@@ -16224,7 +16224,7 @@
       </c>
       <c r="C270" s="3" t="inlineStr">
         <is>
-          <t>目标 ARP 条目未预先创建</t>
+          <t>npu_hardware，目标 ARP 条目未预先创建</t>
         </is>
       </c>
       <c r="D270" s="3" t="inlineStr">
@@ -16281,7 +16281,7 @@
       </c>
       <c r="C271" s="3" t="inlineStr">
         <is>
-          <t>目标 ARP 条目已存在（已用 -arp -g 确认或先 inject rNPU_arp_poison 创建）；dev 用 hccn_tool 查出的 NPU 内部网口名</t>
+          <t>npu_hardware，目标 ARP 条目已存在（已用 -arp -g 确认或先 inject rNPU_arp_poison 创建）；dev 用 hccn_tool 查出的 NPU 内部网口名</t>
         </is>
       </c>
       <c r="D271" s="3" t="inlineStr">
@@ -16338,7 +16338,7 @@
       </c>
       <c r="C272" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_arp_del</t>
+          <t>npu_hardware，已注入 rNPU_arp_del</t>
         </is>
       </c>
       <c r="D272" s="3" t="inlineStr">
@@ -16397,7 +16397,7 @@
       </c>
       <c r="C273" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_arp_del</t>
+          <t>npu_hardware，已注入 rNPU_arp_del</t>
         </is>
       </c>
       <c r="D273" s="3" t="inlineStr">
@@ -16455,7 +16455,7 @@
       </c>
       <c r="C274" s="3" t="inlineStr">
         <is>
-          <t>rNPU_arp_del 可注入</t>
+          <t>npu_hardware，rNPU_arp_del 可注入</t>
         </is>
       </c>
       <c r="D274" s="3" t="inlineStr">
@@ -16514,7 +16514,7 @@
       </c>
       <c r="C275" s="3" t="inlineStr">
         <is>
-          <t>rNPU_arp_del 可注入</t>
+          <t>npu_hardware，rNPU_arp_del 可注入</t>
         </is>
       </c>
       <c r="D275" s="3" t="inlineStr">
@@ -16577,7 +16577,7 @@
       </c>
       <c r="C276" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_arp_del</t>
+          <t>npu_hardware，已 clean rNPU_arp_del</t>
         </is>
       </c>
       <c r="D276" s="3" t="inlineStr">
@@ -16636,7 +16636,7 @@
       </c>
       <c r="C277" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_arp_poison</t>
+          <t>npu_hardware，已注入 rNPU_arp_poison</t>
         </is>
       </c>
       <c r="D277" s="3" t="inlineStr">
@@ -16695,7 +16695,7 @@
       </c>
       <c r="C278" s="3" t="inlineStr">
         <is>
-          <t>rNPU_arp_poison 可注入</t>
+          <t>npu_hardware，rNPU_arp_poison 可注入</t>
         </is>
       </c>
       <c r="D278" s="3" t="inlineStr">
@@ -16752,7 +16752,7 @@
       </c>
       <c r="C279" s="3" t="inlineStr">
         <is>
-          <t>rNPU_arp_poison 可注入</t>
+          <t>npu_hardware，rNPU_arp_poison 可注入</t>
         </is>
       </c>
       <c r="D279" s="3" t="inlineStr">
@@ -16809,7 +16809,7 @@
       </c>
       <c r="C280" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_arp_poison</t>
+          <t>npu_hardware，已 clean rNPU_arp_poison</t>
         </is>
       </c>
       <c r="D280" s="3" t="inlineStr">
@@ -16868,7 +16868,7 @@
       </c>
       <c r="C281" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_arp_poison</t>
+          <t>npu_hardware，已注入 rNPU_arp_poison</t>
         </is>
       </c>
       <c r="D281" s="3" t="inlineStr">
@@ -16923,7 +16923,7 @@
       </c>
       <c r="C282" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_arp_poison</t>
+          <t>npu_hardware，已注入 rNPU_arp_poison</t>
         </is>
       </c>
       <c r="D282" s="3" t="inlineStr">
@@ -16982,7 +16982,7 @@
       </c>
       <c r="C283" s="3" t="inlineStr">
         <is>
-          <t>已查出 chip2 真实 dev（示例 eth2）</t>
+          <t>npu_hardware，已查出 chip2 真实 dev（示例 eth2）</t>
         </is>
       </c>
       <c r="D283" s="3" t="inlineStr">
@@ -17042,7 +17042,7 @@
       </c>
       <c r="C284" s="3" t="inlineStr">
         <is>
-          <t>rNPU_arp_poison 可注入</t>
+          <t>npu_hardware，rNPU_arp_poison 可注入</t>
         </is>
       </c>
       <c r="D284" s="3" t="inlineStr">
@@ -17099,7 +17099,7 @@
       </c>
       <c r="C285" s="3" t="inlineStr">
         <is>
-          <t>已用 hccn_tool -i 2 -status -g 查出目标芯片真实 dev（示例机 chip2=eth2）；ip 选用 NPU 同网段未占用地址</t>
+          <t>npu_hardware，已用 hccn_tool -i 2 -status -g 查出目标芯片真实 dev（示例机 chip2=eth2）；ip 选用 NPU 同网段未占用地址</t>
         </is>
       </c>
       <c r="D285" s="3" t="inlineStr">
@@ -17155,7 +17155,7 @@
       </c>
       <c r="C286" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_arp_poison</t>
+          <t>npu_hardware，已注入 rNPU_arp_poison</t>
         </is>
       </c>
       <c r="D286" s="3" t="inlineStr">
@@ -17213,7 +17213,7 @@
       </c>
       <c r="C287" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_arp_poison</t>
+          <t>npu_hardware，已注入 rNPU_arp_poison</t>
         </is>
       </c>
       <c r="D287" s="3" t="inlineStr">
@@ -17271,7 +17271,7 @@
       </c>
       <c r="C288" s="3" t="inlineStr">
         <is>
-          <t>chip=99 越界，其余参数合法</t>
+          <t>npu_hardware，chip=99 越界，其余参数合法</t>
         </is>
       </c>
       <c r="D288" s="3" t="inlineStr">
@@ -17329,7 +17329,7 @@
       </c>
       <c r="C289" s="3" t="inlineStr">
         <is>
-          <t>chip=99 + mac=invalid</t>
+          <t>npu_hardware，chip=99 + mac=invalid</t>
         </is>
       </c>
       <c r="D289" s="3" t="inlineStr">
@@ -17387,7 +17387,7 @@
       </c>
       <c r="C290" s="3" t="inlineStr">
         <is>
-          <t>mac=invalid（非 MAC 格式）</t>
+          <t>npu_hardware，mac=invalid（非 MAC 格式）</t>
         </is>
       </c>
       <c r="D290" s="3" t="inlineStr">
@@ -17445,7 +17445,7 @@
       </c>
       <c r="C291" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_arp_poison</t>
+          <t>npu_hardware，已注入 rNPU_arp_poison</t>
         </is>
       </c>
       <c r="D291" s="3" t="inlineStr">
@@ -17504,7 +17504,7 @@
       </c>
       <c r="C292" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_arp_poison</t>
+          <t>npu_hardware，已注入 rNPU_arp_poison</t>
         </is>
       </c>
       <c r="D292" s="3" t="inlineStr">
@@ -17562,7 +17562,7 @@
       </c>
       <c r="C293" s="3" t="inlineStr">
         <is>
-          <t>rNPU_arp_poison 可注入</t>
+          <t>npu_hardware，rNPU_arp_poison 可注入</t>
         </is>
       </c>
       <c r="D293" s="3" t="inlineStr">
@@ -17621,7 +17621,7 @@
       </c>
       <c r="C294" s="3" t="inlineStr">
         <is>
-          <t>rNPU_arp_poison 可注入</t>
+          <t>npu_hardware，rNPU_arp_poison 可注入</t>
         </is>
       </c>
       <c r="D294" s="3" t="inlineStr">
@@ -17684,7 +17684,7 @@
       </c>
       <c r="C295" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_arp_poison</t>
+          <t>npu_hardware，已 clean rNPU_arp_poison</t>
         </is>
       </c>
       <c r="D295" s="3" t="inlineStr">
@@ -17743,7 +17743,7 @@
       </c>
       <c r="C296" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_bw_limit</t>
+          <t>npu_hardware，已注入 rNPU_bw_limit</t>
         </is>
       </c>
       <c r="D296" s="3" t="inlineStr">
@@ -17802,7 +17802,7 @@
       </c>
       <c r="C297" s="3" t="inlineStr">
         <is>
-          <t>Atlas NPU+hccn_tool，root，chip0 可用</t>
+          <t>npu_hardware，Atlas NPU+hccn_tool，root，chip0 可用</t>
         </is>
       </c>
       <c r="D297" s="3" t="inlineStr">
@@ -17863,7 +17863,7 @@
       </c>
       <c r="C298" s="3" t="inlineStr">
         <is>
-          <t>Atlas NPU+hccn_tool，root</t>
+          <t>npu_hardware，Atlas NPU+hccn_tool，root</t>
         </is>
       </c>
       <c r="D298" s="3" t="inlineStr">
@@ -17922,7 +17922,7 @@
       </c>
       <c r="C299" s="3" t="inlineStr">
         <is>
-          <t>rNPU_bw_limit 可注入</t>
+          <t>npu_hardware，rNPU_bw_limit 可注入</t>
         </is>
       </c>
       <c r="D299" s="3" t="inlineStr">
@@ -17979,7 +17979,7 @@
       </c>
       <c r="C300" s="3" t="inlineStr">
         <is>
-          <t>rNPU_bw_limit 可注入</t>
+          <t>npu_hardware，rNPU_bw_limit 可注入</t>
         </is>
       </c>
       <c r="D300" s="3" t="inlineStr">
@@ -18036,7 +18036,7 @@
       </c>
       <c r="C301" s="3" t="inlineStr">
         <is>
-          <t>rNPU_bw_limit 可注入</t>
+          <t>npu_hardware，rNPU_bw_limit 可注入</t>
         </is>
       </c>
       <c r="D301" s="3" t="inlineStr">
@@ -18093,7 +18093,7 @@
       </c>
       <c r="C302" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_bw_limit</t>
+          <t>npu_hardware，已 clean rNPU_bw_limit</t>
         </is>
       </c>
       <c r="D302" s="3" t="inlineStr">
@@ -18152,7 +18152,7 @@
       </c>
       <c r="C303" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_bw_limit</t>
+          <t>npu_hardware，已注入 rNPU_bw_limit</t>
         </is>
       </c>
       <c r="D303" s="3" t="inlineStr">
@@ -18211,7 +18211,7 @@
       </c>
       <c r="C304" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_bw_limit</t>
+          <t>npu_hardware，已注入 rNPU_bw_limit</t>
         </is>
       </c>
       <c r="D304" s="3" t="inlineStr">
@@ -18269,7 +18269,7 @@
       </c>
       <c r="C305" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_bw_limit</t>
+          <t>npu_hardware，已注入 rNPU_bw_limit</t>
         </is>
       </c>
       <c r="D305" s="3" t="inlineStr">
@@ -18327,7 +18327,7 @@
       </c>
       <c r="C306" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_bw_limit</t>
+          <t>npu_hardware，已注入 rNPU_bw_limit</t>
         </is>
       </c>
       <c r="D306" s="3" t="inlineStr">
@@ -18386,7 +18386,7 @@
       </c>
       <c r="C307" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_bw_limit</t>
+          <t>npu_hardware，已注入 rNPU_bw_limit</t>
         </is>
       </c>
       <c r="D307" s="3" t="inlineStr">
@@ -18444,7 +18444,7 @@
       </c>
       <c r="C308" s="3" t="inlineStr">
         <is>
-          <t>rNPU_bw_limit 可注入</t>
+          <t>npu_hardware，rNPU_bw_limit 可注入</t>
         </is>
       </c>
       <c r="D308" s="3" t="inlineStr">
@@ -18503,7 +18503,7 @@
       </c>
       <c r="C309" s="3" t="inlineStr">
         <is>
-          <t>rNPU_bw_limit 可注入</t>
+          <t>npu_hardware，rNPU_bw_limit 可注入</t>
         </is>
       </c>
       <c r="D309" s="3" t="inlineStr">
@@ -18566,7 +18566,7 @@
       </c>
       <c r="C310" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_bw_limit</t>
+          <t>npu_hardware，已 clean rNPU_bw_limit</t>
         </is>
       </c>
       <c r="D310" s="3" t="inlineStr">
@@ -18625,7 +18625,7 @@
       </c>
       <c r="C311" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_dscp_tc_change</t>
+          <t>npu_hardware，已注入 rNPU_dscp_tc_change</t>
         </is>
       </c>
       <c r="D311" s="3" t="inlineStr">
@@ -18684,7 +18684,7 @@
       </c>
       <c r="C312" s="3" t="inlineStr">
         <is>
-          <t>Atlas NPU+hccn_tool，root，chip0 可用</t>
+          <t>npu_hardware，Atlas NPU+hccn_tool，root，chip0 可用</t>
         </is>
       </c>
       <c r="D312" s="3" t="inlineStr">
@@ -18745,7 +18745,7 @@
       </c>
       <c r="C313" s="3" t="inlineStr">
         <is>
-          <t>rNPU_dscp_tc_change 可注入</t>
+          <t>npu_hardware，rNPU_dscp_tc_change 可注入</t>
         </is>
       </c>
       <c r="D313" s="3" t="inlineStr">
@@ -18802,7 +18802,7 @@
       </c>
       <c r="C314" s="3" t="inlineStr">
         <is>
-          <t>rNPU_dscp_tc_change 可注入</t>
+          <t>npu_hardware，rNPU_dscp_tc_change 可注入</t>
         </is>
       </c>
       <c r="D314" s="3" t="inlineStr">
@@ -18859,7 +18859,7 @@
       </c>
       <c r="C315" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_dscp_tc_change</t>
+          <t>npu_hardware，已 clean rNPU_dscp_tc_change</t>
         </is>
       </c>
       <c r="D315" s="3" t="inlineStr">
@@ -18918,7 +18918,7 @@
       </c>
       <c r="C316" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_dscp_tc_change</t>
+          <t>npu_hardware，已注入 rNPU_dscp_tc_change</t>
         </is>
       </c>
       <c r="D316" s="3" t="inlineStr">
@@ -18977,7 +18977,7 @@
       </c>
       <c r="C317" s="3" t="inlineStr">
         <is>
-          <t>chip0</t>
+          <t>npu_hardware，chip0</t>
         </is>
       </c>
       <c r="D317" s="3" t="inlineStr">
@@ -19034,7 +19034,7 @@
       </c>
       <c r="C318" s="3" t="inlineStr">
         <is>
-          <t>rNPU_dscp_tc_change 可注入</t>
+          <t>npu_hardware，rNPU_dscp_tc_change 可注入</t>
         </is>
       </c>
       <c r="D318" s="3" t="inlineStr">
@@ -19091,7 +19091,7 @@
       </c>
       <c r="C319" s="3" t="inlineStr">
         <is>
-          <t>Atlas NPU+hccn_tool，root，chip0</t>
+          <t>npu_hardware，Atlas NPU+hccn_tool，root，chip0</t>
         </is>
       </c>
       <c r="D319" s="3" t="inlineStr">
@@ -19148,7 +19148,7 @@
       </c>
       <c r="C320" s="3" t="inlineStr">
         <is>
-          <t>chip0</t>
+          <t>npu_hardware，chip0</t>
         </is>
       </c>
       <c r="D320" s="3" t="inlineStr">
@@ -19205,7 +19205,7 @@
       </c>
       <c r="C321" s="3" t="inlineStr">
         <is>
-          <t>chip0</t>
+          <t>npu_hardware，chip0</t>
         </is>
       </c>
       <c r="D321" s="3" t="inlineStr">
@@ -19262,7 +19262,7 @@
       </c>
       <c r="C322" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_dscp_tc_change</t>
+          <t>npu_hardware，已注入 rNPU_dscp_tc_change</t>
         </is>
       </c>
       <c r="D322" s="3" t="inlineStr">
@@ -19320,7 +19320,7 @@
       </c>
       <c r="C323" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_dscp_tc_change</t>
+          <t>npu_hardware，已注入 rNPU_dscp_tc_change</t>
         </is>
       </c>
       <c r="D323" s="3" t="inlineStr">
@@ -19378,7 +19378,7 @@
       </c>
       <c r="C324" s="3" t="inlineStr">
         <is>
-          <t>chip0</t>
+          <t>npu_hardware，chip0</t>
         </is>
       </c>
       <c r="D324" s="3" t="inlineStr">
@@ -19435,7 +19435,7 @@
       </c>
       <c r="C325" s="3" t="inlineStr">
         <is>
-          <t>chip0</t>
+          <t>npu_hardware，chip0</t>
         </is>
       </c>
       <c r="D325" s="3" t="inlineStr">
@@ -19492,7 +19492,7 @@
       </c>
       <c r="C326" s="3" t="inlineStr">
         <is>
-          <t>chip0</t>
+          <t>npu_hardware，chip0</t>
         </is>
       </c>
       <c r="D326" s="3" t="inlineStr">
@@ -19549,7 +19549,7 @@
       </c>
       <c r="C327" s="3" t="inlineStr">
         <is>
-          <t>chip0</t>
+          <t>npu_hardware，chip0</t>
         </is>
       </c>
       <c r="D327" s="3" t="inlineStr">
@@ -19606,7 +19606,7 @@
       </c>
       <c r="C328" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_dscp_tc_change</t>
+          <t>npu_hardware，已注入 rNPU_dscp_tc_change</t>
         </is>
       </c>
       <c r="D328" s="3" t="inlineStr">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C329" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_dscp_tc_change</t>
+          <t>npu_hardware，已注入 rNPU_dscp_tc_change</t>
         </is>
       </c>
       <c r="D329" s="3" t="inlineStr">
@@ -19723,7 +19723,7 @@
       </c>
       <c r="C330" s="3" t="inlineStr">
         <is>
-          <t>rNPU_dscp_tc_change 可注入</t>
+          <t>npu_hardware，rNPU_dscp_tc_change 可注入</t>
         </is>
       </c>
       <c r="D330" s="3" t="inlineStr">
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C331" s="3" t="inlineStr">
         <is>
-          <t>rNPU_dscp_tc_change 可注入</t>
+          <t>npu_hardware，rNPU_dscp_tc_change 可注入</t>
         </is>
       </c>
       <c r="D331" s="3" t="inlineStr">
@@ -19845,7 +19845,7 @@
       </c>
       <c r="C332" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_dscp_tc_change</t>
+          <t>npu_hardware，已 clean rNPU_dscp_tc_change</t>
         </is>
       </c>
       <c r="D332" s="3" t="inlineStr">
@@ -19904,7 +19904,7 @@
       </c>
       <c r="C333" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_gw_change</t>
+          <t>npu_hardware，已注入 rNPU_gw_change</t>
         </is>
       </c>
       <c r="D333" s="3" t="inlineStr">
@@ -19963,7 +19963,7 @@
       </c>
       <c r="C334" s="3" t="inlineStr">
         <is>
-          <t>NPU 芯片号范围 0-7</t>
+          <t>npu_hardware，NPU 芯片号范围 0-7</t>
         </is>
       </c>
       <c r="D334" s="3" t="inlineStr">
@@ -20023,7 +20023,7 @@
       </c>
       <c r="C335" s="3" t="inlineStr">
         <is>
-          <t>已查出 chip0 的 NPU IP 与网关（同网段不同值）</t>
+          <t>npu_hardware，已查出 chip0 的 NPU IP 与网关（同网段不同值）</t>
         </is>
       </c>
       <c r="D335" s="3" t="inlineStr">
@@ -20081,7 +20081,7 @@
       </c>
       <c r="C336" s="3" t="inlineStr">
         <is>
-          <t>已查出 chip7 的 NPU IP 与网关</t>
+          <t>npu_hardware，已查出 chip7 的 NPU IP 与网关</t>
         </is>
       </c>
       <c r="D336" s="3" t="inlineStr">
@@ -20138,7 +20138,7 @@
       </c>
       <c r="C337" s="3" t="inlineStr">
         <is>
-          <t>rNPU_gw_change 可注入</t>
+          <t>npu_hardware，rNPU_gw_change 可注入</t>
         </is>
       </c>
       <c r="D337" s="3" t="inlineStr">
@@ -20195,7 +20195,7 @@
       </c>
       <c r="C338" s="3" t="inlineStr">
         <is>
-          <t>rNPU_gw_change 可注入</t>
+          <t>npu_hardware，rNPU_gw_change 可注入</t>
         </is>
       </c>
       <c r="D338" s="3" t="inlineStr">
@@ -20252,7 +20252,7 @@
       </c>
       <c r="C339" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_gw_change</t>
+          <t>npu_hardware，已 clean rNPU_gw_change</t>
         </is>
       </c>
       <c r="D339" s="3" t="inlineStr">
@@ -20311,7 +20311,7 @@
       </c>
       <c r="C340" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_gw_change</t>
+          <t>npu_hardware，已注入 rNPU_gw_change</t>
         </is>
       </c>
       <c r="D340" s="3" t="inlineStr">
@@ -20370,7 +20370,7 @@
       </c>
       <c r="C341" s="3" t="inlineStr">
         <is>
-          <t>rNPU_gw_change 可注入</t>
+          <t>npu_hardware，rNPU_gw_change 可注入</t>
         </is>
       </c>
       <c r="D341" s="3" t="inlineStr">
@@ -20427,7 +20427,7 @@
       </c>
       <c r="C342" s="3" t="inlineStr">
         <is>
-          <t>系统未安装 hccn_tool（非 Atlas NPU 机器）</t>
+          <t>npu_hardware，系统未安装 hccn_tool（非 Atlas NPU 机器）</t>
         </is>
       </c>
       <c r="D342" s="3" t="inlineStr">
@@ -20487,7 +20487,7 @@
       </c>
       <c r="C343" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_gw_change</t>
+          <t>npu_hardware，已注入 rNPU_gw_change</t>
         </is>
       </c>
       <c r="D343" s="3" t="inlineStr">
@@ -20545,7 +20545,7 @@
       </c>
       <c r="C344" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_gw_change</t>
+          <t>npu_hardware，已注入 rNPU_gw_change</t>
         </is>
       </c>
       <c r="D344" s="3" t="inlineStr">
@@ -20603,7 +20603,7 @@
       </c>
       <c r="C345" s="3" t="inlineStr">
         <is>
-          <t>inject 时原网关为 none（未设网关），sidecar 存 none</t>
+          <t>npu_hardware，inject 时原网关为 none（未设网关），sidecar 存 none</t>
         </is>
       </c>
       <c r="D345" s="3" t="inlineStr">
@@ -20659,7 +20659,7 @@
       </c>
       <c r="C346" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_gw_change</t>
+          <t>npu_hardware，已注入 rNPU_gw_change</t>
         </is>
       </c>
       <c r="D346" s="3" t="inlineStr">
@@ -20718,7 +20718,7 @@
       </c>
       <c r="C347" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_gw_change</t>
+          <t>npu_hardware，已注入 rNPU_gw_change</t>
         </is>
       </c>
       <c r="D347" s="3" t="inlineStr">
@@ -20776,7 +20776,7 @@
       </c>
       <c r="C348" s="3" t="inlineStr">
         <is>
-          <t>rNPU_gw_change 可注入</t>
+          <t>npu_hardware，rNPU_gw_change 可注入</t>
         </is>
       </c>
       <c r="D348" s="3" t="inlineStr">
@@ -20835,7 +20835,7 @@
       </c>
       <c r="C349" s="3" t="inlineStr">
         <is>
-          <t>rNPU_gw_change 可注入</t>
+          <t>npu_hardware，rNPU_gw_change 可注入</t>
         </is>
       </c>
       <c r="D349" s="3" t="inlineStr">
@@ -20898,7 +20898,7 @@
       </c>
       <c r="C350" s="3" t="inlineStr">
         <is>
-          <t>当前网关已是 10.30.12.254</t>
+          <t>npu_hardware，当前网关已是 10.30.12.254</t>
         </is>
       </c>
       <c r="D350" s="3" t="inlineStr">
@@ -20954,7 +20954,7 @@
       </c>
       <c r="C351" s="3" t="inlineStr">
         <is>
-          <t>已用 hccn_tool -i 2 -ip -g 查出 NPU IP=10.30.12.9/24，当前网关=10.30.12.254</t>
+          <t>npu_hardware，已用 hccn_tool -i 2 -ip -g 查出 NPU IP=10.30.12.9/24，当前网关=10.30.12.254</t>
         </is>
       </c>
       <c r="D351" s="3" t="inlineStr">
@@ -21011,7 +21011,7 @@
       </c>
       <c r="C352" s="3" t="inlineStr">
         <is>
-          <t>NPU IP 在 10.30.12.0/24</t>
+          <t>npu_hardware，NPU IP 在 10.30.12.0/24</t>
         </is>
       </c>
       <c r="D352" s="3" t="inlineStr">
@@ -21067,7 +21067,7 @@
       </c>
       <c r="C353" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_gw_change</t>
+          <t>npu_hardware，已 clean rNPU_gw_change</t>
         </is>
       </c>
       <c r="D353" s="3" t="inlineStr">
@@ -21126,7 +21126,7 @@
       </c>
       <c r="C354" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_ip_change</t>
+          <t>npu_hardware，已注入 rNPU_ip_change</t>
         </is>
       </c>
       <c r="D354" s="3" t="inlineStr">
@@ -21185,7 +21185,7 @@
       </c>
       <c r="C355" s="3" t="inlineStr">
         <is>
-          <t>已查出 chip0 原 IP/掩码，新 IP 与原值不同</t>
+          <t>npu_hardware，已查出 chip0 原 IP/掩码，新 IP 与原值不同</t>
         </is>
       </c>
       <c r="D355" s="3" t="inlineStr">
@@ -21248,7 +21248,7 @@
       </c>
       <c r="C356" s="3" t="inlineStr">
         <is>
-          <t>rNPU_ip_change 可注入</t>
+          <t>npu_hardware，rNPU_ip_change 可注入</t>
         </is>
       </c>
       <c r="D356" s="3" t="inlineStr">
@@ -21305,7 +21305,7 @@
       </c>
       <c r="C357" s="3" t="inlineStr">
         <is>
-          <t>rNPU_ip_change 可注入</t>
+          <t>npu_hardware，rNPU_ip_change 可注入</t>
         </is>
       </c>
       <c r="D357" s="3" t="inlineStr">
@@ -21362,7 +21362,7 @@
       </c>
       <c r="C358" s="3" t="inlineStr">
         <is>
-          <t>rNPU_ip_change 可注入</t>
+          <t>npu_hardware，rNPU_ip_change 可注入</t>
         </is>
       </c>
       <c r="D358" s="3" t="inlineStr">
@@ -21419,7 +21419,7 @@
       </c>
       <c r="C359" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_ip_change</t>
+          <t>npu_hardware，已 clean rNPU_ip_change</t>
         </is>
       </c>
       <c r="D359" s="3" t="inlineStr">
@@ -21478,7 +21478,7 @@
       </c>
       <c r="C360" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_ip_change</t>
+          <t>npu_hardware，已注入 rNPU_ip_change</t>
         </is>
       </c>
       <c r="D360" s="3" t="inlineStr">
@@ -21537,7 +21537,7 @@
       </c>
       <c r="C361" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_ip_change</t>
+          <t>npu_hardware，已注入 rNPU_ip_change</t>
         </is>
       </c>
       <c r="D361" s="3" t="inlineStr">
@@ -21595,7 +21595,7 @@
       </c>
       <c r="C362" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_ip_change</t>
+          <t>npu_hardware，已注入 rNPU_ip_change</t>
         </is>
       </c>
       <c r="D362" s="3" t="inlineStr">
@@ -21653,7 +21653,7 @@
       </c>
       <c r="C363" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_ip_change</t>
+          <t>npu_hardware，已注入 rNPU_ip_change</t>
         </is>
       </c>
       <c r="D363" s="3" t="inlineStr">
@@ -21712,7 +21712,7 @@
       </c>
       <c r="C364" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_ip_change</t>
+          <t>npu_hardware，已注入 rNPU_ip_change</t>
         </is>
       </c>
       <c r="D364" s="3" t="inlineStr">
@@ -21770,7 +21770,7 @@
       </c>
       <c r="C365" s="3" t="inlineStr">
         <is>
-          <t>rNPU_ip_change 可注入</t>
+          <t>npu_hardware，rNPU_ip_change 可注入</t>
         </is>
       </c>
       <c r="D365" s="3" t="inlineStr">
@@ -21829,7 +21829,7 @@
       </c>
       <c r="C366" s="3" t="inlineStr">
         <is>
-          <t>rNPU_ip_change 可注入</t>
+          <t>npu_hardware，rNPU_ip_change 可注入</t>
         </is>
       </c>
       <c r="D366" s="3" t="inlineStr">
@@ -21892,7 +21892,7 @@
       </c>
       <c r="C367" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_ip_change</t>
+          <t>npu_hardware，已 clean rNPU_ip_change</t>
         </is>
       </c>
       <c r="D367" s="3" t="inlineStr">
@@ -21951,7 +21951,7 @@
       </c>
       <c r="C368" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iproute_add</t>
+          <t>npu_hardware，已注入 rNPU_iproute_add</t>
         </is>
       </c>
       <c r="D368" s="3" t="inlineStr">
@@ -22010,7 +22010,7 @@
       </c>
       <c r="C369" s="3" t="inlineStr">
         <is>
-          <t>rNPU_iproute_add 可注入</t>
+          <t>npu_hardware，rNPU_iproute_add 可注入</t>
         </is>
       </c>
       <c r="D369" s="3" t="inlineStr">
@@ -22067,7 +22067,7 @@
       </c>
       <c r="C370" s="3" t="inlineStr">
         <is>
-          <t>rNPU_iproute_add 可注入</t>
+          <t>npu_hardware，rNPU_iproute_add 可注入</t>
         </is>
       </c>
       <c r="D370" s="3" t="inlineStr">
@@ -22124,7 +22124,7 @@
       </c>
       <c r="C371" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_iproute_add</t>
+          <t>npu_hardware，已 clean rNPU_iproute_add</t>
         </is>
       </c>
       <c r="D371" s="3" t="inlineStr">
@@ -22183,7 +22183,7 @@
       </c>
       <c r="C372" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iproute_add</t>
+          <t>npu_hardware，已注入 rNPU_iproute_add</t>
         </is>
       </c>
       <c r="D372" s="3" t="inlineStr">
@@ -22242,7 +22242,7 @@
       </c>
       <c r="C373" s="3" t="inlineStr">
         <is>
-          <t>chip2</t>
+          <t>npu_hardware，chip2</t>
         </is>
       </c>
       <c r="D373" s="3" t="inlineStr">
@@ -22299,7 +22299,7 @@
       </c>
       <c r="C374" s="3" t="inlineStr">
         <is>
-          <t>rNPU_iproute_add 可注入</t>
+          <t>npu_hardware，rNPU_iproute_add 可注入</t>
         </is>
       </c>
       <c r="D374" s="3" t="inlineStr">
@@ -22356,7 +22356,7 @@
       </c>
       <c r="C375" s="3" t="inlineStr">
         <is>
-          <t>chip2，NPU IP/网关已查，dev=eth2</t>
+          <t>npu_hardware，chip2，NPU IP/网关已查，dev=eth2</t>
         </is>
       </c>
       <c r="D375" s="3" t="inlineStr">
@@ -22413,7 +22413,7 @@
       </c>
       <c r="C376" s="3" t="inlineStr">
         <is>
-          <t>chip2</t>
+          <t>npu_hardware，chip2</t>
         </is>
       </c>
       <c r="D376" s="3" t="inlineStr">
@@ -22470,7 +22470,7 @@
       </c>
       <c r="C377" s="3" t="inlineStr">
         <is>
-          <t>chip2</t>
+          <t>npu_hardware，chip2</t>
         </is>
       </c>
       <c r="D377" s="3" t="inlineStr">
@@ -22527,7 +22527,7 @@
       </c>
       <c r="C378" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iproute_add</t>
+          <t>npu_hardware，已注入 rNPU_iproute_add</t>
         </is>
       </c>
       <c r="D378" s="3" t="inlineStr">
@@ -22585,7 +22585,7 @@
       </c>
       <c r="C379" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iproute_add</t>
+          <t>npu_hardware，已注入 rNPU_iproute_add</t>
         </is>
       </c>
       <c r="D379" s="3" t="inlineStr">
@@ -22643,7 +22643,7 @@
       </c>
       <c r="C380" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iproute_add</t>
+          <t>npu_hardware，已注入 rNPU_iproute_add</t>
         </is>
       </c>
       <c r="D380" s="3" t="inlineStr">
@@ -22702,7 +22702,7 @@
       </c>
       <c r="C381" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iproute_add</t>
+          <t>npu_hardware，已注入 rNPU_iproute_add</t>
         </is>
       </c>
       <c r="D381" s="3" t="inlineStr">
@@ -22760,7 +22760,7 @@
       </c>
       <c r="C382" s="3" t="inlineStr">
         <is>
-          <t>rNPU_iproute_add 可注入</t>
+          <t>npu_hardware，rNPU_iproute_add 可注入</t>
         </is>
       </c>
       <c r="D382" s="3" t="inlineStr">
@@ -22819,7 +22819,7 @@
       </c>
       <c r="C383" s="3" t="inlineStr">
         <is>
-          <t>已查出 chip2 的 NPU IP/网关与真实 dev（示例 eth2），ip 选未占用网段</t>
+          <t>npu_hardware，已查出 chip2 的 NPU IP/网关与真实 dev（示例 eth2），ip 选未占用网段</t>
         </is>
       </c>
       <c r="D383" s="3" t="inlineStr">
@@ -22880,7 +22880,7 @@
       </c>
       <c r="C384" s="3" t="inlineStr">
         <is>
-          <t>rNPU_iproute_add 可注入</t>
+          <t>npu_hardware，rNPU_iproute_add 可注入</t>
         </is>
       </c>
       <c r="D384" s="3" t="inlineStr">
@@ -22943,7 +22943,7 @@
       </c>
       <c r="C385" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_iproute_add</t>
+          <t>npu_hardware，已 clean rNPU_iproute_add</t>
         </is>
       </c>
       <c r="D385" s="3" t="inlineStr">
@@ -23002,7 +23002,7 @@
       </c>
       <c r="C386" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iproute_del</t>
+          <t>npu_hardware，已注入 rNPU_iproute_del</t>
         </is>
       </c>
       <c r="D386" s="3" t="inlineStr">
@@ -23061,7 +23061,7 @@
       </c>
       <c r="C387" s="3" t="inlineStr">
         <is>
-          <t>rNPU_iproute_del 可注入</t>
+          <t>npu_hardware，rNPU_iproute_del 可注入</t>
         </is>
       </c>
       <c r="D387" s="3" t="inlineStr">
@@ -23118,7 +23118,7 @@
       </c>
       <c r="C388" s="3" t="inlineStr">
         <is>
-          <t>rNPU_iproute_del 可注入</t>
+          <t>npu_hardware，rNPU_iproute_del 可注入</t>
         </is>
       </c>
       <c r="D388" s="3" t="inlineStr">
@@ -23175,7 +23175,7 @@
       </c>
       <c r="C389" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_iproute_del</t>
+          <t>npu_hardware，已 clean rNPU_iproute_del</t>
         </is>
       </c>
       <c r="D389" s="3" t="inlineStr">
@@ -23234,7 +23234,7 @@
       </c>
       <c r="C390" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iproute_del</t>
+          <t>npu_hardware，已注入 rNPU_iproute_del</t>
         </is>
       </c>
       <c r="D390" s="3" t="inlineStr">
@@ -23293,7 +23293,7 @@
       </c>
       <c r="C391" s="3" t="inlineStr">
         <is>
-          <t>rNPU_iproute_del 可注入</t>
+          <t>npu_hardware，rNPU_iproute_del 可注入</t>
         </is>
       </c>
       <c r="D391" s="3" t="inlineStr">
@@ -23350,7 +23350,7 @@
       </c>
       <c r="C392" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iproute_del</t>
+          <t>npu_hardware，已注入 rNPU_iproute_del</t>
         </is>
       </c>
       <c r="D392" s="3" t="inlineStr">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C393" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iproute_del</t>
+          <t>npu_hardware，已注入 rNPU_iproute_del</t>
         </is>
       </c>
       <c r="D393" s="3" t="inlineStr">
@@ -23466,7 +23466,7 @@
       </c>
       <c r="C394" s="3" t="inlineStr">
         <is>
-          <t>目标 ip_route 已存在（先 rNPU_iproute_add 创建）</t>
+          <t>npu_hardware，目标 ip_route 已存在（先 rNPU_iproute_add 创建）</t>
         </is>
       </c>
       <c r="D394" s="3" t="inlineStr">
@@ -23527,7 +23527,7 @@
       </c>
       <c r="C395" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iproute_del</t>
+          <t>npu_hardware，已注入 rNPU_iproute_del</t>
         </is>
       </c>
       <c r="D395" s="3" t="inlineStr">
@@ -23586,7 +23586,7 @@
       </c>
       <c r="C396" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iproute_del</t>
+          <t>npu_hardware，已注入 rNPU_iproute_del</t>
         </is>
       </c>
       <c r="D396" s="3" t="inlineStr">
@@ -23644,7 +23644,7 @@
       </c>
       <c r="C397" s="3" t="inlineStr">
         <is>
-          <t>rNPU_iproute_del 可注入</t>
+          <t>npu_hardware，rNPU_iproute_del 可注入</t>
         </is>
       </c>
       <c r="D397" s="3" t="inlineStr">
@@ -23703,7 +23703,7 @@
       </c>
       <c r="C398" s="3" t="inlineStr">
         <is>
-          <t>rNPU_iproute_del 可注入</t>
+          <t>npu_hardware，rNPU_iproute_del 可注入</t>
         </is>
       </c>
       <c r="D398" s="3" t="inlineStr">
@@ -23766,7 +23766,7 @@
       </c>
       <c r="C399" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_iproute_del</t>
+          <t>npu_hardware，已 clean rNPU_iproute_del</t>
         </is>
       </c>
       <c r="D399" s="3" t="inlineStr">
@@ -23825,7 +23825,7 @@
       </c>
       <c r="C400" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iprule_add</t>
+          <t>npu_hardware，已注入 rNPU_iprule_add</t>
         </is>
       </c>
       <c r="D400" s="3" t="inlineStr">
@@ -23884,7 +23884,7 @@
       </c>
       <c r="C401" s="3" t="inlineStr">
         <is>
-          <t>rNPU_iprule_add 可注入</t>
+          <t>npu_hardware，rNPU_iprule_add 可注入</t>
         </is>
       </c>
       <c r="D401" s="3" t="inlineStr">
@@ -23941,7 +23941,7 @@
       </c>
       <c r="C402" s="3" t="inlineStr">
         <is>
-          <t>rNPU_iprule_add 可注入</t>
+          <t>npu_hardware，rNPU_iprule_add 可注入</t>
         </is>
       </c>
       <c r="D402" s="3" t="inlineStr">
@@ -23998,7 +23998,7 @@
       </c>
       <c r="C403" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_iprule_add</t>
+          <t>npu_hardware，已 clean rNPU_iprule_add</t>
         </is>
       </c>
       <c r="D403" s="3" t="inlineStr">
@@ -24057,7 +24057,7 @@
       </c>
       <c r="C404" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iprule_add</t>
+          <t>npu_hardware，已注入 rNPU_iprule_add</t>
         </is>
       </c>
       <c r="D404" s="3" t="inlineStr">
@@ -24116,7 +24116,7 @@
       </c>
       <c r="C405" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iprule_add</t>
+          <t>npu_hardware，已注入 rNPU_iprule_add</t>
         </is>
       </c>
       <c r="D405" s="3" t="inlineStr">
@@ -24174,7 +24174,7 @@
       </c>
       <c r="C406" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iprule_add</t>
+          <t>npu_hardware，已注入 rNPU_iprule_add</t>
         </is>
       </c>
       <c r="D406" s="3" t="inlineStr">
@@ -24232,7 +24232,7 @@
       </c>
       <c r="C407" s="3" t="inlineStr">
         <is>
-          <t>chip2</t>
+          <t>npu_hardware，chip2</t>
         </is>
       </c>
       <c r="D407" s="3" t="inlineStr">
@@ -24289,7 +24289,7 @@
       </c>
       <c r="C408" s="3" t="inlineStr">
         <is>
-          <t>rNPU_iprule_add 可注入</t>
+          <t>npu_hardware，rNPU_iprule_add 可注入</t>
         </is>
       </c>
       <c r="D408" s="3" t="inlineStr">
@@ -24346,7 +24346,7 @@
       </c>
       <c r="C409" s="3" t="inlineStr">
         <is>
-          <t>chip2，ip=10.30.12.210</t>
+          <t>npu_hardware，chip2，ip=10.30.12.210</t>
         </is>
       </c>
       <c r="D409" s="3" t="inlineStr">
@@ -24403,7 +24403,7 @@
       </c>
       <c r="C410" s="3" t="inlineStr">
         <is>
-          <t>chip2</t>
+          <t>npu_hardware，chip2</t>
         </is>
       </c>
       <c r="D410" s="3" t="inlineStr">
@@ -24460,7 +24460,7 @@
       </c>
       <c r="C411" s="3" t="inlineStr">
         <is>
-          <t>chip2</t>
+          <t>npu_hardware，chip2</t>
         </is>
       </c>
       <c r="D411" s="3" t="inlineStr">
@@ -24517,7 +24517,7 @@
       </c>
       <c r="C412" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iprule_add</t>
+          <t>npu_hardware，已注入 rNPU_iprule_add</t>
         </is>
       </c>
       <c r="D412" s="3" t="inlineStr">
@@ -24576,7 +24576,7 @@
       </c>
       <c r="C413" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iprule_add</t>
+          <t>npu_hardware，已注入 rNPU_iprule_add</t>
         </is>
       </c>
       <c r="D413" s="3" t="inlineStr">
@@ -24634,7 +24634,7 @@
       </c>
       <c r="C414" s="3" t="inlineStr">
         <is>
-          <t>rNPU_iprule_add 可注入</t>
+          <t>npu_hardware，rNPU_iprule_add 可注入</t>
         </is>
       </c>
       <c r="D414" s="3" t="inlineStr">
@@ -24693,7 +24693,7 @@
       </c>
       <c r="C415" s="3" t="inlineStr">
         <is>
-          <t>已查出 chip2 的 NPU 网段，ip 选未占用地址，table 选未占用表号</t>
+          <t>npu_hardware，已查出 chip2 的 NPU 网段，ip 选未占用地址，table 选未占用表号</t>
         </is>
       </c>
       <c r="D415" s="3" t="inlineStr">
@@ -24754,7 +24754,7 @@
       </c>
       <c r="C416" s="3" t="inlineStr">
         <is>
-          <t>rNPU_iprule_add 可注入</t>
+          <t>npu_hardware，rNPU_iprule_add 可注入</t>
         </is>
       </c>
       <c r="D416" s="3" t="inlineStr">
@@ -24817,7 +24817,7 @@
       </c>
       <c r="C417" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_iprule_add</t>
+          <t>npu_hardware，已 clean rNPU_iprule_add</t>
         </is>
       </c>
       <c r="D417" s="3" t="inlineStr">
@@ -24876,7 +24876,7 @@
       </c>
       <c r="C418" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iprule_del</t>
+          <t>npu_hardware，已注入 rNPU_iprule_del</t>
         </is>
       </c>
       <c r="D418" s="3" t="inlineStr">
@@ -24935,7 +24935,7 @@
       </c>
       <c r="C419" s="3" t="inlineStr">
         <is>
-          <t>rNPU_iprule_del 可注入</t>
+          <t>npu_hardware，rNPU_iprule_del 可注入</t>
         </is>
       </c>
       <c r="D419" s="3" t="inlineStr">
@@ -24992,7 +24992,7 @@
       </c>
       <c r="C420" s="3" t="inlineStr">
         <is>
-          <t>rNPU_iprule_del 可注入</t>
+          <t>npu_hardware，rNPU_iprule_del 可注入</t>
         </is>
       </c>
       <c r="D420" s="3" t="inlineStr">
@@ -25049,7 +25049,7 @@
       </c>
       <c r="C421" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_iprule_del</t>
+          <t>npu_hardware，已 clean rNPU_iprule_del</t>
         </is>
       </c>
       <c r="D421" s="3" t="inlineStr">
@@ -25108,7 +25108,7 @@
       </c>
       <c r="C422" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iprule_del</t>
+          <t>npu_hardware，已注入 rNPU_iprule_del</t>
         </is>
       </c>
       <c r="D422" s="3" t="inlineStr">
@@ -25167,7 +25167,7 @@
       </c>
       <c r="C423" s="3" t="inlineStr">
         <is>
-          <t>rNPU_iprule_del 可注入</t>
+          <t>npu_hardware，rNPU_iprule_del 可注入</t>
         </is>
       </c>
       <c r="D423" s="3" t="inlineStr">
@@ -25224,7 +25224,7 @@
       </c>
       <c r="C424" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iprule_del</t>
+          <t>npu_hardware，已注入 rNPU_iprule_del</t>
         </is>
       </c>
       <c r="D424" s="3" t="inlineStr">
@@ -25282,7 +25282,7 @@
       </c>
       <c r="C425" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iprule_del</t>
+          <t>npu_hardware，已注入 rNPU_iprule_del</t>
         </is>
       </c>
       <c r="D425" s="3" t="inlineStr">
@@ -25340,7 +25340,7 @@
       </c>
       <c r="C426" s="3" t="inlineStr">
         <is>
-          <t>目标 ip rule 已存在（先 rNPU_iprule_add 创建）</t>
+          <t>npu_hardware，目标 ip rule 已存在（先 rNPU_iprule_add 创建）</t>
         </is>
       </c>
       <c r="D426" s="3" t="inlineStr">
@@ -25401,7 +25401,7 @@
       </c>
       <c r="C427" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iprule_del</t>
+          <t>npu_hardware，已注入 rNPU_iprule_del</t>
         </is>
       </c>
       <c r="D427" s="3" t="inlineStr">
@@ -25460,7 +25460,7 @@
       </c>
       <c r="C428" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iprule_del</t>
+          <t>npu_hardware，已注入 rNPU_iprule_del</t>
         </is>
       </c>
       <c r="D428" s="3" t="inlineStr">
@@ -25518,7 +25518,7 @@
       </c>
       <c r="C429" s="3" t="inlineStr">
         <is>
-          <t>rNPU_iprule_del 可注入</t>
+          <t>npu_hardware，rNPU_iprule_del 可注入</t>
         </is>
       </c>
       <c r="D429" s="3" t="inlineStr">
@@ -25577,7 +25577,7 @@
       </c>
       <c r="C430" s="3" t="inlineStr">
         <is>
-          <t>rNPU_iprule_del 可注入</t>
+          <t>npu_hardware，rNPU_iprule_del 可注入</t>
         </is>
       </c>
       <c r="D430" s="3" t="inlineStr">
@@ -25640,7 +25640,7 @@
       </c>
       <c r="C431" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_iprule_del</t>
+          <t>npu_hardware，已 clean rNPU_iprule_del</t>
         </is>
       </c>
       <c r="D431" s="3" t="inlineStr">
@@ -25699,7 +25699,7 @@
       </c>
       <c r="C432" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_link_down</t>
+          <t>npu_hardware，已注入 rNPU_link_down</t>
         </is>
       </c>
       <c r="D432" s="3" t="inlineStr">
@@ -25758,7 +25758,7 @@
       </c>
       <c r="C433" s="3" t="inlineStr">
         <is>
-          <t>Atlas NPU 硬件+hccn_tool，root，chip0 可用</t>
+          <t>npu_hardware，Atlas NPU 硬件+hccn_tool，root，chip0 可用</t>
         </is>
       </c>
       <c r="D433" s="3" t="inlineStr">
@@ -25819,7 +25819,7 @@
       </c>
       <c r="C434" s="3" t="inlineStr">
         <is>
-          <t>rNPU_link_down 可注入</t>
+          <t>npu_hardware，rNPU_link_down 可注入</t>
         </is>
       </c>
       <c r="D434" s="3" t="inlineStr">
@@ -25876,7 +25876,7 @@
       </c>
       <c r="C435" s="3" t="inlineStr">
         <is>
-          <t>rNPU_link_down 可注入</t>
+          <t>npu_hardware，rNPU_link_down 可注入</t>
         </is>
       </c>
       <c r="D435" s="3" t="inlineStr">
@@ -25933,7 +25933,7 @@
       </c>
       <c r="C436" s="3" t="inlineStr">
         <is>
-          <t>rNPU_link_down 可注入</t>
+          <t>npu_hardware，rNPU_link_down 可注入</t>
         </is>
       </c>
       <c r="D436" s="3" t="inlineStr">
@@ -25990,7 +25990,7 @@
       </c>
       <c r="C437" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_link_down</t>
+          <t>npu_hardware，已 clean rNPU_link_down</t>
         </is>
       </c>
       <c r="D437" s="3" t="inlineStr">
@@ -26049,7 +26049,7 @@
       </c>
       <c r="C438" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_link_down</t>
+          <t>npu_hardware，已注入 rNPU_link_down</t>
         </is>
       </c>
       <c r="D438" s="3" t="inlineStr">
@@ -26108,7 +26108,7 @@
       </c>
       <c r="C439" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_link_down</t>
+          <t>npu_hardware，已注入 rNPU_link_down</t>
         </is>
       </c>
       <c r="D439" s="3" t="inlineStr">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C440" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_link_down</t>
+          <t>npu_hardware，已注入 rNPU_link_down</t>
         </is>
       </c>
       <c r="D440" s="3" t="inlineStr">
@@ -26224,7 +26224,7 @@
       </c>
       <c r="C441" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_link_down</t>
+          <t>npu_hardware，已注入 rNPU_link_down</t>
         </is>
       </c>
       <c r="D441" s="3" t="inlineStr">
@@ -26283,7 +26283,7 @@
       </c>
       <c r="C442" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_link_down</t>
+          <t>npu_hardware，已注入 rNPU_link_down</t>
         </is>
       </c>
       <c r="D442" s="3" t="inlineStr">
@@ -26341,7 +26341,7 @@
       </c>
       <c r="C443" s="3" t="inlineStr">
         <is>
-          <t>rNPU_link_down 可注入</t>
+          <t>npu_hardware，rNPU_link_down 可注入</t>
         </is>
       </c>
       <c r="D443" s="3" t="inlineStr">
@@ -26400,7 +26400,7 @@
       </c>
       <c r="C444" s="3" t="inlineStr">
         <is>
-          <t>rNPU_link_down 可注入</t>
+          <t>npu_hardware，rNPU_link_down 可注入</t>
         </is>
       </c>
       <c r="D444" s="3" t="inlineStr">
@@ -26463,7 +26463,7 @@
       </c>
       <c r="C445" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_link_down</t>
+          <t>npu_hardware，已 clean rNPU_link_down</t>
         </is>
       </c>
       <c r="D445" s="3" t="inlineStr">
@@ -26522,7 +26522,7 @@
       </c>
       <c r="C446" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_mtu_mismatch</t>
+          <t>npu_hardware，已注入 rNPU_mtu_mismatch</t>
         </is>
       </c>
       <c r="D446" s="3" t="inlineStr">
@@ -26581,7 +26581,7 @@
       </c>
       <c r="C447" s="3" t="inlineStr">
         <is>
-          <t>已查出 chip2 当前 MTU=1500，size 选不同值（如 1280）</t>
+          <t>npu_hardware，已查出 chip2 当前 MTU=1500，size 选不同值（如 1280）</t>
         </is>
       </c>
       <c r="D447" s="3" t="inlineStr">
@@ -26644,7 +26644,7 @@
       </c>
       <c r="C448" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_mtu_mismatch</t>
+          <t>npu_hardware，已 clean rNPU_mtu_mismatch</t>
         </is>
       </c>
       <c r="D448" s="3" t="inlineStr">
@@ -26703,7 +26703,7 @@
       </c>
       <c r="C449" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_mtu_mismatch</t>
+          <t>npu_hardware，已注入 rNPU_mtu_mismatch</t>
         </is>
       </c>
       <c r="D449" s="3" t="inlineStr">
@@ -26762,7 +26762,7 @@
       </c>
       <c r="C450" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_mtu_mismatch</t>
+          <t>npu_hardware，已注入 rNPU_mtu_mismatch</t>
         </is>
       </c>
       <c r="D450" s="3" t="inlineStr">
@@ -26820,7 +26820,7 @@
       </c>
       <c r="C451" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_mtu_mismatch</t>
+          <t>npu_hardware，已注入 rNPU_mtu_mismatch</t>
         </is>
       </c>
       <c r="D451" s="3" t="inlineStr">
@@ -26878,7 +26878,7 @@
       </c>
       <c r="C452" s="3" t="inlineStr">
         <is>
-          <t>Atlas NPU+hccn_tool，root</t>
+          <t>npu_hardware，Atlas NPU+hccn_tool，root</t>
         </is>
       </c>
       <c r="D452" s="3" t="inlineStr">
@@ -26937,7 +26937,7 @@
       </c>
       <c r="C453" s="3" t="inlineStr">
         <is>
-          <t>rNPU_mtu_mismatch 可注入</t>
+          <t>npu_hardware，rNPU_mtu_mismatch 可注入</t>
         </is>
       </c>
       <c r="D453" s="3" t="inlineStr">
@@ -26994,7 +26994,7 @@
       </c>
       <c r="C454" s="3" t="inlineStr">
         <is>
-          <t>rNPU_mtu_mismatch 可注入</t>
+          <t>npu_hardware，rNPU_mtu_mismatch 可注入</t>
         </is>
       </c>
       <c r="D454" s="3" t="inlineStr">
@@ -27051,7 +27051,7 @@
       </c>
       <c r="C455" s="3" t="inlineStr">
         <is>
-          <t>rNPU_mtu_mismatch 可注入</t>
+          <t>npu_hardware，rNPU_mtu_mismatch 可注入</t>
         </is>
       </c>
       <c r="D455" s="3" t="inlineStr">
@@ -27108,7 +27108,7 @@
       </c>
       <c r="C456" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_mtu_mismatch</t>
+          <t>npu_hardware，已注入 rNPU_mtu_mismatch</t>
         </is>
       </c>
       <c r="D456" s="3" t="inlineStr">
@@ -27167,7 +27167,7 @@
       </c>
       <c r="C457" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_mtu_mismatch</t>
+          <t>npu_hardware，已注入 rNPU_mtu_mismatch</t>
         </is>
       </c>
       <c r="D457" s="3" t="inlineStr">
@@ -27225,7 +27225,7 @@
       </c>
       <c r="C458" s="3" t="inlineStr">
         <is>
-          <t>rNPU_mtu_mismatch 可注入</t>
+          <t>npu_hardware，rNPU_mtu_mismatch 可注入</t>
         </is>
       </c>
       <c r="D458" s="3" t="inlineStr">
@@ -27284,7 +27284,7 @@
       </c>
       <c r="C459" s="3" t="inlineStr">
         <is>
-          <t>rNPU_mtu_mismatch 可注入</t>
+          <t>npu_hardware，rNPU_mtu_mismatch 可注入</t>
         </is>
       </c>
       <c r="D459" s="3" t="inlineStr">
@@ -27347,7 +27347,7 @@
       </c>
       <c r="C460" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_mtu_mismatch</t>
+          <t>npu_hardware，已 clean rNPU_mtu_mismatch</t>
         </is>
       </c>
       <c r="D460" s="3" t="inlineStr">
@@ -27406,7 +27406,7 @@
       </c>
       <c r="C461" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_netdetect_change</t>
+          <t>npu_hardware，已注入 rNPU_netdetect_change</t>
         </is>
       </c>
       <c r="D461" s="3" t="inlineStr">
@@ -27465,7 +27465,7 @@
       </c>
       <c r="C462" s="3" t="inlineStr">
         <is>
-          <t>Atlas NPU+hccn_tool，root，chip0 可用</t>
+          <t>npu_hardware，Atlas NPU+hccn_tool，root，chip0 可用</t>
         </is>
       </c>
       <c r="D462" s="3" t="inlineStr">
@@ -27526,7 +27526,7 @@
       </c>
       <c r="C463" s="3" t="inlineStr">
         <is>
-          <t>rNPU_netdetect_change 可注入</t>
+          <t>npu_hardware，rNPU_netdetect_change 可注入</t>
         </is>
       </c>
       <c r="D463" s="3" t="inlineStr">
@@ -27583,7 +27583,7 @@
       </c>
       <c r="C464" s="3" t="inlineStr">
         <is>
-          <t>rNPU_netdetect_change 可注入</t>
+          <t>npu_hardware，rNPU_netdetect_change 可注入</t>
         </is>
       </c>
       <c r="D464" s="3" t="inlineStr">
@@ -27640,7 +27640,7 @@
       </c>
       <c r="C465" s="3" t="inlineStr">
         <is>
-          <t>rNPU_netdetect_change 可注入</t>
+          <t>npu_hardware，rNPU_netdetect_change 可注入</t>
         </is>
       </c>
       <c r="D465" s="3" t="inlineStr">
@@ -27697,7 +27697,7 @@
       </c>
       <c r="C466" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_netdetect_change</t>
+          <t>npu_hardware，已 clean rNPU_netdetect_change</t>
         </is>
       </c>
       <c r="D466" s="3" t="inlineStr">
@@ -27756,7 +27756,7 @@
       </c>
       <c r="C467" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_netdetect_change</t>
+          <t>npu_hardware，已注入 rNPU_netdetect_change</t>
         </is>
       </c>
       <c r="D467" s="3" t="inlineStr">
@@ -27815,7 +27815,7 @@
       </c>
       <c r="C468" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_netdetect_change</t>
+          <t>npu_hardware，已注入 rNPU_netdetect_change</t>
         </is>
       </c>
       <c r="D468" s="3" t="inlineStr">
@@ -27873,7 +27873,7 @@
       </c>
       <c r="C469" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_netdetect_change</t>
+          <t>npu_hardware，已注入 rNPU_netdetect_change</t>
         </is>
       </c>
       <c r="D469" s="3" t="inlineStr">
@@ -27931,7 +27931,7 @@
       </c>
       <c r="C470" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_netdetect_change</t>
+          <t>npu_hardware，已注入 rNPU_netdetect_change</t>
         </is>
       </c>
       <c r="D470" s="3" t="inlineStr">
@@ -27990,7 +27990,7 @@
       </c>
       <c r="C471" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_netdetect_change</t>
+          <t>npu_hardware，已注入 rNPU_netdetect_change</t>
         </is>
       </c>
       <c r="D471" s="3" t="inlineStr">
@@ -28048,7 +28048,7 @@
       </c>
       <c r="C472" s="3" t="inlineStr">
         <is>
-          <t>rNPU_netdetect_change 可注入</t>
+          <t>npu_hardware，rNPU_netdetect_change 可注入</t>
         </is>
       </c>
       <c r="D472" s="3" t="inlineStr">
@@ -28107,7 +28107,7 @@
       </c>
       <c r="C473" s="3" t="inlineStr">
         <is>
-          <t>rNPU_netdetect_change 可注入</t>
+          <t>npu_hardware，rNPU_netdetect_change 可注入</t>
         </is>
       </c>
       <c r="D473" s="3" t="inlineStr">
@@ -28170,7 +28170,7 @@
       </c>
       <c r="C474" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_netdetect_change</t>
+          <t>npu_hardware，已 clean rNPU_netdetect_change</t>
         </is>
       </c>
       <c r="D474" s="3" t="inlineStr">
@@ -28229,7 +28229,7 @@
       </c>
       <c r="C475" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_roce_port_change</t>
+          <t>npu_hardware，已注入 rNPU_roce_port_change</t>
         </is>
       </c>
       <c r="D475" s="3" t="inlineStr">
@@ -28288,7 +28288,7 @@
       </c>
       <c r="C476" s="3" t="inlineStr">
         <is>
-          <t>Atlas NPU+hccn_tool，root，chip0 可用</t>
+          <t>npu_hardware，Atlas NPU+hccn_tool，root，chip0 可用</t>
         </is>
       </c>
       <c r="D476" s="3" t="inlineStr">
@@ -28349,7 +28349,7 @@
       </c>
       <c r="C477" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_roce_port_change</t>
+          <t>npu_hardware，已 clean rNPU_roce_port_change</t>
         </is>
       </c>
       <c r="D477" s="3" t="inlineStr">
@@ -28408,7 +28408,7 @@
       </c>
       <c r="C478" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_roce_port_change</t>
+          <t>npu_hardware，已注入 rNPU_roce_port_change</t>
         </is>
       </c>
       <c r="D478" s="3" t="inlineStr">
@@ -28467,7 +28467,7 @@
       </c>
       <c r="C479" s="3" t="inlineStr">
         <is>
-          <t>rNPU_roce_port_change 可注入</t>
+          <t>npu_hardware，rNPU_roce_port_change 可注入</t>
         </is>
       </c>
       <c r="D479" s="3" t="inlineStr">
@@ -28524,7 +28524,7 @@
       </c>
       <c r="C480" s="3" t="inlineStr">
         <is>
-          <t>rNPU_roce_port_change 可注入</t>
+          <t>npu_hardware，rNPU_roce_port_change 可注入</t>
         </is>
       </c>
       <c r="D480" s="3" t="inlineStr">
@@ -28581,7 +28581,7 @@
       </c>
       <c r="C481" s="3" t="inlineStr">
         <is>
-          <t>rNPU_roce_port_change 可注入</t>
+          <t>npu_hardware，rNPU_roce_port_change 可注入</t>
         </is>
       </c>
       <c r="D481" s="3" t="inlineStr">
@@ -28638,7 +28638,7 @@
       </c>
       <c r="C482" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_roce_port_change</t>
+          <t>npu_hardware，已注入 rNPU_roce_port_change</t>
         </is>
       </c>
       <c r="D482" s="3" t="inlineStr">
@@ -28696,7 +28696,7 @@
       </c>
       <c r="C483" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_roce_port_change</t>
+          <t>npu_hardware，已注入 rNPU_roce_port_change</t>
         </is>
       </c>
       <c r="D483" s="3" t="inlineStr">
@@ -28754,7 +28754,7 @@
       </c>
       <c r="C484" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_roce_port_change</t>
+          <t>npu_hardware，已注入 rNPU_roce_port_change</t>
         </is>
       </c>
       <c r="D484" s="3" t="inlineStr">
@@ -28813,7 +28813,7 @@
       </c>
       <c r="C485" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_roce_port_change</t>
+          <t>npu_hardware，已注入 rNPU_roce_port_change</t>
         </is>
       </c>
       <c r="D485" s="3" t="inlineStr">
@@ -28871,7 +28871,7 @@
       </c>
       <c r="C486" s="3" t="inlineStr">
         <is>
-          <t>rNPU_roce_port_change 可注入</t>
+          <t>npu_hardware，rNPU_roce_port_change 可注入</t>
         </is>
       </c>
       <c r="D486" s="3" t="inlineStr">
@@ -28930,7 +28930,7 @@
       </c>
       <c r="C487" s="3" t="inlineStr">
         <is>
-          <t>rNPU_roce_port_change 可注入</t>
+          <t>npu_hardware，rNPU_roce_port_change 可注入</t>
         </is>
       </c>
       <c r="D487" s="3" t="inlineStr">
@@ -28993,7 +28993,7 @@
       </c>
       <c r="C488" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_roce_port_change</t>
+          <t>npu_hardware，已 clean rNPU_roce_port_change</t>
         </is>
       </c>
       <c r="D488" s="3" t="inlineStr">
@@ -29052,7 +29052,7 @@
       </c>
       <c r="C489" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_route_add</t>
+          <t>npu_hardware，已注入 rNPU_route_add</t>
         </is>
       </c>
       <c r="D489" s="3" t="inlineStr">
@@ -29111,7 +29111,7 @@
       </c>
       <c r="C490" s="3" t="inlineStr">
         <is>
-          <t>rNPU_route_add 可注入</t>
+          <t>npu_hardware，rNPU_route_add 可注入</t>
         </is>
       </c>
       <c r="D490" s="3" t="inlineStr">
@@ -29168,7 +29168,7 @@
       </c>
       <c r="C491" s="3" t="inlineStr">
         <is>
-          <t>rNPU_route_add 可注入</t>
+          <t>npu_hardware，rNPU_route_add 可注入</t>
         </is>
       </c>
       <c r="D491" s="3" t="inlineStr">
@@ -29225,7 +29225,7 @@
       </c>
       <c r="C492" s="3" t="inlineStr">
         <is>
-          <t>rNPU_route_add 可注入</t>
+          <t>npu_hardware，rNPU_route_add 可注入</t>
         </is>
       </c>
       <c r="D492" s="3" t="inlineStr">
@@ -29282,7 +29282,7 @@
       </c>
       <c r="C493" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_route_add</t>
+          <t>npu_hardware，已 clean rNPU_route_add</t>
         </is>
       </c>
       <c r="D493" s="3" t="inlineStr">
@@ -29341,7 +29341,7 @@
       </c>
       <c r="C494" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_route_add</t>
+          <t>npu_hardware，已注入 rNPU_route_add</t>
         </is>
       </c>
       <c r="D494" s="3" t="inlineStr">
@@ -29400,7 +29400,7 @@
       </c>
       <c r="C495" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_route_add</t>
+          <t>npu_hardware，已注入 rNPU_route_add</t>
         </is>
       </c>
       <c r="D495" s="3" t="inlineStr">
@@ -29458,7 +29458,7 @@
       </c>
       <c r="C496" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_route_add</t>
+          <t>npu_hardware，已注入 rNPU_route_add</t>
         </is>
       </c>
       <c r="D496" s="3" t="inlineStr">
@@ -29516,7 +29516,7 @@
       </c>
       <c r="C497" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_route_add</t>
+          <t>npu_hardware，已注入 rNPU_route_add</t>
         </is>
       </c>
       <c r="D497" s="3" t="inlineStr">
@@ -29575,7 +29575,7 @@
       </c>
       <c r="C498" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_route_add</t>
+          <t>npu_hardware，已注入 rNPU_route_add</t>
         </is>
       </c>
       <c r="D498" s="3" t="inlineStr">
@@ -29633,7 +29633,7 @@
       </c>
       <c r="C499" s="3" t="inlineStr">
         <is>
-          <t>rNPU_route_add 可注入</t>
+          <t>npu_hardware，rNPU_route_add 可注入</t>
         </is>
       </c>
       <c r="D499" s="3" t="inlineStr">
@@ -29692,7 +29692,7 @@
       </c>
       <c r="C500" s="3" t="inlineStr">
         <is>
-          <t>已查出 chip2 的 NPU IP/网关，address 选未占用且不与 NPU 网段冲突的网段</t>
+          <t>npu_hardware，已查出 chip2 的 NPU IP/网关，address 选未占用且不与 NPU 网段冲突的网段</t>
         </is>
       </c>
       <c r="D500" s="3" t="inlineStr">
@@ -29753,7 +29753,7 @@
       </c>
       <c r="C501" s="3" t="inlineStr">
         <is>
-          <t>rNPU_route_add 可注入</t>
+          <t>npu_hardware，rNPU_route_add 可注入</t>
         </is>
       </c>
       <c r="D501" s="3" t="inlineStr">
@@ -29816,7 +29816,7 @@
       </c>
       <c r="C502" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_route_add</t>
+          <t>npu_hardware，已 clean rNPU_route_add</t>
         </is>
       </c>
       <c r="D502" s="3" t="inlineStr">
@@ -29875,7 +29875,7 @@
       </c>
       <c r="C503" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_route_del</t>
+          <t>npu_hardware，已注入 rNPU_route_del</t>
         </is>
       </c>
       <c r="D503" s="3" t="inlineStr">
@@ -29934,7 +29934,7 @@
       </c>
       <c r="C504" s="3" t="inlineStr">
         <is>
-          <t>rNPU_route_del 可注入</t>
+          <t>npu_hardware，rNPU_route_del 可注入</t>
         </is>
       </c>
       <c r="D504" s="3" t="inlineStr">
@@ -29991,7 +29991,7 @@
       </c>
       <c r="C505" s="3" t="inlineStr">
         <is>
-          <t>rNPU_route_del 可注入</t>
+          <t>npu_hardware，rNPU_route_del 可注入</t>
         </is>
       </c>
       <c r="D505" s="3" t="inlineStr">
@@ -30048,7 +30048,7 @@
       </c>
       <c r="C506" s="3" t="inlineStr">
         <is>
-          <t>rNPU_route_del 可注入</t>
+          <t>npu_hardware，rNPU_route_del 可注入</t>
         </is>
       </c>
       <c r="D506" s="3" t="inlineStr">
@@ -30105,7 +30105,7 @@
       </c>
       <c r="C507" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_route_del</t>
+          <t>npu_hardware，已 clean rNPU_route_del</t>
         </is>
       </c>
       <c r="D507" s="3" t="inlineStr">
@@ -30164,7 +30164,7 @@
       </c>
       <c r="C508" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_route_del</t>
+          <t>npu_hardware，已注入 rNPU_route_del</t>
         </is>
       </c>
       <c r="D508" s="3" t="inlineStr">
@@ -30223,7 +30223,7 @@
       </c>
       <c r="C509" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_route_del</t>
+          <t>npu_hardware，已注入 rNPU_route_del</t>
         </is>
       </c>
       <c r="D509" s="3" t="inlineStr">
@@ -30281,7 +30281,7 @@
       </c>
       <c r="C510" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_route_del</t>
+          <t>npu_hardware，已注入 rNPU_route_del</t>
         </is>
       </c>
       <c r="D510" s="3" t="inlineStr">
@@ -30339,7 +30339,7 @@
       </c>
       <c r="C511" s="3" t="inlineStr">
         <is>
-          <t>目标路由已存在（先 rNPU_route_add 创建）</t>
+          <t>npu_hardware，目标路由已存在（先 rNPU_route_add 创建）</t>
         </is>
       </c>
       <c r="D511" s="3" t="inlineStr">
@@ -30400,7 +30400,7 @@
       </c>
       <c r="C512" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_route_del</t>
+          <t>npu_hardware，已注入 rNPU_route_del</t>
         </is>
       </c>
       <c r="D512" s="3" t="inlineStr">
@@ -30459,7 +30459,7 @@
       </c>
       <c r="C513" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_route_del</t>
+          <t>npu_hardware，已注入 rNPU_route_del</t>
         </is>
       </c>
       <c r="D513" s="3" t="inlineStr">
@@ -30517,7 +30517,7 @@
       </c>
       <c r="C514" s="3" t="inlineStr">
         <is>
-          <t>rNPU_route_del 可注入</t>
+          <t>npu_hardware，rNPU_route_del 可注入</t>
         </is>
       </c>
       <c r="D514" s="3" t="inlineStr">
@@ -30576,7 +30576,7 @@
       </c>
       <c r="C515" s="3" t="inlineStr">
         <is>
-          <t>rNPU_route_del 可注入</t>
+          <t>npu_hardware，rNPU_route_del 可注入</t>
         </is>
       </c>
       <c r="D515" s="3" t="inlineStr">
@@ -30639,7 +30639,7 @@
       </c>
       <c r="C516" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_route_del</t>
+          <t>npu_hardware，已 clean rNPU_route_del</t>
         </is>
       </c>
       <c r="D516" s="3" t="inlineStr">
@@ -33870,7 +33870,7 @@
       </c>
       <c r="C571" s="3" t="inlineStr">
         <is>
-          <t>log_level=debug</t>
+          <t>npu_hardware，log_level=debug</t>
         </is>
       </c>
       <c r="D571" s="3" t="inlineStr">
@@ -37003,7 +37003,7 @@
       </c>
       <c r="C625" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_link_down</t>
+          <t>npu_hardware，已注入 rNPU_link_down</t>
         </is>
       </c>
       <c r="D625" s="3" t="inlineStr">
@@ -37061,7 +37061,7 @@
       </c>
       <c r="C626" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_link_down</t>
+          <t>npu_hardware，已注入 rNPU_link_down</t>
         </is>
       </c>
       <c r="D626" s="3" t="inlineStr">
@@ -37120,7 +37120,7 @@
       </c>
       <c r="C627" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_ip_change</t>
+          <t>npu_hardware，已注入 rNPU_ip_change</t>
         </is>
       </c>
       <c r="D627" s="3" t="inlineStr">
@@ -37178,7 +37178,7 @@
       </c>
       <c r="C628" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_ip_change</t>
+          <t>npu_hardware，已注入 rNPU_ip_change</t>
         </is>
       </c>
       <c r="D628" s="3" t="inlineStr">
@@ -37237,7 +37237,7 @@
       </c>
       <c r="C629" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_gw_change</t>
+          <t>npu_hardware，已注入 rNPU_gw_change</t>
         </is>
       </c>
       <c r="D629" s="3" t="inlineStr">
@@ -37295,7 +37295,7 @@
       </c>
       <c r="C630" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_gw_change</t>
+          <t>npu_hardware，已注入 rNPU_gw_change</t>
         </is>
       </c>
       <c r="D630" s="3" t="inlineStr">
@@ -37354,7 +37354,7 @@
       </c>
       <c r="C631" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_arp_poison</t>
+          <t>npu_hardware，已注入 rNPU_arp_poison</t>
         </is>
       </c>
       <c r="D631" s="3" t="inlineStr">
@@ -37412,7 +37412,7 @@
       </c>
       <c r="C632" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_arp_poison</t>
+          <t>npu_hardware，已注入 rNPU_arp_poison</t>
         </is>
       </c>
       <c r="D632" s="3" t="inlineStr">
@@ -37471,7 +37471,7 @@
       </c>
       <c r="C633" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_route_add</t>
+          <t>npu_hardware，已注入 rNPU_route_add</t>
         </is>
       </c>
       <c r="D633" s="3" t="inlineStr">
@@ -37529,7 +37529,7 @@
       </c>
       <c r="C634" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_route_add</t>
+          <t>npu_hardware，已注入 rNPU_route_add</t>
         </is>
       </c>
       <c r="D634" s="3" t="inlineStr">

--- a/tests/e2e/testcases.xlsx
+++ b/tests/e2e/testcases.xlsx
@@ -15641,7 +15641,7 @@
       </c>
       <c r="C260" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_arp_del</t>
+          <t>npu_hardware，已注入 rNPU_arp_del</t>
         </is>
       </c>
       <c r="D260" s="3" t="inlineStr">
@@ -15700,7 +15700,7 @@
       </c>
       <c r="C261" s="3" t="inlineStr">
         <is>
-          <t>rNPU_arp_del 可注入</t>
+          <t>npu_hardware，rNPU_arp_del 可注入</t>
         </is>
       </c>
       <c r="D261" s="3" t="inlineStr">
@@ -15757,7 +15757,7 @@
       </c>
       <c r="C262" s="3" t="inlineStr">
         <is>
-          <t>rNPU_arp_del 可注入</t>
+          <t>npu_hardware，rNPU_arp_del 可注入</t>
         </is>
       </c>
       <c r="D262" s="3" t="inlineStr">
@@ -15814,7 +15814,7 @@
       </c>
       <c r="C263" s="3" t="inlineStr">
         <is>
-          <t>此类 NPU 故障无 /tmp 工件可枚举其标识</t>
+          <t>npu_hardware，此类 NPU 故障无 /tmp 工件可枚举其标识</t>
         </is>
       </c>
       <c r="D263" s="3" t="inlineStr">
@@ -15871,7 +15871,7 @@
       </c>
       <c r="C264" s="3" t="inlineStr">
         <is>
-          <t>已注入 arp_del，sidecar 保存原 MAC</t>
+          <t>npu_hardware，已注入 arp_del，sidecar 保存原 MAC</t>
         </is>
       </c>
       <c r="D264" s="3" t="inlineStr">
@@ -15927,7 +15927,7 @@
       </c>
       <c r="C265" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_arp_del</t>
+          <t>npu_hardware，已 clean rNPU_arp_del</t>
         </is>
       </c>
       <c r="D265" s="3" t="inlineStr">
@@ -15986,7 +15986,7 @@
       </c>
       <c r="C266" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_arp_del</t>
+          <t>npu_hardware，已注入 rNPU_arp_del</t>
         </is>
       </c>
       <c r="D266" s="3" t="inlineStr">
@@ -16045,7 +16045,7 @@
       </c>
       <c r="C267" s="3" t="inlineStr">
         <is>
-          <t>rNPU_arp_del 可注入</t>
+          <t>npu_hardware，rNPU_arp_del 可注入</t>
         </is>
       </c>
       <c r="D267" s="3" t="inlineStr">
@@ -16102,7 +16102,7 @@
       </c>
       <c r="C268" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_arp_del</t>
+          <t>npu_hardware，已注入 rNPU_arp_del</t>
         </is>
       </c>
       <c r="D268" s="3" t="inlineStr">
@@ -16160,7 +16160,7 @@
       </c>
       <c r="C269" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_arp_del</t>
+          <t>npu_hardware，已注入 rNPU_arp_del</t>
         </is>
       </c>
       <c r="D269" s="3" t="inlineStr">
@@ -16218,7 +16218,7 @@
       </c>
       <c r="C270" s="3" t="inlineStr">
         <is>
-          <t>目标 ARP 条目未预先创建</t>
+          <t>npu_hardware，目标 ARP 条目未预先创建</t>
         </is>
       </c>
       <c r="D270" s="3" t="inlineStr">
@@ -16275,7 +16275,7 @@
       </c>
       <c r="C271" s="3" t="inlineStr">
         <is>
-          <t>目标 ARP 条目已存在（已用 -arp -g 确认或先 inject rNPU_arp_poison 创建）；dev 用 hccn_tool 查出的 NPU 内部网口名</t>
+          <t>npu_hardware，目标 ARP 条目已存在（已用 -arp -g 确认或先 inject rNPU_arp_poison 创建）；dev 用 hccn_tool 查出的 NPU 内部网口名</t>
         </is>
       </c>
       <c r="D271" s="3" t="inlineStr">
@@ -16332,7 +16332,7 @@
       </c>
       <c r="C272" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_arp_del</t>
+          <t>npu_hardware，已注入 rNPU_arp_del</t>
         </is>
       </c>
       <c r="D272" s="3" t="inlineStr">
@@ -16391,7 +16391,7 @@
       </c>
       <c r="C273" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_arp_del</t>
+          <t>npu_hardware，已注入 rNPU_arp_del</t>
         </is>
       </c>
       <c r="D273" s="3" t="inlineStr">
@@ -16449,7 +16449,7 @@
       </c>
       <c r="C274" s="3" t="inlineStr">
         <is>
-          <t>rNPU_arp_del 可注入</t>
+          <t>npu_hardware，rNPU_arp_del 可注入</t>
         </is>
       </c>
       <c r="D274" s="3" t="inlineStr">
@@ -16508,7 +16508,7 @@
       </c>
       <c r="C275" s="3" t="inlineStr">
         <is>
-          <t>rNPU_arp_del 可注入</t>
+          <t>npu_hardware，rNPU_arp_del 可注入</t>
         </is>
       </c>
       <c r="D275" s="3" t="inlineStr">
@@ -16571,7 +16571,7 @@
       </c>
       <c r="C276" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_arp_del</t>
+          <t>npu_hardware，已 clean rNPU_arp_del</t>
         </is>
       </c>
       <c r="D276" s="3" t="inlineStr">
@@ -16630,7 +16630,7 @@
       </c>
       <c r="C277" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_arp_poison</t>
+          <t>npu_hardware，已注入 rNPU_arp_poison</t>
         </is>
       </c>
       <c r="D277" s="3" t="inlineStr">
@@ -16689,7 +16689,7 @@
       </c>
       <c r="C278" s="3" t="inlineStr">
         <is>
-          <t>rNPU_arp_poison 可注入</t>
+          <t>npu_hardware，rNPU_arp_poison 可注入</t>
         </is>
       </c>
       <c r="D278" s="3" t="inlineStr">
@@ -16746,7 +16746,7 @@
       </c>
       <c r="C279" s="3" t="inlineStr">
         <is>
-          <t>rNPU_arp_poison 可注入</t>
+          <t>npu_hardware，rNPU_arp_poison 可注入</t>
         </is>
       </c>
       <c r="D279" s="3" t="inlineStr">
@@ -16803,7 +16803,7 @@
       </c>
       <c r="C280" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_arp_poison</t>
+          <t>npu_hardware，已 clean rNPU_arp_poison</t>
         </is>
       </c>
       <c r="D280" s="3" t="inlineStr">
@@ -16862,7 +16862,7 @@
       </c>
       <c r="C281" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_arp_poison</t>
+          <t>npu_hardware，已注入 rNPU_arp_poison</t>
         </is>
       </c>
       <c r="D281" s="3" t="inlineStr">
@@ -16917,7 +16917,7 @@
       </c>
       <c r="C282" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_arp_poison</t>
+          <t>npu_hardware，已注入 rNPU_arp_poison</t>
         </is>
       </c>
       <c r="D282" s="3" t="inlineStr">
@@ -16976,7 +16976,7 @@
       </c>
       <c r="C283" s="3" t="inlineStr">
         <is>
-          <t>已查出 chip2 真实 dev（示例 eth2）</t>
+          <t>npu_hardware，已查出 chip2 真实 dev（示例 eth2）</t>
         </is>
       </c>
       <c r="D283" s="3" t="inlineStr">
@@ -17036,7 +17036,7 @@
       </c>
       <c r="C284" s="3" t="inlineStr">
         <is>
-          <t>rNPU_arp_poison 可注入</t>
+          <t>npu_hardware，rNPU_arp_poison 可注入</t>
         </is>
       </c>
       <c r="D284" s="3" t="inlineStr">
@@ -17093,7 +17093,7 @@
       </c>
       <c r="C285" s="3" t="inlineStr">
         <is>
-          <t>已用 hccn_tool -i 2 -status -g 查出目标芯片真实 dev（示例机 chip2=eth2）；ip 选用 NPU 同网段未占用地址</t>
+          <t>npu_hardware，已用 hccn_tool -i 2 -status -g 查出目标芯片真实 dev（示例机 chip2=eth2）；ip 选用 NPU 同网段未占用地址</t>
         </is>
       </c>
       <c r="D285" s="3" t="inlineStr">
@@ -17149,7 +17149,7 @@
       </c>
       <c r="C286" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_arp_poison</t>
+          <t>npu_hardware，已注入 rNPU_arp_poison</t>
         </is>
       </c>
       <c r="D286" s="3" t="inlineStr">
@@ -17207,7 +17207,7 @@
       </c>
       <c r="C287" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_arp_poison</t>
+          <t>npu_hardware，已注入 rNPU_arp_poison</t>
         </is>
       </c>
       <c r="D287" s="3" t="inlineStr">
@@ -17265,7 +17265,7 @@
       </c>
       <c r="C288" s="3" t="inlineStr">
         <is>
-          <t>chip=99 越界，其余参数合法</t>
+          <t>npu_hardware，chip=99 越界，其余参数合法</t>
         </is>
       </c>
       <c r="D288" s="3" t="inlineStr">
@@ -17323,7 +17323,7 @@
       </c>
       <c r="C289" s="3" t="inlineStr">
         <is>
-          <t>chip=99 + mac=invalid</t>
+          <t>npu_hardware，chip=99 + mac=invalid</t>
         </is>
       </c>
       <c r="D289" s="3" t="inlineStr">
@@ -17381,7 +17381,7 @@
       </c>
       <c r="C290" s="3" t="inlineStr">
         <is>
-          <t>mac=invalid（非 MAC 格式）</t>
+          <t>npu_hardware，mac=invalid（非 MAC 格式）</t>
         </is>
       </c>
       <c r="D290" s="3" t="inlineStr">
@@ -17439,7 +17439,7 @@
       </c>
       <c r="C291" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_arp_poison</t>
+          <t>npu_hardware，已注入 rNPU_arp_poison</t>
         </is>
       </c>
       <c r="D291" s="3" t="inlineStr">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C292" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_arp_poison</t>
+          <t>npu_hardware，已注入 rNPU_arp_poison</t>
         </is>
       </c>
       <c r="D292" s="3" t="inlineStr">
@@ -17556,7 +17556,7 @@
       </c>
       <c r="C293" s="3" t="inlineStr">
         <is>
-          <t>rNPU_arp_poison 可注入</t>
+          <t>npu_hardware，rNPU_arp_poison 可注入</t>
         </is>
       </c>
       <c r="D293" s="3" t="inlineStr">
@@ -17615,7 +17615,7 @@
       </c>
       <c r="C294" s="3" t="inlineStr">
         <is>
-          <t>rNPU_arp_poison 可注入</t>
+          <t>npu_hardware，rNPU_arp_poison 可注入</t>
         </is>
       </c>
       <c r="D294" s="3" t="inlineStr">
@@ -17678,7 +17678,7 @@
       </c>
       <c r="C295" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_arp_poison</t>
+          <t>npu_hardware，已 clean rNPU_arp_poison</t>
         </is>
       </c>
       <c r="D295" s="3" t="inlineStr">
@@ -17737,7 +17737,7 @@
       </c>
       <c r="C296" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_bw_limit</t>
+          <t>npu_hardware，已注入 rNPU_bw_limit</t>
         </is>
       </c>
       <c r="D296" s="3" t="inlineStr">
@@ -17796,7 +17796,7 @@
       </c>
       <c r="C297" s="3" t="inlineStr">
         <is>
-          <t>Atlas NPU+hccn_tool，root，chip0 可用</t>
+          <t>npu_hardware，Atlas NPU+hccn_tool，root，chip0 可用</t>
         </is>
       </c>
       <c r="D297" s="3" t="inlineStr">
@@ -17857,7 +17857,7 @@
       </c>
       <c r="C298" s="3" t="inlineStr">
         <is>
-          <t>Atlas NPU+hccn_tool，root</t>
+          <t>npu_hardware，Atlas NPU+hccn_tool，root</t>
         </is>
       </c>
       <c r="D298" s="3" t="inlineStr">
@@ -17916,7 +17916,7 @@
       </c>
       <c r="C299" s="3" t="inlineStr">
         <is>
-          <t>rNPU_bw_limit 可注入</t>
+          <t>npu_hardware，rNPU_bw_limit 可注入</t>
         </is>
       </c>
       <c r="D299" s="3" t="inlineStr">
@@ -17973,7 +17973,7 @@
       </c>
       <c r="C300" s="3" t="inlineStr">
         <is>
-          <t>rNPU_bw_limit 可注入</t>
+          <t>npu_hardware，rNPU_bw_limit 可注入</t>
         </is>
       </c>
       <c r="D300" s="3" t="inlineStr">
@@ -18030,7 +18030,7 @@
       </c>
       <c r="C301" s="3" t="inlineStr">
         <is>
-          <t>rNPU_bw_limit 可注入</t>
+          <t>npu_hardware，rNPU_bw_limit 可注入</t>
         </is>
       </c>
       <c r="D301" s="3" t="inlineStr">
@@ -18087,7 +18087,7 @@
       </c>
       <c r="C302" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_bw_limit</t>
+          <t>npu_hardware，已 clean rNPU_bw_limit</t>
         </is>
       </c>
       <c r="D302" s="3" t="inlineStr">
@@ -18146,7 +18146,7 @@
       </c>
       <c r="C303" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_bw_limit</t>
+          <t>npu_hardware，已注入 rNPU_bw_limit</t>
         </is>
       </c>
       <c r="D303" s="3" t="inlineStr">
@@ -18205,7 +18205,7 @@
       </c>
       <c r="C304" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_bw_limit</t>
+          <t>npu_hardware，已注入 rNPU_bw_limit</t>
         </is>
       </c>
       <c r="D304" s="3" t="inlineStr">
@@ -18263,7 +18263,7 @@
       </c>
       <c r="C305" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_bw_limit</t>
+          <t>npu_hardware，已注入 rNPU_bw_limit</t>
         </is>
       </c>
       <c r="D305" s="3" t="inlineStr">
@@ -18321,7 +18321,7 @@
       </c>
       <c r="C306" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_bw_limit</t>
+          <t>npu_hardware，已注入 rNPU_bw_limit</t>
         </is>
       </c>
       <c r="D306" s="3" t="inlineStr">
@@ -18380,7 +18380,7 @@
       </c>
       <c r="C307" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_bw_limit</t>
+          <t>npu_hardware，已注入 rNPU_bw_limit</t>
         </is>
       </c>
       <c r="D307" s="3" t="inlineStr">
@@ -18438,7 +18438,7 @@
       </c>
       <c r="C308" s="3" t="inlineStr">
         <is>
-          <t>rNPU_bw_limit 可注入</t>
+          <t>npu_hardware，rNPU_bw_limit 可注入</t>
         </is>
       </c>
       <c r="D308" s="3" t="inlineStr">
@@ -18497,7 +18497,7 @@
       </c>
       <c r="C309" s="3" t="inlineStr">
         <is>
-          <t>rNPU_bw_limit 可注入</t>
+          <t>npu_hardware，rNPU_bw_limit 可注入</t>
         </is>
       </c>
       <c r="D309" s="3" t="inlineStr">
@@ -18560,7 +18560,7 @@
       </c>
       <c r="C310" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_bw_limit</t>
+          <t>npu_hardware，已 clean rNPU_bw_limit</t>
         </is>
       </c>
       <c r="D310" s="3" t="inlineStr">
@@ -18619,7 +18619,7 @@
       </c>
       <c r="C311" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_dscp_tc_change</t>
+          <t>npu_hardware，已注入 rNPU_dscp_tc_change</t>
         </is>
       </c>
       <c r="D311" s="3" t="inlineStr">
@@ -18678,7 +18678,7 @@
       </c>
       <c r="C312" s="3" t="inlineStr">
         <is>
-          <t>Atlas NPU+hccn_tool，root，chip0 可用</t>
+          <t>npu_hardware，Atlas NPU+hccn_tool，root，chip0 可用</t>
         </is>
       </c>
       <c r="D312" s="3" t="inlineStr">
@@ -18739,7 +18739,7 @@
       </c>
       <c r="C313" s="3" t="inlineStr">
         <is>
-          <t>rNPU_dscp_tc_change 可注入</t>
+          <t>npu_hardware，rNPU_dscp_tc_change 可注入</t>
         </is>
       </c>
       <c r="D313" s="3" t="inlineStr">
@@ -18796,7 +18796,7 @@
       </c>
       <c r="C314" s="3" t="inlineStr">
         <is>
-          <t>rNPU_dscp_tc_change 可注入</t>
+          <t>npu_hardware，rNPU_dscp_tc_change 可注入</t>
         </is>
       </c>
       <c r="D314" s="3" t="inlineStr">
@@ -18853,7 +18853,7 @@
       </c>
       <c r="C315" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_dscp_tc_change</t>
+          <t>npu_hardware，已 clean rNPU_dscp_tc_change</t>
         </is>
       </c>
       <c r="D315" s="3" t="inlineStr">
@@ -18912,7 +18912,7 @@
       </c>
       <c r="C316" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_dscp_tc_change</t>
+          <t>npu_hardware，已注入 rNPU_dscp_tc_change</t>
         </is>
       </c>
       <c r="D316" s="3" t="inlineStr">
@@ -18971,7 +18971,7 @@
       </c>
       <c r="C317" s="3" t="inlineStr">
         <is>
-          <t>chip0</t>
+          <t>npu_hardware，chip0</t>
         </is>
       </c>
       <c r="D317" s="3" t="inlineStr">
@@ -19028,7 +19028,7 @@
       </c>
       <c r="C318" s="3" t="inlineStr">
         <is>
-          <t>rNPU_dscp_tc_change 可注入</t>
+          <t>npu_hardware，rNPU_dscp_tc_change 可注入</t>
         </is>
       </c>
       <c r="D318" s="3" t="inlineStr">
@@ -19085,7 +19085,7 @@
       </c>
       <c r="C319" s="3" t="inlineStr">
         <is>
-          <t>Atlas NPU+hccn_tool，root，chip0</t>
+          <t>npu_hardware，Atlas NPU+hccn_tool，root，chip0</t>
         </is>
       </c>
       <c r="D319" s="3" t="inlineStr">
@@ -19142,7 +19142,7 @@
       </c>
       <c r="C320" s="3" t="inlineStr">
         <is>
-          <t>chip0</t>
+          <t>npu_hardware，chip0</t>
         </is>
       </c>
       <c r="D320" s="3" t="inlineStr">
@@ -19199,7 +19199,7 @@
       </c>
       <c r="C321" s="3" t="inlineStr">
         <is>
-          <t>chip0</t>
+          <t>npu_hardware，chip0</t>
         </is>
       </c>
       <c r="D321" s="3" t="inlineStr">
@@ -19256,7 +19256,7 @@
       </c>
       <c r="C322" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_dscp_tc_change</t>
+          <t>npu_hardware，已注入 rNPU_dscp_tc_change</t>
         </is>
       </c>
       <c r="D322" s="3" t="inlineStr">
@@ -19314,7 +19314,7 @@
       </c>
       <c r="C323" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_dscp_tc_change</t>
+          <t>npu_hardware，已注入 rNPU_dscp_tc_change</t>
         </is>
       </c>
       <c r="D323" s="3" t="inlineStr">
@@ -19372,7 +19372,7 @@
       </c>
       <c r="C324" s="3" t="inlineStr">
         <is>
-          <t>chip0</t>
+          <t>npu_hardware，chip0</t>
         </is>
       </c>
       <c r="D324" s="3" t="inlineStr">
@@ -19429,7 +19429,7 @@
       </c>
       <c r="C325" s="3" t="inlineStr">
         <is>
-          <t>chip0</t>
+          <t>npu_hardware，chip0</t>
         </is>
       </c>
       <c r="D325" s="3" t="inlineStr">
@@ -19486,7 +19486,7 @@
       </c>
       <c r="C326" s="3" t="inlineStr">
         <is>
-          <t>chip0</t>
+          <t>npu_hardware，chip0</t>
         </is>
       </c>
       <c r="D326" s="3" t="inlineStr">
@@ -19543,7 +19543,7 @@
       </c>
       <c r="C327" s="3" t="inlineStr">
         <is>
-          <t>chip0</t>
+          <t>npu_hardware，chip0</t>
         </is>
       </c>
       <c r="D327" s="3" t="inlineStr">
@@ -19600,7 +19600,7 @@
       </c>
       <c r="C328" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_dscp_tc_change</t>
+          <t>npu_hardware，已注入 rNPU_dscp_tc_change</t>
         </is>
       </c>
       <c r="D328" s="3" t="inlineStr">
@@ -19659,7 +19659,7 @@
       </c>
       <c r="C329" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_dscp_tc_change</t>
+          <t>npu_hardware，已注入 rNPU_dscp_tc_change</t>
         </is>
       </c>
       <c r="D329" s="3" t="inlineStr">
@@ -19717,7 +19717,7 @@
       </c>
       <c r="C330" s="3" t="inlineStr">
         <is>
-          <t>rNPU_dscp_tc_change 可注入</t>
+          <t>npu_hardware，rNPU_dscp_tc_change 可注入</t>
         </is>
       </c>
       <c r="D330" s="3" t="inlineStr">
@@ -19776,7 +19776,7 @@
       </c>
       <c r="C331" s="3" t="inlineStr">
         <is>
-          <t>rNPU_dscp_tc_change 可注入</t>
+          <t>npu_hardware，rNPU_dscp_tc_change 可注入</t>
         </is>
       </c>
       <c r="D331" s="3" t="inlineStr">
@@ -19839,7 +19839,7 @@
       </c>
       <c r="C332" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_dscp_tc_change</t>
+          <t>npu_hardware，已 clean rNPU_dscp_tc_change</t>
         </is>
       </c>
       <c r="D332" s="3" t="inlineStr">
@@ -19898,7 +19898,7 @@
       </c>
       <c r="C333" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_gw_change</t>
+          <t>npu_hardware，已注入 rNPU_gw_change</t>
         </is>
       </c>
       <c r="D333" s="3" t="inlineStr">
@@ -19957,7 +19957,7 @@
       </c>
       <c r="C334" s="3" t="inlineStr">
         <is>
-          <t>NPU 芯片号范围 0-7</t>
+          <t>npu_hardware，NPU 芯片号范围 0-7</t>
         </is>
       </c>
       <c r="D334" s="3" t="inlineStr">
@@ -20017,7 +20017,7 @@
       </c>
       <c r="C335" s="3" t="inlineStr">
         <is>
-          <t>已查出 chip0 的 NPU IP 与网关（同网段不同值）</t>
+          <t>npu_hardware，已查出 chip0 的 NPU IP 与网关（同网段不同值）</t>
         </is>
       </c>
       <c r="D335" s="3" t="inlineStr">
@@ -20075,7 +20075,7 @@
       </c>
       <c r="C336" s="3" t="inlineStr">
         <is>
-          <t>已查出 chip7 的 NPU IP 与网关</t>
+          <t>npu_hardware，已查出 chip7 的 NPU IP 与网关</t>
         </is>
       </c>
       <c r="D336" s="3" t="inlineStr">
@@ -20132,7 +20132,7 @@
       </c>
       <c r="C337" s="3" t="inlineStr">
         <is>
-          <t>rNPU_gw_change 可注入</t>
+          <t>npu_hardware，rNPU_gw_change 可注入</t>
         </is>
       </c>
       <c r="D337" s="3" t="inlineStr">
@@ -20189,7 +20189,7 @@
       </c>
       <c r="C338" s="3" t="inlineStr">
         <is>
-          <t>rNPU_gw_change 可注入</t>
+          <t>npu_hardware，rNPU_gw_change 可注入</t>
         </is>
       </c>
       <c r="D338" s="3" t="inlineStr">
@@ -20246,7 +20246,7 @@
       </c>
       <c r="C339" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_gw_change</t>
+          <t>npu_hardware，已 clean rNPU_gw_change</t>
         </is>
       </c>
       <c r="D339" s="3" t="inlineStr">
@@ -20305,7 +20305,7 @@
       </c>
       <c r="C340" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_gw_change</t>
+          <t>npu_hardware，已注入 rNPU_gw_change</t>
         </is>
       </c>
       <c r="D340" s="3" t="inlineStr">
@@ -20364,7 +20364,7 @@
       </c>
       <c r="C341" s="3" t="inlineStr">
         <is>
-          <t>rNPU_gw_change 可注入</t>
+          <t>npu_hardware，rNPU_gw_change 可注入</t>
         </is>
       </c>
       <c r="D341" s="3" t="inlineStr">
@@ -20421,7 +20421,7 @@
       </c>
       <c r="C342" s="3" t="inlineStr">
         <is>
-          <t>系统未安装 hccn_tool（非 Atlas NPU 机器）</t>
+          <t>npu_hardware，系统未安装 hccn_tool（非 Atlas NPU 机器）</t>
         </is>
       </c>
       <c r="D342" s="3" t="inlineStr">
@@ -20481,7 +20481,7 @@
       </c>
       <c r="C343" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_gw_change</t>
+          <t>npu_hardware，已注入 rNPU_gw_change</t>
         </is>
       </c>
       <c r="D343" s="3" t="inlineStr">
@@ -20539,7 +20539,7 @@
       </c>
       <c r="C344" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_gw_change</t>
+          <t>npu_hardware，已注入 rNPU_gw_change</t>
         </is>
       </c>
       <c r="D344" s="3" t="inlineStr">
@@ -20597,7 +20597,7 @@
       </c>
       <c r="C345" s="3" t="inlineStr">
         <is>
-          <t>inject 时原网关为 none（未设网关），sidecar 存 none</t>
+          <t>npu_hardware，inject 时原网关为 none（未设网关），sidecar 存 none</t>
         </is>
       </c>
       <c r="D345" s="3" t="inlineStr">
@@ -20653,7 +20653,7 @@
       </c>
       <c r="C346" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_gw_change</t>
+          <t>npu_hardware，已注入 rNPU_gw_change</t>
         </is>
       </c>
       <c r="D346" s="3" t="inlineStr">
@@ -20712,7 +20712,7 @@
       </c>
       <c r="C347" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_gw_change</t>
+          <t>npu_hardware，已注入 rNPU_gw_change</t>
         </is>
       </c>
       <c r="D347" s="3" t="inlineStr">
@@ -20770,7 +20770,7 @@
       </c>
       <c r="C348" s="3" t="inlineStr">
         <is>
-          <t>rNPU_gw_change 可注入</t>
+          <t>npu_hardware，rNPU_gw_change 可注入</t>
         </is>
       </c>
       <c r="D348" s="3" t="inlineStr">
@@ -20829,7 +20829,7 @@
       </c>
       <c r="C349" s="3" t="inlineStr">
         <is>
-          <t>rNPU_gw_change 可注入</t>
+          <t>npu_hardware，rNPU_gw_change 可注入</t>
         </is>
       </c>
       <c r="D349" s="3" t="inlineStr">
@@ -20892,7 +20892,7 @@
       </c>
       <c r="C350" s="3" t="inlineStr">
         <is>
-          <t>当前网关已是 10.30.12.254</t>
+          <t>npu_hardware，当前网关已是 10.30.12.254</t>
         </is>
       </c>
       <c r="D350" s="3" t="inlineStr">
@@ -20948,7 +20948,7 @@
       </c>
       <c r="C351" s="3" t="inlineStr">
         <is>
-          <t>已用 hccn_tool -i 2 -ip -g 查出 NPU IP=10.30.12.9/24，当前网关=10.30.12.254</t>
+          <t>npu_hardware，已用 hccn_tool -i 2 -ip -g 查出 NPU IP=10.30.12.9/24，当前网关=10.30.12.254</t>
         </is>
       </c>
       <c r="D351" s="3" t="inlineStr">
@@ -21005,7 +21005,7 @@
       </c>
       <c r="C352" s="3" t="inlineStr">
         <is>
-          <t>NPU IP 在 10.30.12.0/24</t>
+          <t>npu_hardware，NPU IP 在 10.30.12.0/24</t>
         </is>
       </c>
       <c r="D352" s="3" t="inlineStr">
@@ -21061,7 +21061,7 @@
       </c>
       <c r="C353" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_gw_change</t>
+          <t>npu_hardware，已 clean rNPU_gw_change</t>
         </is>
       </c>
       <c r="D353" s="3" t="inlineStr">
@@ -21120,7 +21120,7 @@
       </c>
       <c r="C354" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_ip_change</t>
+          <t>npu_hardware，已注入 rNPU_ip_change</t>
         </is>
       </c>
       <c r="D354" s="3" t="inlineStr">
@@ -21179,7 +21179,7 @@
       </c>
       <c r="C355" s="3" t="inlineStr">
         <is>
-          <t>已查出 chip0 原 IP/掩码，新 IP 与原值不同</t>
+          <t>npu_hardware，已查出 chip0 原 IP/掩码，新 IP 与原值不同</t>
         </is>
       </c>
       <c r="D355" s="3" t="inlineStr">
@@ -21242,7 +21242,7 @@
       </c>
       <c r="C356" s="3" t="inlineStr">
         <is>
-          <t>rNPU_ip_change 可注入</t>
+          <t>npu_hardware，rNPU_ip_change 可注入</t>
         </is>
       </c>
       <c r="D356" s="3" t="inlineStr">
@@ -21299,7 +21299,7 @@
       </c>
       <c r="C357" s="3" t="inlineStr">
         <is>
-          <t>rNPU_ip_change 可注入</t>
+          <t>npu_hardware，rNPU_ip_change 可注入</t>
         </is>
       </c>
       <c r="D357" s="3" t="inlineStr">
@@ -21356,7 +21356,7 @@
       </c>
       <c r="C358" s="3" t="inlineStr">
         <is>
-          <t>rNPU_ip_change 可注入</t>
+          <t>npu_hardware，rNPU_ip_change 可注入</t>
         </is>
       </c>
       <c r="D358" s="3" t="inlineStr">
@@ -21413,7 +21413,7 @@
       </c>
       <c r="C359" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_ip_change</t>
+          <t>npu_hardware，已 clean rNPU_ip_change</t>
         </is>
       </c>
       <c r="D359" s="3" t="inlineStr">
@@ -21472,7 +21472,7 @@
       </c>
       <c r="C360" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_ip_change</t>
+          <t>npu_hardware，已注入 rNPU_ip_change</t>
         </is>
       </c>
       <c r="D360" s="3" t="inlineStr">
@@ -21531,7 +21531,7 @@
       </c>
       <c r="C361" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_ip_change</t>
+          <t>npu_hardware，已注入 rNPU_ip_change</t>
         </is>
       </c>
       <c r="D361" s="3" t="inlineStr">
@@ -21589,7 +21589,7 @@
       </c>
       <c r="C362" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_ip_change</t>
+          <t>npu_hardware，已注入 rNPU_ip_change</t>
         </is>
       </c>
       <c r="D362" s="3" t="inlineStr">
@@ -21647,7 +21647,7 @@
       </c>
       <c r="C363" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_ip_change</t>
+          <t>npu_hardware，已注入 rNPU_ip_change</t>
         </is>
       </c>
       <c r="D363" s="3" t="inlineStr">
@@ -21706,7 +21706,7 @@
       </c>
       <c r="C364" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_ip_change</t>
+          <t>npu_hardware，已注入 rNPU_ip_change</t>
         </is>
       </c>
       <c r="D364" s="3" t="inlineStr">
@@ -21764,7 +21764,7 @@
       </c>
       <c r="C365" s="3" t="inlineStr">
         <is>
-          <t>rNPU_ip_change 可注入</t>
+          <t>npu_hardware，rNPU_ip_change 可注入</t>
         </is>
       </c>
       <c r="D365" s="3" t="inlineStr">
@@ -21823,7 +21823,7 @@
       </c>
       <c r="C366" s="3" t="inlineStr">
         <is>
-          <t>rNPU_ip_change 可注入</t>
+          <t>npu_hardware，rNPU_ip_change 可注入</t>
         </is>
       </c>
       <c r="D366" s="3" t="inlineStr">
@@ -21886,7 +21886,7 @@
       </c>
       <c r="C367" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_ip_change</t>
+          <t>npu_hardware，已 clean rNPU_ip_change</t>
         </is>
       </c>
       <c r="D367" s="3" t="inlineStr">
@@ -21945,7 +21945,7 @@
       </c>
       <c r="C368" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iproute_add</t>
+          <t>npu_hardware，已注入 rNPU_iproute_add</t>
         </is>
       </c>
       <c r="D368" s="3" t="inlineStr">
@@ -22004,7 +22004,7 @@
       </c>
       <c r="C369" s="3" t="inlineStr">
         <is>
-          <t>rNPU_iproute_add 可注入</t>
+          <t>npu_hardware，rNPU_iproute_add 可注入</t>
         </is>
       </c>
       <c r="D369" s="3" t="inlineStr">
@@ -22061,7 +22061,7 @@
       </c>
       <c r="C370" s="3" t="inlineStr">
         <is>
-          <t>rNPU_iproute_add 可注入</t>
+          <t>npu_hardware，rNPU_iproute_add 可注入</t>
         </is>
       </c>
       <c r="D370" s="3" t="inlineStr">
@@ -22118,7 +22118,7 @@
       </c>
       <c r="C371" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_iproute_add</t>
+          <t>npu_hardware，已 clean rNPU_iproute_add</t>
         </is>
       </c>
       <c r="D371" s="3" t="inlineStr">
@@ -22177,7 +22177,7 @@
       </c>
       <c r="C372" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iproute_add</t>
+          <t>npu_hardware，已注入 rNPU_iproute_add</t>
         </is>
       </c>
       <c r="D372" s="3" t="inlineStr">
@@ -22236,7 +22236,7 @@
       </c>
       <c r="C373" s="3" t="inlineStr">
         <is>
-          <t>chip2</t>
+          <t>npu_hardware，chip2</t>
         </is>
       </c>
       <c r="D373" s="3" t="inlineStr">
@@ -22293,7 +22293,7 @@
       </c>
       <c r="C374" s="3" t="inlineStr">
         <is>
-          <t>rNPU_iproute_add 可注入</t>
+          <t>npu_hardware，rNPU_iproute_add 可注入</t>
         </is>
       </c>
       <c r="D374" s="3" t="inlineStr">
@@ -22350,7 +22350,7 @@
       </c>
       <c r="C375" s="3" t="inlineStr">
         <is>
-          <t>chip2，NPU IP/网关已查，dev=eth2</t>
+          <t>npu_hardware，chip2，NPU IP/网关已查，dev=eth2</t>
         </is>
       </c>
       <c r="D375" s="3" t="inlineStr">
@@ -22407,7 +22407,7 @@
       </c>
       <c r="C376" s="3" t="inlineStr">
         <is>
-          <t>chip2</t>
+          <t>npu_hardware，chip2</t>
         </is>
       </c>
       <c r="D376" s="3" t="inlineStr">
@@ -22464,7 +22464,7 @@
       </c>
       <c r="C377" s="3" t="inlineStr">
         <is>
-          <t>chip2</t>
+          <t>npu_hardware，chip2</t>
         </is>
       </c>
       <c r="D377" s="3" t="inlineStr">
@@ -22521,7 +22521,7 @@
       </c>
       <c r="C378" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iproute_add</t>
+          <t>npu_hardware，已注入 rNPU_iproute_add</t>
         </is>
       </c>
       <c r="D378" s="3" t="inlineStr">
@@ -22579,7 +22579,7 @@
       </c>
       <c r="C379" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iproute_add</t>
+          <t>npu_hardware，已注入 rNPU_iproute_add</t>
         </is>
       </c>
       <c r="D379" s="3" t="inlineStr">
@@ -22637,7 +22637,7 @@
       </c>
       <c r="C380" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iproute_add</t>
+          <t>npu_hardware，已注入 rNPU_iproute_add</t>
         </is>
       </c>
       <c r="D380" s="3" t="inlineStr">
@@ -22696,7 +22696,7 @@
       </c>
       <c r="C381" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iproute_add</t>
+          <t>npu_hardware，已注入 rNPU_iproute_add</t>
         </is>
       </c>
       <c r="D381" s="3" t="inlineStr">
@@ -22754,7 +22754,7 @@
       </c>
       <c r="C382" s="3" t="inlineStr">
         <is>
-          <t>rNPU_iproute_add 可注入</t>
+          <t>npu_hardware，rNPU_iproute_add 可注入</t>
         </is>
       </c>
       <c r="D382" s="3" t="inlineStr">
@@ -22813,7 +22813,7 @@
       </c>
       <c r="C383" s="3" t="inlineStr">
         <is>
-          <t>已查出 chip2 的 NPU IP/网关与真实 dev（示例 eth2），ip 选未占用网段</t>
+          <t>npu_hardware，已查出 chip2 的 NPU IP/网关与真实 dev（示例 eth2），ip 选未占用网段</t>
         </is>
       </c>
       <c r="D383" s="3" t="inlineStr">
@@ -22874,7 +22874,7 @@
       </c>
       <c r="C384" s="3" t="inlineStr">
         <is>
-          <t>rNPU_iproute_add 可注入</t>
+          <t>npu_hardware，rNPU_iproute_add 可注入</t>
         </is>
       </c>
       <c r="D384" s="3" t="inlineStr">
@@ -22937,7 +22937,7 @@
       </c>
       <c r="C385" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_iproute_add</t>
+          <t>npu_hardware，已 clean rNPU_iproute_add</t>
         </is>
       </c>
       <c r="D385" s="3" t="inlineStr">
@@ -22996,7 +22996,7 @@
       </c>
       <c r="C386" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iproute_del</t>
+          <t>npu_hardware，已注入 rNPU_iproute_del</t>
         </is>
       </c>
       <c r="D386" s="3" t="inlineStr">
@@ -23055,7 +23055,7 @@
       </c>
       <c r="C387" s="3" t="inlineStr">
         <is>
-          <t>rNPU_iproute_del 可注入</t>
+          <t>npu_hardware，rNPU_iproute_del 可注入</t>
         </is>
       </c>
       <c r="D387" s="3" t="inlineStr">
@@ -23112,7 +23112,7 @@
       </c>
       <c r="C388" s="3" t="inlineStr">
         <is>
-          <t>rNPU_iproute_del 可注入</t>
+          <t>npu_hardware，rNPU_iproute_del 可注入</t>
         </is>
       </c>
       <c r="D388" s="3" t="inlineStr">
@@ -23169,7 +23169,7 @@
       </c>
       <c r="C389" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_iproute_del</t>
+          <t>npu_hardware，已 clean rNPU_iproute_del</t>
         </is>
       </c>
       <c r="D389" s="3" t="inlineStr">
@@ -23228,7 +23228,7 @@
       </c>
       <c r="C390" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iproute_del</t>
+          <t>npu_hardware，已注入 rNPU_iproute_del</t>
         </is>
       </c>
       <c r="D390" s="3" t="inlineStr">
@@ -23287,7 +23287,7 @@
       </c>
       <c r="C391" s="3" t="inlineStr">
         <is>
-          <t>rNPU_iproute_del 可注入</t>
+          <t>npu_hardware，rNPU_iproute_del 可注入</t>
         </is>
       </c>
       <c r="D391" s="3" t="inlineStr">
@@ -23344,7 +23344,7 @@
       </c>
       <c r="C392" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iproute_del</t>
+          <t>npu_hardware，已注入 rNPU_iproute_del</t>
         </is>
       </c>
       <c r="D392" s="3" t="inlineStr">
@@ -23402,7 +23402,7 @@
       </c>
       <c r="C393" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iproute_del</t>
+          <t>npu_hardware，已注入 rNPU_iproute_del</t>
         </is>
       </c>
       <c r="D393" s="3" t="inlineStr">
@@ -23460,7 +23460,7 @@
       </c>
       <c r="C394" s="3" t="inlineStr">
         <is>
-          <t>目标 ip_route 已存在（先 rNPU_iproute_add 创建）</t>
+          <t>npu_hardware，目标 ip_route 已存在（先 rNPU_iproute_add 创建）</t>
         </is>
       </c>
       <c r="D394" s="3" t="inlineStr">
@@ -23521,7 +23521,7 @@
       </c>
       <c r="C395" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iproute_del</t>
+          <t>npu_hardware，已注入 rNPU_iproute_del</t>
         </is>
       </c>
       <c r="D395" s="3" t="inlineStr">
@@ -23580,7 +23580,7 @@
       </c>
       <c r="C396" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iproute_del</t>
+          <t>npu_hardware，已注入 rNPU_iproute_del</t>
         </is>
       </c>
       <c r="D396" s="3" t="inlineStr">
@@ -23638,7 +23638,7 @@
       </c>
       <c r="C397" s="3" t="inlineStr">
         <is>
-          <t>rNPU_iproute_del 可注入</t>
+          <t>npu_hardware，rNPU_iproute_del 可注入</t>
         </is>
       </c>
       <c r="D397" s="3" t="inlineStr">
@@ -23697,7 +23697,7 @@
       </c>
       <c r="C398" s="3" t="inlineStr">
         <is>
-          <t>rNPU_iproute_del 可注入</t>
+          <t>npu_hardware，rNPU_iproute_del 可注入</t>
         </is>
       </c>
       <c r="D398" s="3" t="inlineStr">
@@ -23760,7 +23760,7 @@
       </c>
       <c r="C399" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_iproute_del</t>
+          <t>npu_hardware，已 clean rNPU_iproute_del</t>
         </is>
       </c>
       <c r="D399" s="3" t="inlineStr">
@@ -23819,7 +23819,7 @@
       </c>
       <c r="C400" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iprule_add</t>
+          <t>npu_hardware，已注入 rNPU_iprule_add</t>
         </is>
       </c>
       <c r="D400" s="3" t="inlineStr">
@@ -23878,7 +23878,7 @@
       </c>
       <c r="C401" s="3" t="inlineStr">
         <is>
-          <t>rNPU_iprule_add 可注入</t>
+          <t>npu_hardware，rNPU_iprule_add 可注入</t>
         </is>
       </c>
       <c r="D401" s="3" t="inlineStr">
@@ -23935,7 +23935,7 @@
       </c>
       <c r="C402" s="3" t="inlineStr">
         <is>
-          <t>rNPU_iprule_add 可注入</t>
+          <t>npu_hardware，rNPU_iprule_add 可注入</t>
         </is>
       </c>
       <c r="D402" s="3" t="inlineStr">
@@ -23992,7 +23992,7 @@
       </c>
       <c r="C403" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_iprule_add</t>
+          <t>npu_hardware，已 clean rNPU_iprule_add</t>
         </is>
       </c>
       <c r="D403" s="3" t="inlineStr">
@@ -24051,7 +24051,7 @@
       </c>
       <c r="C404" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iprule_add</t>
+          <t>npu_hardware，已注入 rNPU_iprule_add</t>
         </is>
       </c>
       <c r="D404" s="3" t="inlineStr">
@@ -24110,7 +24110,7 @@
       </c>
       <c r="C405" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iprule_add</t>
+          <t>npu_hardware，已注入 rNPU_iprule_add</t>
         </is>
       </c>
       <c r="D405" s="3" t="inlineStr">
@@ -24168,7 +24168,7 @@
       </c>
       <c r="C406" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iprule_add</t>
+          <t>npu_hardware，已注入 rNPU_iprule_add</t>
         </is>
       </c>
       <c r="D406" s="3" t="inlineStr">
@@ -24226,7 +24226,7 @@
       </c>
       <c r="C407" s="3" t="inlineStr">
         <is>
-          <t>chip2</t>
+          <t>npu_hardware，chip2</t>
         </is>
       </c>
       <c r="D407" s="3" t="inlineStr">
@@ -24283,7 +24283,7 @@
       </c>
       <c r="C408" s="3" t="inlineStr">
         <is>
-          <t>rNPU_iprule_add 可注入</t>
+          <t>npu_hardware，rNPU_iprule_add 可注入</t>
         </is>
       </c>
       <c r="D408" s="3" t="inlineStr">
@@ -24340,7 +24340,7 @@
       </c>
       <c r="C409" s="3" t="inlineStr">
         <is>
-          <t>chip2，ip=10.30.12.210</t>
+          <t>npu_hardware，chip2，ip=10.30.12.210</t>
         </is>
       </c>
       <c r="D409" s="3" t="inlineStr">
@@ -24397,7 +24397,7 @@
       </c>
       <c r="C410" s="3" t="inlineStr">
         <is>
-          <t>chip2</t>
+          <t>npu_hardware，chip2</t>
         </is>
       </c>
       <c r="D410" s="3" t="inlineStr">
@@ -24454,7 +24454,7 @@
       </c>
       <c r="C411" s="3" t="inlineStr">
         <is>
-          <t>chip2</t>
+          <t>npu_hardware，chip2</t>
         </is>
       </c>
       <c r="D411" s="3" t="inlineStr">
@@ -24511,7 +24511,7 @@
       </c>
       <c r="C412" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iprule_add</t>
+          <t>npu_hardware，已注入 rNPU_iprule_add</t>
         </is>
       </c>
       <c r="D412" s="3" t="inlineStr">
@@ -24570,7 +24570,7 @@
       </c>
       <c r="C413" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iprule_add</t>
+          <t>npu_hardware，已注入 rNPU_iprule_add</t>
         </is>
       </c>
       <c r="D413" s="3" t="inlineStr">
@@ -24628,7 +24628,7 @@
       </c>
       <c r="C414" s="3" t="inlineStr">
         <is>
-          <t>rNPU_iprule_add 可注入</t>
+          <t>npu_hardware，rNPU_iprule_add 可注入</t>
         </is>
       </c>
       <c r="D414" s="3" t="inlineStr">
@@ -24687,7 +24687,7 @@
       </c>
       <c r="C415" s="3" t="inlineStr">
         <is>
-          <t>已查出 chip2 的 NPU 网段，ip 选未占用地址，table 选未占用表号</t>
+          <t>npu_hardware，已查出 chip2 的 NPU 网段，ip 选未占用地址，table 选未占用表号</t>
         </is>
       </c>
       <c r="D415" s="3" t="inlineStr">
@@ -24748,7 +24748,7 @@
       </c>
       <c r="C416" s="3" t="inlineStr">
         <is>
-          <t>rNPU_iprule_add 可注入</t>
+          <t>npu_hardware，rNPU_iprule_add 可注入</t>
         </is>
       </c>
       <c r="D416" s="3" t="inlineStr">
@@ -24811,7 +24811,7 @@
       </c>
       <c r="C417" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_iprule_add</t>
+          <t>npu_hardware，已 clean rNPU_iprule_add</t>
         </is>
       </c>
       <c r="D417" s="3" t="inlineStr">
@@ -24870,7 +24870,7 @@
       </c>
       <c r="C418" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iprule_del</t>
+          <t>npu_hardware，已注入 rNPU_iprule_del</t>
         </is>
       </c>
       <c r="D418" s="3" t="inlineStr">
@@ -24929,7 +24929,7 @@
       </c>
       <c r="C419" s="3" t="inlineStr">
         <is>
-          <t>rNPU_iprule_del 可注入</t>
+          <t>npu_hardware，rNPU_iprule_del 可注入</t>
         </is>
       </c>
       <c r="D419" s="3" t="inlineStr">
@@ -24986,7 +24986,7 @@
       </c>
       <c r="C420" s="3" t="inlineStr">
         <is>
-          <t>rNPU_iprule_del 可注入</t>
+          <t>npu_hardware，rNPU_iprule_del 可注入</t>
         </is>
       </c>
       <c r="D420" s="3" t="inlineStr">
@@ -25043,7 +25043,7 @@
       </c>
       <c r="C421" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_iprule_del</t>
+          <t>npu_hardware，已 clean rNPU_iprule_del</t>
         </is>
       </c>
       <c r="D421" s="3" t="inlineStr">
@@ -25102,7 +25102,7 @@
       </c>
       <c r="C422" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iprule_del</t>
+          <t>npu_hardware，已注入 rNPU_iprule_del</t>
         </is>
       </c>
       <c r="D422" s="3" t="inlineStr">
@@ -25161,7 +25161,7 @@
       </c>
       <c r="C423" s="3" t="inlineStr">
         <is>
-          <t>rNPU_iprule_del 可注入</t>
+          <t>npu_hardware，rNPU_iprule_del 可注入</t>
         </is>
       </c>
       <c r="D423" s="3" t="inlineStr">
@@ -25218,7 +25218,7 @@
       </c>
       <c r="C424" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iprule_del</t>
+          <t>npu_hardware，已注入 rNPU_iprule_del</t>
         </is>
       </c>
       <c r="D424" s="3" t="inlineStr">
@@ -25276,7 +25276,7 @@
       </c>
       <c r="C425" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iprule_del</t>
+          <t>npu_hardware，已注入 rNPU_iprule_del</t>
         </is>
       </c>
       <c r="D425" s="3" t="inlineStr">
@@ -25334,7 +25334,7 @@
       </c>
       <c r="C426" s="3" t="inlineStr">
         <is>
-          <t>目标 ip rule 已存在（先 rNPU_iprule_add 创建）</t>
+          <t>npu_hardware，目标 ip rule 已存在（先 rNPU_iprule_add 创建）</t>
         </is>
       </c>
       <c r="D426" s="3" t="inlineStr">
@@ -25395,7 +25395,7 @@
       </c>
       <c r="C427" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iprule_del</t>
+          <t>npu_hardware，已注入 rNPU_iprule_del</t>
         </is>
       </c>
       <c r="D427" s="3" t="inlineStr">
@@ -25454,7 +25454,7 @@
       </c>
       <c r="C428" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iprule_del</t>
+          <t>npu_hardware，已注入 rNPU_iprule_del</t>
         </is>
       </c>
       <c r="D428" s="3" t="inlineStr">
@@ -25512,7 +25512,7 @@
       </c>
       <c r="C429" s="3" t="inlineStr">
         <is>
-          <t>rNPU_iprule_del 可注入</t>
+          <t>npu_hardware，rNPU_iprule_del 可注入</t>
         </is>
       </c>
       <c r="D429" s="3" t="inlineStr">
@@ -25571,7 +25571,7 @@
       </c>
       <c r="C430" s="3" t="inlineStr">
         <is>
-          <t>rNPU_iprule_del 可注入</t>
+          <t>npu_hardware，rNPU_iprule_del 可注入</t>
         </is>
       </c>
       <c r="D430" s="3" t="inlineStr">
@@ -25634,7 +25634,7 @@
       </c>
       <c r="C431" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_iprule_del</t>
+          <t>npu_hardware，已 clean rNPU_iprule_del</t>
         </is>
       </c>
       <c r="D431" s="3" t="inlineStr">
@@ -25693,7 +25693,7 @@
       </c>
       <c r="C432" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_link_down</t>
+          <t>npu_hardware，已注入 rNPU_link_down</t>
         </is>
       </c>
       <c r="D432" s="3" t="inlineStr">
@@ -25752,7 +25752,7 @@
       </c>
       <c r="C433" s="3" t="inlineStr">
         <is>
-          <t>Atlas NPU 硬件+hccn_tool，root，chip0 可用</t>
+          <t>npu_hardware，Atlas NPU 硬件+hccn_tool，root，chip0 可用</t>
         </is>
       </c>
       <c r="D433" s="3" t="inlineStr">
@@ -25813,7 +25813,7 @@
       </c>
       <c r="C434" s="3" t="inlineStr">
         <is>
-          <t>rNPU_link_down 可注入</t>
+          <t>npu_hardware，rNPU_link_down 可注入</t>
         </is>
       </c>
       <c r="D434" s="3" t="inlineStr">
@@ -25870,7 +25870,7 @@
       </c>
       <c r="C435" s="3" t="inlineStr">
         <is>
-          <t>rNPU_link_down 可注入</t>
+          <t>npu_hardware，rNPU_link_down 可注入</t>
         </is>
       </c>
       <c r="D435" s="3" t="inlineStr">
@@ -25927,7 +25927,7 @@
       </c>
       <c r="C436" s="3" t="inlineStr">
         <is>
-          <t>rNPU_link_down 可注入</t>
+          <t>npu_hardware，rNPU_link_down 可注入</t>
         </is>
       </c>
       <c r="D436" s="3" t="inlineStr">
@@ -25984,7 +25984,7 @@
       </c>
       <c r="C437" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_link_down</t>
+          <t>npu_hardware，已 clean rNPU_link_down</t>
         </is>
       </c>
       <c r="D437" s="3" t="inlineStr">
@@ -26043,7 +26043,7 @@
       </c>
       <c r="C438" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_link_down</t>
+          <t>npu_hardware，已注入 rNPU_link_down</t>
         </is>
       </c>
       <c r="D438" s="3" t="inlineStr">
@@ -26102,7 +26102,7 @@
       </c>
       <c r="C439" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_link_down</t>
+          <t>npu_hardware，已注入 rNPU_link_down</t>
         </is>
       </c>
       <c r="D439" s="3" t="inlineStr">
@@ -26160,7 +26160,7 @@
       </c>
       <c r="C440" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_link_down</t>
+          <t>npu_hardware，已注入 rNPU_link_down</t>
         </is>
       </c>
       <c r="D440" s="3" t="inlineStr">
@@ -26218,7 +26218,7 @@
       </c>
       <c r="C441" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_link_down</t>
+          <t>npu_hardware，已注入 rNPU_link_down</t>
         </is>
       </c>
       <c r="D441" s="3" t="inlineStr">
@@ -26277,7 +26277,7 @@
       </c>
       <c r="C442" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_link_down</t>
+          <t>npu_hardware，已注入 rNPU_link_down</t>
         </is>
       </c>
       <c r="D442" s="3" t="inlineStr">
@@ -26335,7 +26335,7 @@
       </c>
       <c r="C443" s="3" t="inlineStr">
         <is>
-          <t>rNPU_link_down 可注入</t>
+          <t>npu_hardware，rNPU_link_down 可注入</t>
         </is>
       </c>
       <c r="D443" s="3" t="inlineStr">
@@ -26394,7 +26394,7 @@
       </c>
       <c r="C444" s="3" t="inlineStr">
         <is>
-          <t>rNPU_link_down 可注入</t>
+          <t>npu_hardware，rNPU_link_down 可注入</t>
         </is>
       </c>
       <c r="D444" s="3" t="inlineStr">
@@ -26457,7 +26457,7 @@
       </c>
       <c r="C445" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_link_down</t>
+          <t>npu_hardware，已 clean rNPU_link_down</t>
         </is>
       </c>
       <c r="D445" s="3" t="inlineStr">
@@ -26516,7 +26516,7 @@
       </c>
       <c r="C446" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_mtu_mismatch</t>
+          <t>npu_hardware，已注入 rNPU_mtu_mismatch</t>
         </is>
       </c>
       <c r="D446" s="3" t="inlineStr">
@@ -26575,7 +26575,7 @@
       </c>
       <c r="C447" s="3" t="inlineStr">
         <is>
-          <t>已查出 chip2 当前 MTU=1500，size 选不同值（如 1280）</t>
+          <t>npu_hardware，已查出 chip2 当前 MTU=1500，size 选不同值（如 1280）</t>
         </is>
       </c>
       <c r="D447" s="3" t="inlineStr">
@@ -26638,7 +26638,7 @@
       </c>
       <c r="C448" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_mtu_mismatch</t>
+          <t>npu_hardware，已 clean rNPU_mtu_mismatch</t>
         </is>
       </c>
       <c r="D448" s="3" t="inlineStr">
@@ -26697,7 +26697,7 @@
       </c>
       <c r="C449" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_mtu_mismatch</t>
+          <t>npu_hardware，已注入 rNPU_mtu_mismatch</t>
         </is>
       </c>
       <c r="D449" s="3" t="inlineStr">
@@ -26756,7 +26756,7 @@
       </c>
       <c r="C450" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_mtu_mismatch</t>
+          <t>npu_hardware，已注入 rNPU_mtu_mismatch</t>
         </is>
       </c>
       <c r="D450" s="3" t="inlineStr">
@@ -26814,7 +26814,7 @@
       </c>
       <c r="C451" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_mtu_mismatch</t>
+          <t>npu_hardware，已注入 rNPU_mtu_mismatch</t>
         </is>
       </c>
       <c r="D451" s="3" t="inlineStr">
@@ -26872,7 +26872,7 @@
       </c>
       <c r="C452" s="3" t="inlineStr">
         <is>
-          <t>Atlas NPU+hccn_tool，root</t>
+          <t>npu_hardware，Atlas NPU+hccn_tool，root</t>
         </is>
       </c>
       <c r="D452" s="3" t="inlineStr">
@@ -26931,7 +26931,7 @@
       </c>
       <c r="C453" s="3" t="inlineStr">
         <is>
-          <t>rNPU_mtu_mismatch 可注入</t>
+          <t>npu_hardware，rNPU_mtu_mismatch 可注入</t>
         </is>
       </c>
       <c r="D453" s="3" t="inlineStr">
@@ -26988,7 +26988,7 @@
       </c>
       <c r="C454" s="3" t="inlineStr">
         <is>
-          <t>rNPU_mtu_mismatch 可注入</t>
+          <t>npu_hardware，rNPU_mtu_mismatch 可注入</t>
         </is>
       </c>
       <c r="D454" s="3" t="inlineStr">
@@ -27045,7 +27045,7 @@
       </c>
       <c r="C455" s="3" t="inlineStr">
         <is>
-          <t>rNPU_mtu_mismatch 可注入</t>
+          <t>npu_hardware，rNPU_mtu_mismatch 可注入</t>
         </is>
       </c>
       <c r="D455" s="3" t="inlineStr">
@@ -27102,7 +27102,7 @@
       </c>
       <c r="C456" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_mtu_mismatch</t>
+          <t>npu_hardware，已注入 rNPU_mtu_mismatch</t>
         </is>
       </c>
       <c r="D456" s="3" t="inlineStr">
@@ -27161,7 +27161,7 @@
       </c>
       <c r="C457" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_mtu_mismatch</t>
+          <t>npu_hardware，已注入 rNPU_mtu_mismatch</t>
         </is>
       </c>
       <c r="D457" s="3" t="inlineStr">
@@ -27219,7 +27219,7 @@
       </c>
       <c r="C458" s="3" t="inlineStr">
         <is>
-          <t>rNPU_mtu_mismatch 可注入</t>
+          <t>npu_hardware，rNPU_mtu_mismatch 可注入</t>
         </is>
       </c>
       <c r="D458" s="3" t="inlineStr">
@@ -27278,7 +27278,7 @@
       </c>
       <c r="C459" s="3" t="inlineStr">
         <is>
-          <t>rNPU_mtu_mismatch 可注入</t>
+          <t>npu_hardware，rNPU_mtu_mismatch 可注入</t>
         </is>
       </c>
       <c r="D459" s="3" t="inlineStr">
@@ -27341,7 +27341,7 @@
       </c>
       <c r="C460" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_mtu_mismatch</t>
+          <t>npu_hardware，已 clean rNPU_mtu_mismatch</t>
         </is>
       </c>
       <c r="D460" s="3" t="inlineStr">
@@ -27400,7 +27400,7 @@
       </c>
       <c r="C461" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_netdetect_change</t>
+          <t>npu_hardware，已注入 rNPU_netdetect_change</t>
         </is>
       </c>
       <c r="D461" s="3" t="inlineStr">
@@ -27459,7 +27459,7 @@
       </c>
       <c r="C462" s="3" t="inlineStr">
         <is>
-          <t>Atlas NPU+hccn_tool，root，chip0 可用</t>
+          <t>npu_hardware，Atlas NPU+hccn_tool，root，chip0 可用</t>
         </is>
       </c>
       <c r="D462" s="3" t="inlineStr">
@@ -27520,7 +27520,7 @@
       </c>
       <c r="C463" s="3" t="inlineStr">
         <is>
-          <t>rNPU_netdetect_change 可注入</t>
+          <t>npu_hardware，rNPU_netdetect_change 可注入</t>
         </is>
       </c>
       <c r="D463" s="3" t="inlineStr">
@@ -27577,7 +27577,7 @@
       </c>
       <c r="C464" s="3" t="inlineStr">
         <is>
-          <t>rNPU_netdetect_change 可注入</t>
+          <t>npu_hardware，rNPU_netdetect_change 可注入</t>
         </is>
       </c>
       <c r="D464" s="3" t="inlineStr">
@@ -27634,7 +27634,7 @@
       </c>
       <c r="C465" s="3" t="inlineStr">
         <is>
-          <t>rNPU_netdetect_change 可注入</t>
+          <t>npu_hardware，rNPU_netdetect_change 可注入</t>
         </is>
       </c>
       <c r="D465" s="3" t="inlineStr">
@@ -27691,7 +27691,7 @@
       </c>
       <c r="C466" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_netdetect_change</t>
+          <t>npu_hardware，已 clean rNPU_netdetect_change</t>
         </is>
       </c>
       <c r="D466" s="3" t="inlineStr">
@@ -27750,7 +27750,7 @@
       </c>
       <c r="C467" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_netdetect_change</t>
+          <t>npu_hardware，已注入 rNPU_netdetect_change</t>
         </is>
       </c>
       <c r="D467" s="3" t="inlineStr">
@@ -27809,7 +27809,7 @@
       </c>
       <c r="C468" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_netdetect_change</t>
+          <t>npu_hardware，已注入 rNPU_netdetect_change</t>
         </is>
       </c>
       <c r="D468" s="3" t="inlineStr">
@@ -27867,7 +27867,7 @@
       </c>
       <c r="C469" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_netdetect_change</t>
+          <t>npu_hardware，已注入 rNPU_netdetect_change</t>
         </is>
       </c>
       <c r="D469" s="3" t="inlineStr">
@@ -27925,7 +27925,7 @@
       </c>
       <c r="C470" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_netdetect_change</t>
+          <t>npu_hardware，已注入 rNPU_netdetect_change</t>
         </is>
       </c>
       <c r="D470" s="3" t="inlineStr">
@@ -27984,7 +27984,7 @@
       </c>
       <c r="C471" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_netdetect_change</t>
+          <t>npu_hardware，已注入 rNPU_netdetect_change</t>
         </is>
       </c>
       <c r="D471" s="3" t="inlineStr">
@@ -28042,7 +28042,7 @@
       </c>
       <c r="C472" s="3" t="inlineStr">
         <is>
-          <t>rNPU_netdetect_change 可注入</t>
+          <t>npu_hardware，rNPU_netdetect_change 可注入</t>
         </is>
       </c>
       <c r="D472" s="3" t="inlineStr">
@@ -28101,7 +28101,7 @@
       </c>
       <c r="C473" s="3" t="inlineStr">
         <is>
-          <t>rNPU_netdetect_change 可注入</t>
+          <t>npu_hardware，rNPU_netdetect_change 可注入</t>
         </is>
       </c>
       <c r="D473" s="3" t="inlineStr">
@@ -28164,7 +28164,7 @@
       </c>
       <c r="C474" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_netdetect_change</t>
+          <t>npu_hardware，已 clean rNPU_netdetect_change</t>
         </is>
       </c>
       <c r="D474" s="3" t="inlineStr">
@@ -28223,7 +28223,7 @@
       </c>
       <c r="C475" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_roce_port_change</t>
+          <t>npu_hardware，已注入 rNPU_roce_port_change</t>
         </is>
       </c>
       <c r="D475" s="3" t="inlineStr">
@@ -28282,7 +28282,7 @@
       </c>
       <c r="C476" s="3" t="inlineStr">
         <is>
-          <t>Atlas NPU+hccn_tool，root，chip0 可用</t>
+          <t>npu_hardware，Atlas NPU+hccn_tool，root，chip0 可用</t>
         </is>
       </c>
       <c r="D476" s="3" t="inlineStr">
@@ -28343,7 +28343,7 @@
       </c>
       <c r="C477" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_roce_port_change</t>
+          <t>npu_hardware，已 clean rNPU_roce_port_change</t>
         </is>
       </c>
       <c r="D477" s="3" t="inlineStr">
@@ -28402,7 +28402,7 @@
       </c>
       <c r="C478" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_roce_port_change</t>
+          <t>npu_hardware，已注入 rNPU_roce_port_change</t>
         </is>
       </c>
       <c r="D478" s="3" t="inlineStr">
@@ -28461,7 +28461,7 @@
       </c>
       <c r="C479" s="3" t="inlineStr">
         <is>
-          <t>rNPU_roce_port_change 可注入</t>
+          <t>npu_hardware，rNPU_roce_port_change 可注入</t>
         </is>
       </c>
       <c r="D479" s="3" t="inlineStr">
@@ -28518,7 +28518,7 @@
       </c>
       <c r="C480" s="3" t="inlineStr">
         <is>
-          <t>rNPU_roce_port_change 可注入</t>
+          <t>npu_hardware，rNPU_roce_port_change 可注入</t>
         </is>
       </c>
       <c r="D480" s="3" t="inlineStr">
@@ -28575,7 +28575,7 @@
       </c>
       <c r="C481" s="3" t="inlineStr">
         <is>
-          <t>rNPU_roce_port_change 可注入</t>
+          <t>npu_hardware，rNPU_roce_port_change 可注入</t>
         </is>
       </c>
       <c r="D481" s="3" t="inlineStr">
@@ -28632,7 +28632,7 @@
       </c>
       <c r="C482" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_roce_port_change</t>
+          <t>npu_hardware，已注入 rNPU_roce_port_change</t>
         </is>
       </c>
       <c r="D482" s="3" t="inlineStr">
@@ -28690,7 +28690,7 @@
       </c>
       <c r="C483" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_roce_port_change</t>
+          <t>npu_hardware，已注入 rNPU_roce_port_change</t>
         </is>
       </c>
       <c r="D483" s="3" t="inlineStr">
@@ -28748,7 +28748,7 @@
       </c>
       <c r="C484" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_roce_port_change</t>
+          <t>npu_hardware，已注入 rNPU_roce_port_change</t>
         </is>
       </c>
       <c r="D484" s="3" t="inlineStr">
@@ -28807,7 +28807,7 @@
       </c>
       <c r="C485" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_roce_port_change</t>
+          <t>npu_hardware，已注入 rNPU_roce_port_change</t>
         </is>
       </c>
       <c r="D485" s="3" t="inlineStr">
@@ -28865,7 +28865,7 @@
       </c>
       <c r="C486" s="3" t="inlineStr">
         <is>
-          <t>rNPU_roce_port_change 可注入</t>
+          <t>npu_hardware，rNPU_roce_port_change 可注入</t>
         </is>
       </c>
       <c r="D486" s="3" t="inlineStr">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C487" s="3" t="inlineStr">
         <is>
-          <t>rNPU_roce_port_change 可注入</t>
+          <t>npu_hardware，rNPU_roce_port_change 可注入</t>
         </is>
       </c>
       <c r="D487" s="3" t="inlineStr">
@@ -28987,7 +28987,7 @@
       </c>
       <c r="C488" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_roce_port_change</t>
+          <t>npu_hardware，已 clean rNPU_roce_port_change</t>
         </is>
       </c>
       <c r="D488" s="3" t="inlineStr">
@@ -29046,7 +29046,7 @@
       </c>
       <c r="C489" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_route_add</t>
+          <t>npu_hardware，已注入 rNPU_route_add</t>
         </is>
       </c>
       <c r="D489" s="3" t="inlineStr">
@@ -29105,7 +29105,7 @@
       </c>
       <c r="C490" s="3" t="inlineStr">
         <is>
-          <t>rNPU_route_add 可注入</t>
+          <t>npu_hardware，rNPU_route_add 可注入</t>
         </is>
       </c>
       <c r="D490" s="3" t="inlineStr">
@@ -29162,7 +29162,7 @@
       </c>
       <c r="C491" s="3" t="inlineStr">
         <is>
-          <t>rNPU_route_add 可注入</t>
+          <t>npu_hardware，rNPU_route_add 可注入</t>
         </is>
       </c>
       <c r="D491" s="3" t="inlineStr">
@@ -29219,7 +29219,7 @@
       </c>
       <c r="C492" s="3" t="inlineStr">
         <is>
-          <t>rNPU_route_add 可注入</t>
+          <t>npu_hardware，rNPU_route_add 可注入</t>
         </is>
       </c>
       <c r="D492" s="3" t="inlineStr">
@@ -29276,7 +29276,7 @@
       </c>
       <c r="C493" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_route_add</t>
+          <t>npu_hardware，已 clean rNPU_route_add</t>
         </is>
       </c>
       <c r="D493" s="3" t="inlineStr">
@@ -29335,7 +29335,7 @@
       </c>
       <c r="C494" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_route_add</t>
+          <t>npu_hardware，已注入 rNPU_route_add</t>
         </is>
       </c>
       <c r="D494" s="3" t="inlineStr">
@@ -29394,7 +29394,7 @@
       </c>
       <c r="C495" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_route_add</t>
+          <t>npu_hardware，已注入 rNPU_route_add</t>
         </is>
       </c>
       <c r="D495" s="3" t="inlineStr">
@@ -29452,7 +29452,7 @@
       </c>
       <c r="C496" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_route_add</t>
+          <t>npu_hardware，已注入 rNPU_route_add</t>
         </is>
       </c>
       <c r="D496" s="3" t="inlineStr">
@@ -29510,7 +29510,7 @@
       </c>
       <c r="C497" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_route_add</t>
+          <t>npu_hardware，已注入 rNPU_route_add</t>
         </is>
       </c>
       <c r="D497" s="3" t="inlineStr">
@@ -29569,7 +29569,7 @@
       </c>
       <c r="C498" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_route_add</t>
+          <t>npu_hardware，已注入 rNPU_route_add</t>
         </is>
       </c>
       <c r="D498" s="3" t="inlineStr">
@@ -29627,7 +29627,7 @@
       </c>
       <c r="C499" s="3" t="inlineStr">
         <is>
-          <t>rNPU_route_add 可注入</t>
+          <t>npu_hardware，rNPU_route_add 可注入</t>
         </is>
       </c>
       <c r="D499" s="3" t="inlineStr">
@@ -29686,7 +29686,7 @@
       </c>
       <c r="C500" s="3" t="inlineStr">
         <is>
-          <t>已查出 chip2 的 NPU IP/网关，address 选未占用且不与 NPU 网段冲突的网段</t>
+          <t>npu_hardware，已查出 chip2 的 NPU IP/网关，address 选未占用且不与 NPU 网段冲突的网段</t>
         </is>
       </c>
       <c r="D500" s="3" t="inlineStr">
@@ -29747,7 +29747,7 @@
       </c>
       <c r="C501" s="3" t="inlineStr">
         <is>
-          <t>rNPU_route_add 可注入</t>
+          <t>npu_hardware，rNPU_route_add 可注入</t>
         </is>
       </c>
       <c r="D501" s="3" t="inlineStr">
@@ -29810,7 +29810,7 @@
       </c>
       <c r="C502" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_route_add</t>
+          <t>npu_hardware，已 clean rNPU_route_add</t>
         </is>
       </c>
       <c r="D502" s="3" t="inlineStr">
@@ -29869,7 +29869,7 @@
       </c>
       <c r="C503" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_route_del</t>
+          <t>npu_hardware，已注入 rNPU_route_del</t>
         </is>
       </c>
       <c r="D503" s="3" t="inlineStr">
@@ -29928,7 +29928,7 @@
       </c>
       <c r="C504" s="3" t="inlineStr">
         <is>
-          <t>rNPU_route_del 可注入</t>
+          <t>npu_hardware，rNPU_route_del 可注入</t>
         </is>
       </c>
       <c r="D504" s="3" t="inlineStr">
@@ -29985,7 +29985,7 @@
       </c>
       <c r="C505" s="3" t="inlineStr">
         <is>
-          <t>rNPU_route_del 可注入</t>
+          <t>npu_hardware，rNPU_route_del 可注入</t>
         </is>
       </c>
       <c r="D505" s="3" t="inlineStr">
@@ -30042,7 +30042,7 @@
       </c>
       <c r="C506" s="3" t="inlineStr">
         <is>
-          <t>rNPU_route_del 可注入</t>
+          <t>npu_hardware，rNPU_route_del 可注入</t>
         </is>
       </c>
       <c r="D506" s="3" t="inlineStr">
@@ -30099,7 +30099,7 @@
       </c>
       <c r="C507" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_route_del</t>
+          <t>npu_hardware，已 clean rNPU_route_del</t>
         </is>
       </c>
       <c r="D507" s="3" t="inlineStr">
@@ -30158,7 +30158,7 @@
       </c>
       <c r="C508" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_route_del</t>
+          <t>npu_hardware，已注入 rNPU_route_del</t>
         </is>
       </c>
       <c r="D508" s="3" t="inlineStr">
@@ -30217,7 +30217,7 @@
       </c>
       <c r="C509" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_route_del</t>
+          <t>npu_hardware，已注入 rNPU_route_del</t>
         </is>
       </c>
       <c r="D509" s="3" t="inlineStr">
@@ -30275,7 +30275,7 @@
       </c>
       <c r="C510" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_route_del</t>
+          <t>npu_hardware，已注入 rNPU_route_del</t>
         </is>
       </c>
       <c r="D510" s="3" t="inlineStr">
@@ -30333,7 +30333,7 @@
       </c>
       <c r="C511" s="3" t="inlineStr">
         <is>
-          <t>目标路由已存在（先 rNPU_route_add 创建）</t>
+          <t>npu_hardware，目标路由已存在（先 rNPU_route_add 创建）</t>
         </is>
       </c>
       <c r="D511" s="3" t="inlineStr">
@@ -30394,7 +30394,7 @@
       </c>
       <c r="C512" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_route_del</t>
+          <t>npu_hardware，已注入 rNPU_route_del</t>
         </is>
       </c>
       <c r="D512" s="3" t="inlineStr">
@@ -30453,7 +30453,7 @@
       </c>
       <c r="C513" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_route_del</t>
+          <t>npu_hardware，已注入 rNPU_route_del</t>
         </is>
       </c>
       <c r="D513" s="3" t="inlineStr">
@@ -30511,7 +30511,7 @@
       </c>
       <c r="C514" s="3" t="inlineStr">
         <is>
-          <t>rNPU_route_del 可注入</t>
+          <t>npu_hardware，rNPU_route_del 可注入</t>
         </is>
       </c>
       <c r="D514" s="3" t="inlineStr">
@@ -30570,7 +30570,7 @@
       </c>
       <c r="C515" s="3" t="inlineStr">
         <is>
-          <t>rNPU_route_del 可注入</t>
+          <t>npu_hardware，rNPU_route_del 可注入</t>
         </is>
       </c>
       <c r="D515" s="3" t="inlineStr">
@@ -30633,7 +30633,7 @@
       </c>
       <c r="C516" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_route_del</t>
+          <t>npu_hardware，已 clean rNPU_route_del</t>
         </is>
       </c>
       <c r="D516" s="3" t="inlineStr">
@@ -33864,12 +33864,12 @@
       </c>
       <c r="C571" s="3" t="inlineStr">
         <is>
-          <t>log_level=debug</t>
+          <t>npu_hardware，log_level=debug</t>
         </is>
       </c>
       <c r="D571" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rNPU_arp_poison --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55
+          <t>1. 执行 dcat inject rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55
 2. 捕获 stderr 检查是否含 MAC 等敏感参数</t>
         </is>
       </c>
@@ -36997,7 +36997,7 @@
       </c>
       <c r="C625" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_link_down</t>
+          <t>npu_hardware，已注入 rNPU_link_down</t>
         </is>
       </c>
       <c r="D625" s="3" t="inlineStr">
@@ -37055,7 +37055,7 @@
       </c>
       <c r="C626" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_link_down</t>
+          <t>npu_hardware，已注入 rNPU_link_down</t>
         </is>
       </c>
       <c r="D626" s="3" t="inlineStr">
@@ -37114,7 +37114,7 @@
       </c>
       <c r="C627" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_ip_change</t>
+          <t>npu_hardware，已注入 rNPU_ip_change</t>
         </is>
       </c>
       <c r="D627" s="3" t="inlineStr">
@@ -37172,7 +37172,7 @@
       </c>
       <c r="C628" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_ip_change</t>
+          <t>npu_hardware，已注入 rNPU_ip_change</t>
         </is>
       </c>
       <c r="D628" s="3" t="inlineStr">
@@ -37231,7 +37231,7 @@
       </c>
       <c r="C629" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_gw_change</t>
+          <t>npu_hardware，已注入 rNPU_gw_change</t>
         </is>
       </c>
       <c r="D629" s="3" t="inlineStr">
@@ -37289,7 +37289,7 @@
       </c>
       <c r="C630" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_gw_change</t>
+          <t>npu_hardware，已注入 rNPU_gw_change</t>
         </is>
       </c>
       <c r="D630" s="3" t="inlineStr">
@@ -37348,7 +37348,7 @@
       </c>
       <c r="C631" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_arp_poison</t>
+          <t>npu_hardware，已注入 rNPU_arp_poison</t>
         </is>
       </c>
       <c r="D631" s="3" t="inlineStr">
@@ -37406,7 +37406,7 @@
       </c>
       <c r="C632" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_arp_poison</t>
+          <t>npu_hardware，已注入 rNPU_arp_poison</t>
         </is>
       </c>
       <c r="D632" s="3" t="inlineStr">
@@ -37465,7 +37465,7 @@
       </c>
       <c r="C633" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_route_add</t>
+          <t>npu_hardware，已注入 rNPU_route_add</t>
         </is>
       </c>
       <c r="D633" s="3" t="inlineStr">
@@ -37523,7 +37523,7 @@
       </c>
       <c r="C634" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_route_add</t>
+          <t>npu_hardware，已注入 rNPU_route_add</t>
         </is>
       </c>
       <c r="D634" s="3" t="inlineStr">

--- a/tests/e2e/testcases.xlsx
+++ b/tests/e2e/testcases.xlsx
@@ -6687,9 +6687,7 @@
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>1. Manual 严禁对管理网卡执行 rNET_down（将导致 SSH 失联）
-2. 预期脚本/dcat 给出告警或拒绝
-3. 具体防护策略 SPEC 未明确（dcat 不强制，脚本可能不拦截），需与需求方确认</t>
+          <t>1. inject rNET_down --iface=eth0 失败 exit 1（eth0 在测试环境不存在,脚本 ip link set 失败）</t>
         </is>
       </c>
       <c r="G106" s="4" t="inlineStr">
@@ -6714,7 +6712,7 @@
       </c>
       <c r="K106" s="3" t="inlineStr">
         <is>
-          <t>eq:DOWN</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>

--- a/tests/e2e/testcases.xlsx
+++ b/tests/e2e/testcases.xlsx
@@ -15644,7 +15644,7 @@
       </c>
       <c r="D260" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_arp_del --chip=2 --dev=eth2 --ip=10.30.12.200 --force</t>
+          <t>1. dcat inject rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200 --force</t>
         </is>
       </c>
       <c r="E260" s="3" t="inlineStr">
@@ -15703,7 +15703,7 @@
       </c>
       <c r="D261" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_arp_del --chip=-1 --dev=eth2 --ip=10.30.12.200</t>
+          <t>1. dcat inject rNPU_arp --chip=-1 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55</t>
         </is>
       </c>
       <c r="E261" s="3" t="inlineStr">
@@ -15760,7 +15760,7 @@
       </c>
       <c r="D262" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_arp_del --chip=8 --dev=eth2 --ip=10.30.12.200</t>
+          <t>1. dcat inject rNPU_arp --chip=8 --dev=eth2 --ip=10.30.12.200</t>
         </is>
       </c>
       <c r="E262" s="3" t="inlineStr">
@@ -15818,7 +15818,7 @@
       <c r="D263" s="3" t="inlineStr">
         <is>
           <t>1. 执行 dcat clean --all
-2. 检查 rNPU_arp_del 的聚合结果</t>
+2. 检查 rNPU_arp 的聚合结果</t>
         </is>
       </c>
       <c r="E263" s="3" t="inlineStr">
@@ -15874,7 +15874,7 @@
       </c>
       <c r="D264" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat clean rNPU_arp_del --chip=2 --dev=eth2 --ip=10.30.12.200（dev 与创建时一致）
+          <t>1. 执行 dcat clean rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200（dev 与创建时一致）
 2. 改用错误 dev 重试验证失败</t>
         </is>
       </c>
@@ -15930,7 +15930,7 @@
       </c>
       <c r="D265" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_arp_del --chip=2 --dev=eth2 --ip=10.30.12.200
+          <t>1. dcat clean rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200
 2. dcat query（无 uid）</t>
         </is>
       </c>
@@ -15989,7 +15989,7 @@
       </c>
       <c r="D266" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_arp_del --chip=2 --dev=eth2 --ip=10.30.12.200
+          <t>1. dcat clean rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200
 2. 检查恢复状态</t>
         </is>
       </c>
@@ -16048,7 +16048,7 @@
       </c>
       <c r="D267" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_arp_del --chip=2 --dev=eth2 --ip=invalid</t>
+          <t>1. dcat inject rNPU_arp --chip=2 --dev=eth2 --ip=invalid</t>
         </is>
       </c>
       <c r="E267" s="3" t="inlineStr">
@@ -16105,7 +16105,7 @@
       </c>
       <c r="D268" s="3" t="inlineStr">
         <is>
-          <t>1. dcat query rNPU_arp_del（无参数）</t>
+          <t>1. dcat query rNPU_arp（无参数）</t>
         </is>
       </c>
       <c r="E268" s="3" t="inlineStr">
@@ -16136,7 +16136,7 @@
       </c>
       <c r="J268" s="3" t="inlineStr">
         <is>
-          <t>dcat query rNPU_arp_del</t>
+          <t>dcat query rNPU_arp</t>
         </is>
       </c>
       <c r="K268" s="3" t="inlineStr">
@@ -16163,7 +16163,7 @@
       </c>
       <c r="D269" s="3" t="inlineStr">
         <is>
-          <t>1. dcat query rNPU_arp_del --chip=2 --dev=eth2 --ip=10.30.12.200</t>
+          <t>1. dcat query rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200</t>
         </is>
       </c>
       <c r="E269" s="3" t="inlineStr">
@@ -16194,7 +16194,7 @@
       </c>
       <c r="J269" s="3" t="inlineStr">
         <is>
-          <t>dcat query rNPU_arp_del</t>
+          <t>dcat query rNPU_arp</t>
         </is>
       </c>
       <c r="K269" s="3" t="inlineStr">
@@ -16221,7 +16221,7 @@
       </c>
       <c r="D270" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rNPU_arp_del --chip=2 --dev=eth2 --ip=10.30.12.200
+          <t>1. 执行 dcat inject rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200
 2. 检查返回</t>
         </is>
       </c>
@@ -16278,7 +16278,7 @@
       </c>
       <c r="D271" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rNPU_arp_del --chip=2 --dev=eth2 --ip=10.30.12.200
+          <t>1. 执行 dcat inject rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200
 2. 检查 sidecar 与 query</t>
         </is>
       </c>
@@ -16335,8 +16335,8 @@
       </c>
       <c r="D272" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_arp_del --chip=2 --dev=eth2 --ip=10.30.12.200
-2. 再次 dcat inject rNPU_arp_del --chip=2 --dev=eth2 --ip=10.30.12.200</t>
+          <t>1. dcat inject rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200
+2. 再次 dcat inject rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200</t>
         </is>
       </c>
       <c r="E272" s="3" t="inlineStr">
@@ -16394,7 +16394,7 @@
       </c>
       <c r="D273" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_arp_del（无参）</t>
+          <t>1. dcat clean rNPU_arp（无参）</t>
         </is>
       </c>
       <c r="E273" s="3" t="inlineStr">
@@ -16425,7 +16425,7 @@
       </c>
       <c r="J273" s="3" t="inlineStr">
         <is>
-          <t>dcat clean rNPU_arp_del</t>
+          <t>dcat clean rNPU_arp</t>
         </is>
       </c>
       <c r="K273" s="3" t="inlineStr">
@@ -16452,7 +16452,7 @@
       </c>
       <c r="D274" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_arp_del --chip=2 --dev=eth2 --ip=10.30.12.200
+          <t>1. dcat inject rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200
 2. 检查注入状态</t>
         </is>
       </c>
@@ -16511,10 +16511,10 @@
       </c>
       <c r="D275" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_arp_del --chip=2 --dev=eth2 --ip=10.30.12.200
-2. dcat query rNPU_arp_del
-3. dcat clean rNPU_arp_del --chip=2 --dev=eth2 --ip=10.30.12.200
-4. dcat query rNPU_arp_del</t>
+          <t>1. dcat inject rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200
+2. dcat query rNPU_arp
+3. dcat clean rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200
+4. dcat query rNPU_arp</t>
         </is>
       </c>
       <c r="E275" s="3" t="inlineStr">
@@ -16547,7 +16547,7 @@
       </c>
       <c r="J275" s="3" t="inlineStr">
         <is>
-          <t>dcat query rNPU_arp_del</t>
+          <t>dcat query rNPU_arp</t>
         </is>
       </c>
       <c r="K275" s="3" t="inlineStr">
@@ -16574,8 +16574,8 @@
       </c>
       <c r="D276" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_arp_del --chip=2 --dev=eth2 --ip=10.30.12.200
-2. 再次 dcat clean rNPU_arp_del --chip=2 --dev=eth2 --ip=10.30.12.200</t>
+          <t>1. dcat clean rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200
+2. 再次 dcat clean rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200</t>
         </is>
       </c>
       <c r="E276" s="3" t="inlineStr">
@@ -16606,7 +16606,7 @@
       </c>
       <c r="J276" s="3" t="inlineStr">
         <is>
-          <t>dcat clean rNPU_arp_del</t>
+          <t>dcat clean rNPU_arp</t>
         </is>
       </c>
       <c r="K276" s="3" t="inlineStr">
@@ -16633,7 +16633,7 @@
       </c>
       <c r="D277" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_arp_poison --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55 --force</t>
+          <t>1. dcat inject rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55 --force</t>
         </is>
       </c>
       <c r="E277" s="3" t="inlineStr">
@@ -16692,7 +16692,7 @@
       </c>
       <c r="D278" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_arp_poison --chip=-1 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55</t>
+          <t>1. dcat inject rNPU_arp --chip=-1 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55</t>
         </is>
       </c>
       <c r="E278" s="3" t="inlineStr">
@@ -16749,7 +16749,7 @@
       </c>
       <c r="D279" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_arp_poison --chip=8 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55</t>
+          <t>1. dcat inject rNPU_arp --chip=8 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55</t>
         </is>
       </c>
       <c r="E279" s="3" t="inlineStr">
@@ -16806,7 +16806,7 @@
       </c>
       <c r="D280" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_arp_poison --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55
+          <t>1. dcat clean rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55
 2. dcat query（无 uid）</t>
         </is>
       </c>
@@ -16865,7 +16865,7 @@
       </c>
       <c r="D281" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat clean rNPU_arp_poison --chip=2 --dev=eth2 --ip=10.30.12.200</t>
+          <t>1. 执行 dcat clean rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200</t>
         </is>
       </c>
       <c r="E281" s="3" t="inlineStr">
@@ -16920,7 +16920,7 @@
       </c>
       <c r="D282" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_arp_poison --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55
+          <t>1. dcat clean rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55
 2. 检查恢复状态</t>
         </is>
       </c>
@@ -16979,7 +16979,7 @@
       </c>
       <c r="D283" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rNPU_arp_poison --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=invalid
+          <t>1. 执行 dcat inject rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=invalid
 2. 检查返回</t>
         </is>
       </c>
@@ -17039,7 +17039,7 @@
       </c>
       <c r="D284" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_arp_poison --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=invalid</t>
+          <t>1. dcat inject rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=invalid</t>
         </is>
       </c>
       <c r="E284" s="3" t="inlineStr">
@@ -17096,8 +17096,8 @@
       </c>
       <c r="D285" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rNPU_arp_poison --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55
-2. 执行 dcat query rNPU_arp_poison 验证</t>
+          <t>1. 执行 dcat inject rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55
+2. 执行 dcat query rNPU_arp 验证</t>
         </is>
       </c>
       <c r="E285" s="3" t="inlineStr">
@@ -17152,7 +17152,7 @@
       </c>
       <c r="D286" s="3" t="inlineStr">
         <is>
-          <t>1. dcat query rNPU_arp_poison（无参数）</t>
+          <t>1. dcat query rNPU_arp（无参数）</t>
         </is>
       </c>
       <c r="E286" s="3" t="inlineStr">
@@ -17183,7 +17183,7 @@
       </c>
       <c r="J286" s="3" t="inlineStr">
         <is>
-          <t>dcat query rNPU_arp_poison</t>
+          <t>dcat query rNPU_arp</t>
         </is>
       </c>
       <c r="K286" s="3" t="inlineStr">
@@ -17210,7 +17210,7 @@
       </c>
       <c r="D287" s="3" t="inlineStr">
         <is>
-          <t>1. dcat query rNPU_arp_poison --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55</t>
+          <t>1. dcat query rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55</t>
         </is>
       </c>
       <c r="E287" s="3" t="inlineStr">
@@ -17241,7 +17241,7 @@
       </c>
       <c r="J287" s="3" t="inlineStr">
         <is>
-          <t>dcat query rNPU_arp_poison</t>
+          <t>dcat query rNPU_arp</t>
         </is>
       </c>
       <c r="K287" s="3" t="inlineStr">
@@ -17268,7 +17268,7 @@
       </c>
       <c r="D288" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_arp_poison --chip=99 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55</t>
+          <t>1. dcat inject rNPU_arp --chip=99 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55</t>
         </is>
       </c>
       <c r="E288" s="3" t="inlineStr">
@@ -17326,7 +17326,7 @@
       </c>
       <c r="D289" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_arp_poison --chip=99 --dev=eth2 --ip=10.30.12.200 --mac=invalid</t>
+          <t>1. dcat inject rNPU_arp --chip=99 --dev=eth2 --ip=10.30.12.200 --mac=invalid</t>
         </is>
       </c>
       <c r="E289" s="3" t="inlineStr">
@@ -17384,7 +17384,7 @@
       </c>
       <c r="D290" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_arp_poison --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=invalid</t>
+          <t>1. dcat inject rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=invalid</t>
         </is>
       </c>
       <c r="E290" s="3" t="inlineStr">
@@ -17442,8 +17442,8 @@
       </c>
       <c r="D291" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_arp_poison --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55
-2. 再次 dcat inject rNPU_arp_poison --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55</t>
+          <t>1. dcat inject rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55
+2. 再次 dcat inject rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55</t>
         </is>
       </c>
       <c r="E291" s="3" t="inlineStr">
@@ -17501,7 +17501,7 @@
       </c>
       <c r="D292" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_arp_poison（无参）</t>
+          <t>1. dcat clean rNPU_arp（无参）</t>
         </is>
       </c>
       <c r="E292" s="3" t="inlineStr">
@@ -17532,7 +17532,7 @@
       </c>
       <c r="J292" s="3" t="inlineStr">
         <is>
-          <t>dcat clean rNPU_arp_poison</t>
+          <t>dcat clean rNPU_arp</t>
         </is>
       </c>
       <c r="K292" s="3" t="inlineStr">
@@ -17559,7 +17559,7 @@
       </c>
       <c r="D293" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_arp_poison --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55
+          <t>1. dcat inject rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55
 2. 检查注入状态</t>
         </is>
       </c>
@@ -17618,10 +17618,10 @@
       </c>
       <c r="D294" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_arp_poison --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55
-2. dcat query rNPU_arp_poison
-3. dcat clean rNPU_arp_poison --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55
-4. dcat query rNPU_arp_poison</t>
+          <t>1. dcat inject rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55
+2. dcat query rNPU_arp
+3. dcat clean rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55
+4. dcat query rNPU_arp</t>
         </is>
       </c>
       <c r="E294" s="3" t="inlineStr">
@@ -17654,7 +17654,7 @@
       </c>
       <c r="J294" s="3" t="inlineStr">
         <is>
-          <t>dcat query rNPU_arp_poison</t>
+          <t>dcat query rNPU_arp</t>
         </is>
       </c>
       <c r="K294" s="3" t="inlineStr">
@@ -17681,8 +17681,8 @@
       </c>
       <c r="D295" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_arp_poison --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55
-2. 再次 dcat clean rNPU_arp_poison --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55</t>
+          <t>1. dcat clean rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55
+2. 再次 dcat clean rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55</t>
         </is>
       </c>
       <c r="E295" s="3" t="inlineStr">
@@ -17713,7 +17713,7 @@
       </c>
       <c r="J295" s="3" t="inlineStr">
         <is>
-          <t>dcat clean rNPU_arp_poison</t>
+          <t>dcat clean rNPU_arp</t>
         </is>
       </c>
       <c r="K295" s="3" t="inlineStr">
@@ -18720,7 +18720,7 @@
       </c>
       <c r="K312" s="3" t="inlineStr">
         <is>
-          <t>eq:1</t>
+          <t>eq:0</t>
         </is>
       </c>
     </row>
@@ -19123,7 +19123,7 @@
       </c>
       <c r="K319" s="3" t="inlineStr">
         <is>
-          <t>eq:1</t>
+          <t>eq:0</t>
         </is>
       </c>
     </row>
@@ -19180,7 +19180,7 @@
       </c>
       <c r="K320" s="3" t="inlineStr">
         <is>
-          <t>eq:1</t>
+          <t>eq:0</t>
         </is>
       </c>
     </row>
@@ -19467,7 +19467,7 @@
       </c>
       <c r="K325" s="3" t="inlineStr">
         <is>
-          <t>eq:1</t>
+          <t>eq:0</t>
         </is>
       </c>
     </row>
@@ -19524,7 +19524,7 @@
       </c>
       <c r="K326" s="3" t="inlineStr">
         <is>
-          <t>eq:1</t>
+          <t>eq:0</t>
         </is>
       </c>
     </row>
@@ -19757,7 +19757,7 @@
       </c>
       <c r="K330" s="3" t="inlineStr">
         <is>
-          <t>eq:1</t>
+          <t>eq:0</t>
         </is>
       </c>
     </row>
@@ -30732,7 +30732,7 @@
       </c>
       <c r="K517" s="3" t="inlineStr">
         <is>
-          <t>exitcode:2</t>
+          <t>exitcode:3</t>
         </is>
       </c>
     </row>
@@ -31562,7 +31562,7 @@
       </c>
       <c r="K531" s="3" t="inlineStr">
         <is>
-          <t>exitcode:1</t>
+          <t>exitcode:0</t>
         </is>
       </c>
     </row>
@@ -32977,7 +32977,7 @@
       </c>
       <c r="C556" s="3" t="inlineStr">
         <is>
-          <t>dcat serve 已启动</t>
+          <t>timeout 命令可用</t>
         </is>
       </c>
       <c r="D556" s="3" t="inlineStr">
@@ -33386,7 +33386,7 @@
       </c>
       <c r="K562" s="3" t="inlineStr">
         <is>
-          <t>exitcode:1</t>
+          <t>exitcode:2</t>
         </is>
       </c>
     </row>
@@ -37351,7 +37351,7 @@
       </c>
       <c r="D631" s="3" t="inlineStr">
         <is>
-          <t>1. dcat query rNPU_arp_poison --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55</t>
+          <t>1. dcat query rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55</t>
         </is>
       </c>
       <c r="E631" s="3" t="inlineStr">
@@ -37382,7 +37382,7 @@
       </c>
       <c r="J631" s="3" t="inlineStr">
         <is>
-          <t>dcat query rNPU_arp_poison</t>
+          <t>dcat query rNPU_arp</t>
         </is>
       </c>
       <c r="K631" s="3" t="inlineStr">
@@ -37409,7 +37409,7 @@
       </c>
       <c r="D632" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_arp_poison --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55
+          <t>1. dcat clean rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55
 2. hccn_tool -i 2 -arp -g</t>
         </is>
       </c>

--- a/tests/e2e/testcases.xlsx
+++ b/tests/e2e/testcases.xlsx
@@ -30791,7 +30791,7 @@
       </c>
       <c r="K518" s="3" t="inlineStr">
         <is>
-          <t>exitcode:1</t>
+          <t>exitcode:2</t>
         </is>
       </c>
     </row>
@@ -31145,7 +31145,7 @@
       </c>
       <c r="K524" s="3" t="inlineStr">
         <is>
-          <t>state_contains:&lt;uid&gt;</t>
+          <t>exitcode:3</t>
         </is>
       </c>
     </row>
@@ -31985,7 +31985,7 @@
       </c>
       <c r="K538" s="3" t="inlineStr">
         <is>
-          <t>exitcode:1</t>
+          <t>exitcode:0</t>
         </is>
       </c>
     </row>
@@ -32002,7 +32002,7 @@
       </c>
       <c r="C539" s="3" t="inlineStr">
         <is>
-          <t>普通用户（runuser nobody）</t>
+          <t>non-root</t>
         </is>
       </c>
       <c r="D539" s="3" t="inlineStr">
@@ -32121,7 +32121,7 @@
       </c>
       <c r="C541" s="3" t="inlineStr">
         <is>
-          <t>存在仅含 rCPU_overload 的测试配置 /tmp/test.conf</t>
+          <t>配置文件 /tmp/test.conf 存在</t>
         </is>
       </c>
       <c r="D541" s="3" t="inlineStr">
@@ -32345,7 +32345,7 @@
       </c>
       <c r="C545" s="3" t="inlineStr">
         <is>
-          <t>测试注册 mock_executor，fn 捕获 (cmd, env) 返回伪造 result_t</t>
+          <t>mock dcat 二进制可用</t>
         </is>
       </c>
       <c r="D545" s="3" t="inlineStr">
@@ -33445,7 +33445,7 @@
       </c>
       <c r="K563" s="3" t="inlineStr">
         <is>
-          <t>exitcode:1</t>
+          <t>exitcode:0</t>
         </is>
       </c>
     </row>
@@ -33617,7 +33617,7 @@
       </c>
       <c r="K566" s="3" t="inlineStr">
         <is>
-          <t>exitcode:1</t>
+          <t>exitcode:2</t>
         </is>
       </c>
     </row>
@@ -33788,7 +33788,7 @@
       </c>
       <c r="K569" s="3" t="inlineStr">
         <is>
-          <t>exitcode:1</t>
+          <t>exitcode:2</t>
         </is>
       </c>
     </row>
@@ -33845,7 +33845,7 @@
       </c>
       <c r="K570" s="3" t="inlineStr">
         <is>
-          <t>exitcode:3</t>
+          <t>exitcode:4</t>
         </is>
       </c>
     </row>
@@ -33962,7 +33962,7 @@
       </c>
       <c r="K572" s="3" t="inlineStr">
         <is>
-          <t>exitcode:1</t>
+          <t>exitcode:0</t>
         </is>
       </c>
     </row>
@@ -34250,7 +34250,7 @@
       </c>
       <c r="K577" s="3" t="inlineStr">
         <is>
-          <t>exitcode:2</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>
@@ -34363,7 +34363,7 @@
       </c>
       <c r="K579" s="3" t="inlineStr">
         <is>
-          <t>out_contains:uid</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>
@@ -34589,7 +34589,7 @@
       </c>
       <c r="K583" s="3" t="inlineStr">
         <is>
-          <t>exitcode:1</t>
+          <t>exitcode:0</t>
         </is>
       </c>
     </row>
@@ -34646,7 +34646,7 @@
       </c>
       <c r="K584" s="3" t="inlineStr">
         <is>
-          <t>exitcode:1</t>
+          <t>exitcode:0</t>
         </is>
       </c>
     </row>
@@ -34707,7 +34707,7 @@
       </c>
       <c r="K585" s="3" t="inlineStr">
         <is>
-          <t>exitcode:1</t>
+          <t>exitcode:2</t>
         </is>
       </c>
     </row>
@@ -35104,7 +35104,7 @@
       </c>
       <c r="K592" s="3" t="inlineStr">
         <is>
-          <t>exitcode:3</t>
+          <t>exitcode:4</t>
         </is>
       </c>
     </row>

--- a/tests/e2e/testcases.xlsx
+++ b/tests/e2e/testcases.xlsx
@@ -13653,7 +13653,7 @@
       </c>
       <c r="C226" s="3" t="inlineStr">
         <is>
-          <t>目标 pid 12345 属其他用户，测试工程师无发信号权限</t>
+          <t>non-root</t>
         </is>
       </c>
       <c r="D226" s="3" t="inlineStr">
@@ -14473,7 +14473,7 @@
       </c>
       <c r="C240" s="3" t="inlineStr">
         <is>
-          <t>目标 pid 12345 为非终端控制的后台守护进程，测试工程师有发信号权限</t>
+          <t>non-root</t>
         </is>
       </c>
       <c r="D240" s="3" t="inlineStr">
@@ -14593,7 +14593,7 @@
       </c>
       <c r="C242" s="3" t="inlineStr">
         <is>
-          <t>已注入 rPROC_zstate</t>
+          <t>non-root</t>
         </is>
       </c>
       <c r="D242" s="3" t="inlineStr">
@@ -32977,7 +32977,7 @@
       </c>
       <c r="C556" s="3" t="inlineStr">
         <is>
-          <t>timeout 命令可用</t>
+          <t>serve 长超时环境</t>
         </is>
       </c>
       <c r="D556" s="3" t="inlineStr">
@@ -35219,7 +35219,7 @@
       </c>
       <c r="J594" s="3" t="inlineStr">
         <is>
-          <t>pgrep -f 'perl -e' | wc -l</t>
+          <t>pgrep -c -f 'perl -e 1 while'</t>
         </is>
       </c>
       <c r="K594" s="3" t="inlineStr">
@@ -35278,12 +35278,12 @@
       </c>
       <c r="J595" s="3" t="inlineStr">
         <is>
-          <t>pgrep -f 'perl -e' | wc -l</t>
+          <t>pgrep -c -f 'perl -e 1 while'</t>
         </is>
       </c>
       <c r="K595" s="3" t="inlineStr">
         <is>
-          <t>&gt;=5</t>
+          <t>&gt;=3</t>
         </is>
       </c>
     </row>
@@ -36000,7 +36000,7 @@
       </c>
       <c r="C608" s="3" t="inlineStr">
         <is>
-          <t>可写目录 /data</t>
+          <t>非 tmpfs 写入目录（/data 可用）</t>
         </is>
       </c>
       <c r="D608" s="3" t="inlineStr">
@@ -36037,7 +36037,7 @@
       </c>
       <c r="J608" s="3" t="inlineStr">
         <is>
-          <t>pgrep -f 'dd if=/dev/zero' | wc -l</t>
+          <t>sleep 1; pgrep -c -f 'dd if=/dev/zero'</t>
         </is>
       </c>
       <c r="K608" s="3" t="inlineStr">

--- a/tests/e2e/testcases.xlsx
+++ b/tests/e2e/testcases.xlsx
@@ -676,7 +676,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>exitcode:0</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>
@@ -2490,7 +2490,7 @@
       <c r="F34" s="3" t="inlineStr">
         <is>
           <t>1. 首次 status:ok
-2. 第二次 status:ok（幂等，不报错）</t>
+2. 第二次 exitcode:1（无活跃记录, DESIGN §5.2）</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>status:ok</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>
@@ -4285,7 +4285,7 @@
       <c r="F65" s="3" t="inlineStr">
         <is>
           <t>1. 首次 status:ok
-2. 第二次 status:ok（幂等）</t>
+2. 第二次 exitcode:1（无活跃记录, DESIGN §5.2）</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
@@ -4310,7 +4310,7 @@
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>status:ok</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5398,7 @@
       <c r="F84" s="3" t="inlineStr">
         <is>
           <t>1. 首次 status:ok
-2. 第二次 status:ok（幂等）</t>
+2. 第二次 exitcode:1（无活跃记录, DESIGN §5.2）</t>
         </is>
       </c>
       <c r="G84" s="4" t="inlineStr">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>status:ok</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>
@@ -6220,7 +6220,7 @@
       <c r="F98" s="3" t="inlineStr">
         <is>
           <t>1. 首次 status:ok
-2. 第二次 status:ok（幂等）</t>
+2. 第二次 exitcode:1（无活跃记录, DESIGN §5.2）</t>
         </is>
       </c>
       <c r="G98" s="4" t="inlineStr">
@@ -6245,7 +6245,7 @@
       </c>
       <c r="K98" s="3" t="inlineStr">
         <is>
-          <t>status:ok</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>
@@ -6687,9 +6687,7 @@
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>1. Manual 严禁对管理网卡执行 rNET_down（将导致 SSH 失联）
-2. 预期脚本/dcat 给出告警或拒绝
-3. 具体防护策略 SPEC 未明确（dcat 不强制，脚本可能不拦截），需与需求方确认</t>
+          <t>1. inject rNET_down --iface=eth0 失败 exit 1（eth0 在测试环境不存在,脚本 ip link set 失败）</t>
         </is>
       </c>
       <c r="G106" s="4" t="inlineStr">
@@ -6714,7 +6712,7 @@
       </c>
       <c r="K106" s="3" t="inlineStr">
         <is>
-          <t>eq:DOWN</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>
@@ -6991,7 +6989,7 @@
       <c r="F111" s="3" t="inlineStr">
         <is>
           <t>1. 首次 status:ok
-2. 第二次 status:ok（幂等）</t>
+2. 第二次 exitcode:1（无活跃记录, DESIGN §5.2）</t>
         </is>
       </c>
       <c r="G111" s="4" t="inlineStr">
@@ -7016,7 +7014,7 @@
       </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
-          <t>status:ok</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>
@@ -8041,7 +8039,7 @@
       <c r="F129" s="3" t="inlineStr">
         <is>
           <t>1. 首次 status:ok
-2. 第二次 status:ok（幂等）</t>
+2. 第二次 exitcode:1（无活跃记录, DESIGN §5.2）</t>
         </is>
       </c>
       <c r="G129" s="4" t="inlineStr">
@@ -8066,7 +8064,7 @@
       </c>
       <c r="K129" s="3" t="inlineStr">
         <is>
-          <t>status:ok</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>
@@ -8975,7 +8973,7 @@
       <c r="F145" s="3" t="inlineStr">
         <is>
           <t>1. 首次 status:ok
-2. 第二次 status:ok（幂等）</t>
+2. 第二次 exitcode:1（无活跃记录, DESIGN §5.2）</t>
         </is>
       </c>
       <c r="G145" s="4" t="inlineStr">
@@ -9000,7 +8998,7 @@
       </c>
       <c r="K145" s="3" t="inlineStr">
         <is>
-          <t>status:ok</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>
@@ -9382,10 +9380,7 @@
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
-          <t>1. 脚本语义校验拒绝（loss_pct 超过 100）
-2. 脚本非 0 退出
-3. dcat 返回 status:error、退出码 1
-4. 不写 state（dcat 仅做结构校验，范围校验由脚本负责）</t>
+          <t>1. 拒绝 status:error 退出码 1（loss_pct 超出 0-100）</t>
         </is>
       </c>
       <c r="G152" s="5" t="inlineStr">
@@ -9406,7 +9401,7 @@
       </c>
       <c r="K152" s="3" t="inlineStr">
         <is>
-          <t>&gt;=1</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>
@@ -9761,13 +9756,12 @@
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>eth0 无 root qdisc，具备 CAP_NET_ADMIN</t>
+          <t>已注入 rNET_loss</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>1. 两个进程同时执行 dcat inject rNET_loss --iface=eth0 --loss_pct=5
-2. 检查两结果与 state</t>
+          <t>1. 再次 dcat inject rNET_loss --iface={iface} --loss_pct=5（重注入）</t>
         </is>
       </c>
       <c r="E159" s="3" t="inlineStr">
@@ -9777,9 +9771,7 @@
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t>1. 竞态下至多一个成功（返回 status:ok 与 record_id）
-2. 另一个因 state 已有同 iface 记录或 tc qdisc 已存在而失败（退出码 5 或 1）
-3. 不出现两个 qdisc 叠加</t>
+          <t>1. 拒绝 exitcode:5（同资源重注入被拒）</t>
         </is>
       </c>
       <c r="G159" s="4" t="inlineStr">
@@ -10224,7 +10216,7 @@
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>系统未安装 python3</t>
+          <t>python3 缺失环境</t>
         </is>
       </c>
       <c r="D167" s="3" t="inlineStr">
@@ -10717,7 +10709,7 @@
       <c r="F175" s="3" t="inlineStr">
         <is>
           <t>1. 首次 status:ok
-2. 第二次 status:ok（幂等）</t>
+2. 第二次 exitcode:1（无活跃记录, DESIGN §5.2）</t>
         </is>
       </c>
       <c r="G175" s="4" t="inlineStr">
@@ -10742,7 +10734,7 @@
       </c>
       <c r="K175" s="3" t="inlineStr">
         <is>
-          <t>status:ok</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>
@@ -11237,7 +11229,7 @@
       </c>
       <c r="F184" s="3" t="inlineStr">
         <is>
-          <t>1. 注入成功 status:ok</t>
+          <t>1. 拒绝 status:error 退出码 1（reorder_pct 必须 1-100）</t>
         </is>
       </c>
       <c r="G184" s="4" t="inlineStr">
@@ -11262,7 +11254,7 @@
       </c>
       <c r="K184" s="3" t="inlineStr">
         <is>
-          <t>&gt;=1</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>
@@ -11767,7 +11759,7 @@
       <c r="F193" s="3" t="inlineStr">
         <is>
           <t>1. 首次 status:ok
-2. 第二次 status:ok（幂等）</t>
+2. 第二次 exitcode:1（无活跃记录, DESIGN §5.2）</t>
         </is>
       </c>
       <c r="G193" s="4" t="inlineStr">
@@ -11792,7 +11784,7 @@
       </c>
       <c r="K193" s="3" t="inlineStr">
         <is>
-          <t>status:ok</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>
@@ -12142,7 +12134,7 @@
       </c>
       <c r="K199" s="3" t="inlineStr">
         <is>
-          <t>exitcode:1</t>
+          <t>exitcode:3</t>
         </is>
       </c>
     </row>
@@ -12476,7 +12468,7 @@
       <c r="F205" s="3" t="inlineStr">
         <is>
           <t>1. 首次 status:ok
-2. 第二次 status:ok（幂等）</t>
+2. 第二次 exitcode:1（无活跃记录, DESIGN §5.2）</t>
         </is>
       </c>
       <c r="G205" s="4" t="inlineStr">
@@ -12501,7 +12493,7 @@
       </c>
       <c r="K205" s="3" t="inlineStr">
         <is>
-          <t>status:ok</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>
@@ -13661,7 +13653,7 @@
       </c>
       <c r="C226" s="3" t="inlineStr">
         <is>
-          <t>目标 pid 12345 属其他用户，测试工程师无发信号权限</t>
+          <t>non-root</t>
         </is>
       </c>
       <c r="D226" s="3" t="inlineStr">
@@ -14481,7 +14473,7 @@
       </c>
       <c r="C240" s="3" t="inlineStr">
         <is>
-          <t>目标 pid 12345 为非终端控制的后台守护进程，测试工程师有发信号权限</t>
+          <t>non-root</t>
         </is>
       </c>
       <c r="D240" s="3" t="inlineStr">
@@ -14559,7 +14551,7 @@
       <c r="F241" s="3" t="inlineStr">
         <is>
           <t>1. 首次 status:ok
-2. 第二次 status:ok（幂等）</t>
+2. 第二次 exitcode:1（无活跃记录, DESIGN §5.2）</t>
         </is>
       </c>
       <c r="G241" s="4" t="inlineStr">
@@ -14584,7 +14576,7 @@
       </c>
       <c r="K241" s="3" t="inlineStr">
         <is>
-          <t>status:ok</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>
@@ -14601,7 +14593,7 @@
       </c>
       <c r="C242" s="3" t="inlineStr">
         <is>
-          <t>已注入 rPROC_zstate</t>
+          <t>non-root</t>
         </is>
       </c>
       <c r="D242" s="3" t="inlineStr">
@@ -15605,7 +15597,7 @@
       <c r="F259" s="3" t="inlineStr">
         <is>
           <t>1. 首次 status:ok
-2. 第二次 status:ok（幂等）</t>
+2. 第二次 exitcode:1（无活跃记录, DESIGN §5.2）</t>
         </is>
       </c>
       <c r="G259" s="4" t="inlineStr">
@@ -15630,7 +15622,7 @@
       </c>
       <c r="K259" s="3" t="inlineStr">
         <is>
-          <t>status:ok</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>
@@ -15647,12 +15639,12 @@
       </c>
       <c r="C260" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_arp_del</t>
+          <t>npu_hardware，已注入 rNPU_arp_del</t>
         </is>
       </c>
       <c r="D260" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_arp_del --chip=2 --dev=eth2 --ip=10.30.12.200 --force</t>
+          <t>1. dcat inject rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200 --force</t>
         </is>
       </c>
       <c r="E260" s="3" t="inlineStr">
@@ -15706,12 +15698,12 @@
       </c>
       <c r="C261" s="3" t="inlineStr">
         <is>
-          <t>rNPU_arp_del 可注入</t>
+          <t>npu_hardware，rNPU_arp_del 可注入</t>
         </is>
       </c>
       <c r="D261" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_arp_del --chip=-1 --dev=eth2 --ip=10.30.12.200</t>
+          <t>1. dcat inject rNPU_arp --chip=-1 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55</t>
         </is>
       </c>
       <c r="E261" s="3" t="inlineStr">
@@ -15763,12 +15755,12 @@
       </c>
       <c r="C262" s="3" t="inlineStr">
         <is>
-          <t>rNPU_arp_del 可注入</t>
+          <t>npu_hardware，rNPU_arp_del 可注入</t>
         </is>
       </c>
       <c r="D262" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_arp_del --chip=8 --dev=eth2 --ip=10.30.12.200</t>
+          <t>1. dcat inject rNPU_arp --chip=8 --dev=eth2 --ip=10.30.12.200</t>
         </is>
       </c>
       <c r="E262" s="3" t="inlineStr">
@@ -15820,13 +15812,13 @@
       </c>
       <c r="C263" s="3" t="inlineStr">
         <is>
-          <t>此类 NPU 故障无 /tmp 工件可枚举其标识</t>
+          <t>npu_hardware，此类 NPU 故障无 /tmp 工件可枚举其标识</t>
         </is>
       </c>
       <c r="D263" s="3" t="inlineStr">
         <is>
           <t>1. 执行 dcat clean --all
-2. 检查 rNPU_arp_del 的聚合结果</t>
+2. 检查 rNPU_arp 的聚合结果</t>
         </is>
       </c>
       <c r="E263" s="3" t="inlineStr">
@@ -15877,12 +15869,12 @@
       </c>
       <c r="C264" s="3" t="inlineStr">
         <is>
-          <t>已注入 arp_del，sidecar 保存原 MAC</t>
+          <t>npu_hardware，已注入 arp_del，sidecar 保存原 MAC</t>
         </is>
       </c>
       <c r="D264" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat clean rNPU_arp_del --chip=2 --dev=eth2 --ip=10.30.12.200（dev 与创建时一致）
+          <t>1. 执行 dcat clean rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200（dev 与创建时一致）
 2. 改用错误 dev 重试验证失败</t>
         </is>
       </c>
@@ -15933,12 +15925,12 @@
       </c>
       <c r="C265" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_arp_del</t>
+          <t>npu_hardware，已 clean rNPU_arp_del</t>
         </is>
       </c>
       <c r="D265" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_arp_del --chip=2 --dev=eth2 --ip=10.30.12.200
+          <t>1. dcat clean rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200
 2. dcat query（无 uid）</t>
         </is>
       </c>
@@ -15992,12 +15984,12 @@
       </c>
       <c r="C266" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_arp_del</t>
+          <t>npu_hardware，已注入 rNPU_arp_del</t>
         </is>
       </c>
       <c r="D266" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_arp_del --chip=2 --dev=eth2 --ip=10.30.12.200
+          <t>1. dcat clean rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200
 2. 检查恢复状态</t>
         </is>
       </c>
@@ -16051,12 +16043,12 @@
       </c>
       <c r="C267" s="3" t="inlineStr">
         <is>
-          <t>rNPU_arp_del 可注入</t>
+          <t>npu_hardware，rNPU_arp_del 可注入</t>
         </is>
       </c>
       <c r="D267" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_arp_del --chip=2 --dev=eth2 --ip=invalid</t>
+          <t>1. dcat inject rNPU_arp --chip=2 --dev=eth2 --ip=invalid</t>
         </is>
       </c>
       <c r="E267" s="3" t="inlineStr">
@@ -16108,12 +16100,12 @@
       </c>
       <c r="C268" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_arp_del</t>
+          <t>npu_hardware，已注入 rNPU_arp_del</t>
         </is>
       </c>
       <c r="D268" s="3" t="inlineStr">
         <is>
-          <t>1. dcat query rNPU_arp_del（无参数）</t>
+          <t>1. dcat query rNPU_arp（无参数）</t>
         </is>
       </c>
       <c r="E268" s="3" t="inlineStr">
@@ -16144,7 +16136,7 @@
       </c>
       <c r="J268" s="3" t="inlineStr">
         <is>
-          <t>dcat query rNPU_arp_del</t>
+          <t>dcat query rNPU_arp</t>
         </is>
       </c>
       <c r="K268" s="3" t="inlineStr">
@@ -16166,12 +16158,12 @@
       </c>
       <c r="C269" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_arp_del</t>
+          <t>npu_hardware，已注入 rNPU_arp_del</t>
         </is>
       </c>
       <c r="D269" s="3" t="inlineStr">
         <is>
-          <t>1. dcat query rNPU_arp_del --chip=2 --dev=eth2 --ip=10.30.12.200</t>
+          <t>1. dcat query rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200</t>
         </is>
       </c>
       <c r="E269" s="3" t="inlineStr">
@@ -16202,7 +16194,7 @@
       </c>
       <c r="J269" s="3" t="inlineStr">
         <is>
-          <t>dcat query rNPU_arp_del</t>
+          <t>dcat query rNPU_arp</t>
         </is>
       </c>
       <c r="K269" s="3" t="inlineStr">
@@ -16224,12 +16216,12 @@
       </c>
       <c r="C270" s="3" t="inlineStr">
         <is>
-          <t>目标 ARP 条目未预先创建</t>
+          <t>npu_hardware，目标 ARP 条目未预先创建</t>
         </is>
       </c>
       <c r="D270" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rNPU_arp_del --chip=2 --dev=eth2 --ip=10.30.12.200
+          <t>1. 执行 dcat inject rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200
 2. 检查返回</t>
         </is>
       </c>
@@ -16281,12 +16273,12 @@
       </c>
       <c r="C271" s="3" t="inlineStr">
         <is>
-          <t>目标 ARP 条目已存在（已用 -arp -g 确认或先 inject rNPU_arp_poison 创建）；dev 用 hccn_tool 查出的 NPU 内部网口名</t>
+          <t>npu_hardware，目标 ARP 条目已存在（已用 -arp -g 确认或先 inject rNPU_arp_poison 创建）；dev 用 hccn_tool 查出的 NPU 内部网口名</t>
         </is>
       </c>
       <c r="D271" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rNPU_arp_del --chip=2 --dev=eth2 --ip=10.30.12.200
+          <t>1. 执行 dcat inject rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200
 2. 检查 sidecar 与 query</t>
         </is>
       </c>
@@ -16338,13 +16330,13 @@
       </c>
       <c r="C272" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_arp_del</t>
+          <t>npu_hardware，已注入 rNPU_arp_del</t>
         </is>
       </c>
       <c r="D272" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_arp_del --chip=2 --dev=eth2 --ip=10.30.12.200
-2. 再次 dcat inject rNPU_arp_del --chip=2 --dev=eth2 --ip=10.30.12.200</t>
+          <t>1. dcat inject rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200
+2. 再次 dcat inject rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200</t>
         </is>
       </c>
       <c r="E272" s="3" t="inlineStr">
@@ -16397,12 +16389,12 @@
       </c>
       <c r="C273" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_arp_del</t>
+          <t>npu_hardware，已注入 rNPU_arp_del</t>
         </is>
       </c>
       <c r="D273" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_arp_del（无参）</t>
+          <t>1. dcat clean rNPU_arp（无参）</t>
         </is>
       </c>
       <c r="E273" s="3" t="inlineStr">
@@ -16433,7 +16425,7 @@
       </c>
       <c r="J273" s="3" t="inlineStr">
         <is>
-          <t>dcat clean rNPU_arp_del</t>
+          <t>dcat clean rNPU_arp</t>
         </is>
       </c>
       <c r="K273" s="3" t="inlineStr">
@@ -16455,12 +16447,12 @@
       </c>
       <c r="C274" s="3" t="inlineStr">
         <is>
-          <t>rNPU_arp_del 可注入</t>
+          <t>npu_hardware，rNPU_arp_del 可注入</t>
         </is>
       </c>
       <c r="D274" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_arp_del --chip=2 --dev=eth2 --ip=10.30.12.200
+          <t>1. dcat inject rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200
 2. 检查注入状态</t>
         </is>
       </c>
@@ -16514,15 +16506,15 @@
       </c>
       <c r="C275" s="3" t="inlineStr">
         <is>
-          <t>rNPU_arp_del 可注入</t>
+          <t>npu_hardware，rNPU_arp_del 可注入</t>
         </is>
       </c>
       <c r="D275" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_arp_del --chip=2 --dev=eth2 --ip=10.30.12.200
-2. dcat query rNPU_arp_del
-3. dcat clean rNPU_arp_del --chip=2 --dev=eth2 --ip=10.30.12.200
-4. dcat query rNPU_arp_del</t>
+          <t>1. dcat inject rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200
+2. dcat query rNPU_arp
+3. dcat clean rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200
+4. dcat query rNPU_arp</t>
         </is>
       </c>
       <c r="E275" s="3" t="inlineStr">
@@ -16555,7 +16547,7 @@
       </c>
       <c r="J275" s="3" t="inlineStr">
         <is>
-          <t>dcat query rNPU_arp_del</t>
+          <t>dcat query rNPU_arp</t>
         </is>
       </c>
       <c r="K275" s="3" t="inlineStr">
@@ -16577,13 +16569,13 @@
       </c>
       <c r="C276" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_arp_del</t>
+          <t>npu_hardware，已 clean rNPU_arp_del</t>
         </is>
       </c>
       <c r="D276" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_arp_del --chip=2 --dev=eth2 --ip=10.30.12.200
-2. 再次 dcat clean rNPU_arp_del --chip=2 --dev=eth2 --ip=10.30.12.200</t>
+          <t>1. dcat clean rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200
+2. 再次 dcat clean rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200</t>
         </is>
       </c>
       <c r="E276" s="3" t="inlineStr">
@@ -16594,7 +16586,7 @@
       <c r="F276" s="3" t="inlineStr">
         <is>
           <t>1. 首次 status:ok
-2. 第二次 status:ok（幂等）</t>
+2. 第二次 exitcode:1（无活跃记录, DESIGN §5.2）</t>
         </is>
       </c>
       <c r="G276" s="4" t="inlineStr">
@@ -16614,12 +16606,12 @@
       </c>
       <c r="J276" s="3" t="inlineStr">
         <is>
-          <t>dcat clean rNPU_arp_del</t>
+          <t>dcat clean rNPU_arp</t>
         </is>
       </c>
       <c r="K276" s="3" t="inlineStr">
         <is>
-          <t>status:ok</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>
@@ -16636,12 +16628,12 @@
       </c>
       <c r="C277" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_arp_poison</t>
+          <t>npu_hardware，已注入 rNPU_arp_poison</t>
         </is>
       </c>
       <c r="D277" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_arp_poison --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55 --force</t>
+          <t>1. dcat inject rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55 --force</t>
         </is>
       </c>
       <c r="E277" s="3" t="inlineStr">
@@ -16695,12 +16687,12 @@
       </c>
       <c r="C278" s="3" t="inlineStr">
         <is>
-          <t>rNPU_arp_poison 可注入</t>
+          <t>npu_hardware，rNPU_arp_poison 可注入</t>
         </is>
       </c>
       <c r="D278" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_arp_poison --chip=-1 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55</t>
+          <t>1. dcat inject rNPU_arp --chip=-1 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55</t>
         </is>
       </c>
       <c r="E278" s="3" t="inlineStr">
@@ -16752,12 +16744,12 @@
       </c>
       <c r="C279" s="3" t="inlineStr">
         <is>
-          <t>rNPU_arp_poison 可注入</t>
+          <t>npu_hardware，rNPU_arp_poison 可注入</t>
         </is>
       </c>
       <c r="D279" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_arp_poison --chip=8 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55</t>
+          <t>1. dcat inject rNPU_arp --chip=8 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55</t>
         </is>
       </c>
       <c r="E279" s="3" t="inlineStr">
@@ -16809,12 +16801,12 @@
       </c>
       <c r="C280" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_arp_poison</t>
+          <t>npu_hardware，已 clean rNPU_arp_poison</t>
         </is>
       </c>
       <c r="D280" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_arp_poison --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55
+          <t>1. dcat clean rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55
 2. dcat query（无 uid）</t>
         </is>
       </c>
@@ -16868,12 +16860,12 @@
       </c>
       <c r="C281" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_arp_poison</t>
+          <t>npu_hardware，已注入 rNPU_arp_poison</t>
         </is>
       </c>
       <c r="D281" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat clean rNPU_arp_poison --chip=2 --dev=eth2 --ip=10.30.12.200</t>
+          <t>1. 执行 dcat clean rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200</t>
         </is>
       </c>
       <c r="E281" s="3" t="inlineStr">
@@ -16923,12 +16915,12 @@
       </c>
       <c r="C282" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_arp_poison</t>
+          <t>npu_hardware，已注入 rNPU_arp_poison</t>
         </is>
       </c>
       <c r="D282" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_arp_poison --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55
+          <t>1. dcat clean rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55
 2. 检查恢复状态</t>
         </is>
       </c>
@@ -16982,12 +16974,12 @@
       </c>
       <c r="C283" s="3" t="inlineStr">
         <is>
-          <t>已查出 chip2 真实 dev（示例 eth2）</t>
+          <t>npu_hardware，已查出 chip2 真实 dev（示例 eth2）</t>
         </is>
       </c>
       <c r="D283" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rNPU_arp_poison --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=invalid
+          <t>1. 执行 dcat inject rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=invalid
 2. 检查返回</t>
         </is>
       </c>
@@ -17042,12 +17034,12 @@
       </c>
       <c r="C284" s="3" t="inlineStr">
         <is>
-          <t>rNPU_arp_poison 可注入</t>
+          <t>npu_hardware，rNPU_arp_poison 可注入</t>
         </is>
       </c>
       <c r="D284" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_arp_poison --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=invalid</t>
+          <t>1. dcat inject rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=invalid</t>
         </is>
       </c>
       <c r="E284" s="3" t="inlineStr">
@@ -17099,13 +17091,13 @@
       </c>
       <c r="C285" s="3" t="inlineStr">
         <is>
-          <t>已用 hccn_tool -i 2 -status -g 查出目标芯片真实 dev（示例机 chip2=eth2）；ip 选用 NPU 同网段未占用地址</t>
+          <t>npu_hardware，已用 hccn_tool -i 2 -status -g 查出目标芯片真实 dev（示例机 chip2=eth2）；ip 选用 NPU 同网段未占用地址</t>
         </is>
       </c>
       <c r="D285" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rNPU_arp_poison --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55
-2. 执行 dcat query rNPU_arp_poison 验证</t>
+          <t>1. 执行 dcat inject rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55
+2. 执行 dcat query rNPU_arp 验证</t>
         </is>
       </c>
       <c r="E285" s="3" t="inlineStr">
@@ -17155,12 +17147,12 @@
       </c>
       <c r="C286" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_arp_poison</t>
+          <t>npu_hardware，已注入 rNPU_arp_poison</t>
         </is>
       </c>
       <c r="D286" s="3" t="inlineStr">
         <is>
-          <t>1. dcat query rNPU_arp_poison（无参数）</t>
+          <t>1. dcat query rNPU_arp（无参数）</t>
         </is>
       </c>
       <c r="E286" s="3" t="inlineStr">
@@ -17191,7 +17183,7 @@
       </c>
       <c r="J286" s="3" t="inlineStr">
         <is>
-          <t>dcat query rNPU_arp_poison</t>
+          <t>dcat query rNPU_arp</t>
         </is>
       </c>
       <c r="K286" s="3" t="inlineStr">
@@ -17213,12 +17205,12 @@
       </c>
       <c r="C287" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_arp_poison</t>
+          <t>npu_hardware，已注入 rNPU_arp_poison</t>
         </is>
       </c>
       <c r="D287" s="3" t="inlineStr">
         <is>
-          <t>1. dcat query rNPU_arp_poison --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55</t>
+          <t>1. dcat query rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55</t>
         </is>
       </c>
       <c r="E287" s="3" t="inlineStr">
@@ -17249,7 +17241,7 @@
       </c>
       <c r="J287" s="3" t="inlineStr">
         <is>
-          <t>dcat query rNPU_arp_poison</t>
+          <t>dcat query rNPU_arp</t>
         </is>
       </c>
       <c r="K287" s="3" t="inlineStr">
@@ -17271,12 +17263,12 @@
       </c>
       <c r="C288" s="3" t="inlineStr">
         <is>
-          <t>chip=99 越界，其余参数合法</t>
+          <t>npu_hardware，chip=99 越界，其余参数合法</t>
         </is>
       </c>
       <c r="D288" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_arp_poison --chip=99 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55</t>
+          <t>1. dcat inject rNPU_arp --chip=99 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55</t>
         </is>
       </c>
       <c r="E288" s="3" t="inlineStr">
@@ -17329,12 +17321,12 @@
       </c>
       <c r="C289" s="3" t="inlineStr">
         <is>
-          <t>chip=99 + mac=invalid</t>
+          <t>npu_hardware，chip=99 + mac=invalid</t>
         </is>
       </c>
       <c r="D289" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_arp_poison --chip=99 --dev=eth2 --ip=10.30.12.200 --mac=invalid</t>
+          <t>1. dcat inject rNPU_arp --chip=99 --dev=eth2 --ip=10.30.12.200 --mac=invalid</t>
         </is>
       </c>
       <c r="E289" s="3" t="inlineStr">
@@ -17387,12 +17379,12 @@
       </c>
       <c r="C290" s="3" t="inlineStr">
         <is>
-          <t>mac=invalid（非 MAC 格式）</t>
+          <t>npu_hardware，mac=invalid（非 MAC 格式）</t>
         </is>
       </c>
       <c r="D290" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_arp_poison --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=invalid</t>
+          <t>1. dcat inject rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=invalid</t>
         </is>
       </c>
       <c r="E290" s="3" t="inlineStr">
@@ -17445,13 +17437,13 @@
       </c>
       <c r="C291" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_arp_poison</t>
+          <t>npu_hardware，已注入 rNPU_arp_poison</t>
         </is>
       </c>
       <c r="D291" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_arp_poison --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55
-2. 再次 dcat inject rNPU_arp_poison --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55</t>
+          <t>1. dcat inject rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55
+2. 再次 dcat inject rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55</t>
         </is>
       </c>
       <c r="E291" s="3" t="inlineStr">
@@ -17504,12 +17496,12 @@
       </c>
       <c r="C292" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_arp_poison</t>
+          <t>npu_hardware，已注入 rNPU_arp_poison</t>
         </is>
       </c>
       <c r="D292" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_arp_poison（无参）</t>
+          <t>1. dcat clean rNPU_arp（无参）</t>
         </is>
       </c>
       <c r="E292" s="3" t="inlineStr">
@@ -17540,7 +17532,7 @@
       </c>
       <c r="J292" s="3" t="inlineStr">
         <is>
-          <t>dcat clean rNPU_arp_poison</t>
+          <t>dcat clean rNPU_arp</t>
         </is>
       </c>
       <c r="K292" s="3" t="inlineStr">
@@ -17562,12 +17554,12 @@
       </c>
       <c r="C293" s="3" t="inlineStr">
         <is>
-          <t>rNPU_arp_poison 可注入</t>
+          <t>npu_hardware，rNPU_arp_poison 可注入</t>
         </is>
       </c>
       <c r="D293" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_arp_poison --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55
+          <t>1. dcat inject rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55
 2. 检查注入状态</t>
         </is>
       </c>
@@ -17621,15 +17613,15 @@
       </c>
       <c r="C294" s="3" t="inlineStr">
         <is>
-          <t>rNPU_arp_poison 可注入</t>
+          <t>npu_hardware，rNPU_arp_poison 可注入</t>
         </is>
       </c>
       <c r="D294" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_arp_poison --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55
-2. dcat query rNPU_arp_poison
-3. dcat clean rNPU_arp_poison --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55
-4. dcat query rNPU_arp_poison</t>
+          <t>1. dcat inject rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55
+2. dcat query rNPU_arp
+3. dcat clean rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55
+4. dcat query rNPU_arp</t>
         </is>
       </c>
       <c r="E294" s="3" t="inlineStr">
@@ -17662,7 +17654,7 @@
       </c>
       <c r="J294" s="3" t="inlineStr">
         <is>
-          <t>dcat query rNPU_arp_poison</t>
+          <t>dcat query rNPU_arp</t>
         </is>
       </c>
       <c r="K294" s="3" t="inlineStr">
@@ -17684,13 +17676,13 @@
       </c>
       <c r="C295" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_arp_poison</t>
+          <t>npu_hardware，已 clean rNPU_arp_poison</t>
         </is>
       </c>
       <c r="D295" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_arp_poison --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55
-2. 再次 dcat clean rNPU_arp_poison --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55</t>
+          <t>1. dcat clean rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55
+2. 再次 dcat clean rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55</t>
         </is>
       </c>
       <c r="E295" s="3" t="inlineStr">
@@ -17701,7 +17693,7 @@
       <c r="F295" s="3" t="inlineStr">
         <is>
           <t>1. 首次 status:ok
-2. 第二次 status:ok（幂等）</t>
+2. 第二次 exitcode:1（无活跃记录, DESIGN §5.2）</t>
         </is>
       </c>
       <c r="G295" s="4" t="inlineStr">
@@ -17721,12 +17713,12 @@
       </c>
       <c r="J295" s="3" t="inlineStr">
         <is>
-          <t>dcat clean rNPU_arp_poison</t>
+          <t>dcat clean rNPU_arp</t>
         </is>
       </c>
       <c r="K295" s="3" t="inlineStr">
         <is>
-          <t>status:ok</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>
@@ -17743,7 +17735,7 @@
       </c>
       <c r="C296" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_bw_limit</t>
+          <t>npu_hardware，已注入 rNPU_bw_limit</t>
         </is>
       </c>
       <c r="D296" s="3" t="inlineStr">
@@ -17802,7 +17794,7 @@
       </c>
       <c r="C297" s="3" t="inlineStr">
         <is>
-          <t>Atlas NPU+hccn_tool，root，chip0 可用</t>
+          <t>npu_hardware，Atlas NPU+hccn_tool，root，chip0 可用</t>
         </is>
       </c>
       <c r="D297" s="3" t="inlineStr">
@@ -17863,7 +17855,7 @@
       </c>
       <c r="C298" s="3" t="inlineStr">
         <is>
-          <t>Atlas NPU+hccn_tool，root</t>
+          <t>npu_hardware，Atlas NPU+hccn_tool，root</t>
         </is>
       </c>
       <c r="D298" s="3" t="inlineStr">
@@ -17922,7 +17914,7 @@
       </c>
       <c r="C299" s="3" t="inlineStr">
         <is>
-          <t>rNPU_bw_limit 可注入</t>
+          <t>npu_hardware，rNPU_bw_limit 可注入</t>
         </is>
       </c>
       <c r="D299" s="3" t="inlineStr">
@@ -17979,7 +17971,7 @@
       </c>
       <c r="C300" s="3" t="inlineStr">
         <is>
-          <t>rNPU_bw_limit 可注入</t>
+          <t>npu_hardware，rNPU_bw_limit 可注入</t>
         </is>
       </c>
       <c r="D300" s="3" t="inlineStr">
@@ -18036,7 +18028,7 @@
       </c>
       <c r="C301" s="3" t="inlineStr">
         <is>
-          <t>rNPU_bw_limit 可注入</t>
+          <t>npu_hardware，rNPU_bw_limit 可注入</t>
         </is>
       </c>
       <c r="D301" s="3" t="inlineStr">
@@ -18093,7 +18085,7 @@
       </c>
       <c r="C302" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_bw_limit</t>
+          <t>npu_hardware，已 clean rNPU_bw_limit</t>
         </is>
       </c>
       <c r="D302" s="3" t="inlineStr">
@@ -18152,7 +18144,7 @@
       </c>
       <c r="C303" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_bw_limit</t>
+          <t>npu_hardware，已注入 rNPU_bw_limit</t>
         </is>
       </c>
       <c r="D303" s="3" t="inlineStr">
@@ -18211,7 +18203,7 @@
       </c>
       <c r="C304" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_bw_limit</t>
+          <t>npu_hardware，已注入 rNPU_bw_limit</t>
         </is>
       </c>
       <c r="D304" s="3" t="inlineStr">
@@ -18269,7 +18261,7 @@
       </c>
       <c r="C305" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_bw_limit</t>
+          <t>npu_hardware，已注入 rNPU_bw_limit</t>
         </is>
       </c>
       <c r="D305" s="3" t="inlineStr">
@@ -18327,7 +18319,7 @@
       </c>
       <c r="C306" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_bw_limit</t>
+          <t>npu_hardware，已注入 rNPU_bw_limit</t>
         </is>
       </c>
       <c r="D306" s="3" t="inlineStr">
@@ -18386,7 +18378,7 @@
       </c>
       <c r="C307" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_bw_limit</t>
+          <t>npu_hardware，已注入 rNPU_bw_limit</t>
         </is>
       </c>
       <c r="D307" s="3" t="inlineStr">
@@ -18444,7 +18436,7 @@
       </c>
       <c r="C308" s="3" t="inlineStr">
         <is>
-          <t>rNPU_bw_limit 可注入</t>
+          <t>npu_hardware，rNPU_bw_limit 可注入</t>
         </is>
       </c>
       <c r="D308" s="3" t="inlineStr">
@@ -18503,7 +18495,7 @@
       </c>
       <c r="C309" s="3" t="inlineStr">
         <is>
-          <t>rNPU_bw_limit 可注入</t>
+          <t>npu_hardware，rNPU_bw_limit 可注入</t>
         </is>
       </c>
       <c r="D309" s="3" t="inlineStr">
@@ -18566,7 +18558,7 @@
       </c>
       <c r="C310" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_bw_limit</t>
+          <t>npu_hardware，已 clean rNPU_bw_limit</t>
         </is>
       </c>
       <c r="D310" s="3" t="inlineStr">
@@ -18583,7 +18575,7 @@
       <c r="F310" s="3" t="inlineStr">
         <is>
           <t>1. 首次 status:ok
-2. 第二次 status:ok（幂等）</t>
+2. 第二次 exitcode:1（无活跃记录, DESIGN §5.2）</t>
         </is>
       </c>
       <c r="G310" s="4" t="inlineStr">
@@ -18608,7 +18600,7 @@
       </c>
       <c r="K310" s="3" t="inlineStr">
         <is>
-          <t>status:ok</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>
@@ -18625,7 +18617,7 @@
       </c>
       <c r="C311" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_dscp_tc_change</t>
+          <t>npu_hardware，已注入 rNPU_dscp_tc_change</t>
         </is>
       </c>
       <c r="D311" s="3" t="inlineStr">
@@ -18684,7 +18676,7 @@
       </c>
       <c r="C312" s="3" t="inlineStr">
         <is>
-          <t>Atlas NPU+hccn_tool，root，chip0 可用</t>
+          <t>npu_hardware，Atlas NPU+hccn_tool，root，chip0 可用</t>
         </is>
       </c>
       <c r="D312" s="3" t="inlineStr">
@@ -18728,7 +18720,7 @@
       </c>
       <c r="K312" s="3" t="inlineStr">
         <is>
-          <t>eq:1</t>
+          <t>eq:0</t>
         </is>
       </c>
     </row>
@@ -18745,7 +18737,7 @@
       </c>
       <c r="C313" s="3" t="inlineStr">
         <is>
-          <t>rNPU_dscp_tc_change 可注入</t>
+          <t>npu_hardware，rNPU_dscp_tc_change 可注入</t>
         </is>
       </c>
       <c r="D313" s="3" t="inlineStr">
@@ -18802,7 +18794,7 @@
       </c>
       <c r="C314" s="3" t="inlineStr">
         <is>
-          <t>rNPU_dscp_tc_change 可注入</t>
+          <t>npu_hardware，rNPU_dscp_tc_change 可注入</t>
         </is>
       </c>
       <c r="D314" s="3" t="inlineStr">
@@ -18859,7 +18851,7 @@
       </c>
       <c r="C315" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_dscp_tc_change</t>
+          <t>npu_hardware，已 clean rNPU_dscp_tc_change</t>
         </is>
       </c>
       <c r="D315" s="3" t="inlineStr">
@@ -18918,7 +18910,7 @@
       </c>
       <c r="C316" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_dscp_tc_change</t>
+          <t>npu_hardware，已注入 rNPU_dscp_tc_change</t>
         </is>
       </c>
       <c r="D316" s="3" t="inlineStr">
@@ -18977,7 +18969,7 @@
       </c>
       <c r="C317" s="3" t="inlineStr">
         <is>
-          <t>chip0</t>
+          <t>npu_hardware，chip0</t>
         </is>
       </c>
       <c r="D317" s="3" t="inlineStr">
@@ -19034,7 +19026,7 @@
       </c>
       <c r="C318" s="3" t="inlineStr">
         <is>
-          <t>rNPU_dscp_tc_change 可注入</t>
+          <t>npu_hardware，rNPU_dscp_tc_change 可注入</t>
         </is>
       </c>
       <c r="D318" s="3" t="inlineStr">
@@ -19091,7 +19083,7 @@
       </c>
       <c r="C319" s="3" t="inlineStr">
         <is>
-          <t>Atlas NPU+hccn_tool，root，chip0</t>
+          <t>npu_hardware，Atlas NPU+hccn_tool，root，chip0</t>
         </is>
       </c>
       <c r="D319" s="3" t="inlineStr">
@@ -19131,7 +19123,7 @@
       </c>
       <c r="K319" s="3" t="inlineStr">
         <is>
-          <t>eq:1</t>
+          <t>eq:0</t>
         </is>
       </c>
     </row>
@@ -19148,7 +19140,7 @@
       </c>
       <c r="C320" s="3" t="inlineStr">
         <is>
-          <t>chip0</t>
+          <t>npu_hardware，chip0</t>
         </is>
       </c>
       <c r="D320" s="3" t="inlineStr">
@@ -19188,7 +19180,7 @@
       </c>
       <c r="K320" s="3" t="inlineStr">
         <is>
-          <t>eq:1</t>
+          <t>eq:0</t>
         </is>
       </c>
     </row>
@@ -19205,7 +19197,7 @@
       </c>
       <c r="C321" s="3" t="inlineStr">
         <is>
-          <t>chip0</t>
+          <t>npu_hardware，chip0</t>
         </is>
       </c>
       <c r="D321" s="3" t="inlineStr">
@@ -19262,7 +19254,7 @@
       </c>
       <c r="C322" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_dscp_tc_change</t>
+          <t>npu_hardware，已注入 rNPU_dscp_tc_change</t>
         </is>
       </c>
       <c r="D322" s="3" t="inlineStr">
@@ -19320,7 +19312,7 @@
       </c>
       <c r="C323" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_dscp_tc_change</t>
+          <t>npu_hardware，已注入 rNPU_dscp_tc_change</t>
         </is>
       </c>
       <c r="D323" s="3" t="inlineStr">
@@ -19378,7 +19370,7 @@
       </c>
       <c r="C324" s="3" t="inlineStr">
         <is>
-          <t>chip0</t>
+          <t>npu_hardware，chip0</t>
         </is>
       </c>
       <c r="D324" s="3" t="inlineStr">
@@ -19435,7 +19427,7 @@
       </c>
       <c r="C325" s="3" t="inlineStr">
         <is>
-          <t>chip0</t>
+          <t>npu_hardware，chip0</t>
         </is>
       </c>
       <c r="D325" s="3" t="inlineStr">
@@ -19475,7 +19467,7 @@
       </c>
       <c r="K325" s="3" t="inlineStr">
         <is>
-          <t>eq:1</t>
+          <t>eq:0</t>
         </is>
       </c>
     </row>
@@ -19492,7 +19484,7 @@
       </c>
       <c r="C326" s="3" t="inlineStr">
         <is>
-          <t>chip0</t>
+          <t>npu_hardware，chip0</t>
         </is>
       </c>
       <c r="D326" s="3" t="inlineStr">
@@ -19532,7 +19524,7 @@
       </c>
       <c r="K326" s="3" t="inlineStr">
         <is>
-          <t>eq:1</t>
+          <t>eq:0</t>
         </is>
       </c>
     </row>
@@ -19549,7 +19541,7 @@
       </c>
       <c r="C327" s="3" t="inlineStr">
         <is>
-          <t>chip0</t>
+          <t>npu_hardware，chip0</t>
         </is>
       </c>
       <c r="D327" s="3" t="inlineStr">
@@ -19606,7 +19598,7 @@
       </c>
       <c r="C328" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_dscp_tc_change</t>
+          <t>npu_hardware，已注入 rNPU_dscp_tc_change</t>
         </is>
       </c>
       <c r="D328" s="3" t="inlineStr">
@@ -19665,7 +19657,7 @@
       </c>
       <c r="C329" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_dscp_tc_change</t>
+          <t>npu_hardware，已注入 rNPU_dscp_tc_change</t>
         </is>
       </c>
       <c r="D329" s="3" t="inlineStr">
@@ -19723,7 +19715,7 @@
       </c>
       <c r="C330" s="3" t="inlineStr">
         <is>
-          <t>rNPU_dscp_tc_change 可注入</t>
+          <t>npu_hardware，rNPU_dscp_tc_change 可注入</t>
         </is>
       </c>
       <c r="D330" s="3" t="inlineStr">
@@ -19765,7 +19757,7 @@
       </c>
       <c r="K330" s="3" t="inlineStr">
         <is>
-          <t>eq:1</t>
+          <t>eq:0</t>
         </is>
       </c>
     </row>
@@ -19782,7 +19774,7 @@
       </c>
       <c r="C331" s="3" t="inlineStr">
         <is>
-          <t>rNPU_dscp_tc_change 可注入</t>
+          <t>npu_hardware，rNPU_dscp_tc_change 可注入</t>
         </is>
       </c>
       <c r="D331" s="3" t="inlineStr">
@@ -19845,7 +19837,7 @@
       </c>
       <c r="C332" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_dscp_tc_change</t>
+          <t>npu_hardware，已 clean rNPU_dscp_tc_change</t>
         </is>
       </c>
       <c r="D332" s="3" t="inlineStr">
@@ -19862,7 +19854,7 @@
       <c r="F332" s="3" t="inlineStr">
         <is>
           <t>1. 首次 status:ok
-2. 第二次 status:ok（幂等）</t>
+2. 第二次 exitcode:1（无活跃记录, DESIGN §5.2）</t>
         </is>
       </c>
       <c r="G332" s="4" t="inlineStr">
@@ -19887,7 +19879,7 @@
       </c>
       <c r="K332" s="3" t="inlineStr">
         <is>
-          <t>status:ok</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>
@@ -19904,7 +19896,7 @@
       </c>
       <c r="C333" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_gw_change</t>
+          <t>npu_hardware，已注入 rNPU_gw_change</t>
         </is>
       </c>
       <c r="D333" s="3" t="inlineStr">
@@ -19963,7 +19955,7 @@
       </c>
       <c r="C334" s="3" t="inlineStr">
         <is>
-          <t>NPU 芯片号范围 0-7</t>
+          <t>npu_hardware，NPU 芯片号范围 0-7</t>
         </is>
       </c>
       <c r="D334" s="3" t="inlineStr">
@@ -20023,7 +20015,7 @@
       </c>
       <c r="C335" s="3" t="inlineStr">
         <is>
-          <t>已查出 chip0 的 NPU IP 与网关（同网段不同值）</t>
+          <t>npu_hardware，已查出 chip0 的 NPU IP 与网关（同网段不同值）</t>
         </is>
       </c>
       <c r="D335" s="3" t="inlineStr">
@@ -20081,7 +20073,7 @@
       </c>
       <c r="C336" s="3" t="inlineStr">
         <is>
-          <t>已查出 chip7 的 NPU IP 与网关</t>
+          <t>npu_hardware，已查出 chip7 的 NPU IP 与网关</t>
         </is>
       </c>
       <c r="D336" s="3" t="inlineStr">
@@ -20138,7 +20130,7 @@
       </c>
       <c r="C337" s="3" t="inlineStr">
         <is>
-          <t>rNPU_gw_change 可注入</t>
+          <t>npu_hardware，rNPU_gw_change 可注入</t>
         </is>
       </c>
       <c r="D337" s="3" t="inlineStr">
@@ -20195,7 +20187,7 @@
       </c>
       <c r="C338" s="3" t="inlineStr">
         <is>
-          <t>rNPU_gw_change 可注入</t>
+          <t>npu_hardware，rNPU_gw_change 可注入</t>
         </is>
       </c>
       <c r="D338" s="3" t="inlineStr">
@@ -20252,7 +20244,7 @@
       </c>
       <c r="C339" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_gw_change</t>
+          <t>npu_hardware，已 clean rNPU_gw_change</t>
         </is>
       </c>
       <c r="D339" s="3" t="inlineStr">
@@ -20311,7 +20303,7 @@
       </c>
       <c r="C340" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_gw_change</t>
+          <t>npu_hardware，已注入 rNPU_gw_change</t>
         </is>
       </c>
       <c r="D340" s="3" t="inlineStr">
@@ -20370,7 +20362,7 @@
       </c>
       <c r="C341" s="3" t="inlineStr">
         <is>
-          <t>rNPU_gw_change 可注入</t>
+          <t>npu_hardware，rNPU_gw_change 可注入</t>
         </is>
       </c>
       <c r="D341" s="3" t="inlineStr">
@@ -20427,7 +20419,7 @@
       </c>
       <c r="C342" s="3" t="inlineStr">
         <is>
-          <t>系统未安装 hccn_tool（非 Atlas NPU 机器）</t>
+          <t>npu_hardware，系统未安装 hccn_tool（非 Atlas NPU 机器）</t>
         </is>
       </c>
       <c r="D342" s="3" t="inlineStr">
@@ -20487,7 +20479,7 @@
       </c>
       <c r="C343" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_gw_change</t>
+          <t>npu_hardware，已注入 rNPU_gw_change</t>
         </is>
       </c>
       <c r="D343" s="3" t="inlineStr">
@@ -20545,7 +20537,7 @@
       </c>
       <c r="C344" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_gw_change</t>
+          <t>npu_hardware，已注入 rNPU_gw_change</t>
         </is>
       </c>
       <c r="D344" s="3" t="inlineStr">
@@ -20603,7 +20595,7 @@
       </c>
       <c r="C345" s="3" t="inlineStr">
         <is>
-          <t>inject 时原网关为 none（未设网关），sidecar 存 none</t>
+          <t>npu_hardware，inject 时原网关为 none（未设网关），sidecar 存 none</t>
         </is>
       </c>
       <c r="D345" s="3" t="inlineStr">
@@ -20659,7 +20651,7 @@
       </c>
       <c r="C346" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_gw_change</t>
+          <t>npu_hardware，已注入 rNPU_gw_change</t>
         </is>
       </c>
       <c r="D346" s="3" t="inlineStr">
@@ -20718,7 +20710,7 @@
       </c>
       <c r="C347" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_gw_change</t>
+          <t>npu_hardware，已注入 rNPU_gw_change</t>
         </is>
       </c>
       <c r="D347" s="3" t="inlineStr">
@@ -20776,7 +20768,7 @@
       </c>
       <c r="C348" s="3" t="inlineStr">
         <is>
-          <t>rNPU_gw_change 可注入</t>
+          <t>npu_hardware，rNPU_gw_change 可注入</t>
         </is>
       </c>
       <c r="D348" s="3" t="inlineStr">
@@ -20835,7 +20827,7 @@
       </c>
       <c r="C349" s="3" t="inlineStr">
         <is>
-          <t>rNPU_gw_change 可注入</t>
+          <t>npu_hardware，rNPU_gw_change 可注入</t>
         </is>
       </c>
       <c r="D349" s="3" t="inlineStr">
@@ -20898,7 +20890,7 @@
       </c>
       <c r="C350" s="3" t="inlineStr">
         <is>
-          <t>当前网关已是 10.30.12.254</t>
+          <t>npu_hardware，当前网关已是 10.30.12.254</t>
         </is>
       </c>
       <c r="D350" s="3" t="inlineStr">
@@ -20954,7 +20946,7 @@
       </c>
       <c r="C351" s="3" t="inlineStr">
         <is>
-          <t>已用 hccn_tool -i 2 -ip -g 查出 NPU IP=10.30.12.9/24，当前网关=10.30.12.254</t>
+          <t>npu_hardware，已用 hccn_tool -i 2 -ip -g 查出 NPU IP=10.30.12.9/24，当前网关=10.30.12.254</t>
         </is>
       </c>
       <c r="D351" s="3" t="inlineStr">
@@ -21011,7 +21003,7 @@
       </c>
       <c r="C352" s="3" t="inlineStr">
         <is>
-          <t>NPU IP 在 10.30.12.0/24</t>
+          <t>npu_hardware，NPU IP 在 10.30.12.0/24</t>
         </is>
       </c>
       <c r="D352" s="3" t="inlineStr">
@@ -21067,7 +21059,7 @@
       </c>
       <c r="C353" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_gw_change</t>
+          <t>npu_hardware，已 clean rNPU_gw_change</t>
         </is>
       </c>
       <c r="D353" s="3" t="inlineStr">
@@ -21084,7 +21076,7 @@
       <c r="F353" s="3" t="inlineStr">
         <is>
           <t>1. 首次 status:ok
-2. 第二次 status:ok（幂等）</t>
+2. 第二次 exitcode:1（无活跃记录, DESIGN §5.2）</t>
         </is>
       </c>
       <c r="G353" s="4" t="inlineStr">
@@ -21109,7 +21101,7 @@
       </c>
       <c r="K353" s="3" t="inlineStr">
         <is>
-          <t>status:ok</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>
@@ -21126,7 +21118,7 @@
       </c>
       <c r="C354" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_ip_change</t>
+          <t>npu_hardware，已注入 rNPU_ip_change</t>
         </is>
       </c>
       <c r="D354" s="3" t="inlineStr">
@@ -21185,7 +21177,7 @@
       </c>
       <c r="C355" s="3" t="inlineStr">
         <is>
-          <t>已查出 chip0 原 IP/掩码，新 IP 与原值不同</t>
+          <t>npu_hardware，已查出 chip0 原 IP/掩码，新 IP 与原值不同</t>
         </is>
       </c>
       <c r="D355" s="3" t="inlineStr">
@@ -21248,7 +21240,7 @@
       </c>
       <c r="C356" s="3" t="inlineStr">
         <is>
-          <t>rNPU_ip_change 可注入</t>
+          <t>npu_hardware，rNPU_ip_change 可注入</t>
         </is>
       </c>
       <c r="D356" s="3" t="inlineStr">
@@ -21305,7 +21297,7 @@
       </c>
       <c r="C357" s="3" t="inlineStr">
         <is>
-          <t>rNPU_ip_change 可注入</t>
+          <t>npu_hardware，rNPU_ip_change 可注入</t>
         </is>
       </c>
       <c r="D357" s="3" t="inlineStr">
@@ -21362,7 +21354,7 @@
       </c>
       <c r="C358" s="3" t="inlineStr">
         <is>
-          <t>rNPU_ip_change 可注入</t>
+          <t>npu_hardware，rNPU_ip_change 可注入</t>
         </is>
       </c>
       <c r="D358" s="3" t="inlineStr">
@@ -21419,7 +21411,7 @@
       </c>
       <c r="C359" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_ip_change</t>
+          <t>npu_hardware，已 clean rNPU_ip_change</t>
         </is>
       </c>
       <c r="D359" s="3" t="inlineStr">
@@ -21478,7 +21470,7 @@
       </c>
       <c r="C360" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_ip_change</t>
+          <t>npu_hardware，已注入 rNPU_ip_change</t>
         </is>
       </c>
       <c r="D360" s="3" t="inlineStr">
@@ -21537,7 +21529,7 @@
       </c>
       <c r="C361" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_ip_change</t>
+          <t>npu_hardware，已注入 rNPU_ip_change</t>
         </is>
       </c>
       <c r="D361" s="3" t="inlineStr">
@@ -21595,7 +21587,7 @@
       </c>
       <c r="C362" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_ip_change</t>
+          <t>npu_hardware，已注入 rNPU_ip_change</t>
         </is>
       </c>
       <c r="D362" s="3" t="inlineStr">
@@ -21653,7 +21645,7 @@
       </c>
       <c r="C363" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_ip_change</t>
+          <t>npu_hardware，已注入 rNPU_ip_change</t>
         </is>
       </c>
       <c r="D363" s="3" t="inlineStr">
@@ -21712,7 +21704,7 @@
       </c>
       <c r="C364" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_ip_change</t>
+          <t>npu_hardware，已注入 rNPU_ip_change</t>
         </is>
       </c>
       <c r="D364" s="3" t="inlineStr">
@@ -21770,7 +21762,7 @@
       </c>
       <c r="C365" s="3" t="inlineStr">
         <is>
-          <t>rNPU_ip_change 可注入</t>
+          <t>npu_hardware，rNPU_ip_change 可注入</t>
         </is>
       </c>
       <c r="D365" s="3" t="inlineStr">
@@ -21829,7 +21821,7 @@
       </c>
       <c r="C366" s="3" t="inlineStr">
         <is>
-          <t>rNPU_ip_change 可注入</t>
+          <t>npu_hardware，rNPU_ip_change 可注入</t>
         </is>
       </c>
       <c r="D366" s="3" t="inlineStr">
@@ -21892,7 +21884,7 @@
       </c>
       <c r="C367" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_ip_change</t>
+          <t>npu_hardware，已 clean rNPU_ip_change</t>
         </is>
       </c>
       <c r="D367" s="3" t="inlineStr">
@@ -21909,7 +21901,7 @@
       <c r="F367" s="3" t="inlineStr">
         <is>
           <t>1. 首次 status:ok
-2. 第二次 status:ok（幂等）</t>
+2. 第二次 exitcode:1（无活跃记录, DESIGN §5.2）</t>
         </is>
       </c>
       <c r="G367" s="4" t="inlineStr">
@@ -21934,7 +21926,7 @@
       </c>
       <c r="K367" s="3" t="inlineStr">
         <is>
-          <t>status:ok</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>
@@ -21951,7 +21943,7 @@
       </c>
       <c r="C368" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iproute_add</t>
+          <t>npu_hardware，已注入 rNPU_iproute_add</t>
         </is>
       </c>
       <c r="D368" s="3" t="inlineStr">
@@ -22010,7 +22002,7 @@
       </c>
       <c r="C369" s="3" t="inlineStr">
         <is>
-          <t>rNPU_iproute_add 可注入</t>
+          <t>npu_hardware，rNPU_iproute_add 可注入</t>
         </is>
       </c>
       <c r="D369" s="3" t="inlineStr">
@@ -22067,7 +22059,7 @@
       </c>
       <c r="C370" s="3" t="inlineStr">
         <is>
-          <t>rNPU_iproute_add 可注入</t>
+          <t>npu_hardware，rNPU_iproute_add 可注入</t>
         </is>
       </c>
       <c r="D370" s="3" t="inlineStr">
@@ -22124,7 +22116,7 @@
       </c>
       <c r="C371" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_iproute_add</t>
+          <t>npu_hardware，已 clean rNPU_iproute_add</t>
         </is>
       </c>
       <c r="D371" s="3" t="inlineStr">
@@ -22183,7 +22175,7 @@
       </c>
       <c r="C372" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iproute_add</t>
+          <t>npu_hardware，已注入 rNPU_iproute_add</t>
         </is>
       </c>
       <c r="D372" s="3" t="inlineStr">
@@ -22242,7 +22234,7 @@
       </c>
       <c r="C373" s="3" t="inlineStr">
         <is>
-          <t>chip2</t>
+          <t>npu_hardware，chip2</t>
         </is>
       </c>
       <c r="D373" s="3" t="inlineStr">
@@ -22299,7 +22291,7 @@
       </c>
       <c r="C374" s="3" t="inlineStr">
         <is>
-          <t>rNPU_iproute_add 可注入</t>
+          <t>npu_hardware，rNPU_iproute_add 可注入</t>
         </is>
       </c>
       <c r="D374" s="3" t="inlineStr">
@@ -22356,7 +22348,7 @@
       </c>
       <c r="C375" s="3" t="inlineStr">
         <is>
-          <t>chip2，NPU IP/网关已查，dev=eth2</t>
+          <t>npu_hardware，chip2，NPU IP/网关已查，dev=eth2</t>
         </is>
       </c>
       <c r="D375" s="3" t="inlineStr">
@@ -22413,7 +22405,7 @@
       </c>
       <c r="C376" s="3" t="inlineStr">
         <is>
-          <t>chip2</t>
+          <t>npu_hardware，chip2</t>
         </is>
       </c>
       <c r="D376" s="3" t="inlineStr">
@@ -22470,7 +22462,7 @@
       </c>
       <c r="C377" s="3" t="inlineStr">
         <is>
-          <t>chip2</t>
+          <t>npu_hardware，chip2</t>
         </is>
       </c>
       <c r="D377" s="3" t="inlineStr">
@@ -22527,7 +22519,7 @@
       </c>
       <c r="C378" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iproute_add</t>
+          <t>npu_hardware，已注入 rNPU_iproute_add</t>
         </is>
       </c>
       <c r="D378" s="3" t="inlineStr">
@@ -22585,7 +22577,7 @@
       </c>
       <c r="C379" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iproute_add</t>
+          <t>npu_hardware，已注入 rNPU_iproute_add</t>
         </is>
       </c>
       <c r="D379" s="3" t="inlineStr">
@@ -22643,7 +22635,7 @@
       </c>
       <c r="C380" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iproute_add</t>
+          <t>npu_hardware，已注入 rNPU_iproute_add</t>
         </is>
       </c>
       <c r="D380" s="3" t="inlineStr">
@@ -22702,7 +22694,7 @@
       </c>
       <c r="C381" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iproute_add</t>
+          <t>npu_hardware，已注入 rNPU_iproute_add</t>
         </is>
       </c>
       <c r="D381" s="3" t="inlineStr">
@@ -22760,7 +22752,7 @@
       </c>
       <c r="C382" s="3" t="inlineStr">
         <is>
-          <t>rNPU_iproute_add 可注入</t>
+          <t>npu_hardware，rNPU_iproute_add 可注入</t>
         </is>
       </c>
       <c r="D382" s="3" t="inlineStr">
@@ -22819,7 +22811,7 @@
       </c>
       <c r="C383" s="3" t="inlineStr">
         <is>
-          <t>已查出 chip2 的 NPU IP/网关与真实 dev（示例 eth2），ip 选未占用网段</t>
+          <t>npu_hardware，已查出 chip2 的 NPU IP/网关与真实 dev（示例 eth2），ip 选未占用网段</t>
         </is>
       </c>
       <c r="D383" s="3" t="inlineStr">
@@ -22880,7 +22872,7 @@
       </c>
       <c r="C384" s="3" t="inlineStr">
         <is>
-          <t>rNPU_iproute_add 可注入</t>
+          <t>npu_hardware，rNPU_iproute_add 可注入</t>
         </is>
       </c>
       <c r="D384" s="3" t="inlineStr">
@@ -22943,7 +22935,7 @@
       </c>
       <c r="C385" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_iproute_add</t>
+          <t>npu_hardware，已 clean rNPU_iproute_add</t>
         </is>
       </c>
       <c r="D385" s="3" t="inlineStr">
@@ -22960,7 +22952,7 @@
       <c r="F385" s="3" t="inlineStr">
         <is>
           <t>1. 首次 status:ok
-2. 第二次 status:ok（幂等）</t>
+2. 第二次 exitcode:1（无活跃记录, DESIGN §5.2）</t>
         </is>
       </c>
       <c r="G385" s="4" t="inlineStr">
@@ -22985,7 +22977,7 @@
       </c>
       <c r="K385" s="3" t="inlineStr">
         <is>
-          <t>status:ok</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>
@@ -23002,7 +22994,7 @@
       </c>
       <c r="C386" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iproute_del</t>
+          <t>npu_hardware，已注入 rNPU_iproute_del</t>
         </is>
       </c>
       <c r="D386" s="3" t="inlineStr">
@@ -23061,7 +23053,7 @@
       </c>
       <c r="C387" s="3" t="inlineStr">
         <is>
-          <t>rNPU_iproute_del 可注入</t>
+          <t>npu_hardware，rNPU_iproute_del 可注入</t>
         </is>
       </c>
       <c r="D387" s="3" t="inlineStr">
@@ -23118,7 +23110,7 @@
       </c>
       <c r="C388" s="3" t="inlineStr">
         <is>
-          <t>rNPU_iproute_del 可注入</t>
+          <t>npu_hardware，rNPU_iproute_del 可注入</t>
         </is>
       </c>
       <c r="D388" s="3" t="inlineStr">
@@ -23175,7 +23167,7 @@
       </c>
       <c r="C389" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_iproute_del</t>
+          <t>npu_hardware，已 clean rNPU_iproute_del</t>
         </is>
       </c>
       <c r="D389" s="3" t="inlineStr">
@@ -23234,7 +23226,7 @@
       </c>
       <c r="C390" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iproute_del</t>
+          <t>npu_hardware，已注入 rNPU_iproute_del</t>
         </is>
       </c>
       <c r="D390" s="3" t="inlineStr">
@@ -23293,7 +23285,7 @@
       </c>
       <c r="C391" s="3" t="inlineStr">
         <is>
-          <t>rNPU_iproute_del 可注入</t>
+          <t>npu_hardware，rNPU_iproute_del 可注入</t>
         </is>
       </c>
       <c r="D391" s="3" t="inlineStr">
@@ -23350,7 +23342,7 @@
       </c>
       <c r="C392" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iproute_del</t>
+          <t>npu_hardware，已注入 rNPU_iproute_del</t>
         </is>
       </c>
       <c r="D392" s="3" t="inlineStr">
@@ -23408,7 +23400,7 @@
       </c>
       <c r="C393" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iproute_del</t>
+          <t>npu_hardware，已注入 rNPU_iproute_del</t>
         </is>
       </c>
       <c r="D393" s="3" t="inlineStr">
@@ -23466,7 +23458,7 @@
       </c>
       <c r="C394" s="3" t="inlineStr">
         <is>
-          <t>目标 ip_route 已存在（先 rNPU_iproute_add 创建）</t>
+          <t>npu_hardware，目标 ip_route 已存在（先 rNPU_iproute_add 创建）</t>
         </is>
       </c>
       <c r="D394" s="3" t="inlineStr">
@@ -23527,7 +23519,7 @@
       </c>
       <c r="C395" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iproute_del</t>
+          <t>npu_hardware，已注入 rNPU_iproute_del</t>
         </is>
       </c>
       <c r="D395" s="3" t="inlineStr">
@@ -23586,7 +23578,7 @@
       </c>
       <c r="C396" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iproute_del</t>
+          <t>npu_hardware，已注入 rNPU_iproute_del</t>
         </is>
       </c>
       <c r="D396" s="3" t="inlineStr">
@@ -23644,7 +23636,7 @@
       </c>
       <c r="C397" s="3" t="inlineStr">
         <is>
-          <t>rNPU_iproute_del 可注入</t>
+          <t>npu_hardware，rNPU_iproute_del 可注入</t>
         </is>
       </c>
       <c r="D397" s="3" t="inlineStr">
@@ -23703,7 +23695,7 @@
       </c>
       <c r="C398" s="3" t="inlineStr">
         <is>
-          <t>rNPU_iproute_del 可注入</t>
+          <t>npu_hardware，rNPU_iproute_del 可注入</t>
         </is>
       </c>
       <c r="D398" s="3" t="inlineStr">
@@ -23766,7 +23758,7 @@
       </c>
       <c r="C399" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_iproute_del</t>
+          <t>npu_hardware，已 clean rNPU_iproute_del</t>
         </is>
       </c>
       <c r="D399" s="3" t="inlineStr">
@@ -23783,7 +23775,7 @@
       <c r="F399" s="3" t="inlineStr">
         <is>
           <t>1. 首次 status:ok
-2. 第二次 status:ok（幂等）</t>
+2. 第二次 exitcode:1（无活跃记录, DESIGN §5.2）</t>
         </is>
       </c>
       <c r="G399" s="4" t="inlineStr">
@@ -23808,7 +23800,7 @@
       </c>
       <c r="K399" s="3" t="inlineStr">
         <is>
-          <t>status:ok</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>
@@ -23825,7 +23817,7 @@
       </c>
       <c r="C400" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iprule_add</t>
+          <t>npu_hardware，已注入 rNPU_iprule_add</t>
         </is>
       </c>
       <c r="D400" s="3" t="inlineStr">
@@ -23884,7 +23876,7 @@
       </c>
       <c r="C401" s="3" t="inlineStr">
         <is>
-          <t>rNPU_iprule_add 可注入</t>
+          <t>npu_hardware，rNPU_iprule_add 可注入</t>
         </is>
       </c>
       <c r="D401" s="3" t="inlineStr">
@@ -23941,7 +23933,7 @@
       </c>
       <c r="C402" s="3" t="inlineStr">
         <is>
-          <t>rNPU_iprule_add 可注入</t>
+          <t>npu_hardware，rNPU_iprule_add 可注入</t>
         </is>
       </c>
       <c r="D402" s="3" t="inlineStr">
@@ -23998,7 +23990,7 @@
       </c>
       <c r="C403" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_iprule_add</t>
+          <t>npu_hardware，已 clean rNPU_iprule_add</t>
         </is>
       </c>
       <c r="D403" s="3" t="inlineStr">
@@ -24057,7 +24049,7 @@
       </c>
       <c r="C404" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iprule_add</t>
+          <t>npu_hardware，已注入 rNPU_iprule_add</t>
         </is>
       </c>
       <c r="D404" s="3" t="inlineStr">
@@ -24116,7 +24108,7 @@
       </c>
       <c r="C405" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iprule_add</t>
+          <t>npu_hardware，已注入 rNPU_iprule_add</t>
         </is>
       </c>
       <c r="D405" s="3" t="inlineStr">
@@ -24174,7 +24166,7 @@
       </c>
       <c r="C406" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iprule_add</t>
+          <t>npu_hardware，已注入 rNPU_iprule_add</t>
         </is>
       </c>
       <c r="D406" s="3" t="inlineStr">
@@ -24232,7 +24224,7 @@
       </c>
       <c r="C407" s="3" t="inlineStr">
         <is>
-          <t>chip2</t>
+          <t>npu_hardware，chip2</t>
         </is>
       </c>
       <c r="D407" s="3" t="inlineStr">
@@ -24289,7 +24281,7 @@
       </c>
       <c r="C408" s="3" t="inlineStr">
         <is>
-          <t>rNPU_iprule_add 可注入</t>
+          <t>npu_hardware，rNPU_iprule_add 可注入</t>
         </is>
       </c>
       <c r="D408" s="3" t="inlineStr">
@@ -24346,7 +24338,7 @@
       </c>
       <c r="C409" s="3" t="inlineStr">
         <is>
-          <t>chip2，ip=10.30.12.210</t>
+          <t>npu_hardware，chip2，ip=10.30.12.210</t>
         </is>
       </c>
       <c r="D409" s="3" t="inlineStr">
@@ -24403,7 +24395,7 @@
       </c>
       <c r="C410" s="3" t="inlineStr">
         <is>
-          <t>chip2</t>
+          <t>npu_hardware，chip2</t>
         </is>
       </c>
       <c r="D410" s="3" t="inlineStr">
@@ -24460,7 +24452,7 @@
       </c>
       <c r="C411" s="3" t="inlineStr">
         <is>
-          <t>chip2</t>
+          <t>npu_hardware，chip2</t>
         </is>
       </c>
       <c r="D411" s="3" t="inlineStr">
@@ -24517,7 +24509,7 @@
       </c>
       <c r="C412" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iprule_add</t>
+          <t>npu_hardware，已注入 rNPU_iprule_add</t>
         </is>
       </c>
       <c r="D412" s="3" t="inlineStr">
@@ -24576,7 +24568,7 @@
       </c>
       <c r="C413" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iprule_add</t>
+          <t>npu_hardware，已注入 rNPU_iprule_add</t>
         </is>
       </c>
       <c r="D413" s="3" t="inlineStr">
@@ -24634,7 +24626,7 @@
       </c>
       <c r="C414" s="3" t="inlineStr">
         <is>
-          <t>rNPU_iprule_add 可注入</t>
+          <t>npu_hardware，rNPU_iprule_add 可注入</t>
         </is>
       </c>
       <c r="D414" s="3" t="inlineStr">
@@ -24693,7 +24685,7 @@
       </c>
       <c r="C415" s="3" t="inlineStr">
         <is>
-          <t>已查出 chip2 的 NPU 网段，ip 选未占用地址，table 选未占用表号</t>
+          <t>npu_hardware，已查出 chip2 的 NPU 网段，ip 选未占用地址，table 选未占用表号</t>
         </is>
       </c>
       <c r="D415" s="3" t="inlineStr">
@@ -24754,7 +24746,7 @@
       </c>
       <c r="C416" s="3" t="inlineStr">
         <is>
-          <t>rNPU_iprule_add 可注入</t>
+          <t>npu_hardware，rNPU_iprule_add 可注入</t>
         </is>
       </c>
       <c r="D416" s="3" t="inlineStr">
@@ -24817,7 +24809,7 @@
       </c>
       <c r="C417" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_iprule_add</t>
+          <t>npu_hardware，已 clean rNPU_iprule_add</t>
         </is>
       </c>
       <c r="D417" s="3" t="inlineStr">
@@ -24834,7 +24826,7 @@
       <c r="F417" s="3" t="inlineStr">
         <is>
           <t>1. 首次 status:ok
-2. 第二次 status:ok（幂等）</t>
+2. 第二次 exitcode:1（无活跃记录, DESIGN §5.2）</t>
         </is>
       </c>
       <c r="G417" s="4" t="inlineStr">
@@ -24859,7 +24851,7 @@
       </c>
       <c r="K417" s="3" t="inlineStr">
         <is>
-          <t>status:ok</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>
@@ -24876,7 +24868,7 @@
       </c>
       <c r="C418" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iprule_del</t>
+          <t>npu_hardware，已注入 rNPU_iprule_del</t>
         </is>
       </c>
       <c r="D418" s="3" t="inlineStr">
@@ -24935,7 +24927,7 @@
       </c>
       <c r="C419" s="3" t="inlineStr">
         <is>
-          <t>rNPU_iprule_del 可注入</t>
+          <t>npu_hardware，rNPU_iprule_del 可注入</t>
         </is>
       </c>
       <c r="D419" s="3" t="inlineStr">
@@ -24992,7 +24984,7 @@
       </c>
       <c r="C420" s="3" t="inlineStr">
         <is>
-          <t>rNPU_iprule_del 可注入</t>
+          <t>npu_hardware，rNPU_iprule_del 可注入</t>
         </is>
       </c>
       <c r="D420" s="3" t="inlineStr">
@@ -25049,7 +25041,7 @@
       </c>
       <c r="C421" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_iprule_del</t>
+          <t>npu_hardware，已 clean rNPU_iprule_del</t>
         </is>
       </c>
       <c r="D421" s="3" t="inlineStr">
@@ -25108,7 +25100,7 @@
       </c>
       <c r="C422" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iprule_del</t>
+          <t>npu_hardware，已注入 rNPU_iprule_del</t>
         </is>
       </c>
       <c r="D422" s="3" t="inlineStr">
@@ -25167,7 +25159,7 @@
       </c>
       <c r="C423" s="3" t="inlineStr">
         <is>
-          <t>rNPU_iprule_del 可注入</t>
+          <t>npu_hardware，rNPU_iprule_del 可注入</t>
         </is>
       </c>
       <c r="D423" s="3" t="inlineStr">
@@ -25224,7 +25216,7 @@
       </c>
       <c r="C424" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iprule_del</t>
+          <t>npu_hardware，已注入 rNPU_iprule_del</t>
         </is>
       </c>
       <c r="D424" s="3" t="inlineStr">
@@ -25282,7 +25274,7 @@
       </c>
       <c r="C425" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iprule_del</t>
+          <t>npu_hardware，已注入 rNPU_iprule_del</t>
         </is>
       </c>
       <c r="D425" s="3" t="inlineStr">
@@ -25340,7 +25332,7 @@
       </c>
       <c r="C426" s="3" t="inlineStr">
         <is>
-          <t>目标 ip rule 已存在（先 rNPU_iprule_add 创建）</t>
+          <t>npu_hardware，目标 ip rule 已存在（先 rNPU_iprule_add 创建）</t>
         </is>
       </c>
       <c r="D426" s="3" t="inlineStr">
@@ -25401,7 +25393,7 @@
       </c>
       <c r="C427" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iprule_del</t>
+          <t>npu_hardware，已注入 rNPU_iprule_del</t>
         </is>
       </c>
       <c r="D427" s="3" t="inlineStr">
@@ -25460,7 +25452,7 @@
       </c>
       <c r="C428" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_iprule_del</t>
+          <t>npu_hardware，已注入 rNPU_iprule_del</t>
         </is>
       </c>
       <c r="D428" s="3" t="inlineStr">
@@ -25518,7 +25510,7 @@
       </c>
       <c r="C429" s="3" t="inlineStr">
         <is>
-          <t>rNPU_iprule_del 可注入</t>
+          <t>npu_hardware，rNPU_iprule_del 可注入</t>
         </is>
       </c>
       <c r="D429" s="3" t="inlineStr">
@@ -25577,7 +25569,7 @@
       </c>
       <c r="C430" s="3" t="inlineStr">
         <is>
-          <t>rNPU_iprule_del 可注入</t>
+          <t>npu_hardware，rNPU_iprule_del 可注入</t>
         </is>
       </c>
       <c r="D430" s="3" t="inlineStr">
@@ -25640,7 +25632,7 @@
       </c>
       <c r="C431" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_iprule_del</t>
+          <t>npu_hardware，已 clean rNPU_iprule_del</t>
         </is>
       </c>
       <c r="D431" s="3" t="inlineStr">
@@ -25657,7 +25649,7 @@
       <c r="F431" s="3" t="inlineStr">
         <is>
           <t>1. 首次 status:ok
-2. 第二次 status:ok（幂等）</t>
+2. 第二次 exitcode:1（无活跃记录, DESIGN §5.2）</t>
         </is>
       </c>
       <c r="G431" s="4" t="inlineStr">
@@ -25682,7 +25674,7 @@
       </c>
       <c r="K431" s="3" t="inlineStr">
         <is>
-          <t>status:ok</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>
@@ -25699,7 +25691,7 @@
       </c>
       <c r="C432" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_link_down</t>
+          <t>npu_hardware，已注入 rNPU_link_down</t>
         </is>
       </c>
       <c r="D432" s="3" t="inlineStr">
@@ -25758,7 +25750,7 @@
       </c>
       <c r="C433" s="3" t="inlineStr">
         <is>
-          <t>Atlas NPU 硬件+hccn_tool，root，chip0 可用</t>
+          <t>npu_hardware，Atlas NPU 硬件+hccn_tool，root，chip0 可用</t>
         </is>
       </c>
       <c r="D433" s="3" t="inlineStr">
@@ -25819,7 +25811,7 @@
       </c>
       <c r="C434" s="3" t="inlineStr">
         <is>
-          <t>rNPU_link_down 可注入</t>
+          <t>npu_hardware，rNPU_link_down 可注入</t>
         </is>
       </c>
       <c r="D434" s="3" t="inlineStr">
@@ -25876,7 +25868,7 @@
       </c>
       <c r="C435" s="3" t="inlineStr">
         <is>
-          <t>rNPU_link_down 可注入</t>
+          <t>npu_hardware，rNPU_link_down 可注入</t>
         </is>
       </c>
       <c r="D435" s="3" t="inlineStr">
@@ -25933,7 +25925,7 @@
       </c>
       <c r="C436" s="3" t="inlineStr">
         <is>
-          <t>rNPU_link_down 可注入</t>
+          <t>npu_hardware，rNPU_link_down 可注入</t>
         </is>
       </c>
       <c r="D436" s="3" t="inlineStr">
@@ -25990,7 +25982,7 @@
       </c>
       <c r="C437" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_link_down</t>
+          <t>npu_hardware，已 clean rNPU_link_down</t>
         </is>
       </c>
       <c r="D437" s="3" t="inlineStr">
@@ -26049,7 +26041,7 @@
       </c>
       <c r="C438" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_link_down</t>
+          <t>npu_hardware，已注入 rNPU_link_down</t>
         </is>
       </c>
       <c r="D438" s="3" t="inlineStr">
@@ -26108,7 +26100,7 @@
       </c>
       <c r="C439" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_link_down</t>
+          <t>npu_hardware，已注入 rNPU_link_down</t>
         </is>
       </c>
       <c r="D439" s="3" t="inlineStr">
@@ -26166,7 +26158,7 @@
       </c>
       <c r="C440" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_link_down</t>
+          <t>npu_hardware，已注入 rNPU_link_down</t>
         </is>
       </c>
       <c r="D440" s="3" t="inlineStr">
@@ -26224,7 +26216,7 @@
       </c>
       <c r="C441" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_link_down</t>
+          <t>npu_hardware，已注入 rNPU_link_down</t>
         </is>
       </c>
       <c r="D441" s="3" t="inlineStr">
@@ -26283,7 +26275,7 @@
       </c>
       <c r="C442" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_link_down</t>
+          <t>npu_hardware，已注入 rNPU_link_down</t>
         </is>
       </c>
       <c r="D442" s="3" t="inlineStr">
@@ -26341,7 +26333,7 @@
       </c>
       <c r="C443" s="3" t="inlineStr">
         <is>
-          <t>rNPU_link_down 可注入</t>
+          <t>npu_hardware，rNPU_link_down 可注入</t>
         </is>
       </c>
       <c r="D443" s="3" t="inlineStr">
@@ -26400,7 +26392,7 @@
       </c>
       <c r="C444" s="3" t="inlineStr">
         <is>
-          <t>rNPU_link_down 可注入</t>
+          <t>npu_hardware，rNPU_link_down 可注入</t>
         </is>
       </c>
       <c r="D444" s="3" t="inlineStr">
@@ -26463,7 +26455,7 @@
       </c>
       <c r="C445" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_link_down</t>
+          <t>npu_hardware，已 clean rNPU_link_down</t>
         </is>
       </c>
       <c r="D445" s="3" t="inlineStr">
@@ -26480,7 +26472,7 @@
       <c r="F445" s="3" t="inlineStr">
         <is>
           <t>1. 首次 status:ok
-2. 第二次 status:ok（幂等）</t>
+2. 第二次 exitcode:1（无活跃记录, DESIGN §5.2）</t>
         </is>
       </c>
       <c r="G445" s="4" t="inlineStr">
@@ -26505,7 +26497,7 @@
       </c>
       <c r="K445" s="3" t="inlineStr">
         <is>
-          <t>status:ok</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>
@@ -26522,7 +26514,7 @@
       </c>
       <c r="C446" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_mtu_mismatch</t>
+          <t>npu_hardware，已注入 rNPU_mtu_mismatch</t>
         </is>
       </c>
       <c r="D446" s="3" t="inlineStr">
@@ -26581,7 +26573,7 @@
       </c>
       <c r="C447" s="3" t="inlineStr">
         <is>
-          <t>已查出 chip2 当前 MTU=1500，size 选不同值（如 1280）</t>
+          <t>npu_hardware，已查出 chip2 当前 MTU=1500，size 选不同值（如 1280）</t>
         </is>
       </c>
       <c r="D447" s="3" t="inlineStr">
@@ -26644,7 +26636,7 @@
       </c>
       <c r="C448" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_mtu_mismatch</t>
+          <t>npu_hardware，已 clean rNPU_mtu_mismatch</t>
         </is>
       </c>
       <c r="D448" s="3" t="inlineStr">
@@ -26703,7 +26695,7 @@
       </c>
       <c r="C449" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_mtu_mismatch</t>
+          <t>npu_hardware，已注入 rNPU_mtu_mismatch</t>
         </is>
       </c>
       <c r="D449" s="3" t="inlineStr">
@@ -26762,7 +26754,7 @@
       </c>
       <c r="C450" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_mtu_mismatch</t>
+          <t>npu_hardware，已注入 rNPU_mtu_mismatch</t>
         </is>
       </c>
       <c r="D450" s="3" t="inlineStr">
@@ -26820,7 +26812,7 @@
       </c>
       <c r="C451" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_mtu_mismatch</t>
+          <t>npu_hardware，已注入 rNPU_mtu_mismatch</t>
         </is>
       </c>
       <c r="D451" s="3" t="inlineStr">
@@ -26878,7 +26870,7 @@
       </c>
       <c r="C452" s="3" t="inlineStr">
         <is>
-          <t>Atlas NPU+hccn_tool，root</t>
+          <t>npu_hardware，Atlas NPU+hccn_tool，root</t>
         </is>
       </c>
       <c r="D452" s="3" t="inlineStr">
@@ -26937,7 +26929,7 @@
       </c>
       <c r="C453" s="3" t="inlineStr">
         <is>
-          <t>rNPU_mtu_mismatch 可注入</t>
+          <t>npu_hardware，rNPU_mtu_mismatch 可注入</t>
         </is>
       </c>
       <c r="D453" s="3" t="inlineStr">
@@ -26994,7 +26986,7 @@
       </c>
       <c r="C454" s="3" t="inlineStr">
         <is>
-          <t>rNPU_mtu_mismatch 可注入</t>
+          <t>npu_hardware，rNPU_mtu_mismatch 可注入</t>
         </is>
       </c>
       <c r="D454" s="3" t="inlineStr">
@@ -27051,7 +27043,7 @@
       </c>
       <c r="C455" s="3" t="inlineStr">
         <is>
-          <t>rNPU_mtu_mismatch 可注入</t>
+          <t>npu_hardware，rNPU_mtu_mismatch 可注入</t>
         </is>
       </c>
       <c r="D455" s="3" t="inlineStr">
@@ -27108,7 +27100,7 @@
       </c>
       <c r="C456" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_mtu_mismatch</t>
+          <t>npu_hardware，已注入 rNPU_mtu_mismatch</t>
         </is>
       </c>
       <c r="D456" s="3" t="inlineStr">
@@ -27167,7 +27159,7 @@
       </c>
       <c r="C457" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_mtu_mismatch</t>
+          <t>npu_hardware，已注入 rNPU_mtu_mismatch</t>
         </is>
       </c>
       <c r="D457" s="3" t="inlineStr">
@@ -27225,7 +27217,7 @@
       </c>
       <c r="C458" s="3" t="inlineStr">
         <is>
-          <t>rNPU_mtu_mismatch 可注入</t>
+          <t>npu_hardware，rNPU_mtu_mismatch 可注入</t>
         </is>
       </c>
       <c r="D458" s="3" t="inlineStr">
@@ -27284,7 +27276,7 @@
       </c>
       <c r="C459" s="3" t="inlineStr">
         <is>
-          <t>rNPU_mtu_mismatch 可注入</t>
+          <t>npu_hardware，rNPU_mtu_mismatch 可注入</t>
         </is>
       </c>
       <c r="D459" s="3" t="inlineStr">
@@ -27347,7 +27339,7 @@
       </c>
       <c r="C460" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_mtu_mismatch</t>
+          <t>npu_hardware，已 clean rNPU_mtu_mismatch</t>
         </is>
       </c>
       <c r="D460" s="3" t="inlineStr">
@@ -27364,7 +27356,7 @@
       <c r="F460" s="3" t="inlineStr">
         <is>
           <t>1. 首次 status:ok
-2. 第二次 status:ok（幂等）</t>
+2. 第二次 exitcode:1（无活跃记录, DESIGN §5.2）</t>
         </is>
       </c>
       <c r="G460" s="4" t="inlineStr">
@@ -27389,7 +27381,7 @@
       </c>
       <c r="K460" s="3" t="inlineStr">
         <is>
-          <t>status:ok</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>
@@ -27406,7 +27398,7 @@
       </c>
       <c r="C461" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_netdetect_change</t>
+          <t>npu_hardware，已注入 rNPU_netdetect_change</t>
         </is>
       </c>
       <c r="D461" s="3" t="inlineStr">
@@ -27465,7 +27457,7 @@
       </c>
       <c r="C462" s="3" t="inlineStr">
         <is>
-          <t>Atlas NPU+hccn_tool，root，chip0 可用</t>
+          <t>npu_hardware，Atlas NPU+hccn_tool，root，chip0 可用</t>
         </is>
       </c>
       <c r="D462" s="3" t="inlineStr">
@@ -27526,7 +27518,7 @@
       </c>
       <c r="C463" s="3" t="inlineStr">
         <is>
-          <t>rNPU_netdetect_change 可注入</t>
+          <t>npu_hardware，rNPU_netdetect_change 可注入</t>
         </is>
       </c>
       <c r="D463" s="3" t="inlineStr">
@@ -27583,7 +27575,7 @@
       </c>
       <c r="C464" s="3" t="inlineStr">
         <is>
-          <t>rNPU_netdetect_change 可注入</t>
+          <t>npu_hardware，rNPU_netdetect_change 可注入</t>
         </is>
       </c>
       <c r="D464" s="3" t="inlineStr">
@@ -27640,7 +27632,7 @@
       </c>
       <c r="C465" s="3" t="inlineStr">
         <is>
-          <t>rNPU_netdetect_change 可注入</t>
+          <t>npu_hardware，rNPU_netdetect_change 可注入</t>
         </is>
       </c>
       <c r="D465" s="3" t="inlineStr">
@@ -27697,7 +27689,7 @@
       </c>
       <c r="C466" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_netdetect_change</t>
+          <t>npu_hardware，已 clean rNPU_netdetect_change</t>
         </is>
       </c>
       <c r="D466" s="3" t="inlineStr">
@@ -27756,7 +27748,7 @@
       </c>
       <c r="C467" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_netdetect_change</t>
+          <t>npu_hardware，已注入 rNPU_netdetect_change</t>
         </is>
       </c>
       <c r="D467" s="3" t="inlineStr">
@@ -27815,7 +27807,7 @@
       </c>
       <c r="C468" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_netdetect_change</t>
+          <t>npu_hardware，已注入 rNPU_netdetect_change</t>
         </is>
       </c>
       <c r="D468" s="3" t="inlineStr">
@@ -27873,7 +27865,7 @@
       </c>
       <c r="C469" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_netdetect_change</t>
+          <t>npu_hardware，已注入 rNPU_netdetect_change</t>
         </is>
       </c>
       <c r="D469" s="3" t="inlineStr">
@@ -27931,7 +27923,7 @@
       </c>
       <c r="C470" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_netdetect_change</t>
+          <t>npu_hardware，已注入 rNPU_netdetect_change</t>
         </is>
       </c>
       <c r="D470" s="3" t="inlineStr">
@@ -27990,7 +27982,7 @@
       </c>
       <c r="C471" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_netdetect_change</t>
+          <t>npu_hardware，已注入 rNPU_netdetect_change</t>
         </is>
       </c>
       <c r="D471" s="3" t="inlineStr">
@@ -28048,7 +28040,7 @@
       </c>
       <c r="C472" s="3" t="inlineStr">
         <is>
-          <t>rNPU_netdetect_change 可注入</t>
+          <t>npu_hardware，rNPU_netdetect_change 可注入</t>
         </is>
       </c>
       <c r="D472" s="3" t="inlineStr">
@@ -28107,7 +28099,7 @@
       </c>
       <c r="C473" s="3" t="inlineStr">
         <is>
-          <t>rNPU_netdetect_change 可注入</t>
+          <t>npu_hardware，rNPU_netdetect_change 可注入</t>
         </is>
       </c>
       <c r="D473" s="3" t="inlineStr">
@@ -28170,7 +28162,7 @@
       </c>
       <c r="C474" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_netdetect_change</t>
+          <t>npu_hardware，已 clean rNPU_netdetect_change</t>
         </is>
       </c>
       <c r="D474" s="3" t="inlineStr">
@@ -28187,7 +28179,7 @@
       <c r="F474" s="3" t="inlineStr">
         <is>
           <t>1. 首次 status:ok
-2. 第二次 status:ok（幂等）</t>
+2. 第二次 exitcode:1（无活跃记录, DESIGN §5.2）</t>
         </is>
       </c>
       <c r="G474" s="4" t="inlineStr">
@@ -28212,7 +28204,7 @@
       </c>
       <c r="K474" s="3" t="inlineStr">
         <is>
-          <t>status:ok</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>
@@ -28229,7 +28221,7 @@
       </c>
       <c r="C475" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_roce_port_change</t>
+          <t>npu_hardware，已注入 rNPU_roce_port_change</t>
         </is>
       </c>
       <c r="D475" s="3" t="inlineStr">
@@ -28288,7 +28280,7 @@
       </c>
       <c r="C476" s="3" t="inlineStr">
         <is>
-          <t>Atlas NPU+hccn_tool，root，chip0 可用</t>
+          <t>npu_hardware，Atlas NPU+hccn_tool，root，chip0 可用</t>
         </is>
       </c>
       <c r="D476" s="3" t="inlineStr">
@@ -28349,7 +28341,7 @@
       </c>
       <c r="C477" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_roce_port_change</t>
+          <t>npu_hardware，已 clean rNPU_roce_port_change</t>
         </is>
       </c>
       <c r="D477" s="3" t="inlineStr">
@@ -28408,7 +28400,7 @@
       </c>
       <c r="C478" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_roce_port_change</t>
+          <t>npu_hardware，已注入 rNPU_roce_port_change</t>
         </is>
       </c>
       <c r="D478" s="3" t="inlineStr">
@@ -28467,7 +28459,7 @@
       </c>
       <c r="C479" s="3" t="inlineStr">
         <is>
-          <t>rNPU_roce_port_change 可注入</t>
+          <t>npu_hardware，rNPU_roce_port_change 可注入</t>
         </is>
       </c>
       <c r="D479" s="3" t="inlineStr">
@@ -28524,7 +28516,7 @@
       </c>
       <c r="C480" s="3" t="inlineStr">
         <is>
-          <t>rNPU_roce_port_change 可注入</t>
+          <t>npu_hardware，rNPU_roce_port_change 可注入</t>
         </is>
       </c>
       <c r="D480" s="3" t="inlineStr">
@@ -28581,7 +28573,7 @@
       </c>
       <c r="C481" s="3" t="inlineStr">
         <is>
-          <t>rNPU_roce_port_change 可注入</t>
+          <t>npu_hardware，rNPU_roce_port_change 可注入</t>
         </is>
       </c>
       <c r="D481" s="3" t="inlineStr">
@@ -28638,7 +28630,7 @@
       </c>
       <c r="C482" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_roce_port_change</t>
+          <t>npu_hardware，已注入 rNPU_roce_port_change</t>
         </is>
       </c>
       <c r="D482" s="3" t="inlineStr">
@@ -28696,7 +28688,7 @@
       </c>
       <c r="C483" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_roce_port_change</t>
+          <t>npu_hardware，已注入 rNPU_roce_port_change</t>
         </is>
       </c>
       <c r="D483" s="3" t="inlineStr">
@@ -28754,7 +28746,7 @@
       </c>
       <c r="C484" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_roce_port_change</t>
+          <t>npu_hardware，已注入 rNPU_roce_port_change</t>
         </is>
       </c>
       <c r="D484" s="3" t="inlineStr">
@@ -28813,7 +28805,7 @@
       </c>
       <c r="C485" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_roce_port_change</t>
+          <t>npu_hardware，已注入 rNPU_roce_port_change</t>
         </is>
       </c>
       <c r="D485" s="3" t="inlineStr">
@@ -28871,7 +28863,7 @@
       </c>
       <c r="C486" s="3" t="inlineStr">
         <is>
-          <t>rNPU_roce_port_change 可注入</t>
+          <t>npu_hardware，rNPU_roce_port_change 可注入</t>
         </is>
       </c>
       <c r="D486" s="3" t="inlineStr">
@@ -28930,7 +28922,7 @@
       </c>
       <c r="C487" s="3" t="inlineStr">
         <is>
-          <t>rNPU_roce_port_change 可注入</t>
+          <t>npu_hardware，rNPU_roce_port_change 可注入</t>
         </is>
       </c>
       <c r="D487" s="3" t="inlineStr">
@@ -28993,7 +28985,7 @@
       </c>
       <c r="C488" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_roce_port_change</t>
+          <t>npu_hardware，已 clean rNPU_roce_port_change</t>
         </is>
       </c>
       <c r="D488" s="3" t="inlineStr">
@@ -29010,7 +29002,7 @@
       <c r="F488" s="3" t="inlineStr">
         <is>
           <t>1. 首次 status:ok
-2. 第二次 status:ok（幂等）</t>
+2. 第二次 exitcode:1（无活跃记录, DESIGN §5.2）</t>
         </is>
       </c>
       <c r="G488" s="4" t="inlineStr">
@@ -29035,7 +29027,7 @@
       </c>
       <c r="K488" s="3" t="inlineStr">
         <is>
-          <t>status:ok</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>
@@ -29052,7 +29044,7 @@
       </c>
       <c r="C489" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_route_add</t>
+          <t>npu_hardware，已注入 rNPU_route_add</t>
         </is>
       </c>
       <c r="D489" s="3" t="inlineStr">
@@ -29111,7 +29103,7 @@
       </c>
       <c r="C490" s="3" t="inlineStr">
         <is>
-          <t>rNPU_route_add 可注入</t>
+          <t>npu_hardware，rNPU_route_add 可注入</t>
         </is>
       </c>
       <c r="D490" s="3" t="inlineStr">
@@ -29168,7 +29160,7 @@
       </c>
       <c r="C491" s="3" t="inlineStr">
         <is>
-          <t>rNPU_route_add 可注入</t>
+          <t>npu_hardware，rNPU_route_add 可注入</t>
         </is>
       </c>
       <c r="D491" s="3" t="inlineStr">
@@ -29225,7 +29217,7 @@
       </c>
       <c r="C492" s="3" t="inlineStr">
         <is>
-          <t>rNPU_route_add 可注入</t>
+          <t>npu_hardware，rNPU_route_add 可注入</t>
         </is>
       </c>
       <c r="D492" s="3" t="inlineStr">
@@ -29282,7 +29274,7 @@
       </c>
       <c r="C493" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_route_add</t>
+          <t>npu_hardware，已 clean rNPU_route_add</t>
         </is>
       </c>
       <c r="D493" s="3" t="inlineStr">
@@ -29341,7 +29333,7 @@
       </c>
       <c r="C494" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_route_add</t>
+          <t>npu_hardware，已注入 rNPU_route_add</t>
         </is>
       </c>
       <c r="D494" s="3" t="inlineStr">
@@ -29400,7 +29392,7 @@
       </c>
       <c r="C495" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_route_add</t>
+          <t>npu_hardware，已注入 rNPU_route_add</t>
         </is>
       </c>
       <c r="D495" s="3" t="inlineStr">
@@ -29458,7 +29450,7 @@
       </c>
       <c r="C496" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_route_add</t>
+          <t>npu_hardware，已注入 rNPU_route_add</t>
         </is>
       </c>
       <c r="D496" s="3" t="inlineStr">
@@ -29516,7 +29508,7 @@
       </c>
       <c r="C497" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_route_add</t>
+          <t>npu_hardware，已注入 rNPU_route_add</t>
         </is>
       </c>
       <c r="D497" s="3" t="inlineStr">
@@ -29575,7 +29567,7 @@
       </c>
       <c r="C498" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_route_add</t>
+          <t>npu_hardware，已注入 rNPU_route_add</t>
         </is>
       </c>
       <c r="D498" s="3" t="inlineStr">
@@ -29633,7 +29625,7 @@
       </c>
       <c r="C499" s="3" t="inlineStr">
         <is>
-          <t>rNPU_route_add 可注入</t>
+          <t>npu_hardware，rNPU_route_add 可注入</t>
         </is>
       </c>
       <c r="D499" s="3" t="inlineStr">
@@ -29692,7 +29684,7 @@
       </c>
       <c r="C500" s="3" t="inlineStr">
         <is>
-          <t>已查出 chip2 的 NPU IP/网关，address 选未占用且不与 NPU 网段冲突的网段</t>
+          <t>npu_hardware，已查出 chip2 的 NPU IP/网关，address 选未占用且不与 NPU 网段冲突的网段</t>
         </is>
       </c>
       <c r="D500" s="3" t="inlineStr">
@@ -29753,7 +29745,7 @@
       </c>
       <c r="C501" s="3" t="inlineStr">
         <is>
-          <t>rNPU_route_add 可注入</t>
+          <t>npu_hardware，rNPU_route_add 可注入</t>
         </is>
       </c>
       <c r="D501" s="3" t="inlineStr">
@@ -29816,7 +29808,7 @@
       </c>
       <c r="C502" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_route_add</t>
+          <t>npu_hardware，已 clean rNPU_route_add</t>
         </is>
       </c>
       <c r="D502" s="3" t="inlineStr">
@@ -29833,7 +29825,7 @@
       <c r="F502" s="3" t="inlineStr">
         <is>
           <t>1. 首次 status:ok
-2. 第二次 status:ok（幂等）</t>
+2. 第二次 exitcode:1（无活跃记录, DESIGN §5.2）</t>
         </is>
       </c>
       <c r="G502" s="4" t="inlineStr">
@@ -29858,7 +29850,7 @@
       </c>
       <c r="K502" s="3" t="inlineStr">
         <is>
-          <t>status:ok</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>
@@ -29875,7 +29867,7 @@
       </c>
       <c r="C503" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_route_del</t>
+          <t>npu_hardware，已注入 rNPU_route_del</t>
         </is>
       </c>
       <c r="D503" s="3" t="inlineStr">
@@ -29934,7 +29926,7 @@
       </c>
       <c r="C504" s="3" t="inlineStr">
         <is>
-          <t>rNPU_route_del 可注入</t>
+          <t>npu_hardware，rNPU_route_del 可注入</t>
         </is>
       </c>
       <c r="D504" s="3" t="inlineStr">
@@ -29991,7 +29983,7 @@
       </c>
       <c r="C505" s="3" t="inlineStr">
         <is>
-          <t>rNPU_route_del 可注入</t>
+          <t>npu_hardware，rNPU_route_del 可注入</t>
         </is>
       </c>
       <c r="D505" s="3" t="inlineStr">
@@ -30048,7 +30040,7 @@
       </c>
       <c r="C506" s="3" t="inlineStr">
         <is>
-          <t>rNPU_route_del 可注入</t>
+          <t>npu_hardware，rNPU_route_del 可注入</t>
         </is>
       </c>
       <c r="D506" s="3" t="inlineStr">
@@ -30105,7 +30097,7 @@
       </c>
       <c r="C507" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_route_del</t>
+          <t>npu_hardware，已 clean rNPU_route_del</t>
         </is>
       </c>
       <c r="D507" s="3" t="inlineStr">
@@ -30164,7 +30156,7 @@
       </c>
       <c r="C508" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_route_del</t>
+          <t>npu_hardware，已注入 rNPU_route_del</t>
         </is>
       </c>
       <c r="D508" s="3" t="inlineStr">
@@ -30223,7 +30215,7 @@
       </c>
       <c r="C509" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_route_del</t>
+          <t>npu_hardware，已注入 rNPU_route_del</t>
         </is>
       </c>
       <c r="D509" s="3" t="inlineStr">
@@ -30281,7 +30273,7 @@
       </c>
       <c r="C510" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_route_del</t>
+          <t>npu_hardware，已注入 rNPU_route_del</t>
         </is>
       </c>
       <c r="D510" s="3" t="inlineStr">
@@ -30339,7 +30331,7 @@
       </c>
       <c r="C511" s="3" t="inlineStr">
         <is>
-          <t>目标路由已存在（先 rNPU_route_add 创建）</t>
+          <t>npu_hardware，目标路由已存在（先 rNPU_route_add 创建）</t>
         </is>
       </c>
       <c r="D511" s="3" t="inlineStr">
@@ -30400,7 +30392,7 @@
       </c>
       <c r="C512" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_route_del</t>
+          <t>npu_hardware，已注入 rNPU_route_del</t>
         </is>
       </c>
       <c r="D512" s="3" t="inlineStr">
@@ -30459,7 +30451,7 @@
       </c>
       <c r="C513" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_route_del</t>
+          <t>npu_hardware，已注入 rNPU_route_del</t>
         </is>
       </c>
       <c r="D513" s="3" t="inlineStr">
@@ -30517,7 +30509,7 @@
       </c>
       <c r="C514" s="3" t="inlineStr">
         <is>
-          <t>rNPU_route_del 可注入</t>
+          <t>npu_hardware，rNPU_route_del 可注入</t>
         </is>
       </c>
       <c r="D514" s="3" t="inlineStr">
@@ -30576,7 +30568,7 @@
       </c>
       <c r="C515" s="3" t="inlineStr">
         <is>
-          <t>rNPU_route_del 可注入</t>
+          <t>npu_hardware，rNPU_route_del 可注入</t>
         </is>
       </c>
       <c r="D515" s="3" t="inlineStr">
@@ -30639,7 +30631,7 @@
       </c>
       <c r="C516" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNPU_route_del</t>
+          <t>npu_hardware，已 clean rNPU_route_del</t>
         </is>
       </c>
       <c r="D516" s="3" t="inlineStr">
@@ -30656,7 +30648,7 @@
       <c r="F516" s="3" t="inlineStr">
         <is>
           <t>1. 首次 status:ok
-2. 第二次 status:ok（幂等）</t>
+2. 第二次 exitcode:1（无活跃记录, DESIGN §5.2）</t>
         </is>
       </c>
       <c r="G516" s="4" t="inlineStr">
@@ -30681,7 +30673,7 @@
       </c>
       <c r="K516" s="3" t="inlineStr">
         <is>
-          <t>status:ok</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>
@@ -30740,7 +30732,7 @@
       </c>
       <c r="K517" s="3" t="inlineStr">
         <is>
-          <t>exitcode:2</t>
+          <t>exitcode:3</t>
         </is>
       </c>
     </row>
@@ -30799,7 +30791,7 @@
       </c>
       <c r="K518" s="3" t="inlineStr">
         <is>
-          <t>exitcode:1</t>
+          <t>exitcode:2</t>
         </is>
       </c>
     </row>
@@ -31153,7 +31145,7 @@
       </c>
       <c r="K524" s="3" t="inlineStr">
         <is>
-          <t>state_contains:&lt;uid&gt;</t>
+          <t>exitcode:3</t>
         </is>
       </c>
     </row>
@@ -31570,7 +31562,7 @@
       </c>
       <c r="K531" s="3" t="inlineStr">
         <is>
-          <t>exitcode:1</t>
+          <t>exitcode:0</t>
         </is>
       </c>
     </row>
@@ -31993,7 +31985,7 @@
       </c>
       <c r="K538" s="3" t="inlineStr">
         <is>
-          <t>exitcode:1</t>
+          <t>exitcode:0</t>
         </is>
       </c>
     </row>
@@ -32010,7 +32002,7 @@
       </c>
       <c r="C539" s="3" t="inlineStr">
         <is>
-          <t>普通用户（runuser nobody）</t>
+          <t>non-root</t>
         </is>
       </c>
       <c r="D539" s="3" t="inlineStr">
@@ -32129,7 +32121,7 @@
       </c>
       <c r="C541" s="3" t="inlineStr">
         <is>
-          <t>存在仅含 rCPU_overload 的测试配置 /tmp/test.conf</t>
+          <t>配置文件 /tmp/test.conf 存在</t>
         </is>
       </c>
       <c r="D541" s="3" t="inlineStr">
@@ -32353,7 +32345,7 @@
       </c>
       <c r="C545" s="3" t="inlineStr">
         <is>
-          <t>测试注册 mock_executor，fn 捕获 (cmd, env) 返回伪造 result_t</t>
+          <t>mock dcat 二进制可用</t>
         </is>
       </c>
       <c r="D545" s="3" t="inlineStr">
@@ -32985,7 +32977,7 @@
       </c>
       <c r="C556" s="3" t="inlineStr">
         <is>
-          <t>dcat serve 已启动</t>
+          <t>serve 长超时环境</t>
         </is>
       </c>
       <c r="D556" s="3" t="inlineStr">
@@ -33394,7 +33386,7 @@
       </c>
       <c r="K562" s="3" t="inlineStr">
         <is>
-          <t>exitcode:1</t>
+          <t>exitcode:2</t>
         </is>
       </c>
     </row>
@@ -33453,7 +33445,7 @@
       </c>
       <c r="K563" s="3" t="inlineStr">
         <is>
-          <t>exitcode:1</t>
+          <t>exitcode:0</t>
         </is>
       </c>
     </row>
@@ -33625,7 +33617,7 @@
       </c>
       <c r="K566" s="3" t="inlineStr">
         <is>
-          <t>exitcode:1</t>
+          <t>exitcode:2</t>
         </is>
       </c>
     </row>
@@ -33796,7 +33788,7 @@
       </c>
       <c r="K569" s="3" t="inlineStr">
         <is>
-          <t>exitcode:1</t>
+          <t>exitcode:2</t>
         </is>
       </c>
     </row>
@@ -33853,7 +33845,7 @@
       </c>
       <c r="K570" s="3" t="inlineStr">
         <is>
-          <t>exitcode:3</t>
+          <t>exitcode:4</t>
         </is>
       </c>
     </row>
@@ -33870,12 +33862,12 @@
       </c>
       <c r="C571" s="3" t="inlineStr">
         <is>
-          <t>log_level=debug</t>
+          <t>npu_hardware，log_level=debug</t>
         </is>
       </c>
       <c r="D571" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rNPU_arp_poison --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55
+          <t>1. 执行 dcat inject rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55
 2. 捕获 stderr 检查是否含 MAC 等敏感参数</t>
         </is>
       </c>
@@ -33970,7 +33962,7 @@
       </c>
       <c r="K572" s="3" t="inlineStr">
         <is>
-          <t>exitcode:1</t>
+          <t>exitcode:0</t>
         </is>
       </c>
     </row>
@@ -34258,7 +34250,7 @@
       </c>
       <c r="K577" s="3" t="inlineStr">
         <is>
-          <t>exitcode:2</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>
@@ -34371,7 +34363,7 @@
       </c>
       <c r="K579" s="3" t="inlineStr">
         <is>
-          <t>out_contains:uid</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>
@@ -34597,7 +34589,7 @@
       </c>
       <c r="K583" s="3" t="inlineStr">
         <is>
-          <t>exitcode:1</t>
+          <t>exitcode:0</t>
         </is>
       </c>
     </row>
@@ -34654,7 +34646,7 @@
       </c>
       <c r="K584" s="3" t="inlineStr">
         <is>
-          <t>exitcode:1</t>
+          <t>exitcode:0</t>
         </is>
       </c>
     </row>
@@ -34715,7 +34707,7 @@
       </c>
       <c r="K585" s="3" t="inlineStr">
         <is>
-          <t>exitcode:1</t>
+          <t>exitcode:2</t>
         </is>
       </c>
     </row>
@@ -35112,7 +35104,7 @@
       </c>
       <c r="K592" s="3" t="inlineStr">
         <is>
-          <t>exitcode:3</t>
+          <t>exitcode:4</t>
         </is>
       </c>
     </row>
@@ -35227,7 +35219,7 @@
       </c>
       <c r="J594" s="3" t="inlineStr">
         <is>
-          <t>pgrep -f 'perl -e' | wc -l</t>
+          <t>pgrep -c -f 'perl -e 1 while'</t>
         </is>
       </c>
       <c r="K594" s="3" t="inlineStr">
@@ -35286,12 +35278,12 @@
       </c>
       <c r="J595" s="3" t="inlineStr">
         <is>
-          <t>pgrep -f 'perl -e' | wc -l</t>
+          <t>pgrep -c -f 'perl -e 1 while'</t>
         </is>
       </c>
       <c r="K595" s="3" t="inlineStr">
         <is>
-          <t>&gt;=5</t>
+          <t>&gt;=3</t>
         </is>
       </c>
     </row>
@@ -36008,7 +36000,7 @@
       </c>
       <c r="C608" s="3" t="inlineStr">
         <is>
-          <t>可写目录 /data</t>
+          <t>非 tmpfs 写入目录（/data 可用）</t>
         </is>
       </c>
       <c r="D608" s="3" t="inlineStr">
@@ -36045,7 +36037,7 @@
       </c>
       <c r="J608" s="3" t="inlineStr">
         <is>
-          <t>pgrep -f 'dd if=/dev/zero' | wc -l</t>
+          <t>sleep 1; pgrep -c -f 'dd if=/dev/zero'</t>
         </is>
       </c>
       <c r="K608" s="3" t="inlineStr">
@@ -37003,7 +36995,7 @@
       </c>
       <c r="C625" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_link_down</t>
+          <t>npu_hardware，已注入 rNPU_link_down</t>
         </is>
       </c>
       <c r="D625" s="3" t="inlineStr">
@@ -37061,7 +37053,7 @@
       </c>
       <c r="C626" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_link_down</t>
+          <t>npu_hardware，已注入 rNPU_link_down</t>
         </is>
       </c>
       <c r="D626" s="3" t="inlineStr">
@@ -37120,7 +37112,7 @@
       </c>
       <c r="C627" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_ip_change</t>
+          <t>npu_hardware，已注入 rNPU_ip_change</t>
         </is>
       </c>
       <c r="D627" s="3" t="inlineStr">
@@ -37178,7 +37170,7 @@
       </c>
       <c r="C628" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_ip_change</t>
+          <t>npu_hardware，已注入 rNPU_ip_change</t>
         </is>
       </c>
       <c r="D628" s="3" t="inlineStr">
@@ -37237,7 +37229,7 @@
       </c>
       <c r="C629" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_gw_change</t>
+          <t>npu_hardware，已注入 rNPU_gw_change</t>
         </is>
       </c>
       <c r="D629" s="3" t="inlineStr">
@@ -37295,7 +37287,7 @@
       </c>
       <c r="C630" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_gw_change</t>
+          <t>npu_hardware，已注入 rNPU_gw_change</t>
         </is>
       </c>
       <c r="D630" s="3" t="inlineStr">
@@ -37354,12 +37346,12 @@
       </c>
       <c r="C631" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_arp_poison</t>
+          <t>npu_hardware，已注入 rNPU_arp_poison</t>
         </is>
       </c>
       <c r="D631" s="3" t="inlineStr">
         <is>
-          <t>1. dcat query rNPU_arp_poison --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55</t>
+          <t>1. dcat query rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55</t>
         </is>
       </c>
       <c r="E631" s="3" t="inlineStr">
@@ -37390,7 +37382,7 @@
       </c>
       <c r="J631" s="3" t="inlineStr">
         <is>
-          <t>dcat query rNPU_arp_poison</t>
+          <t>dcat query rNPU_arp</t>
         </is>
       </c>
       <c r="K631" s="3" t="inlineStr">
@@ -37412,12 +37404,12 @@
       </c>
       <c r="C632" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_arp_poison</t>
+          <t>npu_hardware，已注入 rNPU_arp_poison</t>
         </is>
       </c>
       <c r="D632" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_arp_poison --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55
+          <t>1. dcat clean rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55
 2. hccn_tool -i 2 -arp -g</t>
         </is>
       </c>
@@ -37471,7 +37463,7 @@
       </c>
       <c r="C633" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_route_add</t>
+          <t>npu_hardware，已注入 rNPU_route_add</t>
         </is>
       </c>
       <c r="D633" s="3" t="inlineStr">
@@ -37529,7 +37521,7 @@
       </c>
       <c r="C634" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNPU_route_add</t>
+          <t>npu_hardware，已注入 rNPU_route_add</t>
         </is>
       </c>
       <c r="D634" s="3" t="inlineStr">

--- a/tests/e2e/testcases.xlsx
+++ b/tests/e2e/testcases.xlsx
@@ -12072,7 +12072,7 @@
       </c>
       <c r="J198" s="3" t="inlineStr">
         <is>
-          <t>dcat query rNET_service_stop</t>
+          <t>dcat query rNET_service_stop --service=nginx</t>
         </is>
       </c>
       <c r="K198" s="3" t="inlineStr">
@@ -12784,7 +12784,7 @@
       </c>
       <c r="K210" s="3" t="inlineStr">
         <is>
-          <t>&gt;=1</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>
@@ -13056,7 +13056,7 @@
       </c>
       <c r="K215" s="3" t="inlineStr">
         <is>
-          <t>&gt;=1</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>

--- a/tests/e2e/testcases.xlsx
+++ b/tests/e2e/testcases.xlsx
@@ -4,14 +4,14 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
     <sheet name="测试用例" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="统计" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'测试用例'!$A$1:$K$1</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'测试用例'!$A$1:$K$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -95,42 +95,42 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
   <cellXfs count="16">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="1" fillId="2" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="3" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="4" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="5" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="1" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="1" fillId="5" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="1" fillId="3" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -494,20 +494,20 @@
   <dimension ref="A1:K634"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="38" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="34" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
+    <col customWidth="1" max="1" min="1" width="11"/>
+    <col customWidth="1" max="2" min="2" width="36"/>
+    <col customWidth="1" max="3" min="3" width="24"/>
+    <col customWidth="1" max="4" min="4" width="42"/>
+    <col customWidth="1" max="5" min="5" width="26"/>
+    <col customWidth="1" max="6" min="6" width="38"/>
+    <col customWidth="1" max="7" min="7" width="8"/>
+    <col customWidth="1" max="8" min="8" width="10"/>
+    <col customWidth="1" max="9" min="9" width="20"/>
+    <col customWidth="1" max="10" min="10" width="34"/>
+    <col customWidth="1" max="11" min="11" width="22"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row customHeight="1" ht="30" r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>用例编号</t>
@@ -564,7 +564,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>TC-001</t>
@@ -622,7 +622,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>TC-002</t>
@@ -680,7 +680,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>TC-003</t>
@@ -735,7 +735,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>TC-004</t>
@@ -795,7 +795,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>TC-005</t>
@@ -856,7 +856,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>TC-006</t>
@@ -914,7 +914,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>TC-007</t>
@@ -975,7 +975,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
           <t>TC-008</t>
@@ -1033,7 +1033,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>TC-009</t>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
           <t>TC-010</t>
@@ -1147,7 +1147,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>TC-011</t>
@@ -1204,7 +1204,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
           <t>TC-012</t>
@@ -1262,7 +1262,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
           <t>TC-013</t>
@@ -1319,7 +1319,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
           <t>TC-014</t>
@@ -1382,7 +1382,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
           <t>TC-015</t>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
           <t>TC-016</t>
@@ -1501,7 +1501,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
           <t>TC-017</t>
@@ -1562,7 +1562,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
           <t>TC-018</t>
@@ -1624,7 +1624,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
           <t>TC-019</t>
@@ -1682,7 +1682,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
           <t>TC-020</t>
@@ -1744,7 +1744,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
           <t>TC-021</t>
@@ -1802,7 +1802,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
           <t>TC-022</t>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
           <t>TC-023</t>
@@ -1919,7 +1919,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
           <t>TC-024</t>
@@ -1977,7 +1977,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
           <t>TC-025</t>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
           <t>TC-026</t>
@@ -2095,7 +2095,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
           <t>TC-027</t>
@@ -2155,7 +2155,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
           <t>TC-028</t>
@@ -2214,7 +2214,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
           <t>TC-029</t>
@@ -2274,7 +2274,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
           <t>TC-030</t>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>具备 root 写 sysfs，内核 CONFIG_HOTPLUG_CPU 支持；部分虚拟化/容器不支持核下线</t>
+          <t>root+sysfs_writable，内核 CONFIG_HOTPLUG_CPU 支持；部分虚拟化/容器不支持核下线；cpu0 无则无法 offline 自动跳过</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -2326,16 +2326,17 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>cat /sys/devices/system/cpu/cpu1/online 2&gt;/dev/null || echo NA</t>
+          <t>cat /sys/devices/system/cpu/cpu2/online 2&gt;/dev/null || echo NA; cat /sys/devices/system/cpu/cpu3/online 2&gt;/dev/null || echo NA</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>eq:0</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="70" customHeight="1">
+          <t>regex:^0\s*
+0</t>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="70" r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
           <t>TC-031</t>
@@ -2388,16 +2389,17 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>cat /sys/devices/system/cpu/cpu1/online 2&gt;/dev/null || echo NA</t>
+          <t>cat /sys/devices/system/cpu/cpu2/online 2&gt;/dev/null || echo NA; cat /sys/devices/system/cpu/cpu3/online 2&gt;/dev/null || echo NA</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>eq:0</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="70" customHeight="1">
+          <t>regex:^0\s*
+0</t>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="70" r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
           <t>TC-032</t>
@@ -2460,7 +2462,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
           <t>TC-033</t>
@@ -2519,7 +2521,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
           <t>TC-034</t>
@@ -2575,7 +2577,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
           <t>TC-035</t>
@@ -2631,7 +2633,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
           <t>TC-036</t>
@@ -2692,7 +2694,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
           <t>TC-037</t>
@@ -2749,7 +2751,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
           <t>TC-038</t>
@@ -2806,7 +2808,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
           <t>TC-039</t>
@@ -2863,7 +2865,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
           <t>TC-040</t>
@@ -2920,7 +2922,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
           <t>TC-041</t>
@@ -2978,7 +2980,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
           <t>TC-042</t>
@@ -3035,7 +3037,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
           <t>TC-043</t>
@@ -3092,7 +3094,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
           <t>TC-044</t>
@@ -3148,7 +3150,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
           <t>TC-045</t>
@@ -3207,7 +3209,7 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
           <t>TC-046</t>
@@ -3266,7 +3268,7 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
           <t>TC-047</t>
@@ -3325,7 +3327,7 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
           <t>TC-048</t>
@@ -3383,7 +3385,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
           <t>TC-049</t>
@@ -3441,7 +3443,7 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
           <t>TC-050</t>
@@ -3499,7 +3501,7 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
           <t>TC-051</t>
@@ -3556,7 +3558,7 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
           <t>TC-052</t>
@@ -3613,7 +3615,7 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
           <t>TC-053</t>
@@ -3670,7 +3672,7 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
           <t>TC-054</t>
@@ -3727,7 +3729,7 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
           <t>TC-055</t>
@@ -3785,7 +3787,7 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
           <t>TC-056</t>
@@ -3842,7 +3844,7 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
           <t>TC-057</t>
@@ -3899,7 +3901,7 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
           <t>TC-058</t>
@@ -3956,7 +3958,7 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
           <t>TC-059</t>
@@ -4015,7 +4017,7 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
           <t>TC-060</t>
@@ -4075,7 +4077,7 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
           <t>TC-061</t>
@@ -4133,7 +4135,7 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
           <t>TC-062</t>
@@ -4192,7 +4194,7 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
           <t>TC-063</t>
@@ -4255,7 +4257,7 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
           <t>TC-064</t>
@@ -4314,7 +4316,7 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
           <t>TC-065</t>
@@ -4373,7 +4375,7 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
           <t>TC-066</t>
@@ -4432,7 +4434,7 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
           <t>TC-067</t>
@@ -4490,7 +4492,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
           <t>TC-068</t>
@@ -4548,7 +4550,7 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
           <t>TC-069</t>
@@ -4606,7 +4608,7 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
           <t>TC-070</t>
@@ -4664,7 +4666,7 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
           <t>TC-071</t>
@@ -4721,7 +4723,7 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
           <t>TC-072</t>
@@ -4779,7 +4781,7 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
           <t>TC-073</t>
@@ -4836,7 +4838,7 @@
         </is>
       </c>
     </row>
-    <row r="75" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
           <t>TC-074</t>
@@ -4895,7 +4897,7 @@
         </is>
       </c>
     </row>
-    <row r="76" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
           <t>TC-075</t>
@@ -4953,7 +4955,7 @@
         </is>
       </c>
     </row>
-    <row r="77" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
           <t>TC-076</t>
@@ -5011,7 +5013,7 @@
         </is>
       </c>
     </row>
-    <row r="78" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
           <t>TC-077</t>
@@ -5068,7 +5070,7 @@
         </is>
       </c>
     </row>
-    <row r="79" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
           <t>TC-078</t>
@@ -5127,7 +5129,7 @@
         </is>
       </c>
     </row>
-    <row r="80" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
           <t>TC-079</t>
@@ -5185,7 +5187,7 @@
         </is>
       </c>
     </row>
-    <row r="81" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
           <t>TC-080</t>
@@ -5244,7 +5246,7 @@
         </is>
       </c>
     </row>
-    <row r="82" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
           <t>TC-081</t>
@@ -5307,7 +5309,7 @@
         </is>
       </c>
     </row>
-    <row r="83" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
           <t>TC-082</t>
@@ -5368,7 +5370,7 @@
         </is>
       </c>
     </row>
-    <row r="84" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
           <t>TC-083</t>
@@ -5427,7 +5429,7 @@
         </is>
       </c>
     </row>
-    <row r="85" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
           <t>TC-084</t>
@@ -5486,7 +5488,7 @@
         </is>
       </c>
     </row>
-    <row r="86" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
           <t>TC-085</t>
@@ -5545,7 +5547,7 @@
         </is>
       </c>
     </row>
-    <row r="87" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
           <t>TC-086</t>
@@ -5603,7 +5605,7 @@
         <v/>
       </c>
     </row>
-    <row r="88" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
           <t>TC-087</t>
@@ -5660,7 +5662,7 @@
         </is>
       </c>
     </row>
-    <row r="89" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
           <t>TC-088</t>
@@ -5717,7 +5719,7 @@
         </is>
       </c>
     </row>
-    <row r="90" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
           <t>TC-089</t>
@@ -5774,7 +5776,7 @@
         </is>
       </c>
     </row>
-    <row r="91" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
           <t>TC-090</t>
@@ -5832,7 +5834,7 @@
         </is>
       </c>
     </row>
-    <row r="92" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
           <t>TC-091</t>
@@ -5890,7 +5892,7 @@
         </is>
       </c>
     </row>
-    <row r="93" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
           <t>TC-092</t>
@@ -5949,7 +5951,7 @@
         </is>
       </c>
     </row>
-    <row r="94" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
           <t>TC-093</t>
@@ -6007,7 +6009,7 @@
         </is>
       </c>
     </row>
-    <row r="95" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
           <t>TC-094</t>
@@ -6066,7 +6068,7 @@
         </is>
       </c>
     </row>
-    <row r="96" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
           <t>TC-095</t>
@@ -6127,7 +6129,7 @@
         </is>
       </c>
     </row>
-    <row r="97" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
           <t>TC-096</t>
@@ -6190,7 +6192,7 @@
         </is>
       </c>
     </row>
-    <row r="98" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
           <t>TC-097</t>
@@ -6249,7 +6251,7 @@
         </is>
       </c>
     </row>
-    <row r="99" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
           <t>TC-098</t>
@@ -6308,7 +6310,7 @@
         </is>
       </c>
     </row>
-    <row r="100" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
           <t>TC-099</t>
@@ -6367,7 +6369,7 @@
         </is>
       </c>
     </row>
-    <row r="101" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
           <t>TC-100</t>
@@ -6426,7 +6428,7 @@
         </is>
       </c>
     </row>
-    <row r="102" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
           <t>TC-101</t>
@@ -6483,7 +6485,7 @@
         </is>
       </c>
     </row>
-    <row r="103" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
           <t>TC-102</t>
@@ -6541,7 +6543,7 @@
         </is>
       </c>
     </row>
-    <row r="104" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
           <t>TC-103</t>
@@ -6599,7 +6601,7 @@
         </is>
       </c>
     </row>
-    <row r="105" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
           <t>TC-104</t>
@@ -6658,7 +6660,7 @@
         </is>
       </c>
     </row>
-    <row r="106" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
           <t>TC-105</t>
@@ -6716,7 +6718,7 @@
         </is>
       </c>
     </row>
-    <row r="107" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
           <t>TC-106</t>
@@ -6774,7 +6776,7 @@
         </is>
       </c>
     </row>
-    <row r="108" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
           <t>TC-107</t>
@@ -6833,7 +6835,7 @@
         </is>
       </c>
     </row>
-    <row r="109" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
           <t>TC-108</t>
@@ -6896,7 +6898,7 @@
         </is>
       </c>
     </row>
-    <row r="110" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
           <t>TC-109</t>
@@ -6959,7 +6961,7 @@
         </is>
       </c>
     </row>
-    <row r="111" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
           <t>TC-110</t>
@@ -7018,7 +7020,7 @@
         </is>
       </c>
     </row>
-    <row r="112" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
           <t>TC-111</t>
@@ -7077,7 +7079,7 @@
         </is>
       </c>
     </row>
-    <row r="113" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
           <t>TC-112</t>
@@ -7136,7 +7138,7 @@
         </is>
       </c>
     </row>
-    <row r="114" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
           <t>TC-113</t>
@@ -7194,7 +7196,7 @@
         <v/>
       </c>
     </row>
-    <row r="115" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
           <t>TC-114</t>
@@ -7251,7 +7253,7 @@
         </is>
       </c>
     </row>
-    <row r="116" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
           <t>TC-115</t>
@@ -7308,7 +7310,7 @@
         </is>
       </c>
     </row>
-    <row r="117" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
           <t>TC-116</t>
@@ -7365,7 +7367,7 @@
         </is>
       </c>
     </row>
-    <row r="118" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
           <t>TC-117</t>
@@ -7422,7 +7424,7 @@
         </is>
       </c>
     </row>
-    <row r="119" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
           <t>TC-118</t>
@@ -7479,7 +7481,7 @@
         </is>
       </c>
     </row>
-    <row r="120" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
           <t>TC-119</t>
@@ -7536,7 +7538,7 @@
         </is>
       </c>
     </row>
-    <row r="121" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
           <t>TC-120</t>
@@ -7593,7 +7595,7 @@
         </is>
       </c>
     </row>
-    <row r="122" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
           <t>TC-121</t>
@@ -7651,7 +7653,7 @@
         </is>
       </c>
     </row>
-    <row r="123" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
           <t>TC-122</t>
@@ -7709,7 +7711,7 @@
         </is>
       </c>
     </row>
-    <row r="124" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
           <t>TC-123</t>
@@ -7768,7 +7770,7 @@
         </is>
       </c>
     </row>
-    <row r="125" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
           <t>TC-124</t>
@@ -7829,7 +7831,7 @@
         </is>
       </c>
     </row>
-    <row r="126" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
           <t>TC-125</t>
@@ -7887,7 +7889,7 @@
         </is>
       </c>
     </row>
-    <row r="127" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
           <t>TC-126</t>
@@ -7946,7 +7948,7 @@
         </is>
       </c>
     </row>
-    <row r="128" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
           <t>TC-127</t>
@@ -8009,7 +8011,7 @@
         </is>
       </c>
     </row>
-    <row r="129" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
           <t>TC-128</t>
@@ -8068,7 +8070,7 @@
         </is>
       </c>
     </row>
-    <row r="130" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
           <t>TC-129</t>
@@ -8127,7 +8129,7 @@
         </is>
       </c>
     </row>
-    <row r="131" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
           <t>TC-130</t>
@@ -8186,7 +8188,7 @@
         </is>
       </c>
     </row>
-    <row r="132" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
           <t>TC-131</t>
@@ -8245,7 +8247,7 @@
         </is>
       </c>
     </row>
-    <row r="133" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
           <t>TC-132</t>
@@ -8302,7 +8304,7 @@
         </is>
       </c>
     </row>
-    <row r="134" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
           <t>TC-133</t>
@@ -8359,7 +8361,7 @@
         </is>
       </c>
     </row>
-    <row r="135" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
           <t>TC-134</t>
@@ -8417,7 +8419,7 @@
         </is>
       </c>
     </row>
-    <row r="136" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
           <t>TC-135</t>
@@ -8474,7 +8476,7 @@
         </is>
       </c>
     </row>
-    <row r="137" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
           <t>TC-136</t>
@@ -8531,7 +8533,7 @@
         </is>
       </c>
     </row>
-    <row r="138" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
           <t>TC-137</t>
@@ -8588,7 +8590,7 @@
         </is>
       </c>
     </row>
-    <row r="139" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
           <t>TC-138</t>
@@ -8646,7 +8648,7 @@
         </is>
       </c>
     </row>
-    <row r="140" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
           <t>TC-139</t>
@@ -8704,7 +8706,7 @@
         </is>
       </c>
     </row>
-    <row r="141" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
           <t>TC-140</t>
@@ -8763,7 +8765,7 @@
         </is>
       </c>
     </row>
-    <row r="142" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
           <t>TC-141</t>
@@ -8821,7 +8823,7 @@
         </is>
       </c>
     </row>
-    <row r="143" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
           <t>TC-142</t>
@@ -8880,7 +8882,7 @@
         </is>
       </c>
     </row>
-    <row r="144" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
           <t>TC-143</t>
@@ -8943,7 +8945,7 @@
         </is>
       </c>
     </row>
-    <row r="145" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
           <t>TC-144</t>
@@ -9002,7 +9004,7 @@
         </is>
       </c>
     </row>
-    <row r="146" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
           <t>TC-145</t>
@@ -9063,7 +9065,7 @@
         </is>
       </c>
     </row>
-    <row r="147" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
           <t>TC-146</t>
@@ -9119,7 +9121,7 @@
         <v/>
       </c>
     </row>
-    <row r="148" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
           <t>TC-147</t>
@@ -9181,7 +9183,7 @@
         </is>
       </c>
     </row>
-    <row r="149" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
           <t>TC-148</t>
@@ -9242,7 +9244,7 @@
         </is>
       </c>
     </row>
-    <row r="150" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
           <t>TC-149</t>
@@ -9297,7 +9299,7 @@
         </is>
       </c>
     </row>
-    <row r="151" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
           <t>TC-150</t>
@@ -9351,7 +9353,7 @@
         </is>
       </c>
     </row>
-    <row r="152" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
           <t>TC-151</t>
@@ -9405,7 +9407,7 @@
         </is>
       </c>
     </row>
-    <row r="153" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
           <t>TC-152</t>
@@ -9459,7 +9461,7 @@
         </is>
       </c>
     </row>
-    <row r="154" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
           <t>TC-153</t>
@@ -9513,7 +9515,7 @@
         </is>
       </c>
     </row>
-    <row r="155" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
           <t>TC-154</t>
@@ -9567,7 +9569,7 @@
         </is>
       </c>
     </row>
-    <row r="156" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
           <t>TC-155</t>
@@ -9629,7 +9631,7 @@
         </is>
       </c>
     </row>
-    <row r="157" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
           <t>TC-156</t>
@@ -9685,7 +9687,7 @@
         </is>
       </c>
     </row>
-    <row r="158" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
           <t>TC-157</t>
@@ -9743,7 +9745,7 @@
         </is>
       </c>
     </row>
-    <row r="159" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
           <t>TC-158</t>
@@ -9800,7 +9802,7 @@
         </is>
       </c>
     </row>
-    <row r="160" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
           <t>TC-159</t>
@@ -9856,7 +9858,7 @@
         </is>
       </c>
     </row>
-    <row r="161" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
           <t>TC-160</t>
@@ -9915,7 +9917,7 @@
         </is>
       </c>
     </row>
-    <row r="162" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
           <t>TC-161</t>
@@ -9974,7 +9976,7 @@
         </is>
       </c>
     </row>
-    <row r="163" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
           <t>TC-162</t>
@@ -10032,7 +10034,7 @@
         <v/>
       </c>
     </row>
-    <row r="164" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
           <t>TC-163</t>
@@ -10089,7 +10091,7 @@
         </is>
       </c>
     </row>
-    <row r="165" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
           <t>TC-164</t>
@@ -10146,7 +10148,7 @@
         </is>
       </c>
     </row>
-    <row r="166" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
           <t>TC-165</t>
@@ -10203,7 +10205,7 @@
         </is>
       </c>
     </row>
-    <row r="167" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
           <t>TC-166</t>
@@ -10263,7 +10265,7 @@
         </is>
       </c>
     </row>
-    <row r="168" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
           <t>TC-167</t>
@@ -10321,7 +10323,7 @@
         </is>
       </c>
     </row>
-    <row r="169" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
           <t>TC-168</t>
@@ -10379,7 +10381,7 @@
         </is>
       </c>
     </row>
-    <row r="170" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
           <t>TC-169</t>
@@ -10438,7 +10440,7 @@
         </is>
       </c>
     </row>
-    <row r="171" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
           <t>TC-170</t>
@@ -10496,7 +10498,7 @@
         </is>
       </c>
     </row>
-    <row r="172" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
           <t>TC-171</t>
@@ -10555,7 +10557,7 @@
         </is>
       </c>
     </row>
-    <row r="173" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
           <t>TC-172</t>
@@ -10618,7 +10620,7 @@
         </is>
       </c>
     </row>
-    <row r="174" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
           <t>TC-173</t>
@@ -10679,7 +10681,7 @@
         </is>
       </c>
     </row>
-    <row r="175" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
           <t>TC-174</t>
@@ -10738,7 +10740,7 @@
         </is>
       </c>
     </row>
-    <row r="176" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
           <t>TC-175</t>
@@ -10797,7 +10799,7 @@
         </is>
       </c>
     </row>
-    <row r="177" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
           <t>TC-176</t>
@@ -10856,7 +10858,7 @@
         </is>
       </c>
     </row>
-    <row r="178" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
           <t>TC-177</t>
@@ -10914,7 +10916,7 @@
         <v/>
       </c>
     </row>
-    <row r="179" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
           <t>TC-178</t>
@@ -10972,7 +10974,7 @@
         </is>
       </c>
     </row>
-    <row r="180" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
           <t>TC-179</t>
@@ -11030,7 +11032,7 @@
         </is>
       </c>
     </row>
-    <row r="181" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
           <t>TC-180</t>
@@ -11087,7 +11089,7 @@
         </is>
       </c>
     </row>
-    <row r="182" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
           <t>TC-181</t>
@@ -11144,7 +11146,7 @@
         </is>
       </c>
     </row>
-    <row r="183" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
           <t>TC-182</t>
@@ -11201,7 +11203,7 @@
         </is>
       </c>
     </row>
-    <row r="184" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
           <t>TC-183</t>
@@ -11258,7 +11260,7 @@
         </is>
       </c>
     </row>
-    <row r="185" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
           <t>TC-184</t>
@@ -11315,7 +11317,7 @@
         </is>
       </c>
     </row>
-    <row r="186" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
           <t>TC-185</t>
@@ -11372,7 +11374,7 @@
         </is>
       </c>
     </row>
-    <row r="187" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
           <t>TC-186</t>
@@ -11429,7 +11431,7 @@
         </is>
       </c>
     </row>
-    <row r="188" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
           <t>TC-187</t>
@@ -11490,7 +11492,7 @@
         </is>
       </c>
     </row>
-    <row r="189" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
           <t>TC-188</t>
@@ -11549,7 +11551,7 @@
         </is>
       </c>
     </row>
-    <row r="190" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
           <t>TC-189</t>
@@ -11607,7 +11609,7 @@
         </is>
       </c>
     </row>
-    <row r="191" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
           <t>TC-190</t>
@@ -11666,7 +11668,7 @@
         </is>
       </c>
     </row>
-    <row r="192" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
           <t>TC-191</t>
@@ -11729,7 +11731,7 @@
         </is>
       </c>
     </row>
-    <row r="193" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
           <t>TC-192</t>
@@ -11788,7 +11790,7 @@
         </is>
       </c>
     </row>
-    <row r="194" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
           <t>TC-193</t>
@@ -11847,7 +11849,7 @@
         </is>
       </c>
     </row>
-    <row r="195" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
           <t>TC-194</t>
@@ -11906,7 +11908,7 @@
         </is>
       </c>
     </row>
-    <row r="196" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
           <t>TC-195</t>
@@ -11965,7 +11967,7 @@
         </is>
       </c>
     </row>
-    <row r="197" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
           <t>TC-196</t>
@@ -12023,7 +12025,7 @@
         </is>
       </c>
     </row>
-    <row r="198" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
           <t>TC-197</t>
@@ -12072,7 +12074,7 @@
       </c>
       <c r="J198" s="3" t="inlineStr">
         <is>
-          <t>dcat query rNET_service_stop --service=nginx</t>
+          <t>dcat query rNET_service_stop</t>
         </is>
       </c>
       <c r="K198" s="3" t="inlineStr">
@@ -12081,7 +12083,7 @@
         </is>
       </c>
     </row>
-    <row r="199" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
           <t>TC-198</t>
@@ -12138,7 +12140,7 @@
         </is>
       </c>
     </row>
-    <row r="200" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
           <t>TC-199</t>
@@ -12197,7 +12199,7 @@
         </is>
       </c>
     </row>
-    <row r="201" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
           <t>TC-200</t>
@@ -12255,7 +12257,7 @@
         </is>
       </c>
     </row>
-    <row r="202" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
           <t>TC-201</t>
@@ -12316,7 +12318,7 @@
         </is>
       </c>
     </row>
-    <row r="203" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
           <t>TC-202</t>
@@ -12375,7 +12377,7 @@
         </is>
       </c>
     </row>
-    <row r="204" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
           <t>TC-203</t>
@@ -12438,7 +12440,7 @@
         </is>
       </c>
     </row>
-    <row r="205" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
           <t>TC-204</t>
@@ -12497,7 +12499,7 @@
         </is>
       </c>
     </row>
-    <row r="206" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
           <t>TC-205</t>
@@ -12552,7 +12554,7 @@
         <v/>
       </c>
     </row>
-    <row r="207" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
           <t>TC-206</t>
@@ -12613,7 +12615,7 @@
         </is>
       </c>
     </row>
-    <row r="208" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
           <t>TC-207</t>
@@ -12670,7 +12672,7 @@
         </is>
       </c>
     </row>
-    <row r="209" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
           <t>TC-208</t>
@@ -12731,7 +12733,7 @@
         </is>
       </c>
     </row>
-    <row r="210" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
           <t>TC-209</t>
@@ -12784,11 +12786,11 @@
       </c>
       <c r="K210" s="3" t="inlineStr">
         <is>
-          <t>exitcode:1</t>
-        </is>
-      </c>
-    </row>
-    <row r="211" ht="70" customHeight="1">
+          <t>&gt;=1</t>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="70" r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
           <t>TC-210</t>
@@ -12842,7 +12844,7 @@
         </is>
       </c>
     </row>
-    <row r="212" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
           <t>TC-211</t>
@@ -12896,7 +12898,7 @@
         </is>
       </c>
     </row>
-    <row r="213" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
           <t>TC-212</t>
@@ -12950,7 +12952,7 @@
         </is>
       </c>
     </row>
-    <row r="214" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
           <t>TC-213</t>
@@ -13004,7 +13006,7 @@
         </is>
       </c>
     </row>
-    <row r="215" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
           <t>TC-214</t>
@@ -13056,11 +13058,11 @@
       </c>
       <c r="K215" s="3" t="inlineStr">
         <is>
-          <t>exitcode:1</t>
-        </is>
-      </c>
-    </row>
-    <row r="216" ht="70" customHeight="1">
+          <t>&gt;=1</t>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="70" r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
           <t>TC-215</t>
@@ -13122,7 +13124,7 @@
         </is>
       </c>
     </row>
-    <row r="217" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
           <t>TC-216</t>
@@ -13179,7 +13181,7 @@
         </is>
       </c>
     </row>
-    <row r="218" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
           <t>TC-217</t>
@@ -13238,7 +13240,7 @@
         </is>
       </c>
     </row>
-    <row r="219" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
           <t>TC-218</t>
@@ -13295,7 +13297,7 @@
         </is>
       </c>
     </row>
-    <row r="220" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
           <t>TC-219</t>
@@ -13352,7 +13354,7 @@
         </is>
       </c>
     </row>
-    <row r="221" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
           <t>TC-220</t>
@@ -13413,7 +13415,7 @@
         </is>
       </c>
     </row>
-    <row r="222" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
           <t>TC-221</t>
@@ -13470,7 +13472,7 @@
         </is>
       </c>
     </row>
-    <row r="223" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
           <t>TC-222</t>
@@ -13527,7 +13529,7 @@
         </is>
       </c>
     </row>
-    <row r="224" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
           <t>TC-223</t>
@@ -13584,7 +13586,7 @@
         </is>
       </c>
     </row>
-    <row r="225" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
           <t>TC-224</t>
@@ -13640,7 +13642,7 @@
         </is>
       </c>
     </row>
-    <row r="226" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
           <t>TC-225</t>
@@ -13698,7 +13700,7 @@
         </is>
       </c>
     </row>
-    <row r="227" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
           <t>TC-226</t>
@@ -13757,7 +13759,7 @@
         </is>
       </c>
     </row>
-    <row r="228" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
           <t>TC-227</t>
@@ -13816,7 +13818,7 @@
         </is>
       </c>
     </row>
-    <row r="229" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
           <t>TC-228</t>
@@ -13875,7 +13877,7 @@
         </is>
       </c>
     </row>
-    <row r="230" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
           <t>TC-229</t>
@@ -13934,7 +13936,7 @@
         </is>
       </c>
     </row>
-    <row r="231" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
           <t>TC-230</t>
@@ -13991,7 +13993,7 @@
         </is>
       </c>
     </row>
-    <row r="232" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
           <t>TC-231</t>
@@ -14048,7 +14050,7 @@
         </is>
       </c>
     </row>
-    <row r="233" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
           <t>TC-232</t>
@@ -14105,7 +14107,7 @@
         </is>
       </c>
     </row>
-    <row r="234" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
           <t>TC-233</t>
@@ -14163,7 +14165,7 @@
         </is>
       </c>
     </row>
-    <row r="235" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
           <t>TC-234</t>
@@ -14221,7 +14223,7 @@
         </is>
       </c>
     </row>
-    <row r="236" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
           <t>TC-235</t>
@@ -14280,7 +14282,7 @@
         </is>
       </c>
     </row>
-    <row r="237" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
           <t>TC-236</t>
@@ -14338,7 +14340,7 @@
         </is>
       </c>
     </row>
-    <row r="238" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
           <t>TC-237</t>
@@ -14397,7 +14399,7 @@
         </is>
       </c>
     </row>
-    <row r="239" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
           <t>TC-238</t>
@@ -14460,7 +14462,7 @@
         </is>
       </c>
     </row>
-    <row r="240" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
           <t>TC-239</t>
@@ -14521,7 +14523,7 @@
         </is>
       </c>
     </row>
-    <row r="241" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
           <t>TC-240</t>
@@ -14580,7 +14582,7 @@
         </is>
       </c>
     </row>
-    <row r="242" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
           <t>TC-241</t>
@@ -14639,7 +14641,7 @@
         </is>
       </c>
     </row>
-    <row r="243" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
           <t>TC-242</t>
@@ -14698,7 +14700,7 @@
         </is>
       </c>
     </row>
-    <row r="244" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
           <t>TC-243</t>
@@ -14753,7 +14755,7 @@
         <v/>
       </c>
     </row>
-    <row r="245" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
           <t>TC-244</t>
@@ -14814,7 +14816,7 @@
         </is>
       </c>
     </row>
-    <row r="246" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
           <t>TC-245</t>
@@ -14869,7 +14871,7 @@
         <v/>
       </c>
     </row>
-    <row r="247" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
           <t>TC-246</t>
@@ -14927,7 +14929,7 @@
         <v/>
       </c>
     </row>
-    <row r="248" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
           <t>TC-247</t>
@@ -14984,7 +14986,7 @@
         </is>
       </c>
     </row>
-    <row r="249" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
           <t>TC-248</t>
@@ -15041,7 +15043,7 @@
         </is>
       </c>
     </row>
-    <row r="250" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
           <t>TC-249</t>
@@ -15098,7 +15100,7 @@
         </is>
       </c>
     </row>
-    <row r="251" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
           <t>TC-250</t>
@@ -15156,7 +15158,7 @@
         </is>
       </c>
     </row>
-    <row r="252" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
           <t>TC-251</t>
@@ -15214,7 +15216,7 @@
         </is>
       </c>
     </row>
-    <row r="253" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
           <t>TC-252</t>
@@ -15273,7 +15275,7 @@
         </is>
       </c>
     </row>
-    <row r="254" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
           <t>TC-253</t>
@@ -15331,7 +15333,7 @@
         </is>
       </c>
     </row>
-    <row r="255" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
           <t>TC-254</t>
@@ -15390,7 +15392,7 @@
         </is>
       </c>
     </row>
-    <row r="256" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
           <t>TC-255</t>
@@ -15447,7 +15449,7 @@
         </is>
       </c>
     </row>
-    <row r="257" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
           <t>TC-256</t>
@@ -15504,7 +15506,7 @@
         </is>
       </c>
     </row>
-    <row r="258" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
           <t>TC-257</t>
@@ -15567,7 +15569,7 @@
         </is>
       </c>
     </row>
-    <row r="259" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
           <t>TC-258</t>
@@ -15626,7 +15628,7 @@
         </is>
       </c>
     </row>
-    <row r="260" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
           <t>TC-259</t>
@@ -15685,7 +15687,7 @@
         </is>
       </c>
     </row>
-    <row r="261" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
           <t>TC-260</t>
@@ -15742,7 +15744,7 @@
         </is>
       </c>
     </row>
-    <row r="262" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
           <t>TC-261</t>
@@ -15799,7 +15801,7 @@
         </is>
       </c>
     </row>
-    <row r="263" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
           <t>TC-262</t>
@@ -15856,7 +15858,7 @@
         </is>
       </c>
     </row>
-    <row r="264" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
           <t>TC-263</t>
@@ -15912,7 +15914,7 @@
         </is>
       </c>
     </row>
-    <row r="265" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
           <t>TC-264</t>
@@ -15971,7 +15973,7 @@
         </is>
       </c>
     </row>
-    <row r="266" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
           <t>TC-265</t>
@@ -16030,7 +16032,7 @@
         </is>
       </c>
     </row>
-    <row r="267" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
           <t>TC-266</t>
@@ -16087,7 +16089,7 @@
         </is>
       </c>
     </row>
-    <row r="268" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
           <t>TC-267</t>
@@ -16145,7 +16147,7 @@
         </is>
       </c>
     </row>
-    <row r="269" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
           <t>TC-268</t>
@@ -16203,7 +16205,7 @@
         </is>
       </c>
     </row>
-    <row r="270" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
           <t>TC-269</t>
@@ -16260,7 +16262,7 @@
         </is>
       </c>
     </row>
-    <row r="271" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
           <t>TC-270</t>
@@ -16317,7 +16319,7 @@
         </is>
       </c>
     </row>
-    <row r="272" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
           <t>TC-271</t>
@@ -16376,7 +16378,7 @@
         </is>
       </c>
     </row>
-    <row r="273" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
           <t>TC-272</t>
@@ -16434,7 +16436,7 @@
         </is>
       </c>
     </row>
-    <row r="274" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
           <t>TC-273</t>
@@ -16493,7 +16495,7 @@
         </is>
       </c>
     </row>
-    <row r="275" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
           <t>TC-274</t>
@@ -16556,7 +16558,7 @@
         </is>
       </c>
     </row>
-    <row r="276" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
           <t>TC-275</t>
@@ -16615,7 +16617,7 @@
         </is>
       </c>
     </row>
-    <row r="277" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
           <t>TC-276</t>
@@ -16674,7 +16676,7 @@
         </is>
       </c>
     </row>
-    <row r="278" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
           <t>TC-277</t>
@@ -16731,7 +16733,7 @@
         </is>
       </c>
     </row>
-    <row r="279" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
           <t>TC-278</t>
@@ -16788,7 +16790,7 @@
         </is>
       </c>
     </row>
-    <row r="280" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
           <t>TC-279</t>
@@ -16847,7 +16849,7 @@
         </is>
       </c>
     </row>
-    <row r="281" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
           <t>TC-280</t>
@@ -16902,7 +16904,7 @@
         </is>
       </c>
     </row>
-    <row r="282" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
           <t>TC-281</t>
@@ -16961,7 +16963,7 @@
         </is>
       </c>
     </row>
-    <row r="283" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
           <t>TC-282</t>
@@ -17021,7 +17023,7 @@
         </is>
       </c>
     </row>
-    <row r="284" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
           <t>TC-283</t>
@@ -17078,7 +17080,7 @@
         </is>
       </c>
     </row>
-    <row r="285" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
           <t>TC-284</t>
@@ -17134,7 +17136,7 @@
         </is>
       </c>
     </row>
-    <row r="286" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
           <t>TC-285</t>
@@ -17192,7 +17194,7 @@
         </is>
       </c>
     </row>
-    <row r="287" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="287">
       <c r="A287" s="2" t="inlineStr">
         <is>
           <t>TC-286</t>
@@ -17250,7 +17252,7 @@
         </is>
       </c>
     </row>
-    <row r="288" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
           <t>TC-287</t>
@@ -17308,7 +17310,7 @@
         </is>
       </c>
     </row>
-    <row r="289" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="289">
       <c r="A289" s="2" t="inlineStr">
         <is>
           <t>TC-288</t>
@@ -17366,7 +17368,7 @@
         </is>
       </c>
     </row>
-    <row r="290" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
           <t>TC-289</t>
@@ -17424,7 +17426,7 @@
         </is>
       </c>
     </row>
-    <row r="291" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
           <t>TC-290</t>
@@ -17483,7 +17485,7 @@
         </is>
       </c>
     </row>
-    <row r="292" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
           <t>TC-291</t>
@@ -17541,7 +17543,7 @@
         </is>
       </c>
     </row>
-    <row r="293" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
           <t>TC-292</t>
@@ -17600,7 +17602,7 @@
         </is>
       </c>
     </row>
-    <row r="294" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
           <t>TC-293</t>
@@ -17663,7 +17665,7 @@
         </is>
       </c>
     </row>
-    <row r="295" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
           <t>TC-294</t>
@@ -17722,7 +17724,7 @@
         </is>
       </c>
     </row>
-    <row r="296" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
           <t>TC-295</t>
@@ -17781,7 +17783,7 @@
         </is>
       </c>
     </row>
-    <row r="297" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
           <t>TC-296</t>
@@ -17842,7 +17844,7 @@
         </is>
       </c>
     </row>
-    <row r="298" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
           <t>TC-297</t>
@@ -17901,7 +17903,7 @@
         </is>
       </c>
     </row>
-    <row r="299" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
           <t>TC-298</t>
@@ -17958,7 +17960,7 @@
         </is>
       </c>
     </row>
-    <row r="300" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
           <t>TC-299</t>
@@ -18015,7 +18017,7 @@
         </is>
       </c>
     </row>
-    <row r="301" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
           <t>TC-300</t>
@@ -18072,7 +18074,7 @@
         </is>
       </c>
     </row>
-    <row r="302" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
           <t>TC-301</t>
@@ -18131,7 +18133,7 @@
         </is>
       </c>
     </row>
-    <row r="303" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="303">
       <c r="A303" s="2" t="inlineStr">
         <is>
           <t>TC-302</t>
@@ -18190,7 +18192,7 @@
         </is>
       </c>
     </row>
-    <row r="304" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
           <t>TC-303</t>
@@ -18248,7 +18250,7 @@
         </is>
       </c>
     </row>
-    <row r="305" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="305">
       <c r="A305" s="2" t="inlineStr">
         <is>
           <t>TC-304</t>
@@ -18306,7 +18308,7 @@
         </is>
       </c>
     </row>
-    <row r="306" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
           <t>TC-305</t>
@@ -18365,7 +18367,7 @@
         </is>
       </c>
     </row>
-    <row r="307" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="307">
       <c r="A307" s="2" t="inlineStr">
         <is>
           <t>TC-306</t>
@@ -18423,7 +18425,7 @@
         </is>
       </c>
     </row>
-    <row r="308" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="308">
       <c r="A308" s="2" t="inlineStr">
         <is>
           <t>TC-307</t>
@@ -18482,7 +18484,7 @@
         </is>
       </c>
     </row>
-    <row r="309" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="309">
       <c r="A309" s="2" t="inlineStr">
         <is>
           <t>TC-308</t>
@@ -18545,7 +18547,7 @@
         </is>
       </c>
     </row>
-    <row r="310" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="310">
       <c r="A310" s="2" t="inlineStr">
         <is>
           <t>TC-309</t>
@@ -18604,7 +18606,7 @@
         </is>
       </c>
     </row>
-    <row r="311" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="311">
       <c r="A311" s="2" t="inlineStr">
         <is>
           <t>TC-310</t>
@@ -18663,7 +18665,7 @@
         </is>
       </c>
     </row>
-    <row r="312" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="312">
       <c r="A312" s="2" t="inlineStr">
         <is>
           <t>TC-311</t>
@@ -18724,7 +18726,7 @@
         </is>
       </c>
     </row>
-    <row r="313" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="313">
       <c r="A313" s="2" t="inlineStr">
         <is>
           <t>TC-312</t>
@@ -18781,7 +18783,7 @@
         </is>
       </c>
     </row>
-    <row r="314" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="314">
       <c r="A314" s="2" t="inlineStr">
         <is>
           <t>TC-313</t>
@@ -18838,7 +18840,7 @@
         </is>
       </c>
     </row>
-    <row r="315" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="315">
       <c r="A315" s="2" t="inlineStr">
         <is>
           <t>TC-314</t>
@@ -18897,7 +18899,7 @@
         </is>
       </c>
     </row>
-    <row r="316" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="316">
       <c r="A316" s="2" t="inlineStr">
         <is>
           <t>TC-315</t>
@@ -18956,7 +18958,7 @@
         </is>
       </c>
     </row>
-    <row r="317" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="317">
       <c r="A317" s="2" t="inlineStr">
         <is>
           <t>TC-316</t>
@@ -19013,7 +19015,7 @@
         </is>
       </c>
     </row>
-    <row r="318" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="318">
       <c r="A318" s="2" t="inlineStr">
         <is>
           <t>TC-317</t>
@@ -19070,7 +19072,7 @@
         </is>
       </c>
     </row>
-    <row r="319" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="319">
       <c r="A319" s="2" t="inlineStr">
         <is>
           <t>TC-318</t>
@@ -19127,7 +19129,7 @@
         </is>
       </c>
     </row>
-    <row r="320" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="320">
       <c r="A320" s="2" t="inlineStr">
         <is>
           <t>TC-319</t>
@@ -19184,7 +19186,7 @@
         </is>
       </c>
     </row>
-    <row r="321" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="321">
       <c r="A321" s="2" t="inlineStr">
         <is>
           <t>TC-320</t>
@@ -19241,7 +19243,7 @@
         </is>
       </c>
     </row>
-    <row r="322" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="322">
       <c r="A322" s="2" t="inlineStr">
         <is>
           <t>TC-321</t>
@@ -19299,7 +19301,7 @@
         </is>
       </c>
     </row>
-    <row r="323" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="323">
       <c r="A323" s="2" t="inlineStr">
         <is>
           <t>TC-322</t>
@@ -19357,7 +19359,7 @@
         </is>
       </c>
     </row>
-    <row r="324" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="324">
       <c r="A324" s="2" t="inlineStr">
         <is>
           <t>TC-323</t>
@@ -19414,7 +19416,7 @@
         </is>
       </c>
     </row>
-    <row r="325" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="325">
       <c r="A325" s="2" t="inlineStr">
         <is>
           <t>TC-324</t>
@@ -19471,7 +19473,7 @@
         </is>
       </c>
     </row>
-    <row r="326" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="326">
       <c r="A326" s="2" t="inlineStr">
         <is>
           <t>TC-325</t>
@@ -19528,7 +19530,7 @@
         </is>
       </c>
     </row>
-    <row r="327" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="327">
       <c r="A327" s="2" t="inlineStr">
         <is>
           <t>TC-326</t>
@@ -19585,7 +19587,7 @@
         </is>
       </c>
     </row>
-    <row r="328" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="328">
       <c r="A328" s="2" t="inlineStr">
         <is>
           <t>TC-327</t>
@@ -19644,7 +19646,7 @@
         </is>
       </c>
     </row>
-    <row r="329" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="329">
       <c r="A329" s="2" t="inlineStr">
         <is>
           <t>TC-328</t>
@@ -19702,7 +19704,7 @@
         </is>
       </c>
     </row>
-    <row r="330" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="330">
       <c r="A330" s="2" t="inlineStr">
         <is>
           <t>TC-329</t>
@@ -19761,7 +19763,7 @@
         </is>
       </c>
     </row>
-    <row r="331" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="331">
       <c r="A331" s="2" t="inlineStr">
         <is>
           <t>TC-330</t>
@@ -19824,7 +19826,7 @@
         </is>
       </c>
     </row>
-    <row r="332" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="332">
       <c r="A332" s="2" t="inlineStr">
         <is>
           <t>TC-331</t>
@@ -19883,7 +19885,7 @@
         </is>
       </c>
     </row>
-    <row r="333" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="333">
       <c r="A333" s="2" t="inlineStr">
         <is>
           <t>TC-332</t>
@@ -19942,7 +19944,7 @@
         </is>
       </c>
     </row>
-    <row r="334" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
           <t>TC-333</t>
@@ -20002,7 +20004,7 @@
         </is>
       </c>
     </row>
-    <row r="335" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="335">
       <c r="A335" s="2" t="inlineStr">
         <is>
           <t>TC-334</t>
@@ -20060,7 +20062,7 @@
         </is>
       </c>
     </row>
-    <row r="336" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="336">
       <c r="A336" s="2" t="inlineStr">
         <is>
           <t>TC-335</t>
@@ -20117,7 +20119,7 @@
         </is>
       </c>
     </row>
-    <row r="337" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="337">
       <c r="A337" s="2" t="inlineStr">
         <is>
           <t>TC-336</t>
@@ -20174,7 +20176,7 @@
         </is>
       </c>
     </row>
-    <row r="338" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="338">
       <c r="A338" s="2" t="inlineStr">
         <is>
           <t>TC-337</t>
@@ -20231,7 +20233,7 @@
         </is>
       </c>
     </row>
-    <row r="339" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="339">
       <c r="A339" s="2" t="inlineStr">
         <is>
           <t>TC-338</t>
@@ -20290,7 +20292,7 @@
         </is>
       </c>
     </row>
-    <row r="340" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="340">
       <c r="A340" s="2" t="inlineStr">
         <is>
           <t>TC-339</t>
@@ -20349,7 +20351,7 @@
         </is>
       </c>
     </row>
-    <row r="341" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="341">
       <c r="A341" s="2" t="inlineStr">
         <is>
           <t>TC-340</t>
@@ -20406,7 +20408,7 @@
         </is>
       </c>
     </row>
-    <row r="342" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="342">
       <c r="A342" s="2" t="inlineStr">
         <is>
           <t>TC-341</t>
@@ -20466,7 +20468,7 @@
         </is>
       </c>
     </row>
-    <row r="343" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="343">
       <c r="A343" s="2" t="inlineStr">
         <is>
           <t>TC-342</t>
@@ -20524,7 +20526,7 @@
         </is>
       </c>
     </row>
-    <row r="344" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="344">
       <c r="A344" s="2" t="inlineStr">
         <is>
           <t>TC-343</t>
@@ -20582,7 +20584,7 @@
         </is>
       </c>
     </row>
-    <row r="345" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="345">
       <c r="A345" s="2" t="inlineStr">
         <is>
           <t>TC-344</t>
@@ -20638,7 +20640,7 @@
         </is>
       </c>
     </row>
-    <row r="346" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="346">
       <c r="A346" s="2" t="inlineStr">
         <is>
           <t>TC-345</t>
@@ -20697,7 +20699,7 @@
         </is>
       </c>
     </row>
-    <row r="347" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="347">
       <c r="A347" s="2" t="inlineStr">
         <is>
           <t>TC-346</t>
@@ -20755,7 +20757,7 @@
         </is>
       </c>
     </row>
-    <row r="348" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="348">
       <c r="A348" s="2" t="inlineStr">
         <is>
           <t>TC-347</t>
@@ -20814,7 +20816,7 @@
         </is>
       </c>
     </row>
-    <row r="349" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="349">
       <c r="A349" s="2" t="inlineStr">
         <is>
           <t>TC-348</t>
@@ -20877,7 +20879,7 @@
         </is>
       </c>
     </row>
-    <row r="350" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="350">
       <c r="A350" s="2" t="inlineStr">
         <is>
           <t>TC-349</t>
@@ -20933,7 +20935,7 @@
         </is>
       </c>
     </row>
-    <row r="351" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="351">
       <c r="A351" s="2" t="inlineStr">
         <is>
           <t>TC-350</t>
@@ -20990,7 +20992,7 @@
         </is>
       </c>
     </row>
-    <row r="352" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="352">
       <c r="A352" s="2" t="inlineStr">
         <is>
           <t>TC-351</t>
@@ -21046,7 +21048,7 @@
         </is>
       </c>
     </row>
-    <row r="353" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="353">
       <c r="A353" s="2" t="inlineStr">
         <is>
           <t>TC-352</t>
@@ -21105,7 +21107,7 @@
         </is>
       </c>
     </row>
-    <row r="354" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="354">
       <c r="A354" s="2" t="inlineStr">
         <is>
           <t>TC-353</t>
@@ -21164,7 +21166,7 @@
         </is>
       </c>
     </row>
-    <row r="355" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="355">
       <c r="A355" s="2" t="inlineStr">
         <is>
           <t>TC-354</t>
@@ -21227,7 +21229,7 @@
         </is>
       </c>
     </row>
-    <row r="356" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="356">
       <c r="A356" s="2" t="inlineStr">
         <is>
           <t>TC-355</t>
@@ -21284,7 +21286,7 @@
         </is>
       </c>
     </row>
-    <row r="357" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="357">
       <c r="A357" s="2" t="inlineStr">
         <is>
           <t>TC-356</t>
@@ -21341,7 +21343,7 @@
         </is>
       </c>
     </row>
-    <row r="358" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="358">
       <c r="A358" s="2" t="inlineStr">
         <is>
           <t>TC-357</t>
@@ -21398,7 +21400,7 @@
         </is>
       </c>
     </row>
-    <row r="359" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="359">
       <c r="A359" s="2" t="inlineStr">
         <is>
           <t>TC-358</t>
@@ -21457,7 +21459,7 @@
         </is>
       </c>
     </row>
-    <row r="360" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="360">
       <c r="A360" s="2" t="inlineStr">
         <is>
           <t>TC-359</t>
@@ -21516,7 +21518,7 @@
         </is>
       </c>
     </row>
-    <row r="361" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="361">
       <c r="A361" s="2" t="inlineStr">
         <is>
           <t>TC-360</t>
@@ -21574,7 +21576,7 @@
         </is>
       </c>
     </row>
-    <row r="362" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="362">
       <c r="A362" s="2" t="inlineStr">
         <is>
           <t>TC-361</t>
@@ -21632,7 +21634,7 @@
         </is>
       </c>
     </row>
-    <row r="363" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="363">
       <c r="A363" s="2" t="inlineStr">
         <is>
           <t>TC-362</t>
@@ -21691,7 +21693,7 @@
         </is>
       </c>
     </row>
-    <row r="364" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="364">
       <c r="A364" s="2" t="inlineStr">
         <is>
           <t>TC-363</t>
@@ -21749,7 +21751,7 @@
         </is>
       </c>
     </row>
-    <row r="365" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="365">
       <c r="A365" s="2" t="inlineStr">
         <is>
           <t>TC-364</t>
@@ -21808,7 +21810,7 @@
         </is>
       </c>
     </row>
-    <row r="366" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="366">
       <c r="A366" s="2" t="inlineStr">
         <is>
           <t>TC-365</t>
@@ -21871,7 +21873,7 @@
         </is>
       </c>
     </row>
-    <row r="367" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="367">
       <c r="A367" s="2" t="inlineStr">
         <is>
           <t>TC-366</t>
@@ -21930,7 +21932,7 @@
         </is>
       </c>
     </row>
-    <row r="368" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="368">
       <c r="A368" s="2" t="inlineStr">
         <is>
           <t>TC-367</t>
@@ -21989,7 +21991,7 @@
         </is>
       </c>
     </row>
-    <row r="369" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="369">
       <c r="A369" s="2" t="inlineStr">
         <is>
           <t>TC-368</t>
@@ -22046,7 +22048,7 @@
         </is>
       </c>
     </row>
-    <row r="370" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="370">
       <c r="A370" s="2" t="inlineStr">
         <is>
           <t>TC-369</t>
@@ -22103,7 +22105,7 @@
         </is>
       </c>
     </row>
-    <row r="371" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="371">
       <c r="A371" s="2" t="inlineStr">
         <is>
           <t>TC-370</t>
@@ -22162,7 +22164,7 @@
         </is>
       </c>
     </row>
-    <row r="372" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="372">
       <c r="A372" s="2" t="inlineStr">
         <is>
           <t>TC-371</t>
@@ -22221,7 +22223,7 @@
         </is>
       </c>
     </row>
-    <row r="373" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="373">
       <c r="A373" s="2" t="inlineStr">
         <is>
           <t>TC-372</t>
@@ -22278,7 +22280,7 @@
         </is>
       </c>
     </row>
-    <row r="374" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="374">
       <c r="A374" s="2" t="inlineStr">
         <is>
           <t>TC-373</t>
@@ -22335,7 +22337,7 @@
         </is>
       </c>
     </row>
-    <row r="375" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="375">
       <c r="A375" s="2" t="inlineStr">
         <is>
           <t>TC-374</t>
@@ -22392,7 +22394,7 @@
         </is>
       </c>
     </row>
-    <row r="376" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="376">
       <c r="A376" s="2" t="inlineStr">
         <is>
           <t>TC-375</t>
@@ -22449,7 +22451,7 @@
         </is>
       </c>
     </row>
-    <row r="377" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="377">
       <c r="A377" s="2" t="inlineStr">
         <is>
           <t>TC-376</t>
@@ -22506,7 +22508,7 @@
         </is>
       </c>
     </row>
-    <row r="378" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="378">
       <c r="A378" s="2" t="inlineStr">
         <is>
           <t>TC-377</t>
@@ -22564,7 +22566,7 @@
         </is>
       </c>
     </row>
-    <row r="379" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="379">
       <c r="A379" s="2" t="inlineStr">
         <is>
           <t>TC-378</t>
@@ -22622,7 +22624,7 @@
         </is>
       </c>
     </row>
-    <row r="380" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="380">
       <c r="A380" s="2" t="inlineStr">
         <is>
           <t>TC-379</t>
@@ -22681,7 +22683,7 @@
         </is>
       </c>
     </row>
-    <row r="381" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="381">
       <c r="A381" s="2" t="inlineStr">
         <is>
           <t>TC-380</t>
@@ -22739,7 +22741,7 @@
         </is>
       </c>
     </row>
-    <row r="382" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="382">
       <c r="A382" s="2" t="inlineStr">
         <is>
           <t>TC-381</t>
@@ -22798,7 +22800,7 @@
         </is>
       </c>
     </row>
-    <row r="383" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="383">
       <c r="A383" s="2" t="inlineStr">
         <is>
           <t>TC-382</t>
@@ -22859,7 +22861,7 @@
         </is>
       </c>
     </row>
-    <row r="384" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="384">
       <c r="A384" s="2" t="inlineStr">
         <is>
           <t>TC-383</t>
@@ -22922,7 +22924,7 @@
         </is>
       </c>
     </row>
-    <row r="385" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="385">
       <c r="A385" s="2" t="inlineStr">
         <is>
           <t>TC-384</t>
@@ -22981,7 +22983,7 @@
         </is>
       </c>
     </row>
-    <row r="386" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="386">
       <c r="A386" s="2" t="inlineStr">
         <is>
           <t>TC-385</t>
@@ -23040,7 +23042,7 @@
         </is>
       </c>
     </row>
-    <row r="387" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="387">
       <c r="A387" s="2" t="inlineStr">
         <is>
           <t>TC-386</t>
@@ -23097,7 +23099,7 @@
         </is>
       </c>
     </row>
-    <row r="388" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="388">
       <c r="A388" s="2" t="inlineStr">
         <is>
           <t>TC-387</t>
@@ -23154,7 +23156,7 @@
         </is>
       </c>
     </row>
-    <row r="389" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="389">
       <c r="A389" s="2" t="inlineStr">
         <is>
           <t>TC-388</t>
@@ -23213,7 +23215,7 @@
         </is>
       </c>
     </row>
-    <row r="390" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="390">
       <c r="A390" s="2" t="inlineStr">
         <is>
           <t>TC-389</t>
@@ -23272,7 +23274,7 @@
         </is>
       </c>
     </row>
-    <row r="391" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="391">
       <c r="A391" s="2" t="inlineStr">
         <is>
           <t>TC-390</t>
@@ -23329,7 +23331,7 @@
         </is>
       </c>
     </row>
-    <row r="392" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="392">
       <c r="A392" s="2" t="inlineStr">
         <is>
           <t>TC-391</t>
@@ -23387,7 +23389,7 @@
         </is>
       </c>
     </row>
-    <row r="393" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="393">
       <c r="A393" s="2" t="inlineStr">
         <is>
           <t>TC-392</t>
@@ -23445,7 +23447,7 @@
         </is>
       </c>
     </row>
-    <row r="394" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="394">
       <c r="A394" s="2" t="inlineStr">
         <is>
           <t>TC-393</t>
@@ -23506,7 +23508,7 @@
         </is>
       </c>
     </row>
-    <row r="395" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="395">
       <c r="A395" s="2" t="inlineStr">
         <is>
           <t>TC-394</t>
@@ -23565,7 +23567,7 @@
         </is>
       </c>
     </row>
-    <row r="396" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="396">
       <c r="A396" s="2" t="inlineStr">
         <is>
           <t>TC-395</t>
@@ -23623,7 +23625,7 @@
         </is>
       </c>
     </row>
-    <row r="397" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="397">
       <c r="A397" s="2" t="inlineStr">
         <is>
           <t>TC-396</t>
@@ -23682,7 +23684,7 @@
         </is>
       </c>
     </row>
-    <row r="398" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="398">
       <c r="A398" s="2" t="inlineStr">
         <is>
           <t>TC-397</t>
@@ -23745,7 +23747,7 @@
         </is>
       </c>
     </row>
-    <row r="399" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="399">
       <c r="A399" s="2" t="inlineStr">
         <is>
           <t>TC-398</t>
@@ -23804,7 +23806,7 @@
         </is>
       </c>
     </row>
-    <row r="400" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="400">
       <c r="A400" s="2" t="inlineStr">
         <is>
           <t>TC-399</t>
@@ -23863,7 +23865,7 @@
         </is>
       </c>
     </row>
-    <row r="401" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="401">
       <c r="A401" s="2" t="inlineStr">
         <is>
           <t>TC-400</t>
@@ -23920,7 +23922,7 @@
         </is>
       </c>
     </row>
-    <row r="402" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="402">
       <c r="A402" s="2" t="inlineStr">
         <is>
           <t>TC-401</t>
@@ -23977,7 +23979,7 @@
         </is>
       </c>
     </row>
-    <row r="403" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="403">
       <c r="A403" s="2" t="inlineStr">
         <is>
           <t>TC-402</t>
@@ -24036,7 +24038,7 @@
         </is>
       </c>
     </row>
-    <row r="404" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="404">
       <c r="A404" s="2" t="inlineStr">
         <is>
           <t>TC-403</t>
@@ -24095,7 +24097,7 @@
         </is>
       </c>
     </row>
-    <row r="405" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="405">
       <c r="A405" s="2" t="inlineStr">
         <is>
           <t>TC-404</t>
@@ -24153,7 +24155,7 @@
         </is>
       </c>
     </row>
-    <row r="406" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="406">
       <c r="A406" s="2" t="inlineStr">
         <is>
           <t>TC-405</t>
@@ -24211,7 +24213,7 @@
         </is>
       </c>
     </row>
-    <row r="407" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="407">
       <c r="A407" s="2" t="inlineStr">
         <is>
           <t>TC-406</t>
@@ -24268,7 +24270,7 @@
         </is>
       </c>
     </row>
-    <row r="408" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="408">
       <c r="A408" s="2" t="inlineStr">
         <is>
           <t>TC-407</t>
@@ -24325,7 +24327,7 @@
         </is>
       </c>
     </row>
-    <row r="409" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="409">
       <c r="A409" s="2" t="inlineStr">
         <is>
           <t>TC-408</t>
@@ -24382,7 +24384,7 @@
         </is>
       </c>
     </row>
-    <row r="410" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="410">
       <c r="A410" s="2" t="inlineStr">
         <is>
           <t>TC-409</t>
@@ -24439,7 +24441,7 @@
         </is>
       </c>
     </row>
-    <row r="411" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="411">
       <c r="A411" s="2" t="inlineStr">
         <is>
           <t>TC-410</t>
@@ -24496,7 +24498,7 @@
         </is>
       </c>
     </row>
-    <row r="412" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="412">
       <c r="A412" s="2" t="inlineStr">
         <is>
           <t>TC-411</t>
@@ -24555,7 +24557,7 @@
         </is>
       </c>
     </row>
-    <row r="413" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="413">
       <c r="A413" s="2" t="inlineStr">
         <is>
           <t>TC-412</t>
@@ -24613,7 +24615,7 @@
         </is>
       </c>
     </row>
-    <row r="414" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="414">
       <c r="A414" s="2" t="inlineStr">
         <is>
           <t>TC-413</t>
@@ -24672,7 +24674,7 @@
         </is>
       </c>
     </row>
-    <row r="415" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="415">
       <c r="A415" s="2" t="inlineStr">
         <is>
           <t>TC-414</t>
@@ -24733,7 +24735,7 @@
         </is>
       </c>
     </row>
-    <row r="416" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="416">
       <c r="A416" s="2" t="inlineStr">
         <is>
           <t>TC-415</t>
@@ -24796,7 +24798,7 @@
         </is>
       </c>
     </row>
-    <row r="417" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="417">
       <c r="A417" s="2" t="inlineStr">
         <is>
           <t>TC-416</t>
@@ -24855,7 +24857,7 @@
         </is>
       </c>
     </row>
-    <row r="418" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="418">
       <c r="A418" s="2" t="inlineStr">
         <is>
           <t>TC-417</t>
@@ -24914,7 +24916,7 @@
         </is>
       </c>
     </row>
-    <row r="419" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="419">
       <c r="A419" s="2" t="inlineStr">
         <is>
           <t>TC-418</t>
@@ -24971,7 +24973,7 @@
         </is>
       </c>
     </row>
-    <row r="420" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="420">
       <c r="A420" s="2" t="inlineStr">
         <is>
           <t>TC-419</t>
@@ -25028,7 +25030,7 @@
         </is>
       </c>
     </row>
-    <row r="421" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="421">
       <c r="A421" s="2" t="inlineStr">
         <is>
           <t>TC-420</t>
@@ -25087,7 +25089,7 @@
         </is>
       </c>
     </row>
-    <row r="422" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="422">
       <c r="A422" s="2" t="inlineStr">
         <is>
           <t>TC-421</t>
@@ -25146,7 +25148,7 @@
         </is>
       </c>
     </row>
-    <row r="423" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="423">
       <c r="A423" s="2" t="inlineStr">
         <is>
           <t>TC-422</t>
@@ -25203,7 +25205,7 @@
         </is>
       </c>
     </row>
-    <row r="424" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="424">
       <c r="A424" s="2" t="inlineStr">
         <is>
           <t>TC-423</t>
@@ -25261,7 +25263,7 @@
         </is>
       </c>
     </row>
-    <row r="425" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="425">
       <c r="A425" s="2" t="inlineStr">
         <is>
           <t>TC-424</t>
@@ -25319,7 +25321,7 @@
         </is>
       </c>
     </row>
-    <row r="426" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="426">
       <c r="A426" s="2" t="inlineStr">
         <is>
           <t>TC-425</t>
@@ -25380,7 +25382,7 @@
         </is>
       </c>
     </row>
-    <row r="427" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="427">
       <c r="A427" s="2" t="inlineStr">
         <is>
           <t>TC-426</t>
@@ -25439,7 +25441,7 @@
         </is>
       </c>
     </row>
-    <row r="428" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="428">
       <c r="A428" s="2" t="inlineStr">
         <is>
           <t>TC-427</t>
@@ -25497,7 +25499,7 @@
         </is>
       </c>
     </row>
-    <row r="429" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="429">
       <c r="A429" s="2" t="inlineStr">
         <is>
           <t>TC-428</t>
@@ -25556,7 +25558,7 @@
         </is>
       </c>
     </row>
-    <row r="430" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="430">
       <c r="A430" s="2" t="inlineStr">
         <is>
           <t>TC-429</t>
@@ -25619,7 +25621,7 @@
         </is>
       </c>
     </row>
-    <row r="431" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="431">
       <c r="A431" s="2" t="inlineStr">
         <is>
           <t>TC-430</t>
@@ -25678,7 +25680,7 @@
         </is>
       </c>
     </row>
-    <row r="432" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="432">
       <c r="A432" s="2" t="inlineStr">
         <is>
           <t>TC-431</t>
@@ -25737,7 +25739,7 @@
         </is>
       </c>
     </row>
-    <row r="433" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="433">
       <c r="A433" s="2" t="inlineStr">
         <is>
           <t>TC-432</t>
@@ -25798,7 +25800,7 @@
         </is>
       </c>
     </row>
-    <row r="434" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="434">
       <c r="A434" s="2" t="inlineStr">
         <is>
           <t>TC-433</t>
@@ -25855,7 +25857,7 @@
         </is>
       </c>
     </row>
-    <row r="435" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="435">
       <c r="A435" s="2" t="inlineStr">
         <is>
           <t>TC-434</t>
@@ -25912,7 +25914,7 @@
         </is>
       </c>
     </row>
-    <row r="436" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="436">
       <c r="A436" s="2" t="inlineStr">
         <is>
           <t>TC-435</t>
@@ -25969,7 +25971,7 @@
         </is>
       </c>
     </row>
-    <row r="437" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="437">
       <c r="A437" s="2" t="inlineStr">
         <is>
           <t>TC-436</t>
@@ -26028,7 +26030,7 @@
         </is>
       </c>
     </row>
-    <row r="438" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="438">
       <c r="A438" s="2" t="inlineStr">
         <is>
           <t>TC-437</t>
@@ -26087,7 +26089,7 @@
         </is>
       </c>
     </row>
-    <row r="439" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="439">
       <c r="A439" s="2" t="inlineStr">
         <is>
           <t>TC-438</t>
@@ -26145,7 +26147,7 @@
         </is>
       </c>
     </row>
-    <row r="440" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="440">
       <c r="A440" s="2" t="inlineStr">
         <is>
           <t>TC-439</t>
@@ -26203,7 +26205,7 @@
         </is>
       </c>
     </row>
-    <row r="441" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="441">
       <c r="A441" s="2" t="inlineStr">
         <is>
           <t>TC-440</t>
@@ -26262,7 +26264,7 @@
         </is>
       </c>
     </row>
-    <row r="442" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="442">
       <c r="A442" s="2" t="inlineStr">
         <is>
           <t>TC-441</t>
@@ -26320,7 +26322,7 @@
         </is>
       </c>
     </row>
-    <row r="443" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="443">
       <c r="A443" s="2" t="inlineStr">
         <is>
           <t>TC-442</t>
@@ -26379,7 +26381,7 @@
         </is>
       </c>
     </row>
-    <row r="444" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="444">
       <c r="A444" s="2" t="inlineStr">
         <is>
           <t>TC-443</t>
@@ -26442,7 +26444,7 @@
         </is>
       </c>
     </row>
-    <row r="445" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="445">
       <c r="A445" s="2" t="inlineStr">
         <is>
           <t>TC-444</t>
@@ -26501,7 +26503,7 @@
         </is>
       </c>
     </row>
-    <row r="446" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="446">
       <c r="A446" s="2" t="inlineStr">
         <is>
           <t>TC-445</t>
@@ -26560,7 +26562,7 @@
         </is>
       </c>
     </row>
-    <row r="447" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="447">
       <c r="A447" s="2" t="inlineStr">
         <is>
           <t>TC-446</t>
@@ -26623,7 +26625,7 @@
         </is>
       </c>
     </row>
-    <row r="448" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="448">
       <c r="A448" s="2" t="inlineStr">
         <is>
           <t>TC-447</t>
@@ -26682,7 +26684,7 @@
         </is>
       </c>
     </row>
-    <row r="449" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="449">
       <c r="A449" s="2" t="inlineStr">
         <is>
           <t>TC-448</t>
@@ -26741,7 +26743,7 @@
         </is>
       </c>
     </row>
-    <row r="450" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="450">
       <c r="A450" s="2" t="inlineStr">
         <is>
           <t>TC-449</t>
@@ -26799,7 +26801,7 @@
         </is>
       </c>
     </row>
-    <row r="451" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="451">
       <c r="A451" s="2" t="inlineStr">
         <is>
           <t>TC-450</t>
@@ -26857,7 +26859,7 @@
         </is>
       </c>
     </row>
-    <row r="452" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="452">
       <c r="A452" s="2" t="inlineStr">
         <is>
           <t>TC-451</t>
@@ -26916,7 +26918,7 @@
         </is>
       </c>
     </row>
-    <row r="453" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="453">
       <c r="A453" s="2" t="inlineStr">
         <is>
           <t>TC-452</t>
@@ -26973,7 +26975,7 @@
         </is>
       </c>
     </row>
-    <row r="454" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="454">
       <c r="A454" s="2" t="inlineStr">
         <is>
           <t>TC-453</t>
@@ -27030,7 +27032,7 @@
         </is>
       </c>
     </row>
-    <row r="455" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="455">
       <c r="A455" s="2" t="inlineStr">
         <is>
           <t>TC-454</t>
@@ -27087,7 +27089,7 @@
         </is>
       </c>
     </row>
-    <row r="456" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="456">
       <c r="A456" s="2" t="inlineStr">
         <is>
           <t>TC-455</t>
@@ -27146,7 +27148,7 @@
         </is>
       </c>
     </row>
-    <row r="457" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="457">
       <c r="A457" s="2" t="inlineStr">
         <is>
           <t>TC-456</t>
@@ -27204,7 +27206,7 @@
         </is>
       </c>
     </row>
-    <row r="458" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="458">
       <c r="A458" s="2" t="inlineStr">
         <is>
           <t>TC-457</t>
@@ -27263,7 +27265,7 @@
         </is>
       </c>
     </row>
-    <row r="459" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="459">
       <c r="A459" s="2" t="inlineStr">
         <is>
           <t>TC-458</t>
@@ -27326,7 +27328,7 @@
         </is>
       </c>
     </row>
-    <row r="460" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="460">
       <c r="A460" s="2" t="inlineStr">
         <is>
           <t>TC-459</t>
@@ -27385,7 +27387,7 @@
         </is>
       </c>
     </row>
-    <row r="461" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="461">
       <c r="A461" s="2" t="inlineStr">
         <is>
           <t>TC-460</t>
@@ -27444,7 +27446,7 @@
         </is>
       </c>
     </row>
-    <row r="462" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="462">
       <c r="A462" s="2" t="inlineStr">
         <is>
           <t>TC-461</t>
@@ -27505,7 +27507,7 @@
         </is>
       </c>
     </row>
-    <row r="463" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="463">
       <c r="A463" s="2" t="inlineStr">
         <is>
           <t>TC-462</t>
@@ -27562,7 +27564,7 @@
         </is>
       </c>
     </row>
-    <row r="464" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="464">
       <c r="A464" s="2" t="inlineStr">
         <is>
           <t>TC-463</t>
@@ -27619,7 +27621,7 @@
         </is>
       </c>
     </row>
-    <row r="465" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="465">
       <c r="A465" s="2" t="inlineStr">
         <is>
           <t>TC-464</t>
@@ -27676,7 +27678,7 @@
         </is>
       </c>
     </row>
-    <row r="466" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="466">
       <c r="A466" s="2" t="inlineStr">
         <is>
           <t>TC-465</t>
@@ -27735,7 +27737,7 @@
         </is>
       </c>
     </row>
-    <row r="467" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="467">
       <c r="A467" s="2" t="inlineStr">
         <is>
           <t>TC-466</t>
@@ -27794,7 +27796,7 @@
         </is>
       </c>
     </row>
-    <row r="468" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="468">
       <c r="A468" s="2" t="inlineStr">
         <is>
           <t>TC-467</t>
@@ -27852,7 +27854,7 @@
         </is>
       </c>
     </row>
-    <row r="469" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="469">
       <c r="A469" s="2" t="inlineStr">
         <is>
           <t>TC-468</t>
@@ -27910,7 +27912,7 @@
         </is>
       </c>
     </row>
-    <row r="470" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="470">
       <c r="A470" s="2" t="inlineStr">
         <is>
           <t>TC-469</t>
@@ -27969,7 +27971,7 @@
         </is>
       </c>
     </row>
-    <row r="471" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="471">
       <c r="A471" s="2" t="inlineStr">
         <is>
           <t>TC-470</t>
@@ -28027,7 +28029,7 @@
         </is>
       </c>
     </row>
-    <row r="472" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="472">
       <c r="A472" s="2" t="inlineStr">
         <is>
           <t>TC-471</t>
@@ -28086,7 +28088,7 @@
         </is>
       </c>
     </row>
-    <row r="473" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="473">
       <c r="A473" s="2" t="inlineStr">
         <is>
           <t>TC-472</t>
@@ -28149,7 +28151,7 @@
         </is>
       </c>
     </row>
-    <row r="474" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="474">
       <c r="A474" s="2" t="inlineStr">
         <is>
           <t>TC-473</t>
@@ -28208,7 +28210,7 @@
         </is>
       </c>
     </row>
-    <row r="475" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="475">
       <c r="A475" s="2" t="inlineStr">
         <is>
           <t>TC-474</t>
@@ -28267,7 +28269,7 @@
         </is>
       </c>
     </row>
-    <row r="476" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="476">
       <c r="A476" s="2" t="inlineStr">
         <is>
           <t>TC-475</t>
@@ -28328,7 +28330,7 @@
         </is>
       </c>
     </row>
-    <row r="477" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="477">
       <c r="A477" s="2" t="inlineStr">
         <is>
           <t>TC-476</t>
@@ -28387,7 +28389,7 @@
         </is>
       </c>
     </row>
-    <row r="478" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="478">
       <c r="A478" s="2" t="inlineStr">
         <is>
           <t>TC-477</t>
@@ -28446,7 +28448,7 @@
         </is>
       </c>
     </row>
-    <row r="479" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="479">
       <c r="A479" s="2" t="inlineStr">
         <is>
           <t>TC-478</t>
@@ -28503,7 +28505,7 @@
         </is>
       </c>
     </row>
-    <row r="480" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="480">
       <c r="A480" s="2" t="inlineStr">
         <is>
           <t>TC-479</t>
@@ -28560,7 +28562,7 @@
         </is>
       </c>
     </row>
-    <row r="481" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="481">
       <c r="A481" s="2" t="inlineStr">
         <is>
           <t>TC-480</t>
@@ -28617,7 +28619,7 @@
         </is>
       </c>
     </row>
-    <row r="482" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="482">
       <c r="A482" s="2" t="inlineStr">
         <is>
           <t>TC-481</t>
@@ -28675,7 +28677,7 @@
         </is>
       </c>
     </row>
-    <row r="483" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="483">
       <c r="A483" s="2" t="inlineStr">
         <is>
           <t>TC-482</t>
@@ -28733,7 +28735,7 @@
         </is>
       </c>
     </row>
-    <row r="484" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="484">
       <c r="A484" s="2" t="inlineStr">
         <is>
           <t>TC-483</t>
@@ -28792,7 +28794,7 @@
         </is>
       </c>
     </row>
-    <row r="485" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="485">
       <c r="A485" s="2" t="inlineStr">
         <is>
           <t>TC-484</t>
@@ -28850,7 +28852,7 @@
         </is>
       </c>
     </row>
-    <row r="486" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="486">
       <c r="A486" s="2" t="inlineStr">
         <is>
           <t>TC-485</t>
@@ -28909,7 +28911,7 @@
         </is>
       </c>
     </row>
-    <row r="487" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="487">
       <c r="A487" s="2" t="inlineStr">
         <is>
           <t>TC-486</t>
@@ -28972,7 +28974,7 @@
         </is>
       </c>
     </row>
-    <row r="488" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="488">
       <c r="A488" s="2" t="inlineStr">
         <is>
           <t>TC-487</t>
@@ -29031,7 +29033,7 @@
         </is>
       </c>
     </row>
-    <row r="489" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="489">
       <c r="A489" s="2" t="inlineStr">
         <is>
           <t>TC-488</t>
@@ -29090,7 +29092,7 @@
         </is>
       </c>
     </row>
-    <row r="490" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="490">
       <c r="A490" s="2" t="inlineStr">
         <is>
           <t>TC-489</t>
@@ -29147,7 +29149,7 @@
         </is>
       </c>
     </row>
-    <row r="491" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="491">
       <c r="A491" s="2" t="inlineStr">
         <is>
           <t>TC-490</t>
@@ -29204,7 +29206,7 @@
         </is>
       </c>
     </row>
-    <row r="492" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="492">
       <c r="A492" s="2" t="inlineStr">
         <is>
           <t>TC-491</t>
@@ -29261,7 +29263,7 @@
         </is>
       </c>
     </row>
-    <row r="493" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="493">
       <c r="A493" s="2" t="inlineStr">
         <is>
           <t>TC-492</t>
@@ -29320,7 +29322,7 @@
         </is>
       </c>
     </row>
-    <row r="494" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="494">
       <c r="A494" s="2" t="inlineStr">
         <is>
           <t>TC-493</t>
@@ -29379,7 +29381,7 @@
         </is>
       </c>
     </row>
-    <row r="495" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="495">
       <c r="A495" s="2" t="inlineStr">
         <is>
           <t>TC-494</t>
@@ -29437,7 +29439,7 @@
         </is>
       </c>
     </row>
-    <row r="496" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="496">
       <c r="A496" s="2" t="inlineStr">
         <is>
           <t>TC-495</t>
@@ -29495,7 +29497,7 @@
         </is>
       </c>
     </row>
-    <row r="497" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="497">
       <c r="A497" s="2" t="inlineStr">
         <is>
           <t>TC-496</t>
@@ -29554,7 +29556,7 @@
         </is>
       </c>
     </row>
-    <row r="498" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="498">
       <c r="A498" s="2" t="inlineStr">
         <is>
           <t>TC-497</t>
@@ -29612,7 +29614,7 @@
         </is>
       </c>
     </row>
-    <row r="499" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="499">
       <c r="A499" s="2" t="inlineStr">
         <is>
           <t>TC-498</t>
@@ -29671,7 +29673,7 @@
         </is>
       </c>
     </row>
-    <row r="500" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="500">
       <c r="A500" s="2" t="inlineStr">
         <is>
           <t>TC-499</t>
@@ -29732,7 +29734,7 @@
         </is>
       </c>
     </row>
-    <row r="501" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="501">
       <c r="A501" s="2" t="inlineStr">
         <is>
           <t>TC-500</t>
@@ -29795,7 +29797,7 @@
         </is>
       </c>
     </row>
-    <row r="502" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="502">
       <c r="A502" s="2" t="inlineStr">
         <is>
           <t>TC-501</t>
@@ -29854,7 +29856,7 @@
         </is>
       </c>
     </row>
-    <row r="503" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="503">
       <c r="A503" s="2" t="inlineStr">
         <is>
           <t>TC-502</t>
@@ -29913,7 +29915,7 @@
         </is>
       </c>
     </row>
-    <row r="504" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="504">
       <c r="A504" s="2" t="inlineStr">
         <is>
           <t>TC-503</t>
@@ -29970,7 +29972,7 @@
         </is>
       </c>
     </row>
-    <row r="505" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="505">
       <c r="A505" s="2" t="inlineStr">
         <is>
           <t>TC-504</t>
@@ -30027,7 +30029,7 @@
         </is>
       </c>
     </row>
-    <row r="506" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="506">
       <c r="A506" s="2" t="inlineStr">
         <is>
           <t>TC-505</t>
@@ -30084,7 +30086,7 @@
         </is>
       </c>
     </row>
-    <row r="507" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="507">
       <c r="A507" s="2" t="inlineStr">
         <is>
           <t>TC-506</t>
@@ -30143,7 +30145,7 @@
         </is>
       </c>
     </row>
-    <row r="508" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="508">
       <c r="A508" s="2" t="inlineStr">
         <is>
           <t>TC-507</t>
@@ -30202,7 +30204,7 @@
         </is>
       </c>
     </row>
-    <row r="509" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="509">
       <c r="A509" s="2" t="inlineStr">
         <is>
           <t>TC-508</t>
@@ -30260,7 +30262,7 @@
         </is>
       </c>
     </row>
-    <row r="510" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="510">
       <c r="A510" s="2" t="inlineStr">
         <is>
           <t>TC-509</t>
@@ -30318,7 +30320,7 @@
         </is>
       </c>
     </row>
-    <row r="511" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="511">
       <c r="A511" s="2" t="inlineStr">
         <is>
           <t>TC-510</t>
@@ -30379,7 +30381,7 @@
         </is>
       </c>
     </row>
-    <row r="512" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="512">
       <c r="A512" s="2" t="inlineStr">
         <is>
           <t>TC-511</t>
@@ -30438,7 +30440,7 @@
         </is>
       </c>
     </row>
-    <row r="513" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="513">
       <c r="A513" s="2" t="inlineStr">
         <is>
           <t>TC-512</t>
@@ -30496,7 +30498,7 @@
         </is>
       </c>
     </row>
-    <row r="514" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="514">
       <c r="A514" s="2" t="inlineStr">
         <is>
           <t>TC-513</t>
@@ -30555,7 +30557,7 @@
         </is>
       </c>
     </row>
-    <row r="515" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="515">
       <c r="A515" s="2" t="inlineStr">
         <is>
           <t>TC-514</t>
@@ -30618,7 +30620,7 @@
         </is>
       </c>
     </row>
-    <row r="516" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="516">
       <c r="A516" s="2" t="inlineStr">
         <is>
           <t>TC-515</t>
@@ -30677,7 +30679,7 @@
         </is>
       </c>
     </row>
-    <row r="517" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="517">
       <c r="A517" s="2" t="inlineStr">
         <is>
           <t>TC-516</t>
@@ -30736,7 +30738,7 @@
         </is>
       </c>
     </row>
-    <row r="518" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="518">
       <c r="A518" s="2" t="inlineStr">
         <is>
           <t>TC-517</t>
@@ -30795,7 +30797,7 @@
         </is>
       </c>
     </row>
-    <row r="519" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="519">
       <c r="A519" s="2" t="inlineStr">
         <is>
           <t>TC-518</t>
@@ -30854,7 +30856,7 @@
         </is>
       </c>
     </row>
-    <row r="520" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="520">
       <c r="A520" s="2" t="inlineStr">
         <is>
           <t>TC-519</t>
@@ -30913,7 +30915,7 @@
         </is>
       </c>
     </row>
-    <row r="521" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="521">
       <c r="A521" s="2" t="inlineStr">
         <is>
           <t>TC-520</t>
@@ -30972,7 +30974,7 @@
         </is>
       </c>
     </row>
-    <row r="522" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="522">
       <c r="A522" s="2" t="inlineStr">
         <is>
           <t>TC-521</t>
@@ -31031,7 +31033,7 @@
         </is>
       </c>
     </row>
-    <row r="523" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="523">
       <c r="A523" s="2" t="inlineStr">
         <is>
           <t>TC-522</t>
@@ -31090,7 +31092,7 @@
         </is>
       </c>
     </row>
-    <row r="524" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="524">
       <c r="A524" s="2" t="inlineStr">
         <is>
           <t>TC-523</t>
@@ -31149,7 +31151,7 @@
         </is>
       </c>
     </row>
-    <row r="525" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="525">
       <c r="A525" s="2" t="inlineStr">
         <is>
           <t>TC-524</t>
@@ -31208,7 +31210,7 @@
         </is>
       </c>
     </row>
-    <row r="526" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="526">
       <c r="A526" s="2" t="inlineStr">
         <is>
           <t>TC-525</t>
@@ -31268,7 +31270,7 @@
         </is>
       </c>
     </row>
-    <row r="527" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="527">
       <c r="A527" s="2" t="inlineStr">
         <is>
           <t>TC-526</t>
@@ -31327,7 +31329,7 @@
         </is>
       </c>
     </row>
-    <row r="528" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="528">
       <c r="A528" s="2" t="inlineStr">
         <is>
           <t>TC-527</t>
@@ -31387,7 +31389,7 @@
         </is>
       </c>
     </row>
-    <row r="529" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="529">
       <c r="A529" s="2" t="inlineStr">
         <is>
           <t>TC-528</t>
@@ -31446,7 +31448,7 @@
         </is>
       </c>
     </row>
-    <row r="530" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="530">
       <c r="A530" s="2" t="inlineStr">
         <is>
           <t>TC-529</t>
@@ -31506,7 +31508,7 @@
         </is>
       </c>
     </row>
-    <row r="531" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="531">
       <c r="A531" s="2" t="inlineStr">
         <is>
           <t>TC-530</t>
@@ -31566,7 +31568,7 @@
         </is>
       </c>
     </row>
-    <row r="532" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="532">
       <c r="A532" s="2" t="inlineStr">
         <is>
           <t>TC-531</t>
@@ -31629,7 +31631,7 @@
         </is>
       </c>
     </row>
-    <row r="533" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="533">
       <c r="A533" s="2" t="inlineStr">
         <is>
           <t>TC-532</t>
@@ -31689,7 +31691,7 @@
         </is>
       </c>
     </row>
-    <row r="534" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="534">
       <c r="A534" s="2" t="inlineStr">
         <is>
           <t>TC-533</t>
@@ -31750,7 +31752,7 @@
         </is>
       </c>
     </row>
-    <row r="535" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="535">
       <c r="A535" s="2" t="inlineStr">
         <is>
           <t>TC-534</t>
@@ -31810,7 +31812,7 @@
         </is>
       </c>
     </row>
-    <row r="536" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="536">
       <c r="A536" s="2" t="inlineStr">
         <is>
           <t>TC-535</t>
@@ -31870,7 +31872,7 @@
         </is>
       </c>
     </row>
-    <row r="537" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="537">
       <c r="A537" s="2" t="inlineStr">
         <is>
           <t>TC-536</t>
@@ -31930,7 +31932,7 @@
         </is>
       </c>
     </row>
-    <row r="538" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="538">
       <c r="A538" s="2" t="inlineStr">
         <is>
           <t>TC-537</t>
@@ -31989,7 +31991,7 @@
         </is>
       </c>
     </row>
-    <row r="539" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="539">
       <c r="A539" s="2" t="inlineStr">
         <is>
           <t>TC-538</t>
@@ -32049,7 +32051,7 @@
         </is>
       </c>
     </row>
-    <row r="540" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="540">
       <c r="A540" s="2" t="inlineStr">
         <is>
           <t>TC-539</t>
@@ -32108,7 +32110,7 @@
         </is>
       </c>
     </row>
-    <row r="541" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="541">
       <c r="A541" s="2" t="inlineStr">
         <is>
           <t>TC-540</t>
@@ -32162,7 +32164,7 @@
         </is>
       </c>
     </row>
-    <row r="542" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="542">
       <c r="A542" s="2" t="inlineStr">
         <is>
           <t>TC-541</t>
@@ -32221,7 +32223,7 @@
         </is>
       </c>
     </row>
-    <row r="543" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="543">
       <c r="A543" s="2" t="inlineStr">
         <is>
           <t>TC-542</t>
@@ -32276,7 +32278,7 @@
         </is>
       </c>
     </row>
-    <row r="544" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="544">
       <c r="A544" s="2" t="inlineStr">
         <is>
           <t>TC-543</t>
@@ -32332,7 +32334,7 @@
         </is>
       </c>
     </row>
-    <row r="545" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="545">
       <c r="A545" s="2" t="inlineStr">
         <is>
           <t>TC-544</t>
@@ -32389,7 +32391,7 @@
         </is>
       </c>
     </row>
-    <row r="546" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="546">
       <c r="A546" s="2" t="inlineStr">
         <is>
           <t>TC-545</t>
@@ -32445,7 +32447,7 @@
         </is>
       </c>
     </row>
-    <row r="547" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="547">
       <c r="A547" s="2" t="inlineStr">
         <is>
           <t>TC-546</t>
@@ -32500,7 +32502,7 @@
         </is>
       </c>
     </row>
-    <row r="548" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="548">
       <c r="A548" s="2" t="inlineStr">
         <is>
           <t>TC-547</t>
@@ -32557,7 +32559,7 @@
         </is>
       </c>
     </row>
-    <row r="549" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="549">
       <c r="A549" s="2" t="inlineStr">
         <is>
           <t>TC-548</t>
@@ -32612,7 +32614,7 @@
         </is>
       </c>
     </row>
-    <row r="550" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="550">
       <c r="A550" s="2" t="inlineStr">
         <is>
           <t>TC-549</t>
@@ -32669,7 +32671,7 @@
         </is>
       </c>
     </row>
-    <row r="551" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="551">
       <c r="A551" s="2" t="inlineStr">
         <is>
           <t>TC-550</t>
@@ -32728,7 +32730,7 @@
         </is>
       </c>
     </row>
-    <row r="552" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="552">
       <c r="A552" s="2" t="inlineStr">
         <is>
           <t>TC-551</t>
@@ -32784,7 +32786,7 @@
         </is>
       </c>
     </row>
-    <row r="553" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="553">
       <c r="A553" s="2" t="inlineStr">
         <is>
           <t>TC-552</t>
@@ -32844,7 +32846,7 @@
         </is>
       </c>
     </row>
-    <row r="554" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="554">
       <c r="A554" s="2" t="inlineStr">
         <is>
           <t>TC-553</t>
@@ -32904,7 +32906,7 @@
         </is>
       </c>
     </row>
-    <row r="555" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="555">
       <c r="A555" s="2" t="inlineStr">
         <is>
           <t>TC-554</t>
@@ -32964,7 +32966,7 @@
         </is>
       </c>
     </row>
-    <row r="556" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="556">
       <c r="A556" s="2" t="inlineStr">
         <is>
           <t>TC-555</t>
@@ -33024,7 +33026,7 @@
         </is>
       </c>
     </row>
-    <row r="557" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="557">
       <c r="A557" s="2" t="inlineStr">
         <is>
           <t>TC-556</t>
@@ -33083,7 +33085,7 @@
         </is>
       </c>
     </row>
-    <row r="558" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="558">
       <c r="A558" s="2" t="inlineStr">
         <is>
           <t>TC-557</t>
@@ -33142,7 +33144,7 @@
         </is>
       </c>
     </row>
-    <row r="559" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="559">
       <c r="A559" s="2" t="inlineStr">
         <is>
           <t>TC-558</t>
@@ -33202,7 +33204,7 @@
         </is>
       </c>
     </row>
-    <row r="560" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="560">
       <c r="A560" s="2" t="inlineStr">
         <is>
           <t>TC-559</t>
@@ -33262,7 +33264,7 @@
         </is>
       </c>
     </row>
-    <row r="561" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="561">
       <c r="A561" s="2" t="inlineStr">
         <is>
           <t>TC-560</t>
@@ -33331,7 +33333,7 @@
         </is>
       </c>
     </row>
-    <row r="562" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="562">
       <c r="A562" s="2" t="inlineStr">
         <is>
           <t>TC-561</t>
@@ -33390,7 +33392,7 @@
         </is>
       </c>
     </row>
-    <row r="563" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="563">
       <c r="A563" s="2" t="inlineStr">
         <is>
           <t>TC-562</t>
@@ -33449,7 +33451,7 @@
         </is>
       </c>
     </row>
-    <row r="564" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="564">
       <c r="A564" s="2" t="inlineStr">
         <is>
           <t>TC-563</t>
@@ -33505,7 +33507,7 @@
         </is>
       </c>
     </row>
-    <row r="565" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="565">
       <c r="A565" s="2" t="inlineStr">
         <is>
           <t>TC-564</t>
@@ -33561,7 +33563,7 @@
         </is>
       </c>
     </row>
-    <row r="566" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="566">
       <c r="A566" s="2" t="inlineStr">
         <is>
           <t>TC-565</t>
@@ -33621,7 +33623,7 @@
         </is>
       </c>
     </row>
-    <row r="567" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="567">
       <c r="A567" s="2" t="inlineStr">
         <is>
           <t>TC-566</t>
@@ -33678,7 +33680,7 @@
         </is>
       </c>
     </row>
-    <row r="568" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="568">
       <c r="A568" s="2" t="inlineStr">
         <is>
           <t>TC-567</t>
@@ -33736,7 +33738,7 @@
         </is>
       </c>
     </row>
-    <row r="569" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="569">
       <c r="A569" s="2" t="inlineStr">
         <is>
           <t>TC-568</t>
@@ -33792,7 +33794,7 @@
         </is>
       </c>
     </row>
-    <row r="570" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="570">
       <c r="A570" s="2" t="inlineStr">
         <is>
           <t>TC-569</t>
@@ -33849,7 +33851,7 @@
         </is>
       </c>
     </row>
-    <row r="571" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="571">
       <c r="A571" s="2" t="inlineStr">
         <is>
           <t>TC-570</t>
@@ -33909,7 +33911,7 @@
         </is>
       </c>
     </row>
-    <row r="572" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="572">
       <c r="A572" s="2" t="inlineStr">
         <is>
           <t>TC-571</t>
@@ -33966,7 +33968,7 @@
         </is>
       </c>
     </row>
-    <row r="573" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="573">
       <c r="A573" s="2" t="inlineStr">
         <is>
           <t>TC-572</t>
@@ -34023,7 +34025,7 @@
         </is>
       </c>
     </row>
-    <row r="574" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="574">
       <c r="A574" s="2" t="inlineStr">
         <is>
           <t>TC-573</t>
@@ -34078,7 +34080,7 @@
         </is>
       </c>
     </row>
-    <row r="575" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="575">
       <c r="A575" s="2" t="inlineStr">
         <is>
           <t>TC-574</t>
@@ -34139,7 +34141,7 @@
         </is>
       </c>
     </row>
-    <row r="576" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="576">
       <c r="A576" s="2" t="inlineStr">
         <is>
           <t>TC-575</t>
@@ -34194,7 +34196,7 @@
         </is>
       </c>
     </row>
-    <row r="577" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="577">
       <c r="A577" s="2" t="inlineStr">
         <is>
           <t>TC-576</t>
@@ -34254,7 +34256,7 @@
         </is>
       </c>
     </row>
-    <row r="578" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="578">
       <c r="A578" s="2" t="inlineStr">
         <is>
           <t>TC-577</t>
@@ -34310,7 +34312,7 @@
         </is>
       </c>
     </row>
-    <row r="579" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="579">
       <c r="A579" s="2" t="inlineStr">
         <is>
           <t>TC-578</t>
@@ -34367,7 +34369,7 @@
         </is>
       </c>
     </row>
-    <row r="580" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="580">
       <c r="A580" s="2" t="inlineStr">
         <is>
           <t>TC-579</t>
@@ -34422,7 +34424,7 @@
         </is>
       </c>
     </row>
-    <row r="581" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="581">
       <c r="A581" s="2" t="inlineStr">
         <is>
           <t>TC-580</t>
@@ -34478,7 +34480,7 @@
         </is>
       </c>
     </row>
-    <row r="582" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="582">
       <c r="A582" s="2" t="inlineStr">
         <is>
           <t>TC-581</t>
@@ -34533,7 +34535,7 @@
         </is>
       </c>
     </row>
-    <row r="583" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="583">
       <c r="A583" s="2" t="inlineStr">
         <is>
           <t>TC-582</t>
@@ -34593,7 +34595,7 @@
         </is>
       </c>
     </row>
-    <row r="584" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="584">
       <c r="A584" s="2" t="inlineStr">
         <is>
           <t>TC-583</t>
@@ -34650,7 +34652,7 @@
         </is>
       </c>
     </row>
-    <row r="585" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="585">
       <c r="A585" s="2" t="inlineStr">
         <is>
           <t>TC-584</t>
@@ -34711,7 +34713,7 @@
         </is>
       </c>
     </row>
-    <row r="586" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="586">
       <c r="A586" s="2" t="inlineStr">
         <is>
           <t>TC-585</t>
@@ -34772,7 +34774,7 @@
         </is>
       </c>
     </row>
-    <row r="587" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="587">
       <c r="A587" s="2" t="inlineStr">
         <is>
           <t>TC-586</t>
@@ -34828,7 +34830,7 @@
         </is>
       </c>
     </row>
-    <row r="588" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="588">
       <c r="A588" s="2" t="inlineStr">
         <is>
           <t>TC-587</t>
@@ -34884,7 +34886,7 @@
         </is>
       </c>
     </row>
-    <row r="589" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="589">
       <c r="A589" s="2" t="inlineStr">
         <is>
           <t>TC-588</t>
@@ -34940,7 +34942,7 @@
         </is>
       </c>
     </row>
-    <row r="590" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="590">
       <c r="A590" s="2" t="inlineStr">
         <is>
           <t>TC-589</t>
@@ -34996,7 +34998,7 @@
         </is>
       </c>
     </row>
-    <row r="591" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="591">
       <c r="A591" s="2" t="inlineStr">
         <is>
           <t>TC-590</t>
@@ -35052,7 +35054,7 @@
         </is>
       </c>
     </row>
-    <row r="592" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="592">
       <c r="A592" s="2" t="inlineStr">
         <is>
           <t>TC-591</t>
@@ -35108,7 +35110,7 @@
         </is>
       </c>
     </row>
-    <row r="593" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="593">
       <c r="A593" s="2" t="inlineStr">
         <is>
           <t>TC-592</t>
@@ -35169,7 +35171,7 @@
         </is>
       </c>
     </row>
-    <row r="594" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="594">
       <c r="A594" s="2" t="inlineStr">
         <is>
           <t>TC-593</t>
@@ -35228,7 +35230,7 @@
         </is>
       </c>
     </row>
-    <row r="595" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="595">
       <c r="A595" s="2" t="inlineStr">
         <is>
           <t>TC-594</t>
@@ -35287,7 +35289,7 @@
         </is>
       </c>
     </row>
-    <row r="596" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="596">
       <c r="A596" s="2" t="inlineStr">
         <is>
           <t>TC-595</t>
@@ -35346,7 +35348,7 @@
         </is>
       </c>
     </row>
-    <row r="597" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="597">
       <c r="A597" s="2" t="inlineStr">
         <is>
           <t>TC-596</t>
@@ -35404,7 +35406,7 @@
         </is>
       </c>
     </row>
-    <row r="598" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="598">
       <c r="A598" s="2" t="inlineStr">
         <is>
           <t>TC-597</t>
@@ -35463,7 +35465,7 @@
         </is>
       </c>
     </row>
-    <row r="599" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="599">
       <c r="A599" s="2" t="inlineStr">
         <is>
           <t>TC-598</t>
@@ -35521,7 +35523,7 @@
         </is>
       </c>
     </row>
-    <row r="600" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="600">
       <c r="A600" s="2" t="inlineStr">
         <is>
           <t>TC-599</t>
@@ -35579,7 +35581,7 @@
         </is>
       </c>
     </row>
-    <row r="601" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="601">
       <c r="A601" s="2" t="inlineStr">
         <is>
           <t>TC-600</t>
@@ -35636,7 +35638,7 @@
         </is>
       </c>
     </row>
-    <row r="602" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="602">
       <c r="A602" s="2" t="inlineStr">
         <is>
           <t>TC-601</t>
@@ -35697,7 +35699,7 @@
         </is>
       </c>
     </row>
-    <row r="603" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="603">
       <c r="A603" s="2" t="inlineStr">
         <is>
           <t>TC-602</t>
@@ -35754,7 +35756,7 @@
         </is>
       </c>
     </row>
-    <row r="604" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="604">
       <c r="A604" s="2" t="inlineStr">
         <is>
           <t>TC-603</t>
@@ -35811,7 +35813,7 @@
         </is>
       </c>
     </row>
-    <row r="605" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="605">
       <c r="A605" s="2" t="inlineStr">
         <is>
           <t>TC-604</t>
@@ -35870,7 +35872,7 @@
         </is>
       </c>
     </row>
-    <row r="606" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="606">
       <c r="A606" s="2" t="inlineStr">
         <is>
           <t>TC-605</t>
@@ -35928,7 +35930,7 @@
         </is>
       </c>
     </row>
-    <row r="607" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="607">
       <c r="A607" s="2" t="inlineStr">
         <is>
           <t>TC-606</t>
@@ -35987,7 +35989,7 @@
         </is>
       </c>
     </row>
-    <row r="608" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="608">
       <c r="A608" s="2" t="inlineStr">
         <is>
           <t>TC-607</t>
@@ -36046,7 +36048,7 @@
         </is>
       </c>
     </row>
-    <row r="609" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="609">
       <c r="A609" s="2" t="inlineStr">
         <is>
           <t>TC-608</t>
@@ -36105,7 +36107,7 @@
         </is>
       </c>
     </row>
-    <row r="610" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="610">
       <c r="A610" s="2" t="inlineStr">
         <is>
           <t>TC-609</t>
@@ -36163,7 +36165,7 @@
         </is>
       </c>
     </row>
-    <row r="611" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="611">
       <c r="A611" s="2" t="inlineStr">
         <is>
           <t>TC-610</t>
@@ -36221,7 +36223,7 @@
         </is>
       </c>
     </row>
-    <row r="612" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="612">
       <c r="A612" s="2" t="inlineStr">
         <is>
           <t>TC-611</t>
@@ -36280,7 +36282,7 @@
         </is>
       </c>
     </row>
-    <row r="613" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="613">
       <c r="A613" s="2" t="inlineStr">
         <is>
           <t>TC-612</t>
@@ -36338,7 +36340,7 @@
         </is>
       </c>
     </row>
-    <row r="614" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="614">
       <c r="A614" s="2" t="inlineStr">
         <is>
           <t>TC-613</t>
@@ -36397,7 +36399,7 @@
         </is>
       </c>
     </row>
-    <row r="615" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="615">
       <c r="A615" s="2" t="inlineStr">
         <is>
           <t>TC-614</t>
@@ -36455,7 +36457,7 @@
         </is>
       </c>
     </row>
-    <row r="616" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="616">
       <c r="A616" s="2" t="inlineStr">
         <is>
           <t>TC-615</t>
@@ -36514,7 +36516,7 @@
         </is>
       </c>
     </row>
-    <row r="617" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="617">
       <c r="A617" s="2" t="inlineStr">
         <is>
           <t>TC-616</t>
@@ -36572,7 +36574,7 @@
         </is>
       </c>
     </row>
-    <row r="618" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="618">
       <c r="A618" s="2" t="inlineStr">
         <is>
           <t>TC-617</t>
@@ -36631,7 +36633,7 @@
         </is>
       </c>
     </row>
-    <row r="619" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="619">
       <c r="A619" s="2" t="inlineStr">
         <is>
           <t>TC-618</t>
@@ -36689,7 +36691,7 @@
         </is>
       </c>
     </row>
-    <row r="620" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="620">
       <c r="A620" s="2" t="inlineStr">
         <is>
           <t>TC-619</t>
@@ -36748,7 +36750,7 @@
         </is>
       </c>
     </row>
-    <row r="621" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="621">
       <c r="A621" s="2" t="inlineStr">
         <is>
           <t>TC-620</t>
@@ -36806,7 +36808,7 @@
         </is>
       </c>
     </row>
-    <row r="622" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="622">
       <c r="A622" s="2" t="inlineStr">
         <is>
           <t>TC-621</t>
@@ -36865,7 +36867,7 @@
         </is>
       </c>
     </row>
-    <row r="623" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="623">
       <c r="A623" s="2" t="inlineStr">
         <is>
           <t>TC-622</t>
@@ -36923,7 +36925,7 @@
         </is>
       </c>
     </row>
-    <row r="624" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="624">
       <c r="A624" s="2" t="inlineStr">
         <is>
           <t>TC-623</t>
@@ -36982,7 +36984,7 @@
         </is>
       </c>
     </row>
-    <row r="625" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="625">
       <c r="A625" s="2" t="inlineStr">
         <is>
           <t>TC-624</t>
@@ -37040,7 +37042,7 @@
         </is>
       </c>
     </row>
-    <row r="626" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="626">
       <c r="A626" s="2" t="inlineStr">
         <is>
           <t>TC-625</t>
@@ -37099,7 +37101,7 @@
         </is>
       </c>
     </row>
-    <row r="627" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="627">
       <c r="A627" s="2" t="inlineStr">
         <is>
           <t>TC-626</t>
@@ -37157,7 +37159,7 @@
         </is>
       </c>
     </row>
-    <row r="628" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="628">
       <c r="A628" s="2" t="inlineStr">
         <is>
           <t>TC-627</t>
@@ -37216,7 +37218,7 @@
         </is>
       </c>
     </row>
-    <row r="629" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="629">
       <c r="A629" s="2" t="inlineStr">
         <is>
           <t>TC-628</t>
@@ -37274,7 +37276,7 @@
         </is>
       </c>
     </row>
-    <row r="630" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="630">
       <c r="A630" s="2" t="inlineStr">
         <is>
           <t>TC-629</t>
@@ -37333,7 +37335,7 @@
         </is>
       </c>
     </row>
-    <row r="631" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="631">
       <c r="A631" s="2" t="inlineStr">
         <is>
           <t>TC-630</t>
@@ -37391,7 +37393,7 @@
         </is>
       </c>
     </row>
-    <row r="632" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="632">
       <c r="A632" s="2" t="inlineStr">
         <is>
           <t>TC-631</t>
@@ -37450,7 +37452,7 @@
         </is>
       </c>
     </row>
-    <row r="633" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="633">
       <c r="A633" s="2" t="inlineStr">
         <is>
           <t>TC-632</t>
@@ -37508,7 +37510,7 @@
         </is>
       </c>
     </row>
-    <row r="634" ht="70" customHeight="1">
+    <row customHeight="1" ht="70" r="634">
       <c r="A634" s="2" t="inlineStr">
         <is>
           <t>TC-633</t>
@@ -37569,7 +37571,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>
 </file>
 
@@ -37582,9 +37584,9 @@
   <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col customWidth="1" max="1" min="1" width="30"/>
+    <col customWidth="1" max="2" min="2" width="12"/>
+    <col customWidth="1" max="3" min="3" width="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -37811,6 +37813,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>
 </file>
--- a/tests/e2e/testcases.xlsx
+++ b/tests/e2e/testcases.xlsx
@@ -2287,7 +2287,7 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>root+sysfs_writable，内核 CONFIG_HOTPLUG_CPU 支持；部分虚拟化/容器不支持核下线；cpu0 无则无法 offline 自动跳过</t>
+          <t>root+sysfs_writable，内核 CONFIG_HOTPLUG_CPU 支持；部分虚拟化/容器不支持核下线；cpu0 不可 offline 自动跳过</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -12074,7 +12074,7 @@
       </c>
       <c r="J198" s="3" t="inlineStr">
         <is>
-          <t>dcat query rNET_service_stop</t>
+          <t>dcat query rNET_service_stop --service=nginx</t>
         </is>
       </c>
       <c r="K198" s="3" t="inlineStr">
@@ -12786,7 +12786,7 @@
       </c>
       <c r="K210" s="3" t="inlineStr">
         <is>
-          <t>&gt;=1</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>
@@ -13058,7 +13058,7 @@
       </c>
       <c r="K215" s="3" t="inlineStr">
         <is>
-          <t>&gt;=1</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>

--- a/tests/e2e/testcases.xlsx
+++ b/tests/e2e/testcases.xlsx
@@ -11921,7 +11921,7 @@
       </c>
       <c r="C196" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNET_service_stop</t>
+          <t>已注入 rNET_service_stop --service=nginx</t>
         </is>
       </c>
       <c r="D196" s="3" t="inlineStr">
@@ -11980,7 +11980,7 @@
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNET_service_stop</t>
+          <t>已注入 rNET_service_stop --service=nginx</t>
         </is>
       </c>
       <c r="D197" s="3" t="inlineStr">
@@ -12038,7 +12038,7 @@
       </c>
       <c r="C198" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNET_service_stop</t>
+          <t>已注入 rNET_service_stop --service=nginx</t>
         </is>
       </c>
       <c r="D198" s="3" t="inlineStr">
@@ -12212,7 +12212,7 @@
       </c>
       <c r="C201" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNET_service_stop</t>
+          <t>已注入 rNET_service_stop --service=nginx</t>
         </is>
       </c>
       <c r="D201" s="3" t="inlineStr">
@@ -15641,7 +15641,7 @@
       </c>
       <c r="C260" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已注入 rNPU_arp_del</t>
+          <t>npu_hardware，已注入 rNPU_arp</t>
         </is>
       </c>
       <c r="D260" s="3" t="inlineStr">
@@ -15700,7 +15700,7 @@
       </c>
       <c r="C261" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，rNPU_arp_del 可注入</t>
+          <t>npu_hardware，rNPU_arp 可注入</t>
         </is>
       </c>
       <c r="D261" s="3" t="inlineStr">
@@ -15757,7 +15757,7 @@
       </c>
       <c r="C262" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，rNPU_arp_del 可注入</t>
+          <t>npu_hardware，rNPU_arp 可注入</t>
         </is>
       </c>
       <c r="D262" s="3" t="inlineStr">
@@ -15927,7 +15927,7 @@
       </c>
       <c r="C265" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已 clean rNPU_arp_del</t>
+          <t>npu_hardware，已 clean rNPU_arp</t>
         </is>
       </c>
       <c r="D265" s="3" t="inlineStr">
@@ -15969,7 +15969,7 @@
       </c>
       <c r="K265" s="3" t="inlineStr">
         <is>
-          <t>state_not_contains:rNPU_arp_del</t>
+          <t>state_not_contains:rNPU_arp</t>
         </is>
       </c>
     </row>
@@ -15986,7 +15986,7 @@
       </c>
       <c r="C266" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已注入 rNPU_arp_del</t>
+          <t>npu_hardware，已注入 rNPU_arp</t>
         </is>
       </c>
       <c r="D266" s="3" t="inlineStr">
@@ -16045,7 +16045,7 @@
       </c>
       <c r="C267" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，rNPU_arp_del 可注入</t>
+          <t>npu_hardware，rNPU_arp 可注入</t>
         </is>
       </c>
       <c r="D267" s="3" t="inlineStr">
@@ -16102,7 +16102,7 @@
       </c>
       <c r="C268" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已注入 rNPU_arp_del</t>
+          <t>npu_hardware，已注入 rNPU_arp</t>
         </is>
       </c>
       <c r="D268" s="3" t="inlineStr">
@@ -16160,7 +16160,7 @@
       </c>
       <c r="C269" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已注入 rNPU_arp_del</t>
+          <t>npu_hardware，已注入 rNPU_arp</t>
         </is>
       </c>
       <c r="D269" s="3" t="inlineStr">
@@ -16275,7 +16275,7 @@
       </c>
       <c r="C271" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，目标 ARP 条目已存在（已用 -arp -g 确认或先 inject rNPU_arp_poison 创建）；dev 用 hccn_tool 查出的 NPU 内部网口名</t>
+          <t>npu_hardware，目标 ARP 条目已存在（已用 -arp -g 确认或先 inject rNPU_arp 创建）；dev 用 hccn_tool 查出的 NPU 内部网口名</t>
         </is>
       </c>
       <c r="D271" s="3" t="inlineStr">
@@ -16332,7 +16332,7 @@
       </c>
       <c r="C272" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已注入 rNPU_arp_del</t>
+          <t>npu_hardware，已注入 rNPU_arp</t>
         </is>
       </c>
       <c r="D272" s="3" t="inlineStr">
@@ -16391,7 +16391,7 @@
       </c>
       <c r="C273" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已注入 rNPU_arp_del</t>
+          <t>npu_hardware，已注入 rNPU_arp</t>
         </is>
       </c>
       <c r="D273" s="3" t="inlineStr">
@@ -16449,7 +16449,7 @@
       </c>
       <c r="C274" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，rNPU_arp_del 可注入</t>
+          <t>npu_hardware，rNPU_arp 可注入</t>
         </is>
       </c>
       <c r="D274" s="3" t="inlineStr">
@@ -16508,7 +16508,7 @@
       </c>
       <c r="C275" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，rNPU_arp_del 可注入</t>
+          <t>npu_hardware，rNPU_arp 可注入</t>
         </is>
       </c>
       <c r="D275" s="3" t="inlineStr">
@@ -16571,7 +16571,7 @@
       </c>
       <c r="C276" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已 clean rNPU_arp_del</t>
+          <t>npu_hardware，已 clean rNPU_arp</t>
         </is>
       </c>
       <c r="D276" s="3" t="inlineStr">
@@ -16630,7 +16630,7 @@
       </c>
       <c r="C277" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已注入 rNPU_arp_poison</t>
+          <t>npu_hardware，已注入 rNPU_arp</t>
         </is>
       </c>
       <c r="D277" s="3" t="inlineStr">
@@ -16689,7 +16689,7 @@
       </c>
       <c r="C278" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，rNPU_arp_poison 可注入</t>
+          <t>npu_hardware，rNPU_arp 可注入</t>
         </is>
       </c>
       <c r="D278" s="3" t="inlineStr">
@@ -16746,7 +16746,7 @@
       </c>
       <c r="C279" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，rNPU_arp_poison 可注入</t>
+          <t>npu_hardware，rNPU_arp 可注入</t>
         </is>
       </c>
       <c r="D279" s="3" t="inlineStr">
@@ -16803,7 +16803,7 @@
       </c>
       <c r="C280" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已 clean rNPU_arp_poison</t>
+          <t>npu_hardware，已 clean rNPU_arp</t>
         </is>
       </c>
       <c r="D280" s="3" t="inlineStr">
@@ -16845,7 +16845,7 @@
       </c>
       <c r="K280" s="3" t="inlineStr">
         <is>
-          <t>state_not_contains:rNPU_arp_poison</t>
+          <t>state_not_contains:rNPU_arp</t>
         </is>
       </c>
     </row>
@@ -16862,7 +16862,7 @@
       </c>
       <c r="C281" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已注入 rNPU_arp_poison</t>
+          <t>npu_hardware，已注入 rNPU_arp</t>
         </is>
       </c>
       <c r="D281" s="3" t="inlineStr">
@@ -16917,7 +16917,7 @@
       </c>
       <c r="C282" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已注入 rNPU_arp_poison</t>
+          <t>npu_hardware，已注入 rNPU_arp</t>
         </is>
       </c>
       <c r="D282" s="3" t="inlineStr">
@@ -17036,7 +17036,7 @@
       </c>
       <c r="C284" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，rNPU_arp_poison 可注入</t>
+          <t>npu_hardware，rNPU_arp 可注入</t>
         </is>
       </c>
       <c r="D284" s="3" t="inlineStr">
@@ -17149,7 +17149,7 @@
       </c>
       <c r="C286" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已注入 rNPU_arp_poison</t>
+          <t>npu_hardware，已注入 rNPU_arp</t>
         </is>
       </c>
       <c r="D286" s="3" t="inlineStr">
@@ -17207,7 +17207,7 @@
       </c>
       <c r="C287" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已注入 rNPU_arp_poison</t>
+          <t>npu_hardware，已注入 rNPU_arp</t>
         </is>
       </c>
       <c r="D287" s="3" t="inlineStr">
@@ -17439,7 +17439,7 @@
       </c>
       <c r="C291" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已注入 rNPU_arp_poison</t>
+          <t>npu_hardware，已注入 rNPU_arp</t>
         </is>
       </c>
       <c r="D291" s="3" t="inlineStr">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C292" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已注入 rNPU_arp_poison</t>
+          <t>npu_hardware，已注入 rNPU_arp</t>
         </is>
       </c>
       <c r="D292" s="3" t="inlineStr">
@@ -17556,7 +17556,7 @@
       </c>
       <c r="C293" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，rNPU_arp_poison 可注入</t>
+          <t>npu_hardware，rNPU_arp 可注入</t>
         </is>
       </c>
       <c r="D293" s="3" t="inlineStr">
@@ -17615,7 +17615,7 @@
       </c>
       <c r="C294" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，rNPU_arp_poison 可注入</t>
+          <t>npu_hardware，rNPU_arp 可注入</t>
         </is>
       </c>
       <c r="D294" s="3" t="inlineStr">
@@ -17678,7 +17678,7 @@
       </c>
       <c r="C295" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已 clean rNPU_arp_poison</t>
+          <t>npu_hardware，已 clean rNPU_arp</t>
         </is>
       </c>
       <c r="D295" s="3" t="inlineStr">
@@ -21945,12 +21945,12 @@
       </c>
       <c r="C368" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已注入 rNPU_iproute_add</t>
+          <t>npu_hardware，已注入 rNPU_iproute</t>
         </is>
       </c>
       <c r="D368" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iproute_add --chip=2 --ip=10.30.50.0 --ip_mask=24 --via=10.30.12.254 --dev=eth2 --table=100 --force</t>
+          <t>1. dcat inject rNPU_iproute --chip=2 --ip=10.30.50.0 --ip_mask=24 --via=10.30.12.254 --dev=eth2 --table=100 --force</t>
         </is>
       </c>
       <c r="E368" s="3" t="inlineStr">
@@ -22004,12 +22004,12 @@
       </c>
       <c r="C369" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，rNPU_iproute_add 可注入</t>
+          <t>npu_hardware，rNPU_iproute 可注入</t>
         </is>
       </c>
       <c r="D369" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iproute_add --chip=-1 --ip=10.30.50.0 --ip_mask=24 --via=10.30.12.254 --dev=eth2 --table=100</t>
+          <t>1. dcat inject rNPU_iproute --chip=-1 --ip=10.30.50.0 --ip_mask=24 --via=10.30.12.254 --dev=eth2 --table=100</t>
         </is>
       </c>
       <c r="E369" s="3" t="inlineStr">
@@ -22061,12 +22061,12 @@
       </c>
       <c r="C370" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，rNPU_iproute_add 可注入</t>
+          <t>npu_hardware，rNPU_iproute 可注入</t>
         </is>
       </c>
       <c r="D370" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iproute_add --chip=8 --ip=10.30.50.0 --ip_mask=24 --via=10.30.12.254 --dev=eth2 --table=100</t>
+          <t>1. dcat inject rNPU_iproute --chip=8 --ip=10.30.50.0 --ip_mask=24 --via=10.30.12.254 --dev=eth2 --table=100</t>
         </is>
       </c>
       <c r="E370" s="3" t="inlineStr">
@@ -22118,12 +22118,12 @@
       </c>
       <c r="C371" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已 clean rNPU_iproute_add</t>
+          <t>npu_hardware，已 clean rNPU_iproute</t>
         </is>
       </c>
       <c r="D371" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_iproute_add --chip=2 --ip=10.30.50.0 --ip_mask=24 --via=10.30.12.254 --dev=eth2 --table=100
+          <t>1. dcat clean rNPU_iproute --chip=2 --ip=10.30.50.0 --ip_mask=24 --via=10.30.12.254 --dev=eth2 --table=100
 2. dcat query（无 uid）</t>
         </is>
       </c>
@@ -22160,7 +22160,7 @@
       </c>
       <c r="K371" s="3" t="inlineStr">
         <is>
-          <t>state_not_contains:rNPU_iproute_add</t>
+          <t>state_not_contains:rNPU_iproute</t>
         </is>
       </c>
     </row>
@@ -22177,12 +22177,12 @@
       </c>
       <c r="C372" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已注入 rNPU_iproute_add</t>
+          <t>npu_hardware，已注入 rNPU_iproute</t>
         </is>
       </c>
       <c r="D372" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_iproute_add --chip=2 --ip=10.30.50.0 --ip_mask=24 --via=10.30.12.254 --dev=eth2 --table=100
+          <t>1. dcat clean rNPU_iproute --chip=2 --ip=10.30.50.0 --ip_mask=24 --via=10.30.12.254 --dev=eth2 --table=100
 2. 检查恢复状态</t>
         </is>
       </c>
@@ -22241,7 +22241,7 @@
       </c>
       <c r="D373" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iproute_add --chip=2 --ip=10.30.50.0 --ip_mask=-1 --via=10.30.12.254 --dev=eth2 --table=100</t>
+          <t>1. dcat inject rNPU_iproute --chip=2 --ip=10.30.50.0 --ip_mask=-1 --via=10.30.12.254 --dev=eth2 --table=100</t>
         </is>
       </c>
       <c r="E373" s="3" t="inlineStr">
@@ -22293,12 +22293,12 @@
       </c>
       <c r="C374" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，rNPU_iproute_add 可注入</t>
+          <t>npu_hardware，rNPU_iproute 可注入</t>
         </is>
       </c>
       <c r="D374" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iproute_add --chip=2 --ip=10.30.50.0 --ip_mask=-1 --via=10.30.12.254 --dev=eth2 --table=100</t>
+          <t>1. dcat inject rNPU_iproute --chip=2 --ip=10.30.50.0 --ip_mask=-1 --via=10.30.12.254 --dev=eth2 --table=100</t>
         </is>
       </c>
       <c r="E374" s="3" t="inlineStr">
@@ -22355,7 +22355,7 @@
       </c>
       <c r="D375" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iproute_add --chip=2 --ip=10.30.50.0 --ip_mask=0 --via=10.30.12.254 --dev=eth2 --table=100</t>
+          <t>1. dcat inject rNPU_iproute --chip=2 --ip=10.30.50.0 --ip_mask=0 --via=10.30.12.254 --dev=eth2 --table=100</t>
         </is>
       </c>
       <c r="E375" s="3" t="inlineStr">
@@ -22412,7 +22412,7 @@
       </c>
       <c r="D376" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iproute_add --chip=2 --ip=10.30.50.1 --ip_mask=32 --via=10.30.12.254 --dev=eth2 --table=100</t>
+          <t>1. dcat inject rNPU_iproute --chip=2 --ip=10.30.50.1 --ip_mask=32 --via=10.30.12.254 --dev=eth2 --table=100</t>
         </is>
       </c>
       <c r="E376" s="3" t="inlineStr">
@@ -22469,7 +22469,7 @@
       </c>
       <c r="D377" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iproute_add --chip=2 --ip=10.30.50.0 --ip_mask=33 --via=10.30.12.254 --dev=eth2 --table=100</t>
+          <t>1. dcat inject rNPU_iproute --chip=2 --ip=10.30.50.0 --ip_mask=33 --via=10.30.12.254 --dev=eth2 --table=100</t>
         </is>
       </c>
       <c r="E377" s="3" t="inlineStr">
@@ -22521,12 +22521,12 @@
       </c>
       <c r="C378" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已注入 rNPU_iproute_add</t>
+          <t>npu_hardware，已注入 rNPU_iproute</t>
         </is>
       </c>
       <c r="D378" s="3" t="inlineStr">
         <is>
-          <t>1. dcat query rNPU_iproute_add（无参数）</t>
+          <t>1. dcat query rNPU_iproute（无参数）</t>
         </is>
       </c>
       <c r="E378" s="3" t="inlineStr">
@@ -22557,7 +22557,7 @@
       </c>
       <c r="J378" s="3" t="inlineStr">
         <is>
-          <t>dcat query rNPU_iproute_add</t>
+          <t>dcat query rNPU_iproute</t>
         </is>
       </c>
       <c r="K378" s="3" t="inlineStr">
@@ -22579,12 +22579,12 @@
       </c>
       <c r="C379" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已注入 rNPU_iproute_add</t>
+          <t>npu_hardware，已注入 rNPU_iproute</t>
         </is>
       </c>
       <c r="D379" s="3" t="inlineStr">
         <is>
-          <t>1. dcat query rNPU_iproute_add --chip=2 --ip=10.30.50.0 --ip_mask=24 --via=10.30.12.254 --dev=eth2 --table=100</t>
+          <t>1. dcat query rNPU_iproute --chip=2 --ip=10.30.50.0 --ip_mask=24 --via=10.30.12.254 --dev=eth2 --table=100</t>
         </is>
       </c>
       <c r="E379" s="3" t="inlineStr">
@@ -22615,7 +22615,7 @@
       </c>
       <c r="J379" s="3" t="inlineStr">
         <is>
-          <t>dcat query rNPU_iproute_add</t>
+          <t>dcat query rNPU_iproute</t>
         </is>
       </c>
       <c r="K379" s="3" t="inlineStr">
@@ -22637,13 +22637,13 @@
       </c>
       <c r="C380" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已注入 rNPU_iproute_add</t>
+          <t>npu_hardware，已注入 rNPU_iproute</t>
         </is>
       </c>
       <c r="D380" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iproute_add --chip=2 --ip=10.30.50.0 --ip_mask=24 --via=10.30.12.254 --dev=eth2 --table=100
-2. 再次 dcat inject rNPU_iproute_add --chip=2 --ip=10.30.50.0 --ip_mask=24 --via=10.30.12.254 --dev=eth2 --table=100</t>
+          <t>1. dcat inject rNPU_iproute --chip=2 --ip=10.30.50.0 --ip_mask=24 --via=10.30.12.254 --dev=eth2 --table=100
+2. 再次 dcat inject rNPU_iproute --chip=2 --ip=10.30.50.0 --ip_mask=24 --via=10.30.12.254 --dev=eth2 --table=100</t>
         </is>
       </c>
       <c r="E380" s="3" t="inlineStr">
@@ -22696,12 +22696,12 @@
       </c>
       <c r="C381" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已注入 rNPU_iproute_add</t>
+          <t>npu_hardware，已注入 rNPU_iproute</t>
         </is>
       </c>
       <c r="D381" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_iproute_add（无参）</t>
+          <t>1. dcat clean rNPU_iproute（无参）</t>
         </is>
       </c>
       <c r="E381" s="3" t="inlineStr">
@@ -22732,7 +22732,7 @@
       </c>
       <c r="J381" s="3" t="inlineStr">
         <is>
-          <t>dcat clean rNPU_iproute_add</t>
+          <t>dcat clean rNPU_iproute</t>
         </is>
       </c>
       <c r="K381" s="3" t="inlineStr">
@@ -22754,12 +22754,12 @@
       </c>
       <c r="C382" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，rNPU_iproute_add 可注入</t>
+          <t>npu_hardware，rNPU_iproute 可注入</t>
         </is>
       </c>
       <c r="D382" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iproute_add --chip=2 --ip=10.30.50.0 --ip_mask=24 --via=10.30.12.254 --dev=eth2 --table=100
+          <t>1. dcat inject rNPU_iproute --chip=2 --ip=10.30.50.0 --ip_mask=24 --via=10.30.12.254 --dev=eth2 --table=100
 2. 检查注入状态</t>
         </is>
       </c>
@@ -22818,9 +22818,9 @@
       </c>
       <c r="D383" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rNPU_iproute_add --chip=2 --ip=10.30.50.0 --ip_mask=24 --via=10.30.12.254 --dev=eth2 --table=100
-2. 执行 dcat query rNPU_iproute_add --chip=2
-3. 执行 dcat clean rNPU_iproute_add --chip=2 --ip=10.30.50.0 --ip_mask=24 --table=100</t>
+          <t>1. 执行 dcat inject rNPU_iproute --chip=2 --ip=10.30.50.0 --ip_mask=24 --via=10.30.12.254 --dev=eth2 --table=100
+2. 执行 dcat query rNPU_iproute --chip=2
+3. 执行 dcat clean rNPU_iproute --chip=2 --ip=10.30.50.0 --ip_mask=24 --table=100</t>
         </is>
       </c>
       <c r="E383" s="3" t="inlineStr">
@@ -22874,15 +22874,15 @@
       </c>
       <c r="C384" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，rNPU_iproute_add 可注入</t>
+          <t>npu_hardware，rNPU_iproute 可注入</t>
         </is>
       </c>
       <c r="D384" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iproute_add --chip=2 --ip=10.30.50.0 --ip_mask=24 --via=10.30.12.254 --dev=eth2 --table=100
-2. dcat query rNPU_iproute_add
-3. dcat clean rNPU_iproute_add --chip=2 --ip=10.30.50.0 --ip_mask=24 --via=10.30.12.254 --dev=eth2 --table=100
-4. dcat query rNPU_iproute_add</t>
+          <t>1. dcat inject rNPU_iproute --chip=2 --ip=10.30.50.0 --ip_mask=24 --via=10.30.12.254 --dev=eth2 --table=100
+2. dcat query rNPU_iproute
+3. dcat clean rNPU_iproute --chip=2 --ip=10.30.50.0 --ip_mask=24 --via=10.30.12.254 --dev=eth2 --table=100
+4. dcat query rNPU_iproute</t>
         </is>
       </c>
       <c r="E384" s="3" t="inlineStr">
@@ -22915,7 +22915,7 @@
       </c>
       <c r="J384" s="3" t="inlineStr">
         <is>
-          <t>dcat query rNPU_iproute_add</t>
+          <t>dcat query rNPU_iproute</t>
         </is>
       </c>
       <c r="K384" s="3" t="inlineStr">
@@ -22937,13 +22937,13 @@
       </c>
       <c r="C385" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已 clean rNPU_iproute_add</t>
+          <t>npu_hardware，已 clean rNPU_iproute</t>
         </is>
       </c>
       <c r="D385" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_iproute_add --chip=2 --ip=10.30.50.0 --ip_mask=24 --via=10.30.12.254 --dev=eth2 --table=100
-2. 再次 dcat clean rNPU_iproute_add --chip=2 --ip=10.30.50.0 --ip_mask=24 --via=10.30.12.254 --dev=eth2 --table=100</t>
+          <t>1. dcat clean rNPU_iproute --chip=2 --ip=10.30.50.0 --ip_mask=24 --via=10.30.12.254 --dev=eth2 --table=100
+2. 再次 dcat clean rNPU_iproute --chip=2 --ip=10.30.50.0 --ip_mask=24 --via=10.30.12.254 --dev=eth2 --table=100</t>
         </is>
       </c>
       <c r="E385" s="3" t="inlineStr">
@@ -22974,7 +22974,7 @@
       </c>
       <c r="J385" s="3" t="inlineStr">
         <is>
-          <t>dcat clean rNPU_iproute_add</t>
+          <t>dcat clean rNPU_iproute</t>
         </is>
       </c>
       <c r="K385" s="3" t="inlineStr">
@@ -22996,12 +22996,12 @@
       </c>
       <c r="C386" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已注入 rNPU_iproute_del</t>
+          <t>npu_hardware，已注入 rNPU_iproute</t>
         </is>
       </c>
       <c r="D386" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iproute_del --chip=2 --ip=10.30.51.0 --ip_mask=24 --table=100 --force</t>
+          <t>1. dcat inject rNPU_iproute --chip=2 --ip=10.30.51.0 --ip_mask=24 --table=100 --force</t>
         </is>
       </c>
       <c r="E386" s="3" t="inlineStr">
@@ -23055,12 +23055,12 @@
       </c>
       <c r="C387" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，rNPU_iproute_del 可注入</t>
+          <t>npu_hardware，rNPU_iproute 可注入</t>
         </is>
       </c>
       <c r="D387" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iproute_del --chip=-1 --ip=10.30.51.0 --ip_mask=24 --table=100</t>
+          <t>1. dcat inject rNPU_iproute --chip=-1 --ip=10.30.51.0 --ip_mask=24 --table=100</t>
         </is>
       </c>
       <c r="E387" s="3" t="inlineStr">
@@ -23112,12 +23112,12 @@
       </c>
       <c r="C388" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，rNPU_iproute_del 可注入</t>
+          <t>npu_hardware，rNPU_iproute 可注入</t>
         </is>
       </c>
       <c r="D388" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iproute_del --chip=8 --ip=10.30.51.0 --ip_mask=24 --table=100</t>
+          <t>1. dcat inject rNPU_iproute --chip=8 --ip=10.30.51.0 --ip_mask=24 --table=100</t>
         </is>
       </c>
       <c r="E388" s="3" t="inlineStr">
@@ -23169,12 +23169,12 @@
       </c>
       <c r="C389" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已 clean rNPU_iproute_del</t>
+          <t>npu_hardware，已 clean rNPU_iproute</t>
         </is>
       </c>
       <c r="D389" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_iproute_del --chip=2 --ip=10.30.51.0 --ip_mask=24 --table=100
+          <t>1. dcat clean rNPU_iproute --chip=2 --ip=10.30.51.0 --ip_mask=24 --table=100
 2. dcat query（无 uid）</t>
         </is>
       </c>
@@ -23211,7 +23211,7 @@
       </c>
       <c r="K389" s="3" t="inlineStr">
         <is>
-          <t>state_not_contains:rNPU_iproute_del</t>
+          <t>state_not_contains:rNPU_iproute</t>
         </is>
       </c>
     </row>
@@ -23228,12 +23228,12 @@
       </c>
       <c r="C390" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已注入 rNPU_iproute_del</t>
+          <t>npu_hardware，已注入 rNPU_iproute</t>
         </is>
       </c>
       <c r="D390" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_iproute_del --chip=2 --ip=10.30.51.0 --ip_mask=24 --table=100
+          <t>1. dcat clean rNPU_iproute --chip=2 --ip=10.30.51.0 --ip_mask=24 --table=100
 2. 检查恢复状态</t>
         </is>
       </c>
@@ -23287,12 +23287,12 @@
       </c>
       <c r="C391" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，rNPU_iproute_del 可注入</t>
+          <t>npu_hardware，rNPU_iproute 可注入</t>
         </is>
       </c>
       <c r="D391" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iproute_del --chip=2 --ip=10.30.51.0 --ip_mask=-1 --table=100</t>
+          <t>1. dcat inject rNPU_iproute --chip=2 --ip=10.30.51.0 --ip_mask=-1 --table=100</t>
         </is>
       </c>
       <c r="E391" s="3" t="inlineStr">
@@ -23344,12 +23344,12 @@
       </c>
       <c r="C392" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已注入 rNPU_iproute_del</t>
+          <t>npu_hardware，已注入 rNPU_iproute</t>
         </is>
       </c>
       <c r="D392" s="3" t="inlineStr">
         <is>
-          <t>1. dcat query rNPU_iproute_del（无参数）</t>
+          <t>1. dcat query rNPU_iproute（无参数）</t>
         </is>
       </c>
       <c r="E392" s="3" t="inlineStr">
@@ -23380,7 +23380,7 @@
       </c>
       <c r="J392" s="3" t="inlineStr">
         <is>
-          <t>dcat query rNPU_iproute_del</t>
+          <t>dcat query rNPU_iproute</t>
         </is>
       </c>
       <c r="K392" s="3" t="inlineStr">
@@ -23402,12 +23402,12 @@
       </c>
       <c r="C393" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已注入 rNPU_iproute_del</t>
+          <t>npu_hardware，已注入 rNPU_iproute</t>
         </is>
       </c>
       <c r="D393" s="3" t="inlineStr">
         <is>
-          <t>1. dcat query rNPU_iproute_del --chip=2 --ip=10.30.51.0 --ip_mask=24 --table=100</t>
+          <t>1. dcat query rNPU_iproute --chip=2 --ip=10.30.51.0 --ip_mask=24 --table=100</t>
         </is>
       </c>
       <c r="E393" s="3" t="inlineStr">
@@ -23438,7 +23438,7 @@
       </c>
       <c r="J393" s="3" t="inlineStr">
         <is>
-          <t>dcat query rNPU_iproute_del</t>
+          <t>dcat query rNPU_iproute</t>
         </is>
       </c>
       <c r="K393" s="3" t="inlineStr">
@@ -23460,14 +23460,14 @@
       </c>
       <c r="C394" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，目标 ip_route 已存在（先 rNPU_iproute_add 创建）</t>
+          <t>npu_hardware，目标 ip_route 已存在（先 rNPU_iproute 创建）</t>
         </is>
       </c>
       <c r="D394" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rNPU_iproute_del --chip=2 --ip=10.30.51.0 --ip_mask=24 --table=100
+          <t>1. 执行 dcat inject rNPU_iproute --chip=2 --ip=10.30.51.0 --ip_mask=24 --table=100
 2. 检查未先创建时的报错
-3. 执行 dcat clean rNPU_iproute_del --chip=2 --ip=10.30.51.0 --ip_mask=24 --table=100</t>
+3. 执行 dcat clean rNPU_iproute --chip=2 --ip=10.30.51.0 --ip_mask=24 --table=100</t>
         </is>
       </c>
       <c r="E394" s="3" t="inlineStr">
@@ -23521,13 +23521,13 @@
       </c>
       <c r="C395" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已注入 rNPU_iproute_del</t>
+          <t>npu_hardware，已注入 rNPU_iproute</t>
         </is>
       </c>
       <c r="D395" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iproute_del --chip=2 --ip=10.30.51.0 --ip_mask=24 --table=100
-2. 再次 dcat inject rNPU_iproute_del --chip=2 --ip=10.30.51.0 --ip_mask=24 --table=100</t>
+          <t>1. dcat inject rNPU_iproute --chip=2 --ip=10.30.51.0 --ip_mask=24 --table=100
+2. 再次 dcat inject rNPU_iproute --chip=2 --ip=10.30.51.0 --ip_mask=24 --table=100</t>
         </is>
       </c>
       <c r="E395" s="3" t="inlineStr">
@@ -23580,12 +23580,12 @@
       </c>
       <c r="C396" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已注入 rNPU_iproute_del</t>
+          <t>npu_hardware，已注入 rNPU_iproute</t>
         </is>
       </c>
       <c r="D396" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_iproute_del（无参）</t>
+          <t>1. dcat clean rNPU_iproute（无参）</t>
         </is>
       </c>
       <c r="E396" s="3" t="inlineStr">
@@ -23616,7 +23616,7 @@
       </c>
       <c r="J396" s="3" t="inlineStr">
         <is>
-          <t>dcat clean rNPU_iproute_del</t>
+          <t>dcat clean rNPU_iproute</t>
         </is>
       </c>
       <c r="K396" s="3" t="inlineStr">
@@ -23638,12 +23638,12 @@
       </c>
       <c r="C397" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，rNPU_iproute_del 可注入</t>
+          <t>npu_hardware，rNPU_iproute 可注入</t>
         </is>
       </c>
       <c r="D397" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iproute_del --chip=2 --ip=10.30.51.0 --ip_mask=24 --table=100
+          <t>1. dcat inject rNPU_iproute --chip=2 --ip=10.30.51.0 --ip_mask=24 --table=100
 2. 检查注入状态</t>
         </is>
       </c>
@@ -23697,15 +23697,15 @@
       </c>
       <c r="C398" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，rNPU_iproute_del 可注入</t>
+          <t>npu_hardware，rNPU_iproute 可注入</t>
         </is>
       </c>
       <c r="D398" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iproute_del --chip=2 --ip=10.30.51.0 --ip_mask=24 --table=100
-2. dcat query rNPU_iproute_del
-3. dcat clean rNPU_iproute_del --chip=2 --ip=10.30.51.0 --ip_mask=24 --table=100
-4. dcat query rNPU_iproute_del</t>
+          <t>1. dcat inject rNPU_iproute --chip=2 --ip=10.30.51.0 --ip_mask=24 --table=100
+2. dcat query rNPU_iproute
+3. dcat clean rNPU_iproute --chip=2 --ip=10.30.51.0 --ip_mask=24 --table=100
+4. dcat query rNPU_iproute</t>
         </is>
       </c>
       <c r="E398" s="3" t="inlineStr">
@@ -23738,7 +23738,7 @@
       </c>
       <c r="J398" s="3" t="inlineStr">
         <is>
-          <t>dcat query rNPU_iproute_del</t>
+          <t>dcat query rNPU_iproute</t>
         </is>
       </c>
       <c r="K398" s="3" t="inlineStr">
@@ -23760,13 +23760,13 @@
       </c>
       <c r="C399" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已 clean rNPU_iproute_del</t>
+          <t>npu_hardware，已 clean rNPU_iproute</t>
         </is>
       </c>
       <c r="D399" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_iproute_del --chip=2 --ip=10.30.51.0 --ip_mask=24 --table=100
-2. 再次 dcat clean rNPU_iproute_del --chip=2 --ip=10.30.51.0 --ip_mask=24 --table=100</t>
+          <t>1. dcat clean rNPU_iproute --chip=2 --ip=10.30.51.0 --ip_mask=24 --table=100
+2. 再次 dcat clean rNPU_iproute --chip=2 --ip=10.30.51.0 --ip_mask=24 --table=100</t>
         </is>
       </c>
       <c r="E399" s="3" t="inlineStr">
@@ -23797,7 +23797,7 @@
       </c>
       <c r="J399" s="3" t="inlineStr">
         <is>
-          <t>dcat clean rNPU_iproute_del</t>
+          <t>dcat clean rNPU_iproute</t>
         </is>
       </c>
       <c r="K399" s="3" t="inlineStr">
@@ -23819,12 +23819,12 @@
       </c>
       <c r="C400" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已注入 rNPU_iprule_add</t>
+          <t>npu_hardware，已注入 rNPU_iprule</t>
         </is>
       </c>
       <c r="D400" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iprule_add --chip=2 --dir=from --ip=10.30.12.210 --table=150 --force</t>
+          <t>1. dcat inject rNPU_iprule --chip=2 --dir=from --ip=10.30.12.210 --table=150 --force</t>
         </is>
       </c>
       <c r="E400" s="3" t="inlineStr">
@@ -23878,12 +23878,12 @@
       </c>
       <c r="C401" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，rNPU_iprule_add 可注入</t>
+          <t>npu_hardware，rNPU_iprule 可注入</t>
         </is>
       </c>
       <c r="D401" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iprule_add --chip=-1 --dir=from --ip=10.30.12.210 --table=150</t>
+          <t>1. dcat inject rNPU_iprule --chip=-1 --dir=from --ip=10.30.12.210 --table=150</t>
         </is>
       </c>
       <c r="E401" s="3" t="inlineStr">
@@ -23935,12 +23935,12 @@
       </c>
       <c r="C402" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，rNPU_iprule_add 可注入</t>
+          <t>npu_hardware，rNPU_iprule 可注入</t>
         </is>
       </c>
       <c r="D402" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iprule_add --chip=8 --dir=from --ip=10.30.12.210 --table=150</t>
+          <t>1. dcat inject rNPU_iprule --chip=8 --dir=from --ip=10.30.12.210 --table=150</t>
         </is>
       </c>
       <c r="E402" s="3" t="inlineStr">
@@ -23992,12 +23992,12 @@
       </c>
       <c r="C403" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已 clean rNPU_iprule_add</t>
+          <t>npu_hardware，已 clean rNPU_iprule</t>
         </is>
       </c>
       <c r="D403" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_iprule_add --chip=2 --dir=from --ip=10.30.12.210 --table=150
+          <t>1. dcat clean rNPU_iprule --chip=2 --dir=from --ip=10.30.12.210 --table=150
 2. dcat query（无 uid）</t>
         </is>
       </c>
@@ -24034,7 +24034,7 @@
       </c>
       <c r="K403" s="3" t="inlineStr">
         <is>
-          <t>state_not_contains:rNPU_iprule_add</t>
+          <t>state_not_contains:rNPU_iprule</t>
         </is>
       </c>
     </row>
@@ -24051,12 +24051,12 @@
       </c>
       <c r="C404" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已注入 rNPU_iprule_add</t>
+          <t>npu_hardware，已注入 rNPU_iprule</t>
         </is>
       </c>
       <c r="D404" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_iprule_add --chip=2 --dir=from --ip=10.30.12.210 --table=150
+          <t>1. dcat clean rNPU_iprule --chip=2 --dir=from --ip=10.30.12.210 --table=150
 2. 检查恢复状态</t>
         </is>
       </c>
@@ -24110,12 +24110,12 @@
       </c>
       <c r="C405" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已注入 rNPU_iprule_add</t>
+          <t>npu_hardware，已注入 rNPU_iprule</t>
         </is>
       </c>
       <c r="D405" s="3" t="inlineStr">
         <is>
-          <t>1. dcat query rNPU_iprule_add（无参数）</t>
+          <t>1. dcat query rNPU_iprule（无参数）</t>
         </is>
       </c>
       <c r="E405" s="3" t="inlineStr">
@@ -24146,7 +24146,7 @@
       </c>
       <c r="J405" s="3" t="inlineStr">
         <is>
-          <t>dcat query rNPU_iprule_add</t>
+          <t>dcat query rNPU_iprule</t>
         </is>
       </c>
       <c r="K405" s="3" t="inlineStr">
@@ -24168,12 +24168,12 @@
       </c>
       <c r="C406" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已注入 rNPU_iprule_add</t>
+          <t>npu_hardware，已注入 rNPU_iprule</t>
         </is>
       </c>
       <c r="D406" s="3" t="inlineStr">
         <is>
-          <t>1. dcat query rNPU_iprule_add --chip=2 --dir=from --ip=10.30.12.210 --table=150</t>
+          <t>1. dcat query rNPU_iprule --chip=2 --dir=from --ip=10.30.12.210 --table=150</t>
         </is>
       </c>
       <c r="E406" s="3" t="inlineStr">
@@ -24204,7 +24204,7 @@
       </c>
       <c r="J406" s="3" t="inlineStr">
         <is>
-          <t>dcat query rNPU_iprule_add</t>
+          <t>dcat query rNPU_iprule</t>
         </is>
       </c>
       <c r="K406" s="3" t="inlineStr">
@@ -24231,7 +24231,7 @@
       </c>
       <c r="D407" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iprule_add --chip=2 --dir=from --ip=10.30.12.210 --table=-1</t>
+          <t>1. dcat inject rNPU_iprule --chip=2 --dir=from --ip=10.30.12.210 --table=-1</t>
         </is>
       </c>
       <c r="E407" s="3" t="inlineStr">
@@ -24283,12 +24283,12 @@
       </c>
       <c r="C408" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，rNPU_iprule_add 可注入</t>
+          <t>npu_hardware，rNPU_iprule 可注入</t>
         </is>
       </c>
       <c r="D408" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iprule_add --chip=2 --dir=from --ip=10.30.12.210 --table=-1</t>
+          <t>1. dcat inject rNPU_iprule --chip=2 --dir=from --ip=10.30.12.210 --table=-1</t>
         </is>
       </c>
       <c r="E408" s="3" t="inlineStr">
@@ -24345,7 +24345,7 @@
       </c>
       <c r="D409" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iprule_add --chip=2 --dir=from --ip=10.30.12.210 --table=0</t>
+          <t>1. dcat inject rNPU_iprule --chip=2 --dir=from --ip=10.30.12.210 --table=0</t>
         </is>
       </c>
       <c r="E409" s="3" t="inlineStr">
@@ -24402,7 +24402,7 @@
       </c>
       <c r="D410" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iprule_add --chip=2 --dir=from --ip=10.30.12.210 --table=255</t>
+          <t>1. dcat inject rNPU_iprule --chip=2 --dir=from --ip=10.30.12.210 --table=255</t>
         </is>
       </c>
       <c r="E410" s="3" t="inlineStr">
@@ -24459,7 +24459,7 @@
       </c>
       <c r="D411" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iprule_add --chip=2 --dir=from --ip=10.30.12.210 --table=256</t>
+          <t>1. dcat inject rNPU_iprule --chip=2 --dir=from --ip=10.30.12.210 --table=256</t>
         </is>
       </c>
       <c r="E411" s="3" t="inlineStr">
@@ -24511,13 +24511,13 @@
       </c>
       <c r="C412" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已注入 rNPU_iprule_add</t>
+          <t>npu_hardware，已注入 rNPU_iprule</t>
         </is>
       </c>
       <c r="D412" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iprule_add --chip=2 --dir=from --ip=10.30.12.210 --table=150
-2. 再次 dcat inject rNPU_iprule_add --chip=2 --dir=from --ip=10.30.12.210 --table=150</t>
+          <t>1. dcat inject rNPU_iprule --chip=2 --dir=from --ip=10.30.12.210 --table=150
+2. 再次 dcat inject rNPU_iprule --chip=2 --dir=from --ip=10.30.12.210 --table=150</t>
         </is>
       </c>
       <c r="E412" s="3" t="inlineStr">
@@ -24570,12 +24570,12 @@
       </c>
       <c r="C413" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已注入 rNPU_iprule_add</t>
+          <t>npu_hardware，已注入 rNPU_iprule</t>
         </is>
       </c>
       <c r="D413" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_iprule_add（无参）</t>
+          <t>1. dcat clean rNPU_iprule（无参）</t>
         </is>
       </c>
       <c r="E413" s="3" t="inlineStr">
@@ -24606,7 +24606,7 @@
       </c>
       <c r="J413" s="3" t="inlineStr">
         <is>
-          <t>dcat clean rNPU_iprule_add</t>
+          <t>dcat clean rNPU_iprule</t>
         </is>
       </c>
       <c r="K413" s="3" t="inlineStr">
@@ -24628,12 +24628,12 @@
       </c>
       <c r="C414" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，rNPU_iprule_add 可注入</t>
+          <t>npu_hardware，rNPU_iprule 可注入</t>
         </is>
       </c>
       <c r="D414" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iprule_add --chip=2 --dir=from --ip=10.30.12.210 --table=150
+          <t>1. dcat inject rNPU_iprule --chip=2 --dir=from --ip=10.30.12.210 --table=150
 2. 检查注入状态</t>
         </is>
       </c>
@@ -24692,9 +24692,9 @@
       </c>
       <c r="D415" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rNPU_iprule_add --chip=2 --dir=from --ip=10.30.12.210 --table=150
-2. 执行 dcat query rNPU_iprule_add --chip=2
-3. 执行 dcat clean rNPU_iprule_add --chip=2 --dir=from --ip=10.30.12.210 --table=150</t>
+          <t>1. 执行 dcat inject rNPU_iprule --chip=2 --dir=from --ip=10.30.12.210 --table=150
+2. 执行 dcat query rNPU_iprule --chip=2
+3. 执行 dcat clean rNPU_iprule --chip=2 --dir=from --ip=10.30.12.210 --table=150</t>
         </is>
       </c>
       <c r="E415" s="3" t="inlineStr">
@@ -24748,15 +24748,15 @@
       </c>
       <c r="C416" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，rNPU_iprule_add 可注入</t>
+          <t>npu_hardware，rNPU_iprule 可注入</t>
         </is>
       </c>
       <c r="D416" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iprule_add --chip=2 --dir=from --ip=10.30.12.210 --table=150
-2. dcat query rNPU_iprule_add
-3. dcat clean rNPU_iprule_add --chip=2 --dir=from --ip=10.30.12.210 --table=150
-4. dcat query rNPU_iprule_add</t>
+          <t>1. dcat inject rNPU_iprule --chip=2 --dir=from --ip=10.30.12.210 --table=150
+2. dcat query rNPU_iprule
+3. dcat clean rNPU_iprule --chip=2 --dir=from --ip=10.30.12.210 --table=150
+4. dcat query rNPU_iprule</t>
         </is>
       </c>
       <c r="E416" s="3" t="inlineStr">
@@ -24789,7 +24789,7 @@
       </c>
       <c r="J416" s="3" t="inlineStr">
         <is>
-          <t>dcat query rNPU_iprule_add</t>
+          <t>dcat query rNPU_iprule</t>
         </is>
       </c>
       <c r="K416" s="3" t="inlineStr">
@@ -24811,13 +24811,13 @@
       </c>
       <c r="C417" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已 clean rNPU_iprule_add</t>
+          <t>npu_hardware，已 clean rNPU_iprule</t>
         </is>
       </c>
       <c r="D417" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_iprule_add --chip=2 --dir=from --ip=10.30.12.210 --table=150
-2. 再次 dcat clean rNPU_iprule_add --chip=2 --dir=from --ip=10.30.12.210 --table=150</t>
+          <t>1. dcat clean rNPU_iprule --chip=2 --dir=from --ip=10.30.12.210 --table=150
+2. 再次 dcat clean rNPU_iprule --chip=2 --dir=from --ip=10.30.12.210 --table=150</t>
         </is>
       </c>
       <c r="E417" s="3" t="inlineStr">
@@ -24848,7 +24848,7 @@
       </c>
       <c r="J417" s="3" t="inlineStr">
         <is>
-          <t>dcat clean rNPU_iprule_add</t>
+          <t>dcat clean rNPU_iprule</t>
         </is>
       </c>
       <c r="K417" s="3" t="inlineStr">
@@ -24870,12 +24870,12 @@
       </c>
       <c r="C418" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已注入 rNPU_iprule_del</t>
+          <t>npu_hardware，已注入 rNPU_iprule</t>
         </is>
       </c>
       <c r="D418" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iprule_del --chip=2 --dir=from --ip=10.30.12.211 --force</t>
+          <t>1. dcat inject rNPU_iprule --chip=2 --dir=from --ip=10.30.12.211 --force</t>
         </is>
       </c>
       <c r="E418" s="3" t="inlineStr">
@@ -24929,12 +24929,12 @@
       </c>
       <c r="C419" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，rNPU_iprule_del 可注入</t>
+          <t>npu_hardware，rNPU_iprule 可注入</t>
         </is>
       </c>
       <c r="D419" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iprule_del --chip=-1 --dir=from --ip=10.30.12.211</t>
+          <t>1. dcat inject rNPU_iprule --chip=-1 --dir=from --ip=10.30.12.211</t>
         </is>
       </c>
       <c r="E419" s="3" t="inlineStr">
@@ -24986,12 +24986,12 @@
       </c>
       <c r="C420" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，rNPU_iprule_del 可注入</t>
+          <t>npu_hardware，rNPU_iprule 可注入</t>
         </is>
       </c>
       <c r="D420" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iprule_del --chip=8 --dir=from --ip=10.30.12.211</t>
+          <t>1. dcat inject rNPU_iprule --chip=8 --dir=from --ip=10.30.12.211</t>
         </is>
       </c>
       <c r="E420" s="3" t="inlineStr">
@@ -25043,12 +25043,12 @@
       </c>
       <c r="C421" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已 clean rNPU_iprule_del</t>
+          <t>npu_hardware，已 clean rNPU_iprule</t>
         </is>
       </c>
       <c r="D421" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_iprule_del --chip=2 --dir=from --ip=10.30.12.211
+          <t>1. dcat clean rNPU_iprule --chip=2 --dir=from --ip=10.30.12.211
 2. dcat query（无 uid）</t>
         </is>
       </c>
@@ -25085,7 +25085,7 @@
       </c>
       <c r="K421" s="3" t="inlineStr">
         <is>
-          <t>state_not_contains:rNPU_iprule_del</t>
+          <t>state_not_contains:rNPU_iprule</t>
         </is>
       </c>
     </row>
@@ -25102,12 +25102,12 @@
       </c>
       <c r="C422" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已注入 rNPU_iprule_del</t>
+          <t>npu_hardware，已注入 rNPU_iprule</t>
         </is>
       </c>
       <c r="D422" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_iprule_del --chip=2 --dir=from --ip=10.30.12.211
+          <t>1. dcat clean rNPU_iprule --chip=2 --dir=from --ip=10.30.12.211
 2. 检查恢复状态</t>
         </is>
       </c>
@@ -25161,12 +25161,12 @@
       </c>
       <c r="C423" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，rNPU_iprule_del 可注入</t>
+          <t>npu_hardware，rNPU_iprule 可注入</t>
         </is>
       </c>
       <c r="D423" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iprule_del --chip=2 --dir=invalid --ip=10.30.12.211</t>
+          <t>1. dcat inject rNPU_iprule --chip=2 --dir=invalid --ip=10.30.12.211</t>
         </is>
       </c>
       <c r="E423" s="3" t="inlineStr">
@@ -25218,12 +25218,12 @@
       </c>
       <c r="C424" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已注入 rNPU_iprule_del</t>
+          <t>npu_hardware，已注入 rNPU_iprule</t>
         </is>
       </c>
       <c r="D424" s="3" t="inlineStr">
         <is>
-          <t>1. dcat query rNPU_iprule_del（无参数）</t>
+          <t>1. dcat query rNPU_iprule（无参数）</t>
         </is>
       </c>
       <c r="E424" s="3" t="inlineStr">
@@ -25254,7 +25254,7 @@
       </c>
       <c r="J424" s="3" t="inlineStr">
         <is>
-          <t>dcat query rNPU_iprule_del</t>
+          <t>dcat query rNPU_iprule</t>
         </is>
       </c>
       <c r="K424" s="3" t="inlineStr">
@@ -25276,12 +25276,12 @@
       </c>
       <c r="C425" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已注入 rNPU_iprule_del</t>
+          <t>npu_hardware，已注入 rNPU_iprule</t>
         </is>
       </c>
       <c r="D425" s="3" t="inlineStr">
         <is>
-          <t>1. dcat query rNPU_iprule_del --chip=2 --dir=from --ip=10.30.12.211</t>
+          <t>1. dcat query rNPU_iprule --chip=2 --dir=from --ip=10.30.12.211</t>
         </is>
       </c>
       <c r="E425" s="3" t="inlineStr">
@@ -25312,7 +25312,7 @@
       </c>
       <c r="J425" s="3" t="inlineStr">
         <is>
-          <t>dcat query rNPU_iprule_del</t>
+          <t>dcat query rNPU_iprule</t>
         </is>
       </c>
       <c r="K425" s="3" t="inlineStr">
@@ -25334,14 +25334,14 @@
       </c>
       <c r="C426" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，目标 ip rule 已存在（先 rNPU_iprule_add 创建）</t>
+          <t>npu_hardware，目标 ip rule 已存在（先 rNPU_iprule 创建）</t>
         </is>
       </c>
       <c r="D426" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rNPU_iprule_del --chip=2 --dir=from --ip=10.30.12.211
+          <t>1. 执行 dcat inject rNPU_iprule --chip=2 --dir=from --ip=10.30.12.211
 2. 检查未先创建时的报错
-3. 执行 dcat clean rNPU_iprule_del --chip=2 --dir=from --ip=10.30.12.211</t>
+3. 执行 dcat clean rNPU_iprule --chip=2 --dir=from --ip=10.30.12.211</t>
         </is>
       </c>
       <c r="E426" s="3" t="inlineStr">
@@ -25395,13 +25395,13 @@
       </c>
       <c r="C427" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已注入 rNPU_iprule_del</t>
+          <t>npu_hardware，已注入 rNPU_iprule</t>
         </is>
       </c>
       <c r="D427" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iprule_del --chip=2 --dir=from --ip=10.30.12.211
-2. 再次 dcat inject rNPU_iprule_del --chip=2 --dir=from --ip=10.30.12.211</t>
+          <t>1. dcat inject rNPU_iprule --chip=2 --dir=from --ip=10.30.12.211
+2. 再次 dcat inject rNPU_iprule --chip=2 --dir=from --ip=10.30.12.211</t>
         </is>
       </c>
       <c r="E427" s="3" t="inlineStr">
@@ -25454,12 +25454,12 @@
       </c>
       <c r="C428" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已注入 rNPU_iprule_del</t>
+          <t>npu_hardware，已注入 rNPU_iprule</t>
         </is>
       </c>
       <c r="D428" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_iprule_del（无参）</t>
+          <t>1. dcat clean rNPU_iprule（无参）</t>
         </is>
       </c>
       <c r="E428" s="3" t="inlineStr">
@@ -25490,7 +25490,7 @@
       </c>
       <c r="J428" s="3" t="inlineStr">
         <is>
-          <t>dcat clean rNPU_iprule_del</t>
+          <t>dcat clean rNPU_iprule</t>
         </is>
       </c>
       <c r="K428" s="3" t="inlineStr">
@@ -25512,12 +25512,12 @@
       </c>
       <c r="C429" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，rNPU_iprule_del 可注入</t>
+          <t>npu_hardware，rNPU_iprule 可注入</t>
         </is>
       </c>
       <c r="D429" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iprule_del --chip=2 --dir=from --ip=10.30.12.211
+          <t>1. dcat inject rNPU_iprule --chip=2 --dir=from --ip=10.30.12.211
 2. 检查注入状态</t>
         </is>
       </c>
@@ -25571,15 +25571,15 @@
       </c>
       <c r="C430" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，rNPU_iprule_del 可注入</t>
+          <t>npu_hardware，rNPU_iprule 可注入</t>
         </is>
       </c>
       <c r="D430" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iprule_del --chip=2 --dir=from --ip=10.30.12.211
-2. dcat query rNPU_iprule_del
-3. dcat clean rNPU_iprule_del --chip=2 --dir=from --ip=10.30.12.211
-4. dcat query rNPU_iprule_del</t>
+          <t>1. dcat inject rNPU_iprule --chip=2 --dir=from --ip=10.30.12.211
+2. dcat query rNPU_iprule
+3. dcat clean rNPU_iprule --chip=2 --dir=from --ip=10.30.12.211
+4. dcat query rNPU_iprule</t>
         </is>
       </c>
       <c r="E430" s="3" t="inlineStr">
@@ -25612,7 +25612,7 @@
       </c>
       <c r="J430" s="3" t="inlineStr">
         <is>
-          <t>dcat query rNPU_iprule_del</t>
+          <t>dcat query rNPU_iprule</t>
         </is>
       </c>
       <c r="K430" s="3" t="inlineStr">
@@ -25634,13 +25634,13 @@
       </c>
       <c r="C431" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已 clean rNPU_iprule_del</t>
+          <t>npu_hardware，已 clean rNPU_iprule</t>
         </is>
       </c>
       <c r="D431" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_iprule_del --chip=2 --dir=from --ip=10.30.12.211
-2. 再次 dcat clean rNPU_iprule_del --chip=2 --dir=from --ip=10.30.12.211</t>
+          <t>1. dcat clean rNPU_iprule --chip=2 --dir=from --ip=10.30.12.211
+2. 再次 dcat clean rNPU_iprule --chip=2 --dir=from --ip=10.30.12.211</t>
         </is>
       </c>
       <c r="E431" s="3" t="inlineStr">
@@ -25671,7 +25671,7 @@
       </c>
       <c r="J431" s="3" t="inlineStr">
         <is>
-          <t>dcat clean rNPU_iprule_del</t>
+          <t>dcat clean rNPU_iprule</t>
         </is>
       </c>
       <c r="K431" s="3" t="inlineStr">
@@ -29046,12 +29046,12 @@
       </c>
       <c r="C489" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已注入 rNPU_route_add</t>
+          <t>npu_hardware，已注入 rNPU_route</t>
         </is>
       </c>
       <c r="D489" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_route_add --chip=2 --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254 --force</t>
+          <t>1. dcat inject rNPU_route --chip=2 --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254 --force</t>
         </is>
       </c>
       <c r="E489" s="3" t="inlineStr">
@@ -29105,12 +29105,12 @@
       </c>
       <c r="C490" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，rNPU_route_add 可注入</t>
+          <t>npu_hardware，rNPU_route 可注入</t>
         </is>
       </c>
       <c r="D490" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_route_add --chip=2 --address=invalid --netmask=255.255.255.0 --gateway=10.30.12.254</t>
+          <t>1. dcat inject rNPU_route --chip=2 --address=invalid --netmask=255.255.255.0 --gateway=10.30.12.254</t>
         </is>
       </c>
       <c r="E490" s="3" t="inlineStr">
@@ -29162,12 +29162,12 @@
       </c>
       <c r="C491" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，rNPU_route_add 可注入</t>
+          <t>npu_hardware，rNPU_route 可注入</t>
         </is>
       </c>
       <c r="D491" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_route_add --chip=-1 --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254</t>
+          <t>1. dcat inject rNPU_route --chip=-1 --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254</t>
         </is>
       </c>
       <c r="E491" s="3" t="inlineStr">
@@ -29219,12 +29219,12 @@
       </c>
       <c r="C492" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，rNPU_route_add 可注入</t>
+          <t>npu_hardware，rNPU_route 可注入</t>
         </is>
       </c>
       <c r="D492" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_route_add --chip=8 --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254</t>
+          <t>1. dcat inject rNPU_route --chip=8 --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254</t>
         </is>
       </c>
       <c r="E492" s="3" t="inlineStr">
@@ -29276,12 +29276,12 @@
       </c>
       <c r="C493" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已 clean rNPU_route_add</t>
+          <t>npu_hardware，已 clean rNPU_route</t>
         </is>
       </c>
       <c r="D493" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_route_add --chip=2 --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254
+          <t>1. dcat clean rNPU_route --chip=2 --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254
 2. dcat query（无 uid）</t>
         </is>
       </c>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="K493" s="3" t="inlineStr">
         <is>
-          <t>state_not_contains:rNPU_route_add</t>
+          <t>state_not_contains:rNPU_route</t>
         </is>
       </c>
     </row>
@@ -29335,12 +29335,12 @@
       </c>
       <c r="C494" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已注入 rNPU_route_add</t>
+          <t>npu_hardware，已注入 rNPU_route</t>
         </is>
       </c>
       <c r="D494" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_route_add --chip=2 --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254
+          <t>1. dcat clean rNPU_route --chip=2 --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254
 2. 检查恢复状态</t>
         </is>
       </c>
@@ -29394,12 +29394,12 @@
       </c>
       <c r="C495" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已注入 rNPU_route_add</t>
+          <t>npu_hardware，已注入 rNPU_route</t>
         </is>
       </c>
       <c r="D495" s="3" t="inlineStr">
         <is>
-          <t>1. dcat query rNPU_route_add（无参数）</t>
+          <t>1. dcat query rNPU_route（无参数）</t>
         </is>
       </c>
       <c r="E495" s="3" t="inlineStr">
@@ -29430,7 +29430,7 @@
       </c>
       <c r="J495" s="3" t="inlineStr">
         <is>
-          <t>dcat query rNPU_route_add</t>
+          <t>dcat query rNPU_route</t>
         </is>
       </c>
       <c r="K495" s="3" t="inlineStr">
@@ -29452,12 +29452,12 @@
       </c>
       <c r="C496" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已注入 rNPU_route_add</t>
+          <t>npu_hardware，已注入 rNPU_route</t>
         </is>
       </c>
       <c r="D496" s="3" t="inlineStr">
         <is>
-          <t>1. dcat query rNPU_route_add --chip=2 --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254</t>
+          <t>1. dcat query rNPU_route --chip=2 --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254</t>
         </is>
       </c>
       <c r="E496" s="3" t="inlineStr">
@@ -29488,7 +29488,7 @@
       </c>
       <c r="J496" s="3" t="inlineStr">
         <is>
-          <t>dcat query rNPU_route_add</t>
+          <t>dcat query rNPU_route</t>
         </is>
       </c>
       <c r="K496" s="3" t="inlineStr">
@@ -29510,13 +29510,13 @@
       </c>
       <c r="C497" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已注入 rNPU_route_add</t>
+          <t>npu_hardware，已注入 rNPU_route</t>
         </is>
       </c>
       <c r="D497" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_route_add --chip=2 --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254
-2. 再次 dcat inject rNPU_route_add --chip=2 --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254</t>
+          <t>1. dcat inject rNPU_route --chip=2 --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254
+2. 再次 dcat inject rNPU_route --chip=2 --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254</t>
         </is>
       </c>
       <c r="E497" s="3" t="inlineStr">
@@ -29569,12 +29569,12 @@
       </c>
       <c r="C498" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已注入 rNPU_route_add</t>
+          <t>npu_hardware，已注入 rNPU_route</t>
         </is>
       </c>
       <c r="D498" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_route_add（无参）</t>
+          <t>1. dcat clean rNPU_route（无参）</t>
         </is>
       </c>
       <c r="E498" s="3" t="inlineStr">
@@ -29605,7 +29605,7 @@
       </c>
       <c r="J498" s="3" t="inlineStr">
         <is>
-          <t>dcat clean rNPU_route_add</t>
+          <t>dcat clean rNPU_route</t>
         </is>
       </c>
       <c r="K498" s="3" t="inlineStr">
@@ -29627,12 +29627,12 @@
       </c>
       <c r="C499" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，rNPU_route_add 可注入</t>
+          <t>npu_hardware，rNPU_route 可注入</t>
         </is>
       </c>
       <c r="D499" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_route_add --chip=2 --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254
+          <t>1. dcat inject rNPU_route --chip=2 --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254
 2. 检查注入状态</t>
         </is>
       </c>
@@ -29691,9 +29691,9 @@
       </c>
       <c r="D500" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rNPU_route_add --chip=2 --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254
-2. 执行 dcat query rNPU_route_add --chip=2
-3. 执行 dcat clean rNPU_route_add --chip=2 --address=10.30.40.0 --netmask=255.255.255.0</t>
+          <t>1. 执行 dcat inject rNPU_route --chip=2 --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254
+2. 执行 dcat query rNPU_route --chip=2
+3. 执行 dcat clean rNPU_route --chip=2 --address=10.30.40.0 --netmask=255.255.255.0</t>
         </is>
       </c>
       <c r="E500" s="3" t="inlineStr">
@@ -29747,15 +29747,15 @@
       </c>
       <c r="C501" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，rNPU_route_add 可注入</t>
+          <t>npu_hardware，rNPU_route 可注入</t>
         </is>
       </c>
       <c r="D501" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_route_add --chip=2 --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254
-2. dcat query rNPU_route_add
-3. dcat clean rNPU_route_add --chip=2 --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254
-4. dcat query rNPU_route_add</t>
+          <t>1. dcat inject rNPU_route --chip=2 --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254
+2. dcat query rNPU_route
+3. dcat clean rNPU_route --chip=2 --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254
+4. dcat query rNPU_route</t>
         </is>
       </c>
       <c r="E501" s="3" t="inlineStr">
@@ -29788,7 +29788,7 @@
       </c>
       <c r="J501" s="3" t="inlineStr">
         <is>
-          <t>dcat query rNPU_route_add</t>
+          <t>dcat query rNPU_route</t>
         </is>
       </c>
       <c r="K501" s="3" t="inlineStr">
@@ -29810,13 +29810,13 @@
       </c>
       <c r="C502" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已 clean rNPU_route_add</t>
+          <t>npu_hardware，已 clean rNPU_route</t>
         </is>
       </c>
       <c r="D502" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_route_add --chip=2 --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254
-2. 再次 dcat clean rNPU_route_add --chip=2 --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254</t>
+          <t>1. dcat clean rNPU_route --chip=2 --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254
+2. 再次 dcat clean rNPU_route --chip=2 --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254</t>
         </is>
       </c>
       <c r="E502" s="3" t="inlineStr">
@@ -29847,7 +29847,7 @@
       </c>
       <c r="J502" s="3" t="inlineStr">
         <is>
-          <t>dcat clean rNPU_route_add</t>
+          <t>dcat clean rNPU_route</t>
         </is>
       </c>
       <c r="K502" s="3" t="inlineStr">
@@ -29869,12 +29869,12 @@
       </c>
       <c r="C503" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已注入 rNPU_route_del</t>
+          <t>npu_hardware，已注入 rNPU_route</t>
         </is>
       </c>
       <c r="D503" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_route_del --chip=2 --address=10.30.41.0 --netmask=255.255.255.0 --force</t>
+          <t>1. dcat inject rNPU_route --chip=2 --address=10.30.41.0 --netmask=255.255.255.0 --force</t>
         </is>
       </c>
       <c r="E503" s="3" t="inlineStr">
@@ -29928,12 +29928,12 @@
       </c>
       <c r="C504" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，rNPU_route_del 可注入</t>
+          <t>npu_hardware，rNPU_route 可注入</t>
         </is>
       </c>
       <c r="D504" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_route_del --chip=2 --address=invalid --netmask=255.255.255.0</t>
+          <t>1. dcat inject rNPU_route --chip=2 --address=invalid --netmask=255.255.255.0</t>
         </is>
       </c>
       <c r="E504" s="3" t="inlineStr">
@@ -29985,12 +29985,12 @@
       </c>
       <c r="C505" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，rNPU_route_del 可注入</t>
+          <t>npu_hardware，rNPU_route 可注入</t>
         </is>
       </c>
       <c r="D505" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_route_del --chip=-1 --address=10.30.41.0 --netmask=255.255.255.0</t>
+          <t>1. dcat inject rNPU_route --chip=-1 --address=10.30.41.0 --netmask=255.255.255.0</t>
         </is>
       </c>
       <c r="E505" s="3" t="inlineStr">
@@ -30042,12 +30042,12 @@
       </c>
       <c r="C506" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，rNPU_route_del 可注入</t>
+          <t>npu_hardware，rNPU_route 可注入</t>
         </is>
       </c>
       <c r="D506" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_route_del --chip=8 --address=10.30.41.0 --netmask=255.255.255.0</t>
+          <t>1. dcat inject rNPU_route --chip=8 --address=10.30.41.0 --netmask=255.255.255.0</t>
         </is>
       </c>
       <c r="E506" s="3" t="inlineStr">
@@ -30099,12 +30099,12 @@
       </c>
       <c r="C507" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已 clean rNPU_route_del</t>
+          <t>npu_hardware，已 clean rNPU_route</t>
         </is>
       </c>
       <c r="D507" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_route_del --chip=2 --address=10.30.41.0 --netmask=255.255.255.0
+          <t>1. dcat clean rNPU_route --chip=2 --address=10.30.41.0 --netmask=255.255.255.0
 2. dcat query（无 uid）</t>
         </is>
       </c>
@@ -30141,7 +30141,7 @@
       </c>
       <c r="K507" s="3" t="inlineStr">
         <is>
-          <t>state_not_contains:rNPU_route_del</t>
+          <t>state_not_contains:rNPU_route</t>
         </is>
       </c>
     </row>
@@ -30158,12 +30158,12 @@
       </c>
       <c r="C508" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已注入 rNPU_route_del</t>
+          <t>npu_hardware，已注入 rNPU_route</t>
         </is>
       </c>
       <c r="D508" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_route_del --chip=2 --address=10.30.41.0 --netmask=255.255.255.0
+          <t>1. dcat clean rNPU_route --chip=2 --address=10.30.41.0 --netmask=255.255.255.0
 2. 检查恢复状态</t>
         </is>
       </c>
@@ -30217,12 +30217,12 @@
       </c>
       <c r="C509" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已注入 rNPU_route_del</t>
+          <t>npu_hardware，已注入 rNPU_route</t>
         </is>
       </c>
       <c r="D509" s="3" t="inlineStr">
         <is>
-          <t>1. dcat query rNPU_route_del（无参数）</t>
+          <t>1. dcat query rNPU_route（无参数）</t>
         </is>
       </c>
       <c r="E509" s="3" t="inlineStr">
@@ -30253,7 +30253,7 @@
       </c>
       <c r="J509" s="3" t="inlineStr">
         <is>
-          <t>dcat query rNPU_route_del</t>
+          <t>dcat query rNPU_route</t>
         </is>
       </c>
       <c r="K509" s="3" t="inlineStr">
@@ -30275,12 +30275,12 @@
       </c>
       <c r="C510" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已注入 rNPU_route_del</t>
+          <t>npu_hardware，已注入 rNPU_route</t>
         </is>
       </c>
       <c r="D510" s="3" t="inlineStr">
         <is>
-          <t>1. dcat query rNPU_route_del --chip=2 --address=10.30.41.0 --netmask=255.255.255.0</t>
+          <t>1. dcat query rNPU_route --chip=2 --address=10.30.41.0 --netmask=255.255.255.0</t>
         </is>
       </c>
       <c r="E510" s="3" t="inlineStr">
@@ -30311,7 +30311,7 @@
       </c>
       <c r="J510" s="3" t="inlineStr">
         <is>
-          <t>dcat query rNPU_route_del</t>
+          <t>dcat query rNPU_route</t>
         </is>
       </c>
       <c r="K510" s="3" t="inlineStr">
@@ -30333,14 +30333,14 @@
       </c>
       <c r="C511" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，目标路由已存在（先 rNPU_route_add 创建）</t>
+          <t>npu_hardware，目标路由已存在（先 rNPU_route 创建）</t>
         </is>
       </c>
       <c r="D511" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rNPU_route_del --chip=2 --address=10.30.41.0 --netmask=255.255.255.0
+          <t>1. 执行 dcat inject rNPU_route --chip=2 --address=10.30.41.0 --netmask=255.255.255.0
 2. 检查未先创建时的报错
-3. 执行 dcat clean rNPU_route_del --chip=2 --address=10.30.41.0 --netmask=255.255.255.0</t>
+3. 执行 dcat clean rNPU_route --chip=2 --address=10.30.41.0 --netmask=255.255.255.0</t>
         </is>
       </c>
       <c r="E511" s="3" t="inlineStr">
@@ -30394,13 +30394,13 @@
       </c>
       <c r="C512" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已注入 rNPU_route_del</t>
+          <t>npu_hardware，已注入 rNPU_route</t>
         </is>
       </c>
       <c r="D512" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_route_del --chip=2 --address=10.30.41.0 --netmask=255.255.255.0
-2. 再次 dcat inject rNPU_route_del --chip=2 --address=10.30.41.0 --netmask=255.255.255.0</t>
+          <t>1. dcat inject rNPU_route --chip=2 --address=10.30.41.0 --netmask=255.255.255.0
+2. 再次 dcat inject rNPU_route --chip=2 --address=10.30.41.0 --netmask=255.255.255.0</t>
         </is>
       </c>
       <c r="E512" s="3" t="inlineStr">
@@ -30453,12 +30453,12 @@
       </c>
       <c r="C513" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已注入 rNPU_route_del</t>
+          <t>npu_hardware，已注入 rNPU_route</t>
         </is>
       </c>
       <c r="D513" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_route_del（无参）</t>
+          <t>1. dcat clean rNPU_route（无参）</t>
         </is>
       </c>
       <c r="E513" s="3" t="inlineStr">
@@ -30489,7 +30489,7 @@
       </c>
       <c r="J513" s="3" t="inlineStr">
         <is>
-          <t>dcat clean rNPU_route_del</t>
+          <t>dcat clean rNPU_route</t>
         </is>
       </c>
       <c r="K513" s="3" t="inlineStr">
@@ -30511,12 +30511,12 @@
       </c>
       <c r="C514" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，rNPU_route_del 可注入</t>
+          <t>npu_hardware，rNPU_route 可注入</t>
         </is>
       </c>
       <c r="D514" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_route_del --chip=2 --address=10.30.41.0 --netmask=255.255.255.0
+          <t>1. dcat inject rNPU_route --chip=2 --address=10.30.41.0 --netmask=255.255.255.0
 2. 检查注入状态</t>
         </is>
       </c>
@@ -30570,15 +30570,15 @@
       </c>
       <c r="C515" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，rNPU_route_del 可注入</t>
+          <t>npu_hardware，rNPU_route 可注入</t>
         </is>
       </c>
       <c r="D515" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_route_del --chip=2 --address=10.30.41.0 --netmask=255.255.255.0
-2. dcat query rNPU_route_del
-3. dcat clean rNPU_route_del --chip=2 --address=10.30.41.0 --netmask=255.255.255.0
-4. dcat query rNPU_route_del</t>
+          <t>1. dcat inject rNPU_route --chip=2 --address=10.30.41.0 --netmask=255.255.255.0
+2. dcat query rNPU_route
+3. dcat clean rNPU_route --chip=2 --address=10.30.41.0 --netmask=255.255.255.0
+4. dcat query rNPU_route</t>
         </is>
       </c>
       <c r="E515" s="3" t="inlineStr">
@@ -30611,7 +30611,7 @@
       </c>
       <c r="J515" s="3" t="inlineStr">
         <is>
-          <t>dcat query rNPU_route_del</t>
+          <t>dcat query rNPU_route</t>
         </is>
       </c>
       <c r="K515" s="3" t="inlineStr">
@@ -30633,13 +30633,13 @@
       </c>
       <c r="C516" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已 clean rNPU_route_del</t>
+          <t>npu_hardware，已 clean rNPU_route</t>
         </is>
       </c>
       <c r="D516" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_route_del --chip=2 --address=10.30.41.0 --netmask=255.255.255.0
-2. 再次 dcat clean rNPU_route_del --chip=2 --address=10.30.41.0 --netmask=255.255.255.0</t>
+          <t>1. dcat clean rNPU_route --chip=2 --address=10.30.41.0 --netmask=255.255.255.0
+2. 再次 dcat clean rNPU_route --chip=2 --address=10.30.41.0 --netmask=255.255.255.0</t>
         </is>
       </c>
       <c r="E516" s="3" t="inlineStr">
@@ -30670,7 +30670,7 @@
       </c>
       <c r="J516" s="3" t="inlineStr">
         <is>
-          <t>dcat clean rNPU_route_del</t>
+          <t>dcat clean rNPU_route</t>
         </is>
       </c>
       <c r="K516" s="3" t="inlineStr">
@@ -35419,7 +35419,7 @@
       </c>
       <c r="C598" s="3" t="inlineStr">
         <is>
-          <t>已注入 --cores=0,1</t>
+          <t>已注入 rCPU_overload --cores=0,1</t>
         </is>
       </c>
       <c r="D598" s="3" t="inlineStr">
@@ -36061,7 +36061,7 @@
       </c>
       <c r="C609" s="3" t="inlineStr">
         <is>
-          <t>已注入 device=/data</t>
+          <t>已注入 rDISK_write_overload --device=/tmp</t>
         </is>
       </c>
       <c r="D609" s="3" t="inlineStr">
@@ -36236,7 +36236,7 @@
       </c>
       <c r="C612" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNET_loss</t>
+          <t>已注入 rNET_loss --iface=dcat-e2e0 --loss_pct=10</t>
         </is>
       </c>
       <c r="D612" s="3" t="inlineStr">
@@ -36353,7 +36353,7 @@
       </c>
       <c r="C614" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNET_delay</t>
+          <t>已注入 rNET_delay --iface=dcat-e2e0 --delay_ms=50</t>
         </is>
       </c>
       <c r="D614" s="3" t="inlineStr">
@@ -36470,7 +36470,7 @@
       </c>
       <c r="C616" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNET_reorder</t>
+          <t>已注入 rNET_reorder --iface=dcat-e2e0 --reorder_pct=10</t>
         </is>
       </c>
       <c r="D616" s="3" t="inlineStr">
@@ -36587,7 +36587,7 @@
       </c>
       <c r="C618" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNET_jitter</t>
+          <t>已注入 rNET_jitter --iface=dcat-e2e0 --delay_ms=30 --jitter_ms=10</t>
         </is>
       </c>
       <c r="D618" s="3" t="inlineStr">
@@ -36704,7 +36704,7 @@
       </c>
       <c r="C620" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNET_bw_limit</t>
+          <t>已注入 rNET_bw_limit --iface=dcat-e2e0 --rate_kbps=1024</t>
         </is>
       </c>
       <c r="D620" s="3" t="inlineStr">
@@ -36821,7 +36821,7 @@
       </c>
       <c r="C622" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNET_degrade</t>
+          <t>已注入 rNET_degrade --iface=dcat-e2e0 --speed_mbps=10</t>
         </is>
       </c>
       <c r="D622" s="3" t="inlineStr">
@@ -37348,7 +37348,7 @@
       </c>
       <c r="C631" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已注入 rNPU_arp_poison</t>
+          <t>npu_hardware，已注入 rNPU_arp</t>
         </is>
       </c>
       <c r="D631" s="3" t="inlineStr">
@@ -37406,7 +37406,7 @@
       </c>
       <c r="C632" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已注入 rNPU_arp_poison</t>
+          <t>npu_hardware，已注入 rNPU_arp</t>
         </is>
       </c>
       <c r="D632" s="3" t="inlineStr">
@@ -37465,12 +37465,12 @@
       </c>
       <c r="C633" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已注入 rNPU_route_add</t>
+          <t>npu_hardware，已注入 rNPU_route</t>
         </is>
       </c>
       <c r="D633" s="3" t="inlineStr">
         <is>
-          <t>1. dcat query rNPU_route_add --chip=2 --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254</t>
+          <t>1. dcat query rNPU_route --chip=2 --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254</t>
         </is>
       </c>
       <c r="E633" s="3" t="inlineStr">
@@ -37501,7 +37501,7 @@
       </c>
       <c r="J633" s="3" t="inlineStr">
         <is>
-          <t>dcat query rNPU_route_add</t>
+          <t>dcat query rNPU_route</t>
         </is>
       </c>
       <c r="K633" s="3" t="inlineStr">
@@ -37523,12 +37523,12 @@
       </c>
       <c r="C634" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已注入 rNPU_route_add</t>
+          <t>npu_hardware，已注入 rNPU_route</t>
         </is>
       </c>
       <c r="D634" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_route_add --chip=2 --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254
+          <t>1. dcat clean rNPU_route --chip=2 --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254
 2. hccn_tool -i 2 -route -g</t>
         </is>
       </c>

--- a/tests/e2e/testcases.xlsx
+++ b/tests/e2e/testcases.xlsx
@@ -9078,7 +9078,7 @@
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>eth0 与 eth1 均已注入 rNET_loss</t>
+          <t>eth0 与 eth1 均已注入 rNET_loss --iface=eth0 --loss_pct=8</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
@@ -9700,7 +9700,7 @@
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>eth0 已注入 rNET_loss（存在 root netem qdisc）</t>
+          <t>eth0 已注入 rNET_loss --iface=eth0 --loss_pct=8（存在 root netem qdisc）</t>
         </is>
       </c>
       <c r="D158" s="3" t="inlineStr">
@@ -11921,7 +11921,7 @@
       </c>
       <c r="C196" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNET_service_stop --service=nginx</t>
+          <t>已注入 rNET_service_stop</t>
         </is>
       </c>
       <c r="D196" s="3" t="inlineStr">
@@ -11980,7 +11980,7 @@
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNET_service_stop --service=nginx</t>
+          <t>已注入 rNET_service_stop</t>
         </is>
       </c>
       <c r="D197" s="3" t="inlineStr">
@@ -12038,7 +12038,7 @@
       </c>
       <c r="C198" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNET_service_stop --service=nginx</t>
+          <t>已注入 rNET_service_stop</t>
         </is>
       </c>
       <c r="D198" s="3" t="inlineStr">
@@ -12212,7 +12212,7 @@
       </c>
       <c r="C201" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNET_service_stop --service=nginx</t>
+          <t>已注入 rNET_service_stop</t>
         </is>
       </c>
       <c r="D201" s="3" t="inlineStr">

--- a/tests/e2e/testcases.xlsx
+++ b/tests/e2e/testcases.xlsx
@@ -35752,7 +35752,7 @@
       </c>
       <c r="K603" s="3" t="inlineStr">
         <is>
-          <t>contains:pid</t>
+          <t>contains:PID</t>
         </is>
       </c>
     </row>

--- a/tests/e2e/testcases.xlsx
+++ b/tests/e2e/testcases.xlsx
@@ -4,14 +4,14 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="测试用例" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="统计" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'测试用例'!$A$1:$K$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'测试用例'!$A$1:$K$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -95,42 +95,42 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="16">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="5" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="3" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -491,23 +491,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K634"/>
+  <dimension ref="A1:K646"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="11"/>
-    <col customWidth="1" max="2" min="2" width="36"/>
-    <col customWidth="1" max="3" min="3" width="24"/>
-    <col customWidth="1" max="4" min="4" width="42"/>
-    <col customWidth="1" max="5" min="5" width="26"/>
-    <col customWidth="1" max="6" min="6" width="38"/>
-    <col customWidth="1" max="7" min="7" width="8"/>
-    <col customWidth="1" max="8" min="8" width="10"/>
-    <col customWidth="1" max="9" min="9" width="20"/>
-    <col customWidth="1" max="10" min="10" width="34"/>
-    <col customWidth="1" max="11" min="11" width="22"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="30" r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>用例编号</t>
@@ -564,7 +564,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="2">
+    <row r="2" ht="70" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>TC-001</t>
@@ -622,7 +622,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="3">
+    <row r="3" ht="70" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>TC-002</t>
@@ -680,7 +680,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="4">
+    <row r="4" ht="70" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>TC-003</t>
@@ -735,7 +735,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="5">
+    <row r="5" ht="70" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>TC-004</t>
@@ -795,7 +795,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="6">
+    <row r="6" ht="70" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>TC-005</t>
@@ -856,7 +856,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="7">
+    <row r="7" ht="70" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>TC-006</t>
@@ -914,7 +914,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="8">
+    <row r="8" ht="70" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>TC-007</t>
@@ -975,7 +975,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="9">
+    <row r="9" ht="70" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
           <t>TC-008</t>
@@ -1033,7 +1033,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="10">
+    <row r="10" ht="70" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>TC-009</t>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="11">
+    <row r="11" ht="70" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
           <t>TC-010</t>
@@ -1147,7 +1147,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="12">
+    <row r="12" ht="70" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>TC-011</t>
@@ -1204,7 +1204,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="13">
+    <row r="13" ht="70" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
           <t>TC-012</t>
@@ -1262,7 +1262,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="14">
+    <row r="14" ht="70" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
           <t>TC-013</t>
@@ -1319,7 +1319,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="15">
+    <row r="15" ht="70" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
           <t>TC-014</t>
@@ -1382,7 +1382,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="16">
+    <row r="16" ht="70" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
           <t>TC-015</t>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="17">
+    <row r="17" ht="70" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
           <t>TC-016</t>
@@ -1501,7 +1501,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="18">
+    <row r="18" ht="70" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
           <t>TC-017</t>
@@ -1562,7 +1562,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="19">
+    <row r="19" ht="70" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
           <t>TC-018</t>
@@ -1624,7 +1624,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="20">
+    <row r="20" ht="70" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
           <t>TC-019</t>
@@ -1682,7 +1682,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="21">
+    <row r="21" ht="70" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
           <t>TC-020</t>
@@ -1744,7 +1744,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="22">
+    <row r="22" ht="70" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
           <t>TC-021</t>
@@ -1802,7 +1802,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="23">
+    <row r="23" ht="70" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
           <t>TC-022</t>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="24">
+    <row r="24" ht="70" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
           <t>TC-023</t>
@@ -1919,7 +1919,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="25">
+    <row r="25" ht="70" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
           <t>TC-024</t>
@@ -1977,7 +1977,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="26">
+    <row r="26" ht="70" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
           <t>TC-025</t>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="27">
+    <row r="27" ht="70" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
           <t>TC-026</t>
@@ -2095,7 +2095,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="28">
+    <row r="28" ht="70" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
           <t>TC-027</t>
@@ -2155,7 +2155,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="29">
+    <row r="29" ht="70" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
           <t>TC-028</t>
@@ -2214,7 +2214,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="30">
+    <row r="30" ht="70" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
           <t>TC-029</t>
@@ -2274,7 +2274,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="31">
+    <row r="31" ht="70" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
           <t>TC-030</t>
@@ -2336,7 +2336,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="32">
+    <row r="32" ht="70" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
           <t>TC-031</t>
@@ -2399,7 +2399,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="33">
+    <row r="33" ht="70" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
           <t>TC-032</t>
@@ -2462,7 +2462,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="34">
+    <row r="34" ht="70" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
           <t>TC-033</t>
@@ -2521,7 +2521,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="35">
+    <row r="35" ht="70" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
           <t>TC-034</t>
@@ -2577,7 +2577,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="36">
+    <row r="36" ht="70" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
           <t>TC-035</t>
@@ -2633,7 +2633,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="37">
+    <row r="37" ht="70" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
           <t>TC-036</t>
@@ -2694,7 +2694,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="38">
+    <row r="38" ht="70" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
           <t>TC-037</t>
@@ -2751,7 +2751,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="39">
+    <row r="39" ht="70" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
           <t>TC-038</t>
@@ -2808,7 +2808,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="40">
+    <row r="40" ht="70" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
           <t>TC-039</t>
@@ -2865,7 +2865,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="41">
+    <row r="41" ht="70" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
           <t>TC-040</t>
@@ -2922,7 +2922,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="42">
+    <row r="42" ht="70" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
           <t>TC-041</t>
@@ -2980,7 +2980,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="43">
+    <row r="43" ht="70" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
           <t>TC-042</t>
@@ -3037,7 +3037,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="44">
+    <row r="44" ht="70" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
           <t>TC-043</t>
@@ -3094,7 +3094,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="45">
+    <row r="45" ht="70" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
           <t>TC-044</t>
@@ -3150,7 +3150,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="46">
+    <row r="46" ht="70" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
           <t>TC-045</t>
@@ -3209,7 +3209,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="47">
+    <row r="47" ht="70" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
           <t>TC-046</t>
@@ -3268,7 +3268,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="48">
+    <row r="48" ht="70" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
           <t>TC-047</t>
@@ -3327,7 +3327,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="49">
+    <row r="49" ht="70" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
           <t>TC-048</t>
@@ -3385,7 +3385,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="50">
+    <row r="50" ht="70" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
           <t>TC-049</t>
@@ -3443,7 +3443,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="51">
+    <row r="51" ht="70" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
           <t>TC-050</t>
@@ -3501,7 +3501,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="52">
+    <row r="52" ht="70" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
           <t>TC-051</t>
@@ -3558,7 +3558,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="53">
+    <row r="53" ht="70" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
           <t>TC-052</t>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="54">
+    <row r="54" ht="70" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
           <t>TC-053</t>
@@ -3672,7 +3672,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="55">
+    <row r="55" ht="70" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
           <t>TC-054</t>
@@ -3729,7 +3729,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="56">
+    <row r="56" ht="70" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
           <t>TC-055</t>
@@ -3787,7 +3787,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="57">
+    <row r="57" ht="70" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
           <t>TC-056</t>
@@ -3844,7 +3844,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="58">
+    <row r="58" ht="70" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
           <t>TC-057</t>
@@ -3901,7 +3901,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="59">
+    <row r="59" ht="70" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
           <t>TC-058</t>
@@ -3958,7 +3958,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="60">
+    <row r="60" ht="70" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
           <t>TC-059</t>
@@ -4017,7 +4017,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="61">
+    <row r="61" ht="70" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
           <t>TC-060</t>
@@ -4077,7 +4077,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="62">
+    <row r="62" ht="70" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
           <t>TC-061</t>
@@ -4135,7 +4135,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="63">
+    <row r="63" ht="70" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
           <t>TC-062</t>
@@ -4194,7 +4194,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="64">
+    <row r="64" ht="70" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
           <t>TC-063</t>
@@ -4257,7 +4257,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="65">
+    <row r="65" ht="70" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
           <t>TC-064</t>
@@ -4316,7 +4316,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="66">
+    <row r="66" ht="70" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
           <t>TC-065</t>
@@ -4375,7 +4375,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="67">
+    <row r="67" ht="70" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
           <t>TC-066</t>
@@ -4434,7 +4434,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="68">
+    <row r="68" ht="70" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
           <t>TC-067</t>
@@ -4492,7 +4492,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="69">
+    <row r="69" ht="70" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
           <t>TC-068</t>
@@ -4550,7 +4550,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="70">
+    <row r="70" ht="70" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
           <t>TC-069</t>
@@ -4608,7 +4608,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="71">
+    <row r="71" ht="70" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
           <t>TC-070</t>
@@ -4666,7 +4666,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="72">
+    <row r="72" ht="70" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
           <t>TC-071</t>
@@ -4723,7 +4723,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="73">
+    <row r="73" ht="70" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
         <is>
           <t>TC-072</t>
@@ -4781,7 +4781,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="74">
+    <row r="74" ht="70" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
           <t>TC-073</t>
@@ -4838,7 +4838,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="75">
+    <row r="75" ht="70" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
           <t>TC-074</t>
@@ -4897,7 +4897,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="76">
+    <row r="76" ht="70" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
           <t>TC-075</t>
@@ -4955,7 +4955,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="77">
+    <row r="77" ht="70" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
           <t>TC-076</t>
@@ -5013,7 +5013,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="78">
+    <row r="78" ht="70" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
           <t>TC-077</t>
@@ -5070,7 +5070,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="79">
+    <row r="79" ht="70" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
         <is>
           <t>TC-078</t>
@@ -5129,7 +5129,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="80">
+    <row r="80" ht="70" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
           <t>TC-079</t>
@@ -5187,7 +5187,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="81">
+    <row r="81" ht="70" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
         <is>
           <t>TC-080</t>
@@ -5246,7 +5246,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="82">
+    <row r="82" ht="70" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
           <t>TC-081</t>
@@ -5309,7 +5309,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="83">
+    <row r="83" ht="70" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
         <is>
           <t>TC-082</t>
@@ -5370,7 +5370,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="84">
+    <row r="84" ht="70" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
           <t>TC-083</t>
@@ -5429,7 +5429,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="85">
+    <row r="85" ht="70" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
         <is>
           <t>TC-084</t>
@@ -5488,7 +5488,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="86">
+    <row r="86" ht="70" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
           <t>TC-085</t>
@@ -5547,7 +5547,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="87">
+    <row r="87" ht="70" customHeight="1">
       <c r="A87" s="2" t="inlineStr">
         <is>
           <t>TC-086</t>
@@ -5605,7 +5605,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="88">
+    <row r="88" ht="70" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
           <t>TC-087</t>
@@ -5662,7 +5662,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="89">
+    <row r="89" ht="70" customHeight="1">
       <c r="A89" s="2" t="inlineStr">
         <is>
           <t>TC-088</t>
@@ -5719,7 +5719,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="90">
+    <row r="90" ht="70" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
           <t>TC-089</t>
@@ -5776,7 +5776,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="91">
+    <row r="91" ht="70" customHeight="1">
       <c r="A91" s="2" t="inlineStr">
         <is>
           <t>TC-090</t>
@@ -5834,7 +5834,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="92">
+    <row r="92" ht="70" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
           <t>TC-091</t>
@@ -5892,7 +5892,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="93">
+    <row r="93" ht="70" customHeight="1">
       <c r="A93" s="2" t="inlineStr">
         <is>
           <t>TC-092</t>
@@ -5951,7 +5951,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="94">
+    <row r="94" ht="70" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
           <t>TC-093</t>
@@ -6009,7 +6009,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="95">
+    <row r="95" ht="70" customHeight="1">
       <c r="A95" s="2" t="inlineStr">
         <is>
           <t>TC-094</t>
@@ -6068,7 +6068,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="96">
+    <row r="96" ht="70" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
           <t>TC-095</t>
@@ -6129,7 +6129,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="97">
+    <row r="97" ht="70" customHeight="1">
       <c r="A97" s="2" t="inlineStr">
         <is>
           <t>TC-096</t>
@@ -6192,7 +6192,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="98">
+    <row r="98" ht="70" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
           <t>TC-097</t>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="99">
+    <row r="99" ht="70" customHeight="1">
       <c r="A99" s="2" t="inlineStr">
         <is>
           <t>TC-098</t>
@@ -6310,7 +6310,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="100">
+    <row r="100" ht="70" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
         <is>
           <t>TC-099</t>
@@ -6369,7 +6369,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="101">
+    <row r="101" ht="70" customHeight="1">
       <c r="A101" s="2" t="inlineStr">
         <is>
           <t>TC-100</t>
@@ -6428,7 +6428,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="102">
+    <row r="102" ht="70" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
         <is>
           <t>TC-101</t>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="103">
+    <row r="103" ht="70" customHeight="1">
       <c r="A103" s="2" t="inlineStr">
         <is>
           <t>TC-102</t>
@@ -6543,7 +6543,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="104">
+    <row r="104" ht="70" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
         <is>
           <t>TC-103</t>
@@ -6601,7 +6601,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="105">
+    <row r="105" ht="70" customHeight="1">
       <c r="A105" s="2" t="inlineStr">
         <is>
           <t>TC-104</t>
@@ -6660,7 +6660,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="106">
+    <row r="106" ht="70" customHeight="1">
       <c r="A106" s="2" t="inlineStr">
         <is>
           <t>TC-105</t>
@@ -6718,7 +6718,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="107">
+    <row r="107" ht="70" customHeight="1">
       <c r="A107" s="2" t="inlineStr">
         <is>
           <t>TC-106</t>
@@ -6776,7 +6776,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="108">
+    <row r="108" ht="70" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
         <is>
           <t>TC-107</t>
@@ -6835,7 +6835,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="109">
+    <row r="109" ht="70" customHeight="1">
       <c r="A109" s="2" t="inlineStr">
         <is>
           <t>TC-108</t>
@@ -6898,7 +6898,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="110">
+    <row r="110" ht="70" customHeight="1">
       <c r="A110" s="2" t="inlineStr">
         <is>
           <t>TC-109</t>
@@ -6961,7 +6961,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="111">
+    <row r="111" ht="70" customHeight="1">
       <c r="A111" s="2" t="inlineStr">
         <is>
           <t>TC-110</t>
@@ -7020,7 +7020,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="112">
+    <row r="112" ht="70" customHeight="1">
       <c r="A112" s="2" t="inlineStr">
         <is>
           <t>TC-111</t>
@@ -7079,7 +7079,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="113">
+    <row r="113" ht="70" customHeight="1">
       <c r="A113" s="2" t="inlineStr">
         <is>
           <t>TC-112</t>
@@ -7138,7 +7138,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="114">
+    <row r="114" ht="70" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
         <is>
           <t>TC-113</t>
@@ -7196,7 +7196,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="115">
+    <row r="115" ht="70" customHeight="1">
       <c r="A115" s="2" t="inlineStr">
         <is>
           <t>TC-114</t>
@@ -7253,7 +7253,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="116">
+    <row r="116" ht="70" customHeight="1">
       <c r="A116" s="2" t="inlineStr">
         <is>
           <t>TC-115</t>
@@ -7310,7 +7310,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="117">
+    <row r="117" ht="70" customHeight="1">
       <c r="A117" s="2" t="inlineStr">
         <is>
           <t>TC-116</t>
@@ -7367,7 +7367,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="118">
+    <row r="118" ht="70" customHeight="1">
       <c r="A118" s="2" t="inlineStr">
         <is>
           <t>TC-117</t>
@@ -7424,7 +7424,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="119">
+    <row r="119" ht="70" customHeight="1">
       <c r="A119" s="2" t="inlineStr">
         <is>
           <t>TC-118</t>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="120">
+    <row r="120" ht="70" customHeight="1">
       <c r="A120" s="2" t="inlineStr">
         <is>
           <t>TC-119</t>
@@ -7538,7 +7538,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="121">
+    <row r="121" ht="70" customHeight="1">
       <c r="A121" s="2" t="inlineStr">
         <is>
           <t>TC-120</t>
@@ -7595,7 +7595,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="122">
+    <row r="122" ht="70" customHeight="1">
       <c r="A122" s="2" t="inlineStr">
         <is>
           <t>TC-121</t>
@@ -7653,7 +7653,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="123">
+    <row r="123" ht="70" customHeight="1">
       <c r="A123" s="2" t="inlineStr">
         <is>
           <t>TC-122</t>
@@ -7711,7 +7711,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="124">
+    <row r="124" ht="70" customHeight="1">
       <c r="A124" s="2" t="inlineStr">
         <is>
           <t>TC-123</t>
@@ -7770,7 +7770,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="125">
+    <row r="125" ht="70" customHeight="1">
       <c r="A125" s="2" t="inlineStr">
         <is>
           <t>TC-124</t>
@@ -7831,7 +7831,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="126">
+    <row r="126" ht="70" customHeight="1">
       <c r="A126" s="2" t="inlineStr">
         <is>
           <t>TC-125</t>
@@ -7889,7 +7889,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="127">
+    <row r="127" ht="70" customHeight="1">
       <c r="A127" s="2" t="inlineStr">
         <is>
           <t>TC-126</t>
@@ -7948,7 +7948,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="128">
+    <row r="128" ht="70" customHeight="1">
       <c r="A128" s="2" t="inlineStr">
         <is>
           <t>TC-127</t>
@@ -8011,7 +8011,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="129">
+    <row r="129" ht="70" customHeight="1">
       <c r="A129" s="2" t="inlineStr">
         <is>
           <t>TC-128</t>
@@ -8070,7 +8070,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="130">
+    <row r="130" ht="70" customHeight="1">
       <c r="A130" s="2" t="inlineStr">
         <is>
           <t>TC-129</t>
@@ -8129,7 +8129,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="131">
+    <row r="131" ht="70" customHeight="1">
       <c r="A131" s="2" t="inlineStr">
         <is>
           <t>TC-130</t>
@@ -8188,7 +8188,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="132">
+    <row r="132" ht="70" customHeight="1">
       <c r="A132" s="2" t="inlineStr">
         <is>
           <t>TC-131</t>
@@ -8247,7 +8247,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="133">
+    <row r="133" ht="70" customHeight="1">
       <c r="A133" s="2" t="inlineStr">
         <is>
           <t>TC-132</t>
@@ -8304,7 +8304,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="134">
+    <row r="134" ht="70" customHeight="1">
       <c r="A134" s="2" t="inlineStr">
         <is>
           <t>TC-133</t>
@@ -8361,7 +8361,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="135">
+    <row r="135" ht="70" customHeight="1">
       <c r="A135" s="2" t="inlineStr">
         <is>
           <t>TC-134</t>
@@ -8419,7 +8419,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="136">
+    <row r="136" ht="70" customHeight="1">
       <c r="A136" s="2" t="inlineStr">
         <is>
           <t>TC-135</t>
@@ -8476,7 +8476,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="137">
+    <row r="137" ht="70" customHeight="1">
       <c r="A137" s="2" t="inlineStr">
         <is>
           <t>TC-136</t>
@@ -8533,7 +8533,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="138">
+    <row r="138" ht="70" customHeight="1">
       <c r="A138" s="2" t="inlineStr">
         <is>
           <t>TC-137</t>
@@ -8590,7 +8590,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="139">
+    <row r="139" ht="70" customHeight="1">
       <c r="A139" s="2" t="inlineStr">
         <is>
           <t>TC-138</t>
@@ -8648,7 +8648,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="140">
+    <row r="140" ht="70" customHeight="1">
       <c r="A140" s="2" t="inlineStr">
         <is>
           <t>TC-139</t>
@@ -8706,7 +8706,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="141">
+    <row r="141" ht="70" customHeight="1">
       <c r="A141" s="2" t="inlineStr">
         <is>
           <t>TC-140</t>
@@ -8765,7 +8765,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="142">
+    <row r="142" ht="70" customHeight="1">
       <c r="A142" s="2" t="inlineStr">
         <is>
           <t>TC-141</t>
@@ -8823,7 +8823,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="143">
+    <row r="143" ht="70" customHeight="1">
       <c r="A143" s="2" t="inlineStr">
         <is>
           <t>TC-142</t>
@@ -8882,7 +8882,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="144">
+    <row r="144" ht="70" customHeight="1">
       <c r="A144" s="2" t="inlineStr">
         <is>
           <t>TC-143</t>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="145">
+    <row r="145" ht="70" customHeight="1">
       <c r="A145" s="2" t="inlineStr">
         <is>
           <t>TC-144</t>
@@ -9004,7 +9004,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="146">
+    <row r="146" ht="70" customHeight="1">
       <c r="A146" s="2" t="inlineStr">
         <is>
           <t>TC-145</t>
@@ -9065,7 +9065,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="147">
+    <row r="147" ht="70" customHeight="1">
       <c r="A147" s="2" t="inlineStr">
         <is>
           <t>TC-146</t>
@@ -9121,7 +9121,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="148">
+    <row r="148" ht="70" customHeight="1">
       <c r="A148" s="2" t="inlineStr">
         <is>
           <t>TC-147</t>
@@ -9183,7 +9183,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="149">
+    <row r="149" ht="70" customHeight="1">
       <c r="A149" s="2" t="inlineStr">
         <is>
           <t>TC-148</t>
@@ -9244,7 +9244,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="150">
+    <row r="150" ht="70" customHeight="1">
       <c r="A150" s="2" t="inlineStr">
         <is>
           <t>TC-149</t>
@@ -9299,7 +9299,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="151">
+    <row r="151" ht="70" customHeight="1">
       <c r="A151" s="2" t="inlineStr">
         <is>
           <t>TC-150</t>
@@ -9353,7 +9353,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="152">
+    <row r="152" ht="70" customHeight="1">
       <c r="A152" s="2" t="inlineStr">
         <is>
           <t>TC-151</t>
@@ -9407,7 +9407,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="153">
+    <row r="153" ht="70" customHeight="1">
       <c r="A153" s="2" t="inlineStr">
         <is>
           <t>TC-152</t>
@@ -9461,7 +9461,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="154">
+    <row r="154" ht="70" customHeight="1">
       <c r="A154" s="2" t="inlineStr">
         <is>
           <t>TC-153</t>
@@ -9515,7 +9515,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="155">
+    <row r="155" ht="70" customHeight="1">
       <c r="A155" s="2" t="inlineStr">
         <is>
           <t>TC-154</t>
@@ -9569,7 +9569,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="156">
+    <row r="156" ht="70" customHeight="1">
       <c r="A156" s="2" t="inlineStr">
         <is>
           <t>TC-155</t>
@@ -9631,7 +9631,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="157">
+    <row r="157" ht="70" customHeight="1">
       <c r="A157" s="2" t="inlineStr">
         <is>
           <t>TC-156</t>
@@ -9687,7 +9687,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="158">
+    <row r="158" ht="70" customHeight="1">
       <c r="A158" s="2" t="inlineStr">
         <is>
           <t>TC-157</t>
@@ -9745,7 +9745,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="159">
+    <row r="159" ht="70" customHeight="1">
       <c r="A159" s="2" t="inlineStr">
         <is>
           <t>TC-158</t>
@@ -9802,7 +9802,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="160">
+    <row r="160" ht="70" customHeight="1">
       <c r="A160" s="2" t="inlineStr">
         <is>
           <t>TC-159</t>
@@ -9858,7 +9858,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="161">
+    <row r="161" ht="70" customHeight="1">
       <c r="A161" s="2" t="inlineStr">
         <is>
           <t>TC-160</t>
@@ -9917,7 +9917,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="162">
+    <row r="162" ht="70" customHeight="1">
       <c r="A162" s="2" t="inlineStr">
         <is>
           <t>TC-161</t>
@@ -9976,7 +9976,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="163">
+    <row r="163" ht="70" customHeight="1">
       <c r="A163" s="2" t="inlineStr">
         <is>
           <t>TC-162</t>
@@ -10034,7 +10034,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="164">
+    <row r="164" ht="70" customHeight="1">
       <c r="A164" s="2" t="inlineStr">
         <is>
           <t>TC-163</t>
@@ -10091,7 +10091,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="165">
+    <row r="165" ht="70" customHeight="1">
       <c r="A165" s="2" t="inlineStr">
         <is>
           <t>TC-164</t>
@@ -10148,7 +10148,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="166">
+    <row r="166" ht="70" customHeight="1">
       <c r="A166" s="2" t="inlineStr">
         <is>
           <t>TC-165</t>
@@ -10205,7 +10205,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="167">
+    <row r="167" ht="70" customHeight="1">
       <c r="A167" s="2" t="inlineStr">
         <is>
           <t>TC-166</t>
@@ -10265,7 +10265,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="168">
+    <row r="168" ht="70" customHeight="1">
       <c r="A168" s="2" t="inlineStr">
         <is>
           <t>TC-167</t>
@@ -10323,7 +10323,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="169">
+    <row r="169" ht="70" customHeight="1">
       <c r="A169" s="2" t="inlineStr">
         <is>
           <t>TC-168</t>
@@ -10381,7 +10381,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="170">
+    <row r="170" ht="70" customHeight="1">
       <c r="A170" s="2" t="inlineStr">
         <is>
           <t>TC-169</t>
@@ -10440,7 +10440,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="171">
+    <row r="171" ht="70" customHeight="1">
       <c r="A171" s="2" t="inlineStr">
         <is>
           <t>TC-170</t>
@@ -10498,7 +10498,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="172">
+    <row r="172" ht="70" customHeight="1">
       <c r="A172" s="2" t="inlineStr">
         <is>
           <t>TC-171</t>
@@ -10557,7 +10557,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="173">
+    <row r="173" ht="70" customHeight="1">
       <c r="A173" s="2" t="inlineStr">
         <is>
           <t>TC-172</t>
@@ -10620,7 +10620,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="174">
+    <row r="174" ht="70" customHeight="1">
       <c r="A174" s="2" t="inlineStr">
         <is>
           <t>TC-173</t>
@@ -10681,7 +10681,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="175">
+    <row r="175" ht="70" customHeight="1">
       <c r="A175" s="2" t="inlineStr">
         <is>
           <t>TC-174</t>
@@ -10740,7 +10740,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="176">
+    <row r="176" ht="70" customHeight="1">
       <c r="A176" s="2" t="inlineStr">
         <is>
           <t>TC-175</t>
@@ -10799,7 +10799,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="177">
+    <row r="177" ht="70" customHeight="1">
       <c r="A177" s="2" t="inlineStr">
         <is>
           <t>TC-176</t>
@@ -10858,7 +10858,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="178">
+    <row r="178" ht="70" customHeight="1">
       <c r="A178" s="2" t="inlineStr">
         <is>
           <t>TC-177</t>
@@ -10916,7 +10916,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="179">
+    <row r="179" ht="70" customHeight="1">
       <c r="A179" s="2" t="inlineStr">
         <is>
           <t>TC-178</t>
@@ -10974,7 +10974,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="180">
+    <row r="180" ht="70" customHeight="1">
       <c r="A180" s="2" t="inlineStr">
         <is>
           <t>TC-179</t>
@@ -11032,7 +11032,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="181">
+    <row r="181" ht="70" customHeight="1">
       <c r="A181" s="2" t="inlineStr">
         <is>
           <t>TC-180</t>
@@ -11089,7 +11089,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="182">
+    <row r="182" ht="70" customHeight="1">
       <c r="A182" s="2" t="inlineStr">
         <is>
           <t>TC-181</t>
@@ -11146,7 +11146,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="183">
+    <row r="183" ht="70" customHeight="1">
       <c r="A183" s="2" t="inlineStr">
         <is>
           <t>TC-182</t>
@@ -11203,7 +11203,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="184">
+    <row r="184" ht="70" customHeight="1">
       <c r="A184" s="2" t="inlineStr">
         <is>
           <t>TC-183</t>
@@ -11260,7 +11260,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="185">
+    <row r="185" ht="70" customHeight="1">
       <c r="A185" s="2" t="inlineStr">
         <is>
           <t>TC-184</t>
@@ -11317,7 +11317,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="186">
+    <row r="186" ht="70" customHeight="1">
       <c r="A186" s="2" t="inlineStr">
         <is>
           <t>TC-185</t>
@@ -11374,7 +11374,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="187">
+    <row r="187" ht="70" customHeight="1">
       <c r="A187" s="2" t="inlineStr">
         <is>
           <t>TC-186</t>
@@ -11431,7 +11431,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="188">
+    <row r="188" ht="70" customHeight="1">
       <c r="A188" s="2" t="inlineStr">
         <is>
           <t>TC-187</t>
@@ -11492,7 +11492,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="189">
+    <row r="189" ht="70" customHeight="1">
       <c r="A189" s="2" t="inlineStr">
         <is>
           <t>TC-188</t>
@@ -11551,7 +11551,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="190">
+    <row r="190" ht="70" customHeight="1">
       <c r="A190" s="2" t="inlineStr">
         <is>
           <t>TC-189</t>
@@ -11609,7 +11609,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="191">
+    <row r="191" ht="70" customHeight="1">
       <c r="A191" s="2" t="inlineStr">
         <is>
           <t>TC-190</t>
@@ -11668,7 +11668,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="192">
+    <row r="192" ht="70" customHeight="1">
       <c r="A192" s="2" t="inlineStr">
         <is>
           <t>TC-191</t>
@@ -11731,7 +11731,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="193">
+    <row r="193" ht="70" customHeight="1">
       <c r="A193" s="2" t="inlineStr">
         <is>
           <t>TC-192</t>
@@ -11790,7 +11790,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="194">
+    <row r="194" ht="70" customHeight="1">
       <c r="A194" s="2" t="inlineStr">
         <is>
           <t>TC-193</t>
@@ -11849,7 +11849,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="195">
+    <row r="195" ht="70" customHeight="1">
       <c r="A195" s="2" t="inlineStr">
         <is>
           <t>TC-194</t>
@@ -11908,7 +11908,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="196">
+    <row r="196" ht="70" customHeight="1">
       <c r="A196" s="2" t="inlineStr">
         <is>
           <t>TC-195</t>
@@ -11967,7 +11967,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="197">
+    <row r="197" ht="70" customHeight="1">
       <c r="A197" s="2" t="inlineStr">
         <is>
           <t>TC-196</t>
@@ -12025,7 +12025,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="198">
+    <row r="198" ht="70" customHeight="1">
       <c r="A198" s="2" t="inlineStr">
         <is>
           <t>TC-197</t>
@@ -12083,7 +12083,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="199">
+    <row r="199" ht="70" customHeight="1">
       <c r="A199" s="2" t="inlineStr">
         <is>
           <t>TC-198</t>
@@ -12140,7 +12140,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="200">
+    <row r="200" ht="70" customHeight="1">
       <c r="A200" s="2" t="inlineStr">
         <is>
           <t>TC-199</t>
@@ -12199,7 +12199,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="201">
+    <row r="201" ht="70" customHeight="1">
       <c r="A201" s="2" t="inlineStr">
         <is>
           <t>TC-200</t>
@@ -12257,7 +12257,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="202">
+    <row r="202" ht="70" customHeight="1">
       <c r="A202" s="2" t="inlineStr">
         <is>
           <t>TC-201</t>
@@ -12318,7 +12318,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="203">
+    <row r="203" ht="70" customHeight="1">
       <c r="A203" s="2" t="inlineStr">
         <is>
           <t>TC-202</t>
@@ -12377,7 +12377,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="204">
+    <row r="204" ht="70" customHeight="1">
       <c r="A204" s="2" t="inlineStr">
         <is>
           <t>TC-203</t>
@@ -12440,7 +12440,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="205">
+    <row r="205" ht="70" customHeight="1">
       <c r="A205" s="2" t="inlineStr">
         <is>
           <t>TC-204</t>
@@ -12499,7 +12499,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="206">
+    <row r="206" ht="70" customHeight="1">
       <c r="A206" s="2" t="inlineStr">
         <is>
           <t>TC-205</t>
@@ -12554,7 +12554,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="207">
+    <row r="207" ht="70" customHeight="1">
       <c r="A207" s="2" t="inlineStr">
         <is>
           <t>TC-206</t>
@@ -12615,7 +12615,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="208">
+    <row r="208" ht="70" customHeight="1">
       <c r="A208" s="2" t="inlineStr">
         <is>
           <t>TC-207</t>
@@ -12672,7 +12672,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="209">
+    <row r="209" ht="70" customHeight="1">
       <c r="A209" s="2" t="inlineStr">
         <is>
           <t>TC-208</t>
@@ -12733,7 +12733,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="210">
+    <row r="210" ht="70" customHeight="1">
       <c r="A210" s="2" t="inlineStr">
         <is>
           <t>TC-209</t>
@@ -12790,7 +12790,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="211">
+    <row r="211" ht="70" customHeight="1">
       <c r="A211" s="2" t="inlineStr">
         <is>
           <t>TC-210</t>
@@ -12844,7 +12844,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="212">
+    <row r="212" ht="70" customHeight="1">
       <c r="A212" s="2" t="inlineStr">
         <is>
           <t>TC-211</t>
@@ -12898,7 +12898,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="213">
+    <row r="213" ht="70" customHeight="1">
       <c r="A213" s="2" t="inlineStr">
         <is>
           <t>TC-212</t>
@@ -12952,7 +12952,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="214">
+    <row r="214" ht="70" customHeight="1">
       <c r="A214" s="2" t="inlineStr">
         <is>
           <t>TC-213</t>
@@ -13006,7 +13006,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="215">
+    <row r="215" ht="70" customHeight="1">
       <c r="A215" s="2" t="inlineStr">
         <is>
           <t>TC-214</t>
@@ -13062,7 +13062,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="216">
+    <row r="216" ht="70" customHeight="1">
       <c r="A216" s="2" t="inlineStr">
         <is>
           <t>TC-215</t>
@@ -13124,7 +13124,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="217">
+    <row r="217" ht="70" customHeight="1">
       <c r="A217" s="2" t="inlineStr">
         <is>
           <t>TC-216</t>
@@ -13181,7 +13181,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="218">
+    <row r="218" ht="70" customHeight="1">
       <c r="A218" s="2" t="inlineStr">
         <is>
           <t>TC-217</t>
@@ -13240,7 +13240,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="219">
+    <row r="219" ht="70" customHeight="1">
       <c r="A219" s="2" t="inlineStr">
         <is>
           <t>TC-218</t>
@@ -13297,7 +13297,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="220">
+    <row r="220" ht="70" customHeight="1">
       <c r="A220" s="2" t="inlineStr">
         <is>
           <t>TC-219</t>
@@ -13354,7 +13354,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="221">
+    <row r="221" ht="70" customHeight="1">
       <c r="A221" s="2" t="inlineStr">
         <is>
           <t>TC-220</t>
@@ -13415,7 +13415,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="222">
+    <row r="222" ht="70" customHeight="1">
       <c r="A222" s="2" t="inlineStr">
         <is>
           <t>TC-221</t>
@@ -13472,7 +13472,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="223">
+    <row r="223" ht="70" customHeight="1">
       <c r="A223" s="2" t="inlineStr">
         <is>
           <t>TC-222</t>
@@ -13529,7 +13529,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="224">
+    <row r="224" ht="70" customHeight="1">
       <c r="A224" s="2" t="inlineStr">
         <is>
           <t>TC-223</t>
@@ -13586,7 +13586,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="225">
+    <row r="225" ht="70" customHeight="1">
       <c r="A225" s="2" t="inlineStr">
         <is>
           <t>TC-224</t>
@@ -13642,7 +13642,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="226">
+    <row r="226" ht="70" customHeight="1">
       <c r="A226" s="2" t="inlineStr">
         <is>
           <t>TC-225</t>
@@ -13700,7 +13700,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="227">
+    <row r="227" ht="70" customHeight="1">
       <c r="A227" s="2" t="inlineStr">
         <is>
           <t>TC-226</t>
@@ -13759,7 +13759,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="228">
+    <row r="228" ht="70" customHeight="1">
       <c r="A228" s="2" t="inlineStr">
         <is>
           <t>TC-227</t>
@@ -13818,7 +13818,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="229">
+    <row r="229" ht="70" customHeight="1">
       <c r="A229" s="2" t="inlineStr">
         <is>
           <t>TC-228</t>
@@ -13877,7 +13877,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="230">
+    <row r="230" ht="70" customHeight="1">
       <c r="A230" s="2" t="inlineStr">
         <is>
           <t>TC-229</t>
@@ -13936,7 +13936,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="231">
+    <row r="231" ht="70" customHeight="1">
       <c r="A231" s="2" t="inlineStr">
         <is>
           <t>TC-230</t>
@@ -13993,7 +13993,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="232">
+    <row r="232" ht="70" customHeight="1">
       <c r="A232" s="2" t="inlineStr">
         <is>
           <t>TC-231</t>
@@ -14050,7 +14050,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="233">
+    <row r="233" ht="70" customHeight="1">
       <c r="A233" s="2" t="inlineStr">
         <is>
           <t>TC-232</t>
@@ -14107,7 +14107,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="234">
+    <row r="234" ht="70" customHeight="1">
       <c r="A234" s="2" t="inlineStr">
         <is>
           <t>TC-233</t>
@@ -14165,7 +14165,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="235">
+    <row r="235" ht="70" customHeight="1">
       <c r="A235" s="2" t="inlineStr">
         <is>
           <t>TC-234</t>
@@ -14223,7 +14223,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="236">
+    <row r="236" ht="70" customHeight="1">
       <c r="A236" s="2" t="inlineStr">
         <is>
           <t>TC-235</t>
@@ -14282,7 +14282,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="237">
+    <row r="237" ht="70" customHeight="1">
       <c r="A237" s="2" t="inlineStr">
         <is>
           <t>TC-236</t>
@@ -14340,7 +14340,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="238">
+    <row r="238" ht="70" customHeight="1">
       <c r="A238" s="2" t="inlineStr">
         <is>
           <t>TC-237</t>
@@ -14399,7 +14399,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="239">
+    <row r="239" ht="70" customHeight="1">
       <c r="A239" s="2" t="inlineStr">
         <is>
           <t>TC-238</t>
@@ -14462,7 +14462,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="240">
+    <row r="240" ht="70" customHeight="1">
       <c r="A240" s="2" t="inlineStr">
         <is>
           <t>TC-239</t>
@@ -14523,7 +14523,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="241">
+    <row r="241" ht="70" customHeight="1">
       <c r="A241" s="2" t="inlineStr">
         <is>
           <t>TC-240</t>
@@ -14582,7 +14582,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="242">
+    <row r="242" ht="70" customHeight="1">
       <c r="A242" s="2" t="inlineStr">
         <is>
           <t>TC-241</t>
@@ -14641,7 +14641,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="243">
+    <row r="243" ht="70" customHeight="1">
       <c r="A243" s="2" t="inlineStr">
         <is>
           <t>TC-242</t>
@@ -14700,7 +14700,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="244">
+    <row r="244" ht="70" customHeight="1">
       <c r="A244" s="2" t="inlineStr">
         <is>
           <t>TC-243</t>
@@ -14755,7 +14755,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="245">
+    <row r="245" ht="70" customHeight="1">
       <c r="A245" s="2" t="inlineStr">
         <is>
           <t>TC-244</t>
@@ -14816,7 +14816,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="246">
+    <row r="246" ht="70" customHeight="1">
       <c r="A246" s="2" t="inlineStr">
         <is>
           <t>TC-245</t>
@@ -14871,7 +14871,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="247">
+    <row r="247" ht="70" customHeight="1">
       <c r="A247" s="2" t="inlineStr">
         <is>
           <t>TC-246</t>
@@ -14929,7 +14929,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="248">
+    <row r="248" ht="70" customHeight="1">
       <c r="A248" s="2" t="inlineStr">
         <is>
           <t>TC-247</t>
@@ -14986,7 +14986,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="249">
+    <row r="249" ht="70" customHeight="1">
       <c r="A249" s="2" t="inlineStr">
         <is>
           <t>TC-248</t>
@@ -15043,7 +15043,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="250">
+    <row r="250" ht="70" customHeight="1">
       <c r="A250" s="2" t="inlineStr">
         <is>
           <t>TC-249</t>
@@ -15100,7 +15100,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="251">
+    <row r="251" ht="70" customHeight="1">
       <c r="A251" s="2" t="inlineStr">
         <is>
           <t>TC-250</t>
@@ -15158,7 +15158,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="252">
+    <row r="252" ht="70" customHeight="1">
       <c r="A252" s="2" t="inlineStr">
         <is>
           <t>TC-251</t>
@@ -15216,7 +15216,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="253">
+    <row r="253" ht="70" customHeight="1">
       <c r="A253" s="2" t="inlineStr">
         <is>
           <t>TC-252</t>
@@ -15275,7 +15275,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="254">
+    <row r="254" ht="70" customHeight="1">
       <c r="A254" s="2" t="inlineStr">
         <is>
           <t>TC-253</t>
@@ -15333,7 +15333,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="255">
+    <row r="255" ht="70" customHeight="1">
       <c r="A255" s="2" t="inlineStr">
         <is>
           <t>TC-254</t>
@@ -15392,7 +15392,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="256">
+    <row r="256" ht="70" customHeight="1">
       <c r="A256" s="2" t="inlineStr">
         <is>
           <t>TC-255</t>
@@ -15449,7 +15449,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="257">
+    <row r="257" ht="70" customHeight="1">
       <c r="A257" s="2" t="inlineStr">
         <is>
           <t>TC-256</t>
@@ -15506,7 +15506,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="258">
+    <row r="258" ht="70" customHeight="1">
       <c r="A258" s="2" t="inlineStr">
         <is>
           <t>TC-257</t>
@@ -15569,7 +15569,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="259">
+    <row r="259" ht="70" customHeight="1">
       <c r="A259" s="2" t="inlineStr">
         <is>
           <t>TC-258</t>
@@ -15628,7 +15628,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="260">
+    <row r="260" ht="70" customHeight="1">
       <c r="A260" s="2" t="inlineStr">
         <is>
           <t>TC-259</t>
@@ -15687,7 +15687,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="261">
+    <row r="261" ht="70" customHeight="1">
       <c r="A261" s="2" t="inlineStr">
         <is>
           <t>TC-260</t>
@@ -15744,7 +15744,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="262">
+    <row r="262" ht="70" customHeight="1">
       <c r="A262" s="2" t="inlineStr">
         <is>
           <t>TC-261</t>
@@ -15801,7 +15801,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="263">
+    <row r="263" ht="70" customHeight="1">
       <c r="A263" s="2" t="inlineStr">
         <is>
           <t>TC-262</t>
@@ -15858,7 +15858,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="264">
+    <row r="264" ht="70" customHeight="1">
       <c r="A264" s="2" t="inlineStr">
         <is>
           <t>TC-263</t>
@@ -15914,7 +15914,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="265">
+    <row r="265" ht="70" customHeight="1">
       <c r="A265" s="2" t="inlineStr">
         <is>
           <t>TC-264</t>
@@ -15973,7 +15973,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="266">
+    <row r="266" ht="70" customHeight="1">
       <c r="A266" s="2" t="inlineStr">
         <is>
           <t>TC-265</t>
@@ -16032,7 +16032,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="267">
+    <row r="267" ht="70" customHeight="1">
       <c r="A267" s="2" t="inlineStr">
         <is>
           <t>TC-266</t>
@@ -16089,7 +16089,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="268">
+    <row r="268" ht="70" customHeight="1">
       <c r="A268" s="2" t="inlineStr">
         <is>
           <t>TC-267</t>
@@ -16147,7 +16147,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="269">
+    <row r="269" ht="70" customHeight="1">
       <c r="A269" s="2" t="inlineStr">
         <is>
           <t>TC-268</t>
@@ -16205,7 +16205,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="270">
+    <row r="270" ht="70" customHeight="1">
       <c r="A270" s="2" t="inlineStr">
         <is>
           <t>TC-269</t>
@@ -16262,7 +16262,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="271">
+    <row r="271" ht="70" customHeight="1">
       <c r="A271" s="2" t="inlineStr">
         <is>
           <t>TC-270</t>
@@ -16319,7 +16319,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="272">
+    <row r="272" ht="70" customHeight="1">
       <c r="A272" s="2" t="inlineStr">
         <is>
           <t>TC-271</t>
@@ -16378,7 +16378,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="273">
+    <row r="273" ht="70" customHeight="1">
       <c r="A273" s="2" t="inlineStr">
         <is>
           <t>TC-272</t>
@@ -16436,7 +16436,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="274">
+    <row r="274" ht="70" customHeight="1">
       <c r="A274" s="2" t="inlineStr">
         <is>
           <t>TC-273</t>
@@ -16495,7 +16495,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="275">
+    <row r="275" ht="70" customHeight="1">
       <c r="A275" s="2" t="inlineStr">
         <is>
           <t>TC-274</t>
@@ -16558,7 +16558,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="276">
+    <row r="276" ht="70" customHeight="1">
       <c r="A276" s="2" t="inlineStr">
         <is>
           <t>TC-275</t>
@@ -16617,7 +16617,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="277">
+    <row r="277" ht="70" customHeight="1">
       <c r="A277" s="2" t="inlineStr">
         <is>
           <t>TC-276</t>
@@ -16676,7 +16676,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="278">
+    <row r="278" ht="70" customHeight="1">
       <c r="A278" s="2" t="inlineStr">
         <is>
           <t>TC-277</t>
@@ -16733,7 +16733,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="279">
+    <row r="279" ht="70" customHeight="1">
       <c r="A279" s="2" t="inlineStr">
         <is>
           <t>TC-278</t>
@@ -16790,7 +16790,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="280">
+    <row r="280" ht="70" customHeight="1">
       <c r="A280" s="2" t="inlineStr">
         <is>
           <t>TC-279</t>
@@ -16849,7 +16849,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="281">
+    <row r="281" ht="70" customHeight="1">
       <c r="A281" s="2" t="inlineStr">
         <is>
           <t>TC-280</t>
@@ -16904,7 +16904,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="282">
+    <row r="282" ht="70" customHeight="1">
       <c r="A282" s="2" t="inlineStr">
         <is>
           <t>TC-281</t>
@@ -16963,7 +16963,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="283">
+    <row r="283" ht="70" customHeight="1">
       <c r="A283" s="2" t="inlineStr">
         <is>
           <t>TC-282</t>
@@ -17023,7 +17023,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="284">
+    <row r="284" ht="70" customHeight="1">
       <c r="A284" s="2" t="inlineStr">
         <is>
           <t>TC-283</t>
@@ -17080,7 +17080,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="285">
+    <row r="285" ht="70" customHeight="1">
       <c r="A285" s="2" t="inlineStr">
         <is>
           <t>TC-284</t>
@@ -17136,7 +17136,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="286">
+    <row r="286" ht="70" customHeight="1">
       <c r="A286" s="2" t="inlineStr">
         <is>
           <t>TC-285</t>
@@ -17194,7 +17194,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="287">
+    <row r="287" ht="70" customHeight="1">
       <c r="A287" s="2" t="inlineStr">
         <is>
           <t>TC-286</t>
@@ -17252,7 +17252,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="288">
+    <row r="288" ht="70" customHeight="1">
       <c r="A288" s="2" t="inlineStr">
         <is>
           <t>TC-287</t>
@@ -17310,7 +17310,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="289">
+    <row r="289" ht="70" customHeight="1">
       <c r="A289" s="2" t="inlineStr">
         <is>
           <t>TC-288</t>
@@ -17368,7 +17368,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="290">
+    <row r="290" ht="70" customHeight="1">
       <c r="A290" s="2" t="inlineStr">
         <is>
           <t>TC-289</t>
@@ -17426,7 +17426,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="291">
+    <row r="291" ht="70" customHeight="1">
       <c r="A291" s="2" t="inlineStr">
         <is>
           <t>TC-290</t>
@@ -17485,7 +17485,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="292">
+    <row r="292" ht="70" customHeight="1">
       <c r="A292" s="2" t="inlineStr">
         <is>
           <t>TC-291</t>
@@ -17543,7 +17543,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="293">
+    <row r="293" ht="70" customHeight="1">
       <c r="A293" s="2" t="inlineStr">
         <is>
           <t>TC-292</t>
@@ -17602,7 +17602,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="294">
+    <row r="294" ht="70" customHeight="1">
       <c r="A294" s="2" t="inlineStr">
         <is>
           <t>TC-293</t>
@@ -17665,7 +17665,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="295">
+    <row r="295" ht="70" customHeight="1">
       <c r="A295" s="2" t="inlineStr">
         <is>
           <t>TC-294</t>
@@ -17724,7 +17724,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="296">
+    <row r="296" ht="70" customHeight="1">
       <c r="A296" s="2" t="inlineStr">
         <is>
           <t>TC-295</t>
@@ -17783,7 +17783,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="297">
+    <row r="297" ht="70" customHeight="1">
       <c r="A297" s="2" t="inlineStr">
         <is>
           <t>TC-296</t>
@@ -17844,7 +17844,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="298">
+    <row r="298" ht="70" customHeight="1">
       <c r="A298" s="2" t="inlineStr">
         <is>
           <t>TC-297</t>
@@ -17903,7 +17903,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="299">
+    <row r="299" ht="70" customHeight="1">
       <c r="A299" s="2" t="inlineStr">
         <is>
           <t>TC-298</t>
@@ -17960,7 +17960,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="300">
+    <row r="300" ht="70" customHeight="1">
       <c r="A300" s="2" t="inlineStr">
         <is>
           <t>TC-299</t>
@@ -18017,7 +18017,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="301">
+    <row r="301" ht="70" customHeight="1">
       <c r="A301" s="2" t="inlineStr">
         <is>
           <t>TC-300</t>
@@ -18074,7 +18074,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="302">
+    <row r="302" ht="70" customHeight="1">
       <c r="A302" s="2" t="inlineStr">
         <is>
           <t>TC-301</t>
@@ -18133,7 +18133,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="303">
+    <row r="303" ht="70" customHeight="1">
       <c r="A303" s="2" t="inlineStr">
         <is>
           <t>TC-302</t>
@@ -18192,7 +18192,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="304">
+    <row r="304" ht="70" customHeight="1">
       <c r="A304" s="2" t="inlineStr">
         <is>
           <t>TC-303</t>
@@ -18250,7 +18250,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="305">
+    <row r="305" ht="70" customHeight="1">
       <c r="A305" s="2" t="inlineStr">
         <is>
           <t>TC-304</t>
@@ -18308,7 +18308,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="306">
+    <row r="306" ht="70" customHeight="1">
       <c r="A306" s="2" t="inlineStr">
         <is>
           <t>TC-305</t>
@@ -18367,7 +18367,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="307">
+    <row r="307" ht="70" customHeight="1">
       <c r="A307" s="2" t="inlineStr">
         <is>
           <t>TC-306</t>
@@ -18425,7 +18425,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="308">
+    <row r="308" ht="70" customHeight="1">
       <c r="A308" s="2" t="inlineStr">
         <is>
           <t>TC-307</t>
@@ -18484,7 +18484,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="309">
+    <row r="309" ht="70" customHeight="1">
       <c r="A309" s="2" t="inlineStr">
         <is>
           <t>TC-308</t>
@@ -18547,7 +18547,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="310">
+    <row r="310" ht="70" customHeight="1">
       <c r="A310" s="2" t="inlineStr">
         <is>
           <t>TC-309</t>
@@ -18606,7 +18606,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="311">
+    <row r="311" ht="70" customHeight="1">
       <c r="A311" s="2" t="inlineStr">
         <is>
           <t>TC-310</t>
@@ -18665,7 +18665,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="312">
+    <row r="312" ht="70" customHeight="1">
       <c r="A312" s="2" t="inlineStr">
         <is>
           <t>TC-311</t>
@@ -18726,7 +18726,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="313">
+    <row r="313" ht="70" customHeight="1">
       <c r="A313" s="2" t="inlineStr">
         <is>
           <t>TC-312</t>
@@ -18783,7 +18783,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="314">
+    <row r="314" ht="70" customHeight="1">
       <c r="A314" s="2" t="inlineStr">
         <is>
           <t>TC-313</t>
@@ -18840,7 +18840,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="315">
+    <row r="315" ht="70" customHeight="1">
       <c r="A315" s="2" t="inlineStr">
         <is>
           <t>TC-314</t>
@@ -18899,7 +18899,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="316">
+    <row r="316" ht="70" customHeight="1">
       <c r="A316" s="2" t="inlineStr">
         <is>
           <t>TC-315</t>
@@ -18958,7 +18958,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="317">
+    <row r="317" ht="70" customHeight="1">
       <c r="A317" s="2" t="inlineStr">
         <is>
           <t>TC-316</t>
@@ -19015,7 +19015,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="318">
+    <row r="318" ht="70" customHeight="1">
       <c r="A318" s="2" t="inlineStr">
         <is>
           <t>TC-317</t>
@@ -19072,7 +19072,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="319">
+    <row r="319" ht="70" customHeight="1">
       <c r="A319" s="2" t="inlineStr">
         <is>
           <t>TC-318</t>
@@ -19129,7 +19129,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="320">
+    <row r="320" ht="70" customHeight="1">
       <c r="A320" s="2" t="inlineStr">
         <is>
           <t>TC-319</t>
@@ -19186,7 +19186,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="321">
+    <row r="321" ht="70" customHeight="1">
       <c r="A321" s="2" t="inlineStr">
         <is>
           <t>TC-320</t>
@@ -19243,7 +19243,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="322">
+    <row r="322" ht="70" customHeight="1">
       <c r="A322" s="2" t="inlineStr">
         <is>
           <t>TC-321</t>
@@ -19301,7 +19301,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="323">
+    <row r="323" ht="70" customHeight="1">
       <c r="A323" s="2" t="inlineStr">
         <is>
           <t>TC-322</t>
@@ -19359,7 +19359,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="324">
+    <row r="324" ht="70" customHeight="1">
       <c r="A324" s="2" t="inlineStr">
         <is>
           <t>TC-323</t>
@@ -19416,7 +19416,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="325">
+    <row r="325" ht="70" customHeight="1">
       <c r="A325" s="2" t="inlineStr">
         <is>
           <t>TC-324</t>
@@ -19473,7 +19473,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="326">
+    <row r="326" ht="70" customHeight="1">
       <c r="A326" s="2" t="inlineStr">
         <is>
           <t>TC-325</t>
@@ -19530,7 +19530,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="327">
+    <row r="327" ht="70" customHeight="1">
       <c r="A327" s="2" t="inlineStr">
         <is>
           <t>TC-326</t>
@@ -19587,7 +19587,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="328">
+    <row r="328" ht="70" customHeight="1">
       <c r="A328" s="2" t="inlineStr">
         <is>
           <t>TC-327</t>
@@ -19646,7 +19646,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="329">
+    <row r="329" ht="70" customHeight="1">
       <c r="A329" s="2" t="inlineStr">
         <is>
           <t>TC-328</t>
@@ -19704,7 +19704,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="330">
+    <row r="330" ht="70" customHeight="1">
       <c r="A330" s="2" t="inlineStr">
         <is>
           <t>TC-329</t>
@@ -19763,7 +19763,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="331">
+    <row r="331" ht="70" customHeight="1">
       <c r="A331" s="2" t="inlineStr">
         <is>
           <t>TC-330</t>
@@ -19826,7 +19826,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="332">
+    <row r="332" ht="70" customHeight="1">
       <c r="A332" s="2" t="inlineStr">
         <is>
           <t>TC-331</t>
@@ -19885,7 +19885,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="333">
+    <row r="333" ht="70" customHeight="1">
       <c r="A333" s="2" t="inlineStr">
         <is>
           <t>TC-332</t>
@@ -19944,7 +19944,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="334">
+    <row r="334" ht="70" customHeight="1">
       <c r="A334" s="2" t="inlineStr">
         <is>
           <t>TC-333</t>
@@ -20004,7 +20004,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="335">
+    <row r="335" ht="70" customHeight="1">
       <c r="A335" s="2" t="inlineStr">
         <is>
           <t>TC-334</t>
@@ -20062,7 +20062,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="336">
+    <row r="336" ht="70" customHeight="1">
       <c r="A336" s="2" t="inlineStr">
         <is>
           <t>TC-335</t>
@@ -20119,7 +20119,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="337">
+    <row r="337" ht="70" customHeight="1">
       <c r="A337" s="2" t="inlineStr">
         <is>
           <t>TC-336</t>
@@ -20176,7 +20176,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="338">
+    <row r="338" ht="70" customHeight="1">
       <c r="A338" s="2" t="inlineStr">
         <is>
           <t>TC-337</t>
@@ -20233,7 +20233,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="339">
+    <row r="339" ht="70" customHeight="1">
       <c r="A339" s="2" t="inlineStr">
         <is>
           <t>TC-338</t>
@@ -20292,7 +20292,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="340">
+    <row r="340" ht="70" customHeight="1">
       <c r="A340" s="2" t="inlineStr">
         <is>
           <t>TC-339</t>
@@ -20351,7 +20351,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="341">
+    <row r="341" ht="70" customHeight="1">
       <c r="A341" s="2" t="inlineStr">
         <is>
           <t>TC-340</t>
@@ -20408,7 +20408,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="342">
+    <row r="342" ht="70" customHeight="1">
       <c r="A342" s="2" t="inlineStr">
         <is>
           <t>TC-341</t>
@@ -20468,7 +20468,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="343">
+    <row r="343" ht="70" customHeight="1">
       <c r="A343" s="2" t="inlineStr">
         <is>
           <t>TC-342</t>
@@ -20526,7 +20526,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="344">
+    <row r="344" ht="70" customHeight="1">
       <c r="A344" s="2" t="inlineStr">
         <is>
           <t>TC-343</t>
@@ -20584,7 +20584,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="345">
+    <row r="345" ht="70" customHeight="1">
       <c r="A345" s="2" t="inlineStr">
         <is>
           <t>TC-344</t>
@@ -20640,7 +20640,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="346">
+    <row r="346" ht="70" customHeight="1">
       <c r="A346" s="2" t="inlineStr">
         <is>
           <t>TC-345</t>
@@ -20699,7 +20699,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="347">
+    <row r="347" ht="70" customHeight="1">
       <c r="A347" s="2" t="inlineStr">
         <is>
           <t>TC-346</t>
@@ -20757,7 +20757,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="348">
+    <row r="348" ht="70" customHeight="1">
       <c r="A348" s="2" t="inlineStr">
         <is>
           <t>TC-347</t>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="349">
+    <row r="349" ht="70" customHeight="1">
       <c r="A349" s="2" t="inlineStr">
         <is>
           <t>TC-348</t>
@@ -20879,7 +20879,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="350">
+    <row r="350" ht="70" customHeight="1">
       <c r="A350" s="2" t="inlineStr">
         <is>
           <t>TC-349</t>
@@ -20935,7 +20935,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="351">
+    <row r="351" ht="70" customHeight="1">
       <c r="A351" s="2" t="inlineStr">
         <is>
           <t>TC-350</t>
@@ -20992,7 +20992,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="352">
+    <row r="352" ht="70" customHeight="1">
       <c r="A352" s="2" t="inlineStr">
         <is>
           <t>TC-351</t>
@@ -21048,7 +21048,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="353">
+    <row r="353" ht="70" customHeight="1">
       <c r="A353" s="2" t="inlineStr">
         <is>
           <t>TC-352</t>
@@ -21107,7 +21107,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="354">
+    <row r="354" ht="70" customHeight="1">
       <c r="A354" s="2" t="inlineStr">
         <is>
           <t>TC-353</t>
@@ -21166,7 +21166,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="355">
+    <row r="355" ht="70" customHeight="1">
       <c r="A355" s="2" t="inlineStr">
         <is>
           <t>TC-354</t>
@@ -21229,7 +21229,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="356">
+    <row r="356" ht="70" customHeight="1">
       <c r="A356" s="2" t="inlineStr">
         <is>
           <t>TC-355</t>
@@ -21286,7 +21286,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="357">
+    <row r="357" ht="70" customHeight="1">
       <c r="A357" s="2" t="inlineStr">
         <is>
           <t>TC-356</t>
@@ -21343,7 +21343,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="358">
+    <row r="358" ht="70" customHeight="1">
       <c r="A358" s="2" t="inlineStr">
         <is>
           <t>TC-357</t>
@@ -21400,7 +21400,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="359">
+    <row r="359" ht="70" customHeight="1">
       <c r="A359" s="2" t="inlineStr">
         <is>
           <t>TC-358</t>
@@ -21459,7 +21459,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="360">
+    <row r="360" ht="70" customHeight="1">
       <c r="A360" s="2" t="inlineStr">
         <is>
           <t>TC-359</t>
@@ -21518,7 +21518,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="361">
+    <row r="361" ht="70" customHeight="1">
       <c r="A361" s="2" t="inlineStr">
         <is>
           <t>TC-360</t>
@@ -21576,7 +21576,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="362">
+    <row r="362" ht="70" customHeight="1">
       <c r="A362" s="2" t="inlineStr">
         <is>
           <t>TC-361</t>
@@ -21634,7 +21634,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="363">
+    <row r="363" ht="70" customHeight="1">
       <c r="A363" s="2" t="inlineStr">
         <is>
           <t>TC-362</t>
@@ -21693,7 +21693,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="364">
+    <row r="364" ht="70" customHeight="1">
       <c r="A364" s="2" t="inlineStr">
         <is>
           <t>TC-363</t>
@@ -21751,7 +21751,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="365">
+    <row r="365" ht="70" customHeight="1">
       <c r="A365" s="2" t="inlineStr">
         <is>
           <t>TC-364</t>
@@ -21810,7 +21810,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="366">
+    <row r="366" ht="70" customHeight="1">
       <c r="A366" s="2" t="inlineStr">
         <is>
           <t>TC-365</t>
@@ -21873,7 +21873,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="367">
+    <row r="367" ht="70" customHeight="1">
       <c r="A367" s="2" t="inlineStr">
         <is>
           <t>TC-366</t>
@@ -21932,7 +21932,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="368">
+    <row r="368" ht="70" customHeight="1">
       <c r="A368" s="2" t="inlineStr">
         <is>
           <t>TC-367</t>
@@ -21991,7 +21991,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="369">
+    <row r="369" ht="70" customHeight="1">
       <c r="A369" s="2" t="inlineStr">
         <is>
           <t>TC-368</t>
@@ -22048,7 +22048,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="370">
+    <row r="370" ht="70" customHeight="1">
       <c r="A370" s="2" t="inlineStr">
         <is>
           <t>TC-369</t>
@@ -22105,7 +22105,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="371">
+    <row r="371" ht="70" customHeight="1">
       <c r="A371" s="2" t="inlineStr">
         <is>
           <t>TC-370</t>
@@ -22164,7 +22164,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="372">
+    <row r="372" ht="70" customHeight="1">
       <c r="A372" s="2" t="inlineStr">
         <is>
           <t>TC-371</t>
@@ -22223,7 +22223,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="373">
+    <row r="373" ht="70" customHeight="1">
       <c r="A373" s="2" t="inlineStr">
         <is>
           <t>TC-372</t>
@@ -22280,7 +22280,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="374">
+    <row r="374" ht="70" customHeight="1">
       <c r="A374" s="2" t="inlineStr">
         <is>
           <t>TC-373</t>
@@ -22337,7 +22337,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="375">
+    <row r="375" ht="70" customHeight="1">
       <c r="A375" s="2" t="inlineStr">
         <is>
           <t>TC-374</t>
@@ -22394,7 +22394,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="376">
+    <row r="376" ht="70" customHeight="1">
       <c r="A376" s="2" t="inlineStr">
         <is>
           <t>TC-375</t>
@@ -22451,7 +22451,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="377">
+    <row r="377" ht="70" customHeight="1">
       <c r="A377" s="2" t="inlineStr">
         <is>
           <t>TC-376</t>
@@ -22508,7 +22508,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="378">
+    <row r="378" ht="70" customHeight="1">
       <c r="A378" s="2" t="inlineStr">
         <is>
           <t>TC-377</t>
@@ -22566,7 +22566,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="379">
+    <row r="379" ht="70" customHeight="1">
       <c r="A379" s="2" t="inlineStr">
         <is>
           <t>TC-378</t>
@@ -22624,7 +22624,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="380">
+    <row r="380" ht="70" customHeight="1">
       <c r="A380" s="2" t="inlineStr">
         <is>
           <t>TC-379</t>
@@ -22683,7 +22683,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="381">
+    <row r="381" ht="70" customHeight="1">
       <c r="A381" s="2" t="inlineStr">
         <is>
           <t>TC-380</t>
@@ -22741,7 +22741,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="382">
+    <row r="382" ht="70" customHeight="1">
       <c r="A382" s="2" t="inlineStr">
         <is>
           <t>TC-381</t>
@@ -22800,7 +22800,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="383">
+    <row r="383" ht="70" customHeight="1">
       <c r="A383" s="2" t="inlineStr">
         <is>
           <t>TC-382</t>
@@ -22861,7 +22861,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="384">
+    <row r="384" ht="70" customHeight="1">
       <c r="A384" s="2" t="inlineStr">
         <is>
           <t>TC-383</t>
@@ -22924,7 +22924,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="385">
+    <row r="385" ht="70" customHeight="1">
       <c r="A385" s="2" t="inlineStr">
         <is>
           <t>TC-384</t>
@@ -22983,7 +22983,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="386">
+    <row r="386" ht="70" customHeight="1">
       <c r="A386" s="2" t="inlineStr">
         <is>
           <t>TC-385</t>
@@ -23042,7 +23042,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="387">
+    <row r="387" ht="70" customHeight="1">
       <c r="A387" s="2" t="inlineStr">
         <is>
           <t>TC-386</t>
@@ -23099,7 +23099,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="388">
+    <row r="388" ht="70" customHeight="1">
       <c r="A388" s="2" t="inlineStr">
         <is>
           <t>TC-387</t>
@@ -23156,7 +23156,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="389">
+    <row r="389" ht="70" customHeight="1">
       <c r="A389" s="2" t="inlineStr">
         <is>
           <t>TC-388</t>
@@ -23215,7 +23215,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="390">
+    <row r="390" ht="70" customHeight="1">
       <c r="A390" s="2" t="inlineStr">
         <is>
           <t>TC-389</t>
@@ -23274,7 +23274,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="391">
+    <row r="391" ht="70" customHeight="1">
       <c r="A391" s="2" t="inlineStr">
         <is>
           <t>TC-390</t>
@@ -23331,7 +23331,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="392">
+    <row r="392" ht="70" customHeight="1">
       <c r="A392" s="2" t="inlineStr">
         <is>
           <t>TC-391</t>
@@ -23389,7 +23389,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="393">
+    <row r="393" ht="70" customHeight="1">
       <c r="A393" s="2" t="inlineStr">
         <is>
           <t>TC-392</t>
@@ -23447,7 +23447,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="394">
+    <row r="394" ht="70" customHeight="1">
       <c r="A394" s="2" t="inlineStr">
         <is>
           <t>TC-393</t>
@@ -23508,7 +23508,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="395">
+    <row r="395" ht="70" customHeight="1">
       <c r="A395" s="2" t="inlineStr">
         <is>
           <t>TC-394</t>
@@ -23567,7 +23567,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="396">
+    <row r="396" ht="70" customHeight="1">
       <c r="A396" s="2" t="inlineStr">
         <is>
           <t>TC-395</t>
@@ -23625,7 +23625,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="397">
+    <row r="397" ht="70" customHeight="1">
       <c r="A397" s="2" t="inlineStr">
         <is>
           <t>TC-396</t>
@@ -23684,7 +23684,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="398">
+    <row r="398" ht="70" customHeight="1">
       <c r="A398" s="2" t="inlineStr">
         <is>
           <t>TC-397</t>
@@ -23747,7 +23747,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="399">
+    <row r="399" ht="70" customHeight="1">
       <c r="A399" s="2" t="inlineStr">
         <is>
           <t>TC-398</t>
@@ -23806,7 +23806,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="400">
+    <row r="400" ht="70" customHeight="1">
       <c r="A400" s="2" t="inlineStr">
         <is>
           <t>TC-399</t>
@@ -23865,7 +23865,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="401">
+    <row r="401" ht="70" customHeight="1">
       <c r="A401" s="2" t="inlineStr">
         <is>
           <t>TC-400</t>
@@ -23922,7 +23922,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="402">
+    <row r="402" ht="70" customHeight="1">
       <c r="A402" s="2" t="inlineStr">
         <is>
           <t>TC-401</t>
@@ -23979,7 +23979,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="403">
+    <row r="403" ht="70" customHeight="1">
       <c r="A403" s="2" t="inlineStr">
         <is>
           <t>TC-402</t>
@@ -24038,7 +24038,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="404">
+    <row r="404" ht="70" customHeight="1">
       <c r="A404" s="2" t="inlineStr">
         <is>
           <t>TC-403</t>
@@ -24097,7 +24097,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="405">
+    <row r="405" ht="70" customHeight="1">
       <c r="A405" s="2" t="inlineStr">
         <is>
           <t>TC-404</t>
@@ -24155,7 +24155,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="406">
+    <row r="406" ht="70" customHeight="1">
       <c r="A406" s="2" t="inlineStr">
         <is>
           <t>TC-405</t>
@@ -24213,7 +24213,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="407">
+    <row r="407" ht="70" customHeight="1">
       <c r="A407" s="2" t="inlineStr">
         <is>
           <t>TC-406</t>
@@ -24270,7 +24270,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="408">
+    <row r="408" ht="70" customHeight="1">
       <c r="A408" s="2" t="inlineStr">
         <is>
           <t>TC-407</t>
@@ -24327,7 +24327,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="409">
+    <row r="409" ht="70" customHeight="1">
       <c r="A409" s="2" t="inlineStr">
         <is>
           <t>TC-408</t>
@@ -24384,7 +24384,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="410">
+    <row r="410" ht="70" customHeight="1">
       <c r="A410" s="2" t="inlineStr">
         <is>
           <t>TC-409</t>
@@ -24441,7 +24441,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="411">
+    <row r="411" ht="70" customHeight="1">
       <c r="A411" s="2" t="inlineStr">
         <is>
           <t>TC-410</t>
@@ -24498,7 +24498,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="412">
+    <row r="412" ht="70" customHeight="1">
       <c r="A412" s="2" t="inlineStr">
         <is>
           <t>TC-411</t>
@@ -24557,7 +24557,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="413">
+    <row r="413" ht="70" customHeight="1">
       <c r="A413" s="2" t="inlineStr">
         <is>
           <t>TC-412</t>
@@ -24615,7 +24615,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="414">
+    <row r="414" ht="70" customHeight="1">
       <c r="A414" s="2" t="inlineStr">
         <is>
           <t>TC-413</t>
@@ -24674,7 +24674,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="415">
+    <row r="415" ht="70" customHeight="1">
       <c r="A415" s="2" t="inlineStr">
         <is>
           <t>TC-414</t>
@@ -24735,7 +24735,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="416">
+    <row r="416" ht="70" customHeight="1">
       <c r="A416" s="2" t="inlineStr">
         <is>
           <t>TC-415</t>
@@ -24798,7 +24798,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="417">
+    <row r="417" ht="70" customHeight="1">
       <c r="A417" s="2" t="inlineStr">
         <is>
           <t>TC-416</t>
@@ -24857,7 +24857,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="418">
+    <row r="418" ht="70" customHeight="1">
       <c r="A418" s="2" t="inlineStr">
         <is>
           <t>TC-417</t>
@@ -24916,7 +24916,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="419">
+    <row r="419" ht="70" customHeight="1">
       <c r="A419" s="2" t="inlineStr">
         <is>
           <t>TC-418</t>
@@ -24973,7 +24973,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="420">
+    <row r="420" ht="70" customHeight="1">
       <c r="A420" s="2" t="inlineStr">
         <is>
           <t>TC-419</t>
@@ -25030,7 +25030,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="421">
+    <row r="421" ht="70" customHeight="1">
       <c r="A421" s="2" t="inlineStr">
         <is>
           <t>TC-420</t>
@@ -25089,7 +25089,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="422">
+    <row r="422" ht="70" customHeight="1">
       <c r="A422" s="2" t="inlineStr">
         <is>
           <t>TC-421</t>
@@ -25148,7 +25148,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="423">
+    <row r="423" ht="70" customHeight="1">
       <c r="A423" s="2" t="inlineStr">
         <is>
           <t>TC-422</t>
@@ -25205,7 +25205,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="424">
+    <row r="424" ht="70" customHeight="1">
       <c r="A424" s="2" t="inlineStr">
         <is>
           <t>TC-423</t>
@@ -25263,7 +25263,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="425">
+    <row r="425" ht="70" customHeight="1">
       <c r="A425" s="2" t="inlineStr">
         <is>
           <t>TC-424</t>
@@ -25321,7 +25321,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="426">
+    <row r="426" ht="70" customHeight="1">
       <c r="A426" s="2" t="inlineStr">
         <is>
           <t>TC-425</t>
@@ -25382,7 +25382,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="427">
+    <row r="427" ht="70" customHeight="1">
       <c r="A427" s="2" t="inlineStr">
         <is>
           <t>TC-426</t>
@@ -25441,7 +25441,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="428">
+    <row r="428" ht="70" customHeight="1">
       <c r="A428" s="2" t="inlineStr">
         <is>
           <t>TC-427</t>
@@ -25499,7 +25499,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="429">
+    <row r="429" ht="70" customHeight="1">
       <c r="A429" s="2" t="inlineStr">
         <is>
           <t>TC-428</t>
@@ -25558,7 +25558,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="430">
+    <row r="430" ht="70" customHeight="1">
       <c r="A430" s="2" t="inlineStr">
         <is>
           <t>TC-429</t>
@@ -25621,7 +25621,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="431">
+    <row r="431" ht="70" customHeight="1">
       <c r="A431" s="2" t="inlineStr">
         <is>
           <t>TC-430</t>
@@ -25680,7 +25680,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="432">
+    <row r="432" ht="70" customHeight="1">
       <c r="A432" s="2" t="inlineStr">
         <is>
           <t>TC-431</t>
@@ -25739,7 +25739,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="433">
+    <row r="433" ht="70" customHeight="1">
       <c r="A433" s="2" t="inlineStr">
         <is>
           <t>TC-432</t>
@@ -25800,7 +25800,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="434">
+    <row r="434" ht="70" customHeight="1">
       <c r="A434" s="2" t="inlineStr">
         <is>
           <t>TC-433</t>
@@ -25857,7 +25857,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="435">
+    <row r="435" ht="70" customHeight="1">
       <c r="A435" s="2" t="inlineStr">
         <is>
           <t>TC-434</t>
@@ -25914,7 +25914,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="436">
+    <row r="436" ht="70" customHeight="1">
       <c r="A436" s="2" t="inlineStr">
         <is>
           <t>TC-435</t>
@@ -25971,7 +25971,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="437">
+    <row r="437" ht="70" customHeight="1">
       <c r="A437" s="2" t="inlineStr">
         <is>
           <t>TC-436</t>
@@ -26030,7 +26030,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="438">
+    <row r="438" ht="70" customHeight="1">
       <c r="A438" s="2" t="inlineStr">
         <is>
           <t>TC-437</t>
@@ -26089,7 +26089,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="439">
+    <row r="439" ht="70" customHeight="1">
       <c r="A439" s="2" t="inlineStr">
         <is>
           <t>TC-438</t>
@@ -26147,7 +26147,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="440">
+    <row r="440" ht="70" customHeight="1">
       <c r="A440" s="2" t="inlineStr">
         <is>
           <t>TC-439</t>
@@ -26205,7 +26205,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="441">
+    <row r="441" ht="70" customHeight="1">
       <c r="A441" s="2" t="inlineStr">
         <is>
           <t>TC-440</t>
@@ -26264,7 +26264,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="442">
+    <row r="442" ht="70" customHeight="1">
       <c r="A442" s="2" t="inlineStr">
         <is>
           <t>TC-441</t>
@@ -26322,7 +26322,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="443">
+    <row r="443" ht="70" customHeight="1">
       <c r="A443" s="2" t="inlineStr">
         <is>
           <t>TC-442</t>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="444">
+    <row r="444" ht="70" customHeight="1">
       <c r="A444" s="2" t="inlineStr">
         <is>
           <t>TC-443</t>
@@ -26444,7 +26444,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="445">
+    <row r="445" ht="70" customHeight="1">
       <c r="A445" s="2" t="inlineStr">
         <is>
           <t>TC-444</t>
@@ -26503,7 +26503,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="446">
+    <row r="446" ht="70" customHeight="1">
       <c r="A446" s="2" t="inlineStr">
         <is>
           <t>TC-445</t>
@@ -26562,7 +26562,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="447">
+    <row r="447" ht="70" customHeight="1">
       <c r="A447" s="2" t="inlineStr">
         <is>
           <t>TC-446</t>
@@ -26625,7 +26625,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="448">
+    <row r="448" ht="70" customHeight="1">
       <c r="A448" s="2" t="inlineStr">
         <is>
           <t>TC-447</t>
@@ -26684,7 +26684,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="449">
+    <row r="449" ht="70" customHeight="1">
       <c r="A449" s="2" t="inlineStr">
         <is>
           <t>TC-448</t>
@@ -26743,7 +26743,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="450">
+    <row r="450" ht="70" customHeight="1">
       <c r="A450" s="2" t="inlineStr">
         <is>
           <t>TC-449</t>
@@ -26801,7 +26801,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="451">
+    <row r="451" ht="70" customHeight="1">
       <c r="A451" s="2" t="inlineStr">
         <is>
           <t>TC-450</t>
@@ -26859,7 +26859,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="452">
+    <row r="452" ht="70" customHeight="1">
       <c r="A452" s="2" t="inlineStr">
         <is>
           <t>TC-451</t>
@@ -26918,7 +26918,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="453">
+    <row r="453" ht="70" customHeight="1">
       <c r="A453" s="2" t="inlineStr">
         <is>
           <t>TC-452</t>
@@ -26975,7 +26975,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="454">
+    <row r="454" ht="70" customHeight="1">
       <c r="A454" s="2" t="inlineStr">
         <is>
           <t>TC-453</t>
@@ -27032,7 +27032,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="455">
+    <row r="455" ht="70" customHeight="1">
       <c r="A455" s="2" t="inlineStr">
         <is>
           <t>TC-454</t>
@@ -27089,7 +27089,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="456">
+    <row r="456" ht="70" customHeight="1">
       <c r="A456" s="2" t="inlineStr">
         <is>
           <t>TC-455</t>
@@ -27148,7 +27148,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="457">
+    <row r="457" ht="70" customHeight="1">
       <c r="A457" s="2" t="inlineStr">
         <is>
           <t>TC-456</t>
@@ -27206,7 +27206,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="458">
+    <row r="458" ht="70" customHeight="1">
       <c r="A458" s="2" t="inlineStr">
         <is>
           <t>TC-457</t>
@@ -27265,7 +27265,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="459">
+    <row r="459" ht="70" customHeight="1">
       <c r="A459" s="2" t="inlineStr">
         <is>
           <t>TC-458</t>
@@ -27328,7 +27328,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="460">
+    <row r="460" ht="70" customHeight="1">
       <c r="A460" s="2" t="inlineStr">
         <is>
           <t>TC-459</t>
@@ -27387,7 +27387,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="461">
+    <row r="461" ht="70" customHeight="1">
       <c r="A461" s="2" t="inlineStr">
         <is>
           <t>TC-460</t>
@@ -27446,7 +27446,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="462">
+    <row r="462" ht="70" customHeight="1">
       <c r="A462" s="2" t="inlineStr">
         <is>
           <t>TC-461</t>
@@ -27507,7 +27507,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="463">
+    <row r="463" ht="70" customHeight="1">
       <c r="A463" s="2" t="inlineStr">
         <is>
           <t>TC-462</t>
@@ -27564,7 +27564,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="464">
+    <row r="464" ht="70" customHeight="1">
       <c r="A464" s="2" t="inlineStr">
         <is>
           <t>TC-463</t>
@@ -27621,7 +27621,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="465">
+    <row r="465" ht="70" customHeight="1">
       <c r="A465" s="2" t="inlineStr">
         <is>
           <t>TC-464</t>
@@ -27678,7 +27678,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="466">
+    <row r="466" ht="70" customHeight="1">
       <c r="A466" s="2" t="inlineStr">
         <is>
           <t>TC-465</t>
@@ -27737,7 +27737,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="467">
+    <row r="467" ht="70" customHeight="1">
       <c r="A467" s="2" t="inlineStr">
         <is>
           <t>TC-466</t>
@@ -27796,7 +27796,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="468">
+    <row r="468" ht="70" customHeight="1">
       <c r="A468" s="2" t="inlineStr">
         <is>
           <t>TC-467</t>
@@ -27854,7 +27854,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="469">
+    <row r="469" ht="70" customHeight="1">
       <c r="A469" s="2" t="inlineStr">
         <is>
           <t>TC-468</t>
@@ -27912,7 +27912,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="470">
+    <row r="470" ht="70" customHeight="1">
       <c r="A470" s="2" t="inlineStr">
         <is>
           <t>TC-469</t>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="471">
+    <row r="471" ht="70" customHeight="1">
       <c r="A471" s="2" t="inlineStr">
         <is>
           <t>TC-470</t>
@@ -28029,7 +28029,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="472">
+    <row r="472" ht="70" customHeight="1">
       <c r="A472" s="2" t="inlineStr">
         <is>
           <t>TC-471</t>
@@ -28088,7 +28088,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="473">
+    <row r="473" ht="70" customHeight="1">
       <c r="A473" s="2" t="inlineStr">
         <is>
           <t>TC-472</t>
@@ -28151,7 +28151,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="474">
+    <row r="474" ht="70" customHeight="1">
       <c r="A474" s="2" t="inlineStr">
         <is>
           <t>TC-473</t>
@@ -28210,7 +28210,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="475">
+    <row r="475" ht="70" customHeight="1">
       <c r="A475" s="2" t="inlineStr">
         <is>
           <t>TC-474</t>
@@ -28269,7 +28269,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="476">
+    <row r="476" ht="70" customHeight="1">
       <c r="A476" s="2" t="inlineStr">
         <is>
           <t>TC-475</t>
@@ -28330,7 +28330,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="477">
+    <row r="477" ht="70" customHeight="1">
       <c r="A477" s="2" t="inlineStr">
         <is>
           <t>TC-476</t>
@@ -28389,7 +28389,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="478">
+    <row r="478" ht="70" customHeight="1">
       <c r="A478" s="2" t="inlineStr">
         <is>
           <t>TC-477</t>
@@ -28448,7 +28448,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="479">
+    <row r="479" ht="70" customHeight="1">
       <c r="A479" s="2" t="inlineStr">
         <is>
           <t>TC-478</t>
@@ -28505,7 +28505,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="480">
+    <row r="480" ht="70" customHeight="1">
       <c r="A480" s="2" t="inlineStr">
         <is>
           <t>TC-479</t>
@@ -28562,7 +28562,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="481">
+    <row r="481" ht="70" customHeight="1">
       <c r="A481" s="2" t="inlineStr">
         <is>
           <t>TC-480</t>
@@ -28619,7 +28619,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="482">
+    <row r="482" ht="70" customHeight="1">
       <c r="A482" s="2" t="inlineStr">
         <is>
           <t>TC-481</t>
@@ -28677,7 +28677,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="483">
+    <row r="483" ht="70" customHeight="1">
       <c r="A483" s="2" t="inlineStr">
         <is>
           <t>TC-482</t>
@@ -28735,7 +28735,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="484">
+    <row r="484" ht="70" customHeight="1">
       <c r="A484" s="2" t="inlineStr">
         <is>
           <t>TC-483</t>
@@ -28794,7 +28794,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="485">
+    <row r="485" ht="70" customHeight="1">
       <c r="A485" s="2" t="inlineStr">
         <is>
           <t>TC-484</t>
@@ -28852,7 +28852,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="486">
+    <row r="486" ht="70" customHeight="1">
       <c r="A486" s="2" t="inlineStr">
         <is>
           <t>TC-485</t>
@@ -28911,7 +28911,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="487">
+    <row r="487" ht="70" customHeight="1">
       <c r="A487" s="2" t="inlineStr">
         <is>
           <t>TC-486</t>
@@ -28974,7 +28974,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="488">
+    <row r="488" ht="70" customHeight="1">
       <c r="A488" s="2" t="inlineStr">
         <is>
           <t>TC-487</t>
@@ -29033,7 +29033,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="489">
+    <row r="489" ht="70" customHeight="1">
       <c r="A489" s="2" t="inlineStr">
         <is>
           <t>TC-488</t>
@@ -29092,7 +29092,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="490">
+    <row r="490" ht="70" customHeight="1">
       <c r="A490" s="2" t="inlineStr">
         <is>
           <t>TC-489</t>
@@ -29149,7 +29149,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="491">
+    <row r="491" ht="70" customHeight="1">
       <c r="A491" s="2" t="inlineStr">
         <is>
           <t>TC-490</t>
@@ -29206,7 +29206,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="492">
+    <row r="492" ht="70" customHeight="1">
       <c r="A492" s="2" t="inlineStr">
         <is>
           <t>TC-491</t>
@@ -29263,7 +29263,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="493">
+    <row r="493" ht="70" customHeight="1">
       <c r="A493" s="2" t="inlineStr">
         <is>
           <t>TC-492</t>
@@ -29322,7 +29322,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="494">
+    <row r="494" ht="70" customHeight="1">
       <c r="A494" s="2" t="inlineStr">
         <is>
           <t>TC-493</t>
@@ -29381,7 +29381,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="495">
+    <row r="495" ht="70" customHeight="1">
       <c r="A495" s="2" t="inlineStr">
         <is>
           <t>TC-494</t>
@@ -29439,7 +29439,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="496">
+    <row r="496" ht="70" customHeight="1">
       <c r="A496" s="2" t="inlineStr">
         <is>
           <t>TC-495</t>
@@ -29497,7 +29497,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="497">
+    <row r="497" ht="70" customHeight="1">
       <c r="A497" s="2" t="inlineStr">
         <is>
           <t>TC-496</t>
@@ -29556,7 +29556,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="498">
+    <row r="498" ht="70" customHeight="1">
       <c r="A498" s="2" t="inlineStr">
         <is>
           <t>TC-497</t>
@@ -29614,7 +29614,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="499">
+    <row r="499" ht="70" customHeight="1">
       <c r="A499" s="2" t="inlineStr">
         <is>
           <t>TC-498</t>
@@ -29673,7 +29673,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="500">
+    <row r="500" ht="70" customHeight="1">
       <c r="A500" s="2" t="inlineStr">
         <is>
           <t>TC-499</t>
@@ -29734,7 +29734,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="501">
+    <row r="501" ht="70" customHeight="1">
       <c r="A501" s="2" t="inlineStr">
         <is>
           <t>TC-500</t>
@@ -29797,7 +29797,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="502">
+    <row r="502" ht="70" customHeight="1">
       <c r="A502" s="2" t="inlineStr">
         <is>
           <t>TC-501</t>
@@ -29856,7 +29856,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="503">
+    <row r="503" ht="70" customHeight="1">
       <c r="A503" s="2" t="inlineStr">
         <is>
           <t>TC-502</t>
@@ -29915,7 +29915,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="504">
+    <row r="504" ht="70" customHeight="1">
       <c r="A504" s="2" t="inlineStr">
         <is>
           <t>TC-503</t>
@@ -29972,7 +29972,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="505">
+    <row r="505" ht="70" customHeight="1">
       <c r="A505" s="2" t="inlineStr">
         <is>
           <t>TC-504</t>
@@ -30029,7 +30029,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="506">
+    <row r="506" ht="70" customHeight="1">
       <c r="A506" s="2" t="inlineStr">
         <is>
           <t>TC-505</t>
@@ -30086,7 +30086,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="507">
+    <row r="507" ht="70" customHeight="1">
       <c r="A507" s="2" t="inlineStr">
         <is>
           <t>TC-506</t>
@@ -30145,7 +30145,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="508">
+    <row r="508" ht="70" customHeight="1">
       <c r="A508" s="2" t="inlineStr">
         <is>
           <t>TC-507</t>
@@ -30204,7 +30204,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="509">
+    <row r="509" ht="70" customHeight="1">
       <c r="A509" s="2" t="inlineStr">
         <is>
           <t>TC-508</t>
@@ -30262,7 +30262,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="510">
+    <row r="510" ht="70" customHeight="1">
       <c r="A510" s="2" t="inlineStr">
         <is>
           <t>TC-509</t>
@@ -30320,7 +30320,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="511">
+    <row r="511" ht="70" customHeight="1">
       <c r="A511" s="2" t="inlineStr">
         <is>
           <t>TC-510</t>
@@ -30381,7 +30381,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="512">
+    <row r="512" ht="70" customHeight="1">
       <c r="A512" s="2" t="inlineStr">
         <is>
           <t>TC-511</t>
@@ -30440,7 +30440,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="513">
+    <row r="513" ht="70" customHeight="1">
       <c r="A513" s="2" t="inlineStr">
         <is>
           <t>TC-512</t>
@@ -30498,7 +30498,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="514">
+    <row r="514" ht="70" customHeight="1">
       <c r="A514" s="2" t="inlineStr">
         <is>
           <t>TC-513</t>
@@ -30557,7 +30557,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="515">
+    <row r="515" ht="70" customHeight="1">
       <c r="A515" s="2" t="inlineStr">
         <is>
           <t>TC-514</t>
@@ -30620,7 +30620,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="516">
+    <row r="516" ht="70" customHeight="1">
       <c r="A516" s="2" t="inlineStr">
         <is>
           <t>TC-515</t>
@@ -30679,7 +30679,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="517">
+    <row r="517" ht="70" customHeight="1">
       <c r="A517" s="2" t="inlineStr">
         <is>
           <t>TC-516</t>
@@ -30738,7 +30738,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="518">
+    <row r="518" ht="70" customHeight="1">
       <c r="A518" s="2" t="inlineStr">
         <is>
           <t>TC-517</t>
@@ -30797,7 +30797,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="519">
+    <row r="519" ht="70" customHeight="1">
       <c r="A519" s="2" t="inlineStr">
         <is>
           <t>TC-518</t>
@@ -30856,7 +30856,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="520">
+    <row r="520" ht="70" customHeight="1">
       <c r="A520" s="2" t="inlineStr">
         <is>
           <t>TC-519</t>
@@ -30915,7 +30915,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="521">
+    <row r="521" ht="70" customHeight="1">
       <c r="A521" s="2" t="inlineStr">
         <is>
           <t>TC-520</t>
@@ -30974,7 +30974,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="522">
+    <row r="522" ht="70" customHeight="1">
       <c r="A522" s="2" t="inlineStr">
         <is>
           <t>TC-521</t>
@@ -31033,7 +31033,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="523">
+    <row r="523" ht="70" customHeight="1">
       <c r="A523" s="2" t="inlineStr">
         <is>
           <t>TC-522</t>
@@ -31092,7 +31092,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="524">
+    <row r="524" ht="70" customHeight="1">
       <c r="A524" s="2" t="inlineStr">
         <is>
           <t>TC-523</t>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="525">
+    <row r="525" ht="70" customHeight="1">
       <c r="A525" s="2" t="inlineStr">
         <is>
           <t>TC-524</t>
@@ -31210,7 +31210,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="526">
+    <row r="526" ht="70" customHeight="1">
       <c r="A526" s="2" t="inlineStr">
         <is>
           <t>TC-525</t>
@@ -31270,7 +31270,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="527">
+    <row r="527" ht="70" customHeight="1">
       <c r="A527" s="2" t="inlineStr">
         <is>
           <t>TC-526</t>
@@ -31329,7 +31329,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="528">
+    <row r="528" ht="70" customHeight="1">
       <c r="A528" s="2" t="inlineStr">
         <is>
           <t>TC-527</t>
@@ -31389,7 +31389,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="529">
+    <row r="529" ht="70" customHeight="1">
       <c r="A529" s="2" t="inlineStr">
         <is>
           <t>TC-528</t>
@@ -31448,7 +31448,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="530">
+    <row r="530" ht="70" customHeight="1">
       <c r="A530" s="2" t="inlineStr">
         <is>
           <t>TC-529</t>
@@ -31508,7 +31508,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="531">
+    <row r="531" ht="70" customHeight="1">
       <c r="A531" s="2" t="inlineStr">
         <is>
           <t>TC-530</t>
@@ -31568,7 +31568,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="532">
+    <row r="532" ht="70" customHeight="1">
       <c r="A532" s="2" t="inlineStr">
         <is>
           <t>TC-531</t>
@@ -31631,7 +31631,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="533">
+    <row r="533" ht="70" customHeight="1">
       <c r="A533" s="2" t="inlineStr">
         <is>
           <t>TC-532</t>
@@ -31691,7 +31691,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="534">
+    <row r="534" ht="70" customHeight="1">
       <c r="A534" s="2" t="inlineStr">
         <is>
           <t>TC-533</t>
@@ -31752,7 +31752,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="535">
+    <row r="535" ht="70" customHeight="1">
       <c r="A535" s="2" t="inlineStr">
         <is>
           <t>TC-534</t>
@@ -31812,7 +31812,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="536">
+    <row r="536" ht="70" customHeight="1">
       <c r="A536" s="2" t="inlineStr">
         <is>
           <t>TC-535</t>
@@ -31872,7 +31872,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="537">
+    <row r="537" ht="70" customHeight="1">
       <c r="A537" s="2" t="inlineStr">
         <is>
           <t>TC-536</t>
@@ -31932,7 +31932,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="538">
+    <row r="538" ht="70" customHeight="1">
       <c r="A538" s="2" t="inlineStr">
         <is>
           <t>TC-537</t>
@@ -31991,7 +31991,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="539">
+    <row r="539" ht="70" customHeight="1">
       <c r="A539" s="2" t="inlineStr">
         <is>
           <t>TC-538</t>
@@ -32051,7 +32051,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="540">
+    <row r="540" ht="70" customHeight="1">
       <c r="A540" s="2" t="inlineStr">
         <is>
           <t>TC-539</t>
@@ -32110,7 +32110,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="541">
+    <row r="541" ht="70" customHeight="1">
       <c r="A541" s="2" t="inlineStr">
         <is>
           <t>TC-540</t>
@@ -32164,7 +32164,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="542">
+    <row r="542" ht="70" customHeight="1">
       <c r="A542" s="2" t="inlineStr">
         <is>
           <t>TC-541</t>
@@ -32223,7 +32223,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="543">
+    <row r="543" ht="70" customHeight="1">
       <c r="A543" s="2" t="inlineStr">
         <is>
           <t>TC-542</t>
@@ -32278,7 +32278,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="544">
+    <row r="544" ht="70" customHeight="1">
       <c r="A544" s="2" t="inlineStr">
         <is>
           <t>TC-543</t>
@@ -32334,7 +32334,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="545">
+    <row r="545" ht="70" customHeight="1">
       <c r="A545" s="2" t="inlineStr">
         <is>
           <t>TC-544</t>
@@ -32391,7 +32391,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="546">
+    <row r="546" ht="70" customHeight="1">
       <c r="A546" s="2" t="inlineStr">
         <is>
           <t>TC-545</t>
@@ -32447,7 +32447,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="547">
+    <row r="547" ht="70" customHeight="1">
       <c r="A547" s="2" t="inlineStr">
         <is>
           <t>TC-546</t>
@@ -32502,7 +32502,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="548">
+    <row r="548" ht="70" customHeight="1">
       <c r="A548" s="2" t="inlineStr">
         <is>
           <t>TC-547</t>
@@ -32559,7 +32559,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="549">
+    <row r="549" ht="70" customHeight="1">
       <c r="A549" s="2" t="inlineStr">
         <is>
           <t>TC-548</t>
@@ -32614,7 +32614,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="550">
+    <row r="550" ht="70" customHeight="1">
       <c r="A550" s="2" t="inlineStr">
         <is>
           <t>TC-549</t>
@@ -32671,7 +32671,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="551">
+    <row r="551" ht="70" customHeight="1">
       <c r="A551" s="2" t="inlineStr">
         <is>
           <t>TC-550</t>
@@ -32730,7 +32730,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="552">
+    <row r="552" ht="70" customHeight="1">
       <c r="A552" s="2" t="inlineStr">
         <is>
           <t>TC-551</t>
@@ -32786,7 +32786,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="553">
+    <row r="553" ht="70" customHeight="1">
       <c r="A553" s="2" t="inlineStr">
         <is>
           <t>TC-552</t>
@@ -32846,7 +32846,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="554">
+    <row r="554" ht="70" customHeight="1">
       <c r="A554" s="2" t="inlineStr">
         <is>
           <t>TC-553</t>
@@ -32906,7 +32906,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="555">
+    <row r="555" ht="70" customHeight="1">
       <c r="A555" s="2" t="inlineStr">
         <is>
           <t>TC-554</t>
@@ -32966,7 +32966,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="556">
+    <row r="556" ht="70" customHeight="1">
       <c r="A556" s="2" t="inlineStr">
         <is>
           <t>TC-555</t>
@@ -33026,7 +33026,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="557">
+    <row r="557" ht="70" customHeight="1">
       <c r="A557" s="2" t="inlineStr">
         <is>
           <t>TC-556</t>
@@ -33085,7 +33085,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="558">
+    <row r="558" ht="70" customHeight="1">
       <c r="A558" s="2" t="inlineStr">
         <is>
           <t>TC-557</t>
@@ -33144,7 +33144,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="559">
+    <row r="559" ht="70" customHeight="1">
       <c r="A559" s="2" t="inlineStr">
         <is>
           <t>TC-558</t>
@@ -33204,7 +33204,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="560">
+    <row r="560" ht="70" customHeight="1">
       <c r="A560" s="2" t="inlineStr">
         <is>
           <t>TC-559</t>
@@ -33264,7 +33264,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="561">
+    <row r="561" ht="70" customHeight="1">
       <c r="A561" s="2" t="inlineStr">
         <is>
           <t>TC-560</t>
@@ -33333,7 +33333,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="562">
+    <row r="562" ht="70" customHeight="1">
       <c r="A562" s="2" t="inlineStr">
         <is>
           <t>TC-561</t>
@@ -33392,7 +33392,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="563">
+    <row r="563" ht="70" customHeight="1">
       <c r="A563" s="2" t="inlineStr">
         <is>
           <t>TC-562</t>
@@ -33451,7 +33451,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="564">
+    <row r="564" ht="70" customHeight="1">
       <c r="A564" s="2" t="inlineStr">
         <is>
           <t>TC-563</t>
@@ -33507,7 +33507,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="565">
+    <row r="565" ht="70" customHeight="1">
       <c r="A565" s="2" t="inlineStr">
         <is>
           <t>TC-564</t>
@@ -33563,7 +33563,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="566">
+    <row r="566" ht="70" customHeight="1">
       <c r="A566" s="2" t="inlineStr">
         <is>
           <t>TC-565</t>
@@ -33623,7 +33623,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="567">
+    <row r="567" ht="70" customHeight="1">
       <c r="A567" s="2" t="inlineStr">
         <is>
           <t>TC-566</t>
@@ -33680,7 +33680,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="568">
+    <row r="568" ht="70" customHeight="1">
       <c r="A568" s="2" t="inlineStr">
         <is>
           <t>TC-567</t>
@@ -33738,7 +33738,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="569">
+    <row r="569" ht="70" customHeight="1">
       <c r="A569" s="2" t="inlineStr">
         <is>
           <t>TC-568</t>
@@ -33794,7 +33794,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="570">
+    <row r="570" ht="70" customHeight="1">
       <c r="A570" s="2" t="inlineStr">
         <is>
           <t>TC-569</t>
@@ -33851,7 +33851,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="571">
+    <row r="571" ht="70" customHeight="1">
       <c r="A571" s="2" t="inlineStr">
         <is>
           <t>TC-570</t>
@@ -33911,7 +33911,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="572">
+    <row r="572" ht="70" customHeight="1">
       <c r="A572" s="2" t="inlineStr">
         <is>
           <t>TC-571</t>
@@ -33968,7 +33968,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="573">
+    <row r="573" ht="70" customHeight="1">
       <c r="A573" s="2" t="inlineStr">
         <is>
           <t>TC-572</t>
@@ -34025,7 +34025,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="574">
+    <row r="574" ht="70" customHeight="1">
       <c r="A574" s="2" t="inlineStr">
         <is>
           <t>TC-573</t>
@@ -34080,7 +34080,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="575">
+    <row r="575" ht="70" customHeight="1">
       <c r="A575" s="2" t="inlineStr">
         <is>
           <t>TC-574</t>
@@ -34141,7 +34141,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="576">
+    <row r="576" ht="70" customHeight="1">
       <c r="A576" s="2" t="inlineStr">
         <is>
           <t>TC-575</t>
@@ -34196,7 +34196,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="577">
+    <row r="577" ht="70" customHeight="1">
       <c r="A577" s="2" t="inlineStr">
         <is>
           <t>TC-576</t>
@@ -34256,7 +34256,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="578">
+    <row r="578" ht="70" customHeight="1">
       <c r="A578" s="2" t="inlineStr">
         <is>
           <t>TC-577</t>
@@ -34312,7 +34312,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="579">
+    <row r="579" ht="70" customHeight="1">
       <c r="A579" s="2" t="inlineStr">
         <is>
           <t>TC-578</t>
@@ -34369,7 +34369,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="580">
+    <row r="580" ht="70" customHeight="1">
       <c r="A580" s="2" t="inlineStr">
         <is>
           <t>TC-579</t>
@@ -34424,7 +34424,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="581">
+    <row r="581" ht="70" customHeight="1">
       <c r="A581" s="2" t="inlineStr">
         <is>
           <t>TC-580</t>
@@ -34480,7 +34480,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="582">
+    <row r="582" ht="70" customHeight="1">
       <c r="A582" s="2" t="inlineStr">
         <is>
           <t>TC-581</t>
@@ -34535,7 +34535,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="583">
+    <row r="583" ht="70" customHeight="1">
       <c r="A583" s="2" t="inlineStr">
         <is>
           <t>TC-582</t>
@@ -34595,7 +34595,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="584">
+    <row r="584" ht="70" customHeight="1">
       <c r="A584" s="2" t="inlineStr">
         <is>
           <t>TC-583</t>
@@ -34652,7 +34652,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="585">
+    <row r="585" ht="70" customHeight="1">
       <c r="A585" s="2" t="inlineStr">
         <is>
           <t>TC-584</t>
@@ -34713,7 +34713,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="586">
+    <row r="586" ht="70" customHeight="1">
       <c r="A586" s="2" t="inlineStr">
         <is>
           <t>TC-585</t>
@@ -34774,7 +34774,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="587">
+    <row r="587" ht="70" customHeight="1">
       <c r="A587" s="2" t="inlineStr">
         <is>
           <t>TC-586</t>
@@ -34830,7 +34830,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="588">
+    <row r="588" ht="70" customHeight="1">
       <c r="A588" s="2" t="inlineStr">
         <is>
           <t>TC-587</t>
@@ -34886,7 +34886,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="589">
+    <row r="589" ht="70" customHeight="1">
       <c r="A589" s="2" t="inlineStr">
         <is>
           <t>TC-588</t>
@@ -34942,7 +34942,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="590">
+    <row r="590" ht="70" customHeight="1">
       <c r="A590" s="2" t="inlineStr">
         <is>
           <t>TC-589</t>
@@ -34998,7 +34998,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="591">
+    <row r="591" ht="70" customHeight="1">
       <c r="A591" s="2" t="inlineStr">
         <is>
           <t>TC-590</t>
@@ -35054,7 +35054,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="592">
+    <row r="592" ht="70" customHeight="1">
       <c r="A592" s="2" t="inlineStr">
         <is>
           <t>TC-591</t>
@@ -35110,7 +35110,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="593">
+    <row r="593" ht="70" customHeight="1">
       <c r="A593" s="2" t="inlineStr">
         <is>
           <t>TC-592</t>
@@ -35171,7 +35171,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="594">
+    <row r="594" ht="70" customHeight="1">
       <c r="A594" s="2" t="inlineStr">
         <is>
           <t>TC-593</t>
@@ -35230,7 +35230,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="595">
+    <row r="595" ht="70" customHeight="1">
       <c r="A595" s="2" t="inlineStr">
         <is>
           <t>TC-594</t>
@@ -35289,7 +35289,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="596">
+    <row r="596" ht="70" customHeight="1">
       <c r="A596" s="2" t="inlineStr">
         <is>
           <t>TC-595</t>
@@ -35348,7 +35348,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="597">
+    <row r="597" ht="70" customHeight="1">
       <c r="A597" s="2" t="inlineStr">
         <is>
           <t>TC-596</t>
@@ -35406,7 +35406,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="598">
+    <row r="598" ht="70" customHeight="1">
       <c r="A598" s="2" t="inlineStr">
         <is>
           <t>TC-597</t>
@@ -35465,7 +35465,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="599">
+    <row r="599" ht="70" customHeight="1">
       <c r="A599" s="2" t="inlineStr">
         <is>
           <t>TC-598</t>
@@ -35523,7 +35523,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="600">
+    <row r="600" ht="70" customHeight="1">
       <c r="A600" s="2" t="inlineStr">
         <is>
           <t>TC-599</t>
@@ -35581,7 +35581,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="601">
+    <row r="601" ht="70" customHeight="1">
       <c r="A601" s="2" t="inlineStr">
         <is>
           <t>TC-600</t>
@@ -35638,7 +35638,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="602">
+    <row r="602" ht="70" customHeight="1">
       <c r="A602" s="2" t="inlineStr">
         <is>
           <t>TC-601</t>
@@ -35699,7 +35699,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="603">
+    <row r="603" ht="70" customHeight="1">
       <c r="A603" s="2" t="inlineStr">
         <is>
           <t>TC-602</t>
@@ -35756,7 +35756,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="604">
+    <row r="604" ht="70" customHeight="1">
       <c r="A604" s="2" t="inlineStr">
         <is>
           <t>TC-603</t>
@@ -35813,7 +35813,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="605">
+    <row r="605" ht="70" customHeight="1">
       <c r="A605" s="2" t="inlineStr">
         <is>
           <t>TC-604</t>
@@ -35872,7 +35872,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="606">
+    <row r="606" ht="70" customHeight="1">
       <c r="A606" s="2" t="inlineStr">
         <is>
           <t>TC-605</t>
@@ -35930,7 +35930,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="607">
+    <row r="607" ht="70" customHeight="1">
       <c r="A607" s="2" t="inlineStr">
         <is>
           <t>TC-606</t>
@@ -35989,7 +35989,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="608">
+    <row r="608" ht="70" customHeight="1">
       <c r="A608" s="2" t="inlineStr">
         <is>
           <t>TC-607</t>
@@ -36048,7 +36048,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="609">
+    <row r="609" ht="70" customHeight="1">
       <c r="A609" s="2" t="inlineStr">
         <is>
           <t>TC-608</t>
@@ -36107,7 +36107,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="610">
+    <row r="610" ht="70" customHeight="1">
       <c r="A610" s="2" t="inlineStr">
         <is>
           <t>TC-609</t>
@@ -36165,7 +36165,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="611">
+    <row r="611" ht="70" customHeight="1">
       <c r="A611" s="2" t="inlineStr">
         <is>
           <t>TC-610</t>
@@ -36223,7 +36223,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="612">
+    <row r="612" ht="70" customHeight="1">
       <c r="A612" s="2" t="inlineStr">
         <is>
           <t>TC-611</t>
@@ -36282,7 +36282,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="613">
+    <row r="613" ht="70" customHeight="1">
       <c r="A613" s="2" t="inlineStr">
         <is>
           <t>TC-612</t>
@@ -36340,7 +36340,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="614">
+    <row r="614" ht="70" customHeight="1">
       <c r="A614" s="2" t="inlineStr">
         <is>
           <t>TC-613</t>
@@ -36399,7 +36399,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="615">
+    <row r="615" ht="70" customHeight="1">
       <c r="A615" s="2" t="inlineStr">
         <is>
           <t>TC-614</t>
@@ -36457,7 +36457,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="616">
+    <row r="616" ht="70" customHeight="1">
       <c r="A616" s="2" t="inlineStr">
         <is>
           <t>TC-615</t>
@@ -36516,7 +36516,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="617">
+    <row r="617" ht="70" customHeight="1">
       <c r="A617" s="2" t="inlineStr">
         <is>
           <t>TC-616</t>
@@ -36574,7 +36574,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="618">
+    <row r="618" ht="70" customHeight="1">
       <c r="A618" s="2" t="inlineStr">
         <is>
           <t>TC-617</t>
@@ -36633,7 +36633,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="619">
+    <row r="619" ht="70" customHeight="1">
       <c r="A619" s="2" t="inlineStr">
         <is>
           <t>TC-618</t>
@@ -36691,7 +36691,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="620">
+    <row r="620" ht="70" customHeight="1">
       <c r="A620" s="2" t="inlineStr">
         <is>
           <t>TC-619</t>
@@ -36750,7 +36750,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="621">
+    <row r="621" ht="70" customHeight="1">
       <c r="A621" s="2" t="inlineStr">
         <is>
           <t>TC-620</t>
@@ -36808,7 +36808,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="622">
+    <row r="622" ht="70" customHeight="1">
       <c r="A622" s="2" t="inlineStr">
         <is>
           <t>TC-621</t>
@@ -36867,7 +36867,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="623">
+    <row r="623" ht="70" customHeight="1">
       <c r="A623" s="2" t="inlineStr">
         <is>
           <t>TC-622</t>
@@ -36925,7 +36925,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="624">
+    <row r="624" ht="70" customHeight="1">
       <c r="A624" s="2" t="inlineStr">
         <is>
           <t>TC-623</t>
@@ -36984,7 +36984,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="625">
+    <row r="625" ht="70" customHeight="1">
       <c r="A625" s="2" t="inlineStr">
         <is>
           <t>TC-624</t>
@@ -37042,7 +37042,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="626">
+    <row r="626" ht="70" customHeight="1">
       <c r="A626" s="2" t="inlineStr">
         <is>
           <t>TC-625</t>
@@ -37101,7 +37101,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="627">
+    <row r="627" ht="70" customHeight="1">
       <c r="A627" s="2" t="inlineStr">
         <is>
           <t>TC-626</t>
@@ -37159,7 +37159,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="628">
+    <row r="628" ht="70" customHeight="1">
       <c r="A628" s="2" t="inlineStr">
         <is>
           <t>TC-627</t>
@@ -37218,7 +37218,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="629">
+    <row r="629" ht="70" customHeight="1">
       <c r="A629" s="2" t="inlineStr">
         <is>
           <t>TC-628</t>
@@ -37276,7 +37276,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="630">
+    <row r="630" ht="70" customHeight="1">
       <c r="A630" s="2" t="inlineStr">
         <is>
           <t>TC-629</t>
@@ -37335,7 +37335,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="631">
+    <row r="631" ht="70" customHeight="1">
       <c r="A631" s="2" t="inlineStr">
         <is>
           <t>TC-630</t>
@@ -37393,7 +37393,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="632">
+    <row r="632" ht="70" customHeight="1">
       <c r="A632" s="2" t="inlineStr">
         <is>
           <t>TC-631</t>
@@ -37452,7 +37452,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="633">
+    <row r="633" ht="70" customHeight="1">
       <c r="A633" s="2" t="inlineStr">
         <is>
           <t>TC-632</t>
@@ -37510,7 +37510,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="70" r="634">
+    <row r="634" ht="70" customHeight="1">
       <c r="A634" s="2" t="inlineStr">
         <is>
           <t>TC-633</t>
@@ -37569,9 +37569,725 @@
         </is>
       </c>
     </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>TC-634</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>rNPU_aic_load-正常注入</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>npu_compute</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>1. dcat inject rNPU_aic_load --chip=0 --load_pct=30
+2. 检查注入状态</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>--chip=0 --load_pct=30</t>
+        </is>
+      </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>1. status:ok record_id=N
+2. AICore 负载注入成功</t>
+        </is>
+      </c>
+      <c r="G635" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H635" t="inlineStr">
+        <is>
+          <t>US-09</t>
+        </is>
+      </c>
+      <c r="I635" t="inlineStr">
+        <is>
+          <t>AI补全-计算类</t>
+        </is>
+      </c>
+      <c r="J635" t="inlineStr">
+        <is>
+          <t>dcat query rNPU_aic_load --chip=0</t>
+        </is>
+      </c>
+      <c r="K635" t="inlineStr">
+        <is>
+          <t>confirmed:true</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>TC-635</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>rNPU_aic_load-端到端 inject→query→clean→query 无残留</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>npu_compute</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>1. dcat inject rNPU_aic_load --chip=0 --load_pct=30
+2. dcat query rNPU_aic_load --chip=0
+3. dcat clean rNPU_aic_load --chip=0
+4. dcat query rNPU_aic_load --chip=0</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>--chip=0 --load_pct=30</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>1. inject status:ok
+2. query confirmed:true
+3. clean status:ok
+4. query confirmed:false 无残留</t>
+        </is>
+      </c>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H636" t="inlineStr">
+        <is>
+          <t>US-09</t>
+        </is>
+      </c>
+      <c r="I636" t="inlineStr">
+        <is>
+          <t>AI补全-计算类</t>
+        </is>
+      </c>
+      <c r="J636" t="inlineStr">
+        <is>
+          <t>dcat query rNPU_aic_load --chip=0</t>
+        </is>
+      </c>
+      <c r="K636" t="inlineStr">
+        <is>
+          <t>confirmed:true→false</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>TC-636</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>rNPU_aic_load-无参拒绝</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>npu_compute</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>1. dcat inject rNPU_aic_load</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>无参</t>
+        </is>
+      </c>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>1. 缺少必填参数 --chip，拒绝 exit 1</t>
+        </is>
+      </c>
+      <c r="G637" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H637" t="inlineStr">
+        <is>
+          <t>US-09</t>
+        </is>
+      </c>
+      <c r="I637" t="inlineStr">
+        <is>
+          <t>AI补全-计算类</t>
+        </is>
+      </c>
+      <c r="J637" t="inlineStr">
+        <is>
+          <t>（注入未执行）</t>
+        </is>
+      </c>
+      <c r="K637" t="inlineStr">
+        <is>
+          <t>exitcode:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>TC-637</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>rNPU_aicpu_load-正常注入</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>npu_compute</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>1. dcat inject rNPU_aicpu_load --chip=0 --load_pct=30
+2. 检查注入状态</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>--chip=0 --load_pct=30</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>1. status:ok record_id=N
+2. AICpu 负载注入成功</t>
+        </is>
+      </c>
+      <c r="G638" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H638" t="inlineStr">
+        <is>
+          <t>US-09</t>
+        </is>
+      </c>
+      <c r="I638" t="inlineStr">
+        <is>
+          <t>AI补全-计算类</t>
+        </is>
+      </c>
+      <c r="J638" t="inlineStr">
+        <is>
+          <t>dcat query rNPU_aicpu_load --chip=0</t>
+        </is>
+      </c>
+      <c r="K638" t="inlineStr">
+        <is>
+          <t>confirmed:true</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>TC-638</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>rNPU_aicpu_load-端到端 inject→query→clean→query 无残留</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>npu_compute</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>1. dcat inject rNPU_aicpu_load --chip=0 --load_pct=30
+2. dcat query rNPU_aicpu_load --chip=0
+3. dcat clean rNPU_aicpu_load --chip=0
+4. dcat query rNPU_aicpu_load --chip=0</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>--chip=0 --load_pct=30</t>
+        </is>
+      </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>1. inject status:ok
+2. query confirmed:true
+3. clean status:ok
+4. query confirmed:false 无残留</t>
+        </is>
+      </c>
+      <c r="G639" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H639" t="inlineStr">
+        <is>
+          <t>US-09</t>
+        </is>
+      </c>
+      <c r="I639" t="inlineStr">
+        <is>
+          <t>AI补全-计算类</t>
+        </is>
+      </c>
+      <c r="J639" t="inlineStr">
+        <is>
+          <t>dcat query rNPU_aicpu_load --chip=0</t>
+        </is>
+      </c>
+      <c r="K639" t="inlineStr">
+        <is>
+          <t>confirmed:true→false</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>TC-639</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>rNPU_aicpu_load-无参拒绝</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>npu_compute</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>1. dcat inject rNPU_aicpu_load</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>无参</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>1. 缺少必填参数 --chip，拒绝 exit 1</t>
+        </is>
+      </c>
+      <c r="G640" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H640" t="inlineStr">
+        <is>
+          <t>US-09</t>
+        </is>
+      </c>
+      <c r="I640" t="inlineStr">
+        <is>
+          <t>AI补全-计算类</t>
+        </is>
+      </c>
+      <c r="J640" t="inlineStr">
+        <is>
+          <t>（注入未执行）</t>
+        </is>
+      </c>
+      <c r="K640" t="inlineStr">
+        <is>
+          <t>exitcode:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>TC-640</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>rNPU_aiv_load-正常注入</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>npu_compute</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>1. dcat inject rNPU_aiv_load --chip=0 --load_pct=30
+2. 检查注入状态</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>--chip=0 --load_pct=30</t>
+        </is>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>1. status:ok record_id=N
+2. AIVector 负载注入成功</t>
+        </is>
+      </c>
+      <c r="G641" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H641" t="inlineStr">
+        <is>
+          <t>US-09</t>
+        </is>
+      </c>
+      <c r="I641" t="inlineStr">
+        <is>
+          <t>AI补全-计算类</t>
+        </is>
+      </c>
+      <c r="J641" t="inlineStr">
+        <is>
+          <t>dcat query rNPU_aiv_load --chip=0</t>
+        </is>
+      </c>
+      <c r="K641" t="inlineStr">
+        <is>
+          <t>confirmed:true</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>TC-641</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>rNPU_aiv_load-端到端 inject→query→clean→query 无残留</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>npu_compute</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>1. dcat inject rNPU_aiv_load --chip=0 --load_pct=30
+2. dcat query rNPU_aiv_load --chip=0
+3. dcat clean rNPU_aiv_load --chip=0
+4. dcat query rNPU_aiv_load --chip=0</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>--chip=0 --load_pct=30</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>1. inject status:ok
+2. query confirmed:true
+3. clean status:ok
+4. query confirmed:false 无残留</t>
+        </is>
+      </c>
+      <c r="G642" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H642" t="inlineStr">
+        <is>
+          <t>US-09</t>
+        </is>
+      </c>
+      <c r="I642" t="inlineStr">
+        <is>
+          <t>AI补全-计算类</t>
+        </is>
+      </c>
+      <c r="J642" t="inlineStr">
+        <is>
+          <t>dcat query rNPU_aiv_load --chip=0</t>
+        </is>
+      </c>
+      <c r="K642" t="inlineStr">
+        <is>
+          <t>confirmed:true→false</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>TC-642</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>rNPU_aiv_load-无参拒绝</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>npu_compute</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>1. dcat inject rNPU_aiv_load</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>无参</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>1. 缺少必填参数 --chip，拒绝 exit 1</t>
+        </is>
+      </c>
+      <c r="G643" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H643" t="inlineStr">
+        <is>
+          <t>US-09</t>
+        </is>
+      </c>
+      <c r="I643" t="inlineStr">
+        <is>
+          <t>AI补全-计算类</t>
+        </is>
+      </c>
+      <c r="J643" t="inlineStr">
+        <is>
+          <t>（注入未执行）</t>
+        </is>
+      </c>
+      <c r="K643" t="inlineStr">
+        <is>
+          <t>exitcode:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>TC-643</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>rNPU_hbm_load-正常注入</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>npu_compute</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>1. dcat inject rNPU_hbm_load --chip=0 --size=500M
+2. 检查注入状态</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>--chip=0 --size=500M</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>1. status:ok record_id=N
+2. HBM 内存负载注入成功</t>
+        </is>
+      </c>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H644" t="inlineStr">
+        <is>
+          <t>US-09</t>
+        </is>
+      </c>
+      <c r="I644" t="inlineStr">
+        <is>
+          <t>AI补全-计算类</t>
+        </is>
+      </c>
+      <c r="J644" t="inlineStr">
+        <is>
+          <t>dcat query rNPU_hbm_load --chip=0</t>
+        </is>
+      </c>
+      <c r="K644" t="inlineStr">
+        <is>
+          <t>confirmed:true</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>TC-644</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>rNPU_hbm_load-端到端 inject→query→clean→query 无残留</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>npu_compute</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>1. dcat inject rNPU_hbm_load --chip=0 --size=500M
+2. dcat query rNPU_hbm_load --chip=0
+3. dcat clean rNPU_hbm_load --chip=0
+4. dcat query rNPU_hbm_load --chip=0</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>--chip=0 --size=500M</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>1. inject status:ok
+2. query confirmed:true
+3. clean status:ok
+4. query confirmed:false 无残留</t>
+        </is>
+      </c>
+      <c r="G645" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H645" t="inlineStr">
+        <is>
+          <t>US-09</t>
+        </is>
+      </c>
+      <c r="I645" t="inlineStr">
+        <is>
+          <t>AI补全-计算类</t>
+        </is>
+      </c>
+      <c r="J645" t="inlineStr">
+        <is>
+          <t>dcat query rNPU_hbm_load --chip=0</t>
+        </is>
+      </c>
+      <c r="K645" t="inlineStr">
+        <is>
+          <t>confirmed:true→false</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>TC-645</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>rNPU_hbm_load-无参拒绝</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>npu_compute</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>1. dcat inject rNPU_hbm_load</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>无参</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>1. 缺少必填参数 --chip，拒绝 exit 1</t>
+        </is>
+      </c>
+      <c r="G646" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H646" t="inlineStr">
+        <is>
+          <t>US-09</t>
+        </is>
+      </c>
+      <c r="I646" t="inlineStr">
+        <is>
+          <t>AI补全-计算类</t>
+        </is>
+      </c>
+      <c r="J646" t="inlineStr">
+        <is>
+          <t>（注入未执行）</t>
+        </is>
+      </c>
+      <c r="K646" t="inlineStr">
+        <is>
+          <t>exitcode:1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -37584,9 +38300,9 @@
   <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="30"/>
-    <col customWidth="1" max="2" min="2" width="12"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -37813,6 +38529,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/tests/e2e/testcases.xlsx
+++ b/tests/e2e/testcases.xlsx
@@ -37587,13 +37587,13 @@
       </c>
       <c r="D635" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_aic_load --chip=0 --load_pct=30
+          <t>1. dcat inject rNPU_aic_load --chip={chip} --load_pct=30
 2. 检查注入状态</t>
         </is>
       </c>
       <c r="E635" t="inlineStr">
         <is>
-          <t>--chip=0 --load_pct=30</t>
+          <t>--chip={chip} --load_pct=30</t>
         </is>
       </c>
       <c r="F635" t="inlineStr">
@@ -37619,7 +37619,7 @@
       </c>
       <c r="J635" t="inlineStr">
         <is>
-          <t>dcat query rNPU_aic_load --chip=0</t>
+          <t>dcat query rNPU_aic_load --chip={chip}</t>
         </is>
       </c>
       <c r="K635" t="inlineStr">
@@ -37646,15 +37646,15 @@
       </c>
       <c r="D636" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_aic_load --chip=0 --load_pct=30
-2. dcat query rNPU_aic_load --chip=0
-3. dcat clean rNPU_aic_load --chip=0
-4. dcat query rNPU_aic_load --chip=0</t>
+          <t>1. dcat inject rNPU_aic_load --chip={chip} --load_pct=30
+2. dcat query rNPU_aic_load --chip={chip}
+3. dcat clean rNPU_aic_load --chip={chip}
+4. dcat query rNPU_aic_load --chip={chip}</t>
         </is>
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>--chip=0 --load_pct=30</t>
+          <t>--chip={chip} --load_pct=30</t>
         </is>
       </c>
       <c r="F636" t="inlineStr">
@@ -37682,7 +37682,7 @@
       </c>
       <c r="J636" t="inlineStr">
         <is>
-          <t>dcat query rNPU_aic_load --chip=0</t>
+          <t>dcat query rNPU_aic_load --chip={chip}</t>
         </is>
       </c>
       <c r="K636" t="inlineStr">
@@ -37744,7 +37744,7 @@
       </c>
       <c r="K637" t="inlineStr">
         <is>
-          <t>exitcode:1</t>
+          <t>exitcode:3</t>
         </is>
       </c>
     </row>
@@ -37766,13 +37766,13 @@
       </c>
       <c r="D638" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_aicpu_load --chip=0 --load_pct=30
+          <t>1. dcat inject rNPU_aicpu_load --chip={chip} --load_pct=30
 2. 检查注入状态</t>
         </is>
       </c>
       <c r="E638" t="inlineStr">
         <is>
-          <t>--chip=0 --load_pct=30</t>
+          <t>--chip={chip} --load_pct=30</t>
         </is>
       </c>
       <c r="F638" t="inlineStr">
@@ -37798,7 +37798,7 @@
       </c>
       <c r="J638" t="inlineStr">
         <is>
-          <t>dcat query rNPU_aicpu_load --chip=0</t>
+          <t>dcat query rNPU_aicpu_load --chip={chip}</t>
         </is>
       </c>
       <c r="K638" t="inlineStr">
@@ -37825,15 +37825,15 @@
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_aicpu_load --chip=0 --load_pct=30
-2. dcat query rNPU_aicpu_load --chip=0
-3. dcat clean rNPU_aicpu_load --chip=0
-4. dcat query rNPU_aicpu_load --chip=0</t>
+          <t>1. dcat inject rNPU_aicpu_load --chip={chip} --load_pct=30
+2. dcat query rNPU_aicpu_load --chip={chip}
+3. dcat clean rNPU_aicpu_load --chip={chip}
+4. dcat query rNPU_aicpu_load --chip={chip}</t>
         </is>
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>--chip=0 --load_pct=30</t>
+          <t>--chip={chip} --load_pct=30</t>
         </is>
       </c>
       <c r="F639" t="inlineStr">
@@ -37861,7 +37861,7 @@
       </c>
       <c r="J639" t="inlineStr">
         <is>
-          <t>dcat query rNPU_aicpu_load --chip=0</t>
+          <t>dcat query rNPU_aicpu_load --chip={chip}</t>
         </is>
       </c>
       <c r="K639" t="inlineStr">
@@ -37923,7 +37923,7 @@
       </c>
       <c r="K640" t="inlineStr">
         <is>
-          <t>exitcode:1</t>
+          <t>exitcode:3</t>
         </is>
       </c>
     </row>
@@ -37945,13 +37945,13 @@
       </c>
       <c r="D641" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_aiv_load --chip=0 --load_pct=30
+          <t>1. dcat inject rNPU_aiv_load --chip={chip} --load_pct=30
 2. 检查注入状态</t>
         </is>
       </c>
       <c r="E641" t="inlineStr">
         <is>
-          <t>--chip=0 --load_pct=30</t>
+          <t>--chip={chip} --load_pct=30</t>
         </is>
       </c>
       <c r="F641" t="inlineStr">
@@ -37977,7 +37977,7 @@
       </c>
       <c r="J641" t="inlineStr">
         <is>
-          <t>dcat query rNPU_aiv_load --chip=0</t>
+          <t>dcat query rNPU_aiv_load --chip={chip}</t>
         </is>
       </c>
       <c r="K641" t="inlineStr">
@@ -38004,15 +38004,15 @@
       </c>
       <c r="D642" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_aiv_load --chip=0 --load_pct=30
-2. dcat query rNPU_aiv_load --chip=0
-3. dcat clean rNPU_aiv_load --chip=0
-4. dcat query rNPU_aiv_load --chip=0</t>
+          <t>1. dcat inject rNPU_aiv_load --chip={chip} --load_pct=30
+2. dcat query rNPU_aiv_load --chip={chip}
+3. dcat clean rNPU_aiv_load --chip={chip}
+4. dcat query rNPU_aiv_load --chip={chip}</t>
         </is>
       </c>
       <c r="E642" t="inlineStr">
         <is>
-          <t>--chip=0 --load_pct=30</t>
+          <t>--chip={chip} --load_pct=30</t>
         </is>
       </c>
       <c r="F642" t="inlineStr">
@@ -38040,7 +38040,7 @@
       </c>
       <c r="J642" t="inlineStr">
         <is>
-          <t>dcat query rNPU_aiv_load --chip=0</t>
+          <t>dcat query rNPU_aiv_load --chip={chip}</t>
         </is>
       </c>
       <c r="K642" t="inlineStr">
@@ -38102,7 +38102,7 @@
       </c>
       <c r="K643" t="inlineStr">
         <is>
-          <t>exitcode:1</t>
+          <t>exitcode:3</t>
         </is>
       </c>
     </row>
@@ -38124,13 +38124,13 @@
       </c>
       <c r="D644" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_hbm_load --chip=0 --size=500M
+          <t>1. dcat inject rNPU_hbm_load --chip={chip} --size=500M
 2. 检查注入状态</t>
         </is>
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>--chip=0 --size=500M</t>
+          <t>--chip={chip} --size=500M</t>
         </is>
       </c>
       <c r="F644" t="inlineStr">
@@ -38156,7 +38156,7 @@
       </c>
       <c r="J644" t="inlineStr">
         <is>
-          <t>dcat query rNPU_hbm_load --chip=0</t>
+          <t>dcat query rNPU_hbm_load --chip={chip}</t>
         </is>
       </c>
       <c r="K644" t="inlineStr">
@@ -38183,15 +38183,15 @@
       </c>
       <c r="D645" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_hbm_load --chip=0 --size=500M
-2. dcat query rNPU_hbm_load --chip=0
-3. dcat clean rNPU_hbm_load --chip=0
-4. dcat query rNPU_hbm_load --chip=0</t>
+          <t>1. dcat inject rNPU_hbm_load --chip={chip} --size=500M
+2. dcat query rNPU_hbm_load --chip={chip}
+3. dcat clean rNPU_hbm_load --chip={chip}
+4. dcat query rNPU_hbm_load --chip={chip}</t>
         </is>
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>--chip=0 --size=500M</t>
+          <t>--chip={chip} --size=500M</t>
         </is>
       </c>
       <c r="F645" t="inlineStr">
@@ -38219,7 +38219,7 @@
       </c>
       <c r="J645" t="inlineStr">
         <is>
-          <t>dcat query rNPU_hbm_load --chip=0</t>
+          <t>dcat query rNPU_hbm_load --chip={chip}</t>
         </is>
       </c>
       <c r="K645" t="inlineStr">
@@ -38281,7 +38281,7 @@
       </c>
       <c r="K646" t="inlineStr">
         <is>
-          <t>exitcode:1</t>
+          <t>exitcode:3</t>
         </is>
       </c>
     </row>

--- a/tests/e2e/testcases.xlsx
+++ b/tests/e2e/testcases.xlsx
@@ -15646,7 +15646,7 @@
       </c>
       <c r="D260" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200 --force</t>
+          <t>1. dcat inject rNPU_arp --chip={chip} --dev={dev} --ip=10.30.12.200 --force</t>
         </is>
       </c>
       <c r="E260" s="3" t="inlineStr">
@@ -15678,7 +15678,7 @@
       </c>
       <c r="J260" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -arp -g 2&gt;/dev/null</t>
+          <t>hccn_tool -i {chip} -arp -g 2&gt;/dev/null</t>
         </is>
       </c>
       <c r="K260" s="3" t="inlineStr">
@@ -15705,7 +15705,7 @@
       </c>
       <c r="D261" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_arp --chip=-1 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55</t>
+          <t>1. dcat inject rNPU_arp --chip=-1 --dev={dev} --ip=10.30.12.200 --mac=00:11:22:33:44:55</t>
         </is>
       </c>
       <c r="E261" s="3" t="inlineStr">
@@ -15762,7 +15762,7 @@
       </c>
       <c r="D262" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_arp --chip=8 --dev=eth2 --ip=10.30.12.200</t>
+          <t>1. dcat inject rNPU_arp --chip=8 --dev={dev} --ip=10.30.12.200</t>
         </is>
       </c>
       <c r="E262" s="3" t="inlineStr">
@@ -15797,7 +15797,7 @@
       </c>
       <c r="K262" s="3" t="inlineStr">
         <is>
-          <t>exitcode:1</t>
+          <t>exitcode:3</t>
         </is>
       </c>
     </row>
@@ -15849,7 +15849,7 @@
       <c r="I263" s="3" t="inlineStr"/>
       <c r="J263" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -arp -g 2&gt;/dev/null</t>
+          <t>hccn_tool -i {chip} -arp -g 2&gt;/dev/null</t>
         </is>
       </c>
       <c r="K263" s="3" t="inlineStr">
@@ -15876,7 +15876,7 @@
       </c>
       <c r="D264" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat clean rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200（dev 与创建时一致）
+          <t>1. 执行 dcat clean rNPU_arp --chip={chip} --dev={dev} --ip=10.30.12.200（dev 与创建时一致）
 2. 改用错误 dev 重试验证失败</t>
         </is>
       </c>
@@ -15905,7 +15905,7 @@
       <c r="I264" s="3" t="inlineStr"/>
       <c r="J264" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -arp -g 2&gt;/dev/null</t>
+          <t>hccn_tool -i {chip} -arp -g 2&gt;/dev/null</t>
         </is>
       </c>
       <c r="K264" s="3" t="inlineStr">
@@ -15932,7 +15932,7 @@
       </c>
       <c r="D265" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200
+          <t>1. dcat clean rNPU_arp --chip={chip} --dev={dev} --ip=10.30.12.200
 2. dcat query（无 uid）</t>
         </is>
       </c>
@@ -15991,7 +15991,7 @@
       </c>
       <c r="D266" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200
+          <t>1. dcat clean rNPU_arp --chip={chip} --dev={dev} --ip=10.30.12.200
 2. 检查恢复状态</t>
         </is>
       </c>
@@ -16023,7 +16023,7 @@
       </c>
       <c r="J266" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -arp -g 2&gt;/dev/null</t>
+          <t>hccn_tool -i {chip} -arp -g 2&gt;/dev/null</t>
         </is>
       </c>
       <c r="K266" s="3" t="inlineStr">
@@ -16050,7 +16050,7 @@
       </c>
       <c r="D267" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_arp --chip=2 --dev=eth2 --ip=invalid</t>
+          <t>1. dcat inject rNPU_arp --chip={chip} --dev={dev} --ip=invalid</t>
         </is>
       </c>
       <c r="E267" s="3" t="inlineStr">
@@ -16085,7 +16085,7 @@
       </c>
       <c r="K267" s="3" t="inlineStr">
         <is>
-          <t>exitcode:1</t>
+          <t>exitcode:3</t>
         </is>
       </c>
     </row>
@@ -16165,7 +16165,7 @@
       </c>
       <c r="D269" s="3" t="inlineStr">
         <is>
-          <t>1. dcat query rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200</t>
+          <t>1. dcat query rNPU_arp --chip={chip} --dev={dev} --ip=10.30.12.200</t>
         </is>
       </c>
       <c r="E269" s="3" t="inlineStr">
@@ -16223,7 +16223,7 @@
       </c>
       <c r="D270" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200
+          <t>1. 执行 dcat inject rNPU_arp --chip={chip} --dev={dev} --ip=10.30.12.200
 2. 检查返回</t>
         </is>
       </c>
@@ -16258,7 +16258,7 @@
       </c>
       <c r="K270" s="3" t="inlineStr">
         <is>
-          <t>exitcode:1</t>
+          <t>exitcode:3</t>
         </is>
       </c>
     </row>
@@ -16280,7 +16280,7 @@
       </c>
       <c r="D271" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200
+          <t>1. 执行 dcat inject rNPU_arp --chip={chip} --dev={dev} --ip=10.30.12.200
 2. 检查 sidecar 与 query</t>
         </is>
       </c>
@@ -16310,7 +16310,7 @@
       <c r="I271" s="3" t="inlineStr"/>
       <c r="J271" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -arp -g 2&gt;/dev/null</t>
+          <t>hccn_tool -i {chip} -arp -g 2&gt;/dev/null</t>
         </is>
       </c>
       <c r="K271" s="3" t="inlineStr">
@@ -16337,8 +16337,8 @@
       </c>
       <c r="D272" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200
-2. 再次 dcat inject rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200</t>
+          <t>1. dcat inject rNPU_arp --chip={chip} --dev={dev} --ip=10.30.12.200
+2. 再次 dcat inject rNPU_arp --chip={chip} --dev={dev} --ip=10.30.12.200</t>
         </is>
       </c>
       <c r="E272" s="3" t="inlineStr">
@@ -16454,7 +16454,7 @@
       </c>
       <c r="D274" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200
+          <t>1. dcat inject rNPU_arp --chip={chip} --dev={dev} --ip=10.30.12.200
 2. 检查注入状态</t>
         </is>
       </c>
@@ -16486,7 +16486,7 @@
       </c>
       <c r="J274" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -arp -g 2&gt;/dev/null</t>
+          <t>hccn_tool -i {chip} -arp -g 2&gt;/dev/null</t>
         </is>
       </c>
       <c r="K274" s="3" t="inlineStr">
@@ -16513,9 +16513,9 @@
       </c>
       <c r="D275" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200
+          <t>1. dcat inject rNPU_arp --chip={chip} --dev={dev} --ip=10.30.12.200
 2. dcat query rNPU_arp
-3. dcat clean rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200
+3. dcat clean rNPU_arp --chip={chip} --dev={dev} --ip=10.30.12.200
 4. dcat query rNPU_arp</t>
         </is>
       </c>
@@ -16549,12 +16549,12 @@
       </c>
       <c r="J275" s="3" t="inlineStr">
         <is>
-          <t>dcat query rNPU_arp</t>
+          <t>hccn_tool -i {chip} -arp -g 2&gt;/dev/null</t>
         </is>
       </c>
       <c r="K275" s="3" t="inlineStr">
         <is>
-          <t>confirmed:true→false</t>
+          <t>notcontains:10.30.12.200</t>
         </is>
       </c>
     </row>
@@ -16576,8 +16576,8 @@
       </c>
       <c r="D276" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200
-2. 再次 dcat clean rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200</t>
+          <t>1. dcat clean rNPU_arp --chip={chip} --dev={dev} --ip=10.30.12.200
+2. 再次 dcat clean rNPU_arp --chip={chip} --dev={dev} --ip=10.30.12.200</t>
         </is>
       </c>
       <c r="E276" s="3" t="inlineStr">
@@ -16635,7 +16635,7 @@
       </c>
       <c r="D277" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55 --force</t>
+          <t>1. dcat inject rNPU_arp --chip={chip} --dev={dev} --ip=10.30.12.200 --mac=00:11:22:33:44:55 --force</t>
         </is>
       </c>
       <c r="E277" s="3" t="inlineStr">
@@ -16667,7 +16667,7 @@
       </c>
       <c r="J277" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -arp -g 2&gt;/dev/null</t>
+          <t>hccn_tool -i {chip} -arp -g 2&gt;/dev/null</t>
         </is>
       </c>
       <c r="K277" s="3" t="inlineStr">
@@ -16694,7 +16694,7 @@
       </c>
       <c r="D278" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_arp --chip=-1 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55</t>
+          <t>1. dcat inject rNPU_arp --chip=-1 --dev={dev} --ip=10.30.12.200 --mac=00:11:22:33:44:55</t>
         </is>
       </c>
       <c r="E278" s="3" t="inlineStr">
@@ -16751,7 +16751,7 @@
       </c>
       <c r="D279" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_arp --chip=8 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55</t>
+          <t>1. dcat inject rNPU_arp --chip=8 --dev={dev} --ip=10.30.12.200 --mac=00:11:22:33:44:55</t>
         </is>
       </c>
       <c r="E279" s="3" t="inlineStr">
@@ -16808,7 +16808,7 @@
       </c>
       <c r="D280" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55
+          <t>1. dcat clean rNPU_arp --chip={chip} --dev={dev} --ip=10.30.12.200 --mac=00:11:22:33:44:55
 2. dcat query（无 uid）</t>
         </is>
       </c>
@@ -16867,7 +16867,7 @@
       </c>
       <c r="D281" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat clean rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200</t>
+          <t>1. 执行 dcat clean rNPU_arp --chip={chip} --dev={dev} --ip=10.30.12.200</t>
         </is>
       </c>
       <c r="E281" s="3" t="inlineStr">
@@ -16895,7 +16895,7 @@
       <c r="I281" s="3" t="inlineStr"/>
       <c r="J281" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -arp -g 2&gt;/dev/null</t>
+          <t>hccn_tool -i {chip} -arp -g 2&gt;/dev/null</t>
         </is>
       </c>
       <c r="K281" s="3" t="inlineStr">
@@ -16922,7 +16922,7 @@
       </c>
       <c r="D282" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55
+          <t>1. dcat clean rNPU_arp --chip={chip} --dev={dev} --ip=10.30.12.200 --mac=00:11:22:33:44:55
 2. 检查恢复状态</t>
         </is>
       </c>
@@ -16954,7 +16954,7 @@
       </c>
       <c r="J282" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -arp -g 2&gt;/dev/null</t>
+          <t>hccn_tool -i {chip} -arp -g 2&gt;/dev/null</t>
         </is>
       </c>
       <c r="K282" s="3" t="inlineStr">
@@ -16981,7 +16981,7 @@
       </c>
       <c r="D283" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=invalid
+          <t>1. 执行 dcat inject rNPU_arp --chip={chip} --dev={dev} --ip=10.30.12.200 --mac=invalid
 2. 检查返回</t>
         </is>
       </c>
@@ -17041,7 +17041,7 @@
       </c>
       <c r="D284" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=invalid</t>
+          <t>1. dcat inject rNPU_arp --chip={chip} --dev={dev} --ip=10.30.12.200 --mac=invalid</t>
         </is>
       </c>
       <c r="E284" s="3" t="inlineStr">
@@ -17098,7 +17098,7 @@
       </c>
       <c r="D285" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55
+          <t>1. 执行 dcat inject rNPU_arp --chip={chip} --dev={dev} --ip=10.30.12.200 --mac=00:11:22:33:44:55
 2. 执行 dcat query rNPU_arp 验证</t>
         </is>
       </c>
@@ -17127,7 +17127,7 @@
       <c r="I285" s="3" t="inlineStr"/>
       <c r="J285" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -arp -g 2&gt;/dev/null</t>
+          <t>hccn_tool -i {chip} -arp -g 2&gt;/dev/null</t>
         </is>
       </c>
       <c r="K285" s="3" t="inlineStr">
@@ -17212,7 +17212,7 @@
       </c>
       <c r="D287" s="3" t="inlineStr">
         <is>
-          <t>1. dcat query rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55</t>
+          <t>1. dcat query rNPU_arp --chip={chip} --dev={dev} --ip=10.30.12.200 --mac=00:11:22:33:44:55</t>
         </is>
       </c>
       <c r="E287" s="3" t="inlineStr">
@@ -17270,7 +17270,7 @@
       </c>
       <c r="D288" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_arp --chip=99 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55</t>
+          <t>1. dcat inject rNPU_arp --chip=99 --dev={dev} --ip=10.30.12.200 --mac=00:11:22:33:44:55</t>
         </is>
       </c>
       <c r="E288" s="3" t="inlineStr">
@@ -17328,7 +17328,7 @@
       </c>
       <c r="D289" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_arp --chip=99 --dev=eth2 --ip=10.30.12.200 --mac=invalid</t>
+          <t>1. dcat inject rNPU_arp --chip=99 --dev={dev} --ip=10.30.12.200 --mac=invalid</t>
         </is>
       </c>
       <c r="E289" s="3" t="inlineStr">
@@ -17386,7 +17386,7 @@
       </c>
       <c r="D290" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=invalid</t>
+          <t>1. dcat inject rNPU_arp --chip={chip} --dev={dev} --ip=10.30.12.200 --mac=invalid</t>
         </is>
       </c>
       <c r="E290" s="3" t="inlineStr">
@@ -17444,8 +17444,8 @@
       </c>
       <c r="D291" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55
-2. 再次 dcat inject rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55</t>
+          <t>1. dcat inject rNPU_arp --chip={chip} --dev={dev} --ip=10.30.12.200 --mac=00:11:22:33:44:55
+2. 再次 dcat inject rNPU_arp --chip={chip} --dev={dev} --ip=10.30.12.200 --mac=00:11:22:33:44:55</t>
         </is>
       </c>
       <c r="E291" s="3" t="inlineStr">
@@ -17561,7 +17561,7 @@
       </c>
       <c r="D293" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55
+          <t>1. dcat inject rNPU_arp --chip={chip} --dev={dev} --ip=10.30.12.200 --mac=00:11:22:33:44:55
 2. 检查注入状态</t>
         </is>
       </c>
@@ -17593,7 +17593,7 @@
       </c>
       <c r="J293" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -arp -g 2&gt;/dev/null</t>
+          <t>hccn_tool -i {chip} -arp -g 2&gt;/dev/null</t>
         </is>
       </c>
       <c r="K293" s="3" t="inlineStr">
@@ -17620,9 +17620,9 @@
       </c>
       <c r="D294" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55
+          <t>1. dcat inject rNPU_arp --chip={chip} --dev={dev} --ip=10.30.12.200 --mac=00:11:22:33:44:55
 2. dcat query rNPU_arp
-3. dcat clean rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55
+3. dcat clean rNPU_arp --chip={chip} --dev={dev} --ip=10.30.12.200 --mac=00:11:22:33:44:55
 4. dcat query rNPU_arp</t>
         </is>
       </c>
@@ -17656,12 +17656,12 @@
       </c>
       <c r="J294" s="3" t="inlineStr">
         <is>
-          <t>dcat query rNPU_arp</t>
+          <t>hccn_tool -i {chip} -arp -g 2&gt;/dev/null</t>
         </is>
       </c>
       <c r="K294" s="3" t="inlineStr">
         <is>
-          <t>confirmed:true→false</t>
+          <t>notcontains:00:11:22:33:44:55</t>
         </is>
       </c>
     </row>
@@ -17683,8 +17683,8 @@
       </c>
       <c r="D295" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55
-2. 再次 dcat clean rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55</t>
+          <t>1. dcat clean rNPU_arp --chip={chip} --dev={dev} --ip=10.30.12.200 --mac=00:11:22:33:44:55
+2. 再次 dcat clean rNPU_arp --chip={chip} --dev={dev} --ip=10.30.12.200 --mac=00:11:22:33:44:55</t>
         </is>
       </c>
       <c r="E295" s="3" t="inlineStr">
@@ -17742,12 +17742,12 @@
       </c>
       <c r="D296" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_bw_limit --chip=2 --bw_limit=1000 --force</t>
+          <t>1. dcat inject rNPU_bw_limit --chip={chip} --bw_limit=50000 --force</t>
         </is>
       </c>
       <c r="E296" s="3" t="inlineStr">
         <is>
-          <t>--chip=0 --bw_limit=1000 --force</t>
+          <t>--chip=0 --bw_limit=50000 --force</t>
         </is>
       </c>
       <c r="F296" s="3" t="inlineStr">
@@ -17774,7 +17774,7 @@
       </c>
       <c r="J296" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -shaping -g 2&gt;/dev/null | grep -oE 'bw_limit\[[0-9]+'</t>
+          <t>hccn_tool -i {chip} -shaping -g 2&gt;/dev/null | grep -oE 'bw_limit\[[0-9]+'</t>
         </is>
       </c>
       <c r="K296" s="3" t="inlineStr">
@@ -17801,9 +17801,9 @@
       </c>
       <c r="D297" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rNPU_bw_limit --chip=2 --bw_limit=1000
-2. 执行 dcat query rNPU_bw_limit --chip=2
-3. 执行 dcat clean rNPU_bw_limit --chip=2</t>
+          <t>1. 执行 dcat inject rNPU_bw_limit --chip={chip} --bw_limit=50000
+2. 执行 dcat query rNPU_bw_limit --chip={chip}
+3. 执行 dcat clean rNPU_bw_limit --chip={chip}</t>
         </is>
       </c>
       <c r="E297" s="3" t="inlineStr">
@@ -17840,7 +17840,7 @@
       </c>
       <c r="K297" s="3" t="inlineStr">
         <is>
-          <t>exitcode:1</t>
+          <t>status:ok</t>
         </is>
       </c>
     </row>
@@ -17862,7 +17862,7 @@
       </c>
       <c r="D298" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rNPU_bw_limit --chip=2 --bw_limit=0
+          <t>1. 执行 dcat inject rNPU_bw_limit --chip={chip} --bw_limit=0
 2. 执行 --bw_limit=-1 / --bw_limit=abc</t>
         </is>
       </c>
@@ -17921,7 +17921,7 @@
       </c>
       <c r="D299" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_bw_limit --chip=2 --bw_limit=-1</t>
+          <t>1. dcat inject rNPU_bw_limit --chip={chip} --bw_limit=-1</t>
         </is>
       </c>
       <c r="E299" s="3" t="inlineStr">
@@ -17978,7 +17978,7 @@
       </c>
       <c r="D300" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_bw_limit --chip=2 --bw_limit=0</t>
+          <t>1. dcat inject rNPU_bw_limit --chip={chip} --bw_limit=0</t>
         </is>
       </c>
       <c r="E300" s="3" t="inlineStr">
@@ -18035,7 +18035,7 @@
       </c>
       <c r="D301" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_bw_limit --chip=2 --bw_limit=abc</t>
+          <t>1. dcat inject rNPU_bw_limit --chip={chip} --bw_limit=abc</t>
         </is>
       </c>
       <c r="E301" s="3" t="inlineStr">
@@ -18092,7 +18092,7 @@
       </c>
       <c r="D302" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_bw_limit --chip=2 --bw_limit=1000
+          <t>1. dcat clean rNPU_bw_limit --chip={chip} --bw_limit=50000
 2. dcat query（无 uid）</t>
         </is>
       </c>
@@ -18151,13 +18151,13 @@
       </c>
       <c r="D303" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_bw_limit --chip=2 --bw_limit=1000
+          <t>1. dcat clean rNPU_bw_limit --chip={chip} --bw_limit=50000
 2. 检查恢复状态</t>
         </is>
       </c>
       <c r="E303" s="3" t="inlineStr">
         <is>
-          <t>--chip=0 --bw_limit=1000</t>
+          <t>--chip=0 --bw_limit=50000</t>
         </is>
       </c>
       <c r="F303" s="3" t="inlineStr">
@@ -18183,7 +18183,7 @@
       </c>
       <c r="J303" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -shaping -g 2&gt;/dev/null | grep -oE 'bw_limit\[[0-9]+'</t>
+          <t>hccn_tool -i {chip} -shaping -g 2&gt;/dev/null | grep -oE 'bw_limit\[[0-9]+'</t>
         </is>
       </c>
       <c r="K303" s="3" t="inlineStr">
@@ -18268,12 +18268,12 @@
       </c>
       <c r="D305" s="3" t="inlineStr">
         <is>
-          <t>1. dcat query rNPU_bw_limit --chip=2 --bw_limit=1000</t>
+          <t>1. dcat query rNPU_bw_limit --chip={chip} --bw_limit=50000</t>
         </is>
       </c>
       <c r="E305" s="3" t="inlineStr">
         <is>
-          <t>--chip=0 --bw_limit=1000</t>
+          <t>--chip=0 --bw_limit=50000</t>
         </is>
       </c>
       <c r="F305" s="3" t="inlineStr">
@@ -18326,13 +18326,13 @@
       </c>
       <c r="D306" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_bw_limit --chip=2 --bw_limit=1000
-2. 再次 dcat inject rNPU_bw_limit --chip=2 --bw_limit=1000</t>
+          <t>1. dcat inject rNPU_bw_limit --chip={chip} --bw_limit=50000
+2. 再次 dcat inject rNPU_bw_limit --chip={chip} --bw_limit=50000</t>
         </is>
       </c>
       <c r="E306" s="3" t="inlineStr">
         <is>
-          <t>--chip=0 --bw_limit=1000</t>
+          <t>--chip=0 --bw_limit=50000</t>
         </is>
       </c>
       <c r="F306" s="3" t="inlineStr">
@@ -18443,13 +18443,13 @@
       </c>
       <c r="D308" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_bw_limit --chip=2 --bw_limit=1000
+          <t>1. dcat inject rNPU_bw_limit --chip={chip} --bw_limit=50000
 2. 检查注入状态</t>
         </is>
       </c>
       <c r="E308" s="3" t="inlineStr">
         <is>
-          <t>--chip=0 --bw_limit=1000</t>
+          <t>--chip=0 --bw_limit=50000</t>
         </is>
       </c>
       <c r="F308" s="3" t="inlineStr">
@@ -18475,7 +18475,7 @@
       </c>
       <c r="J308" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -shaping -g 2&gt;/dev/null | grep -oE 'bw_limit\[[0-9]+'</t>
+          <t>hccn_tool -i {chip} -shaping -g 2&gt;/dev/null | grep -oE 'bw_limit\[[0-9]+'</t>
         </is>
       </c>
       <c r="K308" s="3" t="inlineStr">
@@ -18502,15 +18502,15 @@
       </c>
       <c r="D309" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_bw_limit --chip=2 --bw_limit=1000
+          <t>1. dcat inject rNPU_bw_limit --chip={chip} --bw_limit=50000
 2. dcat query rNPU_bw_limit
-3. dcat clean rNPU_bw_limit --chip=2 --bw_limit=1000
+3. dcat clean rNPU_bw_limit --chip={chip} --bw_limit=50000
 4. dcat query rNPU_bw_limit</t>
         </is>
       </c>
       <c r="E309" s="3" t="inlineStr">
         <is>
-          <t>--chip=0 --bw_limit=1000</t>
+          <t>--chip=0 --bw_limit=50000</t>
         </is>
       </c>
       <c r="F309" s="3" t="inlineStr">
@@ -18565,13 +18565,13 @@
       </c>
       <c r="D310" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_bw_limit --chip=2 --bw_limit=1000
-2. 再次 dcat clean rNPU_bw_limit --chip=2 --bw_limit=1000</t>
+          <t>1. dcat clean rNPU_bw_limit --chip={chip} --bw_limit=50000
+2. 再次 dcat clean rNPU_bw_limit --chip={chip} --bw_limit=50000</t>
         </is>
       </c>
       <c r="E310" s="3" t="inlineStr">
         <is>
-          <t>--chip=0 --bw_limit=1000</t>
+          <t>--chip=0 --bw_limit=50000</t>
         </is>
       </c>
       <c r="F310" s="3" t="inlineStr">
@@ -18624,7 +18624,7 @@
       </c>
       <c r="D311" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_dscp_tc_change --chip=2 --dscp=46 --tc=0 --force</t>
+          <t>1. dcat inject rNPU_dscp_tc_change --chip={chip} --dscp=46 --tc=3 --force</t>
         </is>
       </c>
       <c r="E311" s="3" t="inlineStr">
@@ -18656,12 +18656,12 @@
       </c>
       <c r="J311" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -dscp_to_tc -g dscp 46 2&gt;/dev/null | awk '$1==46{print $2}'</t>
+          <t>hccn_tool -i {chip} -dscp_to_tc -g dscp 46 2&gt;/dev/null | awk '$1==46{print $2}'</t>
         </is>
       </c>
       <c r="K311" s="3" t="inlineStr">
         <is>
-          <t>eq:1</t>
+          <t>eq:3</t>
         </is>
       </c>
     </row>
@@ -18683,9 +18683,9 @@
       </c>
       <c r="D312" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rNPU_dscp_tc_change --chip=2 --dscp=46 --tc=0
-2. 执行 dcat query rNPU_dscp_tc_change --chip=2 --dscp=46
-3. 执行 dcat clean rNPU_dscp_tc_change --chip=2 --dscp=46 --tc=0</t>
+          <t>1. 执行 dcat inject rNPU_dscp_tc_change --chip={chip} --dscp=46 --tc=3
+2. 执行 dcat query rNPU_dscp_tc_change --chip={chip} --dscp=46
+3. 执行 dcat clean rNPU_dscp_tc_change --chip={chip} --dscp=46 --tc=3</t>
         </is>
       </c>
       <c r="E312" s="3" t="inlineStr">
@@ -18717,12 +18717,12 @@
       </c>
       <c r="J312" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -dscp_to_tc -g dscp 46 2&gt;/dev/null | awk '$1==46{print $2}'</t>
+          <t>hccn_tool -i {chip} -dscp_to_tc -g dscp 46 2&gt;/dev/null | awk '$1==46{print $2}'</t>
         </is>
       </c>
       <c r="K312" s="3" t="inlineStr">
         <is>
-          <t>eq:0</t>
+          <t>eq:3</t>
         </is>
       </c>
     </row>
@@ -18858,7 +18858,7 @@
       </c>
       <c r="D315" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_dscp_tc_change --chip=2 --dscp=46 --tc=0
+          <t>1. dcat clean rNPU_dscp_tc_change --chip={chip} --dscp=46 --tc=0
 2. dcat query（无 uid）</t>
         </is>
       </c>
@@ -18917,7 +18917,7 @@
       </c>
       <c r="D316" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_dscp_tc_change --chip=2 --dscp=46 --tc=0
+          <t>1. dcat clean rNPU_dscp_tc_change --chip={chip} --dscp=46 --tc=0
 2. 检查恢复状态</t>
         </is>
       </c>
@@ -18949,7 +18949,7 @@
       </c>
       <c r="J316" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -dscp_to_tc -g dscp 46 2&gt;/dev/null | awk '$1==46{print $2}'</t>
+          <t>hccn_tool -i {chip} -dscp_to_tc -g dscp 46 2&gt;/dev/null | awk '$1==46{print $2}'</t>
         </is>
       </c>
       <c r="K316" s="3" t="inlineStr">
@@ -18976,7 +18976,7 @@
       </c>
       <c r="D317" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_dscp_tc_change --chip=2 --dscp=-1 --tc=0</t>
+          <t>1. dcat inject rNPU_dscp_tc_change --chip={chip} --dscp=-1 --tc=0</t>
         </is>
       </c>
       <c r="E317" s="3" t="inlineStr">
@@ -19033,7 +19033,7 @@
       </c>
       <c r="D318" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_dscp_tc_change --chip=2 --dscp=-1 --tc=0</t>
+          <t>1. dcat inject rNPU_dscp_tc_change --chip={chip} --dscp=-1 --tc=0</t>
         </is>
       </c>
       <c r="E318" s="3" t="inlineStr">
@@ -19090,7 +19090,7 @@
       </c>
       <c r="D319" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_dscp_tc_change --chip=2 --dscp=0 --tc=0</t>
+          <t>1. dcat inject rNPU_dscp_tc_change --chip={chip} --dscp=0 --tc=0</t>
         </is>
       </c>
       <c r="E319" s="3" t="inlineStr">
@@ -19120,7 +19120,7 @@
       </c>
       <c r="J319" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -dscp_to_tc -g dscp 46 2&gt;/dev/null | awk '$1==46{print $2}'</t>
+          <t>hccn_tool -i {chip} -dscp_to_tc -g dscp 46 2&gt;/dev/null | awk '$1==46{print $2}'</t>
         </is>
       </c>
       <c r="K319" s="3" t="inlineStr">
@@ -19147,7 +19147,7 @@
       </c>
       <c r="D320" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_dscp_tc_change --chip=2 --dscp=63 --tc=0</t>
+          <t>1. dcat inject rNPU_dscp_tc_change --chip={chip} --dscp=63 --tc=0</t>
         </is>
       </c>
       <c r="E320" s="3" t="inlineStr">
@@ -19177,7 +19177,7 @@
       </c>
       <c r="J320" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -dscp_to_tc -g dscp 46 2&gt;/dev/null | awk '$1==46{print $2}'</t>
+          <t>hccn_tool -i {chip} -dscp_to_tc -g dscp 46 2&gt;/dev/null | awk '$1==46{print $2}'</t>
         </is>
       </c>
       <c r="K320" s="3" t="inlineStr">
@@ -19204,7 +19204,7 @@
       </c>
       <c r="D321" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_dscp_tc_change --chip=2 --dscp=64 --tc=0</t>
+          <t>1. dcat inject rNPU_dscp_tc_change --chip={chip} --dscp=64 --tc=0</t>
         </is>
       </c>
       <c r="E321" s="3" t="inlineStr">
@@ -19319,7 +19319,7 @@
       </c>
       <c r="D323" s="3" t="inlineStr">
         <is>
-          <t>1. dcat query rNPU_dscp_tc_change --chip=2 --dscp=46 --tc=0</t>
+          <t>1. dcat query rNPU_dscp_tc_change --chip={chip} --dscp=46 --tc=0</t>
         </is>
       </c>
       <c r="E323" s="3" t="inlineStr">
@@ -19377,7 +19377,7 @@
       </c>
       <c r="D324" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_dscp_tc_change --chip=2 --dscp=46 --tc=-1</t>
+          <t>1. dcat inject rNPU_dscp_tc_change --chip={chip} --dscp=46 --tc=-1</t>
         </is>
       </c>
       <c r="E324" s="3" t="inlineStr">
@@ -19434,7 +19434,7 @@
       </c>
       <c r="D325" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_dscp_tc_change --chip=2 --dscp=46 --tc=0</t>
+          <t>1. dcat inject rNPU_dscp_tc_change --chip={chip} --dscp=46 --tc=3</t>
         </is>
       </c>
       <c r="E325" s="3" t="inlineStr">
@@ -19464,12 +19464,12 @@
       </c>
       <c r="J325" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -dscp_to_tc -g dscp 46 2&gt;/dev/null | awk '$1==46{print $2}'</t>
+          <t>hccn_tool -i {chip} -dscp_to_tc -g dscp 46 2&gt;/dev/null | awk '$1==46{print $2}'</t>
         </is>
       </c>
       <c r="K325" s="3" t="inlineStr">
         <is>
-          <t>eq:0</t>
+          <t>eq:3</t>
         </is>
       </c>
     </row>
@@ -19491,7 +19491,7 @@
       </c>
       <c r="D326" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_dscp_tc_change --chip=2 --dscp=46 --tc=7</t>
+          <t>1. dcat inject rNPU_dscp_tc_change --chip={chip} --dscp=46 --tc=7</t>
         </is>
       </c>
       <c r="E326" s="3" t="inlineStr">
@@ -19521,7 +19521,7 @@
       </c>
       <c r="J326" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -dscp_to_tc -g dscp 46 2&gt;/dev/null | awk '$1==46{print $2}'</t>
+          <t>hccn_tool -i {chip} -dscp_to_tc -g dscp 46 2&gt;/dev/null | awk '$1==46{print $2}'</t>
         </is>
       </c>
       <c r="K326" s="3" t="inlineStr">
@@ -19548,7 +19548,7 @@
       </c>
       <c r="D327" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_dscp_tc_change --chip=2 --dscp=46 --tc=8</t>
+          <t>1. dcat inject rNPU_dscp_tc_change --chip={chip} --dscp=46 --tc=8</t>
         </is>
       </c>
       <c r="E327" s="3" t="inlineStr">
@@ -19605,8 +19605,8 @@
       </c>
       <c r="D328" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_dscp_tc_change --chip=2 --dscp=46 --tc=0
-2. 再次 dcat inject rNPU_dscp_tc_change --chip=2 --dscp=46 --tc=0</t>
+          <t>1. dcat inject rNPU_dscp_tc_change --chip={chip} --dscp=46 --tc=3
+2. 再次 dcat inject rNPU_dscp_tc_change --chip={chip} --dscp=46 --tc=3</t>
         </is>
       </c>
       <c r="E328" s="3" t="inlineStr">
@@ -19722,7 +19722,7 @@
       </c>
       <c r="D330" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_dscp_tc_change --chip=2 --dscp=46 --tc=0
+          <t>1. dcat inject rNPU_dscp_tc_change --chip={chip} --dscp=46 --tc=3
 2. 检查注入状态</t>
         </is>
       </c>
@@ -19754,12 +19754,12 @@
       </c>
       <c r="J330" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -dscp_to_tc -g dscp 46 2&gt;/dev/null | awk '$1==46{print $2}'</t>
+          <t>hccn_tool -i {chip} -dscp_to_tc -g dscp 46 2&gt;/dev/null | awk '$1==46{print $2}'</t>
         </is>
       </c>
       <c r="K330" s="3" t="inlineStr">
         <is>
-          <t>eq:0</t>
+          <t>eq:3</t>
         </is>
       </c>
     </row>
@@ -19781,9 +19781,9 @@
       </c>
       <c r="D331" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_dscp_tc_change --chip=2 --dscp=46 --tc=0
+          <t>1. dcat inject rNPU_dscp_tc_change --chip={chip} --dscp=46 --tc=3
 2. dcat query rNPU_dscp_tc_change
-3. dcat clean rNPU_dscp_tc_change --chip=2 --dscp=46 --tc=0
+3. dcat clean rNPU_dscp_tc_change --chip={chip} --dscp=46 --tc=3
 4. dcat query rNPU_dscp_tc_change</t>
         </is>
       </c>
@@ -19844,8 +19844,8 @@
       </c>
       <c r="D332" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_dscp_tc_change --chip=2 --dscp=46 --tc=0
-2. 再次 dcat clean rNPU_dscp_tc_change --chip=2 --dscp=46 --tc=0</t>
+          <t>1. dcat clean rNPU_dscp_tc_change --chip={chip} --dscp=46 --tc=0
+2. 再次 dcat clean rNPU_dscp_tc_change --chip={chip} --dscp=46 --tc=0</t>
         </is>
       </c>
       <c r="E332" s="3" t="inlineStr">
@@ -19903,7 +19903,7 @@
       </c>
       <c r="D333" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_gw_change --chip=2 --gateway=10.30.12.1 --force</t>
+          <t>1. dcat inject rNPU_gw_change --chip={chip} --gateway=10.30.12.1 --force</t>
         </is>
       </c>
       <c r="E333" s="3" t="inlineStr">
@@ -19935,7 +19935,7 @@
       </c>
       <c r="J333" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -gateway -g 2&gt;/dev/null</t>
+          <t>hccn_tool -i {chip} -gateway -g 2&gt;/dev/null</t>
         </is>
       </c>
       <c r="K333" s="3" t="inlineStr">
@@ -20022,7 +20022,7 @@
       </c>
       <c r="D335" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rNPU_gw_change --chip=2 --gateway=&lt;同网段≠当前值&gt;</t>
+          <t>1. 执行 dcat inject rNPU_gw_change --chip={chip} --gateway=&lt;同网段≠当前值&gt;</t>
         </is>
       </c>
       <c r="E335" s="3" t="inlineStr">
@@ -20053,7 +20053,7 @@
       </c>
       <c r="J335" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -gateway -g 2&gt;/dev/null</t>
+          <t>hccn_tool -i {chip} -gateway -g 2&gt;/dev/null</t>
         </is>
       </c>
       <c r="K335" s="3" t="inlineStr">
@@ -20110,7 +20110,7 @@
       </c>
       <c r="J336" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -gateway -g 2&gt;/dev/null</t>
+          <t>hccn_tool -i {chip} -gateway -g 2&gt;/dev/null</t>
         </is>
       </c>
       <c r="K336" s="3" t="inlineStr">
@@ -20251,7 +20251,7 @@
       </c>
       <c r="D339" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_gw_change --chip=2 --gateway=10.30.12.1
+          <t>1. dcat clean rNPU_gw_change --chip={chip} --gateway=10.30.12.1
 2. dcat query（无 uid）</t>
         </is>
       </c>
@@ -20310,7 +20310,7 @@
       </c>
       <c r="D340" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_gw_change --chip=2 --gateway=10.30.12.1
+          <t>1. dcat clean rNPU_gw_change --chip={chip} --gateway=10.30.12.1
 2. 检查恢复状态</t>
         </is>
       </c>
@@ -20342,7 +20342,7 @@
       </c>
       <c r="J340" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -gateway -g 2&gt;/dev/null</t>
+          <t>hccn_tool -i {chip} -gateway -g 2&gt;/dev/null</t>
         </is>
       </c>
       <c r="K340" s="3" t="inlineStr">
@@ -20369,7 +20369,7 @@
       </c>
       <c r="D341" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_gw_change --chip=2 --gateway=invalid</t>
+          <t>1. dcat inject rNPU_gw_change --chip={chip} --gateway=invalid</t>
         </is>
       </c>
       <c r="E341" s="3" t="inlineStr">
@@ -20426,7 +20426,7 @@
       </c>
       <c r="D342" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rNPU_gw_change --chip=2 --gateway=&lt;任意&gt;
+          <t>1. 执行 dcat inject rNPU_gw_change --chip={chip} --gateway=&lt;任意&gt;
 2. 检查返回</t>
         </is>
       </c>
@@ -20544,7 +20544,7 @@
       </c>
       <c r="D344" s="3" t="inlineStr">
         <is>
-          <t>1. dcat query rNPU_gw_change --chip=2 --gateway=10.30.12.1</t>
+          <t>1. dcat query rNPU_gw_change --chip={chip} --gateway=10.30.12.1</t>
         </is>
       </c>
       <c r="E344" s="3" t="inlineStr">
@@ -20602,7 +20602,7 @@
       </c>
       <c r="D345" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat clean rNPU_gw_change --chip=2
+          <t>1. 执行 dcat clean rNPU_gw_change --chip={chip}
 2. 检查是否设回网关</t>
         </is>
       </c>
@@ -20631,7 +20631,7 @@
       <c r="I345" s="3" t="inlineStr"/>
       <c r="J345" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -gateway -g 2&gt;/dev/null</t>
+          <t>hccn_tool -i {chip} -gateway -g 2&gt;/dev/null</t>
         </is>
       </c>
       <c r="K345" s="3" t="inlineStr">
@@ -20658,8 +20658,8 @@
       </c>
       <c r="D346" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_gw_change --chip=2 --gateway=10.30.12.1
-2. 再次 dcat inject rNPU_gw_change --chip=2 --gateway=10.30.12.1</t>
+          <t>1. dcat inject rNPU_gw_change --chip={chip} --gateway=10.30.12.1
+2. 再次 dcat inject rNPU_gw_change --chip={chip} --gateway=10.30.12.1</t>
         </is>
       </c>
       <c r="E346" s="3" t="inlineStr">
@@ -20775,7 +20775,7 @@
       </c>
       <c r="D348" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_gw_change --chip=2 --gateway=10.30.12.1
+          <t>1. dcat inject rNPU_gw_change --chip={chip} --gateway=10.30.12.1
 2. 检查注入状态</t>
         </is>
       </c>
@@ -20807,7 +20807,7 @@
       </c>
       <c r="J348" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -gateway -g 2&gt;/dev/null</t>
+          <t>hccn_tool -i {chip} -gateway -g 2&gt;/dev/null</t>
         </is>
       </c>
       <c r="K348" s="3" t="inlineStr">
@@ -20834,9 +20834,9 @@
       </c>
       <c r="D349" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_gw_change --chip=2 --gateway=10.30.12.1
+          <t>1. dcat inject rNPU_gw_change --chip={chip} --gateway=10.30.12.1
 2. dcat query rNPU_gw_change
-3. dcat clean rNPU_gw_change --chip=2 --gateway=10.30.12.1
+3. dcat clean rNPU_gw_change --chip={chip} --gateway=10.30.12.1
 4. dcat query rNPU_gw_change</t>
         </is>
       </c>
@@ -20897,7 +20897,7 @@
       </c>
       <c r="D350" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rNPU_gw_change --chip=2 --gateway=10.30.12.254（与当前相同）
+          <t>1. 执行 dcat inject rNPU_gw_change --chip={chip} --gateway=10.30.12.254（与当前相同）
 2. 检查 query 返回</t>
         </is>
       </c>
@@ -20953,7 +20953,7 @@
       </c>
       <c r="D351" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rNPU_gw_change --chip=2 --gateway=10.30.12.1（同网段且≠当前网关）
+          <t>1. 执行 dcat inject rNPU_gw_change --chip={chip} --gateway=10.30.12.1（同网段且≠当前网关）
 2. 检查 sidecar 与 query</t>
         </is>
       </c>
@@ -20983,7 +20983,7 @@
       <c r="I351" s="3" t="inlineStr"/>
       <c r="J351" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -gateway -g 2&gt;/dev/null</t>
+          <t>hccn_tool -i {chip} -gateway -g 2&gt;/dev/null</t>
         </is>
       </c>
       <c r="K351" s="3" t="inlineStr">
@@ -21010,7 +21010,7 @@
       </c>
       <c r="D352" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rNPU_gw_change --chip=2 --gateway=192.168.1.1（不同网段）
+          <t>1. 执行 dcat inject rNPU_gw_change --chip={chip} --gateway=192.168.1.1（不同网段）
 2. 检查返回</t>
         </is>
       </c>
@@ -21066,8 +21066,8 @@
       </c>
       <c r="D353" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_gw_change --chip=2 --gateway=10.30.12.1
-2. 再次 dcat clean rNPU_gw_change --chip=2 --gateway=10.30.12.1</t>
+          <t>1. dcat clean rNPU_gw_change --chip={chip} --gateway=10.30.12.1
+2. 再次 dcat clean rNPU_gw_change --chip={chip} --gateway=10.30.12.1</t>
         </is>
       </c>
       <c r="E353" s="3" t="inlineStr">
@@ -21125,7 +21125,7 @@
       </c>
       <c r="D354" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_ip_change --chip=2 --address=192.168.1.100 --netmask=255.255.255.0 --force</t>
+          <t>1. dcat inject rNPU_ip_change --chip={chip} --address=192.168.1.100 --netmask=255.255.255.0 --force</t>
         </is>
       </c>
       <c r="E354" s="3" t="inlineStr">
@@ -21157,7 +21157,7 @@
       </c>
       <c r="J354" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -ip -g 2&gt;/dev/null</t>
+          <t>hccn_tool -i {chip} -ip -g 2&gt;/dev/null</t>
         </is>
       </c>
       <c r="K354" s="3" t="inlineStr">
@@ -21184,9 +21184,9 @@
       </c>
       <c r="D355" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rNPU_ip_change --chip=2 --address=192.168.1.100 --netmask=255.255.255.0
-2. 执行 dcat query rNPU_ip_change --chip=2
-3. 执行 dcat clean rNPU_ip_change --chip=2
+          <t>1. 执行 dcat inject rNPU_ip_change --chip={chip} --address=192.168.1.100 --netmask=255.255.255.0
+2. 执行 dcat query rNPU_ip_change --chip={chip}
+3. 执行 dcat clean rNPU_ip_change --chip={chip}
 4. 模拟 sidecar 丢失后 clean 验证缺省值</t>
         </is>
       </c>
@@ -21220,7 +21220,7 @@
       </c>
       <c r="J355" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -ip -g 2&gt;/dev/null</t>
+          <t>hccn_tool -i {chip} -ip -g 2&gt;/dev/null</t>
         </is>
       </c>
       <c r="K355" s="3" t="inlineStr">
@@ -21247,7 +21247,7 @@
       </c>
       <c r="D356" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_ip_change --chip=2 --address=invalid --netmask=255.255.255.0</t>
+          <t>1. dcat inject rNPU_ip_change --chip={chip} --address=invalid --netmask=255.255.255.0</t>
         </is>
       </c>
       <c r="E356" s="3" t="inlineStr">
@@ -21418,7 +21418,7 @@
       </c>
       <c r="D359" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_ip_change --chip=2 --address=192.168.1.100 --netmask=255.255.255.0
+          <t>1. dcat clean rNPU_ip_change --chip={chip} --address=192.168.1.100 --netmask=255.255.255.0
 2. dcat query（无 uid）</t>
         </is>
       </c>
@@ -21477,7 +21477,7 @@
       </c>
       <c r="D360" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_ip_change --chip=2 --address=192.168.1.100 --netmask=255.255.255.0
+          <t>1. dcat clean rNPU_ip_change --chip={chip} --address=192.168.1.100 --netmask=255.255.255.0
 2. 检查恢复状态</t>
         </is>
       </c>
@@ -21509,7 +21509,7 @@
       </c>
       <c r="J360" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -ip -g 2&gt;/dev/null</t>
+          <t>hccn_tool -i {chip} -ip -g 2&gt;/dev/null</t>
         </is>
       </c>
       <c r="K360" s="3" t="inlineStr">
@@ -21594,7 +21594,7 @@
       </c>
       <c r="D362" s="3" t="inlineStr">
         <is>
-          <t>1. dcat query rNPU_ip_change --chip=2 --address=192.168.1.100 --netmask=255.255.255.0</t>
+          <t>1. dcat query rNPU_ip_change --chip={chip} --address=192.168.1.100 --netmask=255.255.255.0</t>
         </is>
       </c>
       <c r="E362" s="3" t="inlineStr">
@@ -21652,8 +21652,8 @@
       </c>
       <c r="D363" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_ip_change --chip=2 --address=192.168.1.100 --netmask=255.255.255.0
-2. 再次 dcat inject rNPU_ip_change --chip=2 --address=192.168.1.100 --netmask=255.255.255.0</t>
+          <t>1. dcat inject rNPU_ip_change --chip={chip} --address=192.168.1.100 --netmask=255.255.255.0
+2. 再次 dcat inject rNPU_ip_change --chip={chip} --address=192.168.1.100 --netmask=255.255.255.0</t>
         </is>
       </c>
       <c r="E363" s="3" t="inlineStr">
@@ -21769,7 +21769,7 @@
       </c>
       <c r="D365" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_ip_change --chip=2 --address=192.168.1.100 --netmask=255.255.255.0
+          <t>1. dcat inject rNPU_ip_change --chip={chip} --address=192.168.1.100 --netmask=255.255.255.0
 2. 检查注入状态</t>
         </is>
       </c>
@@ -21801,7 +21801,7 @@
       </c>
       <c r="J365" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -ip -g 2&gt;/dev/null</t>
+          <t>hccn_tool -i {chip} -ip -g 2&gt;/dev/null</t>
         </is>
       </c>
       <c r="K365" s="3" t="inlineStr">
@@ -21828,9 +21828,9 @@
       </c>
       <c r="D366" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_ip_change --chip=2 --address=192.168.1.100 --netmask=255.255.255.0
+          <t>1. dcat inject rNPU_ip_change --chip={chip} --address=192.168.1.100 --netmask=255.255.255.0
 2. dcat query rNPU_ip_change
-3. dcat clean rNPU_ip_change --chip=2 --address=192.168.1.100 --netmask=255.255.255.0
+3. dcat clean rNPU_ip_change --chip={chip} --address=192.168.1.100 --netmask=255.255.255.0
 4. dcat query rNPU_ip_change</t>
         </is>
       </c>
@@ -21891,8 +21891,8 @@
       </c>
       <c r="D367" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_ip_change --chip=2 --address=192.168.1.100 --netmask=255.255.255.0
-2. 再次 dcat clean rNPU_ip_change --chip=2 --address=192.168.1.100 --netmask=255.255.255.0</t>
+          <t>1. dcat clean rNPU_ip_change --chip={chip} --address=192.168.1.100 --netmask=255.255.255.0
+2. 再次 dcat clean rNPU_ip_change --chip={chip} --address=192.168.1.100 --netmask=255.255.255.0</t>
         </is>
       </c>
       <c r="E367" s="3" t="inlineStr">
@@ -21950,7 +21950,7 @@
       </c>
       <c r="D368" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iproute --chip=2 --ip=10.30.50.0 --ip_mask=24 --via=10.30.12.254 --dev=eth2 --table=100 --force</t>
+          <t>1. dcat inject rNPU_iproute --chip={chip} --ip=10.30.50.0 --ip_mask=24 --via=10.30.12.254 --dev=eth2 --table=100 --force</t>
         </is>
       </c>
       <c r="E368" s="3" t="inlineStr">
@@ -21982,7 +21982,7 @@
       </c>
       <c r="J368" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -ip_route -g table 100 2&gt;/dev/null</t>
+          <t>hccn_tool -i {chip} -ip_route -g table 100 2&gt;/dev/null</t>
         </is>
       </c>
       <c r="K368" s="3" t="inlineStr">
@@ -22123,7 +22123,7 @@
       </c>
       <c r="D371" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_iproute --chip=2 --ip=10.30.50.0 --ip_mask=24 --via=10.30.12.254 --dev=eth2 --table=100
+          <t>1. dcat clean rNPU_iproute --chip={chip} --ip=10.30.50.0 --ip_mask=24 --via=10.30.12.254 --dev=eth2 --table=100
 2. dcat query（无 uid）</t>
         </is>
       </c>
@@ -22182,7 +22182,7 @@
       </c>
       <c r="D372" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_iproute --chip=2 --ip=10.30.50.0 --ip_mask=24 --via=10.30.12.254 --dev=eth2 --table=100
+          <t>1. dcat clean rNPU_iproute --chip={chip} --ip=10.30.50.0 --ip_mask=24 --via=10.30.12.254 --dev=eth2 --table=100
 2. 检查恢复状态</t>
         </is>
       </c>
@@ -22214,7 +22214,7 @@
       </c>
       <c r="J372" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -ip_route -g table 100 2&gt;/dev/null</t>
+          <t>hccn_tool -i {chip} -ip_route -g table 100 2&gt;/dev/null</t>
         </is>
       </c>
       <c r="K372" s="3" t="inlineStr">
@@ -22241,7 +22241,7 @@
       </c>
       <c r="D373" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iproute --chip=2 --ip=10.30.50.0 --ip_mask=-1 --via=10.30.12.254 --dev=eth2 --table=100</t>
+          <t>1. dcat inject rNPU_iproute --chip={chip} --ip=10.30.50.0 --ip_mask=-1 --via=10.30.12.254 --dev=eth2 --table=100</t>
         </is>
       </c>
       <c r="E373" s="3" t="inlineStr">
@@ -22298,7 +22298,7 @@
       </c>
       <c r="D374" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iproute --chip=2 --ip=10.30.50.0 --ip_mask=-1 --via=10.30.12.254 --dev=eth2 --table=100</t>
+          <t>1. dcat inject rNPU_iproute --chip={chip} --ip=10.30.50.0 --ip_mask=-1 --via=10.30.12.254 --dev=eth2 --table=100</t>
         </is>
       </c>
       <c r="E374" s="3" t="inlineStr">
@@ -22355,7 +22355,7 @@
       </c>
       <c r="D375" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iproute --chip=2 --ip=10.30.50.0 --ip_mask=0 --via=10.30.12.254 --dev=eth2 --table=100</t>
+          <t>1. dcat inject rNPU_iproute --chip={chip} --ip=10.30.50.0 --ip_mask=0 --via=10.30.12.254 --dev=eth2 --table=100</t>
         </is>
       </c>
       <c r="E375" s="3" t="inlineStr">
@@ -22385,7 +22385,7 @@
       </c>
       <c r="J375" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -ip_route -g table 100 2&gt;/dev/null</t>
+          <t>hccn_tool -i {chip} -ip_route -g table 100 2&gt;/dev/null</t>
         </is>
       </c>
       <c r="K375" s="3" t="inlineStr">
@@ -22412,7 +22412,7 @@
       </c>
       <c r="D376" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iproute --chip=2 --ip=10.30.50.1 --ip_mask=32 --via=10.30.12.254 --dev=eth2 --table=100</t>
+          <t>1. dcat inject rNPU_iproute --chip={chip} --ip=10.30.50.1 --ip_mask=32 --via=10.30.12.254 --dev=eth2 --table=100</t>
         </is>
       </c>
       <c r="E376" s="3" t="inlineStr">
@@ -22442,7 +22442,7 @@
       </c>
       <c r="J376" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -ip_route -g table 100 2&gt;/dev/null</t>
+          <t>hccn_tool -i {chip} -ip_route -g table 100 2&gt;/dev/null</t>
         </is>
       </c>
       <c r="K376" s="3" t="inlineStr">
@@ -22469,7 +22469,7 @@
       </c>
       <c r="D377" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iproute --chip=2 --ip=10.30.50.0 --ip_mask=33 --via=10.30.12.254 --dev=eth2 --table=100</t>
+          <t>1. dcat inject rNPU_iproute --chip={chip} --ip=10.30.50.0 --ip_mask=33 --via=10.30.12.254 --dev=eth2 --table=100</t>
         </is>
       </c>
       <c r="E377" s="3" t="inlineStr">
@@ -22584,7 +22584,7 @@
       </c>
       <c r="D379" s="3" t="inlineStr">
         <is>
-          <t>1. dcat query rNPU_iproute --chip=2 --ip=10.30.50.0 --ip_mask=24 --via=10.30.12.254 --dev=eth2 --table=100</t>
+          <t>1. dcat query rNPU_iproute --chip={chip} --ip=10.30.50.0 --ip_mask=24 --via=10.30.12.254 --dev=eth2 --table=100</t>
         </is>
       </c>
       <c r="E379" s="3" t="inlineStr">
@@ -22642,8 +22642,8 @@
       </c>
       <c r="D380" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iproute --chip=2 --ip=10.30.50.0 --ip_mask=24 --via=10.30.12.254 --dev=eth2 --table=100
-2. 再次 dcat inject rNPU_iproute --chip=2 --ip=10.30.50.0 --ip_mask=24 --via=10.30.12.254 --dev=eth2 --table=100</t>
+          <t>1. dcat inject rNPU_iproute --chip={chip} --ip=10.30.50.0 --ip_mask=24 --via=10.30.12.254 --dev=eth2 --table=100
+2. 再次 dcat inject rNPU_iproute --chip={chip} --ip=10.30.50.0 --ip_mask=24 --via=10.30.12.254 --dev=eth2 --table=100</t>
         </is>
       </c>
       <c r="E380" s="3" t="inlineStr">
@@ -22759,7 +22759,7 @@
       </c>
       <c r="D382" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iproute --chip=2 --ip=10.30.50.0 --ip_mask=24 --via=10.30.12.254 --dev=eth2 --table=100
+          <t>1. dcat inject rNPU_iproute --chip={chip} --ip=10.30.50.0 --ip_mask=24 --via=10.30.12.254 --dev=eth2 --table=100
 2. 检查注入状态</t>
         </is>
       </c>
@@ -22791,7 +22791,7 @@
       </c>
       <c r="J382" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -ip_route -g table 100 2&gt;/dev/null</t>
+          <t>hccn_tool -i {chip} -ip_route -g table 100 2&gt;/dev/null</t>
         </is>
       </c>
       <c r="K382" s="3" t="inlineStr">
@@ -22818,9 +22818,9 @@
       </c>
       <c r="D383" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rNPU_iproute --chip=2 --ip=10.30.50.0 --ip_mask=24 --via=10.30.12.254 --dev=eth2 --table=100
-2. 执行 dcat query rNPU_iproute --chip=2
-3. 执行 dcat clean rNPU_iproute --chip=2 --ip=10.30.50.0 --ip_mask=24 --table=100</t>
+          <t>1. 执行 dcat inject rNPU_iproute --chip={chip} --ip=10.30.50.0 --ip_mask=24 --via=10.30.12.254 --dev=eth2 --table=100
+2. 执行 dcat query rNPU_iproute --chip={chip}
+3. 执行 dcat clean rNPU_iproute --chip={chip} --ip=10.30.50.0 --ip_mask=24 --table=100</t>
         </is>
       </c>
       <c r="E383" s="3" t="inlineStr">
@@ -22852,7 +22852,7 @@
       </c>
       <c r="J383" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -ip_route -g table 100 2&gt;/dev/null</t>
+          <t>hccn_tool -i {chip} -ip_route -g table 100 2&gt;/dev/null</t>
         </is>
       </c>
       <c r="K383" s="3" t="inlineStr">
@@ -22879,9 +22879,9 @@
       </c>
       <c r="D384" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iproute --chip=2 --ip=10.30.50.0 --ip_mask=24 --via=10.30.12.254 --dev=eth2 --table=100
+          <t>1. dcat inject rNPU_iproute --chip={chip} --ip=10.30.50.0 --ip_mask=24 --via=10.30.12.254 --dev=eth2 --table=100
 2. dcat query rNPU_iproute
-3. dcat clean rNPU_iproute --chip=2 --ip=10.30.50.0 --ip_mask=24 --via=10.30.12.254 --dev=eth2 --table=100
+3. dcat clean rNPU_iproute --chip={chip} --ip=10.30.50.0 --ip_mask=24 --via=10.30.12.254 --dev=eth2 --table=100
 4. dcat query rNPU_iproute</t>
         </is>
       </c>
@@ -22942,8 +22942,8 @@
       </c>
       <c r="D385" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_iproute --chip=2 --ip=10.30.50.0 --ip_mask=24 --via=10.30.12.254 --dev=eth2 --table=100
-2. 再次 dcat clean rNPU_iproute --chip=2 --ip=10.30.50.0 --ip_mask=24 --via=10.30.12.254 --dev=eth2 --table=100</t>
+          <t>1. dcat clean rNPU_iproute --chip={chip} --ip=10.30.50.0 --ip_mask=24 --via=10.30.12.254 --dev=eth2 --table=100
+2. 再次 dcat clean rNPU_iproute --chip={chip} --ip=10.30.50.0 --ip_mask=24 --via=10.30.12.254 --dev=eth2 --table=100</t>
         </is>
       </c>
       <c r="E385" s="3" t="inlineStr">
@@ -23001,7 +23001,7 @@
       </c>
       <c r="D386" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iproute --chip=2 --ip=10.30.51.0 --ip_mask=24 --table=100 --force</t>
+          <t>1. dcat inject rNPU_iproute --chip={chip} --ip=10.30.51.0 --ip_mask=24 --table=100 --force</t>
         </is>
       </c>
       <c r="E386" s="3" t="inlineStr">
@@ -23033,7 +23033,7 @@
       </c>
       <c r="J386" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -ip_route -g table 100 2&gt;/dev/null</t>
+          <t>hccn_tool -i {chip} -ip_route -g table 100 2&gt;/dev/null</t>
         </is>
       </c>
       <c r="K386" s="3" t="inlineStr">
@@ -23174,7 +23174,7 @@
       </c>
       <c r="D389" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_iproute --chip=2 --ip=10.30.51.0 --ip_mask=24 --table=100
+          <t>1. dcat clean rNPU_iproute --chip={chip} --ip=10.30.51.0 --ip_mask=24 --table=100
 2. dcat query（无 uid）</t>
         </is>
       </c>
@@ -23233,7 +23233,7 @@
       </c>
       <c r="D390" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_iproute --chip=2 --ip=10.30.51.0 --ip_mask=24 --table=100
+          <t>1. dcat clean rNPU_iproute --chip={chip} --ip=10.30.51.0 --ip_mask=24 --table=100
 2. 检查恢复状态</t>
         </is>
       </c>
@@ -23265,7 +23265,7 @@
       </c>
       <c r="J390" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -ip_route -g table 100 2&gt;/dev/null</t>
+          <t>hccn_tool -i {chip} -ip_route -g table 100 2&gt;/dev/null</t>
         </is>
       </c>
       <c r="K390" s="3" t="inlineStr">
@@ -23292,7 +23292,7 @@
       </c>
       <c r="D391" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iproute --chip=2 --ip=10.30.51.0 --ip_mask=-1 --table=100</t>
+          <t>1. dcat inject rNPU_iproute --chip={chip} --ip=10.30.51.0 --ip_mask=-1 --table=100</t>
         </is>
       </c>
       <c r="E391" s="3" t="inlineStr">
@@ -23407,7 +23407,7 @@
       </c>
       <c r="D393" s="3" t="inlineStr">
         <is>
-          <t>1. dcat query rNPU_iproute --chip=2 --ip=10.30.51.0 --ip_mask=24 --table=100</t>
+          <t>1. dcat query rNPU_iproute --chip={chip} --ip=10.30.51.0 --ip_mask=24 --table=100</t>
         </is>
       </c>
       <c r="E393" s="3" t="inlineStr">
@@ -23465,9 +23465,9 @@
       </c>
       <c r="D394" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rNPU_iproute --chip=2 --ip=10.30.51.0 --ip_mask=24 --table=100
+          <t>1. 执行 dcat inject rNPU_iproute --chip={chip} --ip=10.30.51.0 --ip_mask=24 --table=100
 2. 检查未先创建时的报错
-3. 执行 dcat clean rNPU_iproute --chip=2 --ip=10.30.51.0 --ip_mask=24 --table=100</t>
+3. 执行 dcat clean rNPU_iproute --chip={chip} --ip=10.30.51.0 --ip_mask=24 --table=100</t>
         </is>
       </c>
       <c r="E394" s="3" t="inlineStr">
@@ -23499,7 +23499,7 @@
       </c>
       <c r="J394" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -ip_route -g table 100 2&gt;/dev/null</t>
+          <t>hccn_tool -i {chip} -ip_route -g table 100 2&gt;/dev/null</t>
         </is>
       </c>
       <c r="K394" s="3" t="inlineStr">
@@ -23526,8 +23526,8 @@
       </c>
       <c r="D395" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iproute --chip=2 --ip=10.30.51.0 --ip_mask=24 --table=100
-2. 再次 dcat inject rNPU_iproute --chip=2 --ip=10.30.51.0 --ip_mask=24 --table=100</t>
+          <t>1. dcat inject rNPU_iproute --chip={chip} --ip=10.30.51.0 --ip_mask=24 --table=100
+2. 再次 dcat inject rNPU_iproute --chip={chip} --ip=10.30.51.0 --ip_mask=24 --table=100</t>
         </is>
       </c>
       <c r="E395" s="3" t="inlineStr">
@@ -23643,7 +23643,7 @@
       </c>
       <c r="D397" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iproute --chip=2 --ip=10.30.51.0 --ip_mask=24 --table=100
+          <t>1. dcat inject rNPU_iproute --chip={chip} --ip=10.30.51.0 --ip_mask=24 --table=100
 2. 检查注入状态</t>
         </is>
       </c>
@@ -23675,7 +23675,7 @@
       </c>
       <c r="J397" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -ip_route -g table 100 2&gt;/dev/null</t>
+          <t>hccn_tool -i {chip} -ip_route -g table 100 2&gt;/dev/null</t>
         </is>
       </c>
       <c r="K397" s="3" t="inlineStr">
@@ -23702,9 +23702,9 @@
       </c>
       <c r="D398" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iproute --chip=2 --ip=10.30.51.0 --ip_mask=24 --table=100
+          <t>1. dcat inject rNPU_iproute --chip={chip} --ip=10.30.51.0 --ip_mask=24 --table=100
 2. dcat query rNPU_iproute
-3. dcat clean rNPU_iproute --chip=2 --ip=10.30.51.0 --ip_mask=24 --table=100
+3. dcat clean rNPU_iproute --chip={chip} --ip=10.30.51.0 --ip_mask=24 --table=100
 4. dcat query rNPU_iproute</t>
         </is>
       </c>
@@ -23765,8 +23765,8 @@
       </c>
       <c r="D399" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_iproute --chip=2 --ip=10.30.51.0 --ip_mask=24 --table=100
-2. 再次 dcat clean rNPU_iproute --chip=2 --ip=10.30.51.0 --ip_mask=24 --table=100</t>
+          <t>1. dcat clean rNPU_iproute --chip={chip} --ip=10.30.51.0 --ip_mask=24 --table=100
+2. 再次 dcat clean rNPU_iproute --chip={chip} --ip=10.30.51.0 --ip_mask=24 --table=100</t>
         </is>
       </c>
       <c r="E399" s="3" t="inlineStr">
@@ -23824,7 +23824,7 @@
       </c>
       <c r="D400" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iprule --chip=2 --dir=from --ip=10.30.12.210 --table=150 --force</t>
+          <t>1. dcat inject rNPU_iprule --chip={chip} --dir=from --ip=10.30.12.210 --table=150 --force</t>
         </is>
       </c>
       <c r="E400" s="3" t="inlineStr">
@@ -23856,7 +23856,7 @@
       </c>
       <c r="J400" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -ip_rule -g 2&gt;/dev/null</t>
+          <t>hccn_tool -i {chip} -ip_rule -g 2&gt;/dev/null</t>
         </is>
       </c>
       <c r="K400" s="3" t="inlineStr">
@@ -23997,7 +23997,7 @@
       </c>
       <c r="D403" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_iprule --chip=2 --dir=from --ip=10.30.12.210 --table=150
+          <t>1. dcat clean rNPU_iprule --chip={chip} --dir=from --ip=10.30.12.210 --table=150
 2. dcat query（无 uid）</t>
         </is>
       </c>
@@ -24056,7 +24056,7 @@
       </c>
       <c r="D404" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_iprule --chip=2 --dir=from --ip=10.30.12.210 --table=150
+          <t>1. dcat clean rNPU_iprule --chip={chip} --dir=from --ip=10.30.12.210 --table=150
 2. 检查恢复状态</t>
         </is>
       </c>
@@ -24088,7 +24088,7 @@
       </c>
       <c r="J404" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -ip_rule -g 2&gt;/dev/null</t>
+          <t>hccn_tool -i {chip} -ip_rule -g 2&gt;/dev/null</t>
         </is>
       </c>
       <c r="K404" s="3" t="inlineStr">
@@ -24173,7 +24173,7 @@
       </c>
       <c r="D406" s="3" t="inlineStr">
         <is>
-          <t>1. dcat query rNPU_iprule --chip=2 --dir=from --ip=10.30.12.210 --table=150</t>
+          <t>1. dcat query rNPU_iprule --chip={chip} --dir=from --ip=10.30.12.210 --table=150</t>
         </is>
       </c>
       <c r="E406" s="3" t="inlineStr">
@@ -24231,7 +24231,7 @@
       </c>
       <c r="D407" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iprule --chip=2 --dir=from --ip=10.30.12.210 --table=-1</t>
+          <t>1. dcat inject rNPU_iprule --chip={chip} --dir=from --ip=10.30.12.210 --table=-1</t>
         </is>
       </c>
       <c r="E407" s="3" t="inlineStr">
@@ -24288,7 +24288,7 @@
       </c>
       <c r="D408" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iprule --chip=2 --dir=from --ip=10.30.12.210 --table=-1</t>
+          <t>1. dcat inject rNPU_iprule --chip={chip} --dir=from --ip=10.30.12.210 --table=-1</t>
         </is>
       </c>
       <c r="E408" s="3" t="inlineStr">
@@ -24345,7 +24345,7 @@
       </c>
       <c r="D409" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iprule --chip=2 --dir=from --ip=10.30.12.210 --table=0</t>
+          <t>1. dcat inject rNPU_iprule --chip={chip} --dir=from --ip=10.30.12.210 --table=0</t>
         </is>
       </c>
       <c r="E409" s="3" t="inlineStr">
@@ -24375,7 +24375,7 @@
       </c>
       <c r="J409" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -ip_rule -g 2&gt;/dev/null</t>
+          <t>hccn_tool -i {chip} -ip_rule -g 2&gt;/dev/null</t>
         </is>
       </c>
       <c r="K409" s="3" t="inlineStr">
@@ -24402,7 +24402,7 @@
       </c>
       <c r="D410" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iprule --chip=2 --dir=from --ip=10.30.12.210 --table=255</t>
+          <t>1. dcat inject rNPU_iprule --chip={chip} --dir=from --ip=10.30.12.210 --table=255</t>
         </is>
       </c>
       <c r="E410" s="3" t="inlineStr">
@@ -24432,7 +24432,7 @@
       </c>
       <c r="J410" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -ip_rule -g 2&gt;/dev/null</t>
+          <t>hccn_tool -i {chip} -ip_rule -g 2&gt;/dev/null</t>
         </is>
       </c>
       <c r="K410" s="3" t="inlineStr">
@@ -24459,7 +24459,7 @@
       </c>
       <c r="D411" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iprule --chip=2 --dir=from --ip=10.30.12.210 --table=256</t>
+          <t>1. dcat inject rNPU_iprule --chip={chip} --dir=from --ip=10.30.12.210 --table=256</t>
         </is>
       </c>
       <c r="E411" s="3" t="inlineStr">
@@ -24516,8 +24516,8 @@
       </c>
       <c r="D412" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iprule --chip=2 --dir=from --ip=10.30.12.210 --table=150
-2. 再次 dcat inject rNPU_iprule --chip=2 --dir=from --ip=10.30.12.210 --table=150</t>
+          <t>1. dcat inject rNPU_iprule --chip={chip} --dir=from --ip=10.30.12.210 --table=150
+2. 再次 dcat inject rNPU_iprule --chip={chip} --dir=from --ip=10.30.12.210 --table=150</t>
         </is>
       </c>
       <c r="E412" s="3" t="inlineStr">
@@ -24633,7 +24633,7 @@
       </c>
       <c r="D414" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iprule --chip=2 --dir=from --ip=10.30.12.210 --table=150
+          <t>1. dcat inject rNPU_iprule --chip={chip} --dir=from --ip=10.30.12.210 --table=150
 2. 检查注入状态</t>
         </is>
       </c>
@@ -24665,7 +24665,7 @@
       </c>
       <c r="J414" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -ip_rule -g 2&gt;/dev/null</t>
+          <t>hccn_tool -i {chip} -ip_rule -g 2&gt;/dev/null</t>
         </is>
       </c>
       <c r="K414" s="3" t="inlineStr">
@@ -24692,9 +24692,9 @@
       </c>
       <c r="D415" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rNPU_iprule --chip=2 --dir=from --ip=10.30.12.210 --table=150
-2. 执行 dcat query rNPU_iprule --chip=2
-3. 执行 dcat clean rNPU_iprule --chip=2 --dir=from --ip=10.30.12.210 --table=150</t>
+          <t>1. 执行 dcat inject rNPU_iprule --chip={chip} --dir=from --ip=10.30.12.210 --table=150
+2. 执行 dcat query rNPU_iprule --chip={chip}
+3. 执行 dcat clean rNPU_iprule --chip={chip} --dir=from --ip=10.30.12.210 --table=150</t>
         </is>
       </c>
       <c r="E415" s="3" t="inlineStr">
@@ -24726,7 +24726,7 @@
       </c>
       <c r="J415" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -ip_rule -g 2&gt;/dev/null</t>
+          <t>hccn_tool -i {chip} -ip_rule -g 2&gt;/dev/null</t>
         </is>
       </c>
       <c r="K415" s="3" t="inlineStr">
@@ -24753,9 +24753,9 @@
       </c>
       <c r="D416" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iprule --chip=2 --dir=from --ip=10.30.12.210 --table=150
+          <t>1. dcat inject rNPU_iprule --chip={chip} --dir=from --ip=10.30.12.210 --table=150
 2. dcat query rNPU_iprule
-3. dcat clean rNPU_iprule --chip=2 --dir=from --ip=10.30.12.210 --table=150
+3. dcat clean rNPU_iprule --chip={chip} --dir=from --ip=10.30.12.210 --table=150
 4. dcat query rNPU_iprule</t>
         </is>
       </c>
@@ -24816,8 +24816,8 @@
       </c>
       <c r="D417" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_iprule --chip=2 --dir=from --ip=10.30.12.210 --table=150
-2. 再次 dcat clean rNPU_iprule --chip=2 --dir=from --ip=10.30.12.210 --table=150</t>
+          <t>1. dcat clean rNPU_iprule --chip={chip} --dir=from --ip=10.30.12.210 --table=150
+2. 再次 dcat clean rNPU_iprule --chip={chip} --dir=from --ip=10.30.12.210 --table=150</t>
         </is>
       </c>
       <c r="E417" s="3" t="inlineStr">
@@ -24875,7 +24875,7 @@
       </c>
       <c r="D418" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iprule --chip=2 --dir=from --ip=10.30.12.211 --force</t>
+          <t>1. dcat inject rNPU_iprule --chip={chip} --dir=from --ip=10.30.12.211 --force</t>
         </is>
       </c>
       <c r="E418" s="3" t="inlineStr">
@@ -24907,7 +24907,7 @@
       </c>
       <c r="J418" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -ip_rule -g 2&gt;/dev/null</t>
+          <t>hccn_tool -i {chip} -ip_rule -g 2&gt;/dev/null</t>
         </is>
       </c>
       <c r="K418" s="3" t="inlineStr">
@@ -25048,7 +25048,7 @@
       </c>
       <c r="D421" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_iprule --chip=2 --dir=from --ip=10.30.12.211
+          <t>1. dcat clean rNPU_iprule --chip={chip} --dir=from --ip=10.30.12.211
 2. dcat query（无 uid）</t>
         </is>
       </c>
@@ -25107,7 +25107,7 @@
       </c>
       <c r="D422" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_iprule --chip=2 --dir=from --ip=10.30.12.211
+          <t>1. dcat clean rNPU_iprule --chip={chip} --dir=from --ip=10.30.12.211
 2. 检查恢复状态</t>
         </is>
       </c>
@@ -25139,7 +25139,7 @@
       </c>
       <c r="J422" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -ip_rule -g 2&gt;/dev/null</t>
+          <t>hccn_tool -i {chip} -ip_rule -g 2&gt;/dev/null</t>
         </is>
       </c>
       <c r="K422" s="3" t="inlineStr">
@@ -25166,7 +25166,7 @@
       </c>
       <c r="D423" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iprule --chip=2 --dir=invalid --ip=10.30.12.211</t>
+          <t>1. dcat inject rNPU_iprule --chip={chip} --dir=invalid --ip=10.30.12.211</t>
         </is>
       </c>
       <c r="E423" s="3" t="inlineStr">
@@ -25281,7 +25281,7 @@
       </c>
       <c r="D425" s="3" t="inlineStr">
         <is>
-          <t>1. dcat query rNPU_iprule --chip=2 --dir=from --ip=10.30.12.211</t>
+          <t>1. dcat query rNPU_iprule --chip={chip} --dir=from --ip=10.30.12.211</t>
         </is>
       </c>
       <c r="E425" s="3" t="inlineStr">
@@ -25339,9 +25339,9 @@
       </c>
       <c r="D426" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rNPU_iprule --chip=2 --dir=from --ip=10.30.12.211
+          <t>1. 执行 dcat inject rNPU_iprule --chip={chip} --dir=from --ip=10.30.12.211
 2. 检查未先创建时的报错
-3. 执行 dcat clean rNPU_iprule --chip=2 --dir=from --ip=10.30.12.211</t>
+3. 执行 dcat clean rNPU_iprule --chip={chip} --dir=from --ip=10.30.12.211</t>
         </is>
       </c>
       <c r="E426" s="3" t="inlineStr">
@@ -25373,7 +25373,7 @@
       </c>
       <c r="J426" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -ip_rule -g 2&gt;/dev/null</t>
+          <t>hccn_tool -i {chip} -ip_rule -g 2&gt;/dev/null</t>
         </is>
       </c>
       <c r="K426" s="3" t="inlineStr">
@@ -25400,8 +25400,8 @@
       </c>
       <c r="D427" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iprule --chip=2 --dir=from --ip=10.30.12.211
-2. 再次 dcat inject rNPU_iprule --chip=2 --dir=from --ip=10.30.12.211</t>
+          <t>1. dcat inject rNPU_iprule --chip={chip} --dir=from --ip=10.30.12.211
+2. 再次 dcat inject rNPU_iprule --chip={chip} --dir=from --ip=10.30.12.211</t>
         </is>
       </c>
       <c r="E427" s="3" t="inlineStr">
@@ -25517,7 +25517,7 @@
       </c>
       <c r="D429" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iprule --chip=2 --dir=from --ip=10.30.12.211
+          <t>1. dcat inject rNPU_iprule --chip={chip} --dir=from --ip=10.30.12.211
 2. 检查注入状态</t>
         </is>
       </c>
@@ -25549,7 +25549,7 @@
       </c>
       <c r="J429" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -ip_rule -g 2&gt;/dev/null</t>
+          <t>hccn_tool -i {chip} -ip_rule -g 2&gt;/dev/null</t>
         </is>
       </c>
       <c r="K429" s="3" t="inlineStr">
@@ -25576,9 +25576,9 @@
       </c>
       <c r="D430" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iprule --chip=2 --dir=from --ip=10.30.12.211
+          <t>1. dcat inject rNPU_iprule --chip={chip} --dir=from --ip=10.30.12.211
 2. dcat query rNPU_iprule
-3. dcat clean rNPU_iprule --chip=2 --dir=from --ip=10.30.12.211
+3. dcat clean rNPU_iprule --chip={chip} --dir=from --ip=10.30.12.211
 4. dcat query rNPU_iprule</t>
         </is>
       </c>
@@ -25639,8 +25639,8 @@
       </c>
       <c r="D431" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_iprule --chip=2 --dir=from --ip=10.30.12.211
-2. 再次 dcat clean rNPU_iprule --chip=2 --dir=from --ip=10.30.12.211</t>
+          <t>1. dcat clean rNPU_iprule --chip={chip} --dir=from --ip=10.30.12.211
+2. 再次 dcat clean rNPU_iprule --chip={chip} --dir=from --ip=10.30.12.211</t>
         </is>
       </c>
       <c r="E431" s="3" t="inlineStr">
@@ -25698,7 +25698,7 @@
       </c>
       <c r="D432" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_link_down --chip=2 --force</t>
+          <t>1. dcat inject rNPU_link_down --chip={chip} --force</t>
         </is>
       </c>
       <c r="E432" s="3" t="inlineStr">
@@ -25730,7 +25730,7 @@
       </c>
       <c r="J432" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -link -g 2&gt;/dev/null</t>
+          <t>hccn_tool -i {chip} -link -g 2&gt;/dev/null</t>
         </is>
       </c>
       <c r="K432" s="3" t="inlineStr">
@@ -25757,9 +25757,9 @@
       </c>
       <c r="D433" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rNPU_link_down --chip=2
-2. 执行 dcat query rNPU_link_down --chip=2
-3. 执行 dcat clean rNPU_link_down --chip=2</t>
+          <t>1. 执行 dcat inject rNPU_link_down --chip={chip}
+2. 执行 dcat query rNPU_link_down --chip={chip}
+3. 执行 dcat clean rNPU_link_down --chip={chip}</t>
         </is>
       </c>
       <c r="E433" s="3" t="inlineStr">
@@ -25791,7 +25791,7 @@
       </c>
       <c r="J433" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -link -g 2&gt;/dev/null</t>
+          <t>hccn_tool -i {chip} -link -g 2&gt;/dev/null</t>
         </is>
       </c>
       <c r="K433" s="3" t="inlineStr">
@@ -25989,7 +25989,7 @@
       </c>
       <c r="D437" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_link_down --chip=2
+          <t>1. dcat clean rNPU_link_down --chip={chip}
 2. dcat query（无 uid）</t>
         </is>
       </c>
@@ -26048,7 +26048,7 @@
       </c>
       <c r="D438" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_link_down --chip=2
+          <t>1. dcat clean rNPU_link_down --chip={chip}
 2. 检查恢复状态</t>
         </is>
       </c>
@@ -26080,7 +26080,7 @@
       </c>
       <c r="J438" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -link -g 2&gt;/dev/null</t>
+          <t>hccn_tool -i {chip} -link -g 2&gt;/dev/null</t>
         </is>
       </c>
       <c r="K438" s="3" t="inlineStr">
@@ -26165,7 +26165,7 @@
       </c>
       <c r="D440" s="3" t="inlineStr">
         <is>
-          <t>1. dcat query rNPU_link_down --chip=2</t>
+          <t>1. dcat query rNPU_link_down --chip={chip}</t>
         </is>
       </c>
       <c r="E440" s="3" t="inlineStr">
@@ -26223,8 +26223,8 @@
       </c>
       <c r="D441" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_link_down --chip=2
-2. 再次 dcat inject rNPU_link_down --chip=2</t>
+          <t>1. dcat inject rNPU_link_down --chip={chip}
+2. 再次 dcat inject rNPU_link_down --chip={chip}</t>
         </is>
       </c>
       <c r="E441" s="3" t="inlineStr">
@@ -26340,7 +26340,7 @@
       </c>
       <c r="D443" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_link_down --chip=2
+          <t>1. dcat inject rNPU_link_down --chip={chip}
 2. 检查注入状态</t>
         </is>
       </c>
@@ -26372,7 +26372,7 @@
       </c>
       <c r="J443" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -link -g 2&gt;/dev/null</t>
+          <t>hccn_tool -i {chip} -link -g 2&gt;/dev/null</t>
         </is>
       </c>
       <c r="K443" s="3" t="inlineStr">
@@ -26399,9 +26399,9 @@
       </c>
       <c r="D444" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_link_down --chip=2
+          <t>1. dcat inject rNPU_link_down --chip={chip}
 2. dcat query rNPU_link_down
-3. dcat clean rNPU_link_down --chip=2
+3. dcat clean rNPU_link_down --chip={chip}
 4. dcat query rNPU_link_down</t>
         </is>
       </c>
@@ -26462,8 +26462,8 @@
       </c>
       <c r="D445" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_link_down --chip=2
-2. 再次 dcat clean rNPU_link_down --chip=2</t>
+          <t>1. dcat clean rNPU_link_down --chip={chip}
+2. 再次 dcat clean rNPU_link_down --chip={chip}</t>
         </is>
       </c>
       <c r="E445" s="3" t="inlineStr">
@@ -26521,7 +26521,7 @@
       </c>
       <c r="D446" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_mtu_mismatch --chip=2 --size=1280 --force</t>
+          <t>1. dcat inject rNPU_mtu_mismatch --chip={chip} --size=1280 --force</t>
         </is>
       </c>
       <c r="E446" s="3" t="inlineStr">
@@ -26553,7 +26553,7 @@
       </c>
       <c r="J446" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -mtu -g 2&gt;/dev/null | grep -oE 'mtu:[0-9]+'</t>
+          <t>hccn_tool -i {chip} -mtu -g 2&gt;/dev/null | grep -oE 'mtu:[0-9]+'</t>
         </is>
       </c>
       <c r="K446" s="3" t="inlineStr">
@@ -26580,10 +26580,10 @@
       </c>
       <c r="D447" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rNPU_mtu_mismatch --chip=2 --size=1280
-2. 执行 dcat query rNPU_mtu_mismatch --chip=2
+          <t>1. 执行 dcat inject rNPU_mtu_mismatch --chip={chip} --size=1280
+2. 执行 dcat query rNPU_mtu_mismatch --chip={chip}
 3. 检查 size=当前值时的 no-op
-4. 执行 dcat clean rNPU_mtu_mismatch --chip=2</t>
+4. 执行 dcat clean rNPU_mtu_mismatch --chip={chip}</t>
         </is>
       </c>
       <c r="E447" s="3" t="inlineStr">
@@ -26643,7 +26643,7 @@
       </c>
       <c r="D448" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_mtu_mismatch --chip=2 --size=1280
+          <t>1. dcat clean rNPU_mtu_mismatch --chip={chip} --size=1280
 2. dcat query（无 uid）</t>
         </is>
       </c>
@@ -26702,7 +26702,7 @@
       </c>
       <c r="D449" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_mtu_mismatch --chip=2 --size=1280
+          <t>1. dcat clean rNPU_mtu_mismatch --chip={chip} --size=1280
 2. 检查恢复状态</t>
         </is>
       </c>
@@ -26734,7 +26734,7 @@
       </c>
       <c r="J449" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -mtu -g 2&gt;/dev/null | grep -oE 'mtu:[0-9]+'</t>
+          <t>hccn_tool -i {chip} -mtu -g 2&gt;/dev/null | grep -oE 'mtu:[0-9]+'</t>
         </is>
       </c>
       <c r="K449" s="3" t="inlineStr">
@@ -26819,7 +26819,7 @@
       </c>
       <c r="D451" s="3" t="inlineStr">
         <is>
-          <t>1. dcat query rNPU_mtu_mismatch --chip=2 --size=1280</t>
+          <t>1. dcat query rNPU_mtu_mismatch --chip={chip} --size=1280</t>
         </is>
       </c>
       <c r="E451" s="3" t="inlineStr">
@@ -26877,7 +26877,7 @@
       </c>
       <c r="D452" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rNPU_mtu_mismatch --chip=2 --size=0
+          <t>1. 执行 dcat inject rNPU_mtu_mismatch --chip={chip} --size=0
 2. 执行 --size=-1 / --size=abc</t>
         </is>
       </c>
@@ -26936,7 +26936,7 @@
       </c>
       <c r="D453" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_mtu_mismatch --chip=2 --size=-1</t>
+          <t>1. dcat inject rNPU_mtu_mismatch --chip={chip} --size=-1</t>
         </is>
       </c>
       <c r="E453" s="3" t="inlineStr">
@@ -26993,7 +26993,7 @@
       </c>
       <c r="D454" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_mtu_mismatch --chip=2 --size=0</t>
+          <t>1. dcat inject rNPU_mtu_mismatch --chip={chip} --size=0</t>
         </is>
       </c>
       <c r="E454" s="3" t="inlineStr">
@@ -27050,7 +27050,7 @@
       </c>
       <c r="D455" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_mtu_mismatch --chip=2 --size=abc</t>
+          <t>1. dcat inject rNPU_mtu_mismatch --chip={chip} --size=abc</t>
         </is>
       </c>
       <c r="E455" s="3" t="inlineStr">
@@ -27107,8 +27107,8 @@
       </c>
       <c r="D456" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_mtu_mismatch --chip=2 --size=1280
-2. 再次 dcat inject rNPU_mtu_mismatch --chip=2 --size=1280</t>
+          <t>1. dcat inject rNPU_mtu_mismatch --chip={chip} --size=1280
+2. 再次 dcat inject rNPU_mtu_mismatch --chip={chip} --size=1280</t>
         </is>
       </c>
       <c r="E456" s="3" t="inlineStr">
@@ -27224,7 +27224,7 @@
       </c>
       <c r="D458" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_mtu_mismatch --chip=2 --size=1280
+          <t>1. dcat inject rNPU_mtu_mismatch --chip={chip} --size=1280
 2. 检查注入状态</t>
         </is>
       </c>
@@ -27256,7 +27256,7 @@
       </c>
       <c r="J458" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -mtu -g 2&gt;/dev/null | grep -oE 'mtu:[0-9]+'</t>
+          <t>hccn_tool -i {chip} -mtu -g 2&gt;/dev/null | grep -oE 'mtu:[0-9]+'</t>
         </is>
       </c>
       <c r="K458" s="3" t="inlineStr">
@@ -27283,9 +27283,9 @@
       </c>
       <c r="D459" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_mtu_mismatch --chip=2 --size=1280
+          <t>1. dcat inject rNPU_mtu_mismatch --chip={chip} --size=1280
 2. dcat query rNPU_mtu_mismatch
-3. dcat clean rNPU_mtu_mismatch --chip=2 --size=1280
+3. dcat clean rNPU_mtu_mismatch --chip={chip} --size=1280
 4. dcat query rNPU_mtu_mismatch</t>
         </is>
       </c>
@@ -27346,8 +27346,8 @@
       </c>
       <c r="D460" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_mtu_mismatch --chip=2 --size=1280
-2. 再次 dcat clean rNPU_mtu_mismatch --chip=2 --size=1280</t>
+          <t>1. dcat clean rNPU_mtu_mismatch --chip={chip} --size=1280
+2. 再次 dcat clean rNPU_mtu_mismatch --chip={chip} --size=1280</t>
         </is>
       </c>
       <c r="E460" s="3" t="inlineStr">
@@ -27405,7 +27405,7 @@
       </c>
       <c r="D461" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_netdetect_change --chip=2 --address=10.0.0.99 --force</t>
+          <t>1. dcat inject rNPU_netdetect_change --chip={chip} --address=10.0.0.99 --force</t>
         </is>
       </c>
       <c r="E461" s="3" t="inlineStr">
@@ -27437,7 +27437,7 @@
       </c>
       <c r="J461" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -netdetect -g 2&gt;/dev/null</t>
+          <t>hccn_tool -i {chip} -netdetect -g 2&gt;/dev/null</t>
         </is>
       </c>
       <c r="K461" s="3" t="inlineStr">
@@ -27464,9 +27464,9 @@
       </c>
       <c r="D462" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rNPU_netdetect_change --chip=2 --address=10.0.0.99
-2. 执行 dcat query rNPU_netdetect_change --chip=2
-3. 执行 dcat clean rNPU_netdetect_change --chip=2</t>
+          <t>1. 执行 dcat inject rNPU_netdetect_change --chip={chip} --address=10.0.0.99
+2. 执行 dcat query rNPU_netdetect_change --chip={chip}
+3. 执行 dcat clean rNPU_netdetect_change --chip={chip}</t>
         </is>
       </c>
       <c r="E462" s="3" t="inlineStr">
@@ -27498,7 +27498,7 @@
       </c>
       <c r="J462" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -netdetect -g 2&gt;/dev/null</t>
+          <t>hccn_tool -i {chip} -netdetect -g 2&gt;/dev/null</t>
         </is>
       </c>
       <c r="K462" s="3" t="inlineStr">
@@ -27525,7 +27525,7 @@
       </c>
       <c r="D463" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_netdetect_change --chip=2 --address=invalid</t>
+          <t>1. dcat inject rNPU_netdetect_change --chip={chip} --address=invalid</t>
         </is>
       </c>
       <c r="E463" s="3" t="inlineStr">
@@ -27696,7 +27696,7 @@
       </c>
       <c r="D466" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_netdetect_change --chip=2 --address=10.0.0.99
+          <t>1. dcat clean rNPU_netdetect_change --chip={chip} --address=10.0.0.99
 2. dcat query（无 uid）</t>
         </is>
       </c>
@@ -27755,7 +27755,7 @@
       </c>
       <c r="D467" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_netdetect_change --chip=2 --address=10.0.0.99
+          <t>1. dcat clean rNPU_netdetect_change --chip={chip} --address=10.0.0.99
 2. 检查恢复状态</t>
         </is>
       </c>
@@ -27787,7 +27787,7 @@
       </c>
       <c r="J467" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -netdetect -g 2&gt;/dev/null</t>
+          <t>hccn_tool -i {chip} -netdetect -g 2&gt;/dev/null</t>
         </is>
       </c>
       <c r="K467" s="3" t="inlineStr">
@@ -27872,7 +27872,7 @@
       </c>
       <c r="D469" s="3" t="inlineStr">
         <is>
-          <t>1. dcat query rNPU_netdetect_change --chip=2 --address=10.0.0.99</t>
+          <t>1. dcat query rNPU_netdetect_change --chip={chip} --address=10.0.0.99</t>
         </is>
       </c>
       <c r="E469" s="3" t="inlineStr">
@@ -27930,8 +27930,8 @@
       </c>
       <c r="D470" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_netdetect_change --chip=2 --address=10.0.0.99
-2. 再次 dcat inject rNPU_netdetect_change --chip=2 --address=10.0.0.99</t>
+          <t>1. dcat inject rNPU_netdetect_change --chip={chip} --address=10.0.0.99
+2. 再次 dcat inject rNPU_netdetect_change --chip={chip} --address=10.0.0.99</t>
         </is>
       </c>
       <c r="E470" s="3" t="inlineStr">
@@ -28047,7 +28047,7 @@
       </c>
       <c r="D472" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_netdetect_change --chip=2 --address=10.0.0.99
+          <t>1. dcat inject rNPU_netdetect_change --chip={chip} --address=10.0.0.99
 2. 检查注入状态</t>
         </is>
       </c>
@@ -28079,7 +28079,7 @@
       </c>
       <c r="J472" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -netdetect -g 2&gt;/dev/null</t>
+          <t>hccn_tool -i {chip} -netdetect -g 2&gt;/dev/null</t>
         </is>
       </c>
       <c r="K472" s="3" t="inlineStr">
@@ -28106,9 +28106,9 @@
       </c>
       <c r="D473" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_netdetect_change --chip=2 --address=10.0.0.99
+          <t>1. dcat inject rNPU_netdetect_change --chip={chip} --address=10.0.0.99
 2. dcat query rNPU_netdetect_change
-3. dcat clean rNPU_netdetect_change --chip=2 --address=10.0.0.99
+3. dcat clean rNPU_netdetect_change --chip={chip} --address=10.0.0.99
 4. dcat query rNPU_netdetect_change</t>
         </is>
       </c>
@@ -28169,8 +28169,8 @@
       </c>
       <c r="D474" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_netdetect_change --chip=2 --address=10.0.0.99
-2. 再次 dcat clean rNPU_netdetect_change --chip=2 --address=10.0.0.99</t>
+          <t>1. dcat clean rNPU_netdetect_change --chip={chip} --address=10.0.0.99
+2. 再次 dcat clean rNPU_netdetect_change --chip={chip} --address=10.0.0.99</t>
         </is>
       </c>
       <c r="E474" s="3" t="inlineStr">
@@ -28228,7 +28228,7 @@
       </c>
       <c r="D475" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_roce_port_change --chip=2 --port=4792 --force</t>
+          <t>1. dcat inject rNPU_roce_port_change --chip={chip} --port=4792 --force</t>
         </is>
       </c>
       <c r="E475" s="3" t="inlineStr">
@@ -28260,7 +28260,7 @@
       </c>
       <c r="J475" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -udp -g 2&gt;/dev/null</t>
+          <t>hccn_tool -i {chip} -udp -g 2&gt;/dev/null</t>
         </is>
       </c>
       <c r="K475" s="3" t="inlineStr">
@@ -28287,9 +28287,9 @@
       </c>
       <c r="D476" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rNPU_roce_port_change --chip=2 --port=4792
-2. 执行 dcat query rNPU_roce_port_change --chip=2
-3. 执行 dcat clean rNPU_roce_port_change --chip=2</t>
+          <t>1. 执行 dcat inject rNPU_roce_port_change --chip={chip} --port=4792
+2. 执行 dcat query rNPU_roce_port_change --chip={chip}
+3. 执行 dcat clean rNPU_roce_port_change --chip={chip}</t>
         </is>
       </c>
       <c r="E476" s="3" t="inlineStr">
@@ -28321,7 +28321,7 @@
       </c>
       <c r="J476" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -udp -g 2&gt;/dev/null</t>
+          <t>hccn_tool -i {chip} -udp -g 2&gt;/dev/null</t>
         </is>
       </c>
       <c r="K476" s="3" t="inlineStr">
@@ -28348,7 +28348,7 @@
       </c>
       <c r="D477" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_roce_port_change --chip=2 --port=4792
+          <t>1. dcat clean rNPU_roce_port_change --chip={chip} --port=4792
 2. dcat query（无 uid）</t>
         </is>
       </c>
@@ -28407,7 +28407,7 @@
       </c>
       <c r="D478" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_roce_port_change --chip=2 --port=4792
+          <t>1. dcat clean rNPU_roce_port_change --chip={chip} --port=4792
 2. 检查恢复状态</t>
         </is>
       </c>
@@ -28439,7 +28439,7 @@
       </c>
       <c r="J478" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -udp -g 2&gt;/dev/null</t>
+          <t>hccn_tool -i {chip} -udp -g 2&gt;/dev/null</t>
         </is>
       </c>
       <c r="K478" s="3" t="inlineStr">
@@ -28466,7 +28466,7 @@
       </c>
       <c r="D479" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_roce_port_change --chip=2 --port=-1</t>
+          <t>1. dcat inject rNPU_roce_port_change --chip={chip} --port=-1</t>
         </is>
       </c>
       <c r="E479" s="3" t="inlineStr">
@@ -28523,7 +28523,7 @@
       </c>
       <c r="D480" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_roce_port_change --chip=2 --port=0</t>
+          <t>1. dcat inject rNPU_roce_port_change --chip={chip} --port=0</t>
         </is>
       </c>
       <c r="E480" s="3" t="inlineStr">
@@ -28580,7 +28580,7 @@
       </c>
       <c r="D481" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_roce_port_change --chip=2 --port=65536</t>
+          <t>1. dcat inject rNPU_roce_port_change --chip={chip} --port=65536</t>
         </is>
       </c>
       <c r="E481" s="3" t="inlineStr">
@@ -28695,7 +28695,7 @@
       </c>
       <c r="D483" s="3" t="inlineStr">
         <is>
-          <t>1. dcat query rNPU_roce_port_change --chip=2 --port=4792</t>
+          <t>1. dcat query rNPU_roce_port_change --chip={chip} --port=4792</t>
         </is>
       </c>
       <c r="E483" s="3" t="inlineStr">
@@ -28753,8 +28753,8 @@
       </c>
       <c r="D484" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_roce_port_change --chip=2 --port=4792
-2. 再次 dcat inject rNPU_roce_port_change --chip=2 --port=4792</t>
+          <t>1. dcat inject rNPU_roce_port_change --chip={chip} --port=4792
+2. 再次 dcat inject rNPU_roce_port_change --chip={chip} --port=4792</t>
         </is>
       </c>
       <c r="E484" s="3" t="inlineStr">
@@ -28870,7 +28870,7 @@
       </c>
       <c r="D486" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_roce_port_change --chip=2 --port=4792
+          <t>1. dcat inject rNPU_roce_port_change --chip={chip} --port=4792
 2. 检查注入状态</t>
         </is>
       </c>
@@ -28902,7 +28902,7 @@
       </c>
       <c r="J486" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -udp -g 2&gt;/dev/null</t>
+          <t>hccn_tool -i {chip} -udp -g 2&gt;/dev/null</t>
         </is>
       </c>
       <c r="K486" s="3" t="inlineStr">
@@ -28929,9 +28929,9 @@
       </c>
       <c r="D487" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_roce_port_change --chip=2 --port=4792
+          <t>1. dcat inject rNPU_roce_port_change --chip={chip} --port=4792
 2. dcat query rNPU_roce_port_change
-3. dcat clean rNPU_roce_port_change --chip=2 --port=4792
+3. dcat clean rNPU_roce_port_change --chip={chip} --port=4792
 4. dcat query rNPU_roce_port_change</t>
         </is>
       </c>
@@ -28992,8 +28992,8 @@
       </c>
       <c r="D488" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_roce_port_change --chip=2 --port=4792
-2. 再次 dcat clean rNPU_roce_port_change --chip=2 --port=4792</t>
+          <t>1. dcat clean rNPU_roce_port_change --chip={chip} --port=4792
+2. 再次 dcat clean rNPU_roce_port_change --chip={chip} --port=4792</t>
         </is>
       </c>
       <c r="E488" s="3" t="inlineStr">
@@ -29051,7 +29051,7 @@
       </c>
       <c r="D489" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_route --chip=2 --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254 --force</t>
+          <t>1. dcat inject rNPU_route --chip={chip} --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254 --force</t>
         </is>
       </c>
       <c r="E489" s="3" t="inlineStr">
@@ -29083,7 +29083,7 @@
       </c>
       <c r="J489" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -route -g 2&gt;/dev/null</t>
+          <t>hccn_tool -i {chip} -route -g 2&gt;/dev/null</t>
         </is>
       </c>
       <c r="K489" s="3" t="inlineStr">
@@ -29110,7 +29110,7 @@
       </c>
       <c r="D490" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_route --chip=2 --address=invalid --netmask=255.255.255.0 --gateway=10.30.12.254</t>
+          <t>1. dcat inject rNPU_route --chip={chip} --address=invalid --netmask=255.255.255.0 --gateway=10.30.12.254</t>
         </is>
       </c>
       <c r="E490" s="3" t="inlineStr">
@@ -29281,7 +29281,7 @@
       </c>
       <c r="D493" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_route --chip=2 --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254
+          <t>1. dcat clean rNPU_route --chip={chip} --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254
 2. dcat query（无 uid）</t>
         </is>
       </c>
@@ -29340,7 +29340,7 @@
       </c>
       <c r="D494" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_route --chip=2 --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254
+          <t>1. dcat clean rNPU_route --chip={chip} --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254
 2. 检查恢复状态</t>
         </is>
       </c>
@@ -29372,7 +29372,7 @@
       </c>
       <c r="J494" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -route -g 2&gt;/dev/null</t>
+          <t>hccn_tool -i {chip} -route -g 2&gt;/dev/null</t>
         </is>
       </c>
       <c r="K494" s="3" t="inlineStr">
@@ -29457,7 +29457,7 @@
       </c>
       <c r="D496" s="3" t="inlineStr">
         <is>
-          <t>1. dcat query rNPU_route --chip=2 --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254</t>
+          <t>1. dcat query rNPU_route --chip={chip} --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254</t>
         </is>
       </c>
       <c r="E496" s="3" t="inlineStr">
@@ -29515,8 +29515,8 @@
       </c>
       <c r="D497" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_route --chip=2 --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254
-2. 再次 dcat inject rNPU_route --chip=2 --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254</t>
+          <t>1. dcat inject rNPU_route --chip={chip} --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254
+2. 再次 dcat inject rNPU_route --chip={chip} --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254</t>
         </is>
       </c>
       <c r="E497" s="3" t="inlineStr">
@@ -29632,7 +29632,7 @@
       </c>
       <c r="D499" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_route --chip=2 --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254
+          <t>1. dcat inject rNPU_route --chip={chip} --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254
 2. 检查注入状态</t>
         </is>
       </c>
@@ -29664,7 +29664,7 @@
       </c>
       <c r="J499" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -route -g 2&gt;/dev/null</t>
+          <t>hccn_tool -i {chip} -route -g 2&gt;/dev/null</t>
         </is>
       </c>
       <c r="K499" s="3" t="inlineStr">
@@ -29691,9 +29691,9 @@
       </c>
       <c r="D500" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rNPU_route --chip=2 --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254
-2. 执行 dcat query rNPU_route --chip=2
-3. 执行 dcat clean rNPU_route --chip=2 --address=10.30.40.0 --netmask=255.255.255.0</t>
+          <t>1. 执行 dcat inject rNPU_route --chip={chip} --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254
+2. 执行 dcat query rNPU_route --chip={chip}
+3. 执行 dcat clean rNPU_route --chip={chip} --address=10.30.40.0 --netmask=255.255.255.0</t>
         </is>
       </c>
       <c r="E500" s="3" t="inlineStr">
@@ -29725,7 +29725,7 @@
       </c>
       <c r="J500" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -route -g 2&gt;/dev/null</t>
+          <t>hccn_tool -i {chip} -route -g 2&gt;/dev/null</t>
         </is>
       </c>
       <c r="K500" s="3" t="inlineStr">
@@ -29752,9 +29752,9 @@
       </c>
       <c r="D501" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_route --chip=2 --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254
+          <t>1. dcat inject rNPU_route --chip={chip} --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254
 2. dcat query rNPU_route
-3. dcat clean rNPU_route --chip=2 --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254
+3. dcat clean rNPU_route --chip={chip} --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254
 4. dcat query rNPU_route</t>
         </is>
       </c>
@@ -29815,8 +29815,8 @@
       </c>
       <c r="D502" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_route --chip=2 --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254
-2. 再次 dcat clean rNPU_route --chip=2 --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254</t>
+          <t>1. dcat clean rNPU_route --chip={chip} --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254
+2. 再次 dcat clean rNPU_route --chip={chip} --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254</t>
         </is>
       </c>
       <c r="E502" s="3" t="inlineStr">
@@ -29874,7 +29874,7 @@
       </c>
       <c r="D503" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_route --chip=2 --address=10.30.41.0 --netmask=255.255.255.0 --force</t>
+          <t>1. dcat inject rNPU_route --chip={chip} --address=10.30.41.0 --netmask=255.255.255.0 --force</t>
         </is>
       </c>
       <c r="E503" s="3" t="inlineStr">
@@ -29906,7 +29906,7 @@
       </c>
       <c r="J503" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -route -g 2&gt;/dev/null</t>
+          <t>hccn_tool -i {chip} -route -g 2&gt;/dev/null</t>
         </is>
       </c>
       <c r="K503" s="3" t="inlineStr">
@@ -29933,7 +29933,7 @@
       </c>
       <c r="D504" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_route --chip=2 --address=invalid --netmask=255.255.255.0</t>
+          <t>1. dcat inject rNPU_route --chip={chip} --address=invalid --netmask=255.255.255.0</t>
         </is>
       </c>
       <c r="E504" s="3" t="inlineStr">
@@ -30104,7 +30104,7 @@
       </c>
       <c r="D507" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_route --chip=2 --address=10.30.41.0 --netmask=255.255.255.0
+          <t>1. dcat clean rNPU_route --chip={chip} --address=10.30.41.0 --netmask=255.255.255.0
 2. dcat query（无 uid）</t>
         </is>
       </c>
@@ -30163,7 +30163,7 @@
       </c>
       <c r="D508" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_route --chip=2 --address=10.30.41.0 --netmask=255.255.255.0
+          <t>1. dcat clean rNPU_route --chip={chip} --address=10.30.41.0 --netmask=255.255.255.0
 2. 检查恢复状态</t>
         </is>
       </c>
@@ -30195,7 +30195,7 @@
       </c>
       <c r="J508" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -route -g 2&gt;/dev/null</t>
+          <t>hccn_tool -i {chip} -route -g 2&gt;/dev/null</t>
         </is>
       </c>
       <c r="K508" s="3" t="inlineStr">
@@ -30280,7 +30280,7 @@
       </c>
       <c r="D510" s="3" t="inlineStr">
         <is>
-          <t>1. dcat query rNPU_route --chip=2 --address=10.30.41.0 --netmask=255.255.255.0</t>
+          <t>1. dcat query rNPU_route --chip={chip} --address=10.30.41.0 --netmask=255.255.255.0</t>
         </is>
       </c>
       <c r="E510" s="3" t="inlineStr">
@@ -30338,9 +30338,9 @@
       </c>
       <c r="D511" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rNPU_route --chip=2 --address=10.30.41.0 --netmask=255.255.255.0
+          <t>1. 执行 dcat inject rNPU_route --chip={chip} --address=10.30.41.0 --netmask=255.255.255.0
 2. 检查未先创建时的报错
-3. 执行 dcat clean rNPU_route --chip=2 --address=10.30.41.0 --netmask=255.255.255.0</t>
+3. 执行 dcat clean rNPU_route --chip={chip} --address=10.30.41.0 --netmask=255.255.255.0</t>
         </is>
       </c>
       <c r="E511" s="3" t="inlineStr">
@@ -30372,7 +30372,7 @@
       </c>
       <c r="J511" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -route -g 2&gt;/dev/null</t>
+          <t>hccn_tool -i {chip} -route -g 2&gt;/dev/null</t>
         </is>
       </c>
       <c r="K511" s="3" t="inlineStr">
@@ -30399,8 +30399,8 @@
       </c>
       <c r="D512" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_route --chip=2 --address=10.30.41.0 --netmask=255.255.255.0
-2. 再次 dcat inject rNPU_route --chip=2 --address=10.30.41.0 --netmask=255.255.255.0</t>
+          <t>1. dcat inject rNPU_route --chip={chip} --address=10.30.41.0 --netmask=255.255.255.0
+2. 再次 dcat inject rNPU_route --chip={chip} --address=10.30.41.0 --netmask=255.255.255.0</t>
         </is>
       </c>
       <c r="E512" s="3" t="inlineStr">
@@ -30516,7 +30516,7 @@
       </c>
       <c r="D514" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_route --chip=2 --address=10.30.41.0 --netmask=255.255.255.0
+          <t>1. dcat inject rNPU_route --chip={chip} --address=10.30.41.0 --netmask=255.255.255.0
 2. 检查注入状态</t>
         </is>
       </c>
@@ -30548,7 +30548,7 @@
       </c>
       <c r="J514" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -route -g 2&gt;/dev/null</t>
+          <t>hccn_tool -i {chip} -route -g 2&gt;/dev/null</t>
         </is>
       </c>
       <c r="K514" s="3" t="inlineStr">
@@ -30575,9 +30575,9 @@
       </c>
       <c r="D515" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_route --chip=2 --address=10.30.41.0 --netmask=255.255.255.0
+          <t>1. dcat inject rNPU_route --chip={chip} --address=10.30.41.0 --netmask=255.255.255.0
 2. dcat query rNPU_route
-3. dcat clean rNPU_route --chip=2 --address=10.30.41.0 --netmask=255.255.255.0
+3. dcat clean rNPU_route --chip={chip} --address=10.30.41.0 --netmask=255.255.255.0
 4. dcat query rNPU_route</t>
         </is>
       </c>
@@ -30638,8 +30638,8 @@
       </c>
       <c r="D516" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_route --chip=2 --address=10.30.41.0 --netmask=255.255.255.0
-2. 再次 dcat clean rNPU_route --chip=2 --address=10.30.41.0 --netmask=255.255.255.0</t>
+          <t>1. dcat clean rNPU_route --chip={chip} --address=10.30.41.0 --netmask=255.255.255.0
+2. 再次 dcat clean rNPU_route --chip={chip} --address=10.30.41.0 --netmask=255.255.255.0</t>
         </is>
       </c>
       <c r="E516" s="3" t="inlineStr">
@@ -37002,7 +37002,7 @@
       </c>
       <c r="D625" s="3" t="inlineStr">
         <is>
-          <t>1. dcat query rNPU_link_down --chip=2</t>
+          <t>1. dcat query rNPU_link_down --chip={chip}</t>
         </is>
       </c>
       <c r="E625" s="3" t="inlineStr">
@@ -37060,7 +37060,7 @@
       </c>
       <c r="D626" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_link_down --chip=2
+          <t>1. dcat clean rNPU_link_down --chip={chip}
 2. hccn_tool -i 0 -link -g</t>
         </is>
       </c>
@@ -37092,7 +37092,7 @@
       </c>
       <c r="J626" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 0 -link -g</t>
+          <t>hccn_tool -i {chip} -link -g</t>
         </is>
       </c>
       <c r="K626" s="3" t="inlineStr">
@@ -37119,7 +37119,7 @@
       </c>
       <c r="D627" s="3" t="inlineStr">
         <is>
-          <t>1. dcat query rNPU_ip_change --chip=2 --address=192.168.1.100 --netmask=255.255.255.0</t>
+          <t>1. dcat query rNPU_ip_change --chip={chip} --address=192.168.1.100 --netmask=255.255.255.0</t>
         </is>
       </c>
       <c r="E627" s="3" t="inlineStr">
@@ -37177,7 +37177,7 @@
       </c>
       <c r="D628" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_ip_change --chip=2 --address=192.168.1.100 --netmask=255.255.255.0
+          <t>1. dcat clean rNPU_ip_change --chip={chip} --address=192.168.1.100 --netmask=255.255.255.0
 2. hccn_tool -i 0 -ip -g</t>
         </is>
       </c>
@@ -37209,7 +37209,7 @@
       </c>
       <c r="J628" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 0 -ip -g</t>
+          <t>hccn_tool -i {chip} -ip -g</t>
         </is>
       </c>
       <c r="K628" s="3" t="inlineStr">
@@ -37236,7 +37236,7 @@
       </c>
       <c r="D629" s="3" t="inlineStr">
         <is>
-          <t>1. dcat query rNPU_gw_change --chip=2 --gateway=10.30.12.1</t>
+          <t>1. dcat query rNPU_gw_change --chip={chip} --gateway=10.30.12.1</t>
         </is>
       </c>
       <c r="E629" s="3" t="inlineStr">
@@ -37294,7 +37294,7 @@
       </c>
       <c r="D630" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_gw_change --chip=2 --gateway=10.30.12.1
+          <t>1. dcat clean rNPU_gw_change --chip={chip} --gateway=10.30.12.1
 2. hccn_tool -i 2 -gateway -g</t>
         </is>
       </c>
@@ -37326,7 +37326,7 @@
       </c>
       <c r="J630" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -gateway -g</t>
+          <t>hccn_tool -i {chip} -gateway -g</t>
         </is>
       </c>
       <c r="K630" s="3" t="inlineStr">
@@ -37353,7 +37353,7 @@
       </c>
       <c r="D631" s="3" t="inlineStr">
         <is>
-          <t>1. dcat query rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55</t>
+          <t>1. dcat query rNPU_arp --chip={chip} --dev={dev} --ip=10.30.12.200 --mac=00:11:22:33:44:55</t>
         </is>
       </c>
       <c r="E631" s="3" t="inlineStr">
@@ -37411,7 +37411,7 @@
       </c>
       <c r="D632" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55
+          <t>1. dcat clean rNPU_arp --chip={chip} --dev={dev} --ip=10.30.12.200 --mac=00:11:22:33:44:55
 2. hccn_tool -i 2 -arp -g</t>
         </is>
       </c>
@@ -37443,7 +37443,7 @@
       </c>
       <c r="J632" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -arp -g</t>
+          <t>hccn_tool -i {chip} -arp -g</t>
         </is>
       </c>
       <c r="K632" s="3" t="inlineStr">
@@ -37470,7 +37470,7 @@
       </c>
       <c r="D633" s="3" t="inlineStr">
         <is>
-          <t>1. dcat query rNPU_route --chip=2 --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254</t>
+          <t>1. dcat query rNPU_route --chip={chip} --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254</t>
         </is>
       </c>
       <c r="E633" s="3" t="inlineStr">
@@ -37528,7 +37528,7 @@
       </c>
       <c r="D634" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_route --chip=2 --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254
+          <t>1. dcat clean rNPU_route --chip={chip} --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254
 2. hccn_tool -i 2 -route -g</t>
         </is>
       </c>
@@ -37560,7 +37560,7 @@
       </c>
       <c r="J634" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i 2 -route -g</t>
+          <t>hccn_tool -i {chip} -route -g</t>
         </is>
       </c>
       <c r="K634" s="3" t="inlineStr">

--- a/tests/e2e/testcases.xlsx
+++ b/tests/e2e/testcases.xlsx
@@ -15849,12 +15849,12 @@
       <c r="I263" s="3" t="inlineStr"/>
       <c r="J263" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i {chip} -arp -g 2&gt;/dev/null</t>
+          <t>（注入未执行）</t>
         </is>
       </c>
       <c r="K263" s="3" t="inlineStr">
         <is>
-          <t>contains:10.20.10.200</t>
+          <t>status:ok</t>
         </is>
       </c>
     </row>

--- a/tests/e2e/testcases.xlsx
+++ b/tests/e2e/testcases.xlsx
@@ -15683,7 +15683,7 @@
       </c>
       <c r="K260" s="3" t="inlineStr">
         <is>
-          <t>notcontains:10.20.10.200</t>
+          <t>notcontains:10.30.12.200</t>
         </is>
       </c>
     </row>
@@ -15910,7 +15910,7 @@
       </c>
       <c r="K264" s="3" t="inlineStr">
         <is>
-          <t>contains:10.20.10.200</t>
+          <t>contains:10.30.12.200</t>
         </is>
       </c>
     </row>
@@ -16028,7 +16028,7 @@
       </c>
       <c r="K266" s="3" t="inlineStr">
         <is>
-          <t>contains:10.20.10.200</t>
+          <t>contains:10.30.12.200</t>
         </is>
       </c>
     </row>
@@ -16315,7 +16315,7 @@
       </c>
       <c r="K271" s="3" t="inlineStr">
         <is>
-          <t>notcontains:10.20.10.200</t>
+          <t>notcontains:10.30.12.200</t>
         </is>
       </c>
     </row>
@@ -16491,7 +16491,7 @@
       </c>
       <c r="K274" s="3" t="inlineStr">
         <is>
-          <t>notcontains:10.20.10.200</t>
+          <t>notcontains:10.30.12.200</t>
         </is>
       </c>
     </row>

--- a/tests/e2e/testcases.xlsx
+++ b/tests/e2e/testcases.xlsx
@@ -15646,7 +15646,7 @@
       </c>
       <c r="D260" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_arp --chip={chip} --dev={dev} --ip=10.30.12.200 --force</t>
+          <t>1. dcat inject rNPU_arp --chip={chip} --dev={dev} --ip=10.30.12.200 --mac=00:11:22:33:44:55 --force</t>
         </is>
       </c>
       <c r="E260" s="3" t="inlineStr">
@@ -15683,7 +15683,7 @@
       </c>
       <c r="K260" s="3" t="inlineStr">
         <is>
-          <t>notcontains:10.30.12.200</t>
+          <t>contains:10.30.12.200</t>
         </is>
       </c>
     </row>
@@ -15762,7 +15762,7 @@
       </c>
       <c r="D262" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_arp --chip=8 --dev={dev} --ip=10.30.12.200</t>
+          <t>1. dcat inject rNPU_arp --chip=8 --dev={dev} --ip=10.30.12.200 --mac=00:11:22:33:44:55</t>
         </is>
       </c>
       <c r="E262" s="3" t="inlineStr">
@@ -15797,7 +15797,7 @@
       </c>
       <c r="K262" s="3" t="inlineStr">
         <is>
-          <t>exitcode:3</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>
@@ -15871,7 +15871,7 @@
       </c>
       <c r="C264" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已注入 arp_del，sidecar 保存原 MAC</t>
+          <t>npu_hardware，已注入 rNPU_arp</t>
         </is>
       </c>
       <c r="D264" s="3" t="inlineStr">
@@ -15910,7 +15910,7 @@
       </c>
       <c r="K264" s="3" t="inlineStr">
         <is>
-          <t>contains:10.30.12.200</t>
+          <t>notcontains:10.30.12.200</t>
         </is>
       </c>
     </row>
@@ -16028,7 +16028,7 @@
       </c>
       <c r="K266" s="3" t="inlineStr">
         <is>
-          <t>contains:10.30.12.200</t>
+          <t>notcontains:10.30.12.200</t>
         </is>
       </c>
     </row>
@@ -16050,7 +16050,7 @@
       </c>
       <c r="D267" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_arp --chip={chip} --dev={dev} --ip=invalid</t>
+          <t>1. dcat inject rNPU_arp --chip={chip} --dev={dev} --ip=invalid --mac=00:11:22:33:44:55</t>
         </is>
       </c>
       <c r="E267" s="3" t="inlineStr">
@@ -16085,7 +16085,7 @@
       </c>
       <c r="K267" s="3" t="inlineStr">
         <is>
-          <t>exitcode:3</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>
@@ -16223,7 +16223,7 @@
       </c>
       <c r="D270" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rNPU_arp --chip={chip} --dev={dev} --ip=10.30.12.200
+          <t>1. 执行 dcat inject rNPU_arp --chip={chip} --dev={dev} --ip=10.30.12.200 --mac=00:11:22:33:44:55
 2. 检查返回</t>
         </is>
       </c>
@@ -16258,7 +16258,7 @@
       </c>
       <c r="K270" s="3" t="inlineStr">
         <is>
-          <t>exitcode:3</t>
+          <t>exitcode:1</t>
         </is>
       </c>
     </row>
@@ -16315,7 +16315,7 @@
       </c>
       <c r="K271" s="3" t="inlineStr">
         <is>
-          <t>notcontains:10.30.12.200</t>
+          <t>contains:10.30.12.200</t>
         </is>
       </c>
     </row>
@@ -16337,8 +16337,8 @@
       </c>
       <c r="D272" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_arp --chip={chip} --dev={dev} --ip=10.30.12.200
-2. 再次 dcat inject rNPU_arp --chip={chip} --dev={dev} --ip=10.30.12.200</t>
+          <t>1. dcat inject rNPU_arp --chip={chip} --dev={dev} --ip=10.30.12.200 --mac=00:11:22:33:44:55
+2. 再次 dcat inject rNPU_arp --chip={chip} --dev={dev} --ip=10.30.12.200 --mac=00:11:22:33:44:55</t>
         </is>
       </c>
       <c r="E272" s="3" t="inlineStr">
@@ -16491,7 +16491,7 @@
       </c>
       <c r="K274" s="3" t="inlineStr">
         <is>
-          <t>notcontains:10.30.12.200</t>
+          <t>contains:10.30.12.200</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="K275" s="3" t="inlineStr">
         <is>
-          <t>notcontains:10.30.12.200</t>
+          <t>contains:10.30.12.200</t>
         </is>
       </c>
     </row>
@@ -17747,7 +17747,7 @@
       </c>
       <c r="E296" s="3" t="inlineStr">
         <is>
-          <t>--chip=0 --bw_limit=50000 --force</t>
+          <t>--chip={chip} --bw_limit=50000 --force</t>
         </is>
       </c>
       <c r="F296" s="3" t="inlineStr">
@@ -17808,12 +17808,12 @@
       </c>
       <c r="E297" s="3" t="inlineStr">
         <is>
-          <t>chip=0；bw_limit=1000</t>
+          <t>chip={chip}；bw_limit=50000</t>
         </is>
       </c>
       <c r="F297" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 -shaping -s bw_limit 1000，降低 RoCE 吞吐
+          <t>1. 执行 -shaping -s bw_limit 50000，降低 RoCE 吞吐
 2. query 检查当前 bw_limit&lt;MAX_BW 则 confirmed:true
 3. clean 执行 -shaping -s bw_limit 100000（MAX_BW 硬编码）；若芯片原始限速非 100000 则无法精确还原</t>
         </is>
@@ -17863,7 +17863,7 @@
       <c r="D298" s="3" t="inlineStr">
         <is>
           <t>1. 执行 dcat inject rNPU_bw_limit --chip={chip} --bw_limit=0
-2. 执行 --bw_limit=-1 / --bw_limit=abc</t>
+2. 执行 dcat inject rNPU_bw_limit --chip={chip} --bw_limit=-1</t>
         </is>
       </c>
       <c r="E298" s="3" t="inlineStr">
@@ -18087,7 +18087,7 @@
       </c>
       <c r="C302" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已 clean rNPU_bw_limit</t>
+          <t>npu_hardware，已注入 rNPU_bw_limit</t>
         </is>
       </c>
       <c r="D302" s="3" t="inlineStr">
@@ -18157,7 +18157,7 @@
       </c>
       <c r="E303" s="3" t="inlineStr">
         <is>
-          <t>--chip=0 --bw_limit=50000</t>
+          <t>--chip={chip} --bw_limit=50000</t>
         </is>
       </c>
       <c r="F303" s="3" t="inlineStr">
@@ -18273,7 +18273,7 @@
       </c>
       <c r="E305" s="3" t="inlineStr">
         <is>
-          <t>--chip=0 --bw_limit=50000</t>
+          <t>--chip={chip} --bw_limit=50000</t>
         </is>
       </c>
       <c r="F305" s="3" t="inlineStr">
@@ -18332,7 +18332,7 @@
       </c>
       <c r="E306" s="3" t="inlineStr">
         <is>
-          <t>--chip=0 --bw_limit=50000</t>
+          <t>--chip={chip} --bw_limit=50000</t>
         </is>
       </c>
       <c r="F306" s="3" t="inlineStr">
@@ -18449,7 +18449,7 @@
       </c>
       <c r="E308" s="3" t="inlineStr">
         <is>
-          <t>--chip=0 --bw_limit=50000</t>
+          <t>--chip={chip} --bw_limit=50000</t>
         </is>
       </c>
       <c r="F308" s="3" t="inlineStr">
@@ -18510,7 +18510,7 @@
       </c>
       <c r="E309" s="3" t="inlineStr">
         <is>
-          <t>--chip=0 --bw_limit=50000</t>
+          <t>--chip={chip} --bw_limit=50000</t>
         </is>
       </c>
       <c r="F309" s="3" t="inlineStr">
@@ -18560,7 +18560,7 @@
       </c>
       <c r="C310" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已 clean rNPU_bw_limit</t>
+          <t>npu_hardware，已注入 rNPU_bw_limit</t>
         </is>
       </c>
       <c r="D310" s="3" t="inlineStr">
@@ -18571,7 +18571,7 @@
       </c>
       <c r="E310" s="3" t="inlineStr">
         <is>
-          <t>--chip=0 --bw_limit=50000</t>
+          <t>--chip={chip} --bw_limit=50000</t>
         </is>
       </c>
       <c r="F310" s="3" t="inlineStr">
@@ -18629,7 +18629,7 @@
       </c>
       <c r="E311" s="3" t="inlineStr">
         <is>
-          <t>--chip=0 --dscp=46 --tc=0 --force</t>
+          <t>--chip={chip} --dscp=46 --tc=3 --force</t>
         </is>
       </c>
       <c r="F311" s="3" t="inlineStr">
@@ -18690,7 +18690,7 @@
       </c>
       <c r="E312" s="3" t="inlineStr">
         <is>
-          <t>chip=0；dscp=46；tc=0</t>
+          <t>chip={chip}；dscp=46；tc=3</t>
         </is>
       </c>
       <c r="F312" s="3" t="inlineStr">
@@ -18853,7 +18853,7 @@
       </c>
       <c r="C315" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已 clean rNPU_dscp_tc_change</t>
+          <t>npu_hardware，已注入 rNPU_dscp_tc_change</t>
         </is>
       </c>
       <c r="D315" s="3" t="inlineStr">
@@ -18923,7 +18923,7 @@
       </c>
       <c r="E316" s="3" t="inlineStr">
         <is>
-          <t>--chip=0 --dscp=46 --tc=0</t>
+          <t>--chip={chip} --dscp=46 --tc=0</t>
         </is>
       </c>
       <c r="F316" s="3" t="inlineStr">
@@ -19090,7 +19090,7 @@
       </c>
       <c r="D319" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_dscp_tc_change --chip={chip} --dscp=0 --tc=0</t>
+          <t>1. dcat inject rNPU_dscp_tc_change --chip={chip} --dscp=0 --tc=2</t>
         </is>
       </c>
       <c r="E319" s="3" t="inlineStr">
@@ -19120,12 +19120,12 @@
       </c>
       <c r="J319" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i {chip} -dscp_to_tc -g dscp 46 2&gt;/dev/null | awk '$1==46{print $2}'</t>
+          <t>hccn_tool -i {chip} -dscp_to_tc -g dscp 0 2&gt;/dev/null | awk '$1==0{print $2}'</t>
         </is>
       </c>
       <c r="K319" s="3" t="inlineStr">
         <is>
-          <t>eq:0</t>
+          <t>eq:2</t>
         </is>
       </c>
     </row>
@@ -19147,7 +19147,7 @@
       </c>
       <c r="D320" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_dscp_tc_change --chip={chip} --dscp=63 --tc=0</t>
+          <t>1. dcat inject rNPU_dscp_tc_change --chip={chip} --dscp=63 --tc=2</t>
         </is>
       </c>
       <c r="E320" s="3" t="inlineStr">
@@ -19177,12 +19177,12 @@
       </c>
       <c r="J320" s="3" t="inlineStr">
         <is>
-          <t>hccn_tool -i {chip} -dscp_to_tc -g dscp 46 2&gt;/dev/null | awk '$1==46{print $2}'</t>
+          <t>hccn_tool -i {chip} -dscp_to_tc -g dscp 63 2&gt;/dev/null | awk '$1==63{print $2}'</t>
         </is>
       </c>
       <c r="K320" s="3" t="inlineStr">
         <is>
-          <t>eq:0</t>
+          <t>eq:2</t>
         </is>
       </c>
     </row>
@@ -19324,7 +19324,7 @@
       </c>
       <c r="E323" s="3" t="inlineStr">
         <is>
-          <t>--chip=0 --dscp=46 --tc=0</t>
+          <t>--chip={chip} --dscp=46 --tc=3</t>
         </is>
       </c>
       <c r="F323" s="3" t="inlineStr">
@@ -19481,7 +19481,7 @@
       </c>
       <c r="B326" s="3" t="inlineStr">
         <is>
-          <t>rNPU_dscp_tc_change-tc=7 最大值接受</t>
+          <t>rNPU_dscp_tc_change-tc=3 最大值接受</t>
         </is>
       </c>
       <c r="C326" s="3" t="inlineStr">
@@ -19491,12 +19491,12 @@
       </c>
       <c r="D326" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_dscp_tc_change --chip={chip} --dscp=46 --tc=7</t>
+          <t>1. dcat inject rNPU_dscp_tc_change --chip={chip} --dscp=46 --tc=3</t>
         </is>
       </c>
       <c r="E326" s="3" t="inlineStr">
         <is>
-          <t>dscp=46；tc=7</t>
+          <t>dscp=46；tc=3</t>
         </is>
       </c>
       <c r="F326" s="3" t="inlineStr">
@@ -19526,7 +19526,7 @@
       </c>
       <c r="K326" s="3" t="inlineStr">
         <is>
-          <t>eq:0</t>
+          <t>eq:3</t>
         </is>
       </c>
     </row>
@@ -19558,7 +19558,7 @@
       </c>
       <c r="F327" s="3" t="inlineStr">
         <is>
-          <t>1. 拒绝（须 0-7）status:error 退出码 1</t>
+          <t>1. 拒绝（须 0-3）status:error 退出码 1</t>
         </is>
       </c>
       <c r="G327" s="4" t="inlineStr">
@@ -19611,7 +19611,7 @@
       </c>
       <c r="E328" s="3" t="inlineStr">
         <is>
-          <t>--chip=0 --dscp=46 --tc=0</t>
+          <t>--chip={chip} --dscp=46 --tc=3</t>
         </is>
       </c>
       <c r="F328" s="3" t="inlineStr">
@@ -19728,7 +19728,7 @@
       </c>
       <c r="E330" s="3" t="inlineStr">
         <is>
-          <t>--chip=0 --dscp=46 --tc=0</t>
+          <t>--chip={chip} --dscp=46 --tc=3</t>
         </is>
       </c>
       <c r="F330" s="3" t="inlineStr">
@@ -19789,7 +19789,7 @@
       </c>
       <c r="E331" s="3" t="inlineStr">
         <is>
-          <t>--chip=0 --dscp=46 --tc=0</t>
+          <t>--chip={chip} --dscp=46 --tc=3</t>
         </is>
       </c>
       <c r="F331" s="3" t="inlineStr">
@@ -19839,7 +19839,7 @@
       </c>
       <c r="C332" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已 clean rNPU_dscp_tc_change</t>
+          <t>npu_hardware，已注入 rNPU_dscp_tc_change</t>
         </is>
       </c>
       <c r="D332" s="3" t="inlineStr">
@@ -19850,7 +19850,7 @@
       </c>
       <c r="E332" s="3" t="inlineStr">
         <is>
-          <t>--chip=0 --dscp=46 --tc=0</t>
+          <t>--chip={chip} --dscp=46 --tc=3</t>
         </is>
       </c>
       <c r="F332" s="3" t="inlineStr">
@@ -19903,7 +19903,7 @@
       </c>
       <c r="D333" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_gw_change --chip={chip} --gateway=10.30.12.1 --force</t>
+          <t>1. dcat inject rNPU_gw_change --chip={chip} --gateway=10.0.0.200 --force</t>
         </is>
       </c>
       <c r="E333" s="3" t="inlineStr">
@@ -19940,7 +19940,7 @@
       </c>
       <c r="K333" s="3" t="inlineStr">
         <is>
-          <t>contains:10.20.10.3</t>
+          <t>contains:10.0.0.200</t>
         </is>
       </c>
     </row>
@@ -20022,7 +20022,7 @@
       </c>
       <c r="D335" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rNPU_gw_change --chip={chip} --gateway=&lt;同网段≠当前值&gt;</t>
+          <t>1. 执行 dcat inject rNPU_gw_change --chip={chip} --gateway=10.0.0.200</t>
         </is>
       </c>
       <c r="E335" s="3" t="inlineStr">
@@ -20058,7 +20058,7 @@
       </c>
       <c r="K335" s="3" t="inlineStr">
         <is>
-          <t>contains:10.20.10.3</t>
+          <t>contains:10.0.0.200</t>
         </is>
       </c>
     </row>
@@ -20080,7 +20080,7 @@
       </c>
       <c r="D336" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rNPU_gw_change --chip=7 --gateway=&lt;同网段≠当前值&gt;</t>
+          <t>1. 执行 dcat inject rNPU_gw_change --chip={chip} --gateway=10.0.0.200</t>
         </is>
       </c>
       <c r="E336" s="3" t="inlineStr">
@@ -20115,7 +20115,7 @@
       </c>
       <c r="K336" s="3" t="inlineStr">
         <is>
-          <t>contains:10.20.10.3</t>
+          <t>contains:10.0.0.200</t>
         </is>
       </c>
     </row>
@@ -20137,7 +20137,7 @@
       </c>
       <c r="D337" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_gw_change --chip=-1 --gateway=10.30.12.1</t>
+          <t>1. dcat inject rNPU_gw_change --chip=-1 --gateway=10.0.0.200</t>
         </is>
       </c>
       <c r="E337" s="3" t="inlineStr">
@@ -20194,7 +20194,7 @@
       </c>
       <c r="D338" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_gw_change --chip=8 --gateway=10.30.12.1</t>
+          <t>1. dcat inject rNPU_gw_change --chip=8 --gateway=10.0.0.200</t>
         </is>
       </c>
       <c r="E338" s="3" t="inlineStr">
@@ -20347,7 +20347,7 @@
       </c>
       <c r="K340" s="3" t="inlineStr">
         <is>
-          <t>notcontains:10.20.10.3</t>
+          <t>notcontains:10.0.0.200</t>
         </is>
       </c>
     </row>
@@ -20636,7 +20636,7 @@
       </c>
       <c r="K345" s="3" t="inlineStr">
         <is>
-          <t>notcontains:10.20.10.3</t>
+          <t>notcontains:10.0.0.200</t>
         </is>
       </c>
     </row>
@@ -20658,7 +20658,7 @@
       </c>
       <c r="D346" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_gw_change --chip={chip} --gateway=10.30.12.1
+          <t>1. dcat inject rNPU_gw_change --chip={chip} --gateway=10.0.0.200
 2. 再次 dcat inject rNPU_gw_change --chip={chip} --gateway=10.30.12.1</t>
         </is>
       </c>
@@ -20775,7 +20775,7 @@
       </c>
       <c r="D348" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_gw_change --chip={chip} --gateway=10.30.12.1
+          <t>1. dcat inject rNPU_gw_change --chip={chip} --gateway=10.0.0.200
 2. 检查注入状态</t>
         </is>
       </c>
@@ -20812,7 +20812,7 @@
       </c>
       <c r="K348" s="3" t="inlineStr">
         <is>
-          <t>contains:10.20.10.3</t>
+          <t>contains:10.0.0.200</t>
         </is>
       </c>
     </row>
@@ -20834,7 +20834,7 @@
       </c>
       <c r="D349" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_gw_change --chip={chip} --gateway=10.30.12.1
+          <t>1. dcat inject rNPU_gw_change --chip={chip} --gateway=10.0.0.200
 2. dcat query rNPU_gw_change
 3. dcat clean rNPU_gw_change --chip={chip} --gateway=10.30.12.1
 4. dcat query rNPU_gw_change</t>
@@ -20897,7 +20897,7 @@
       </c>
       <c r="D350" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rNPU_gw_change --chip={chip} --gateway=10.30.12.254（与当前相同）
+          <t>1. 执行 dcat inject rNPU_gw_change --chip={chip} --gateway=10.0.0.200
 2. 检查 query 返回</t>
         </is>
       </c>
@@ -20953,7 +20953,7 @@
       </c>
       <c r="D351" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rNPU_gw_change --chip={chip} --gateway=10.30.12.1（同网段且≠当前网关）
+          <t>1. 执行 dcat inject rNPU_gw_change --chip={chip} --gateway=10.0.0.200（同网段且≠当前网关）
 2. 检查 sidecar 与 query</t>
         </is>
       </c>
@@ -20988,7 +20988,7 @@
       </c>
       <c r="K351" s="3" t="inlineStr">
         <is>
-          <t>contains:10.20.10.3</t>
+          <t>contains:10.0.0.200</t>
         </is>
       </c>
     </row>
@@ -21066,7 +21066,7 @@
       </c>
       <c r="D353" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_gw_change --chip={chip} --gateway=10.30.12.1
+          <t>1. dcat clean rNPU_gw_change --chip={chip} --gateway=10.0.0.200
 2. 再次 dcat clean rNPU_gw_change --chip={chip} --gateway=10.30.12.1</t>
         </is>
       </c>
@@ -21162,7 +21162,7 @@
       </c>
       <c r="K354" s="3" t="inlineStr">
         <is>
-          <t>contains:10.0.0.99</t>
+          <t>contains:192.168.1.100</t>
         </is>
       </c>
     </row>
@@ -21225,7 +21225,7 @@
       </c>
       <c r="K355" s="3" t="inlineStr">
         <is>
-          <t>contains:10.0.0.99</t>
+          <t>contains:192.168.1.100</t>
         </is>
       </c>
     </row>
@@ -21514,7 +21514,7 @@
       </c>
       <c r="K360" s="3" t="inlineStr">
         <is>
-          <t>notcontains:10.0.0.99</t>
+          <t>notcontains:192.168.1.100</t>
         </is>
       </c>
     </row>
@@ -21806,7 +21806,7 @@
       </c>
       <c r="K365" s="3" t="inlineStr">
         <is>
-          <t>contains:10.0.0.99</t>
+          <t>contains:192.168.1.100</t>
         </is>
       </c>
     </row>
@@ -21950,7 +21950,7 @@
       </c>
       <c r="D368" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iproute --chip={chip} --ip=10.30.50.0 --ip_mask=24 --via=10.30.12.254 --dev=eth2 --table=100 --force</t>
+          <t>1. dcat inject rNPU_iproute --chip={chip} --ip=10.30.50.0 --ip_mask=24 --via=10.0.0.254 --dev={dev} --table=100 --force</t>
         </is>
       </c>
       <c r="E368" s="3" t="inlineStr">
@@ -22009,7 +22009,7 @@
       </c>
       <c r="D369" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iproute --chip=-1 --ip=10.30.50.0 --ip_mask=24 --via=10.30.12.254 --dev=eth2 --table=100</t>
+          <t>1. dcat inject rNPU_iproute --chip=-1 --ip=10.30.50.0 --ip_mask=24 --via=10.0.0.254 --dev={dev} --table=100</t>
         </is>
       </c>
       <c r="E369" s="3" t="inlineStr">
@@ -22066,7 +22066,7 @@
       </c>
       <c r="D370" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iproute --chip=8 --ip=10.30.50.0 --ip_mask=24 --via=10.30.12.254 --dev=eth2 --table=100</t>
+          <t>1. dcat inject rNPU_iproute --chip=8 --ip=10.30.50.0 --ip_mask=24 --via=10.0.0.254 --dev={dev} --table=100</t>
         </is>
       </c>
       <c r="E370" s="3" t="inlineStr">
@@ -22182,7 +22182,7 @@
       </c>
       <c r="D372" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_iproute --chip={chip} --ip=10.30.50.0 --ip_mask=24 --via=10.30.12.254 --dev=eth2 --table=100
+          <t>1. dcat clean rNPU_iproute --chip={chip} --ip=10.30.50.0 --ip_mask=24 --via=10.0.0.254 --dev={dev} --table=100
 2. 检查恢复状态</t>
         </is>
       </c>
@@ -22241,7 +22241,7 @@
       </c>
       <c r="D373" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iproute --chip={chip} --ip=10.30.50.0 --ip_mask=-1 --via=10.30.12.254 --dev=eth2 --table=100</t>
+          <t>1. dcat inject rNPU_iproute --chip={chip} --ip=10.30.50.0 --ip_mask=-1 --via=10.0.0.254 --dev={dev} --table=100</t>
         </is>
       </c>
       <c r="E373" s="3" t="inlineStr">
@@ -22298,7 +22298,7 @@
       </c>
       <c r="D374" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iproute --chip={chip} --ip=10.30.50.0 --ip_mask=-1 --via=10.30.12.254 --dev=eth2 --table=100</t>
+          <t>1. dcat inject rNPU_iproute --chip={chip} --ip=10.30.50.0 --ip_mask=-1 --via=10.0.0.254 --dev={dev} --table=100</t>
         </is>
       </c>
       <c r="E374" s="3" t="inlineStr">
@@ -22355,7 +22355,7 @@
       </c>
       <c r="D375" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iproute --chip={chip} --ip=10.30.50.0 --ip_mask=0 --via=10.30.12.254 --dev=eth2 --table=100</t>
+          <t>1. dcat inject rNPU_iproute --chip={chip} --ip=10.30.50.0 --ip_mask=0 --via=10.0.0.254 --dev={dev} --table=100</t>
         </is>
       </c>
       <c r="E375" s="3" t="inlineStr">
@@ -22412,7 +22412,7 @@
       </c>
       <c r="D376" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iproute --chip={chip} --ip=10.30.50.1 --ip_mask=32 --via=10.30.12.254 --dev=eth2 --table=100</t>
+          <t>1. dcat inject rNPU_iproute --chip={chip} --ip=10.30.50.1 --ip_mask=32 --via=10.0.0.254 --dev={dev} --table=100</t>
         </is>
       </c>
       <c r="E376" s="3" t="inlineStr">
@@ -22447,7 +22447,7 @@
       </c>
       <c r="K376" s="3" t="inlineStr">
         <is>
-          <t>contains:10.30.50.0</t>
+          <t>contains:10.30.50.1</t>
         </is>
       </c>
     </row>
@@ -22469,7 +22469,7 @@
       </c>
       <c r="D377" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iproute --chip={chip} --ip=10.30.50.0 --ip_mask=33 --via=10.30.12.254 --dev=eth2 --table=100</t>
+          <t>1. dcat inject rNPU_iproute --chip={chip} --ip=10.30.50.0 --ip_mask=33 --via=10.0.0.254 --dev={dev} --table=100</t>
         </is>
       </c>
       <c r="E377" s="3" t="inlineStr">
@@ -22584,7 +22584,7 @@
       </c>
       <c r="D379" s="3" t="inlineStr">
         <is>
-          <t>1. dcat query rNPU_iproute --chip={chip} --ip=10.30.50.0 --ip_mask=24 --via=10.30.12.254 --dev=eth2 --table=100</t>
+          <t>1. dcat query rNPU_iproute --chip={chip} --ip=10.30.50.0 --ip_mask=24 --via=10.0.0.254 --dev={dev} --table=100</t>
         </is>
       </c>
       <c r="E379" s="3" t="inlineStr">
@@ -22642,7 +22642,7 @@
       </c>
       <c r="D380" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iproute --chip={chip} --ip=10.30.50.0 --ip_mask=24 --via=10.30.12.254 --dev=eth2 --table=100
+          <t>1. dcat inject rNPU_iproute --chip={chip} --ip=10.30.50.0 --ip_mask=24 --via=10.0.0.254 --dev={dev} --table=100
 2. 再次 dcat inject rNPU_iproute --chip={chip} --ip=10.30.50.0 --ip_mask=24 --via=10.30.12.254 --dev=eth2 --table=100</t>
         </is>
       </c>
@@ -22759,7 +22759,7 @@
       </c>
       <c r="D382" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iproute --chip={chip} --ip=10.30.50.0 --ip_mask=24 --via=10.30.12.254 --dev=eth2 --table=100
+          <t>1. dcat inject rNPU_iproute --chip={chip} --ip=10.30.50.0 --ip_mask=24 --via=10.0.0.254 --dev={dev} --table=100
 2. 检查注入状态</t>
         </is>
       </c>
@@ -22818,7 +22818,7 @@
       </c>
       <c r="D383" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rNPU_iproute --chip={chip} --ip=10.30.50.0 --ip_mask=24 --via=10.30.12.254 --dev=eth2 --table=100
+          <t>1. 执行 dcat inject rNPU_iproute --chip={chip} --ip=10.30.50.0 --ip_mask=24 --via=10.0.0.254 --dev={dev} --table=100
 2. 执行 dcat query rNPU_iproute --chip={chip}
 3. 执行 dcat clean rNPU_iproute --chip={chip} --ip=10.30.50.0 --ip_mask=24 --table=100</t>
         </is>
@@ -22879,7 +22879,7 @@
       </c>
       <c r="D384" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iproute --chip={chip} --ip=10.30.50.0 --ip_mask=24 --via=10.30.12.254 --dev=eth2 --table=100
+          <t>1. dcat inject rNPU_iproute --chip={chip} --ip=10.30.50.0 --ip_mask=24 --via=10.0.0.254 --dev={dev} --table=100
 2. dcat query rNPU_iproute
 3. dcat clean rNPU_iproute --chip={chip} --ip=10.30.50.0 --ip_mask=24 --via=10.30.12.254 --dev=eth2 --table=100
 4. dcat query rNPU_iproute</t>
@@ -22942,7 +22942,7 @@
       </c>
       <c r="D385" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_iproute --chip={chip} --ip=10.30.50.0 --ip_mask=24 --via=10.30.12.254 --dev=eth2 --table=100
+          <t>1. dcat clean rNPU_iproute --chip={chip} --ip=10.30.50.0 --ip_mask=24 --via=10.0.0.254 --dev={dev} --table=100
 2. 再次 dcat clean rNPU_iproute --chip={chip} --ip=10.30.50.0 --ip_mask=24 --via=10.30.12.254 --dev=eth2 --table=100</t>
         </is>
       </c>
@@ -23001,7 +23001,7 @@
       </c>
       <c r="D386" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iproute --chip={chip} --ip=10.30.51.0 --ip_mask=24 --table=100 --force</t>
+          <t>1. dcat inject rNPU_iproute --chip={chip} --ip=10.30.51.0 --ip_mask=24 --via=10.0.0.254 --dev={dev} --table=100 --force</t>
         </is>
       </c>
       <c r="E386" s="3" t="inlineStr">
@@ -23038,7 +23038,7 @@
       </c>
       <c r="K386" s="3" t="inlineStr">
         <is>
-          <t>notcontains:10.30.51.0</t>
+          <t>contains:10.30.51.0</t>
         </is>
       </c>
     </row>
@@ -23060,7 +23060,7 @@
       </c>
       <c r="D387" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iproute --chip=-1 --ip=10.30.51.0 --ip_mask=24 --table=100</t>
+          <t>1. dcat inject rNPU_iproute --chip=-1 --ip=10.30.51.0 --ip_mask=24 --via=10.0.0.254 --dev={dev} --table=100</t>
         </is>
       </c>
       <c r="E387" s="3" t="inlineStr">
@@ -23117,7 +23117,7 @@
       </c>
       <c r="D388" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iproute --chip=8 --ip=10.30.51.0 --ip_mask=24 --table=100</t>
+          <t>1. dcat inject rNPU_iproute --chip=8 --ip=10.30.51.0 --ip_mask=24 --via=10.0.0.254 --dev={dev} --table=100</t>
         </is>
       </c>
       <c r="E388" s="3" t="inlineStr">
@@ -23270,7 +23270,7 @@
       </c>
       <c r="K390" s="3" t="inlineStr">
         <is>
-          <t>contains:10.30.51.0</t>
+          <t>notcontains:10.30.51.0</t>
         </is>
       </c>
     </row>
@@ -23292,7 +23292,7 @@
       </c>
       <c r="D391" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iproute --chip={chip} --ip=10.30.51.0 --ip_mask=-1 --table=100</t>
+          <t>1. dcat inject rNPU_iproute --chip={chip} --ip=10.30.51.0 --ip_mask=-1 --via=10.0.0.254 --dev={dev} --table=100</t>
         </is>
       </c>
       <c r="E391" s="3" t="inlineStr">
@@ -23465,7 +23465,7 @@
       </c>
       <c r="D394" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rNPU_iproute --chip={chip} --ip=10.30.51.0 --ip_mask=24 --table=100
+          <t>1. 执行 dcat inject rNPU_iproute --chip={chip} --ip=10.30.51.0 --ip_mask=24 --via=10.0.0.254 --dev={dev} --table=100
 2. 检查未先创建时的报错
 3. 执行 dcat clean rNPU_iproute --chip={chip} --ip=10.30.51.0 --ip_mask=24 --table=100</t>
         </is>
@@ -23526,7 +23526,7 @@
       </c>
       <c r="D395" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iproute --chip={chip} --ip=10.30.51.0 --ip_mask=24 --table=100
+          <t>1. dcat inject rNPU_iproute --chip={chip} --ip=10.30.51.0 --ip_mask=24 --via=10.0.0.254 --dev={dev} --table=100
 2. 再次 dcat inject rNPU_iproute --chip={chip} --ip=10.30.51.0 --ip_mask=24 --table=100</t>
         </is>
       </c>
@@ -23643,7 +23643,7 @@
       </c>
       <c r="D397" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iproute --chip={chip} --ip=10.30.51.0 --ip_mask=24 --table=100
+          <t>1. dcat inject rNPU_iproute --chip={chip} --ip=10.30.51.0 --ip_mask=24 --via=10.0.0.254 --dev={dev} --table=100
 2. 检查注入状态</t>
         </is>
       </c>
@@ -23680,7 +23680,7 @@
       </c>
       <c r="K397" s="3" t="inlineStr">
         <is>
-          <t>notcontains:10.30.51.0</t>
+          <t>contains:10.30.51.0</t>
         </is>
       </c>
     </row>
@@ -23702,7 +23702,7 @@
       </c>
       <c r="D398" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iproute --chip={chip} --ip=10.30.51.0 --ip_mask=24 --table=100
+          <t>1. dcat inject rNPU_iproute --chip={chip} --ip=10.30.51.0 --ip_mask=24 --via=10.0.0.254 --dev={dev} --table=100
 2. dcat query rNPU_iproute
 3. dcat clean rNPU_iproute --chip={chip} --ip=10.30.51.0 --ip_mask=24 --table=100
 4. dcat query rNPU_iproute</t>
@@ -23861,7 +23861,7 @@
       </c>
       <c r="K400" s="3" t="inlineStr">
         <is>
-          <t>contains:10.20.10.210</t>
+          <t>contains:10.30.12.210</t>
         </is>
       </c>
     </row>
@@ -24093,7 +24093,7 @@
       </c>
       <c r="K404" s="3" t="inlineStr">
         <is>
-          <t>notcontains:10.20.10.210</t>
+          <t>notcontains:10.30.12.210</t>
         </is>
       </c>
     </row>
@@ -24380,7 +24380,7 @@
       </c>
       <c r="K409" s="3" t="inlineStr">
         <is>
-          <t>contains:10.20.10.210</t>
+          <t>contains:10.30.12.210</t>
         </is>
       </c>
     </row>
@@ -24437,7 +24437,7 @@
       </c>
       <c r="K410" s="3" t="inlineStr">
         <is>
-          <t>contains:10.20.10.210</t>
+          <t>contains:10.30.12.210</t>
         </is>
       </c>
     </row>
@@ -24670,7 +24670,7 @@
       </c>
       <c r="K414" s="3" t="inlineStr">
         <is>
-          <t>contains:10.20.10.210</t>
+          <t>contains:10.30.12.210</t>
         </is>
       </c>
     </row>
@@ -24731,7 +24731,7 @@
       </c>
       <c r="K415" s="3" t="inlineStr">
         <is>
-          <t>contains:10.20.10.210</t>
+          <t>contains:10.30.12.210</t>
         </is>
       </c>
     </row>
@@ -24875,7 +24875,7 @@
       </c>
       <c r="D418" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iprule --chip={chip} --dir=from --ip=10.30.12.211 --force</t>
+          <t>1. dcat inject rNPU_iprule --chip={chip} --dir=from --ip=10.30.12.211 --table=150 --force</t>
         </is>
       </c>
       <c r="E418" s="3" t="inlineStr">
@@ -24912,7 +24912,7 @@
       </c>
       <c r="K418" s="3" t="inlineStr">
         <is>
-          <t>notcontains:10.20.10.211</t>
+          <t>contains:10.30.12.211</t>
         </is>
       </c>
     </row>
@@ -24934,7 +24934,7 @@
       </c>
       <c r="D419" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iprule --chip=-1 --dir=from --ip=10.30.12.211</t>
+          <t>1. dcat inject rNPU_iprule --chip=-1 --dir=from --ip=10.30.12.211 --table=150</t>
         </is>
       </c>
       <c r="E419" s="3" t="inlineStr">
@@ -24991,7 +24991,7 @@
       </c>
       <c r="D420" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iprule --chip=8 --dir=from --ip=10.30.12.211</t>
+          <t>1. dcat inject rNPU_iprule --chip=8 --dir=from --ip=10.30.12.211 --table=150</t>
         </is>
       </c>
       <c r="E420" s="3" t="inlineStr">
@@ -25144,7 +25144,7 @@
       </c>
       <c r="K422" s="3" t="inlineStr">
         <is>
-          <t>contains:10.20.10.211</t>
+          <t>notcontains:10.30.12.211</t>
         </is>
       </c>
     </row>
@@ -25166,7 +25166,7 @@
       </c>
       <c r="D423" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iprule --chip={chip} --dir=invalid --ip=10.30.12.211</t>
+          <t>1. dcat inject rNPU_iprule --chip={chip} --dir=invalid --ip=10.30.12.211 --table=150</t>
         </is>
       </c>
       <c r="E423" s="3" t="inlineStr">
@@ -25339,7 +25339,7 @@
       </c>
       <c r="D426" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rNPU_iprule --chip={chip} --dir=from --ip=10.30.12.211
+          <t>1. 执行 dcat inject rNPU_iprule --chip={chip} --dir=from --ip=10.30.12.211 --table=150
 2. 检查未先创建时的报错
 3. 执行 dcat clean rNPU_iprule --chip={chip} --dir=from --ip=10.30.12.211</t>
         </is>
@@ -25378,7 +25378,7 @@
       </c>
       <c r="K426" s="3" t="inlineStr">
         <is>
-          <t>notcontains:10.20.10.211</t>
+          <t>notcontains:10.30.12.211</t>
         </is>
       </c>
     </row>
@@ -25400,7 +25400,7 @@
       </c>
       <c r="D427" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iprule --chip={chip} --dir=from --ip=10.30.12.211
+          <t>1. dcat inject rNPU_iprule --chip={chip} --dir=from --ip=10.30.12.211 --table=150
 2. 再次 dcat inject rNPU_iprule --chip={chip} --dir=from --ip=10.30.12.211</t>
         </is>
       </c>
@@ -25517,7 +25517,7 @@
       </c>
       <c r="D429" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iprule --chip={chip} --dir=from --ip=10.30.12.211
+          <t>1. dcat inject rNPU_iprule --chip={chip} --dir=from --ip=10.30.12.211 --table=150
 2. 检查注入状态</t>
         </is>
       </c>
@@ -25554,7 +25554,7 @@
       </c>
       <c r="K429" s="3" t="inlineStr">
         <is>
-          <t>notcontains:10.20.10.211</t>
+          <t>contains:10.30.12.211</t>
         </is>
       </c>
     </row>
@@ -25576,7 +25576,7 @@
       </c>
       <c r="D430" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iprule --chip={chip} --dir=from --ip=10.30.12.211
+          <t>1. dcat inject rNPU_iprule --chip={chip} --dir=from --ip=10.30.12.211 --table=150
 2. dcat query rNPU_iprule
 3. dcat clean rNPU_iprule --chip={chip} --dir=from --ip=10.30.12.211
 4. dcat query rNPU_iprule</t>
@@ -26616,12 +26616,12 @@
       </c>
       <c r="J447" s="3" t="inlineStr">
         <is>
-          <t>（注入被拒绝，未生效，无系统观测）</t>
+          <t>hccn_tool -i {chip} -mtu -g 2&gt;/dev/null | grep -oE 'mtu:[0-9]+'</t>
         </is>
       </c>
       <c r="K447" s="3" t="inlineStr">
         <is>
-          <t>exitcode:1</t>
+          <t>contains:1280</t>
         </is>
       </c>
     </row>
@@ -26638,7 +26638,7 @@
       </c>
       <c r="C448" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已 clean rNPU_mtu_mismatch</t>
+          <t>npu_hardware，已注入 rNPU_mtu_mismatch</t>
         </is>
       </c>
       <c r="D448" s="3" t="inlineStr">
@@ -27341,7 +27341,7 @@
       </c>
       <c r="C460" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已 clean rNPU_mtu_mismatch</t>
+          <t>npu_hardware，已注入 rNPU_mtu_mismatch</t>
         </is>
       </c>
       <c r="D460" s="3" t="inlineStr">
@@ -27691,7 +27691,7 @@
       </c>
       <c r="C466" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已 clean rNPU_netdetect_change</t>
+          <t>npu_hardware，已注入 rNPU_netdetect_change</t>
         </is>
       </c>
       <c r="D466" s="3" t="inlineStr">
@@ -28164,7 +28164,7 @@
       </c>
       <c r="C474" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已 clean rNPU_netdetect_change</t>
+          <t>npu_hardware，已注入 rNPU_netdetect_change</t>
         </is>
       </c>
       <c r="D474" s="3" t="inlineStr">
@@ -28343,7 +28343,7 @@
       </c>
       <c r="C477" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已 clean rNPU_roce_port_change</t>
+          <t>npu_hardware，已注入 rNPU_roce_port_change</t>
         </is>
       </c>
       <c r="D477" s="3" t="inlineStr">
@@ -28987,7 +28987,7 @@
       </c>
       <c r="C488" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已 clean rNPU_roce_port_change</t>
+          <t>npu_hardware，已注入 rNPU_roce_port_change</t>
         </is>
       </c>
       <c r="D488" s="3" t="inlineStr">
@@ -29051,7 +29051,7 @@
       </c>
       <c r="D489" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_route --chip={chip} --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254 --force</t>
+          <t>1. dcat inject rNPU_route --chip={chip} --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.0.0.254 --force</t>
         </is>
       </c>
       <c r="E489" s="3" t="inlineStr">
@@ -29110,7 +29110,7 @@
       </c>
       <c r="D490" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_route --chip={chip} --address=invalid --netmask=255.255.255.0 --gateway=10.30.12.254</t>
+          <t>1. dcat inject rNPU_route --chip={chip} --address=invalid --netmask=255.255.255.0 --gateway=10.0.0.254</t>
         </is>
       </c>
       <c r="E490" s="3" t="inlineStr">
@@ -29167,7 +29167,7 @@
       </c>
       <c r="D491" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_route --chip=-1 --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254</t>
+          <t>1. dcat inject rNPU_route --chip=-1 --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.0.0.254</t>
         </is>
       </c>
       <c r="E491" s="3" t="inlineStr">
@@ -29224,7 +29224,7 @@
       </c>
       <c r="D492" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_route --chip=8 --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254</t>
+          <t>1. dcat inject rNPU_route --chip=8 --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.0.0.254</t>
         </is>
       </c>
       <c r="E492" s="3" t="inlineStr">
@@ -29276,12 +29276,12 @@
       </c>
       <c r="C493" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已 clean rNPU_route</t>
+          <t>npu_hardware，已注入 rNPU_route</t>
         </is>
       </c>
       <c r="D493" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_route --chip={chip} --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254
+          <t>1. dcat clean rNPU_route --chip={chip} --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.0.0.254
 2. dcat query（无 uid）</t>
         </is>
       </c>
@@ -29340,7 +29340,7 @@
       </c>
       <c r="D494" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_route --chip={chip} --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254
+          <t>1. dcat clean rNPU_route --chip={chip} --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.0.0.254
 2. 检查恢复状态</t>
         </is>
       </c>
@@ -29457,7 +29457,7 @@
       </c>
       <c r="D496" s="3" t="inlineStr">
         <is>
-          <t>1. dcat query rNPU_route --chip={chip} --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254</t>
+          <t>1. dcat query rNPU_route --chip={chip} --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.0.0.254</t>
         </is>
       </c>
       <c r="E496" s="3" t="inlineStr">
@@ -29515,7 +29515,7 @@
       </c>
       <c r="D497" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_route --chip={chip} --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254
+          <t>1. dcat inject rNPU_route --chip={chip} --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.0.0.254
 2. 再次 dcat inject rNPU_route --chip={chip} --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254</t>
         </is>
       </c>
@@ -29632,7 +29632,7 @@
       </c>
       <c r="D499" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_route --chip={chip} --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254
+          <t>1. dcat inject rNPU_route --chip={chip} --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.0.0.254
 2. 检查注入状态</t>
         </is>
       </c>
@@ -29691,9 +29691,9 @@
       </c>
       <c r="D500" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rNPU_route --chip={chip} --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254
+          <t>1. 执行 dcat inject rNPU_route --chip={chip} --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.0.0.254
 2. 执行 dcat query rNPU_route --chip={chip}
-3. 执行 dcat clean rNPU_route --chip={chip} --address=10.30.40.0 --netmask=255.255.255.0</t>
+3. 执行 dcat clean rNPU_route --chip={chip} --address=10.30.40.0 --netmask=255.255.255.0ress=10.30.40.0 --netmask=255.255.255.0</t>
         </is>
       </c>
       <c r="E500" s="3" t="inlineStr">
@@ -29752,7 +29752,7 @@
       </c>
       <c r="D501" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_route --chip={chip} --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254
+          <t>1. dcat inject rNPU_route --chip={chip} --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.0.0.254
 2. dcat query rNPU_route
 3. dcat clean rNPU_route --chip={chip} --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254
 4. dcat query rNPU_route</t>
@@ -29810,12 +29810,12 @@
       </c>
       <c r="C502" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已 clean rNPU_route</t>
+          <t>npu_hardware，已注入 rNPU_route</t>
         </is>
       </c>
       <c r="D502" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_route --chip={chip} --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254
+          <t>1. dcat clean rNPU_route --chip={chip} --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.0.0.254
 2. 再次 dcat clean rNPU_route --chip={chip} --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254</t>
         </is>
       </c>
@@ -29874,7 +29874,7 @@
       </c>
       <c r="D503" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_route --chip={chip} --address=10.30.41.0 --netmask=255.255.255.0 --force</t>
+          <t>1. dcat inject rNPU_route --chip={chip} --address=10.30.41.0 --netmask=255.255.255.0 --gateway=10.0.0.254 --force</t>
         </is>
       </c>
       <c r="E503" s="3" t="inlineStr">
@@ -29911,7 +29911,7 @@
       </c>
       <c r="K503" s="3" t="inlineStr">
         <is>
-          <t>notcontains:10.30.41.0</t>
+          <t>contains:10.30.41.0</t>
         </is>
       </c>
     </row>
@@ -29933,7 +29933,7 @@
       </c>
       <c r="D504" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_route --chip={chip} --address=invalid --netmask=255.255.255.0</t>
+          <t>1. dcat inject rNPU_route --chip={chip} --address=invalid --netmask=255.255.255.0 --gateway=10.0.0.254</t>
         </is>
       </c>
       <c r="E504" s="3" t="inlineStr">
@@ -29990,7 +29990,7 @@
       </c>
       <c r="D505" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_route --chip=-1 --address=10.30.41.0 --netmask=255.255.255.0</t>
+          <t>1. dcat inject rNPU_route --chip=-1 --address=10.30.41.0 --netmask=255.255.255.0 --gateway=10.0.0.254</t>
         </is>
       </c>
       <c r="E505" s="3" t="inlineStr">
@@ -30047,7 +30047,7 @@
       </c>
       <c r="D506" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_route --chip=8 --address=10.30.41.0 --netmask=255.255.255.0</t>
+          <t>1. dcat inject rNPU_route --chip=8 --address=10.30.41.0 --netmask=255.255.255.0 --gateway=10.0.0.254</t>
         </is>
       </c>
       <c r="E506" s="3" t="inlineStr">
@@ -30099,12 +30099,12 @@
       </c>
       <c r="C507" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已 clean rNPU_route</t>
+          <t>npu_hardware，已注入 rNPU_route</t>
         </is>
       </c>
       <c r="D507" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_route --chip={chip} --address=10.30.41.0 --netmask=255.255.255.0
+          <t>1. dcat clean rNPU_route --chip={chip} --address=10.30.41.0 --netmask=255.255.255.0 --gateway=10.0.0.254
 2. dcat query（无 uid）</t>
         </is>
       </c>
@@ -30163,7 +30163,7 @@
       </c>
       <c r="D508" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_route --chip={chip} --address=10.30.41.0 --netmask=255.255.255.0
+          <t>1. dcat clean rNPU_route --chip={chip} --address=10.30.41.0 --netmask=255.255.255.0 --gateway=10.0.0.254
 2. 检查恢复状态</t>
         </is>
       </c>
@@ -30200,7 +30200,7 @@
       </c>
       <c r="K508" s="3" t="inlineStr">
         <is>
-          <t>contains:10.30.41.0</t>
+          <t>notcontains:10.30.41.0</t>
         </is>
       </c>
     </row>
@@ -30280,7 +30280,7 @@
       </c>
       <c r="D510" s="3" t="inlineStr">
         <is>
-          <t>1. dcat query rNPU_route --chip={chip} --address=10.30.41.0 --netmask=255.255.255.0</t>
+          <t>1. dcat query rNPU_route --chip={chip} --address=10.30.41.0 --netmask=255.255.255.0 --gateway=10.0.0.254</t>
         </is>
       </c>
       <c r="E510" s="3" t="inlineStr">
@@ -30338,7 +30338,7 @@
       </c>
       <c r="D511" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rNPU_route --chip={chip} --address=10.30.41.0 --netmask=255.255.255.0
+          <t>1. 执行 dcat inject rNPU_route --chip={chip} --address=10.30.41.0 --netmask=255.255.255.0 --gateway=10.0.0.254
 2. 检查未先创建时的报错
 3. 执行 dcat clean rNPU_route --chip={chip} --address=10.30.41.0 --netmask=255.255.255.0</t>
         </is>
@@ -30399,7 +30399,7 @@
       </c>
       <c r="D512" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_route --chip={chip} --address=10.30.41.0 --netmask=255.255.255.0
+          <t>1. dcat inject rNPU_route --chip={chip} --address=10.30.41.0 --netmask=255.255.255.0 --gateway=10.0.0.254
 2. 再次 dcat inject rNPU_route --chip={chip} --address=10.30.41.0 --netmask=255.255.255.0</t>
         </is>
       </c>
@@ -30516,7 +30516,7 @@
       </c>
       <c r="D514" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_route --chip={chip} --address=10.30.41.0 --netmask=255.255.255.0
+          <t>1. dcat inject rNPU_route --chip={chip} --address=10.30.41.0 --netmask=255.255.255.0 --gateway=10.0.0.254
 2. 检查注入状态</t>
         </is>
       </c>
@@ -30553,7 +30553,7 @@
       </c>
       <c r="K514" s="3" t="inlineStr">
         <is>
-          <t>notcontains:10.30.41.0</t>
+          <t>contains:10.30.41.0</t>
         </is>
       </c>
     </row>
@@ -30575,7 +30575,7 @@
       </c>
       <c r="D515" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_route --chip={chip} --address=10.30.41.0 --netmask=255.255.255.0
+          <t>1. dcat inject rNPU_route --chip={chip} --address=10.30.41.0 --netmask=255.255.255.0 --gateway=10.0.0.254
 2. dcat query rNPU_route
 3. dcat clean rNPU_route --chip={chip} --address=10.30.41.0 --netmask=255.255.255.0
 4. dcat query rNPU_route</t>
@@ -30633,12 +30633,12 @@
       </c>
       <c r="C516" s="3" t="inlineStr">
         <is>
-          <t>npu_hardware，已 clean rNPU_route</t>
+          <t>npu_hardware，已注入 rNPU_route</t>
         </is>
       </c>
       <c r="D516" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_route --chip={chip} --address=10.30.41.0 --netmask=255.255.255.0
+          <t>1. dcat clean rNPU_route --chip={chip} --address=10.30.41.0 --netmask=255.255.255.0 --gateway=10.0.0.254
 2. 再次 dcat clean rNPU_route --chip={chip} --address=10.30.41.0 --netmask=255.255.255.0</t>
         </is>
       </c>
@@ -37097,7 +37097,7 @@
       </c>
       <c r="K626" s="3" t="inlineStr">
         <is>
-          <t>notcontains:&lt;注入值&gt;</t>
+          <t>notcontains:DOWN</t>
         </is>
       </c>
     </row>
@@ -37178,7 +37178,7 @@
       <c r="D628" s="3" t="inlineStr">
         <is>
           <t>1. dcat clean rNPU_ip_change --chip={chip} --address=192.168.1.100 --netmask=255.255.255.0
-2. hccn_tool -i 0 -ip -g</t>
+2. hccn_tool -i {chip} -ip -g</t>
         </is>
       </c>
       <c r="E628" s="3" t="inlineStr">
@@ -37214,7 +37214,7 @@
       </c>
       <c r="K628" s="3" t="inlineStr">
         <is>
-          <t>notcontains:&lt;注入值&gt;</t>
+          <t>notcontains:192.168.1.100</t>
         </is>
       </c>
     </row>
@@ -37236,7 +37236,7 @@
       </c>
       <c r="D629" s="3" t="inlineStr">
         <is>
-          <t>1. dcat query rNPU_gw_change --chip={chip} --gateway=10.30.12.1</t>
+          <t>1. dcat query rNPU_gw_change --chip={chip} --gateway=10.0.0.200</t>
         </is>
       </c>
       <c r="E629" s="3" t="inlineStr">
@@ -37295,7 +37295,7 @@
       <c r="D630" s="3" t="inlineStr">
         <is>
           <t>1. dcat clean rNPU_gw_change --chip={chip} --gateway=10.30.12.1
-2. hccn_tool -i 2 -gateway -g</t>
+2. hccn_tool -i {chip} -gateway -g</t>
         </is>
       </c>
       <c r="E630" s="3" t="inlineStr">
@@ -37331,7 +37331,7 @@
       </c>
       <c r="K630" s="3" t="inlineStr">
         <is>
-          <t>notcontains:&lt;注入值&gt;</t>
+          <t>notcontains:10.0.0.200</t>
         </is>
       </c>
     </row>
@@ -37448,7 +37448,7 @@
       </c>
       <c r="K632" s="3" t="inlineStr">
         <is>
-          <t>notcontains:&lt;注入值&gt;</t>
+          <t>notcontains:00:11:22:33:44:55</t>
         </is>
       </c>
     </row>
@@ -37470,7 +37470,7 @@
       </c>
       <c r="D633" s="3" t="inlineStr">
         <is>
-          <t>1. dcat query rNPU_route --chip={chip} --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254</t>
+          <t>1. dcat query rNPU_route --chip={chip} --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.0.0.254</t>
         </is>
       </c>
       <c r="E633" s="3" t="inlineStr">
@@ -37528,7 +37528,7 @@
       </c>
       <c r="D634" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_route --chip={chip} --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.30.12.254
+          <t>1. dcat clean rNPU_route --chip={chip} --address=10.30.40.0 --netmask=255.255.255.0 --gateway=10.0.0.254
 2. hccn_tool -i 2 -route -g</t>
         </is>
       </c>
@@ -37565,7 +37565,7 @@
       </c>
       <c r="K634" s="3" t="inlineStr">
         <is>
-          <t>notcontains:&lt;注入值&gt;</t>
+          <t>notcontains:10.30.40.0</t>
         </is>
       </c>
     </row>
@@ -37719,7 +37719,7 @@
       </c>
       <c r="F637" t="inlineStr">
         <is>
-          <t>1. 缺少必填参数 --chip，拒绝 exit 1</t>
+          <t>1. 缺少必填参数 --chip，拒绝 exit 3</t>
         </is>
       </c>
       <c r="G637" t="inlineStr">
@@ -37898,7 +37898,7 @@
       </c>
       <c r="F640" t="inlineStr">
         <is>
-          <t>1. 缺少必填参数 --chip，拒绝 exit 1</t>
+          <t>1. 缺少必填参数 --chip，拒绝 exit 3</t>
         </is>
       </c>
       <c r="G640" t="inlineStr">
@@ -38077,7 +38077,7 @@
       </c>
       <c r="F643" t="inlineStr">
         <is>
-          <t>1. 缺少必填参数 --chip，拒绝 exit 1</t>
+          <t>1. 缺少必填参数 --chip，拒绝 exit 3</t>
         </is>
       </c>
       <c r="G643" t="inlineStr">
@@ -38256,7 +38256,7 @@
       </c>
       <c r="F646" t="inlineStr">
         <is>
-          <t>1. 缺少必填参数 --chip，拒绝 exit 1</t>
+          <t>1. 缺少必填参数 --chip，拒绝 exit 3</t>
         </is>
       </c>
       <c r="G646" t="inlineStr">

--- a/tests/e2e/testcases.xlsx
+++ b/tests/e2e/testcases.xlsx
@@ -19903,12 +19903,12 @@
       </c>
       <c r="D333" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_gw_change --chip={chip} --gateway=10.0.0.200 --force</t>
+          <t>1. dcat inject rNPU_gw_change --chip={chip} --gateway=10.0.0.1 --force</t>
         </is>
       </c>
       <c r="E333" s="3" t="inlineStr">
         <is>
-          <t>--chip=2 --gateway=10.30.12.1 --force</t>
+          <t>--chip=2 --gateway=10.0.0.1 --force</t>
         </is>
       </c>
       <c r="F333" s="3" t="inlineStr">
@@ -19940,7 +19940,7 @@
       </c>
       <c r="K333" s="3" t="inlineStr">
         <is>
-          <t>contains:10.0.0.200</t>
+          <t>contains:10.0.0.1</t>
         </is>
       </c>
     </row>
@@ -20022,7 +20022,7 @@
       </c>
       <c r="D335" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rNPU_gw_change --chip={chip} --gateway=10.0.0.200</t>
+          <t>1. 执行 dcat inject rNPU_gw_change --chip={chip} --gateway=10.0.0.1</t>
         </is>
       </c>
       <c r="E335" s="3" t="inlineStr">
@@ -20058,7 +20058,7 @@
       </c>
       <c r="K335" s="3" t="inlineStr">
         <is>
-          <t>contains:10.0.0.200</t>
+          <t>contains:10.0.0.1</t>
         </is>
       </c>
     </row>
@@ -20080,7 +20080,7 @@
       </c>
       <c r="D336" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rNPU_gw_change --chip={chip} --gateway=10.0.0.200</t>
+          <t>1. 执行 dcat inject rNPU_gw_change --chip={chip} --gateway=10.0.0.1</t>
         </is>
       </c>
       <c r="E336" s="3" t="inlineStr">
@@ -20115,7 +20115,7 @@
       </c>
       <c r="K336" s="3" t="inlineStr">
         <is>
-          <t>contains:10.0.0.200</t>
+          <t>contains:10.0.0.1</t>
         </is>
       </c>
     </row>
@@ -20137,7 +20137,7 @@
       </c>
       <c r="D337" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_gw_change --chip=-1 --gateway=10.0.0.200</t>
+          <t>1. dcat inject rNPU_gw_change --chip=-1 --gateway=10.0.0.1</t>
         </is>
       </c>
       <c r="E337" s="3" t="inlineStr">
@@ -20194,7 +20194,7 @@
       </c>
       <c r="D338" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_gw_change --chip=8 --gateway=10.0.0.200</t>
+          <t>1. dcat inject rNPU_gw_change --chip=8 --gateway=10.0.0.1</t>
         </is>
       </c>
       <c r="E338" s="3" t="inlineStr">
@@ -20251,7 +20251,7 @@
       </c>
       <c r="D339" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_gw_change --chip={chip} --gateway=10.30.12.1
+          <t>1. dcat clean rNPU_gw_change --chip={chip} --gateway=10.0.0.1
 2. dcat query（无 uid）</t>
         </is>
       </c>
@@ -20310,13 +20310,13 @@
       </c>
       <c r="D340" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_gw_change --chip={chip} --gateway=10.30.12.1
+          <t>1. dcat clean rNPU_gw_change --chip={chip} --gateway=10.0.0.1
 2. 检查恢复状态</t>
         </is>
       </c>
       <c r="E340" s="3" t="inlineStr">
         <is>
-          <t>--chip=2 --gateway=10.30.12.1</t>
+          <t>--chip=2 --gateway=10.0.0.1</t>
         </is>
       </c>
       <c r="F340" s="3" t="inlineStr">
@@ -20347,7 +20347,7 @@
       </c>
       <c r="K340" s="3" t="inlineStr">
         <is>
-          <t>notcontains:10.0.0.200</t>
+          <t>notcontains:10.0.0.1</t>
         </is>
       </c>
     </row>
@@ -20544,12 +20544,12 @@
       </c>
       <c r="D344" s="3" t="inlineStr">
         <is>
-          <t>1. dcat query rNPU_gw_change --chip={chip} --gateway=10.30.12.1</t>
+          <t>1. dcat query rNPU_gw_change --chip={chip} --gateway=10.0.0.1</t>
         </is>
       </c>
       <c r="E344" s="3" t="inlineStr">
         <is>
-          <t>--chip=2 --gateway=10.30.12.1</t>
+          <t>--chip=2 --gateway=10.0.0.1</t>
         </is>
       </c>
       <c r="F344" s="3" t="inlineStr">
@@ -20636,7 +20636,7 @@
       </c>
       <c r="K345" s="3" t="inlineStr">
         <is>
-          <t>notcontains:10.0.0.200</t>
+          <t>notcontains:10.0.0.1</t>
         </is>
       </c>
     </row>
@@ -20658,13 +20658,13 @@
       </c>
       <c r="D346" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_gw_change --chip={chip} --gateway=10.0.0.200
-2. 再次 dcat inject rNPU_gw_change --chip={chip} --gateway=10.30.12.1</t>
+          <t>1. dcat inject rNPU_gw_change --chip={chip} --gateway=10.0.0.1
+2. 再次 dcat inject rNPU_gw_change --chip={chip} --gateway=10.0.0.1</t>
         </is>
       </c>
       <c r="E346" s="3" t="inlineStr">
         <is>
-          <t>--chip=2 --gateway=10.30.12.1</t>
+          <t>--chip=2 --gateway=10.0.0.1</t>
         </is>
       </c>
       <c r="F346" s="3" t="inlineStr">
@@ -20775,13 +20775,13 @@
       </c>
       <c r="D348" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_gw_change --chip={chip} --gateway=10.0.0.200
+          <t>1. dcat inject rNPU_gw_change --chip={chip} --gateway=10.0.0.1
 2. 检查注入状态</t>
         </is>
       </c>
       <c r="E348" s="3" t="inlineStr">
         <is>
-          <t>--chip=2 --gateway=10.30.12.1</t>
+          <t>--chip=2 --gateway=10.0.0.1</t>
         </is>
       </c>
       <c r="F348" s="3" t="inlineStr">
@@ -20812,7 +20812,7 @@
       </c>
       <c r="K348" s="3" t="inlineStr">
         <is>
-          <t>contains:10.0.0.200</t>
+          <t>contains:10.0.0.1</t>
         </is>
       </c>
     </row>
@@ -20834,15 +20834,15 @@
       </c>
       <c r="D349" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_gw_change --chip={chip} --gateway=10.0.0.200
+          <t>1. dcat inject rNPU_gw_change --chip={chip} --gateway=10.0.0.1
 2. dcat query rNPU_gw_change
-3. dcat clean rNPU_gw_change --chip={chip} --gateway=10.30.12.1
+3. dcat clean rNPU_gw_change --chip={chip} --gateway=10.0.0.1
 4. dcat query rNPU_gw_change</t>
         </is>
       </c>
       <c r="E349" s="3" t="inlineStr">
         <is>
-          <t>--chip=2 --gateway=10.30.12.1</t>
+          <t>--chip=2 --gateway=10.0.0.1</t>
         </is>
       </c>
       <c r="F349" s="3" t="inlineStr">
@@ -20897,13 +20897,13 @@
       </c>
       <c r="D350" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rNPU_gw_change --chip={chip} --gateway=10.0.0.200
+          <t>1. 执行 dcat inject rNPU_gw_change --chip={chip} --gateway=10.0.0.1
 2. 检查 query 返回</t>
         </is>
       </c>
       <c r="E350" s="3" t="inlineStr">
         <is>
-          <t>chip=2；gateway=10.30.12.254（同当前）</t>
+          <t>chip=2；gateway=10.0.0.254（同当前）</t>
         </is>
       </c>
       <c r="F350" s="3" t="inlineStr">
@@ -20953,19 +20953,19 @@
       </c>
       <c r="D351" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rNPU_gw_change --chip={chip} --gateway=10.0.0.200（同网段且≠当前网关）
+          <t>1. 执行 dcat inject rNPU_gw_change --chip={chip} --gateway=10.0.0.1（同网段且≠当前网关）
 2. 检查 sidecar 与 query</t>
         </is>
       </c>
       <c r="E351" s="3" t="inlineStr">
         <is>
-          <t>chip=2；gateway=10.30.12.1</t>
+          <t>chip=2；gateway=10.0.0.1</t>
         </is>
       </c>
       <c r="F351" s="3" t="inlineStr">
         <is>
           <t>1. 先 -gateway -g 取原值 .254 存 sidecar
-2. 再 -gateway -s gateway 10.30.12.1
+2. 再 -gateway -s gateway 10.0.0.1
 3. 返回 status:ok
 4. query 比对当前网关与原值不同则 confirmed:true</t>
         </is>
@@ -20988,7 +20988,7 @@
       </c>
       <c r="K351" s="3" t="inlineStr">
         <is>
-          <t>contains:10.0.0.200</t>
+          <t>contains:10.0.0.1</t>
         </is>
       </c>
     </row>
@@ -21066,13 +21066,13 @@
       </c>
       <c r="D353" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_gw_change --chip={chip} --gateway=10.0.0.200
-2. 再次 dcat clean rNPU_gw_change --chip={chip} --gateway=10.30.12.1</t>
+          <t>1. dcat clean rNPU_gw_change --chip={chip} --gateway=10.0.0.1
+2. 再次 dcat clean rNPU_gw_change --chip={chip} --gateway=10.0.0.1</t>
         </is>
       </c>
       <c r="E353" s="3" t="inlineStr">
         <is>
-          <t>--chip=2 --gateway=10.30.12.1</t>
+          <t>--chip=2 --gateway=10.0.0.1</t>
         </is>
       </c>
       <c r="F353" s="3" t="inlineStr">
@@ -37236,12 +37236,12 @@
       </c>
       <c r="D629" s="3" t="inlineStr">
         <is>
-          <t>1. dcat query rNPU_gw_change --chip={chip} --gateway=10.0.0.200</t>
+          <t>1. dcat query rNPU_gw_change --chip={chip} --gateway=10.0.0.1</t>
         </is>
       </c>
       <c r="E629" s="3" t="inlineStr">
         <is>
-          <t>chip=2；gateway=10.30.12.1</t>
+          <t>chip=2；gateway=10.0.0.1</t>
         </is>
       </c>
       <c r="F629" s="3" t="inlineStr">
@@ -37294,13 +37294,13 @@
       </c>
       <c r="D630" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_gw_change --chip={chip} --gateway=10.30.12.1
+          <t>1. dcat clean rNPU_gw_change --chip={chip} --gateway=10.0.0.1
 2. hccn_tool -i {chip} -gateway -g</t>
         </is>
       </c>
       <c r="E630" s="3" t="inlineStr">
         <is>
-          <t>chip=2；gateway=10.30.12.1</t>
+          <t>chip=2；gateway=10.0.0.1</t>
         </is>
       </c>
       <c r="F630" s="3" t="inlineStr">
@@ -37331,7 +37331,7 @@
       </c>
       <c r="K630" s="3" t="inlineStr">
         <is>
-          <t>notcontains:10.0.0.200</t>
+          <t>notcontains:10.0.0.1</t>
         </is>
       </c>
     </row>

--- a/tests/e2e/testcases.xlsx
+++ b/tests/e2e/testcases.xlsx
@@ -1492,7 +1492,7 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>cat /sys/devices/system/cpu/cpu1/online 2&gt;/dev/null || echo NA</t>
+          <t>cat /sys/devices/system/cpu/cpu0/online 2&gt;/dev/null || echo NA</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>cat /sys/devices/system/cpu/cpu1/online 2&gt;/dev/null || echo NA</t>
+          <t>cat /sys/devices/system/cpu/cpu2/online 2&gt;/dev/null || echo NA</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>device1=/data（目录）；device2=/dev/sdb1（非目录设备）</t>
+          <t>device1=/data（目录）；device2=/tmp（非目录设备）</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>device=/data；workers 缺省；size_mb 缺省</t>
+          <t>device=/tmp；workers 缺省；size_mb 缺省</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
@@ -3069,7 +3069,7 @@
           <t>1. 对应 DCAT_PARAM_WORKERS/SIZE_MB 环境变量未设置
 2. 脚本走默认 workers=4、size_mb=200
 3. 返回 status:ok 与 record_id
-4. /data 下出现 dcat.stress.* 临时文件与 4 个 dd 进程</t>
+4. /tmp 下出现 dcat.stress.* 临时文件与 4 个 dd 进程</t>
         </is>
       </c>
       <c r="G44" s="6" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNET_bw_limit</t>
+          <t>已注入 rNET_bw_limit</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNET_bw_limit</t>
+          <t>已注入 rNET_bw_limit</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNET_degrade</t>
+          <t>已注入 rNET_degrade</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNET_degrade</t>
+          <t>已注入 rNET_degrade</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNET_delay</t>
+          <t>已注入 rNET_delay</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
@@ -6205,7 +6205,7 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNET_delay</t>
+          <t>已注入 rNET_delay</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
@@ -6323,7 +6323,7 @@
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNET_down</t>
+          <t>已注入 rNET_down</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNET_down</t>
+          <t>已注入 rNET_down</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
@@ -7092,7 +7092,7 @@
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNET_jitter</t>
+          <t>已注入 rNET_jitter</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
@@ -8024,7 +8024,7 @@
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNET_jitter</t>
+          <t>已注入 rNET_jitter</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
@@ -8142,7 +8142,7 @@
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNET_link_flap</t>
+          <t>已注入 rNET_link_flap</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
@@ -8958,7 +8958,7 @@
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNET_link_flap</t>
+          <t>已注入 rNET_link_flap</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
@@ -9930,7 +9930,7 @@
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNET_port_occupy</t>
+          <t>已注入 rNET_port_occupy</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr">
@@ -10694,7 +10694,7 @@
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNET_port_occupy</t>
+          <t>已注入 rNET_port_occupy</t>
         </is>
       </c>
       <c r="D175" s="3" t="inlineStr">
@@ -10812,7 +10812,7 @@
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNET_reorder</t>
+          <t>已注入 rNET_reorder</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr">
@@ -11744,7 +11744,7 @@
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNET_reorder</t>
+          <t>已注入 rNET_reorder</t>
         </is>
       </c>
       <c r="D193" s="3" t="inlineStr">
@@ -11862,7 +11862,7 @@
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNET_service_stop</t>
+          <t>已注入 rNET_service_stop</t>
         </is>
       </c>
       <c r="D195" s="3" t="inlineStr">
@@ -12453,7 +12453,7 @@
       </c>
       <c r="C205" s="3" t="inlineStr">
         <is>
-          <t>已 clean rNET_service_stop</t>
+          <t>已注入 rNET_service_stop</t>
         </is>
       </c>
       <c r="D205" s="3" t="inlineStr">
@@ -36066,7 +36066,7 @@
       </c>
       <c r="D609" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rDISK_write_overload --device=/data
+          <t>1. dcat clean rDISK_write_overload --device=/tmp
 2. ls /data/dcat.stress.* 2&gt;&amp;1</t>
         </is>
       </c>
@@ -36098,7 +36098,7 @@
       </c>
       <c r="J609" s="3" t="inlineStr">
         <is>
-          <t>ls /data/dcat.stress.* 2&gt;&amp;1</t>
+          <t>ls /tmp/dcat.stress.* 2&gt;&amp;1</t>
         </is>
       </c>
       <c r="K609" s="3" t="inlineStr">
@@ -36178,12 +36178,12 @@
       </c>
       <c r="C611" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNET_loss</t>
+          <t>已注入 rNET_loss --iface={iface} --loss_pct=10</t>
         </is>
       </c>
       <c r="D611" s="3" t="inlineStr">
         <is>
-          <t>1. dcat query rNET_loss --iface=eth0</t>
+          <t>1. dcat query rNET_loss --iface={iface}</t>
         </is>
       </c>
       <c r="E611" s="3" t="inlineStr">
@@ -36214,7 +36214,7 @@
       </c>
       <c r="J611" s="3" t="inlineStr">
         <is>
-          <t>dcat query rNET_loss --iface=eth0</t>
+          <t>dcat query rNET_loss --iface={iface}</t>
         </is>
       </c>
       <c r="K611" s="3" t="inlineStr">
@@ -36241,8 +36241,8 @@
       </c>
       <c r="D612" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNET_loss --iface=eth0
-2. ls /tmp/dcat-rNET_loss-eth0.sidecar 2&gt;&amp;1</t>
+          <t>1. dcat clean rNET_loss --iface={iface}
+2. ls /tmp/dcat-rNET_loss-{iface}.sidecar 2&gt;&amp;1</t>
         </is>
       </c>
       <c r="E612" s="3" t="inlineStr">
@@ -36273,7 +36273,7 @@
       </c>
       <c r="J612" s="3" t="inlineStr">
         <is>
-          <t>ls /tmp/dcat-rNET_loss-eth0.sidecar 2&gt;&amp;1</t>
+          <t>ls /tmp/dcat-rNET_loss-{iface}.sidecar 2&gt;&amp;1</t>
         </is>
       </c>
       <c r="K612" s="3" t="inlineStr">
@@ -36295,12 +36295,12 @@
       </c>
       <c r="C613" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNET_delay</t>
+          <t>已注入 rNET_delay --iface={iface} --delay_ms=50</t>
         </is>
       </c>
       <c r="D613" s="3" t="inlineStr">
         <is>
-          <t>1. dcat query rNET_delay --iface=eth0</t>
+          <t>1. dcat query rNET_delay --iface={iface}</t>
         </is>
       </c>
       <c r="E613" s="3" t="inlineStr">
@@ -36331,7 +36331,7 @@
       </c>
       <c r="J613" s="3" t="inlineStr">
         <is>
-          <t>dcat query rNET_delay --iface=eth0</t>
+          <t>dcat query rNET_delay --iface={iface}</t>
         </is>
       </c>
       <c r="K613" s="3" t="inlineStr">
@@ -36358,8 +36358,8 @@
       </c>
       <c r="D614" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNET_delay --iface=eth0
-2. ls /tmp/dcat-rNET_delay-eth0.sidecar 2&gt;&amp;1</t>
+          <t>1. dcat clean rNET_delay --iface={iface}
+2. ls /tmp/dcat-rNET_delay-{iface}.sidecar 2&gt;&amp;1</t>
         </is>
       </c>
       <c r="E614" s="3" t="inlineStr">
@@ -36390,7 +36390,7 @@
       </c>
       <c r="J614" s="3" t="inlineStr">
         <is>
-          <t>ls /tmp/dcat-rNET_delay-eth0.sidecar 2&gt;&amp;1</t>
+          <t>ls /tmp/dcat-rNET_delay-{iface}.sidecar 2&gt;&amp;1</t>
         </is>
       </c>
       <c r="K614" s="3" t="inlineStr">
@@ -36412,12 +36412,12 @@
       </c>
       <c r="C615" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNET_reorder</t>
+          <t>已注入 rNET_reorder --iface={iface} --reorder_pct=10</t>
         </is>
       </c>
       <c r="D615" s="3" t="inlineStr">
         <is>
-          <t>1. dcat query rNET_reorder --iface=eth0</t>
+          <t>1. dcat query rNET_reorder --iface={iface}</t>
         </is>
       </c>
       <c r="E615" s="3" t="inlineStr">
@@ -36448,7 +36448,7 @@
       </c>
       <c r="J615" s="3" t="inlineStr">
         <is>
-          <t>dcat query rNET_reorder --iface=eth0</t>
+          <t>dcat query rNET_reorder --iface={iface}</t>
         </is>
       </c>
       <c r="K615" s="3" t="inlineStr">
@@ -36475,8 +36475,8 @@
       </c>
       <c r="D616" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNET_reorder --iface=eth0
-2. ls /tmp/dcat-rNET_reorder-eth0.sidecar 2&gt;&amp;1</t>
+          <t>1. dcat clean rNET_reorder --iface={iface}
+2. ls /tmp/dcat-rNET_reorder-{iface}.sidecar 2&gt;&amp;1</t>
         </is>
       </c>
       <c r="E616" s="3" t="inlineStr">
@@ -36507,7 +36507,7 @@
       </c>
       <c r="J616" s="3" t="inlineStr">
         <is>
-          <t>ls /tmp/dcat-rNET_reorder-eth0.sidecar 2&gt;&amp;1</t>
+          <t>ls /tmp/dcat-rNET_reorder-{iface}.sidecar 2&gt;&amp;1</t>
         </is>
       </c>
       <c r="K616" s="3" t="inlineStr">
@@ -36529,12 +36529,12 @@
       </c>
       <c r="C617" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNET_jitter</t>
+          <t>已注入 rNET_jitter --iface={iface} --delay_ms=30 --jitter_ms=10</t>
         </is>
       </c>
       <c r="D617" s="3" t="inlineStr">
         <is>
-          <t>1. dcat query rNET_jitter --iface=eth0</t>
+          <t>1. dcat query rNET_jitter --iface={iface}</t>
         </is>
       </c>
       <c r="E617" s="3" t="inlineStr">
@@ -36565,7 +36565,7 @@
       </c>
       <c r="J617" s="3" t="inlineStr">
         <is>
-          <t>dcat query rNET_jitter --iface=eth0</t>
+          <t>dcat query rNET_jitter --iface={iface}</t>
         </is>
       </c>
       <c r="K617" s="3" t="inlineStr">
@@ -36592,8 +36592,8 @@
       </c>
       <c r="D618" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNET_jitter --iface=eth0
-2. ls /tmp/dcat-rNET_jitter-eth0.sidecar 2&gt;&amp;1</t>
+          <t>1. dcat clean rNET_jitter --iface={iface}
+2. ls /tmp/dcat-rNET_jitter-{iface}.sidecar 2&gt;&amp;1</t>
         </is>
       </c>
       <c r="E618" s="3" t="inlineStr">
@@ -36624,7 +36624,7 @@
       </c>
       <c r="J618" s="3" t="inlineStr">
         <is>
-          <t>ls /tmp/dcat-rNET_jitter-eth0.sidecar 2&gt;&amp;1</t>
+          <t>ls /tmp/dcat-rNET_jitter-{iface}.sidecar 2&gt;&amp;1</t>
         </is>
       </c>
       <c r="K618" s="3" t="inlineStr">
@@ -36646,12 +36646,12 @@
       </c>
       <c r="C619" s="3" t="inlineStr">
         <is>
-          <t>已注入 rNET_bw_limit</t>
+          <t>已注入 rNET_bw_limit --iface={iface} --rate_kbps=1024</t>
         </is>
       </c>
       <c r="D619" s="3" t="inlineStr">
         <is>
-          <t>1. dcat query rNET_bw_limit --iface=eth0</t>
+          <t>1. dcat query rNET_bw_limit --iface={iface}</t>
         </is>
       </c>
       <c r="E619" s="3" t="inlineStr">
@@ -36682,7 +36682,7 @@
       </c>
       <c r="J619" s="3" t="inlineStr">
         <is>
-          <t>dcat query rNET_bw_limit --iface=eth0</t>
+          <t>dcat query rNET_bw_limit --iface={iface}</t>
         </is>
       </c>
       <c r="K619" s="3" t="inlineStr">
@@ -36709,8 +36709,8 @@
       </c>
       <c r="D620" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNET_bw_limit --iface=eth0
-2. ls /tmp/dcat-rNET_bw_limit-eth0.sidecar 2&gt;&amp;1</t>
+          <t>1. dcat clean rNET_bw_limit --iface={iface}
+2. ls /tmp/dcat-rNET_bw_limit-{iface}.sidecar 2&gt;&amp;1</t>
         </is>
       </c>
       <c r="E620" s="3" t="inlineStr">
@@ -36741,7 +36741,7 @@
       </c>
       <c r="J620" s="3" t="inlineStr">
         <is>
-          <t>ls /tmp/dcat-rNET_bw_limit-eth0.sidecar 2&gt;&amp;1</t>
+          <t>ls /tmp/dcat-rNET_bw_limit-{iface}.sidecar 2&gt;&amp;1</t>
         </is>
       </c>
       <c r="K620" s="3" t="inlineStr">

--- a/tests/e2e/testcases.xlsx
+++ b/tests/e2e/testcases.xlsx
@@ -21125,12 +21125,12 @@
       </c>
       <c r="D354" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_ip_change --chip={chip} --address=192.168.1.100 --netmask=255.255.255.0 --force</t>
+          <t>1. dcat inject rNPU_ip_change --chip={chip} --address=10.0.0.50 --netmask=255.255.255.0 --force</t>
         </is>
       </c>
       <c r="E354" s="3" t="inlineStr">
         <is>
-          <t>--chip=0 --address=192.168.1.100 --netmask=255.255.255.0 --force</t>
+          <t>--chip=0 --address=10.0.0.50 --netmask=255.255.255.0 --force</t>
         </is>
       </c>
       <c r="F354" s="3" t="inlineStr">
@@ -21162,7 +21162,7 @@
       </c>
       <c r="K354" s="3" t="inlineStr">
         <is>
-          <t>contains:192.168.1.100</t>
+          <t>contains:10.0.0.50</t>
         </is>
       </c>
     </row>
@@ -21184,7 +21184,7 @@
       </c>
       <c r="D355" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rNPU_ip_change --chip={chip} --address=192.168.1.100 --netmask=255.255.255.0
+          <t>1. 执行 dcat inject rNPU_ip_change --chip={chip} --address=10.0.0.50 --netmask=255.255.255.0
 2. 执行 dcat query rNPU_ip_change --chip={chip}
 3. 执行 dcat clean rNPU_ip_change --chip={chip}
 4. 模拟 sidecar 丢失后 clean 验证缺省值</t>
@@ -21192,12 +21192,12 @@
       </c>
       <c r="E355" s="3" t="inlineStr">
         <is>
-          <t>chip=0；address=192.168.1.100；netmask=255.255.255.0</t>
+          <t>chip=0；address=10.0.0.50；netmask=255.255.255.0</t>
         </is>
       </c>
       <c r="F355" s="3" t="inlineStr">
         <is>
-          <t>1. 先 -ip -g 取原值存 sidecar，再 -ip -s address 192.168.1.100 netmask 255.255.255.0
+          <t>1. 先 -ip -g 取原值存 sidecar，再 -ip -s address 10.0.0.50 netmask 255.255.255.0
 2. query 比对当前 IP 与原值不同则 confirmed:true
 3. clean 从 sidecar 还原原 IP
 4. sidecar 丢失则恢复为缺省 0.0.0.0/255.255.255.0</t>
@@ -21225,7 +21225,7 @@
       </c>
       <c r="K355" s="3" t="inlineStr">
         <is>
-          <t>contains:192.168.1.100</t>
+          <t>contains:10.0.0.50</t>
         </is>
       </c>
     </row>
@@ -21304,7 +21304,7 @@
       </c>
       <c r="D357" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_ip_change --chip=-1 --address=192.168.1.100 --netmask=255.255.255.0</t>
+          <t>1. dcat inject rNPU_ip_change --chip=-1 --address=10.0.0.50 --netmask=255.255.255.0</t>
         </is>
       </c>
       <c r="E357" s="3" t="inlineStr">
@@ -21361,7 +21361,7 @@
       </c>
       <c r="D358" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_ip_change --chip=8 --address=192.168.1.100 --netmask=255.255.255.0</t>
+          <t>1. dcat inject rNPU_ip_change --chip=8 --address=10.0.0.50 --netmask=255.255.255.0</t>
         </is>
       </c>
       <c r="E358" s="3" t="inlineStr">
@@ -21418,7 +21418,7 @@
       </c>
       <c r="D359" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_ip_change --chip={chip} --address=192.168.1.100 --netmask=255.255.255.0
+          <t>1. dcat clean rNPU_ip_change --chip={chip} --address=10.0.0.50 --netmask=255.255.255.0
 2. dcat query（无 uid）</t>
         </is>
       </c>
@@ -21477,13 +21477,13 @@
       </c>
       <c r="D360" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_ip_change --chip={chip} --address=192.168.1.100 --netmask=255.255.255.0
+          <t>1. dcat clean rNPU_ip_change --chip={chip} --address=10.0.0.50 --netmask=255.255.255.0
 2. 检查恢复状态</t>
         </is>
       </c>
       <c r="E360" s="3" t="inlineStr">
         <is>
-          <t>--chip=0 --address=192.168.1.100 --netmask=255.255.255.0</t>
+          <t>--chip=0 --address=10.0.0.50 --netmask=255.255.255.0</t>
         </is>
       </c>
       <c r="F360" s="3" t="inlineStr">
@@ -21514,7 +21514,7 @@
       </c>
       <c r="K360" s="3" t="inlineStr">
         <is>
-          <t>notcontains:192.168.1.100</t>
+          <t>notcontains:10.0.0.50</t>
         </is>
       </c>
     </row>
@@ -21594,12 +21594,12 @@
       </c>
       <c r="D362" s="3" t="inlineStr">
         <is>
-          <t>1. dcat query rNPU_ip_change --chip={chip} --address=192.168.1.100 --netmask=255.255.255.0</t>
+          <t>1. dcat query rNPU_ip_change --chip={chip} --address=10.0.0.50 --netmask=255.255.255.0</t>
         </is>
       </c>
       <c r="E362" s="3" t="inlineStr">
         <is>
-          <t>--chip=0 --address=192.168.1.100 --netmask=255.255.255.0</t>
+          <t>--chip=0 --address=10.0.0.50 --netmask=255.255.255.0</t>
         </is>
       </c>
       <c r="F362" s="3" t="inlineStr">
@@ -21652,13 +21652,13 @@
       </c>
       <c r="D363" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_ip_change --chip={chip} --address=192.168.1.100 --netmask=255.255.255.0
-2. 再次 dcat inject rNPU_ip_change --chip={chip} --address=192.168.1.100 --netmask=255.255.255.0</t>
+          <t>1. dcat inject rNPU_ip_change --chip={chip} --address=10.0.0.50 --netmask=255.255.255.0
+2. 再次 dcat inject rNPU_ip_change --chip={chip} --address=10.0.0.50 --netmask=255.255.255.0</t>
         </is>
       </c>
       <c r="E363" s="3" t="inlineStr">
         <is>
-          <t>--chip=0 --address=192.168.1.100 --netmask=255.255.255.0</t>
+          <t>--chip=0 --address=10.0.0.50 --netmask=255.255.255.0</t>
         </is>
       </c>
       <c r="F363" s="3" t="inlineStr">
@@ -21769,13 +21769,13 @@
       </c>
       <c r="D365" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_ip_change --chip={chip} --address=192.168.1.100 --netmask=255.255.255.0
+          <t>1. dcat inject rNPU_ip_change --chip={chip} --address=10.0.0.50 --netmask=255.255.255.0
 2. 检查注入状态</t>
         </is>
       </c>
       <c r="E365" s="3" t="inlineStr">
         <is>
-          <t>--chip=0 --address=192.168.1.100 --netmask=255.255.255.0</t>
+          <t>--chip=0 --address=10.0.0.50 --netmask=255.255.255.0</t>
         </is>
       </c>
       <c r="F365" s="3" t="inlineStr">
@@ -21806,7 +21806,7 @@
       </c>
       <c r="K365" s="3" t="inlineStr">
         <is>
-          <t>contains:192.168.1.100</t>
+          <t>contains:10.0.0.50</t>
         </is>
       </c>
     </row>
@@ -21828,15 +21828,15 @@
       </c>
       <c r="D366" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_ip_change --chip={chip} --address=192.168.1.100 --netmask=255.255.255.0
+          <t>1. dcat inject rNPU_ip_change --chip={chip} --address=10.0.0.50 --netmask=255.255.255.0
 2. dcat query rNPU_ip_change
-3. dcat clean rNPU_ip_change --chip={chip} --address=192.168.1.100 --netmask=255.255.255.0
+3. dcat clean rNPU_ip_change --chip={chip} --address=10.0.0.50 --netmask=255.255.255.0
 4. dcat query rNPU_ip_change</t>
         </is>
       </c>
       <c r="E366" s="3" t="inlineStr">
         <is>
-          <t>--chip=0 --address=192.168.1.100 --netmask=255.255.255.0</t>
+          <t>--chip=0 --address=10.0.0.50 --netmask=255.255.255.0</t>
         </is>
       </c>
       <c r="F366" s="3" t="inlineStr">
@@ -21891,13 +21891,13 @@
       </c>
       <c r="D367" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_ip_change --chip={chip} --address=192.168.1.100 --netmask=255.255.255.0
-2. 再次 dcat clean rNPU_ip_change --chip={chip} --address=192.168.1.100 --netmask=255.255.255.0</t>
+          <t>1. dcat clean rNPU_ip_change --chip={chip} --address=10.0.0.50 --netmask=255.255.255.0
+2. 再次 dcat clean rNPU_ip_change --chip={chip} --address=10.0.0.50 --netmask=255.255.255.0</t>
         </is>
       </c>
       <c r="E367" s="3" t="inlineStr">
         <is>
-          <t>--chip=0 --address=192.168.1.100 --netmask=255.255.255.0</t>
+          <t>--chip=0 --address=10.0.0.50 --netmask=255.255.255.0</t>
         </is>
       </c>
       <c r="F367" s="3" t="inlineStr">
@@ -37119,12 +37119,12 @@
       </c>
       <c r="D627" s="3" t="inlineStr">
         <is>
-          <t>1. dcat query rNPU_ip_change --chip={chip} --address=192.168.1.100 --netmask=255.255.255.0</t>
+          <t>1. dcat query rNPU_ip_change --chip={chip} --address=10.0.0.50 --netmask=255.255.255.0</t>
         </is>
       </c>
       <c r="E627" s="3" t="inlineStr">
         <is>
-          <t>chip=0；address=192.168.1.100；netmask=255.255.255.0</t>
+          <t>chip=0；address=10.0.0.50；netmask=255.255.255.0</t>
         </is>
       </c>
       <c r="F627" s="3" t="inlineStr">
@@ -37177,13 +37177,13 @@
       </c>
       <c r="D628" s="3" t="inlineStr">
         <is>
-          <t>1. dcat clean rNPU_ip_change --chip={chip} --address=192.168.1.100 --netmask=255.255.255.0
+          <t>1. dcat clean rNPU_ip_change --chip={chip} --address=10.0.0.50 --netmask=255.255.255.0
 2. hccn_tool -i {chip} -ip -g</t>
         </is>
       </c>
       <c r="E628" s="3" t="inlineStr">
         <is>
-          <t>chip=0；address=192.168.1.100；netmask=255.255.255.0</t>
+          <t>chip=0；address=10.0.0.50；netmask=255.255.255.0</t>
         </is>
       </c>
       <c r="F628" s="3" t="inlineStr">
@@ -37214,7 +37214,7 @@
       </c>
       <c r="K628" s="3" t="inlineStr">
         <is>
-          <t>notcontains:192.168.1.100</t>
+          <t>notcontains:10.0.0.50</t>
         </is>
       </c>
     </row>

--- a/tests/e2e/testcases.xlsx
+++ b/tests/e2e/testcases.xlsx
@@ -15854,7 +15854,7 @@
       </c>
       <c r="K263" s="3" t="inlineStr">
         <is>
-          <t>status:ok</t>
+          <t>exitcode:0</t>
         </is>
       </c>
     </row>
@@ -16253,12 +16253,12 @@
       <c r="I270" s="3" t="inlineStr"/>
       <c r="J270" s="3" t="inlineStr">
         <is>
-          <t>（注入被拒绝，未生效，无系统观测）</t>
+          <t>hccn_tool -i {chip} -arp -g 2&gt;/dev/null</t>
         </is>
       </c>
       <c r="K270" s="3" t="inlineStr">
         <is>
-          <t>exitcode:1</t>
+          <t>contains:10.30.12.200</t>
         </is>
       </c>
     </row>
@@ -16280,7 +16280,7 @@
       </c>
       <c r="D271" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rNPU_arp --chip={chip} --dev={dev} --ip=10.30.12.200
+          <t>1. 执行 dcat inject rNPU_arp --chip={chip} --dev={dev} --ip=10.30.12.200 --mac=00:11:22:33:44:55
 2. 检查 sidecar 与 query</t>
         </is>
       </c>
@@ -16454,7 +16454,7 @@
       </c>
       <c r="D274" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_arp --chip={chip} --dev={dev} --ip=10.30.12.200
+          <t>1. dcat inject rNPU_arp --chip={chip} --dev={dev} --ip=10.30.12.200 --mac=00:11:22:33:44:55
 2. 检查注入状态</t>
         </is>
       </c>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="D275" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_arp --chip={chip} --dev={dev} --ip=10.30.12.200
+          <t>1. dcat inject rNPU_arp --chip={chip} --dev={dev} --ip=10.30.12.200 --mac=00:11:22:33:44:55
 2. dcat query rNPU_arp
 3. dcat clean rNPU_arp --chip={chip} --dev={dev} --ip=10.30.12.200
 4. dcat query rNPU_arp</t>
@@ -17862,8 +17862,7 @@
       </c>
       <c r="D298" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rNPU_bw_limit --chip={chip} --bw_limit=0
-2. 执行 dcat inject rNPU_bw_limit --chip={chip} --bw_limit=-1</t>
+          <t>1. dcat clean rNPU_bw_limit（无参，防残留） | 2. 执行 dcat inject rNPU_bw_limit --chip={chip} --bw_limit=0 | 3. 执行 dcat inject rNPU_bw_limit --chip={chip} --bw_limit=-1</t>
         </is>
       </c>
       <c r="E298" s="3" t="inlineStr">
@@ -20926,12 +20925,12 @@
       <c r="I350" s="3" t="inlineStr"/>
       <c r="J350" s="3" t="inlineStr">
         <is>
-          <t>（注入被拒绝，未生效，无系统观测）</t>
+          <t>hccn_tool -i {chip} -gateway -g 2&gt;/dev/null</t>
         </is>
       </c>
       <c r="K350" s="3" t="inlineStr">
         <is>
-          <t>exitcode:1</t>
+          <t>contains:10.0.0.1</t>
         </is>
       </c>
     </row>
@@ -21247,7 +21246,7 @@
       </c>
       <c r="D356" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_ip_change --chip={chip} --address=invalid --netmask=255.255.255.0</t>
+          <t>1. dcat clean rNPU_ip_change（无参，防残留） | 2. dcat inject rNPU_ip_change --chip={chip} --address=invalid --netmask=255.255.255.0</t>
         </is>
       </c>
       <c r="E356" s="3" t="inlineStr">
@@ -22355,7 +22354,7 @@
       </c>
       <c r="D375" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_iproute --chip={chip} --ip=10.30.50.0 --ip_mask=0 --via=10.0.0.254 --dev={dev} --table=100</t>
+          <t>1. dcat inject rNPU_iproute --chip={chip} --ip=0.0.0.0 --ip_mask=0 --via=10.0.0.254 --dev={dev} --table=100</t>
         </is>
       </c>
       <c r="E375" s="3" t="inlineStr">
@@ -22390,7 +22389,7 @@
       </c>
       <c r="K375" s="3" t="inlineStr">
         <is>
-          <t>contains:10.30.50.0</t>
+          <t>contains:default</t>
         </is>
       </c>
     </row>
@@ -27525,7 +27524,7 @@
       </c>
       <c r="D463" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_netdetect_change --chip={chip} --address=invalid</t>
+          <t>1. dcat clean rNPU_netdetect_change（无参，防残留） | 2. dcat inject rNPU_netdetect_change --chip={chip} --address=invalid</t>
         </is>
       </c>
       <c r="E463" s="3" t="inlineStr">
@@ -28466,7 +28465,7 @@
       </c>
       <c r="D479" s="3" t="inlineStr">
         <is>
-          <t>1. dcat inject rNPU_roce_port_change --chip={chip} --port=-1</t>
+          <t>1. dcat clean rNPU_roce_port_change（无参，防残留） | 2. dcat inject rNPU_roce_port_change --chip={chip} --port=-1</t>
         </is>
       </c>
       <c r="E479" s="3" t="inlineStr">
@@ -33869,8 +33868,7 @@
       </c>
       <c r="D571" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat inject rNPU_arp --chip=2 --dev=eth2 --ip=10.30.12.200 --mac=00:11:22:33:44:55
-2. 捕获 stderr 检查是否含 MAC 等敏感参数</t>
+          <t>1. 执行 dcat inject rNPU_arp --chip={chip} --dev={dev} --ip=10.30.12.200 --mac=00:11:22:33:44:55 | 2. 捕获 stderr 检查是否含 MAC 等敏感参数</t>
         </is>
       </c>
       <c r="E571" s="3" t="inlineStr">

--- a/tests/e2e/testcases.xlsx
+++ b/tests/e2e/testcases.xlsx
@@ -13137,18 +13137,17 @@
       </c>
       <c r="C217" s="3" t="inlineStr">
         <is>
-          <t>已以 direction=in 注入（仅 INPUT 规则）</t>
+          <t>已注入 rNET_tcp_loss --port=18080 --direction=in（仅 INPUT 规则）</t>
         </is>
       </c>
       <c r="D217" s="3" t="inlineStr">
         <is>
-          <t>1. 执行 dcat query rNET_tcp_loss --port=8080 --direction=out
-2. 检查 confirmed 与退出码</t>
+          <t>1. 执行 dcat query rNET_tcp_loss --port=18080 --direction=out</t>
         </is>
       </c>
       <c r="E217" s="3" t="inlineStr">
         <is>
-          <t>port=8080；query direction=out</t>
+          <t>前置已注入 port=18080 direction=in；query direction=out 不应匹配</t>
         </is>
       </c>
       <c r="F217" s="3" t="inlineStr">
@@ -13177,7 +13176,7 @@
       </c>
       <c r="K217" s="3" t="inlineStr">
         <is>
-          <t>state_contains:&lt;uid&gt;</t>
+          <t>state_not_contains:&lt;uid&gt;</t>
         </is>
       </c>
     </row>
